--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>22681</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>13.3400001525879</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>13.1599998474121</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>8990</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>13.1599998474121</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>13.1199998855591</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>12.960000038147</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>3796</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>12.7600002288818</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>12.9399995803833</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>13.039999961853</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>18533</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>13.0200004577637</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>13.0799999237061</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>13.039999961853</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>14910</v>
+        <v>11101</v>
       </c>
       <c r="C2715" t="n">
-        <v>12.1999998092651</v>
+        <v>12.2600002288818</v>
       </c>
       <c r="D2715" t="n">
-        <v>11.6999998092651</v>
+        <v>11.7200002670288</v>
       </c>
       <c r="E2715" t="n">
-        <v>11.6999998092651</v>
+        <v>12.2600002288818</v>
       </c>
       <c r="F2715" t="n">
-        <v>11.9200000762939</v>
+        <v>11.8599996566772</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>4181</v>
+        <v>14910</v>
       </c>
       <c r="C2716" t="n">
-        <v>12.1400003433228</v>
+        <v>12.1999998092651</v>
       </c>
       <c r="D2716" t="n">
-        <v>11.7200002670288</v>
+        <v>11.6999998092651</v>
       </c>
       <c r="E2716" t="n">
-        <v>11.7200002670288</v>
+        <v>11.6999998092651</v>
       </c>
       <c r="F2716" t="n">
-        <v>12.1000003814697</v>
+        <v>11.9200000762939</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>17251</v>
+        <v>4181</v>
       </c>
       <c r="C2717" t="n">
-        <v>12.6800003051758</v>
+        <v>12.1400003433228</v>
       </c>
       <c r="D2717" t="n">
-        <v>11.960000038147</v>
+        <v>11.7200002670288</v>
       </c>
       <c r="E2717" t="n">
-        <v>11.960000038147</v>
+        <v>11.7200002670288</v>
       </c>
       <c r="F2717" t="n">
-        <v>12.6199998855591</v>
+        <v>12.1000003814697</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>17558</v>
+        <v>17251</v>
       </c>
       <c r="C2718" t="n">
-        <v>13</v>
+        <v>12.6800003051758</v>
       </c>
       <c r="D2718" t="n">
-        <v>12.5200004577637</v>
+        <v>11.960000038147</v>
       </c>
       <c r="E2718" t="n">
+        <v>11.960000038147</v>
+      </c>
+      <c r="F2718" t="n">
         <v>12.6199998855591</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>13</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>22681</v>
+        <v>17558</v>
       </c>
       <c r="C2719" t="n">
-        <v>13.3400001525879</v>
+        <v>13</v>
       </c>
       <c r="D2719" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>12.6199998855591</v>
+      </c>
+      <c r="F2719" t="n">
         <v>13</v>
-      </c>
-      <c r="E2719" t="n">
-        <v>13</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>13.1599998474121</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>8990</v>
+        <v>22681</v>
       </c>
       <c r="C2720" t="n">
+        <v>13.3400001525879</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2720" t="n">
         <v>13.1599998474121</v>
-      </c>
-      <c r="D2720" t="n">
-        <v>12.8999996185303</v>
-      </c>
-      <c r="E2720" t="n">
-        <v>13.1199998855591</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>12.960000038147</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>3796</v>
+        <v>8990</v>
       </c>
       <c r="C2721" t="n">
-        <v>13.1000003814697</v>
+        <v>13.1599998474121</v>
       </c>
       <c r="D2721" t="n">
-        <v>12.7600002288818</v>
+        <v>12.8999996185303</v>
       </c>
       <c r="E2721" t="n">
-        <v>12.9399995803833</v>
+        <v>13.1199998855591</v>
       </c>
       <c r="F2721" t="n">
-        <v>13.039999961853</v>
+        <v>12.960000038147</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>18533</v>
+        <v>3796</v>
       </c>
       <c r="C2722" t="n">
-        <v>13.3000001907349</v>
+        <v>13.1000003814697</v>
       </c>
       <c r="D2722" t="n">
-        <v>13.0200004577637</v>
+        <v>12.7600002288818</v>
       </c>
       <c r="E2722" t="n">
-        <v>13.0799999237061</v>
+        <v>12.9399995803833</v>
       </c>
       <c r="F2722" t="n">
         <v>13.039999961853</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>7191</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>13.1400003433228</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>12.7799997329712</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>12.9200000762939</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>6.84846591949463</v>
+        <v>6.84846544265747</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455717086792</v>
+        <v>6.71455669403076</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44674015045166</v>
+        <v>6.4467396736145</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544902801514</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.33196067810059</v>
+        <v>6.3319616317749</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544902801514</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546102523804</v>
+        <v>5.70546054840088</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>5.71502542495728</v>
+        <v>5.71502590179443</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31329965591431</v>
+        <v>5.31330060958862</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84415245056152</v>
+        <v>5.84415197372437</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937250137329</v>
+        <v>5.72937297821045</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935041427612</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458293914795</v>
+        <v>5.94458389282227</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1884880065918</v>
+        <v>6.18848752975464</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7006778717041</v>
+        <v>5.70067882537842</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244829177856</v>
+        <v>4.78244781494141</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>4.87331438064575</v>
+        <v>4.87331485748291</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5954647064209</v>
+        <v>5.59546422958374</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677328109741</v>
+        <v>5.45677375793457</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460870742798</v>
+        <v>5.17460918426514</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>5.23678016662598</v>
+        <v>5.23678112030029</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069259643555</v>
+        <v>5.26069307327271</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.97374582290649</v>
+        <v>4.97374677658081</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028051376343</v>
+        <v>4.61028003692627</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984491348267</v>
+        <v>4.61984539031982</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732414245605</v>
+        <v>4.58732461929321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985275268555</v>
+        <v>4.39985227584839</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.59200000762939</v>
       </c>
       <c r="G58" t="n">
-        <v>4.39219999313354</v>
+        <v>4.39220094680786</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.2391619682312</v>
+        <v>4.23916244506836</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>4.0937762260437</v>
+        <v>4.09377574920654</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916885375977</v>
+        <v>4.01916980743408</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793968200684</v>
+        <v>4.39793920516968</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202053070068</v>
+        <v>4.57202100753784</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871948242188</v>
+        <v>4.46871995925903</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265055656433</v>
+        <v>3.94265079498291</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726386070251</v>
+        <v>3.79726409912109</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987460136414</v>
+        <v>3.73987436294556</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813410758972</v>
+        <v>3.77813386917114</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723096847534</v>
+        <v>4.78723049163818</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851793289185</v>
+        <v>5.30851745605469</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.05504751205444</v>
+        <v>5.0550479888916</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417774200439</v>
+        <v>5.07417726516724</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653650283813</v>
+        <v>4.73653697967529</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680641174316</v>
+        <v>4.46680688858032</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>4.22768449783325</v>
+        <v>4.22768402099609</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559885025024</v>
+        <v>4.18559837341309</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942451477051</v>
+        <v>4.18942499160767</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550840377808</v>
+        <v>4.27550888061523</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16072988510132</v>
+        <v>4.16072940826416</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603349685669</v>
+        <v>4.17603397369385</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157020568848</v>
+        <v>5.02157068252563</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113876342773</v>
+        <v>4.92113924026489</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G103" t="n">
-        <v>4.95939874649048</v>
+        <v>4.95939922332764</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548358917236</v>
+        <v>5.04548311233521</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756622314453</v>
+        <v>7.74756574630737</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367635726929</v>
+        <v>7.06367588043213</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237419128418</v>
+        <v>6.98237466812134</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.38456869125366</v>
+        <v>6.3845682144165</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718215942383</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718215942383</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>5.87762928009033</v>
+        <v>5.87762880325317</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370901107788</v>
+        <v>6.07370948791504</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325132369995</v>
+        <v>6.74325180053711</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195379257202</v>
+        <v>6.55195426940918</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.06892681121826</v>
+        <v>6.0689263343811</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83936882019043</v>
+        <v>5.83936929702759</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.625</v>
       </c>
       <c r="G128" t="n">
-        <v>6.33674335479736</v>
+        <v>6.33674383163452</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.35109043121338</v>
+        <v>6.3510913848877</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.35109043121338</v>
+        <v>6.3510913848877</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935041427612</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370901107788</v>
+        <v>6.07370948791504</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805240631104</v>
+        <v>6.19805288314819</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>6.63803768157959</v>
+        <v>6.63803815841675</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>7.05889368057251</v>
+        <v>7.05889415740967</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>6.95846223831177</v>
+        <v>6.95846176147461</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>6.9967212677002</v>
+        <v>6.99672174453735</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75281715393066</v>
+        <v>6.75281667709351</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>6.95367956161499</v>
+        <v>6.95368003845215</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.33627557754517</v>
+        <v>7.33627605438232</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.9388632774353</v>
+        <v>7.93886375427246</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91017055511475</v>
+        <v>7.91017007827759</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>7.84321546554565</v>
+        <v>7.8432149887085</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234474182129</v>
+        <v>7.86234426498413</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626037597656</v>
+        <v>7.77626085281372</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712278366089</v>
+        <v>7.97712469100952</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451347351074</v>
+        <v>8.03451251983643</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.8336501121521</v>
+        <v>7.83364963531494</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103984832764</v>
+        <v>7.89103937149048</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492603302002</v>
+        <v>8.68492698669434</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622772216797</v>
+        <v>8.76622676849365</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65622997283936</v>
+        <v>8.6562328338623</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G179" t="n">
-        <v>8.35015296936035</v>
+        <v>8.35015392303467</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.17798614501953</v>
+        <v>8.17798519134521</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>8.20668029785156</v>
+        <v>8.20668125152588</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451620101929</v>
+        <v>7.92451667785645</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581195831299</v>
+        <v>8.22581100463867</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34059047698975</v>
+        <v>8.34058952331543</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.27363395690918</v>
+        <v>8.2736349105835</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101680755615</v>
+        <v>8.55101776123047</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968982696533</v>
+        <v>9.23969078063965</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317497253418</v>
+        <v>9.05317401885986</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708324432373</v>
+        <v>9.18708229064941</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882789611816</v>
+        <v>9.03882598876953</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.13447666168213</v>
+        <v>9.13447570800781</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.17273616790771</v>
+        <v>9.1727352142334</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>9.51707172393799</v>
+        <v>9.5170726776123</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587827682495</v>
+        <v>10.3587837219238</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>10.473560333252</v>
+        <v>10.4735622406006</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>11.1813640594482</v>
+        <v>11.1813650131226</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1813640594482</v>
+        <v>11.1813650131226</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G215" t="n">
-        <v>11.200493812561</v>
+        <v>11.2004928588867</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831266403198</v>
+        <v>10.4831275939941</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370275497437</v>
+        <v>10.8370265960693</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.961371421814</v>
+        <v>10.9613704681396</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.1144104003906</v>
+        <v>11.1144094467163</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630971908569</v>
+        <v>11.3630962371826</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117839813232</v>
+        <v>11.6117858886719</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G227" t="n">
-        <v>11.5639600753784</v>
+        <v>11.5639591217041</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456922531128</v>
+        <v>11.7456932067871</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648229598999</v>
+        <v>11.7648220062256</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G230" t="n">
-        <v>11.6309146881104</v>
+        <v>11.630913734436</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708990097046</v>
+        <v>12.0708980560303</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961048126221</v>
+        <v>12.3961057662964</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474180221558</v>
+        <v>12.1474189758301</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.25</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7169981002808</v>
+        <v>11.7169990539551</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839508056641</v>
+        <v>11.7839517593384</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G239" t="n">
-        <v>12.4247999191284</v>
+        <v>12.4248008728027</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717250823975</v>
+        <v>13.3717260360718</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446575164795</v>
+        <v>15.2446565628052</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8132295608521</v>
+        <v>12.8132305145264</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G256" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G264" t="n">
-        <v>14.1061315536499</v>
+        <v>14.1061305999756</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973794937134</v>
+        <v>13.7973804473877</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044082641602</v>
+        <v>13.6044092178345</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>13.8359727859497</v>
+        <v>13.835973739624</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869714736938</v>
+        <v>11.8869724273682</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>11.8676767349243</v>
+        <v>11.86767578125</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063383102417</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>10.680908203125</v>
+        <v>10.6809072494507</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.7291507720947</v>
+        <v>10.729151725769</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431409835815</v>
+        <v>11.4431400299072</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738794326782</v>
+        <v>10.8738803863525</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.008957862854</v>
+        <v>11.0089588165283</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695356369019</v>
+        <v>10.1695375442505</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273591995239</v>
+        <v>11.3273582458496</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G303" t="n">
-        <v>11.7132997512817</v>
+        <v>11.7133007049561</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212247848511</v>
+        <v>11.2212257385254</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054430007935</v>
+        <v>11.1054439544678</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>11.5299777984619</v>
+        <v>11.5299787521362</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334926605225</v>
+        <v>11.4334936141968</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220527648926</v>
+        <v>12.0220518112183</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G320" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>12.0027542114258</v>
+        <v>12.0027551651001</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G322" t="n">
-        <v>12.0027542114258</v>
+        <v>12.0027551651001</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387308120728</v>
+        <v>11.8387317657471</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>11.915919303894</v>
+        <v>11.9159183502197</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044082641602</v>
+        <v>13.6044092178345</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.710542678833</v>
+        <v>13.7105436325073</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552713394165</v>
+        <v>13.8552694320679</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807004928589</v>
+        <v>13.9806995391846</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>14.75</v>
       </c>
       <c r="G341" t="n">
-        <v>14.2315635681152</v>
+        <v>14.2315626144409</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.4920721054077</v>
+        <v>14.492073059082</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G345" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G347" t="n">
-        <v>14.5789089202881</v>
+        <v>14.5789098739624</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.405237197876</v>
+        <v>14.4052362442017</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G352" t="n">
-        <v>13.0158491134644</v>
+        <v>13.01584815979</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527210235596</v>
+        <v>12.5527219772339</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386606216431</v>
+        <v>12.9386615753174</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.8807706832886</v>
+        <v>12.8807697296143</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G357" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.0062007904053</v>
+        <v>13.006199836731</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447950363159</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G366" t="n">
-        <v>12.7939348220825</v>
+        <v>12.7939338684082</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4272899627686</v>
+        <v>12.4272890090942</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>11.9641609191895</v>
+        <v>11.9641618728638</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150220870972</v>
+        <v>12.2150230407715</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474838256836</v>
+        <v>12.147481918335</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185369491577</v>
+        <v>12.1185388565063</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325973510742</v>
+        <v>11.7325963973999</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>12.2536163330078</v>
+        <v>12.2536172866821</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>11.9641609191895</v>
+        <v>11.9641618728638</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545135498047</v>
+        <v>11.9545125961304</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.2439680099487</v>
+        <v>12.243968963623</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G398" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G399" t="n">
-        <v>12.7939348220825</v>
+        <v>12.7939338684082</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228788375854</v>
+        <v>12.8228797912598</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447950363159</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G416" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193649291992</v>
+        <v>12.9193639755249</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>13.0544424057007</v>
+        <v>13.054443359375</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>12.8904190063477</v>
+        <v>12.8904180526733</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>12.8807706832886</v>
+        <v>12.8807697296143</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>13.2184677124023</v>
+        <v>13.2184686660767</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>13.2860088348389</v>
+        <v>13.2860078811646</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G436" t="n">
-        <v>13.2088193893433</v>
+        <v>13.2088203430176</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974477767944</v>
+        <v>12.6974487304688</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>12.6395578384399</v>
+        <v>12.6395568847656</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13</v>
       </c>
       <c r="G444" t="n">
-        <v>12.5430717468262</v>
+        <v>12.5430727005005</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3693981170654</v>
+        <v>12.3693990707397</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.8676767349243</v>
+        <v>11.86767578125</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>12.2536163330078</v>
+        <v>12.2536172866821</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1860780715942</v>
+        <v>12.1860771179199</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>12.1764287948608</v>
+        <v>12.1764278411865</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>12.0895910263062</v>
+        <v>12.0895919799805</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185369491577</v>
+        <v>12.1185388565063</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G472" t="n">
-        <v>12.1764287948608</v>
+        <v>12.1764278411865</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554733276367</v>
+        <v>9.45554828643799</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816593170166</v>
+        <v>9.65816497802734</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625078201294</v>
+        <v>10.3625068664551</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107494354248</v>
+        <v>10.4107503890991</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>10.4203987121582</v>
+        <v>10.4203996658325</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063383102417</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764980316162</v>
+        <v>11.0764970779419</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.7195014953613</v>
+        <v>10.7195024490356</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G491" t="n">
-        <v>11.2791166305542</v>
+        <v>11.2791175842285</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>10.9028253555298</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G494" t="n">
-        <v>10.9028253555298</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G496" t="n">
-        <v>10.9028253555298</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7388000488281</v>
+        <v>10.7387990951538</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>10.8545827865601</v>
+        <v>10.8545818328857</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078971862793</v>
+        <v>10.7078981399536</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189531326294</v>
+        <v>10.2189521789551</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612144470215</v>
+        <v>10.5612154006958</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025415420532</v>
+        <v>10.5025405883789</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763519287109</v>
+        <v>10.7763509750366</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763519287109</v>
+        <v>10.7763509750366</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G521" t="n">
-        <v>10.8545827865601</v>
+        <v>10.8545818328857</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>10.9328126907349</v>
+        <v>10.9328136444092</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.9523706436157</v>
+        <v>10.9523696899414</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G529" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634256362915</v>
+        <v>10.4634246826172</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069620132446</v>
+        <v>10.3069639205933</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261028289795</v>
+        <v>9.17261123657227</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509357452393</v>
+        <v>9.50509262084961</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619869232178</v>
+        <v>9.45619964599609</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G551" t="n">
-        <v>9.20194816589355</v>
+        <v>9.20194721221924</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G556" t="n">
-        <v>8.53698062896729</v>
+        <v>8.5369815826416</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.8499059677124</v>
+        <v>8.84990692138672</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>10.5</v>
       </c>
       <c r="G572" t="n">
-        <v>10.2678470611572</v>
+        <v>10.2678480148315</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G577" t="n">
-        <v>9.20194816589355</v>
+        <v>9.20194721221924</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>9.2215051651001</v>
+        <v>9.22150421142578</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>8.94769477844238</v>
+        <v>8.9476957321167</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9</v>
       </c>
       <c r="G588" t="n">
-        <v>8.80101299285889</v>
+        <v>8.80101203918457</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211811065674</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.99659061431885</v>
+        <v>8.99658966064453</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492267608643</v>
+        <v>9.95492362976074</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.75</v>
       </c>
       <c r="G605" t="n">
-        <v>9.53443050384521</v>
+        <v>9.5344295501709</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G623" t="n">
-        <v>10.0918273925781</v>
+        <v>10.0918264389038</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>9.69089126586914</v>
+        <v>9.69089221954346</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354545593262</v>
+        <v>9.57354640960693</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>9.13349437713623</v>
+        <v>9.13349533081055</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835975646973</v>
+        <v>8.91835880279541</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>8.99659061431885</v>
+        <v>8.99658966064453</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52464962005615</v>
+        <v>9.52465057373047</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376552581787</v>
+        <v>9.56376647949219</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G656" t="n">
-        <v>9.2215051651001</v>
+        <v>9.22150421142578</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437942504883</v>
+        <v>9.09437847137451</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956607818604</v>
+        <v>9.74956512451172</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>9.75</v>
       </c>
       <c r="G689" t="n">
-        <v>9.53443050384521</v>
+        <v>9.5344295501709</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575664520264</v>
+        <v>9.47575569152832</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211811065674</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G711" t="n">
-        <v>8.34140300750732</v>
+        <v>8.34140396118164</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560436248779</v>
+        <v>8.15560531616211</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211811065674</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G716" t="n">
-        <v>8.34140300750732</v>
+        <v>8.34140396118164</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626934051514</v>
+        <v>8.12626838684082</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G719" t="n">
-        <v>8.22405624389648</v>
+        <v>8.2240571975708</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742458343506</v>
+        <v>8.51742362976074</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G722" t="n">
-        <v>8.73255920410156</v>
+        <v>8.73256015777588</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.6347713470459</v>
+        <v>8.63477039337158</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9</v>
       </c>
       <c r="G725" t="n">
-        <v>8.80101299285889</v>
+        <v>8.80101203918457</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902187347412</v>
+        <v>8.88902282714844</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G734" t="n">
-        <v>8.04803657531738</v>
+        <v>8.04803562164307</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262889862061</v>
+        <v>7.40262937545776</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>6.8647894859314</v>
+        <v>6.86478900909424</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>7.5</v>
       </c>
       <c r="G742" t="n">
-        <v>7.33417701721191</v>
+        <v>7.33417654037476</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.15815687179565</v>
+        <v>7.1581563949585</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385478973389</v>
+        <v>6.46385431289673</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G748" t="n">
-        <v>5.57397413253784</v>
+        <v>5.573974609375</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G749" t="n">
-        <v>5.32950210571289</v>
+        <v>5.32950162887573</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738567352295</v>
+        <v>4.31738519668579</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>4.29782772064209</v>
+        <v>4.29782819747925</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00935029983521</v>
+        <v>4.00934982299805</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156077384949</v>
+        <v>3.91156101226807</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.9800136089325</v>
+        <v>3.98001313209534</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669706344604</v>
+        <v>4.12669658660889</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630514144897</v>
+        <v>4.58630561828613</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502912521362</v>
+        <v>5.08502960205078</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055614471436</v>
+        <v>4.84055662155151</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>5.47618532180786</v>
+        <v>5.4761848449707</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.32950210571289</v>
+        <v>5.32950162887573</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G780" t="n">
-        <v>5.42729139328003</v>
+        <v>5.42729091644287</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G784" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928060531616</v>
+        <v>5.33928108215332</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.3001651763916</v>
+        <v>5.30016469955444</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.25</v>
       </c>
       <c r="G795" t="n">
-        <v>5.13392353057861</v>
+        <v>5.13392400741577</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171281814575</v>
+        <v>5.23171234130859</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>5.24149179458618</v>
+        <v>5.24149131774902</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215438842773</v>
+        <v>5.21215534210205</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166221618652</v>
+        <v>4.79166269302368</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.97746133804321</v>
+        <v>4.97746181488037</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>5.04591369628906</v>
+        <v>5.0459132194519</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>4.97746133804321</v>
+        <v>4.97746181488037</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>5.42729139328003</v>
+        <v>5.42729091644287</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220546722412</v>
+        <v>5.65220642089844</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>5.47618532180786</v>
+        <v>5.4761848449707</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441665649414</v>
+        <v>5.55441617965698</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264751434326</v>
+        <v>5.63264799118042</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>5.71087884902954</v>
+        <v>5.7108793258667</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>6.4736328125</v>
+        <v>6.47363328933716</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004487991333</v>
+        <v>6.19004535675049</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402521133423</v>
+        <v>6.01402473449707</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G835" t="n">
-        <v>6.06291913986206</v>
+        <v>6.06291961669922</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672857284546</v>
+        <v>6.33672904968262</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>6.48341274261475</v>
+        <v>6.48341226577759</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G840" t="n">
-        <v>6.73766374588013</v>
+        <v>6.73766326904297</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>6.43451738357544</v>
+        <v>6.4345178604126</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G843" t="n">
-        <v>6.48341274261475</v>
+        <v>6.48341226577759</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>6.09225654602051</v>
+        <v>6.09225606918335</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>6.41495943069458</v>
+        <v>6.41495990753174</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>6.08247661590576</v>
+        <v>6.08247709274292</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.14115047454834</v>
+        <v>6.14115142822266</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.00424575805664</v>
+        <v>6.0042462348938</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955223083496</v>
+        <v>5.76955270767212</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977373123169</v>
+        <v>5.75977325439453</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>5.60331106185913</v>
+        <v>5.60331058502197</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>5.82822561264038</v>
+        <v>5.82822608947754</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021577835083</v>
+        <v>5.74021530151367</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>5.66198444366455</v>
+        <v>5.66198396682739</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G868" t="n">
-        <v>5.57397413253784</v>
+        <v>5.573974609375</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>5.69132089614868</v>
+        <v>5.69132137298584</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G876" t="n">
-        <v>5.71087884902954</v>
+        <v>5.7108793258667</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>5.30994415283203</v>
+        <v>5.30994367599487</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G881" t="n">
-        <v>5.42729139328003</v>
+        <v>5.42729091644287</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>6.53230667114258</v>
+        <v>6.53230619430542</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>6.65943241119385</v>
+        <v>6.65943193435669</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G890" t="n">
-        <v>6.48341274261475</v>
+        <v>6.48341226577759</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987445831299</v>
+        <v>6.63987493515015</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G897" t="n">
-        <v>7.87201690673828</v>
+        <v>7.87201642990112</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96002721786499</v>
+        <v>7.96002626419067</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489116668701</v>
+        <v>7.74489068984985</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G900" t="n">
-        <v>7.72533321380615</v>
+        <v>7.72533273696899</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>7.62754392623901</v>
+        <v>7.62754440307617</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G902" t="n">
-        <v>7.62754392623901</v>
+        <v>7.62754440307617</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75466918945312</v>
+        <v>7.75466966629028</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G904" t="n">
-        <v>7.67643785476685</v>
+        <v>7.676438331604</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G905" t="n">
-        <v>7.73511123657227</v>
+        <v>7.73511171340942</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842849731445</v>
+        <v>7.58842802047729</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>7.39285039901733</v>
+        <v>7.39284992218018</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G908" t="n">
-        <v>7.64710187911987</v>
+        <v>7.64710140228271</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>7.41240835189819</v>
+        <v>7.41240787506104</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G910" t="n">
-        <v>6.95279932022095</v>
+        <v>6.95279979705811</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147270202637</v>
+        <v>7.01147317886353</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572418212891</v>
+        <v>7.26572465896606</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7</v>
       </c>
       <c r="G918" t="n">
-        <v>6.8452320098877</v>
+        <v>6.84523153305054</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412593841553</v>
+        <v>6.89412641525269</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191522598267</v>
+        <v>6.99191570281982</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218685150146</v>
+        <v>7.42218732833862</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G938" t="n">
-        <v>7.96002721786499</v>
+        <v>7.96002626419067</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312154769897</v>
+        <v>7.82312202453613</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G946" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G949" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>8.59565544128418</v>
+        <v>8.5956563949585</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897174835205</v>
+        <v>8.44897270202637</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37074089050293</v>
+        <v>8.37073993682861</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>8.22405624389648</v>
+        <v>8.2240571975708</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G961" t="n">
-        <v>8.16538333892822</v>
+        <v>8.16538429260254</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339412689209</v>
+        <v>8.25339317321777</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>8.45874977111816</v>
+        <v>8.45875072479248</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G970" t="n">
-        <v>8.16538333892822</v>
+        <v>8.16538429260254</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482051849365</v>
+        <v>9.07482147216797</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.4953145980835</v>
+        <v>9.49531364440918</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>9.24106311798096</v>
+        <v>9.24106216430664</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>9.74956607818604</v>
+        <v>9.74956512451172</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G979" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804315567017</v>
+        <v>11.4804306030273</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G987" t="n">
-        <v>12.4387636184692</v>
+        <v>12.4387645721436</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G990" t="n">
-        <v>12.947265625</v>
+        <v>12.9472665786743</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926742553711</v>
+        <v>13.5926733016968</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882518768311</v>
+        <v>13.7882528305054</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705633163452</v>
+        <v>14.5705642700195</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.3188648223877</v>
+        <v>13.3188638687134</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.0059404373169</v>
+        <v>13.0059413909912</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.2823009490967</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.1258382797241</v>
+        <v>12.1258392333984</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.9668254852295</v>
+        <v>12.9668245315552</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.5365524291992</v>
+        <v>12.5365533828735</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.3384237289429</v>
+        <v>13.3384227752686</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.8078107833862</v>
+        <v>13.8078098297119</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.5952262878418</v>
+        <v>12.5952253341675</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583215713501</v>
+        <v>12.4583206176758</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.2823009490967</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.2823009490967</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.715124130249</v>
+        <v>11.7151250839233</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.0476064682007</v>
+        <v>12.047607421875</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734571456909</v>
+        <v>12.6734580993652</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.184513092041</v>
+        <v>12.1845121383667</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.4192056655884</v>
+        <v>12.4192066192627</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409748077393</v>
+        <v>12.3409738540649</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.279748916626</v>
+        <v>13.2797498703003</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1057" t="n">
-        <v>10.5416574478149</v>
+        <v>10.5416564941406</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.209174156189</v>
+        <v>10.2091732025146</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025415420532</v>
+        <v>10.5025405883789</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.80101299285889</v>
+        <v>8.80101203918457</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206703186035</v>
+        <v>8.31206798553467</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543441772461</v>
+        <v>8.60543346405029</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570652008057</v>
+        <v>9.03570556640625</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.17261028289795</v>
+        <v>9.17261123657227</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0918273925781</v>
+        <v>10.0918264389038</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003303527832</v>
+        <v>10.6003293991089</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.9523706436157</v>
+        <v>10.9523696899414</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.181960105896</v>
+        <v>13.1819591522217</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1094" t="n">
-        <v>13.3775396347046</v>
+        <v>13.3775386810303</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882518768311</v>
+        <v>13.7882528305054</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1097" t="n">
-        <v>13.8078107833862</v>
+        <v>13.8078098297119</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1098" t="n">
-        <v>13.9055986404419</v>
+        <v>13.9055995941162</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>13.8273677825928</v>
+        <v>13.8273687362671</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771978378296</v>
+        <v>14.2771987915039</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>14.4532175064087</v>
+        <v>14.4532165527344</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030466079712</v>
+        <v>14.9030475616455</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.7074699401855</v>
+        <v>14.7074689865112</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>15</v>
       </c>
       <c r="G1107" t="n">
-        <v>14.6683540344238</v>
+        <v>14.6683530807495</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.6683540344238</v>
+        <v>14.6683530807495</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181831359863</v>
+        <v>15.1181840896606</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396114349365</v>
+        <v>15.9396104812622</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666488647461</v>
+        <v>19.1666507720947</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981067657471</v>
+        <v>22.1981086730957</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>21.1713218688965</v>
+        <v>21.1713237762451</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558464050293</v>
+        <v>21.8558483123779</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>21.3180084228516</v>
+        <v>21.3180065155029</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>20.6334857940674</v>
+        <v>20.6334838867188</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691116333008</v>
+        <v>21.2691135406494</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>21.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>20.7801666259766</v>
+        <v>20.7801685333252</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>21</v>
       </c>
       <c r="G1152" t="n">
-        <v>20.5356941223145</v>
+        <v>20.5356960296631</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0561008453369</v>
+        <v>24.0560989379883</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538906097412</v>
+        <v>24.1538887023926</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.322681427002</v>
+        <v>23.3226833343506</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7848434448242</v>
+        <v>22.7848415374756</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359485626221</v>
+        <v>22.7359504699707</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.2958965301514</v>
+        <v>22.2958984375</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1173" t="n">
-        <v>22.4425811767578</v>
+        <v>22.4425830841064</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.5892639160156</v>
+        <v>22.5892658233643</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.5403690338135</v>
+        <v>22.5403671264648</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157943725586</v>
+        <v>21.4157962799072</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>21.7091655731201</v>
+        <v>21.7091636657715</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>21.0735340118408</v>
+        <v>21.0735321044922</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113739013672</v>
+        <v>21.6113758087158</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>21.7091655731201</v>
+        <v>21.7091636657715</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>21.0735340118408</v>
+        <v>21.0735321044922</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>21.0735340118408</v>
+        <v>21.0735321044922</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.3180084228516</v>
+        <v>21.3180065155029</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>21.7091655731201</v>
+        <v>21.7091636657715</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.2958965301514</v>
+        <v>22.2958984375</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.926851272583</v>
+        <v>20.9268493652344</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401165008545</v>
+        <v>20.3401184082031</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470909118652</v>
+        <v>19.1470928192139</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.4038963317871</v>
+        <v>18.4038944244385</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.2669887542725</v>
+        <v>18.2669906616211</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1224" t="n">
-        <v>17.4651184082031</v>
+        <v>17.4651203155518</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1225" t="n">
-        <v>17.4651184082031</v>
+        <v>17.4651203155518</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521949768066</v>
+        <v>17.1521968841553</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.783148765564</v>
+        <v>15.7831478118896</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112087249756</v>
+        <v>16.3112106323242</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.9174995422363</v>
+        <v>16.917501449585</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348491668701</v>
+        <v>17.0348472595215</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>18</v>
       </c>
       <c r="G1237" t="n">
-        <v>17.6020259857178</v>
+        <v>17.6020240783691</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108688354492</v>
+        <v>17.2108669281006</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1240" t="n">
-        <v>17.0739612579346</v>
+        <v>17.0739631652832</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1241" t="n">
-        <v>17.054407119751</v>
+        <v>17.0544052124023</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.4038963317871</v>
+        <v>18.4038944244385</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1243" t="n">
-        <v>17.6411399841309</v>
+        <v>17.6411418914795</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042362213135</v>
+        <v>17.5042343139648</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979434967041</v>
+        <v>16.8979454040527</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521949768066</v>
+        <v>17.1521968841553</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.721923828125</v>
+        <v>16.7219219207764</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761753082275</v>
+        <v>16.9761734008789</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.721923828125</v>
+        <v>16.7219219207764</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414817810059</v>
+        <v>16.7414798736572</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>19.594820022583</v>
+        <v>19.5948181152344</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6342830657959</v>
+        <v>19.6342849731445</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>21.8542404174805</v>
+        <v>21.8542423248291</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.8542404174805</v>
+        <v>21.8542423248291</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.5750865936279</v>
+        <v>19.5750846862793</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>18.5687065124512</v>
+        <v>18.5687046051025</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.3777542114258</v>
+        <v>19.3777561187744</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1294" t="n">
-        <v>19.2988224029541</v>
+        <v>19.2988243103027</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>19.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>19.2396259307861</v>
+        <v>19.2396240234375</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.7132148742676</v>
+        <v>19.7132167816162</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.5089149475098</v>
+        <v>21.5089130401611</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>21.1635894775391</v>
+        <v>21.1635875701904</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.8182621002197</v>
+        <v>20.8182601928711</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.6737518310547</v>
+        <v>19.6737499237061</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.2988224029541</v>
+        <v>19.2988243103027</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.6145496368408</v>
+        <v>19.6145515441895</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>23.75</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.4328765869141</v>
+        <v>23.4328784942627</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>22.2982330322266</v>
+        <v>22.2982311248779</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>21.2622528076172</v>
+        <v>21.2622509002686</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>22.8902206420898</v>
+        <v>22.8902225494385</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1340" t="n">
-        <v>26.1856250762939</v>
+        <v>26.1856231689453</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1349" t="n">
-        <v>24.05446434021</v>
+        <v>24.0544624328613</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.4230098724365</v>
+        <v>23.4230117797852</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G1354" t="n">
-        <v>23.1467475891113</v>
+        <v>23.14674949646</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.7126235961914</v>
+        <v>22.71262550354</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.0086193084717</v>
+        <v>23.008617401123</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1361" t="n">
-        <v>23.5216751098633</v>
+        <v>23.5216770172119</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1365" t="n">
-        <v>24.6464519500732</v>
+        <v>24.6464538574219</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1373" t="n">
-        <v>24.9029808044434</v>
+        <v>24.902982711792</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>24.7648525238037</v>
+        <v>24.7648506164551</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1375" t="n">
-        <v>24.4096584320068</v>
+        <v>24.4096565246582</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1376" t="n">
-        <v>24.4293918609619</v>
+        <v>24.4293899536133</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1379" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.5872554779053</v>
+        <v>24.5872535705566</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.2250881195068</v>
+        <v>26.2250900268555</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1384" t="n">
-        <v>28.4351787567139</v>
+        <v>28.4351806640625</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1391" t="n">
-        <v>24.5872554779053</v>
+        <v>24.5872535705566</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1393" t="n">
-        <v>24.6267185211182</v>
+        <v>24.6267204284668</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>24.6069889068604</v>
+        <v>24.6069869995117</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>24.7253837585449</v>
+        <v>24.7253856658936</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>24.4688549041748</v>
+        <v>24.4688568115234</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>24.4293918609619</v>
+        <v>24.4293899536133</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>24.1531295776367</v>
+        <v>24.1531276702881</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>24.4688549041748</v>
+        <v>24.4688568115234</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1408" t="n">
-        <v>24.05446434021</v>
+        <v>24.0544624328613</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3899230957031</v>
+        <v>24.3899250030518</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.3307266235352</v>
+        <v>24.3307247161865</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.3440780639648</v>
+        <v>23.3440799713135</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.4230098724365</v>
+        <v>23.4230117797852</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>24.685920715332</v>
+        <v>24.6859188079834</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>26.3434886932373</v>
+        <v>26.3434867858887</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.0341396331787</v>
+        <v>27.0341415405273</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>28.4154472351074</v>
+        <v>28.4154453277588</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>29.6980895996094</v>
+        <v>29.6980876922607</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1446" t="n">
-        <v>29.7770214080811</v>
+        <v>29.7770195007324</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1448" t="n">
-        <v>30.3295440673828</v>
+        <v>30.3295421600342</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>30.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>30.0927486419678</v>
+        <v>30.0927467346191</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.4218273162842</v>
+        <v>29.4218254089355</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>30.4676723480225</v>
+        <v>30.4676742553711</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G1465" t="n">
-        <v>35.8547706604004</v>
+        <v>35.8547668457031</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>39.0712356567383</v>
+        <v>39.0712394714355</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1469" t="n">
-        <v>36.269157409668</v>
+        <v>36.2691612243652</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>40.3538818359375</v>
+        <v>40.3538856506348</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>42.6599998474121</v>
       </c>
       <c r="G1475" t="n">
-        <v>42.0903778076172</v>
+        <v>42.0903816223145</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>42.2482414245605</v>
+        <v>42.2482452392578</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1477" t="n">
-        <v>42.5837020874023</v>
+        <v>42.5837059020996</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>43.0178298950195</v>
+        <v>43.0178260803223</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>42.6231689453125</v>
+        <v>42.6231727600098</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>43</v>
       </c>
       <c r="G1480" t="n">
-        <v>42.425838470459</v>
+        <v>42.4258422851562</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.2615966796875</v>
+        <v>41.2615928649902</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>42.6399993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.0706443786621</v>
+        <v>42.0706481933594</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1492" t="n">
-        <v>45.5831108093262</v>
+        <v>45.5831146240234</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>38.4199981689453</v>
       </c>
       <c r="G1493" t="n">
-        <v>37.9069938659668</v>
+        <v>37.9069900512695</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1495" t="n">
-        <v>32.6185646057129</v>
+        <v>32.6185684204102</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1500" t="n">
-        <v>30.4676723480225</v>
+        <v>30.4676742553711</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>30.9215316772461</v>
+        <v>30.9215297698975</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1504" t="n">
-        <v>31.0201969146729</v>
+        <v>31.0201950073242</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>31.3951206207275</v>
+        <v>31.3951225280762</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1508" t="n">
-        <v>30.9215316772461</v>
+        <v>30.9215297698975</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>12.7200002670288</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>19351</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>12.7799997329712</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>12.3800001144409</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>12.5600004196167</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>6.84846544265747</v>
+        <v>6.84846591949463</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455669403076</v>
+        <v>6.71455717086792</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4850001335144</v>
+        <v>6.48499965667725</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>6.27935457229614</v>
+        <v>6.2793550491333</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>6.06414461135864</v>
+        <v>6.06414413452148</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31330060958862</v>
+        <v>5.31330013275146</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.74850273132324</v>
+        <v>5.7485032081604</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937297821045</v>
+        <v>5.72937250137329</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.0258846282959</v>
+        <v>6.02588510513306</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935041427612</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>6.18848752975464</v>
+        <v>6.1884880065918</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414781570435</v>
+        <v>5.95414733886719</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154443740845</v>
+        <v>5.79154491424561</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.70067882537842</v>
+        <v>5.7006778717041</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244781494141</v>
+        <v>4.78244829177856</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>4.87331485748291</v>
+        <v>4.87331438064575</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.06461238861084</v>
+        <v>5.064612865448</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.59546422958374</v>
+        <v>5.5954647064209</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.32286500930786</v>
+        <v>5.3228645324707</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.29416990280151</v>
+        <v>5.29417037963867</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460918426514</v>
+        <v>5.17460870742798</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>5.23678112030029</v>
+        <v>5.23678064346313</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.97374677658081</v>
+        <v>4.97374629974365</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G45" t="n">
-        <v>4.68297338485718</v>
+        <v>4.68297290802002</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028003692627</v>
+        <v>4.61028051376343</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>4.63897466659546</v>
+        <v>4.6389741897583</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984539031982</v>
+        <v>4.61984491348267</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732461929321</v>
+        <v>4.58732414245605</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40559148788452</v>
+        <v>4.40559101104736</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.59200000762939</v>
       </c>
       <c r="G58" t="n">
-        <v>4.39220094680786</v>
+        <v>4.3922004699707</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.23916244506836</v>
+        <v>4.2391619682312</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202100753784</v>
+        <v>4.57202053070068</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726409912109</v>
+        <v>3.79726386070251</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.8259584903717</v>
+        <v>3.82595825195312</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813386917114</v>
+        <v>3.77813410758972</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222255706787</v>
+        <v>3.73222231864929</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.45199108123779</v>
+        <v>5.45199060440063</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>5.12200164794922</v>
+        <v>5.12200212478638</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.0550479888916</v>
+        <v>5.05504751205444</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>4.9546160697937</v>
+        <v>4.95461654663086</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653697967529</v>
+        <v>4.73653650283813</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680688858032</v>
+        <v>4.46680641174316</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>4.22768402099609</v>
+        <v>4.22768449783325</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942499160767</v>
+        <v>4.18942451477051</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603397369385</v>
+        <v>4.17603349685669</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472860336304</v>
+        <v>4.20472812652588</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846477508545</v>
+        <v>4.29846429824829</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157068252563</v>
+        <v>5.02157020568848</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113924026489</v>
+        <v>4.92113876342773</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548311233521</v>
+        <v>5.04548263549805</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G105" t="n">
-        <v>5.40894937515259</v>
+        <v>5.40894889831543</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>6.79585886001587</v>
+        <v>6.79585838317871</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.3845682144165</v>
+        <v>6.38456773757935</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>5.87762880325317</v>
+        <v>5.87762928009033</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>6.06414461135864</v>
+        <v>6.06414413452148</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370948791504</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325180053711</v>
+        <v>6.74325227737427</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.0689263343811</v>
+        <v>6.06892681121826</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848064422607</v>
+        <v>6.40848016738892</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935041427612</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370948791504</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933616638184</v>
+        <v>6.82933568954468</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>7.16888999938965</v>
+        <v>7.16888952255249</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>6.97280979156494</v>
+        <v>6.97280931472778</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584733963013</v>
+        <v>7.12584781646729</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>7.05889415740967</v>
+        <v>7.05889368057251</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>6.95846176147461</v>
+        <v>6.95846223831177</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.92498445510864</v>
+        <v>6.9249849319458</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>6.85324811935425</v>
+        <v>6.85324859619141</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>6.97280979156494</v>
+        <v>6.97280931472778</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976392745972</v>
+        <v>7.03976345062256</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886375427246</v>
+        <v>7.93886423110962</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.0919017791748</v>
+        <v>8.09190368652344</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91017007827759</v>
+        <v>7.91016960144043</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.67104721069336</v>
+        <v>7.6710467338562</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.996253490448</v>
+        <v>7.99625396728516</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712469100952</v>
+        <v>7.97712421417236</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060424804688</v>
+        <v>7.90060377120972</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.83364963531494</v>
+        <v>7.8336501121521</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103937149048</v>
+        <v>7.89103984832764</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.89582204818726</v>
+        <v>7.89582252502441</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492698669434</v>
+        <v>8.6849250793457</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.6562328338623</v>
+        <v>8.65623188018799</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.17798519134521</v>
+        <v>8.17798614501953</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.25450611114502</v>
+        <v>8.25450706481934</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451667785645</v>
+        <v>7.9245171546936</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754734039307</v>
+        <v>8.29754829406738</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.2736349105835</v>
+        <v>8.27363586425781</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.1057825088501</v>
+        <v>9.10578155517578</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23969078063965</v>
+        <v>9.23968982696533</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708229064941</v>
+        <v>9.1870813369751</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882598876953</v>
+        <v>9.03882694244385</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.1727352142334</v>
+        <v>9.17273616790771</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185855865479</v>
+        <v>9.41185760498047</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>10.4735622406006</v>
+        <v>10.4735612869263</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>11.1813650131226</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1813650131226</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518060684204</v>
+        <v>10.9518051147461</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.0431413650513</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.0431413650513</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831275939941</v>
+        <v>10.4831266403198</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8274621963501</v>
+        <v>10.8274631500244</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370265960693</v>
+        <v>10.8370275497437</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117858886719</v>
+        <v>11.6117849349976</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708980560303</v>
+        <v>12.0708990097046</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474189758301</v>
+        <v>12.1474180221558</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.25</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7169990539551</v>
+        <v>11.7169981002808</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G239" t="n">
-        <v>12.4248008728027</v>
+        <v>12.4247999191284</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.6160984039307</v>
+        <v>12.616096496582</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169612884521</v>
+        <v>12.8169603347778</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717260360718</v>
+        <v>13.3717231750488</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446565628052</v>
+        <v>15.2446575164795</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272216796875</v>
+        <v>13.5272226333618</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G256" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000663757324</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G264" t="n">
-        <v>14.1061305999756</v>
+        <v>14.1061315536499</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877311706543</v>
+        <v>13.7877321243286</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973804473877</v>
+        <v>13.7973794937134</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044092178345</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>13.835973739624</v>
+        <v>13.8359727859497</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921413421631</v>
+        <v>13.3921422958374</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.8063383102417</v>
+        <v>10.8063402175903</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>10.6809072494507</v>
+        <v>10.680908203125</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484483718872</v>
+        <v>10.7484474182129</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.729151725769</v>
+        <v>10.7291507720947</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.250171661377</v>
+        <v>11.2501707077026</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>11.1922798156738</v>
+        <v>11.1922807693481</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738803863525</v>
+        <v>10.8738794326782</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072355270386</v>
+        <v>10.5072345733643</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>10.9124736785889</v>
+        <v>10.9124727249146</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685720443726</v>
+        <v>11.5685729980469</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273582458496</v>
+        <v>11.3273591995239</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G306" t="n">
-        <v>11.7808389663696</v>
+        <v>11.7808399200439</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>11.1922798156738</v>
+        <v>11.1922807693481</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212257385254</v>
+        <v>11.2212247848511</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>11.5299787521362</v>
+        <v>11.5299777984619</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334936141968</v>
+        <v>11.4334945678711</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220518112183</v>
+        <v>12.0220527648926</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>11.9159183502197</v>
+        <v>11.915919303894</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640926361084</v>
+        <v>13.0640916824341</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044092178345</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693307876587</v>
+        <v>13.4693298339844</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886264801025</v>
+        <v>13.4886255264282</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.7105436325073</v>
+        <v>13.7105417251587</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9806995391846</v>
+        <v>13.9807004928589</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>14.75</v>
       </c>
       <c r="G341" t="n">
-        <v>14.2315626144409</v>
+        <v>14.2315635681152</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G347" t="n">
-        <v>14.5789098739624</v>
+        <v>14.5789089202881</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052362442017</v>
+        <v>14.4052352905273</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G352" t="n">
-        <v>13.01584815979</v>
+        <v>13.0158491134644</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386615753174</v>
+        <v>12.9386625289917</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000663757324</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G357" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.0447950363159</v>
+        <v>13.0447959899902</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>12.726393699646</v>
+        <v>12.7263927459717</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755334854126</v>
+        <v>12.4755325317383</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4272890090942</v>
+        <v>12.4272899627686</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>11.9641618728638</v>
+        <v>11.9641609191895</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.147481918335</v>
+        <v>12.1474828720093</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185388565063</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176416397095</v>
+        <v>12.4176425933838</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194332122803</v>
+        <v>11.8194341659546</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966217041016</v>
+        <v>11.8966207504272</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>11.9641618728638</v>
+        <v>11.9641609191895</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G393" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545125961304</v>
+        <v>11.9545135498047</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G398" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.8325290679932</v>
+        <v>12.8325281143188</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>13.0447950363159</v>
+        <v>13.0447959899902</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G413" t="n">
-        <v>12.9097156524658</v>
+        <v>12.9097166061401</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115081787109</v>
+        <v>12.3115072250366</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G416" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>12.8904180526733</v>
+        <v>12.8904190063477</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167463302612</v>
+        <v>12.7167453765869</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.8325290679932</v>
+        <v>12.8325281143188</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>13.179874420166</v>
+        <v>13.1798753738403</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G434" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G436" t="n">
-        <v>13.2088203430176</v>
+        <v>13.2088193893433</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>12.726393699646</v>
+        <v>12.7263927459717</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>12.1764278411865</v>
+        <v>12.1764287948608</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185388565063</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308038711548</v>
+        <v>12.3308048248291</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G472" t="n">
-        <v>12.1764278411865</v>
+        <v>12.1764287948608</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124034881592</v>
+        <v>12.0124025344849</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747055053711</v>
+        <v>11.6747064590454</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554828643799</v>
+        <v>9.45554733276367</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711090087891</v>
+        <v>9.68711185455322</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923480987549</v>
+        <v>10.0923490524292</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>10.4203996658325</v>
+        <v>10.4203987121582</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.8063383102417</v>
+        <v>10.8063402175903</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.7195024490356</v>
+        <v>10.71950340271</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G490" t="n">
-        <v>11.4527893066406</v>
+        <v>11.4527902603149</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G491" t="n">
-        <v>11.2791175842285</v>
+        <v>11.2791166305542</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256359100342</v>
+        <v>10.8256368637085</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7387990951538</v>
+        <v>10.7388000488281</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612154006958</v>
+        <v>10.5612144470215</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763509750366</v>
+        <v>10.7763500213623</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110445022583</v>
+        <v>11.0110454559326</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763509750366</v>
+        <v>10.7763500213623</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>10.9328136444092</v>
+        <v>10.9328126907349</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634246826172</v>
+        <v>10.4634256362915</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069639205933</v>
+        <v>10.3069629669189</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233818054199</v>
+        <v>8.74233913421631</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432834625244</v>
+        <v>8.65432929992676</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>10.5</v>
       </c>
       <c r="G572" t="n">
-        <v>10.2678480148315</v>
+        <v>10.2678470611572</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G580" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.1237154006958</v>
+        <v>9.12371635437012</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G594" t="n">
-        <v>9.31929397583008</v>
+        <v>9.31929302215576</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492362976074</v>
+        <v>9.95492267608643</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.75</v>
       </c>
       <c r="G605" t="n">
-        <v>9.5344295501709</v>
+        <v>9.53443050384521</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G620" t="n">
-        <v>9.55398845672607</v>
+        <v>9.55398750305176</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G623" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354640960693</v>
+        <v>9.57354545593262</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>9.13349533081055</v>
+        <v>9.13349437713623</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233818054199</v>
+        <v>8.74233913421631</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548454284668</v>
+        <v>9.04548358917236</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835880279541</v>
+        <v>8.91835784912109</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G656" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437847137451</v>
+        <v>9.09437942504883</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956607818604</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>9.75</v>
       </c>
       <c r="G689" t="n">
-        <v>9.5344295501709</v>
+        <v>9.53443050384521</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G711" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G716" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G719" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924385070801</v>
+        <v>8.87924289703369</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>6.86478900909424</v>
+        <v>6.8647894859314</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385431289673</v>
+        <v>6.46385478973389</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G748" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834590911865</v>
+        <v>4.93834638595581</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.7134313583374</v>
+        <v>4.71343088150024</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760622024536</v>
+        <v>4.30760669708252</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10224914550781</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357671737671</v>
+        <v>4.04357624053955</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>4.29782819747925</v>
+        <v>4.29782772064209</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00934982299805</v>
+        <v>4.00935029983521</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.98001313209534</v>
+        <v>3.9800136089325</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10224914550781</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691761016846</v>
+        <v>4.11691808700562</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630561828613</v>
+        <v>4.58630514144897</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055662155151</v>
+        <v>4.84055614471436</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.44684886932373</v>
+        <v>5.44684839248657</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485870361328</v>
+        <v>5.53485822677612</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773344039917</v>
+        <v>5.40773296356201</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.25</v>
       </c>
       <c r="G795" t="n">
-        <v>5.13392400741577</v>
+        <v>5.13392353057861</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171234130859</v>
+        <v>5.23171281814575</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>5.24149131774902</v>
+        <v>5.24149179458618</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834590911865</v>
+        <v>4.93834638595581</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>5.0459132194519</v>
+        <v>5.04591369628906</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G828" t="n">
-        <v>5.44684886932373</v>
+        <v>5.44684839248657</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264799118042</v>
+        <v>5.63264846801758</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314064025879</v>
+        <v>6.05314111709595</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G840" t="n">
-        <v>6.73766326904297</v>
+        <v>6.73766374588013</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>6.08247709274292</v>
+        <v>6.08247661590576</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.14115142822266</v>
+        <v>6.1411509513855</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G855" t="n">
-        <v>5.92601490020752</v>
+        <v>5.92601537704468</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78911018371582</v>
+        <v>5.78911066055298</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>5.60331058502197</v>
+        <v>5.60331106185913</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>5.82822608947754</v>
+        <v>5.82822561264038</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G868" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>5.95535182952881</v>
+        <v>5.95535135269165</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>6.53230619430542</v>
+        <v>6.53230667114258</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>6.65943193435669</v>
+        <v>6.65943241119385</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700067520142</v>
+        <v>6.76700019836426</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655815124512</v>
+        <v>6.78655862808228</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G902" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75466966629028</v>
+        <v>7.75466918945312</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G905" t="n">
-        <v>7.73511171340942</v>
+        <v>7.73511123657227</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>7.39284992218018</v>
+        <v>7.39285039901733</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G908" t="n">
-        <v>7.64710140228271</v>
+        <v>7.64710187911987</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>7.41240787506104</v>
+        <v>7.41240835189819</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7</v>
       </c>
       <c r="G918" t="n">
-        <v>6.84523153305054</v>
+        <v>6.8452320098877</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G919" t="n">
-        <v>6.71810579299927</v>
+        <v>6.71810626983643</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G920" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G921" t="n">
-        <v>6.71810579299927</v>
+        <v>6.71810626983643</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412641525269</v>
+        <v>6.89412593841553</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793537139893</v>
+        <v>7.16793489456177</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>7.5395336151123</v>
+        <v>7.53953409194946</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>7.5395336151123</v>
+        <v>7.53953409194946</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G938" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G946" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G949" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G951" t="n">
-        <v>9.31929397583008</v>
+        <v>9.31929302215576</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>8.5956563949585</v>
+        <v>8.59565544128418</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37073993682861</v>
+        <v>8.37074089050293</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>8.45875072479248</v>
+        <v>8.45874977111816</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449924468994</v>
+        <v>8.20449829101562</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.49531364440918</v>
+        <v>9.4953145980835</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>9.24106216430664</v>
+        <v>9.24106311798096</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956607818604</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9107036590576</v>
+        <v>11.9107027053833</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G996" t="n">
-        <v>15.0790672302246</v>
+        <v>15.0790681838989</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705642700195</v>
+        <v>14.5705652236938</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.3188638687134</v>
+        <v>13.3188648223877</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.0059413909912</v>
+        <v>13.0059404373169</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.2823028564453</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867223739624</v>
+        <v>12.0867233276367</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5561103820801</v>
+        <v>12.5561113357544</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.3996486663818</v>
+        <v>12.3996496200562</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.5365533828735</v>
+        <v>12.5365524291992</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.5952253341675</v>
+        <v>12.5952262878418</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.2823028564453</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.2823028564453</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.3996486663818</v>
+        <v>12.3996496200562</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.4192066192627</v>
+        <v>12.4192056655884</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409738540649</v>
+        <v>12.3409748077393</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220994949341</v>
+        <v>10.5220985412598</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.2091732025146</v>
+        <v>10.209174156189</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.3265218734741</v>
+        <v>10.3265209197998</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.1819591522217</v>
+        <v>13.181960105896</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>13.8273687362671</v>
+        <v>13.8273677825928</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>14.4532165527344</v>
+        <v>14.4532175064087</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749866485596</v>
+        <v>14.3749856948853</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030475616455</v>
+        <v>14.9030466079712</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.7074689865112</v>
+        <v>14.7074699401855</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396104812622</v>
+        <v>15.9396095275879</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.3890113830566</v>
+        <v>20.3890132904053</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981086730957</v>
+        <v>22.1981105804443</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.7580585479736</v>
+        <v>21.758056640625</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>21.1713237762451</v>
+        <v>21.1713218688965</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602687835693</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602687835693</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>21.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>20.7801685333252</v>
+        <v>20.7801666259766</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>21</v>
       </c>
       <c r="G1152" t="n">
-        <v>20.5356960296631</v>
+        <v>20.5356941223145</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>24.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.9583110809326</v>
+        <v>23.9583129882812</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7848415374756</v>
+        <v>22.7848434448242</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.5403671264648</v>
+        <v>22.5403690338135</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.9268493652344</v>
+        <v>20.926851272583</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3890113830566</v>
+        <v>20.3890132904053</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511714935303</v>
+        <v>19.8511695861816</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.7533836364746</v>
+        <v>19.7533855438232</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470928192139</v>
+        <v>19.1470909118652</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.2669906616211</v>
+        <v>18.2669887542725</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.3698825836182</v>
+        <v>16.3698806762695</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329769134521</v>
+        <v>16.2329788208008</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743068695068</v>
+        <v>16.1743049621582</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.917501449585</v>
+        <v>16.9174995422363</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304248809814</v>
+        <v>17.2304267883301</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1241" t="n">
-        <v>17.0544052124023</v>
+        <v>17.054407119751</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042343139648</v>
+        <v>17.5042324066162</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.484676361084</v>
+        <v>17.4846782684326</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.5459022521973</v>
+        <v>16.5459041595459</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761734008789</v>
+        <v>16.9761753082275</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414798736572</v>
+        <v>16.7414817810059</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>19.5948181152344</v>
+        <v>19.594820022583</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6342849731445</v>
+        <v>19.6342830657959</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.5750846862793</v>
+        <v>19.5750865936279</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>18.5687046051025</v>
+        <v>18.5687065124512</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.3777561187744</v>
+        <v>19.3777542114258</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1294" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>19.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>19.2396240234375</v>
+        <v>19.2396259307861</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.7132167816162</v>
+        <v>19.7132148742676</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.5089130401611</v>
+        <v>21.5089149475098</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>21.1635875701904</v>
+        <v>21.1635894775391</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.8182601928711</v>
+        <v>20.8182621002197</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.6737499237061</v>
+        <v>19.6737518310547</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.6145515441895</v>
+        <v>19.6145496368408</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>23.75</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.4328784942627</v>
+        <v>23.4328765869141</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>22.2982311248779</v>
+        <v>22.2982330322266</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>21.2622509002686</v>
+        <v>21.2622528076172</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>22.8902225494385</v>
+        <v>22.8902206420898</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1340" t="n">
-        <v>26.1856231689453</v>
+        <v>26.1856250762939</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1349" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G1354" t="n">
-        <v>23.14674949646</v>
+        <v>23.1467475891113</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.71262550354</v>
+        <v>22.7126235961914</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.008617401123</v>
+        <v>23.0086193084717</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1361" t="n">
-        <v>23.5216770172119</v>
+        <v>23.5216751098633</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1365" t="n">
-        <v>24.6464538574219</v>
+        <v>24.6464519500732</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1373" t="n">
-        <v>24.902982711792</v>
+        <v>24.9029808044434</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>24.7648506164551</v>
+        <v>24.7648525238037</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1375" t="n">
-        <v>24.4096565246582</v>
+        <v>24.4096584320068</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1376" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1379" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.2250900268555</v>
+        <v>26.2250881195068</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1384" t="n">
-        <v>28.4351806640625</v>
+        <v>28.4351787567139</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1391" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1393" t="n">
-        <v>24.6267204284668</v>
+        <v>24.6267185211182</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>24.6069869995117</v>
+        <v>24.6069889068604</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>24.7253856658936</v>
+        <v>24.7253837585449</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>24.1531276702881</v>
+        <v>24.1531295776367</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1408" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3899250030518</v>
+        <v>24.3899230957031</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.3307247161865</v>
+        <v>24.3307266235352</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.3440799713135</v>
+        <v>23.3440780639648</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>24.6859188079834</v>
+        <v>24.685920715332</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>26.3434867858887</v>
+        <v>26.3434886932373</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.0341415405273</v>
+        <v>27.0341396331787</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>28.4154453277588</v>
+        <v>28.4154472351074</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>29.6980876922607</v>
+        <v>29.6980895996094</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1446" t="n">
-        <v>29.7770195007324</v>
+        <v>29.7770214080811</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1448" t="n">
-        <v>30.3295421600342</v>
+        <v>30.3295440673828</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>30.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>30.0927467346191</v>
+        <v>30.0927486419678</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.4218254089355</v>
+        <v>29.4218273162842</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G1465" t="n">
-        <v>35.8547668457031</v>
+        <v>35.8547706604004</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>39.0712394714355</v>
+        <v>39.0712356567383</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1469" t="n">
-        <v>36.2691612243652</v>
+        <v>36.269157409668</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>40.3538856506348</v>
+        <v>40.3538818359375</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>42.6599998474121</v>
       </c>
       <c r="G1475" t="n">
-        <v>42.0903816223145</v>
+        <v>42.0903778076172</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>42.2482452392578</v>
+        <v>42.2482414245605</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1477" t="n">
-        <v>42.5837059020996</v>
+        <v>42.5837020874023</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>43.0178260803223</v>
+        <v>43.0178298950195</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>42.6231727600098</v>
+        <v>42.6231689453125</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>43</v>
       </c>
       <c r="G1480" t="n">
-        <v>42.4258422851562</v>
+        <v>42.425838470459</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.2615928649902</v>
+        <v>41.2615966796875</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>42.6399993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.0706481933594</v>
+        <v>42.0706443786621</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1492" t="n">
-        <v>45.5831146240234</v>
+        <v>45.5831108093262</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>38.4199981689453</v>
       </c>
       <c r="G1493" t="n">
-        <v>37.9069900512695</v>
+        <v>37.9069938659668</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1495" t="n">
-        <v>32.6185684204102</v>
+        <v>32.6185646057129</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1500" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1504" t="n">
-        <v>31.0201950073242</v>
+        <v>31.0201969146729</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>31.3951225280762</v>
+        <v>31.3951206207275</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1508" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -71236,7 +71236,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="D2726" t="n">
-        <v>12.3800001144409</v>
+        <v>12.3599996566772</v>
       </c>
       <c r="E2726" t="n">
         <v>12.5600004196167</v>
@@ -71248,6 +71248,32 @@
         <v>12.3599996566772</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>24622</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>13.1800003051758</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>12.539999961853</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>12.539999961853</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>13.1800003051758</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>13.1800003051758</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -447,7 +447,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455717086792</v>
+        <v>6.71455764770508</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48499965667725</v>
+        <v>6.4850001335144</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4467396736145</v>
+        <v>6.44674015045166</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2793550491333</v>
+        <v>6.27935457229614</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>6.06414413452148</v>
+        <v>6.06414461135864</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3319616317749</v>
+        <v>6.33196115493774</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546054840088</v>
+        <v>5.70546102523804</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>5.71502590179443</v>
+        <v>5.71502542495728</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31330013275146</v>
+        <v>5.31329965591431</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.02588510513306</v>
+        <v>6.0258846282959</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935136795044</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458389282227</v>
+        <v>5.94458293914795</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458709716797</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154491424561</v>
+        <v>5.79154443740845</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7006778717041</v>
+        <v>5.70067834854126</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244829177856</v>
+        <v>4.78244876861572</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62940979003906</v>
+        <v>4.62941026687622</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.064612865448</v>
+        <v>5.06461238861084</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.3228645324707</v>
+        <v>5.32286500930786</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844957351685</v>
+        <v>4.73844909667969</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G45" t="n">
-        <v>4.68297290802002</v>
+        <v>4.68297338485718</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028051376343</v>
+        <v>4.61028003692627</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984491348267</v>
+        <v>4.61984443664551</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732414245605</v>
+        <v>4.58732461929321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985227584839</v>
+        <v>4.39985275268555</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.2391619682312</v>
+        <v>4.23916244506836</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916980743408</v>
+        <v>4.01916933059692</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793920516968</v>
+        <v>4.39793968200684</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202053070068</v>
+        <v>4.57202100753784</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871995925903</v>
+        <v>4.46871900558472</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.06508111953735</v>
+        <v>4.0650806427002</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265079498291</v>
+        <v>3.94265007972717</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.82595825195312</v>
+        <v>3.82595872879028</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987436294556</v>
+        <v>3.73987460136414</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222231864929</v>
+        <v>3.73222255706787</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8489146232605</v>
+        <v>3.84891486167908</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723049163818</v>
+        <v>4.7872314453125</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.45199060440063</v>
+        <v>5.45199108123779</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07895994186401</v>
+        <v>5.07895946502686</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851745605469</v>
+        <v>5.30851793289185</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373525619507</v>
+        <v>5.30373477935791</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>5.12200212478638</v>
+        <v>5.12200164794922</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.05504751205444</v>
+        <v>5.0550479888916</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G90" t="n">
-        <v>4.38646078109741</v>
+        <v>4.38646125793457</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559837341309</v>
+        <v>4.18559885025024</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942451477051</v>
+        <v>4.18942499160767</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550888061523</v>
+        <v>4.27550840377808</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16072940826416</v>
+        <v>4.16072988510132</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603349685669</v>
+        <v>4.17603397369385</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472812652588</v>
+        <v>4.20472860336304</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157020568848</v>
+        <v>5.02156972885132</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113876342773</v>
+        <v>4.92113924026489</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G103" t="n">
-        <v>4.95939922332764</v>
+        <v>4.95939874649048</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548263549805</v>
+        <v>5.04548311233521</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G105" t="n">
-        <v>5.40894889831543</v>
+        <v>5.40894937515259</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756574630737</v>
+        <v>7.74756622314453</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237466812134</v>
+        <v>6.98237419128418</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.38456773757935</v>
+        <v>6.38456869125366</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458709716797</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>6.06414413452148</v>
+        <v>6.06414461135864</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325227737427</v>
+        <v>6.74325180053711</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.06892681121826</v>
+        <v>6.0689263343811</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848016738892</v>
+        <v>6.40848112106323</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935136795044</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933568954468</v>
+        <v>6.82933664321899</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>7.16888952255249</v>
+        <v>7.16889047622681</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>6.97280931472778</v>
+        <v>6.97280979156494</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584781646729</v>
+        <v>7.12584686279297</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.9249849319458</v>
+        <v>6.92498445510864</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87237787246704</v>
+        <v>6.8723783493042</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064474105835</v>
+        <v>6.69064521789551</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>6.85324859619141</v>
+        <v>6.85324811935425</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>6.95368003845215</v>
+        <v>6.95367956161499</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>6.97280931472778</v>
+        <v>6.97280979156494</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>7.03019857406616</v>
+        <v>7.03019905090332</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976345062256</v>
+        <v>7.03976392745972</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.33627605438232</v>
+        <v>7.33627557754517</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886423110962</v>
+        <v>7.93886375427246</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.09190368652344</v>
+        <v>8.0919017791748</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712789535522</v>
+        <v>7.86712837219238</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91016960144043</v>
+        <v>7.91017007827759</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.6710467338562</v>
+        <v>7.67104768753052</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234426498413</v>
+        <v>7.86234474182129</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626085281372</v>
+        <v>7.77626037597656</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.99625396728516</v>
+        <v>7.996253490448</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712421417236</v>
+        <v>7.97712373733521</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451251983643</v>
+        <v>8.03451347351074</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060377120972</v>
+        <v>7.90060424804688</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669597625732</v>
+        <v>7.76669645309448</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103984832764</v>
+        <v>7.89103937149048</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.89582252502441</v>
+        <v>7.89582204818726</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.6849250793457</v>
+        <v>8.68492698669434</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622676849365</v>
+        <v>8.76622772216797</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>8.46493339538574</v>
+        <v>8.46493244171143</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.25450706481934</v>
+        <v>8.2545051574707</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.9245171546936</v>
+        <v>7.92451572418213</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754829406738</v>
+        <v>8.29754734039307</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.27363586425781</v>
+        <v>8.2736349105835</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101776123047</v>
+        <v>8.55101680755615</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.0675220489502</v>
+        <v>9.06752109527588</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968982696533</v>
+        <v>9.23968887329102</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317401885986</v>
+        <v>9.05317497253418</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.1870813369751</v>
+        <v>9.18708229064941</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185760498047</v>
+        <v>9.41185855865479</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>9.5170726776123</v>
+        <v>9.51707172393799</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620147705078</v>
+        <v>9.53620338439941</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587837219238</v>
+        <v>10.3587827682495</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.253568649292</v>
+        <v>10.2535705566406</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2004928588867</v>
+        <v>11.200493812561</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518051147461</v>
+        <v>10.9518060684204</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431394577026</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431394577026</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.9613704681396</v>
+        <v>10.961371421814</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.1144094467163</v>
+        <v>11.1144104003906</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630962371826</v>
+        <v>11.3630971908569</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456932067871</v>
+        <v>11.7456912994385</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648220062256</v>
+        <v>11.7648229598999</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>11.6691732406616</v>
+        <v>11.6691741943359</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.616096496582</v>
+        <v>12.6160984039307</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169603347778</v>
+        <v>12.8169622421265</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717231750488</v>
+        <v>13.3717260360718</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272226333618</v>
+        <v>13.5272216796875</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8132305145264</v>
+        <v>12.8132295608521</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000663757324</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877321243286</v>
+        <v>13.7877311706543</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044101715088</v>
+        <v>13.6044082641602</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921422958374</v>
+        <v>13.3921413421631</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.131630897522</v>
+        <v>13.1316318511963</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869724273682</v>
+        <v>11.8869714736938</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2887649536133</v>
+        <v>11.2887659072876</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.2887649536133</v>
+        <v>11.2887659072876</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.8063402175903</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484474182129</v>
+        <v>10.7484483718872</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431400299072</v>
+        <v>11.4431409835815</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.2501707077026</v>
+        <v>11.250171661377</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.0089588165283</v>
+        <v>11.008957862854</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072345733643</v>
+        <v>10.5072355270386</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695375442505</v>
+        <v>10.1695356369019</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>10.9124727249146</v>
+        <v>10.9124736785889</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685729980469</v>
+        <v>11.5685720443726</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G303" t="n">
-        <v>11.7133007049561</v>
+        <v>11.7132997512817</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606470108032</v>
+        <v>12.0606460571289</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G306" t="n">
-        <v>11.7808399200439</v>
+        <v>11.7808389663696</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054439544678</v>
+        <v>11.1054430007935</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334945678711</v>
+        <v>11.4334926605225</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606470108032</v>
+        <v>12.0606460571289</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G320" t="n">
-        <v>12.1281862258911</v>
+        <v>12.1281852722168</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G322" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387317657471</v>
+        <v>11.8387308120728</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640916824341</v>
+        <v>13.0640926361084</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044101715088</v>
+        <v>13.6044082641602</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693298339844</v>
+        <v>13.4693307876587</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886255264282</v>
+        <v>13.4886264801025</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.7105417251587</v>
+        <v>13.710542678833</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552694320679</v>
+        <v>13.8552713394165</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8745679855347</v>
+        <v>13.8745670318604</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.492073059082</v>
+        <v>14.4920721054077</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G345" t="n">
-        <v>14.5113697052002</v>
+        <v>14.5113706588745</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.5113697052002</v>
+        <v>14.5113706588745</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052352905273</v>
+        <v>14.405237197876</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527219772339</v>
+        <v>12.5527210235596</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386625289917</v>
+        <v>12.9386606216431</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.8807697296143</v>
+        <v>12.8807706832886</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000663757324</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.006199836731</v>
+        <v>13.0062007904053</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.131630897522</v>
+        <v>13.1316318511963</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G366" t="n">
-        <v>12.7939338684082</v>
+        <v>12.7939348220825</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>12.7263927459717</v>
+        <v>12.726393699646</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755325317383</v>
+        <v>12.4755334854126</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150230407715</v>
+        <v>12.2150220870972</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474828720093</v>
+        <v>12.1474838256836</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176425933838</v>
+        <v>12.4176416397095</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194341659546</v>
+        <v>11.8194332122803</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325963973999</v>
+        <v>11.7325973510742</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966207504272</v>
+        <v>11.8966217041016</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1281862258911</v>
+        <v>12.1281852722168</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G393" t="n">
-        <v>12.1378345489502</v>
+        <v>12.1378355026245</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.243968963623</v>
+        <v>12.2439680099487</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G399" t="n">
-        <v>12.7939338684082</v>
+        <v>12.7939348220825</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228797912598</v>
+        <v>12.8228788375854</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6685037612915</v>
+        <v>12.6685028076172</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483089447021</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G413" t="n">
-        <v>12.9097166061401</v>
+        <v>12.9097156524658</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115072250366</v>
+        <v>12.3115081787109</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193639755249</v>
+        <v>12.9193649291992</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>13.054443359375</v>
+        <v>13.0544424057007</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483089447021</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167453765869</v>
+        <v>12.7167463302612</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>12.8807697296143</v>
+        <v>12.8807706832886</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483089447021</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>13.2184686660767</v>
+        <v>13.2184677124023</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>13.2860078811646</v>
+        <v>13.2860088348389</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>13.1798753738403</v>
+        <v>13.179874420166</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G434" t="n">
-        <v>13.8745679855347</v>
+        <v>13.8745670318604</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974487304688</v>
+        <v>12.6974477767944</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>12.7263927459717</v>
+        <v>12.726393699646</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>12.6395568847656</v>
+        <v>12.6395578384399</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13</v>
       </c>
       <c r="G444" t="n">
-        <v>12.5430727005005</v>
+        <v>12.5430717468262</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>12.6685037612915</v>
+        <v>12.6685028076172</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3693990707397</v>
+        <v>12.3693981170654</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1860771179199</v>
+        <v>12.1860780715942</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>12.0895919799805</v>
+        <v>12.0895910263062</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1378345489502</v>
+        <v>12.1378355026245</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308048248291</v>
+        <v>12.3308038711548</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124025344849</v>
+        <v>12.0124034881592</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747064590454</v>
+        <v>11.6747055053711</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816497802734</v>
+        <v>9.65816593170166</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711185455322</v>
+        <v>9.68711090087891</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923490524292</v>
+        <v>10.0923480987549</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625068664551</v>
+        <v>10.3625078201294</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107503890991</v>
+        <v>10.4107494354248</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.8063402175903</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764970779419</v>
+        <v>11.0764980316162</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.71950340271</v>
+        <v>10.7195014953613</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G490" t="n">
-        <v>11.4527902603149</v>
+        <v>11.4527893066406</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028253555298</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256368637085</v>
+        <v>10.8256359100342</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G494" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028253555298</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G496" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028253555298</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545827865601</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078981399536</v>
+        <v>10.7078971862793</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189521789551</v>
+        <v>10.2189531326294</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763519287109</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110454559326</v>
+        <v>11.0110445022583</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763519287109</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G521" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545827865601</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G529" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069629669189</v>
+        <v>10.3069620132446</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509262084961</v>
+        <v>9.50509357452393</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619964599609</v>
+        <v>9.45619869232178</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G551" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432929992676</v>
+        <v>8.65432834625244</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G556" t="n">
-        <v>8.5369815826416</v>
+        <v>8.53698062896729</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.84990692138672</v>
+        <v>8.8499059677124</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G577" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G580" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12371635437012</v>
+        <v>9.1237154006958</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>8.9476957321167</v>
+        <v>8.94769477844238</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9</v>
       </c>
       <c r="G588" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G594" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G620" t="n">
-        <v>9.55398750305176</v>
+        <v>9.55398845672607</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>9.69089221954346</v>
+        <v>9.69089126586914</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548358917236</v>
+        <v>9.04548454284668</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835784912109</v>
+        <v>8.91835975646973</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52465057373047</v>
+        <v>9.52464962005615</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376647949219</v>
+        <v>9.56376552581787</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575569152832</v>
+        <v>9.47575664520264</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560531616211</v>
+        <v>8.15560436248779</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626838684082</v>
+        <v>8.12626934051514</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742362976074</v>
+        <v>8.51742458343506</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G722" t="n">
-        <v>8.73256015777588</v>
+        <v>8.73255920410156</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.63477039337158</v>
+        <v>8.6347713470459</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924289703369</v>
+        <v>8.87924385070801</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9</v>
       </c>
       <c r="G725" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902282714844</v>
+        <v>8.88902187347412</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G734" t="n">
-        <v>8.04803562164307</v>
+        <v>8.04803657531738</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262937545776</v>
+        <v>7.40262889862061</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>7.5</v>
       </c>
       <c r="G742" t="n">
-        <v>7.33417654037476</v>
+        <v>7.33417701721191</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.1581563949585</v>
+        <v>7.15815687179565</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G749" t="n">
-        <v>5.32950162887573</v>
+        <v>5.32950210571289</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.71343088150024</v>
+        <v>4.7134313583374</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760669708252</v>
+        <v>4.30760622024536</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738519668579</v>
+        <v>4.31738567352295</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357624053955</v>
+        <v>4.04357671737671</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156101226807</v>
+        <v>3.91156077384949</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669658660889</v>
+        <v>4.12669706344604</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691808700562</v>
+        <v>4.11691761016846</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502960205078</v>
+        <v>5.08502912521362</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.32950162887573</v>
+        <v>5.32950210571289</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G780" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485822677612</v>
+        <v>5.53485870361328</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G784" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773296356201</v>
+        <v>5.40773344039917</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928108215332</v>
+        <v>5.33928060531616</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016469955444</v>
+        <v>5.3001651763916</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215534210205</v>
+        <v>5.21215438842773</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166269302368</v>
+        <v>4.79166221618652</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220642089844</v>
+        <v>5.65220546722412</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441617965698</v>
+        <v>5.55441665649414</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G828" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264846801758</v>
+        <v>5.63264751434326</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>5.7108793258667</v>
+        <v>5.71087884902954</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>6.47363328933716</v>
+        <v>6.4736328125</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004535675049</v>
+        <v>6.19004487991333</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402473449707</v>
+        <v>6.01402521133423</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G835" t="n">
-        <v>6.06291961669922</v>
+        <v>6.06291913986206</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314111709595</v>
+        <v>6.05314064025879</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672904968262</v>
+        <v>6.33672857284546</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>6.4345178604126</v>
+        <v>6.43451738357544</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G843" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>6.09225606918335</v>
+        <v>6.09225654602051</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>6.41495990753174</v>
+        <v>6.41495943069458</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.1411509513855</v>
+        <v>6.14115047454834</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.0042462348938</v>
+        <v>6.00424575805664</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G855" t="n">
-        <v>5.92601537704468</v>
+        <v>5.92601490020752</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78911066055298</v>
+        <v>5.78911018371582</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955270767212</v>
+        <v>5.76955223083496</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977325439453</v>
+        <v>5.75977373123169</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021530151367</v>
+        <v>5.74021577835083</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>5.66198396682739</v>
+        <v>5.66198444366455</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>5.69132137298584</v>
+        <v>5.69132089614868</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>5.95535135269165</v>
+        <v>5.95535182952881</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G876" t="n">
-        <v>5.7108793258667</v>
+        <v>5.71087884902954</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>5.30994367599487</v>
+        <v>5.30994415283203</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G881" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G890" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987493515015</v>
+        <v>6.63987445831299</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700019836426</v>
+        <v>6.76700067520142</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655862808228</v>
+        <v>6.78655815124512</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G897" t="n">
-        <v>7.87201642990112</v>
+        <v>7.87201690673828</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489068984985</v>
+        <v>7.74489116668701</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G900" t="n">
-        <v>7.72533273696899</v>
+        <v>7.72533321380615</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G904" t="n">
-        <v>7.676438331604</v>
+        <v>7.67643785476685</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842802047729</v>
+        <v>7.58842849731445</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G910" t="n">
-        <v>6.95279979705811</v>
+        <v>6.95279932022095</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147317886353</v>
+        <v>7.01147270202637</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572465896606</v>
+        <v>7.26572418212891</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G919" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G920" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G921" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793489456177</v>
+        <v>7.16793537139893</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191570281982</v>
+        <v>6.99191522598267</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218732833862</v>
+        <v>7.42218685150146</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312202453613</v>
+        <v>7.82312154769897</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G951" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897270202637</v>
+        <v>8.44897174835205</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G961" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339317321777</v>
+        <v>8.25339412689209</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449829101562</v>
+        <v>8.20449924468994</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G970" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482147216797</v>
+        <v>9.07482051849365</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G979" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804306030273</v>
+        <v>11.4804315567017</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9107027053833</v>
+        <v>11.9107036590576</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G987" t="n">
-        <v>12.4387645721436</v>
+        <v>12.4387636184692</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G990" t="n">
-        <v>12.9472665786743</v>
+        <v>12.947265625</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926733016968</v>
+        <v>13.5926742553711</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G996" t="n">
-        <v>15.0790681838989</v>
+        <v>15.0790672302246</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705652236938</v>
+        <v>14.5705633163452</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.1258392333984</v>
+        <v>12.1258382797241</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867233276367</v>
+        <v>12.0867223739624</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.9668245315552</v>
+        <v>12.9668254852295</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5561113357544</v>
+        <v>12.5561103820801</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.3384227752686</v>
+        <v>13.3384237289429</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583206176758</v>
+        <v>12.4583215713501</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.7151250839233</v>
+        <v>11.715124130249</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.047607421875</v>
+        <v>12.0476064682007</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734580993652</v>
+        <v>12.6734571456909</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.1845121383667</v>
+        <v>12.184513092041</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.2797498703003</v>
+        <v>13.279748916626</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1057" t="n">
-        <v>10.5416564941406</v>
+        <v>10.5416574478149</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220985412598</v>
+        <v>10.5220994949341</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206798553467</v>
+        <v>8.31206703186035</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543346405029</v>
+        <v>8.60543441772461</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570556640625</v>
+        <v>9.03570652008057</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.3265209197998</v>
+        <v>10.3265218734741</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003293991089</v>
+        <v>10.6003303527832</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1094" t="n">
-        <v>13.3775386810303</v>
+        <v>13.3775396347046</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1097" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1098" t="n">
-        <v>13.9055995941162</v>
+        <v>13.9055986404419</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771987915039</v>
+        <v>14.2771978378296</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749856948853</v>
+        <v>14.3749866485596</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>15</v>
       </c>
       <c r="G1107" t="n">
-        <v>14.6683530807495</v>
+        <v>14.6683540344238</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.6683530807495</v>
+        <v>14.6683540344238</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181840896606</v>
+        <v>15.1181831359863</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396095275879</v>
+        <v>15.9396114349365</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666507720947</v>
+        <v>19.1666488647461</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981105804443</v>
+        <v>22.1981067657471</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.758056640625</v>
+        <v>21.7580585479736</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558483123779</v>
+        <v>21.8558464050293</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602668762207</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602668762207</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>21.3180065155029</v>
+        <v>21.3180084228516</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>20.6334838867188</v>
+        <v>20.6334857940674</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691135406494</v>
+        <v>21.2691116333008</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0560989379883</v>
+        <v>24.0561008453369</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538887023926</v>
+        <v>24.1538906097412</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>24.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.9583129882812</v>
+        <v>23.9583110809326</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.3226833343506</v>
+        <v>23.322681427002</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359504699707</v>
+        <v>22.7359485626221</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1173" t="n">
-        <v>22.4425830841064</v>
+        <v>22.4425811767578</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.5892658233643</v>
+        <v>22.5892639160156</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157962799072</v>
+        <v>21.4157943725586</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113758087158</v>
+        <v>21.6113739013672</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.3180065155029</v>
+        <v>21.3180084228516</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401184082031</v>
+        <v>20.3401165008545</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511695861816</v>
+        <v>19.8511714935303</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.7533855438232</v>
+        <v>19.7533836364746</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1224" t="n">
-        <v>17.4651203155518</v>
+        <v>17.4651184082031</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1225" t="n">
-        <v>17.4651203155518</v>
+        <v>17.4651184082031</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.7831478118896</v>
+        <v>15.783148765564</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112106323242</v>
+        <v>16.3112087249756</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.3698806762695</v>
+        <v>16.3698825836182</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329788208008</v>
+        <v>16.2329769134521</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743049621582</v>
+        <v>16.1743068695068</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348472595215</v>
+        <v>17.0348491668701</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>18</v>
       </c>
       <c r="G1237" t="n">
-        <v>17.6020240783691</v>
+        <v>17.6020259857178</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304267883301</v>
+        <v>17.2304248809814</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108669281006</v>
+        <v>17.2108688354492</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1240" t="n">
-        <v>17.0739631652832</v>
+        <v>17.0739612579346</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1243" t="n">
-        <v>17.6411418914795</v>
+        <v>17.6411399841309</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042324066162</v>
+        <v>17.5042362213135</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.4846782684326</v>
+        <v>17.484676361084</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979454040527</v>
+        <v>16.8979434967041</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.5459041595459</v>
+        <v>16.5459022521973</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>13.1800003051758</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>6686</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>6.84846591949463</v>
+        <v>6.84846639633179</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455764770508</v>
+        <v>6.71455717086792</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4850001335144</v>
+        <v>6.48499965667725</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44674015045166</v>
+        <v>6.4467396736145</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.33196115493774</v>
+        <v>6.3319616317749</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546102523804</v>
+        <v>5.70546054840088</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>5.71502542495728</v>
+        <v>5.71502590179443</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31329965591431</v>
+        <v>5.31330013275146</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84415197372437</v>
+        <v>5.84415149688721</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937250137329</v>
+        <v>5.72937297821045</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.0258846282959</v>
+        <v>6.02588510513306</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935136795044</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458293914795</v>
+        <v>5.94458389282227</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414733886719</v>
+        <v>5.95414781570435</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>5.83458709716797</v>
+        <v>5.83458662033081</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154443740845</v>
+        <v>5.79154491424561</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.70067834854126</v>
+        <v>5.7006778717041</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244876861572</v>
+        <v>4.78244781494141</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62941026687622</v>
+        <v>4.62940979003906</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.06461238861084</v>
+        <v>5.064612865448</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.32286500930786</v>
+        <v>5.3228645324707</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069307327271</v>
+        <v>5.26069355010986</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G45" t="n">
-        <v>4.68297338485718</v>
+        <v>4.68297290802002</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028003692627</v>
+        <v>4.61028051376343</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984443664551</v>
+        <v>4.61984491348267</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732461929321</v>
+        <v>4.58732414245605</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985275268555</v>
+        <v>4.39985227584839</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40559101104736</v>
+        <v>4.40559148788452</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.23916244506836</v>
+        <v>4.2391619682312</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916933059692</v>
+        <v>4.01916980743408</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793968200684</v>
+        <v>4.39793920516968</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202100753784</v>
+        <v>4.57202053070068</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871900558472</v>
+        <v>4.46871995925903</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.0650806427002</v>
+        <v>4.06508159637451</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265007972717</v>
+        <v>3.94265079498291</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.82595872879028</v>
+        <v>3.8259584903717</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813410758972</v>
+        <v>3.77813386917114</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222255706787</v>
+        <v>3.73222231864929</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.84891486167908</v>
+        <v>3.8489146232605</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.7872314453125</v>
+        <v>4.78723096847534</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.45199108123779</v>
+        <v>5.45199060440063</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07895946502686</v>
+        <v>5.07895994186401</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851793289185</v>
+        <v>5.30851745605469</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373477935791</v>
+        <v>5.30373525619507</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.0550479888916</v>
+        <v>5.05504751205444</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417726516724</v>
+        <v>5.07417678833008</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>4.22768449783325</v>
+        <v>4.22768402099609</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559885025024</v>
+        <v>4.18559837341309</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942499160767</v>
+        <v>4.18942451477051</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550840377808</v>
+        <v>4.27550888061523</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.1167311668396</v>
+        <v>4.11673164367676</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603397369385</v>
+        <v>4.17603349685669</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472860336304</v>
+        <v>4.20472812652588</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02156972885132</v>
+        <v>5.02157020568848</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G103" t="n">
-        <v>4.95939874649048</v>
+        <v>4.95939922332764</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548311233521</v>
+        <v>5.04548263549805</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756622314453</v>
+        <v>7.74756574630737</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>7.25497436523438</v>
+        <v>7.25497388839722</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367588043213</v>
+        <v>7.06367635726929</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804136276245</v>
+        <v>6.52804183959961</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237419128418</v>
+        <v>6.98237466812134</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>6.79585838317871</v>
+        <v>6.79585886001587</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.38456869125366</v>
+        <v>6.3845682144165</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>5.83458709716797</v>
+        <v>5.83458662033081</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>5.87762928009033</v>
+        <v>5.87762880325317</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.0689263343811</v>
+        <v>6.06892681121826</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848112106323</v>
+        <v>6.40848016738892</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.35109090805054</v>
+        <v>6.3510913848877</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.35109090805054</v>
+        <v>6.3510913848877</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935136795044</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805288314819</v>
+        <v>6.19805335998535</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933664321899</v>
+        <v>6.82933616638184</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>7.16889047622681</v>
+        <v>7.16888999938965</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>6.97280979156494</v>
+        <v>6.97280931472778</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584686279297</v>
+        <v>7.12584781646729</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.92498445510864</v>
+        <v>6.9249849319458</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.8723783493042</v>
+        <v>6.87237787246704</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064521789551</v>
+        <v>6.69064426422119</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>6.97280979156494</v>
+        <v>6.97280931472778</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>7.03019905090332</v>
+        <v>7.03019857406616</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976392745972</v>
+        <v>7.03976345062256</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.33627557754517</v>
+        <v>7.33627605438232</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886375427246</v>
+        <v>7.93886423110962</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.0919017791748</v>
+        <v>8.09190368652344</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712837219238</v>
+        <v>7.86712789535522</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91017007827759</v>
+        <v>7.91016960144043</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.67104768753052</v>
+        <v>7.6710467338562</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>7.8432149887085</v>
+        <v>7.84321594238281</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234474182129</v>
+        <v>7.86234521865845</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626037597656</v>
+        <v>7.77626085281372</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.996253490448</v>
+        <v>7.99625396728516</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712373733521</v>
+        <v>7.97712421417236</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451347351074</v>
+        <v>8.03451251983643</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060424804688</v>
+        <v>7.90060377120972</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669645309448</v>
+        <v>7.76669597625732</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103937149048</v>
+        <v>7.89103889465332</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.89582204818726</v>
+        <v>7.89582252502441</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492698669434</v>
+        <v>8.6849250793457</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>9.00535011291504</v>
+        <v>9.00535106658936</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622772216797</v>
+        <v>8.76622676849365</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.4171085357666</v>
+        <v>8.41710758209229</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>8.46493244171143</v>
+        <v>8.46493434906006</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.2545051574707</v>
+        <v>8.25450706481934</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451572418213</v>
+        <v>7.9245171546936</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754734039307</v>
+        <v>8.29754829406738</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G192" t="n">
-        <v>8.43623828887939</v>
+        <v>8.43623733520508</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101680755615</v>
+        <v>8.55101776123047</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.06752109527588</v>
+        <v>9.0675220489502</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.10578155517578</v>
+        <v>9.1057825088501</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968887329102</v>
+        <v>9.23968982696533</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317497253418</v>
+        <v>9.05317401885986</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.13447570800781</v>
+        <v>9.1344747543335</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>9.51707172393799</v>
+        <v>9.5170726776123</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620338439941</v>
+        <v>9.53620147705078</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587827682495</v>
+        <v>10.3587837219238</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.2535705566406</v>
+        <v>10.2535696029663</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G215" t="n">
-        <v>11.200493812561</v>
+        <v>11.2004928588867</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518060684204</v>
+        <v>10.9518051147461</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.0431394577026</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.0431394577026</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831266403198</v>
+        <v>10.4831275939941</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8274631500244</v>
+        <v>10.8274621963501</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370275497437</v>
+        <v>10.837028503418</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.961371421814</v>
+        <v>10.9613704681396</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.1144104003906</v>
+        <v>11.1144094467163</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630971908569</v>
+        <v>11.3630962371826</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456912994385</v>
+        <v>11.7456932067871</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648229598999</v>
+        <v>11.7648220062256</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>11.6691741943359</v>
+        <v>11.6691732406616</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961057662964</v>
+        <v>12.3961067199707</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.6160984039307</v>
+        <v>12.616096496582</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169622421265</v>
+        <v>12.8169603347778</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717260360718</v>
+        <v>13.3717241287231</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446575164795</v>
+        <v>15.2446565628052</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272216796875</v>
+        <v>13.5272226333618</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>13.3246021270752</v>
+        <v>13.3246030807495</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>12.6878004074097</v>
+        <v>12.6877994537354</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8132295608521</v>
+        <v>12.8132305145264</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>13.1509284973145</v>
+        <v>13.1509294509888</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973794937134</v>
+        <v>13.7973804473877</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044082641602</v>
+        <v>13.6044092178345</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>13.8359727859497</v>
+        <v>13.835973739624</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921413421631</v>
+        <v>13.3921422958374</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869714736938</v>
+        <v>11.8869724273682</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G277" t="n">
-        <v>11.539626121521</v>
+        <v>11.5396270751953</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3756017684937</v>
+        <v>11.3756008148193</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>11.8676767349243</v>
+        <v>11.86767578125</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484483718872</v>
+        <v>10.7484474182129</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431409835815</v>
+        <v>11.4431400299072</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.250171661377</v>
+        <v>11.2501707077026</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.008957862854</v>
+        <v>11.0089588165283</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072355270386</v>
+        <v>10.5072345733643</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695356369019</v>
+        <v>10.1695375442505</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G303" t="n">
-        <v>11.7132997512817</v>
+        <v>11.7133007049561</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G306" t="n">
-        <v>11.7808389663696</v>
+        <v>11.7808399200439</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G307" t="n">
-        <v>11.587869644165</v>
+        <v>11.5878686904907</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054430007935</v>
+        <v>11.1054439544678</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334926605225</v>
+        <v>11.4334936141968</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220527648926</v>
+        <v>12.0220518112183</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G320" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640926361084</v>
+        <v>13.0640916824341</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044082641602</v>
+        <v>13.6044092178345</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693307876587</v>
+        <v>13.4693298339844</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552713394165</v>
+        <v>13.8552703857422</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807004928589</v>
+        <v>13.9807014465332</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.4920721054077</v>
+        <v>14.492073059082</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G345" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.405237197876</v>
+        <v>14.4052362442017</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824247360229</v>
+        <v>14.4824256896973</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386606216431</v>
+        <v>12.9386615753174</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.0062007904053</v>
+        <v>13.006199836731</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G366" t="n">
-        <v>12.7939348220825</v>
+        <v>12.7939338684082</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360420227051</v>
+        <v>12.7360429763794</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>12.726393699646</v>
+        <v>12.7263927459717</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755334854126</v>
+        <v>12.4755325317383</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150220870972</v>
+        <v>12.2150230407715</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474838256836</v>
+        <v>12.1474828720093</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194332122803</v>
+        <v>11.8194341659546</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G383" t="n">
-        <v>11.6940031051636</v>
+        <v>11.6940040588379</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325973510742</v>
+        <v>11.7325963973999</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966217041016</v>
+        <v>11.8966207504272</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G393" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.2439680099487</v>
+        <v>12.243968963623</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G399" t="n">
-        <v>12.7939348220825</v>
+        <v>12.7939338684082</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G400" t="n">
-        <v>12.649206161499</v>
+        <v>12.6492052078247</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228788375854</v>
+        <v>12.8228797912598</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115081787109</v>
+        <v>12.3115072250366</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193649291992</v>
+        <v>12.9193639755249</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>13.0544424057007</v>
+        <v>13.054443359375</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>13.2184677124023</v>
+        <v>13.2184686660767</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G434" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974477767944</v>
+        <v>12.6974496841431</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G439" t="n">
-        <v>12.649206161499</v>
+        <v>12.6492052078247</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>12.726393699646</v>
+        <v>12.7263927459717</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13</v>
       </c>
       <c r="G444" t="n">
-        <v>12.5430717468262</v>
+        <v>12.5430727005005</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044794082642</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G450" t="n">
-        <v>12.6781520843506</v>
+        <v>12.6781530380249</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3693981170654</v>
+        <v>12.3693990707397</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.8676767349243</v>
+        <v>11.86767578125</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044794082642</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1860780715942</v>
+        <v>12.1860771179199</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9834585189819</v>
+        <v>11.9834575653076</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>12.0895910263062</v>
+        <v>12.0895929336548</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308038711548</v>
+        <v>12.3308048248291</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747055053711</v>
+        <v>11.6747074127197</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554733276367</v>
+        <v>9.45554828643799</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625078201294</v>
+        <v>10.3625068664551</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107494354248</v>
+        <v>10.4107503890991</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764980316162</v>
+        <v>11.0764970779419</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.7195014953613</v>
+        <v>10.71950340271</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>10.9028253555298</v>
+        <v>10.9028234481812</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256359100342</v>
+        <v>10.8256368637085</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G494" t="n">
-        <v>10.9028253555298</v>
+        <v>10.9028234481812</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G496" t="n">
-        <v>10.9028253555298</v>
+        <v>10.9028234481812</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>10.8545827865601</v>
+        <v>10.8545818328857</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078971862793</v>
+        <v>10.7078981399536</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189531326294</v>
+        <v>10.2189521789551</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025415420532</v>
+        <v>10.5025405883789</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763519287109</v>
+        <v>10.7763500213623</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110445022583</v>
+        <v>11.0110454559326</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763519287109</v>
+        <v>10.7763500213623</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G521" t="n">
-        <v>10.8545827865601</v>
+        <v>10.8545818328857</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G529" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069620132446</v>
+        <v>10.3069629669189</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509357452393</v>
+        <v>9.50509262084961</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619869232178</v>
+        <v>9.45619964599609</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G551" t="n">
-        <v>9.20194816589355</v>
+        <v>9.20194721221924</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233818054199</v>
+        <v>8.74233913421631</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432834625244</v>
+        <v>8.65432929992676</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G556" t="n">
-        <v>8.53698062896729</v>
+        <v>8.5369815826416</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.8499059677124</v>
+        <v>8.84990692138672</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G577" t="n">
-        <v>9.20194816589355</v>
+        <v>9.20194721221924</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G580" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.1237154006958</v>
+        <v>9.12371635437012</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>8.94769477844238</v>
+        <v>8.9476957321167</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9</v>
       </c>
       <c r="G588" t="n">
-        <v>8.80101299285889</v>
+        <v>8.80101203918457</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211811065674</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G594" t="n">
-        <v>9.31929397583008</v>
+        <v>9.31929302215576</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G620" t="n">
-        <v>9.55398845672607</v>
+        <v>9.55398750305176</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>9.69089126586914</v>
+        <v>9.69089221954346</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233818054199</v>
+        <v>8.74233913421631</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548454284668</v>
+        <v>9.04548358917236</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835975646973</v>
+        <v>8.91835784912109</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52464962005615</v>
+        <v>9.52465057373047</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376552581787</v>
+        <v>9.56376647949219</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575664520264</v>
+        <v>9.47575569152832</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211811065674</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560436248779</v>
+        <v>8.15560531616211</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211811065674</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626934051514</v>
+        <v>8.12626838684082</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742458343506</v>
+        <v>8.51742362976074</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G722" t="n">
-        <v>8.73255920410156</v>
+        <v>8.73256015777588</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.6347713470459</v>
+        <v>8.63477039337158</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924385070801</v>
+        <v>8.87924289703369</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9</v>
       </c>
       <c r="G725" t="n">
-        <v>8.80101299285889</v>
+        <v>8.80101203918457</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902187347412</v>
+        <v>8.88902282714844</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G734" t="n">
-        <v>8.04803657531738</v>
+        <v>8.04803562164307</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262889862061</v>
+        <v>7.40262937545776</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>7.5</v>
       </c>
       <c r="G742" t="n">
-        <v>7.33417701721191</v>
+        <v>7.33417654037476</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.15815687179565</v>
+        <v>7.1581563949585</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G749" t="n">
-        <v>5.32950210571289</v>
+        <v>5.32950162887573</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834590911865</v>
+        <v>4.93834638595581</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.7134313583374</v>
+        <v>4.71343088150024</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760622024536</v>
+        <v>4.30760669708252</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10224914550781</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738567352295</v>
+        <v>4.31738519668579</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357671737671</v>
+        <v>4.04357624053955</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156077384949</v>
+        <v>3.91156101226807</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669706344604</v>
+        <v>4.12669658660889</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10224914550781</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691761016846</v>
+        <v>4.11691808700562</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502912521362</v>
+        <v>5.08502960205078</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.32950210571289</v>
+        <v>5.32950162887573</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G780" t="n">
-        <v>5.42729139328003</v>
+        <v>5.42729091644287</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.44684886932373</v>
+        <v>5.44684839248657</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485870361328</v>
+        <v>5.53485822677612</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G784" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773344039917</v>
+        <v>5.40773296356201</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928060531616</v>
+        <v>5.33928108215332</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.3001651763916</v>
+        <v>5.30016469955444</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215438842773</v>
+        <v>5.21215534210205</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166221618652</v>
+        <v>4.79166269302368</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834590911865</v>
+        <v>4.93834638595581</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>5.42729139328003</v>
+        <v>5.42729091644287</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220546722412</v>
+        <v>5.65220642089844</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441665649414</v>
+        <v>5.55441617965698</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G828" t="n">
-        <v>5.44684886932373</v>
+        <v>5.44684839248657</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264751434326</v>
+        <v>5.63264846801758</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>5.71087884902954</v>
+        <v>5.7108793258667</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>6.4736328125</v>
+        <v>6.47363328933716</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004487991333</v>
+        <v>6.19004535675049</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402521133423</v>
+        <v>6.01402473449707</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G835" t="n">
-        <v>6.06291913986206</v>
+        <v>6.06291961669922</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314064025879</v>
+        <v>6.05314111709595</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672857284546</v>
+        <v>6.33672904968262</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>6.48341274261475</v>
+        <v>6.48341226577759</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>6.43451738357544</v>
+        <v>6.4345178604126</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G843" t="n">
-        <v>6.48341274261475</v>
+        <v>6.48341226577759</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>6.09225654602051</v>
+        <v>6.09225606918335</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>6.41495943069458</v>
+        <v>6.41495990753174</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.14115047454834</v>
+        <v>6.1411509513855</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.00424575805664</v>
+        <v>6.0042462348938</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G855" t="n">
-        <v>5.92601490020752</v>
+        <v>5.92601537704468</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78911018371582</v>
+        <v>5.78911066055298</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955223083496</v>
+        <v>5.76955270767212</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977373123169</v>
+        <v>5.75977325439453</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021577835083</v>
+        <v>5.74021530151367</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>5.66198444366455</v>
+        <v>5.66198396682739</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>5.69132089614868</v>
+        <v>5.69132137298584</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>5.95535182952881</v>
+        <v>5.95535135269165</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G876" t="n">
-        <v>5.71087884902954</v>
+        <v>5.7108793258667</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>5.30994415283203</v>
+        <v>5.30994367599487</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G881" t="n">
-        <v>5.42729139328003</v>
+        <v>5.42729091644287</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G890" t="n">
-        <v>6.48341274261475</v>
+        <v>6.48341226577759</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987445831299</v>
+        <v>6.63987493515015</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700067520142</v>
+        <v>6.76700019836426</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655815124512</v>
+        <v>6.78655862808228</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G897" t="n">
-        <v>7.87201690673828</v>
+        <v>7.87201642990112</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489116668701</v>
+        <v>7.74489068984985</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G900" t="n">
-        <v>7.72533321380615</v>
+        <v>7.72533273696899</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G904" t="n">
-        <v>7.67643785476685</v>
+        <v>7.676438331604</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842849731445</v>
+        <v>7.58842802047729</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G910" t="n">
-        <v>6.95279932022095</v>
+        <v>6.95279979705811</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147270202637</v>
+        <v>7.01147317886353</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572418212891</v>
+        <v>7.26572465896606</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G919" t="n">
-        <v>6.71810579299927</v>
+        <v>6.71810626983643</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G920" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G921" t="n">
-        <v>6.71810579299927</v>
+        <v>6.71810626983643</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793537139893</v>
+        <v>7.16793489456177</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191522598267</v>
+        <v>6.99191570281982</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218685150146</v>
+        <v>7.42218732833862</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>7.5395336151123</v>
+        <v>7.53953409194946</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>7.5395336151123</v>
+        <v>7.53953409194946</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312154769897</v>
+        <v>7.82312202453613</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G951" t="n">
-        <v>9.31929397583008</v>
+        <v>9.31929302215576</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897174835205</v>
+        <v>8.44897270202637</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G961" t="n">
-        <v>8.16538333892822</v>
+        <v>8.16538429260254</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339412689209</v>
+        <v>8.25339317321777</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449924468994</v>
+        <v>8.20449829101562</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G970" t="n">
-        <v>8.16538333892822</v>
+        <v>8.16538429260254</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482051849365</v>
+        <v>9.07482147216797</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G979" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804315567017</v>
+        <v>11.4804306030273</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9107036590576</v>
+        <v>11.9107027053833</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G987" t="n">
-        <v>12.4387636184692</v>
+        <v>12.4387645721436</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G990" t="n">
-        <v>12.947265625</v>
+        <v>12.9472665786743</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926742553711</v>
+        <v>13.5926733016968</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G996" t="n">
-        <v>15.0790672302246</v>
+        <v>15.0790681838989</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705633163452</v>
+        <v>14.5705652236938</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.2823009490967</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.1258382797241</v>
+        <v>12.1258392333984</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867223739624</v>
+        <v>12.0867233276367</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.9668254852295</v>
+        <v>12.9668245315552</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5561103820801</v>
+        <v>12.5561113357544</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.3996486663818</v>
+        <v>12.3996496200562</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.3384237289429</v>
+        <v>13.3384227752686</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.8078107833862</v>
+        <v>13.8078098297119</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583215713501</v>
+        <v>12.4583206176758</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.2823009490967</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.2823009490967</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.715124130249</v>
+        <v>11.7151250839233</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.0476064682007</v>
+        <v>12.047607421875</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.3996486663818</v>
+        <v>12.3996496200562</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734571456909</v>
+        <v>12.6734580993652</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.184513092041</v>
+        <v>12.1845121383667</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.279748916626</v>
+        <v>13.2797498703003</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1057" t="n">
-        <v>10.5416574478149</v>
+        <v>10.5416564941406</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220994949341</v>
+        <v>10.5220985412598</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025415420532</v>
+        <v>10.5025405883789</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.80101299285889</v>
+        <v>8.80101203918457</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206703186035</v>
+        <v>8.31206798553467</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543441772461</v>
+        <v>8.60543346405029</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570652008057</v>
+        <v>9.03570556640625</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.3265218734741</v>
+        <v>10.3265209197998</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003303527832</v>
+        <v>10.6003293991089</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1094" t="n">
-        <v>13.3775396347046</v>
+        <v>13.3775386810303</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1097" t="n">
-        <v>13.8078107833862</v>
+        <v>13.8078098297119</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1098" t="n">
-        <v>13.9055986404419</v>
+        <v>13.9055995941162</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771978378296</v>
+        <v>14.2771987915039</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749866485596</v>
+        <v>14.3749856948853</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>15</v>
       </c>
       <c r="G1107" t="n">
-        <v>14.6683540344238</v>
+        <v>14.6683530807495</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.6683540344238</v>
+        <v>14.6683530807495</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181831359863</v>
+        <v>15.1181840896606</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396114349365</v>
+        <v>15.9396095275879</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666488647461</v>
+        <v>19.1666507720947</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.3890113830566</v>
+        <v>20.3890132904053</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981067657471</v>
+        <v>22.1981105804443</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.7580585479736</v>
+        <v>21.758056640625</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558464050293</v>
+        <v>21.8558483123779</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602687835693</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602687835693</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>21.3180084228516</v>
+        <v>21.3180065155029</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>20.6334857940674</v>
+        <v>20.6334838867188</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691116333008</v>
+        <v>21.2691135406494</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0561008453369</v>
+        <v>24.0560989379883</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538906097412</v>
+        <v>24.1538887023926</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>24.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.9583110809326</v>
+        <v>23.9583129882812</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.322681427002</v>
+        <v>23.3226833343506</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359485626221</v>
+        <v>22.7359504699707</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1173" t="n">
-        <v>22.4425811767578</v>
+        <v>22.4425830841064</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.5892639160156</v>
+        <v>22.5892658233643</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157943725586</v>
+        <v>21.4157962799072</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>21.7091655731201</v>
+        <v>21.7091636657715</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>21.0735340118408</v>
+        <v>21.0735321044922</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113739013672</v>
+        <v>21.6113758087158</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>21.7091655731201</v>
+        <v>21.7091636657715</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>21.0735340118408</v>
+        <v>21.0735321044922</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>21.0735340118408</v>
+        <v>21.0735321044922</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.3180084228516</v>
+        <v>21.3180065155029</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>21.7091655731201</v>
+        <v>21.7091636657715</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401165008545</v>
+        <v>20.3401184082031</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3890113830566</v>
+        <v>20.3890132904053</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511714935303</v>
+        <v>19.8511695861816</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.7533836364746</v>
+        <v>19.7533855438232</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.4038963317871</v>
+        <v>18.4038944244385</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1224" t="n">
-        <v>17.4651184082031</v>
+        <v>17.4651203155518</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1225" t="n">
-        <v>17.4651184082031</v>
+        <v>17.4651203155518</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521949768066</v>
+        <v>17.1521968841553</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.783148765564</v>
+        <v>15.7831478118896</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112087249756</v>
+        <v>16.3112106323242</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.3698825836182</v>
+        <v>16.3698806762695</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329769134521</v>
+        <v>16.2329788208008</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743068695068</v>
+        <v>16.1743049621582</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348491668701</v>
+        <v>17.0348472595215</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>18</v>
       </c>
       <c r="G1237" t="n">
-        <v>17.6020259857178</v>
+        <v>17.6020240783691</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304248809814</v>
+        <v>17.2304267883301</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108688354492</v>
+        <v>17.2108669281006</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1240" t="n">
-        <v>17.0739612579346</v>
+        <v>17.0739631652832</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.4038963317871</v>
+        <v>18.4038944244385</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1243" t="n">
-        <v>17.6411399841309</v>
+        <v>17.6411418914795</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042362213135</v>
+        <v>17.5042324066162</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.484676361084</v>
+        <v>17.4846782684326</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979434967041</v>
+        <v>16.8979454040527</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.5459022521973</v>
+        <v>16.5459041595459</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521949768066</v>
+        <v>17.1521968841553</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>12.8000001907349</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>56382</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>12.8400001525879</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -447,7 +447,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455669403076</v>
+        <v>6.71455764770508</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48500061035156</v>
+        <v>6.4850001335144</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44673919677734</v>
+        <v>6.44674015045166</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>5.71502590179443</v>
+        <v>5.71502542495728</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31330013275146</v>
+        <v>5.31329965591431</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84415197372437</v>
+        <v>5.84415149688721</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.74850273132324</v>
+        <v>5.7485032081604</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937297821045</v>
+        <v>5.72937250137329</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935041427612</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458389282227</v>
+        <v>5.94458341598511</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>6.18848752975464</v>
+        <v>6.1884880065918</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414781570435</v>
+        <v>5.95414733886719</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154443740845</v>
+        <v>5.79154491424561</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.70067882537842</v>
+        <v>5.70067834854126</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>5.27504014968872</v>
+        <v>5.27503967285156</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244781494141</v>
+        <v>4.78244876861572</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.6294093132019</v>
+        <v>4.62941026687622</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.06461238861084</v>
+        <v>5.06461191177368</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677375793457</v>
+        <v>5.45677328109741</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.3228645324707</v>
+        <v>5.32286500930786</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460870742798</v>
+        <v>5.17460918426514</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.97374677658081</v>
+        <v>4.97374582290649</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G45" t="n">
-        <v>4.68297338485718</v>
+        <v>4.68297386169434</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028051376343</v>
+        <v>4.61028003692627</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749671936035</v>
+        <v>4.62749719619751</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984539031982</v>
+        <v>4.61984443664551</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671644210815</v>
+        <v>4.55671691894531</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732414245605</v>
+        <v>4.58732461929321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G55" t="n">
-        <v>4.4228081703186</v>
+        <v>4.42280864715576</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985227584839</v>
+        <v>4.39985275268555</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.59200000762939</v>
       </c>
       <c r="G58" t="n">
-        <v>4.39220094680786</v>
+        <v>4.3922004699707</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>4.09377527236938</v>
+        <v>4.09377574920654</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916980743408</v>
+        <v>4.01916933059692</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793920516968</v>
+        <v>4.39793968200684</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202100753784</v>
+        <v>4.57202053070068</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871995925903</v>
+        <v>4.46871900558472</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.06508159637451</v>
+        <v>4.0650806427002</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265055656433</v>
+        <v>3.94265007972717</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691870689392</v>
+        <v>3.71691846847534</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987436294556</v>
+        <v>3.73987460136414</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813386917114</v>
+        <v>3.7781343460083</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463863372803</v>
+        <v>4.29463815689087</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723096847534</v>
+        <v>4.7872314453125</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07895994186401</v>
+        <v>5.07895946502686</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851745605469</v>
+        <v>5.308518409729</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.05504751205444</v>
+        <v>5.0550479888916</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417726516724</v>
+        <v>5.07417774200439</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>4.93548631668091</v>
+        <v>4.93548583984375</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653697967529</v>
+        <v>4.73653650283813</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680688858032</v>
+        <v>4.46680641174316</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>4.22768402099609</v>
+        <v>4.22768449783325</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559837341309</v>
+        <v>4.18559885025024</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G95" t="n">
-        <v>4.31376838684082</v>
+        <v>4.31376886367798</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16072940826416</v>
+        <v>4.16073036193848</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.1167311668396</v>
+        <v>4.11673164367676</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.2047290802002</v>
+        <v>4.20472812652588</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846477508545</v>
+        <v>4.29846429824829</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157068252563</v>
+        <v>5.02157020568848</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756574630737</v>
+        <v>7.74756622314453</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367588043213</v>
+        <v>7.06367635726929</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237466812134</v>
+        <v>6.98237419128418</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.3845682144165</v>
+        <v>6.38456869125366</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370948791504</v>
+        <v>6.07370853424072</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195426940918</v>
+        <v>6.55195379257202</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.06892681121826</v>
+        <v>6.0689263343811</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.625</v>
       </c>
       <c r="G128" t="n">
-        <v>6.33674383163452</v>
+        <v>6.33674335479736</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935041427612</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370948791504</v>
+        <v>6.07370853424072</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805335998535</v>
+        <v>6.19805288314819</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>7.16888952255249</v>
+        <v>7.16888999938965</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584733963013</v>
+        <v>7.12584686279297</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>6.96802711486816</v>
+        <v>6.96802663803101</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>6.99672174453735</v>
+        <v>6.9967212677002</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.9249849319458</v>
+        <v>6.92498445510864</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87237787246704</v>
+        <v>6.8723783493042</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064474105835</v>
+        <v>6.69064521789551</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976440429688</v>
+        <v>7.03976345062256</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.33627605438232</v>
+        <v>7.33627557754517</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886375427246</v>
+        <v>7.9388632774353</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712741851807</v>
+        <v>7.86712837219238</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>7.84321451187134</v>
+        <v>7.84321546554565</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234474182129</v>
+        <v>7.86234521865845</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626037597656</v>
+        <v>7.7762598991394</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712373733521</v>
+        <v>7.97712326049805</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451251983643</v>
+        <v>8.03451347351074</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.83364963531494</v>
+        <v>7.83365058898926</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669597625732</v>
+        <v>7.76669645309448</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492603302002</v>
+        <v>8.68492698669434</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622676849365</v>
+        <v>8.76622772216797</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65623188018799</v>
+        <v>8.65623092651367</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G179" t="n">
-        <v>8.35015487670898</v>
+        <v>8.35015296936035</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.17798519134521</v>
+        <v>8.17798709869385</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>8.20668125152588</v>
+        <v>8.20668029785156</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.25450611114502</v>
+        <v>8.2545051574707</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451667785645</v>
+        <v>7.92451620101929</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581195831299</v>
+        <v>8.22581100463867</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34058856964111</v>
+        <v>8.34058952331543</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.27363586425781</v>
+        <v>8.2736349105835</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G192" t="n">
-        <v>8.43623828887939</v>
+        <v>8.43623924255371</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92883110046387</v>
+        <v>8.92883014678955</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.0675220489502</v>
+        <v>9.06752109527588</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.1057825088501</v>
+        <v>9.10578155517578</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23969078063965</v>
+        <v>9.23968887329102</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708324432373</v>
+        <v>9.18708229064941</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882598876953</v>
+        <v>9.03882694244385</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.1727352142334</v>
+        <v>9.17273616790771</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185760498047</v>
+        <v>9.41185855865479</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>9.5170726776123</v>
+        <v>9.51707172393799</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620147705078</v>
+        <v>9.53620338439941</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.253568649292</v>
+        <v>10.2535696029663</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>11.1813650131226</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1813650131226</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.0431413650513</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.0431413650513</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370265960693</v>
+        <v>10.8370275497437</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.9613704681396</v>
+        <v>10.961371421814</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630962371826</v>
+        <v>11.3630971908569</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117858886719</v>
+        <v>11.6117849349976</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G227" t="n">
-        <v>11.5639591217041</v>
+        <v>11.5639600753784</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456932067871</v>
+        <v>11.7456912994385</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648220062256</v>
+        <v>11.7648229598999</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708980560303</v>
+        <v>12.0708990097046</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961067199707</v>
+        <v>12.3961057662964</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474189758301</v>
+        <v>12.1474170684814</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717250823975</v>
+        <v>13.3717260360718</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446565628052</v>
+        <v>15.2446575164795</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.038592338562</v>
+        <v>14.0385932922363</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>13.8456220626831</v>
+        <v>13.8456230163574</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8132305145264</v>
+        <v>12.8132295608521</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G256" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G264" t="n">
-        <v>14.1061305999756</v>
+        <v>14.1061315536499</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877311706543</v>
+        <v>13.78773021698</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973804473877</v>
+        <v>13.7973794937134</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>13.835973739624</v>
+        <v>13.8359727859497</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921413421631</v>
+        <v>13.3921422958374</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G280" t="n">
-        <v>11.665057182312</v>
+        <v>11.6650581359863</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>11.75</v>
       </c>
       <c r="G284" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.8063383102417</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>10.6809072494507</v>
+        <v>10.680908203125</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.729151725769</v>
+        <v>10.7291507720947</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431400299072</v>
+        <v>11.4431409835815</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.250171661377</v>
+        <v>11.2501707077026</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738803863525</v>
+        <v>10.8738794326782</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.0089588165283</v>
+        <v>11.008957862854</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072355270386</v>
+        <v>10.5072364807129</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695375442505</v>
+        <v>10.1695365905762</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>10.9124736785889</v>
+        <v>10.9124727249146</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273582458496</v>
+        <v>11.3273601531982</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G307" t="n">
-        <v>11.587869644165</v>
+        <v>11.5878686904907</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>11.75</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212257385254</v>
+        <v>11.2212247848511</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054439544678</v>
+        <v>11.1054420471191</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>11.5299787521362</v>
+        <v>11.5299777984619</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334936141968</v>
+        <v>11.4334926605225</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220518112183</v>
+        <v>12.0220527648926</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G320" t="n">
-        <v>12.1281862258911</v>
+        <v>12.1281852722168</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G322" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>11.9159183502197</v>
+        <v>11.915919303894</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640926361084</v>
+        <v>13.0640916824341</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693307876587</v>
+        <v>13.4693298339844</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.7105436325073</v>
+        <v>13.710542678833</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552694320679</v>
+        <v>13.8552713394165</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9806995391846</v>
+        <v>13.9807004928589</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>14.7815284729004</v>
+        <v>14.7815275192261</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.492073059082</v>
+        <v>14.4920721054077</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5692615509033</v>
+        <v>14.569260597229</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G347" t="n">
-        <v>14.5789098739624</v>
+        <v>14.5789089202881</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052362442017</v>
+        <v>14.405237197876</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G352" t="n">
-        <v>13.01584815979</v>
+        <v>13.0158491134644</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527219772339</v>
+        <v>12.5527210235596</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386615753174</v>
+        <v>12.9386606216431</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.8807697296143</v>
+        <v>12.8807716369629</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G357" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.006199836731</v>
+        <v>13.0062017440796</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.0447950363159</v>
+        <v>13.0447959899902</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755334854126</v>
+        <v>12.4755325317383</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4272890090942</v>
+        <v>12.4272899627686</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>11.9641618728638</v>
+        <v>11.9641599655151</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150230407715</v>
+        <v>12.2150220870972</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.147481918335</v>
+        <v>12.1474838256836</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185388565063</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1571311950684</v>
+        <v>12.1571321487427</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194332122803</v>
+        <v>11.8194341659546</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>11.9641618728638</v>
+        <v>11.9641599655151</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1281862258911</v>
+        <v>12.1281852722168</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G393" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.243968963623</v>
+        <v>12.2439670562744</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G398" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G400" t="n">
-        <v>12.649206161499</v>
+        <v>12.6492052078247</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>12.5623693466187</v>
+        <v>12.562370300293</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228797912598</v>
+        <v>12.8228788375854</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>13.0447950363159</v>
+        <v>13.0447959899902</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>12.5623693466187</v>
+        <v>12.562370300293</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G416" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193639755249</v>
+        <v>12.9193649291992</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>12.8904180526733</v>
+        <v>12.8904190063477</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>12.8807697296143</v>
+        <v>12.8807716369629</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G434" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G436" t="n">
-        <v>13.2088203430176</v>
+        <v>13.2088193893433</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974487304688</v>
+        <v>12.6974477767944</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G439" t="n">
-        <v>12.649206161499</v>
+        <v>12.6492052078247</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>12.6395568847656</v>
+        <v>12.6395578384399</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13</v>
       </c>
       <c r="G444" t="n">
-        <v>12.5430727005005</v>
+        <v>12.5430717468262</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1860771179199</v>
+        <v>12.1860780715942</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>12.1764278411865</v>
+        <v>12.1764287948608</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9834585189819</v>
+        <v>11.9834594726562</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>12.0895919799805</v>
+        <v>12.0895910263062</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185388565063</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308038711548</v>
+        <v>12.3308048248291</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G472" t="n">
-        <v>12.1764278411865</v>
+        <v>12.1764287948608</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.2246713638306</v>
+        <v>12.2246723175049</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747055053711</v>
+        <v>11.6747064590454</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554828643799</v>
+        <v>9.45554733276367</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816497802734</v>
+        <v>9.65816688537598</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625068664551</v>
+        <v>10.3625078201294</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107503890991</v>
+        <v>10.4107494354248</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>10.4203996658325</v>
+        <v>10.4203977584839</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.8063383102417</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G491" t="n">
-        <v>11.2791175842285</v>
+        <v>11.2791166305542</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256359100342</v>
+        <v>10.8256368637085</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545827865601</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078981399536</v>
+        <v>10.7078971862793</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189521789551</v>
+        <v>10.2189531326294</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612154006958</v>
+        <v>10.5612144470215</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763509750366</v>
+        <v>10.7763519287109</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763509750366</v>
+        <v>10.7763519287109</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G521" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545827865601</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>10.9328136444092</v>
+        <v>10.9328126907349</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G529" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634246826172</v>
+        <v>10.4634256362915</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069639205933</v>
+        <v>10.3069620132446</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509262084961</v>
+        <v>9.50509357452393</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619964599609</v>
+        <v>9.45619869232178</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G551" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G556" t="n">
-        <v>8.5369815826416</v>
+        <v>8.53698062896729</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.84990692138672</v>
+        <v>8.8499059677124</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>10.5</v>
       </c>
       <c r="G572" t="n">
-        <v>10.2678480148315</v>
+        <v>10.2678470611572</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G577" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>8.9476957321167</v>
+        <v>8.94769477844238</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9</v>
       </c>
       <c r="G588" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492362976074</v>
+        <v>9.95492267608643</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.75</v>
       </c>
       <c r="G605" t="n">
-        <v>9.5344295501709</v>
+        <v>9.53443050384521</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G623" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>9.69089221954346</v>
+        <v>9.69089126586914</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354640960693</v>
+        <v>9.57354545593262</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>9.13349533081055</v>
+        <v>9.13349437713623</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835880279541</v>
+        <v>8.91835975646973</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52465057373047</v>
+        <v>9.52464962005615</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376647949219</v>
+        <v>9.56376552581787</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G656" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437847137451</v>
+        <v>9.09437942504883</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956607818604</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>9.75</v>
       </c>
       <c r="G689" t="n">
-        <v>9.5344295501709</v>
+        <v>9.53443050384521</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575569152832</v>
+        <v>9.47575664520264</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G711" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560531616211</v>
+        <v>8.15560436248779</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G716" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626838684082</v>
+        <v>8.12626934051514</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G719" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742362976074</v>
+        <v>8.51742458343506</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G722" t="n">
-        <v>8.73256015777588</v>
+        <v>8.73255920410156</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.63477039337158</v>
+        <v>8.6347713470459</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9</v>
       </c>
       <c r="G725" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902282714844</v>
+        <v>8.88902187347412</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G734" t="n">
-        <v>8.04803562164307</v>
+        <v>8.04803657531738</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262937545776</v>
+        <v>7.40262889862061</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>6.86478900909424</v>
+        <v>6.8647894859314</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>7.5</v>
       </c>
       <c r="G742" t="n">
-        <v>7.33417654037476</v>
+        <v>7.33417701721191</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.1581563949585</v>
+        <v>7.15815687179565</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385431289673</v>
+        <v>6.46385478973389</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G748" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G749" t="n">
-        <v>5.32950162887573</v>
+        <v>5.32950210571289</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738519668579</v>
+        <v>4.31738567352295</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>4.29782819747925</v>
+        <v>4.29782772064209</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00934982299805</v>
+        <v>4.00935029983521</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156101226807</v>
+        <v>3.91156077384949</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.98001313209534</v>
+        <v>3.9800136089325</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669658660889</v>
+        <v>4.12669706344604</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630561828613</v>
+        <v>4.58630514144897</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502960205078</v>
+        <v>5.08502912521362</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055662155151</v>
+        <v>4.84055614471436</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.32950162887573</v>
+        <v>5.32950210571289</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G780" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G784" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928108215332</v>
+        <v>5.33928060531616</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016469955444</v>
+        <v>5.3001651763916</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.25</v>
       </c>
       <c r="G795" t="n">
-        <v>5.13392400741577</v>
+        <v>5.13392353057861</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171234130859</v>
+        <v>5.23171281814575</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>5.24149131774902</v>
+        <v>5.24149179458618</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215534210205</v>
+        <v>5.21215438842773</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166269302368</v>
+        <v>4.79166221618652</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>5.0459132194519</v>
+        <v>5.04591369628906</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220642089844</v>
+        <v>5.65220546722412</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441617965698</v>
+        <v>5.55441665649414</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264799118042</v>
+        <v>5.63264751434326</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>5.7108793258667</v>
+        <v>5.71087884902954</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>6.47363328933716</v>
+        <v>6.4736328125</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004535675049</v>
+        <v>6.19004487991333</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402473449707</v>
+        <v>6.01402521133423</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G835" t="n">
-        <v>6.06291961669922</v>
+        <v>6.06291913986206</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672904968262</v>
+        <v>6.33672857284546</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G840" t="n">
-        <v>6.73766326904297</v>
+        <v>6.73766374588013</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>6.4345178604126</v>
+        <v>6.43451738357544</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G843" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>6.09225606918335</v>
+        <v>6.09225654602051</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>6.41495990753174</v>
+        <v>6.41495943069458</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>6.08247709274292</v>
+        <v>6.08247661590576</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.14115142822266</v>
+        <v>6.14115047454834</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.0042462348938</v>
+        <v>6.00424575805664</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955270767212</v>
+        <v>5.76955223083496</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977325439453</v>
+        <v>5.75977373123169</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>5.60331058502197</v>
+        <v>5.60331106185913</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>5.82822608947754</v>
+        <v>5.82822561264038</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021530151367</v>
+        <v>5.74021577835083</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>5.66198396682739</v>
+        <v>5.66198444366455</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G868" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>5.69132137298584</v>
+        <v>5.69132089614868</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G876" t="n">
-        <v>5.7108793258667</v>
+        <v>5.71087884902954</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>5.30994367599487</v>
+        <v>5.30994415283203</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G881" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>6.53230619430542</v>
+        <v>6.53230667114258</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>6.65943193435669</v>
+        <v>6.65943241119385</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G890" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987493515015</v>
+        <v>6.63987445831299</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G897" t="n">
-        <v>7.87201642990112</v>
+        <v>7.87201690673828</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489068984985</v>
+        <v>7.74489116668701</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G900" t="n">
-        <v>7.72533273696899</v>
+        <v>7.72533321380615</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G902" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75466966629028</v>
+        <v>7.75466918945312</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G904" t="n">
-        <v>7.676438331604</v>
+        <v>7.67643785476685</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G905" t="n">
-        <v>7.73511171340942</v>
+        <v>7.73511123657227</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842802047729</v>
+        <v>7.58842849731445</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>7.39284992218018</v>
+        <v>7.39285039901733</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G908" t="n">
-        <v>7.64710140228271</v>
+        <v>7.64710187911987</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>7.41240787506104</v>
+        <v>7.41240835189819</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G910" t="n">
-        <v>6.95279979705811</v>
+        <v>6.95279932022095</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147317886353</v>
+        <v>7.01147270202637</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572465896606</v>
+        <v>7.26572418212891</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7</v>
       </c>
       <c r="G918" t="n">
-        <v>6.84523153305054</v>
+        <v>6.8452320098877</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412641525269</v>
+        <v>6.89412593841553</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191570281982</v>
+        <v>6.99191522598267</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218732833862</v>
+        <v>7.42218685150146</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G938" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312202453613</v>
+        <v>7.82312154769897</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G946" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G949" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>8.5956563949585</v>
+        <v>8.59565544128418</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897270202637</v>
+        <v>8.44897174835205</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37073993682861</v>
+        <v>8.37074089050293</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G961" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339317321777</v>
+        <v>8.25339412689209</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>8.45875072479248</v>
+        <v>8.45874977111816</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G970" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482147216797</v>
+        <v>9.07482051849365</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.49531364440918</v>
+        <v>9.4953145980835</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>9.24106216430664</v>
+        <v>9.24106311798096</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956607818604</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G979" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804306030273</v>
+        <v>11.4804315567017</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G987" t="n">
-        <v>12.4387645721436</v>
+        <v>12.4387636184692</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G990" t="n">
-        <v>12.9472665786743</v>
+        <v>12.947265625</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926733016968</v>
+        <v>13.5926742553711</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705642700195</v>
+        <v>14.5705633163452</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.3188638687134</v>
+        <v>13.3188648223877</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.0059413909912</v>
+        <v>13.0059404373169</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.2823028564453</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.1258392333984</v>
+        <v>12.1258382797241</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.9668245315552</v>
+        <v>12.9668254852295</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.5365533828735</v>
+        <v>12.5365524291992</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.3384227752686</v>
+        <v>13.3384237289429</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.5952253341675</v>
+        <v>12.5952262878418</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583206176758</v>
+        <v>12.4583215713501</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.2823028564453</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.2823028564453</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.7151250839233</v>
+        <v>11.715124130249</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.047607421875</v>
+        <v>12.0476064682007</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734580993652</v>
+        <v>12.6734571456909</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.1845121383667</v>
+        <v>12.184513092041</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.4192066192627</v>
+        <v>12.4192056655884</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409738540649</v>
+        <v>12.3409748077393</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.2797498703003</v>
+        <v>13.279748916626</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1057" t="n">
-        <v>10.5416564941406</v>
+        <v>10.5416574478149</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.2091732025146</v>
+        <v>10.209174156189</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206798553467</v>
+        <v>8.31206703186035</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543346405029</v>
+        <v>8.60543441772461</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570556640625</v>
+        <v>9.03570652008057</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003293991089</v>
+        <v>10.6003303527832</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.1819591522217</v>
+        <v>13.181960105896</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1094" t="n">
-        <v>13.3775386810303</v>
+        <v>13.3775396347046</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1097" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1098" t="n">
-        <v>13.9055995941162</v>
+        <v>13.9055986404419</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>13.8273687362671</v>
+        <v>13.8273677825928</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771987915039</v>
+        <v>14.2771978378296</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>14.4532165527344</v>
+        <v>14.4532175064087</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030475616455</v>
+        <v>14.9030466079712</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.7074689865112</v>
+        <v>14.7074699401855</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>15</v>
       </c>
       <c r="G1107" t="n">
-        <v>14.6683530807495</v>
+        <v>14.6683540344238</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.6683530807495</v>
+        <v>14.6683540344238</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181840896606</v>
+        <v>15.1181831359863</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396104812622</v>
+        <v>15.9396114349365</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666507720947</v>
+        <v>19.1666488647461</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981086730957</v>
+        <v>22.1981067657471</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>21.1713237762451</v>
+        <v>21.1713218688965</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558483123779</v>
+        <v>21.8558464050293</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>21.3180065155029</v>
+        <v>21.3180084228516</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>20.6334838867188</v>
+        <v>20.6334857940674</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691135406494</v>
+        <v>21.2691116333008</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>21.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>20.7801685333252</v>
+        <v>20.7801666259766</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>21</v>
       </c>
       <c r="G1152" t="n">
-        <v>20.5356960296631</v>
+        <v>20.5356941223145</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0560989379883</v>
+        <v>24.0561008453369</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538887023926</v>
+        <v>24.1538906097412</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.3226833343506</v>
+        <v>23.322681427002</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7848415374756</v>
+        <v>22.7848434448242</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359504699707</v>
+        <v>22.7359485626221</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1173" t="n">
-        <v>22.4425830841064</v>
+        <v>22.4425811767578</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.5892658233643</v>
+        <v>22.5892639160156</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.5403671264648</v>
+        <v>22.5403690338135</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157962799072</v>
+        <v>21.4157943725586</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113758087158</v>
+        <v>21.6113739013672</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.3180065155029</v>
+        <v>21.3180084228516</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.9268493652344</v>
+        <v>20.926851272583</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401184082031</v>
+        <v>20.3401165008545</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470928192139</v>
+        <v>19.1470909118652</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.2669906616211</v>
+        <v>18.2669887542725</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1224" t="n">
-        <v>17.4651203155518</v>
+        <v>17.4651184082031</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1225" t="n">
-        <v>17.4651203155518</v>
+        <v>17.4651184082031</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.7831478118896</v>
+        <v>15.783148765564</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112106323242</v>
+        <v>16.3112087249756</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.917501449585</v>
+        <v>16.9174995422363</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348472595215</v>
+        <v>17.0348491668701</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>18</v>
       </c>
       <c r="G1237" t="n">
-        <v>17.6020240783691</v>
+        <v>17.6020259857178</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108669281006</v>
+        <v>17.2108688354492</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1240" t="n">
-        <v>17.0739631652832</v>
+        <v>17.0739612579346</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1241" t="n">
-        <v>17.0544052124023</v>
+        <v>17.054407119751</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1243" t="n">
-        <v>17.6411418914795</v>
+        <v>17.6411399841309</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042343139648</v>
+        <v>17.5042362213135</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979454040527</v>
+        <v>16.8979434967041</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761734008789</v>
+        <v>16.9761753082275</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414798736572</v>
+        <v>16.7414817810059</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>19.5948181152344</v>
+        <v>19.594820022583</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6342849731445</v>
+        <v>19.6342830657959</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.5750846862793</v>
+        <v>19.5750865936279</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>18.5687046051025</v>
+        <v>18.5687065124512</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.3777561187744</v>
+        <v>19.3777542114258</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1294" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>19.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>19.2396240234375</v>
+        <v>19.2396259307861</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.7132167816162</v>
+        <v>19.7132148742676</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.5089130401611</v>
+        <v>21.5089149475098</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>21.1635875701904</v>
+        <v>21.1635894775391</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.8182601928711</v>
+        <v>20.8182621002197</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.6737499237061</v>
+        <v>19.6737518310547</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.6145515441895</v>
+        <v>19.6145496368408</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>23.75</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.4328784942627</v>
+        <v>23.4328765869141</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>22.2982311248779</v>
+        <v>22.2982330322266</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>21.2622509002686</v>
+        <v>21.2622528076172</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>22.8902225494385</v>
+        <v>22.8902206420898</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1340" t="n">
-        <v>26.1856231689453</v>
+        <v>26.1856250762939</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1349" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G1354" t="n">
-        <v>23.14674949646</v>
+        <v>23.1467475891113</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.71262550354</v>
+        <v>22.7126235961914</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.008617401123</v>
+        <v>23.0086193084717</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1361" t="n">
-        <v>23.5216770172119</v>
+        <v>23.5216751098633</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1365" t="n">
-        <v>24.6464538574219</v>
+        <v>24.6464519500732</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1373" t="n">
-        <v>24.902982711792</v>
+        <v>24.9029808044434</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>24.7648506164551</v>
+        <v>24.7648525238037</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1375" t="n">
-        <v>24.4096565246582</v>
+        <v>24.4096584320068</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1376" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1379" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.2250900268555</v>
+        <v>26.2250881195068</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1384" t="n">
-        <v>28.4351806640625</v>
+        <v>28.4351787567139</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1391" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1393" t="n">
-        <v>24.6267204284668</v>
+        <v>24.6267185211182</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>24.6069869995117</v>
+        <v>24.6069889068604</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>24.7253856658936</v>
+        <v>24.7253837585449</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>24.1531276702881</v>
+        <v>24.1531295776367</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1408" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3899250030518</v>
+        <v>24.3899230957031</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.3307247161865</v>
+        <v>24.3307266235352</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.3440799713135</v>
+        <v>23.3440780639648</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>24.6859188079834</v>
+        <v>24.685920715332</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>26.3434867858887</v>
+        <v>26.3434886932373</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.0341415405273</v>
+        <v>27.0341396331787</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>28.4154453277588</v>
+        <v>28.4154472351074</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>29.6980876922607</v>
+        <v>29.6980895996094</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1446" t="n">
-        <v>29.7770195007324</v>
+        <v>29.7770214080811</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1448" t="n">
-        <v>30.3295421600342</v>
+        <v>30.3295440673828</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>30.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>30.0927467346191</v>
+        <v>30.0927486419678</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.4218254089355</v>
+        <v>29.4218273162842</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G1465" t="n">
-        <v>35.8547668457031</v>
+        <v>35.8547706604004</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>39.0712394714355</v>
+        <v>39.0712356567383</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1469" t="n">
-        <v>36.2691612243652</v>
+        <v>36.269157409668</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>40.3538856506348</v>
+        <v>40.3538818359375</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>42.6599998474121</v>
       </c>
       <c r="G1475" t="n">
-        <v>42.0903816223145</v>
+        <v>42.0903778076172</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>42.2482452392578</v>
+        <v>42.2482414245605</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1477" t="n">
-        <v>42.5837059020996</v>
+        <v>42.5837020874023</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>43.0178260803223</v>
+        <v>43.0178298950195</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>42.6231727600098</v>
+        <v>42.6231689453125</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>43</v>
       </c>
       <c r="G1480" t="n">
-        <v>42.4258422851562</v>
+        <v>42.425838470459</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.2615928649902</v>
+        <v>41.2615966796875</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>42.6399993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.0706481933594</v>
+        <v>42.0706443786621</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1492" t="n">
-        <v>45.5831146240234</v>
+        <v>45.5831108093262</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>38.4199981689453</v>
       </c>
       <c r="G1493" t="n">
-        <v>37.9069900512695</v>
+        <v>37.9069938659668</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1495" t="n">
-        <v>32.6185684204102</v>
+        <v>32.6185646057129</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1500" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1504" t="n">
-        <v>31.0201950073242</v>
+        <v>31.0201969146729</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>31.3951225280762</v>
+        <v>31.3951206207275</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1508" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>12.8999996185303</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>49332</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>12.7200002670288</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>11.4399995803833</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>11.5</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>16628</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>11.7200002670288</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>11.539999961853</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>11.539999961853</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>11.6599998474121</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>5957</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>11.5799999237061</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>11.5799999237061</v>
       </c>
       <c r="D2737" t="n">
-        <v>11.4399995803833</v>
+        <v>11.4200000762939</v>
       </c>
       <c r="E2737" t="n">
         <v>11.5</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>11.4200000762939</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>7655</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>11.5200004577637</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>11.2200002670288</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>11.3999996185303</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>11.2600002288818</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>11138</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>11.539999961853</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>23939</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>11.0200004577637</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>11.0200004577637</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>11.1599998474121</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>6.84846544265747</v>
+        <v>6.84846591949463</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455717086792</v>
+        <v>6.71455764770508</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48500061035156</v>
+        <v>6.4850001335144</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4467396736145</v>
+        <v>6.44674015045166</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544998168945</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3319616317749</v>
+        <v>6.33196115493774</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544998168945</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546054840088</v>
+        <v>5.70546102523804</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>5.71502590179443</v>
+        <v>5.71502542495728</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31329917907715</v>
+        <v>5.31329965591431</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84415149688721</v>
+        <v>5.84415197372437</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.74850273132324</v>
+        <v>5.7485032081604</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937297821045</v>
+        <v>5.72937250137329</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.02588510513306</v>
+        <v>6.0258846282959</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935136795044</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>6.00197219848633</v>
+        <v>6.00197267532349</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9541482925415</v>
+        <v>5.95414733886719</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458709716797</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7006778717041</v>
+        <v>5.70067834854126</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>5.27504062652588</v>
+        <v>5.27504014968872</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244829177856</v>
+        <v>4.78244876861572</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679216384888</v>
+        <v>4.90679168701172</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62940979003906</v>
+        <v>4.62941026687622</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.064612865448</v>
+        <v>5.06461238861084</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677328109741</v>
+        <v>5.45677375793457</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.75</v>
       </c>
       <c r="G37" t="n">
-        <v>5.49981498718262</v>
+        <v>5.49981546401978</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.3228645324707</v>
+        <v>5.32286500930786</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844957351685</v>
+        <v>4.73844909667969</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G45" t="n">
-        <v>4.68297290802002</v>
+        <v>4.68297338485718</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749624252319</v>
+        <v>4.62749671936035</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>4.63897466659546</v>
+        <v>4.6389741897583</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984491348267</v>
+        <v>4.61984443664551</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671691894531</v>
+        <v>4.55671644210815</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732414245605</v>
+        <v>4.58732461929321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G53" t="n">
-        <v>4.53184747695923</v>
+        <v>4.53184795379639</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G54" t="n">
-        <v>4.53184747695923</v>
+        <v>4.53184795379639</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G55" t="n">
-        <v>4.42280864715576</v>
+        <v>4.4228081703186</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985227584839</v>
+        <v>4.39985275268555</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.59200000762939</v>
       </c>
       <c r="G58" t="n">
-        <v>4.39219999313354</v>
+        <v>4.3922004699707</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.2391619682312</v>
+        <v>4.23916244506836</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>4.0937762260437</v>
+        <v>4.09377574920654</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916980743408</v>
+        <v>4.01916933059692</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793920516968</v>
+        <v>4.39793968200684</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202053070068</v>
+        <v>4.57202100753784</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871995925903</v>
+        <v>4.46871900558472</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.06508159637451</v>
+        <v>4.0650806427002</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265055656433</v>
+        <v>3.94265007972717</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691846847534</v>
+        <v>3.71691870689392</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>3.80682873725891</v>
+        <v>3.80682897567749</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813386917114</v>
+        <v>3.77813410758972</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8489146232605</v>
+        <v>3.84891486167908</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463863372803</v>
+        <v>4.29463815689087</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723049163818</v>
+        <v>4.7872314453125</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07895994186401</v>
+        <v>5.07895946502686</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851745605469</v>
+        <v>5.30851793289185</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373525619507</v>
+        <v>5.30373477935791</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>5.12200212478638</v>
+        <v>5.12200164794922</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.05504751205444</v>
+        <v>5.0550479888916</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653697967529</v>
+        <v>4.73653650283813</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G90" t="n">
-        <v>4.38646078109741</v>
+        <v>4.38646125793457</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942403793335</v>
+        <v>4.18942499160767</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16072940826416</v>
+        <v>4.16072988510132</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.11673164367676</v>
+        <v>4.1167311668396</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472812652588</v>
+        <v>4.20472860336304</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157068252563</v>
+        <v>5.02156972885132</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113971710205</v>
+        <v>4.92113924026489</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548263549805</v>
+        <v>5.04548311233521</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G105" t="n">
-        <v>5.40894985198975</v>
+        <v>5.40894937515259</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>7.25497388839722</v>
+        <v>7.25497436523438</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367635726929</v>
+        <v>7.06367588043213</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804088592529</v>
+        <v>6.52804136276245</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>6.79585933685303</v>
+        <v>6.79585838317871</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.3845682144165</v>
+        <v>6.38456869125366</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718215942383</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718215942383</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458709716797</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370853424072</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325227737427</v>
+        <v>6.74325180053711</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195379257202</v>
+        <v>6.55195426940918</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848064422607</v>
+        <v>6.40848112106323</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.625</v>
       </c>
       <c r="G128" t="n">
-        <v>6.33674430847168</v>
+        <v>6.33674383163452</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935136795044</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370853424072</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>6.63803863525391</v>
+        <v>6.63803815841675</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933521270752</v>
+        <v>6.82933664321899</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>7.16888999938965</v>
+        <v>7.16889047622681</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>6.97280931472778</v>
+        <v>6.97280979156494</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584733963013</v>
+        <v>7.12584686279297</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>7.05889320373535</v>
+        <v>7.05889368057251</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>6.95846176147461</v>
+        <v>6.95846223831177</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>6.99672222137451</v>
+        <v>6.99672174453735</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.9249849319458</v>
+        <v>6.92498445510864</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87237787246704</v>
+        <v>6.8723783493042</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064426422119</v>
+        <v>6.69064521789551</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>6.97280931472778</v>
+        <v>6.97280979156494</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>7.03019857406616</v>
+        <v>7.03019905090332</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886423110962</v>
+        <v>7.93886375427246</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.09190273284912</v>
+        <v>8.0919017791748</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712694168091</v>
+        <v>7.86712837219238</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91017055511475</v>
+        <v>7.91017007827759</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.67104721069336</v>
+        <v>7.67104768753052</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>7.84321594238281</v>
+        <v>7.8432149887085</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.99625301361084</v>
+        <v>7.996253490448</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712326049805</v>
+        <v>7.97712373733521</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451251983643</v>
+        <v>8.03451347351074</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060520172119</v>
+        <v>7.90060424804688</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669549942017</v>
+        <v>7.76669645309448</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.8958215713501</v>
+        <v>7.89582204818726</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492603302002</v>
+        <v>8.68492698669434</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65623092651367</v>
+        <v>8.65623188018799</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.41710948944092</v>
+        <v>8.4171085357666</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>8.46493339538574</v>
+        <v>8.46493244171143</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.25450611114502</v>
+        <v>8.2545051574707</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581005096436</v>
+        <v>8.22581100463867</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34059047698975</v>
+        <v>8.34058952331543</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754829406738</v>
+        <v>8.29754734039307</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G192" t="n">
-        <v>8.43623924255371</v>
+        <v>8.43623828887939</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92883110046387</v>
+        <v>8.92883014678955</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.1057825088501</v>
+        <v>9.10578155517578</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968982696533</v>
+        <v>9.23968887329102</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708419799805</v>
+        <v>9.18708229064941</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.1727352142334</v>
+        <v>9.17273616790771</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185760498047</v>
+        <v>9.41185855865479</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620147705078</v>
+        <v>9.53620338439941</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587837219238</v>
+        <v>10.3587827682495</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.2535696029663</v>
+        <v>10.2535705566406</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>11.1813631057739</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1813631057739</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518051147461</v>
+        <v>10.9518060684204</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.0431413650513</v>
+        <v>10.0431394577026</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.0431413650513</v>
+        <v>10.0431394577026</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831256866455</v>
+        <v>10.4831266403198</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.1144094467163</v>
+        <v>11.1144104003906</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G227" t="n">
-        <v>11.5639600753784</v>
+        <v>11.5639591217041</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456922531128</v>
+        <v>11.7456912994385</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648239135742</v>
+        <v>11.7648229598999</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>11.6691732406616</v>
+        <v>11.6691741943359</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708999633789</v>
+        <v>12.0708990097046</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474170684814</v>
+        <v>12.1474180221558</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169612884521</v>
+        <v>12.8169622421265</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717241287231</v>
+        <v>13.3717260360718</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>13.8456230163574</v>
+        <v>13.8456220626831</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>12.6877994537354</v>
+        <v>12.6878004074097</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8132305145264</v>
+        <v>12.8132295608521</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>13.1509294509888</v>
+        <v>13.1509284973145</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000663757324</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.5</v>
       </c>
       <c r="G260" t="n">
-        <v>13.0254974365234</v>
+        <v>13.0254983901978</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.9869041442871</v>
+        <v>12.9869031906128</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G264" t="n">
-        <v>14.1061325073242</v>
+        <v>14.1061315536499</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877321243286</v>
+        <v>13.7877311706543</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044101715088</v>
+        <v>13.6044082641602</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921422958374</v>
+        <v>13.3921413421631</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869724273682</v>
+        <v>11.8869714736938</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.288763999939</v>
+        <v>11.2887659072876</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.288763999939</v>
+        <v>11.2887659072876</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.8063402175903</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.7291498184204</v>
+        <v>10.7291507720947</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431400299072</v>
+        <v>11.4431409835815</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738784790039</v>
+        <v>10.8738794326782</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G295" t="n">
-        <v>10.844934463501</v>
+        <v>10.8449335098267</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072345733643</v>
+        <v>10.5072355270386</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695365905762</v>
+        <v>10.1695356369019</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G303" t="n">
-        <v>11.7133007049561</v>
+        <v>11.7132997512817</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.436939239502</v>
+        <v>12.4369382858276</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606470108032</v>
+        <v>12.0606460571289</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G306" t="n">
-        <v>11.7808399200439</v>
+        <v>11.7808389663696</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054439544678</v>
+        <v>11.1054430007935</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334936141968</v>
+        <v>11.4334926605225</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220537185669</v>
+        <v>12.0220527648926</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606470108032</v>
+        <v>12.0606460571289</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G322" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>11.9159202575684</v>
+        <v>11.915919303894</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640916824341</v>
+        <v>13.0640926361084</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044101715088</v>
+        <v>13.6044082641602</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693288803101</v>
+        <v>13.4693307876587</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552694320679</v>
+        <v>13.8552713394165</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8745679855347</v>
+        <v>13.8745670318604</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>14.75</v>
       </c>
       <c r="G341" t="n">
-        <v>14.2315626144409</v>
+        <v>14.2315635681152</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.492073059082</v>
+        <v>14.4920721054077</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G345" t="n">
-        <v>14.5113697052002</v>
+        <v>14.5113706588745</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.5113697052002</v>
+        <v>14.5113706588745</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052362442017</v>
+        <v>14.405237197876</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824237823486</v>
+        <v>14.4824247360229</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G351" t="n">
-        <v>13.9999990463257</v>
+        <v>13.9999980926514</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386625289917</v>
+        <v>12.9386606216431</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000663757324</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.006199836731</v>
+        <v>13.0062007904053</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G366" t="n">
-        <v>12.7939338684082</v>
+        <v>12.7939348220825</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4272909164429</v>
+        <v>12.4272899627686</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150230407715</v>
+        <v>12.2150220870972</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474828720093</v>
+        <v>12.1474838256836</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176425933838</v>
+        <v>12.4176416397095</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194341659546</v>
+        <v>11.8194332122803</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>11.6843528747559</v>
+        <v>11.6843538284302</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325963973999</v>
+        <v>11.7325973510742</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G386" t="n">
-        <v>11.6843528747559</v>
+        <v>11.6843538284302</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966207504272</v>
+        <v>11.8966217041016</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G393" t="n">
-        <v>12.1378345489502</v>
+        <v>12.1378355026245</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545125961304</v>
+        <v>11.9545135498047</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G399" t="n">
-        <v>12.7939338684082</v>
+        <v>12.7939348220825</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228797912598</v>
+        <v>12.8228788375854</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483089447021</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115072250366</v>
+        <v>12.3115081787109</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193639755249</v>
+        <v>12.9193649291992</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G419" t="n">
-        <v>12.9869041442871</v>
+        <v>12.9869031906128</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>13.054443359375</v>
+        <v>13.0544424057007</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483089447021</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167453765869</v>
+        <v>12.7167463302612</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483089447021</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>13.2184686660767</v>
+        <v>13.2184677124023</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>13.1798753738403</v>
+        <v>13.179874420166</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G434" t="n">
-        <v>13.8745679855347</v>
+        <v>13.8745670318604</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974487304688</v>
+        <v>12.6974477767944</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13</v>
       </c>
       <c r="G444" t="n">
-        <v>12.5430727005005</v>
+        <v>12.5430717468262</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3694000244141</v>
+        <v>12.3693981170654</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1860771179199</v>
+        <v>12.1860780715942</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>12.0895919799805</v>
+        <v>12.0895910263062</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1378345489502</v>
+        <v>12.1378355026245</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308048248291</v>
+        <v>12.3308038711548</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>12.1088886260986</v>
+        <v>12.1088895797729</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747064590454</v>
+        <v>11.6747055053711</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816497802734</v>
+        <v>9.65816593170166</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711185455322</v>
+        <v>9.68711090087891</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923490524292</v>
+        <v>10.0923480987549</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625068664551</v>
+        <v>10.3625078201294</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107503890991</v>
+        <v>10.4107494354248</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.8063402175903</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764970779419</v>
+        <v>11.0764980316162</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.7195024490356</v>
+        <v>10.7195014953613</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G490" t="n">
-        <v>11.4527902603149</v>
+        <v>11.4527893066406</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G491" t="n">
-        <v>11.2791156768799</v>
+        <v>11.2791166305542</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256368637085</v>
+        <v>10.8256359100342</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545827865601</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078981399536</v>
+        <v>10.7078971862793</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189521789551</v>
+        <v>10.2189531326294</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763519287109</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110454559326</v>
+        <v>11.0110445022583</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763519287109</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G521" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545827865601</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G529" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069629669189</v>
+        <v>10.3069620132446</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509262084961</v>
+        <v>9.50509357452393</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619964599609</v>
+        <v>9.45619869232178</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G551" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432929992676</v>
+        <v>8.65432834625244</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G556" t="n">
-        <v>8.5369815826416</v>
+        <v>8.53698062896729</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.84990692138672</v>
+        <v>8.8499059677124</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G577" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G580" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12371635437012</v>
+        <v>9.1237154006958</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>8.9476957321167</v>
+        <v>8.94769477844238</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9</v>
       </c>
       <c r="G588" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G594" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G620" t="n">
-        <v>9.55398750305176</v>
+        <v>9.55398845672607</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>9.69089221954346</v>
+        <v>9.69089126586914</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548358917236</v>
+        <v>9.04548454284668</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835784912109</v>
+        <v>8.91835975646973</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52465057373047</v>
+        <v>9.52464962005615</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376647949219</v>
+        <v>9.56376552581787</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575569152832</v>
+        <v>9.47575664520264</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560531616211</v>
+        <v>8.15560436248779</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211811065674</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626838684082</v>
+        <v>8.12626934051514</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742362976074</v>
+        <v>8.51742458343506</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G722" t="n">
-        <v>8.73256015777588</v>
+        <v>8.73255920410156</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.63477039337158</v>
+        <v>8.6347713470459</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924289703369</v>
+        <v>8.87924385070801</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9</v>
       </c>
       <c r="G725" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902282714844</v>
+        <v>8.88902187347412</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G734" t="n">
-        <v>8.04803562164307</v>
+        <v>8.04803657531738</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262937545776</v>
+        <v>7.40262889862061</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>7.5</v>
       </c>
       <c r="G742" t="n">
-        <v>7.33417654037476</v>
+        <v>7.33417701721191</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.1581563949585</v>
+        <v>7.15815687179565</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G749" t="n">
-        <v>5.32950162887573</v>
+        <v>5.32950210571289</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.71343088150024</v>
+        <v>4.7134313583374</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760669708252</v>
+        <v>4.30760622024536</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738519668579</v>
+        <v>4.31738567352295</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357624053955</v>
+        <v>4.04357671737671</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156101226807</v>
+        <v>3.91156077384949</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669658660889</v>
+        <v>4.12669706344604</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691808700562</v>
+        <v>4.11691761016846</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502960205078</v>
+        <v>5.08502912521362</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.32950162887573</v>
+        <v>5.32950210571289</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G780" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485822677612</v>
+        <v>5.53485870361328</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G784" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773296356201</v>
+        <v>5.40773344039917</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928108215332</v>
+        <v>5.33928060531616</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016469955444</v>
+        <v>5.3001651763916</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215534210205</v>
+        <v>5.21215438842773</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166269302368</v>
+        <v>4.79166221618652</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220642089844</v>
+        <v>5.65220546722412</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441617965698</v>
+        <v>5.55441665649414</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G828" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264846801758</v>
+        <v>5.63264751434326</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>5.7108793258667</v>
+        <v>5.71087884902954</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>6.47363328933716</v>
+        <v>6.4736328125</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004535675049</v>
+        <v>6.19004487991333</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402473449707</v>
+        <v>6.01402521133423</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G835" t="n">
-        <v>6.06291961669922</v>
+        <v>6.06291913986206</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314111709595</v>
+        <v>6.05314064025879</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672904968262</v>
+        <v>6.33672857284546</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>6.4345178604126</v>
+        <v>6.43451738357544</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G843" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>6.09225606918335</v>
+        <v>6.09225654602051</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>6.41495990753174</v>
+        <v>6.41495943069458</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.1411509513855</v>
+        <v>6.14115047454834</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.0042462348938</v>
+        <v>6.00424575805664</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G855" t="n">
-        <v>5.92601537704468</v>
+        <v>5.92601490020752</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78911066055298</v>
+        <v>5.78911018371582</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955270767212</v>
+        <v>5.76955223083496</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977325439453</v>
+        <v>5.75977373123169</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021530151367</v>
+        <v>5.74021577835083</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>5.66198396682739</v>
+        <v>5.66198444366455</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>5.69132137298584</v>
+        <v>5.69132089614868</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>5.95535135269165</v>
+        <v>5.95535182952881</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G876" t="n">
-        <v>5.7108793258667</v>
+        <v>5.71087884902954</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>5.30994367599487</v>
+        <v>5.30994415283203</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G881" t="n">
-        <v>5.42729091644287</v>
+        <v>5.42729139328003</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G890" t="n">
-        <v>6.48341226577759</v>
+        <v>6.48341274261475</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987493515015</v>
+        <v>6.63987445831299</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700019836426</v>
+        <v>6.76700067520142</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655862808228</v>
+        <v>6.78655815124512</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G897" t="n">
-        <v>7.87201642990112</v>
+        <v>7.87201690673828</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489068984985</v>
+        <v>7.74489116668701</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G900" t="n">
-        <v>7.72533273696899</v>
+        <v>7.72533321380615</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G904" t="n">
-        <v>7.676438331604</v>
+        <v>7.67643785476685</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842802047729</v>
+        <v>7.58842849731445</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G910" t="n">
-        <v>6.95279979705811</v>
+        <v>6.95279932022095</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147317886353</v>
+        <v>7.01147270202637</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572465896606</v>
+        <v>7.26572418212891</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G919" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G920" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G921" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793489456177</v>
+        <v>7.16793537139893</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191570281982</v>
+        <v>6.99191522598267</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218732833862</v>
+        <v>7.42218685150146</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312202453613</v>
+        <v>7.82312154769897</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G951" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897270202637</v>
+        <v>8.44897174835205</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G961" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339317321777</v>
+        <v>8.25339412689209</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449829101562</v>
+        <v>8.20449924468994</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G970" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482147216797</v>
+        <v>9.07482051849365</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G979" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804306030273</v>
+        <v>11.4804315567017</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9107027053833</v>
+        <v>11.9107036590576</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G987" t="n">
-        <v>12.4387645721436</v>
+        <v>12.4387636184692</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G990" t="n">
-        <v>12.9472665786743</v>
+        <v>12.947265625</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926733016968</v>
+        <v>13.5926742553711</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G996" t="n">
-        <v>15.0790681838989</v>
+        <v>15.0790672302246</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705652236938</v>
+        <v>14.5705633163452</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.1258392333984</v>
+        <v>12.1258382797241</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867233276367</v>
+        <v>12.0867223739624</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.9668245315552</v>
+        <v>12.9668254852295</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5561113357544</v>
+        <v>12.5561103820801</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.3384227752686</v>
+        <v>13.3384237289429</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583206176758</v>
+        <v>12.4583215713501</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.7151250839233</v>
+        <v>11.715124130249</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.047607421875</v>
+        <v>12.0476064682007</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734580993652</v>
+        <v>12.6734571456909</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.1845121383667</v>
+        <v>12.184513092041</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.2797498703003</v>
+        <v>13.279748916626</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1057" t="n">
-        <v>10.5416564941406</v>
+        <v>10.5416574478149</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220985412598</v>
+        <v>10.5220994949341</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.80101203918457</v>
+        <v>8.80101299285889</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206798553467</v>
+        <v>8.31206703186035</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543346405029</v>
+        <v>8.60543441772461</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570556640625</v>
+        <v>9.03570652008057</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.3265209197998</v>
+        <v>10.3265218734741</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003293991089</v>
+        <v>10.6003303527832</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1094" t="n">
-        <v>13.3775386810303</v>
+        <v>13.3775396347046</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1097" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1098" t="n">
-        <v>13.9055995941162</v>
+        <v>13.9055986404419</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771987915039</v>
+        <v>14.2771978378296</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749856948853</v>
+        <v>14.3749866485596</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>15</v>
       </c>
       <c r="G1107" t="n">
-        <v>14.6683530807495</v>
+        <v>14.6683540344238</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.6683530807495</v>
+        <v>14.6683540344238</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181840896606</v>
+        <v>15.1181831359863</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396095275879</v>
+        <v>15.9396114349365</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666507720947</v>
+        <v>19.1666488647461</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981105804443</v>
+        <v>22.1981067657471</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.758056640625</v>
+        <v>21.7580585479736</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558483123779</v>
+        <v>21.8558464050293</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602668762207</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602668762207</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>21.3180065155029</v>
+        <v>21.3180084228516</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>20.6334838867188</v>
+        <v>20.6334857940674</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691135406494</v>
+        <v>21.2691116333008</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0560989379883</v>
+        <v>24.0561008453369</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538887023926</v>
+        <v>24.1538906097412</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>24.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.9583129882812</v>
+        <v>23.9583110809326</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.3226833343506</v>
+        <v>23.322681427002</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359504699707</v>
+        <v>22.7359485626221</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1173" t="n">
-        <v>22.4425830841064</v>
+        <v>22.4425811767578</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.5892658233643</v>
+        <v>22.5892639160156</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157962799072</v>
+        <v>21.4157943725586</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113758087158</v>
+        <v>21.6113739013672</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.3180065155029</v>
+        <v>21.3180084228516</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>21.7091636657715</v>
+        <v>21.7091655731201</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401184082031</v>
+        <v>20.3401165008545</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511695861816</v>
+        <v>19.8511714935303</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.7533855438232</v>
+        <v>19.7533836364746</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1224" t="n">
-        <v>17.4651203155518</v>
+        <v>17.4651184082031</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1225" t="n">
-        <v>17.4651203155518</v>
+        <v>17.4651184082031</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.7831478118896</v>
+        <v>15.783148765564</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112106323242</v>
+        <v>16.3112087249756</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.3698806762695</v>
+        <v>16.3698825836182</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329788208008</v>
+        <v>16.2329769134521</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743049621582</v>
+        <v>16.1743068695068</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348472595215</v>
+        <v>17.0348491668701</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>18</v>
       </c>
       <c r="G1237" t="n">
-        <v>17.6020240783691</v>
+        <v>17.6020259857178</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304267883301</v>
+        <v>17.2304248809814</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108669281006</v>
+        <v>17.2108688354492</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1240" t="n">
-        <v>17.0739631652832</v>
+        <v>17.0739612579346</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1243" t="n">
-        <v>17.6411418914795</v>
+        <v>17.6411399841309</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042324066162</v>
+        <v>17.5042362213135</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.4846782684326</v>
+        <v>17.484676361084</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979454040527</v>
+        <v>16.8979434967041</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.5459041595459</v>
+        <v>16.5459022521973</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -71646,13 +71646,13 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B2742" t="n">
-        <v>26390</v>
+        <v>26500</v>
       </c>
       <c r="C2742" t="n">
         <v>11.2200002670288</v>
       </c>
       <c r="D2742" t="n">
-        <v>10.6400003433228</v>
+        <v>10.6000003814697</v>
       </c>
       <c r="E2742" t="n">
         <v>11.1599998474121</v>
@@ -71664,6 +71664,32 @@
         <v>10.6000003814697</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>29679</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>10.6199998855591</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>10.6199998855591</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>6.84846591949463</v>
+        <v>6.84846544265747</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455764770508</v>
+        <v>6.71455717086792</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4850001335144</v>
+        <v>6.48499965667725</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>6.06414461135864</v>
+        <v>6.06414413452148</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31329965591431</v>
+        <v>5.31330013275146</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7485032081604</v>
+        <v>5.74850273132324</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937250137329</v>
+        <v>5.72937297821045</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.0258846282959</v>
+        <v>6.02588510513306</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935136795044</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>6.00197267532349</v>
+        <v>6.00197219848633</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1884880065918</v>
+        <v>6.18848752975464</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414733886719</v>
+        <v>5.9541482925415</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154443740845</v>
+        <v>5.79154396057129</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244876861572</v>
+        <v>4.78244781494141</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679168701172</v>
+        <v>4.90679216384888</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5954647064209</v>
+        <v>5.59546422958374</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>5.4424262046814</v>
+        <v>5.44242572784424</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677375793457</v>
+        <v>5.45677328109741</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.75</v>
       </c>
       <c r="G37" t="n">
-        <v>5.49981546401978</v>
+        <v>5.49981498718262</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.32286500930786</v>
+        <v>5.3228645324707</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.29417037963867</v>
+        <v>5.29416990280151</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844909667969</v>
+        <v>4.73844957351685</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984443664551</v>
+        <v>4.61984491348267</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671644210815</v>
+        <v>4.55671691894531</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732461929321</v>
+        <v>4.58732414245605</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G55" t="n">
-        <v>4.4228081703186</v>
+        <v>4.42280864715576</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985275268555</v>
+        <v>4.39985227584839</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40559101104736</v>
+        <v>4.40559148788452</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.59200000762939</v>
       </c>
       <c r="G58" t="n">
-        <v>4.3922004699707</v>
+        <v>4.39219999313354</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.23916244506836</v>
+        <v>4.2391619682312</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>4.09377574920654</v>
+        <v>4.0937762260437</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871900558472</v>
+        <v>4.46871995925903</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.0650806427002</v>
+        <v>4.06508159637451</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265007972717</v>
+        <v>3.94265103340149</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691870689392</v>
+        <v>3.71691846847534</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.82595872879028</v>
+        <v>3.8259584903717</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987460136414</v>
+        <v>3.73987436294556</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>3.80682897567749</v>
+        <v>3.80682849884033</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222255706787</v>
+        <v>3.73222279548645</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.84891486167908</v>
+        <v>3.84891438484192</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463815689087</v>
+        <v>4.29463863372803</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.7872314453125</v>
+        <v>4.78723096847534</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07895946502686</v>
+        <v>5.07895994186401</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851793289185</v>
+        <v>5.30851745605469</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373477935791</v>
+        <v>5.30373525619507</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>5.12200164794922</v>
+        <v>5.12200212478638</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.0550479888916</v>
+        <v>5.05504751205444</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417726516724</v>
+        <v>5.07417774200439</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>4.93548631668091</v>
+        <v>4.93548583984375</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>4.22768449783325</v>
+        <v>4.22768402099609</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559885025024</v>
+        <v>4.18559789657593</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942499160767</v>
+        <v>4.18942451477051</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550840377808</v>
+        <v>4.27550888061523</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G95" t="n">
-        <v>4.31376838684082</v>
+        <v>4.31376791000366</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.1167311668396</v>
+        <v>4.11673164367676</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846429824829</v>
+        <v>4.29846477508545</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02156972885132</v>
+        <v>5.02157068252563</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548311233521</v>
+        <v>5.04548263549805</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>7.25497436523438</v>
+        <v>7.25497388839722</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367588043213</v>
+        <v>7.06367635726929</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804136276245</v>
+        <v>6.52804183959961</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237419128418</v>
+        <v>6.98237466812134</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>6.79585838317871</v>
+        <v>6.79585886001587</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.38456869125366</v>
+        <v>6.38456916809082</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718215942383</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718215942383</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>6.06414461135864</v>
+        <v>6.06414413452148</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325180053711</v>
+        <v>6.74325227737427</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83936929702759</v>
+        <v>5.83936882019043</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848112106323</v>
+        <v>6.40848064422607</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.35109090805054</v>
+        <v>6.35109043121338</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.35109090805054</v>
+        <v>6.35109043121338</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935136795044</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805288314819</v>
+        <v>6.19805240631104</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933664321899</v>
+        <v>6.82933616638184</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>7.16889047622681</v>
+        <v>7.16888999938965</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584686279297</v>
+        <v>7.12584781646729</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>7.05889368057251</v>
+        <v>7.05889320373535</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>6.95846223831177</v>
+        <v>6.95846271514893</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75281667709351</v>
+        <v>6.75281620025635</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.8723783493042</v>
+        <v>6.87237787246704</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>6.85324811935425</v>
+        <v>6.85324859619141</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>7.03019905090332</v>
+        <v>7.03019857406616</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886375427246</v>
+        <v>7.93886518478394</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712837219238</v>
+        <v>7.86712741851807</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91017007827759</v>
+        <v>7.91017055511475</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G162" t="n">
-        <v>7.66626501083374</v>
+        <v>7.66626453399658</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234474182129</v>
+        <v>7.86234521865845</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712373733521</v>
+        <v>7.97712278366089</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060424804688</v>
+        <v>7.90060520172119</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669645309448</v>
+        <v>7.76669549942017</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103937149048</v>
+        <v>7.89104032516479</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492698669434</v>
+        <v>8.68492603302002</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65623188018799</v>
+        <v>8.65623092651367</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.17798614501953</v>
+        <v>8.17798709869385</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>8.46493244171143</v>
+        <v>8.46493339538574</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.2545051574707</v>
+        <v>8.25450611114502</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451572418213</v>
+        <v>7.92451620101929</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581100463867</v>
+        <v>8.22581195831299</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34058952331543</v>
+        <v>8.34059047698975</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101680755615</v>
+        <v>8.55101776123047</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.06752109527588</v>
+        <v>9.0675220489502</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968887329102</v>
+        <v>9.23968982696533</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317497253418</v>
+        <v>9.05317401885986</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708229064941</v>
+        <v>9.18708324432373</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882694244385</v>
+        <v>9.03882789611816</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.17273616790771</v>
+        <v>9.1727352142334</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620338439941</v>
+        <v>9.53620052337646</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.2535705566406</v>
+        <v>10.2535696029663</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>11.25</v>
       </c>
       <c r="G212" t="n">
-        <v>10.7605085372925</v>
+        <v>10.7605094909668</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G215" t="n">
-        <v>11.200493812561</v>
+        <v>11.2004928588867</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.0431394577026</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.0431394577026</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831266403198</v>
+        <v>10.4831275939941</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8274631500244</v>
+        <v>10.8274621963501</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370275497437</v>
+        <v>10.8370265960693</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117849349976</v>
+        <v>11.6117858886719</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G227" t="n">
-        <v>11.5639591217041</v>
+        <v>11.5639610290527</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456912994385</v>
+        <v>11.7456922531128</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961057662964</v>
+        <v>12.3961048126221</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.25</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7169981002808</v>
+        <v>11.7169990539551</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839517593384</v>
+        <v>11.7839527130127</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169622421265</v>
+        <v>12.8169612884521</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.038592338562</v>
+        <v>14.0385932922363</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>13.8456220626831</v>
+        <v>13.8456230163574</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G248" t="n">
-        <v>13.3728446960449</v>
+        <v>13.3728437423706</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272216796875</v>
+        <v>13.5272207260132</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G250" t="n">
-        <v>13.4307355880737</v>
+        <v>13.4307346343994</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.5</v>
       </c>
       <c r="G260" t="n">
-        <v>13.0254983901978</v>
+        <v>13.0254974365234</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.9869031906128</v>
+        <v>12.9869041442871</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G264" t="n">
-        <v>14.1061315536499</v>
+        <v>14.1061325073242</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973794937134</v>
+        <v>13.7973804473877</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044082641602</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>13.8359727859497</v>
+        <v>13.835973739624</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921413421631</v>
+        <v>13.3921422958374</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869714736938</v>
+        <v>11.8869733810425</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G280" t="n">
-        <v>11.665057182312</v>
+        <v>11.6650581359863</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.2887659072876</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>11.75</v>
       </c>
       <c r="G284" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063383102417</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484483718872</v>
+        <v>10.7484493255615</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.250171661377</v>
+        <v>11.2501707077026</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G295" t="n">
-        <v>10.8449335098267</v>
+        <v>10.844934463501</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695356369019</v>
+        <v>10.1695365905762</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247406005859</v>
+        <v>11.1247396469116</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G303" t="n">
-        <v>11.7132997512817</v>
+        <v>11.7133016586304</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G307" t="n">
-        <v>11.587869644165</v>
+        <v>11.5878686904907</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>11.75</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212247848511</v>
+        <v>11.2212257385254</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334926605225</v>
+        <v>11.4334936141968</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G320" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640926361084</v>
+        <v>13.0640916824341</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044082641602</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693307876587</v>
+        <v>13.4693298339844</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G332" t="n">
-        <v>13.4307355880737</v>
+        <v>13.4307346343994</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886264801025</v>
+        <v>13.4886274337769</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552713394165</v>
+        <v>13.8552703857422</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>14.75</v>
       </c>
       <c r="G341" t="n">
-        <v>14.2315635681152</v>
+        <v>14.2315626144409</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>14.7815284729004</v>
+        <v>14.7815275192261</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G345" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5692615509033</v>
+        <v>14.569260597229</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527210235596</v>
+        <v>12.5527200698853</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386606216431</v>
+        <v>12.9386615753174</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.8807706832886</v>
+        <v>12.8807716369629</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447950363159</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G366" t="n">
-        <v>12.7939348220825</v>
+        <v>12.7939338684082</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360420227051</v>
+        <v>12.7360429763794</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4272899627686</v>
+        <v>12.4272909164429</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474838256836</v>
+        <v>12.1474828720093</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176416397095</v>
+        <v>12.4176425933838</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1571311950684</v>
+        <v>12.1571321487427</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194332122803</v>
+        <v>11.8194341659546</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G383" t="n">
-        <v>11.6940031051636</v>
+        <v>11.6940021514893</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>11.6843538284302</v>
+        <v>11.6843528747559</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325973510742</v>
+        <v>11.7325963973999</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G386" t="n">
-        <v>11.6843538284302</v>
+        <v>11.6843528747559</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966217041016</v>
+        <v>11.8966207504272</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G393" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545135498047</v>
+        <v>11.9545125961304</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.2439680099487</v>
+        <v>12.2439670562744</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G399" t="n">
-        <v>12.7939348220825</v>
+        <v>12.7939338684082</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G400" t="n">
-        <v>12.649206161499</v>
+        <v>12.6492052078247</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>12.8711223602295</v>
+        <v>12.8711214065552</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447950363159</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G413" t="n">
-        <v>12.9097156524658</v>
+        <v>12.9097166061401</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193649291992</v>
+        <v>12.9193639755249</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G419" t="n">
-        <v>12.9869031906128</v>
+        <v>12.9869041442871</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>13.0544424057007</v>
+        <v>13.054443359375</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772548675537</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167463302612</v>
+        <v>12.7167453765869</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>12.8807706832886</v>
+        <v>12.8807716369629</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483089447021</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>13.2184677124023</v>
+        <v>13.2184686660767</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>13.179874420166</v>
+        <v>13.1798753738403</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G434" t="n">
-        <v>13.8745670318604</v>
+        <v>13.8745679855347</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>13.9324588775635</v>
+        <v>13.9324579238892</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974477767944</v>
+        <v>12.6974487304688</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G439" t="n">
-        <v>12.649206161499</v>
+        <v>12.6492052078247</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>12.6395578384399</v>
+        <v>12.6395587921143</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>12.4851808547974</v>
+        <v>12.485179901123</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3693981170654</v>
+        <v>12.3694000244141</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1860780715942</v>
+        <v>12.1860771179199</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>12.0895910263062</v>
+        <v>12.0895919799805</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1378355026245</v>
+        <v>12.1378345489502</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308038711548</v>
+        <v>12.3308048248291</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>12.1088895797729</v>
+        <v>12.1088886260986</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124034881592</v>
+        <v>12.0124044418335</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554733276367</v>
+        <v>9.45554637908936</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711090087891</v>
+        <v>9.68711185455322</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923480987549</v>
+        <v>10.0923500061035</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107494354248</v>
+        <v>10.4107503890991</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063383102417</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764980316162</v>
+        <v>11.0764961242676</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.7195014953613</v>
+        <v>10.7195024490356</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G490" t="n">
-        <v>11.4527893066406</v>
+        <v>11.4527912139893</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7388000488281</v>
+        <v>10.7387990951538</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>11.25</v>
       </c>
       <c r="G498" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545827865601</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>10.6199998855591</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>8980</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>6.84846639633179</v>
+        <v>6.84846591949463</v>
       </c>
       <c r="H2" t="n">
         <v>24440</v>
@@ -456,7 +456,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455717086792</v>
+        <v>6.71455764770508</v>
       </c>
       <c r="H3" t="n">
         <v>54991</v>
@@ -485,7 +485,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48499965667725</v>
+        <v>6.4850001335144</v>
       </c>
       <c r="H4" t="n">
         <v>46846</v>
@@ -572,7 +572,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544902801514</v>
       </c>
       <c r="H7" t="n">
         <v>40228</v>
@@ -688,7 +688,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544902801514</v>
       </c>
       <c r="H11" t="n">
         <v>125780</v>
@@ -920,7 +920,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935041427612</v>
       </c>
       <c r="H19" t="n">
         <v>89617</v>
@@ -978,7 +978,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458389282227</v>
+        <v>5.94458341598511</v>
       </c>
       <c r="H21" t="n">
         <v>47413</v>
@@ -1123,7 +1123,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7006778717041</v>
+        <v>5.70067882537842</v>
       </c>
       <c r="H26" t="n">
         <v>83256</v>
@@ -1152,7 +1152,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>5.27504014968872</v>
+        <v>5.27504062652588</v>
       </c>
       <c r="H27" t="n">
         <v>92262</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244781494141</v>
+        <v>4.78244829177856</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1297,7 +1297,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.064612865448</v>
+        <v>5.06461238861084</v>
       </c>
       <c r="H32" t="n">
         <v>19857</v>
@@ -1355,7 +1355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5954647064209</v>
+        <v>5.59546375274658</v>
       </c>
       <c r="H34" t="n">
         <v>87689</v>
@@ -1413,7 +1413,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677375793457</v>
+        <v>5.45677280426025</v>
       </c>
       <c r="H36" t="n">
         <v>102398</v>
@@ -1442,7 +1442,7 @@
         <v>5.75</v>
       </c>
       <c r="G37" t="n">
-        <v>5.49981546401978</v>
+        <v>5.49981594085693</v>
       </c>
       <c r="H37" t="n">
         <v>45357</v>
@@ -1500,7 +1500,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.29417037963867</v>
+        <v>5.29416990280151</v>
       </c>
       <c r="H39" t="n">
         <v>54047</v>
@@ -1529,7 +1529,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460870742798</v>
+        <v>5.17460823059082</v>
       </c>
       <c r="H40" t="n">
         <v>27727</v>
@@ -1587,7 +1587,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069355010986</v>
+        <v>5.26069307327271</v>
       </c>
       <c r="H42" t="n">
         <v>79999</v>
@@ -1645,7 +1645,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844909667969</v>
+        <v>4.73844957351685</v>
       </c>
       <c r="H44" t="n">
         <v>146124</v>
@@ -1732,7 +1732,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749671936035</v>
+        <v>4.62749719619751</v>
       </c>
       <c r="H47" t="n">
         <v>92990</v>
@@ -1790,7 +1790,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>4.6389741897583</v>
+        <v>4.63897466659546</v>
       </c>
       <c r="H49" t="n">
         <v>45504</v>
@@ -1993,7 +1993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985227584839</v>
+        <v>4.39985179901123</v>
       </c>
       <c r="H56" t="n">
         <v>6922</v>
@@ -2022,7 +2022,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40559148788452</v>
+        <v>4.40559101104736</v>
       </c>
       <c r="H57" t="n">
         <v>12685</v>
@@ -2138,7 +2138,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916980743408</v>
+        <v>4.01916933059692</v>
       </c>
       <c r="H61" t="n">
         <v>8387</v>
@@ -2167,7 +2167,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793920516968</v>
+        <v>4.39793968200684</v>
       </c>
       <c r="H62" t="n">
         <v>183307</v>
@@ -2225,7 +2225,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871995925903</v>
+        <v>4.46871948242188</v>
       </c>
       <c r="H64" t="n">
         <v>136790</v>
@@ -2254,7 +2254,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H65" t="n">
         <v>59895</v>
@@ -2283,7 +2283,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.06508159637451</v>
+        <v>4.06508111953735</v>
       </c>
       <c r="H66" t="n">
         <v>69251</v>
@@ -2312,7 +2312,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265079498291</v>
+        <v>3.94265031814575</v>
       </c>
       <c r="H67" t="n">
         <v>49492</v>
@@ -2370,7 +2370,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726386070251</v>
+        <v>3.79726409912109</v>
       </c>
       <c r="H69" t="n">
         <v>35741</v>
@@ -2457,7 +2457,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>3.80682897567749</v>
+        <v>3.80682873725891</v>
       </c>
       <c r="H72" t="n">
         <v>32798</v>
@@ -2486,7 +2486,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813386917114</v>
+        <v>3.77813410758972</v>
       </c>
       <c r="H73" t="n">
         <v>13357</v>
@@ -2515,7 +2515,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222231864929</v>
+        <v>3.73222255706787</v>
       </c>
       <c r="H74" t="n">
         <v>23567</v>
@@ -2573,7 +2573,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463815689087</v>
+        <v>4.29463863372803</v>
       </c>
       <c r="H76" t="n">
         <v>172014</v>
@@ -2602,7 +2602,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723096847534</v>
+        <v>4.78723049163818</v>
       </c>
       <c r="H77" t="n">
         <v>182115</v>
@@ -2660,7 +2660,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07895994186401</v>
+        <v>5.07896041870117</v>
       </c>
       <c r="H79" t="n">
         <v>724913</v>
@@ -2718,7 +2718,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373525619507</v>
+        <v>5.30373573303223</v>
       </c>
       <c r="H81" t="n">
         <v>264110</v>
@@ -2747,7 +2747,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>5.12200164794922</v>
+        <v>5.12200212478638</v>
       </c>
       <c r="H82" t="n">
         <v>94676</v>
@@ -2776,7 +2776,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.05504751205444</v>
+        <v>5.0550479888916</v>
       </c>
       <c r="H83" t="n">
         <v>85082</v>
@@ -2805,7 +2805,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417678833008</v>
+        <v>5.07417726516724</v>
       </c>
       <c r="H84" t="n">
         <v>122889</v>
@@ -2834,7 +2834,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>4.93548631668091</v>
+        <v>4.93548583984375</v>
       </c>
       <c r="H85" t="n">
         <v>71889</v>
@@ -2863,7 +2863,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>4.95461654663086</v>
+        <v>4.9546160697937</v>
       </c>
       <c r="H86" t="n">
         <v>66959</v>
@@ -2892,7 +2892,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653650283813</v>
+        <v>4.73653745651245</v>
       </c>
       <c r="H87" t="n">
         <v>101740</v>
@@ -2921,7 +2921,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680641174316</v>
+        <v>4.46680688858032</v>
       </c>
       <c r="H88" t="n">
         <v>98603</v>
@@ -2979,7 +2979,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G90" t="n">
-        <v>4.38646125793457</v>
+        <v>4.38646173477173</v>
       </c>
       <c r="H90" t="n">
         <v>233892</v>
@@ -3008,7 +3008,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H91" t="n">
         <v>78370</v>
@@ -3037,7 +3037,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559837341309</v>
+        <v>4.18559885025024</v>
       </c>
       <c r="H92" t="n">
         <v>40037</v>
@@ -3066,7 +3066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942451477051</v>
+        <v>4.18942499160767</v>
       </c>
       <c r="H93" t="n">
         <v>83730</v>
@@ -3095,7 +3095,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550888061523</v>
+        <v>4.27550840377808</v>
       </c>
       <c r="H94" t="n">
         <v>105195</v>
@@ -3124,7 +3124,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G95" t="n">
-        <v>4.31376838684082</v>
+        <v>4.31376886367798</v>
       </c>
       <c r="H95" t="n">
         <v>42012</v>
@@ -3182,7 +3182,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.11673164367676</v>
+        <v>4.1167311668396</v>
       </c>
       <c r="H97" t="n">
         <v>33027</v>
@@ -3211,7 +3211,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603349685669</v>
+        <v>4.17603397369385</v>
       </c>
       <c r="H98" t="n">
         <v>54021</v>
@@ -3240,7 +3240,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472812652588</v>
+        <v>4.20472860336304</v>
       </c>
       <c r="H99" t="n">
         <v>30978</v>
@@ -3269,7 +3269,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846429824829</v>
+        <v>4.29846477508545</v>
       </c>
       <c r="H100" t="n">
         <v>67373</v>
@@ -3298,7 +3298,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157020568848</v>
+        <v>5.02157068252563</v>
       </c>
       <c r="H101" t="n">
         <v>322788</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113924026489</v>
+        <v>4.92113876342773</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3356,7 +3356,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G103" t="n">
-        <v>4.95939922332764</v>
+        <v>4.95939874649048</v>
       </c>
       <c r="H103" t="n">
         <v>129996</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H106" t="n">
         <v>756136</v>
@@ -3472,7 +3472,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756574630737</v>
+        <v>7.74756669998169</v>
       </c>
       <c r="H107" t="n">
         <v>830490</v>
@@ -3501,7 +3501,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>7.25497388839722</v>
+        <v>7.25497341156006</v>
       </c>
       <c r="H108" t="n">
         <v>611973</v>
@@ -3559,7 +3559,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H110" t="n">
         <v>192489</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804183959961</v>
+        <v>6.52804136276245</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3646,7 +3646,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237466812134</v>
+        <v>6.98237419128418</v>
       </c>
       <c r="H113" t="n">
         <v>407399</v>
@@ -3704,7 +3704,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.3845682144165</v>
+        <v>6.38456869125366</v>
       </c>
       <c r="H115" t="n">
         <v>131401</v>
@@ -3878,7 +3878,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370901107788</v>
+        <v>6.07370853424072</v>
       </c>
       <c r="H121" t="n">
         <v>194455</v>
@@ -3907,7 +3907,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325180053711</v>
+        <v>6.74325227737427</v>
       </c>
       <c r="H122" t="n">
         <v>283137</v>
@@ -3936,7 +3936,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195426940918</v>
+        <v>6.55195474624634</v>
       </c>
       <c r="H123" t="n">
         <v>388485</v>
@@ -3965,7 +3965,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.06892681121826</v>
+        <v>6.0689263343811</v>
       </c>
       <c r="H124" t="n">
         <v>130995</v>
@@ -4052,7 +4052,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848016738892</v>
+        <v>6.40848064422607</v>
       </c>
       <c r="H127" t="n">
         <v>110989</v>
@@ -4168,7 +4168,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935041427612</v>
       </c>
       <c r="H131" t="n">
         <v>52660</v>
@@ -4197,7 +4197,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370901107788</v>
+        <v>6.07370853424072</v>
       </c>
       <c r="H132" t="n">
         <v>115535</v>
@@ -4226,7 +4226,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805335998535</v>
+        <v>6.19805240631104</v>
       </c>
       <c r="H133" t="n">
         <v>77921</v>
@@ -4342,7 +4342,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>6.97280931472778</v>
+        <v>6.97280979156494</v>
       </c>
       <c r="H137" t="n">
         <v>53595</v>
@@ -4371,7 +4371,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584781646729</v>
+        <v>7.12584733963013</v>
       </c>
       <c r="H138" t="n">
         <v>47644</v>
@@ -4603,7 +4603,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H146" t="n">
         <v>18313</v>
@@ -4632,7 +4632,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.9249849319458</v>
+        <v>6.92498397827148</v>
       </c>
       <c r="H147" t="n">
         <v>105405</v>
@@ -4719,7 +4719,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064426422119</v>
+        <v>6.69064521789551</v>
       </c>
       <c r="H150" t="n">
         <v>35920</v>
@@ -4806,7 +4806,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>6.97280931472778</v>
+        <v>6.97280979156494</v>
       </c>
       <c r="H153" t="n">
         <v>63748</v>
@@ -4835,7 +4835,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>7.03019857406616</v>
+        <v>7.03019905090332</v>
       </c>
       <c r="H154" t="n">
         <v>34070</v>
@@ -4893,7 +4893,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.33627605438232</v>
+        <v>7.33627557754517</v>
       </c>
       <c r="H156" t="n">
         <v>116091</v>
@@ -4922,7 +4922,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886423110962</v>
+        <v>7.93886375427246</v>
       </c>
       <c r="H157" t="n">
         <v>265495</v>
@@ -4951,7 +4951,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.09190368652344</v>
+        <v>8.0919017791748</v>
       </c>
       <c r="H158" t="n">
         <v>272541</v>
@@ -5038,7 +5038,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.6710467338562</v>
+        <v>7.67104721069336</v>
       </c>
       <c r="H161" t="n">
         <v>97882</v>
@@ -5067,7 +5067,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G162" t="n">
-        <v>7.66626501083374</v>
+        <v>7.66626453399658</v>
       </c>
       <c r="H162" t="n">
         <v>71695</v>
@@ -5096,7 +5096,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>7.84321594238281</v>
+        <v>7.84321546554565</v>
       </c>
       <c r="H163" t="n">
         <v>118168</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626085281372</v>
+        <v>7.77626037597656</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.99625396728516</v>
+        <v>7.996253490448</v>
       </c>
       <c r="H166" t="n">
         <v>48102</v>
@@ -5212,7 +5212,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712421417236</v>
+        <v>7.97712373733521</v>
       </c>
       <c r="H167" t="n">
         <v>31192</v>
@@ -5241,7 +5241,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451251983643</v>
+        <v>8.03451156616211</v>
       </c>
       <c r="H168" t="n">
         <v>39269</v>
@@ -5299,7 +5299,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.8336501121521</v>
+        <v>7.83364963531494</v>
       </c>
       <c r="H170" t="n">
         <v>41230</v>
@@ -5328,7 +5328,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669597625732</v>
+        <v>7.76669549942017</v>
       </c>
       <c r="H171" t="n">
         <v>80513</v>
@@ -5357,7 +5357,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103889465332</v>
+        <v>7.89104032516479</v>
       </c>
       <c r="H172" t="n">
         <v>61552</v>
@@ -5415,7 +5415,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H174" t="n">
         <v>135297</v>
@@ -5444,7 +5444,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.6849250793457</v>
+        <v>8.68492603302002</v>
       </c>
       <c r="H175" t="n">
         <v>251570</v>
@@ -5473,7 +5473,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>9.00535106658936</v>
+        <v>9.00534915924072</v>
       </c>
       <c r="H176" t="n">
         <v>166097</v>
@@ -5560,7 +5560,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G179" t="n">
-        <v>8.35015392303467</v>
+        <v>8.35015296936035</v>
       </c>
       <c r="H179" t="n">
         <v>237396</v>
@@ -5647,7 +5647,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>8.46493434906006</v>
+        <v>8.46493339538574</v>
       </c>
       <c r="H182" t="n">
         <v>82708</v>
@@ -5705,7 +5705,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.25450706481934</v>
+        <v>8.2545051574707</v>
       </c>
       <c r="H184" t="n">
         <v>33220</v>
@@ -5734,7 +5734,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.9245171546936</v>
+        <v>7.92451763153076</v>
       </c>
       <c r="H185" t="n">
         <v>122464</v>
@@ -5763,7 +5763,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581100463867</v>
+        <v>8.22581195831299</v>
       </c>
       <c r="H186" t="n">
         <v>99183</v>
@@ -5821,7 +5821,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H188" t="n">
         <v>34542</v>
@@ -5879,7 +5879,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.2736349105835</v>
+        <v>8.27363586425781</v>
       </c>
       <c r="H190" t="n">
         <v>51064</v>
@@ -5908,7 +5908,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H191" t="n">
         <v>24030</v>
@@ -5937,7 +5937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G192" t="n">
-        <v>8.43623733520508</v>
+        <v>8.43623924255371</v>
       </c>
       <c r="H192" t="n">
         <v>44995</v>
@@ -5966,7 +5966,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101776123047</v>
+        <v>8.55101680755615</v>
       </c>
       <c r="H193" t="n">
         <v>104665</v>
@@ -5995,7 +5995,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92883014678955</v>
+        <v>8.92882919311523</v>
       </c>
       <c r="H194" t="n">
         <v>196106</v>
@@ -6024,7 +6024,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.0675220489502</v>
+        <v>9.06752109527588</v>
       </c>
       <c r="H195" t="n">
         <v>116469</v>
@@ -6053,7 +6053,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.1057825088501</v>
+        <v>9.10578155517578</v>
       </c>
       <c r="H196" t="n">
         <v>198688</v>
@@ -6111,7 +6111,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317401885986</v>
+        <v>9.05317497253418</v>
       </c>
       <c r="H198" t="n">
         <v>156638</v>
@@ -6140,7 +6140,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708229064941</v>
+        <v>9.18708324432373</v>
       </c>
       <c r="H199" t="n">
         <v>82966</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.1344747543335</v>
+        <v>9.13447666168213</v>
       </c>
       <c r="H201" t="n">
         <v>49199</v>
@@ -6227,7 +6227,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.17273616790771</v>
+        <v>9.17273712158203</v>
       </c>
       <c r="H202" t="n">
         <v>47674</v>
@@ -6256,7 +6256,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185855865479</v>
+        <v>9.41185760498047</v>
       </c>
       <c r="H203" t="n">
         <v>115834</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6314,7 +6314,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>9.5170726776123</v>
+        <v>9.51707172393799</v>
       </c>
       <c r="H205" t="n">
         <v>125905</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6401,7 +6401,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620147705078</v>
+        <v>9.53620338439941</v>
       </c>
       <c r="H208" t="n">
         <v>78401</v>
@@ -6430,7 +6430,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587837219238</v>
+        <v>10.3587827682495</v>
       </c>
       <c r="H209" t="n">
         <v>324694</v>
@@ -6488,7 +6488,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.2535696029663</v>
+        <v>10.253568649292</v>
       </c>
       <c r="H211" t="n">
         <v>105355</v>
@@ -6604,7 +6604,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2004928588867</v>
+        <v>11.200493812561</v>
       </c>
       <c r="H215" t="n">
         <v>33710</v>
@@ -6633,7 +6633,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518051147461</v>
+        <v>10.9518060684204</v>
       </c>
       <c r="H216" t="n">
         <v>101398</v>
@@ -6662,7 +6662,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H217" t="n">
         <v>175009</v>
@@ -6691,7 +6691,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H218" t="n">
         <v>270935</v>
@@ -6720,7 +6720,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831275939941</v>
+        <v>10.4831266403198</v>
       </c>
       <c r="H219" t="n">
         <v>128669</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692110061646</v>
+        <v>10.5692100524902</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6836,7 +6836,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.9613704681396</v>
+        <v>10.961371421814</v>
       </c>
       <c r="H223" t="n">
         <v>86558</v>
@@ -6894,7 +6894,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630962371826</v>
+        <v>11.3630971908569</v>
       </c>
       <c r="H225" t="n">
         <v>187509</v>
@@ -6952,7 +6952,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G227" t="n">
-        <v>11.5639591217041</v>
+        <v>11.5639600753784</v>
       </c>
       <c r="H227" t="n">
         <v>116721</v>
@@ -6981,7 +6981,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456932067871</v>
+        <v>11.7456922531128</v>
       </c>
       <c r="H228" t="n">
         <v>176751</v>
@@ -7010,7 +7010,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648220062256</v>
+        <v>11.7648229598999</v>
       </c>
       <c r="H229" t="n">
         <v>87480</v>
@@ -7097,7 +7097,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708990097046</v>
+        <v>12.0708980560303</v>
       </c>
       <c r="H232" t="n">
         <v>161563</v>
@@ -7126,7 +7126,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961067199707</v>
+        <v>12.3961048126221</v>
       </c>
       <c r="H233" t="n">
         <v>317127</v>
@@ -7155,7 +7155,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H234" t="n">
         <v>153081</v>
@@ -7184,7 +7184,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H235" t="n">
         <v>95580</v>
@@ -7213,7 +7213,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474180221558</v>
+        <v>12.1474170684814</v>
       </c>
       <c r="H236" t="n">
         <v>111282</v>
@@ -7358,7 +7358,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169603347778</v>
+        <v>12.8169612884521</v>
       </c>
       <c r="H241" t="n">
         <v>122373</v>
@@ -7387,7 +7387,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717241287231</v>
+        <v>13.3717250823975</v>
       </c>
       <c r="H242" t="n">
         <v>100896</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272226333618</v>
+        <v>13.5272216796875</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7619,7 +7619,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G250" t="n">
-        <v>13.4307355880737</v>
+        <v>13.430736541748</v>
       </c>
       <c r="H250" t="n">
         <v>48278</v>
@@ -7648,7 +7648,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>13.3246030807495</v>
+        <v>13.3246021270752</v>
       </c>
       <c r="H251" t="n">
         <v>49468</v>
@@ -7677,7 +7677,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>12.6877994537354</v>
+        <v>12.6878004074097</v>
       </c>
       <c r="H252" t="n">
         <v>71435</v>
@@ -7764,7 +7764,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>13.1509294509888</v>
+        <v>13.1509284973145</v>
       </c>
       <c r="H255" t="n">
         <v>47379</v>
@@ -7793,7 +7793,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G256" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H256" t="n">
         <v>44658</v>
@@ -7851,7 +7851,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H258" t="n">
         <v>48422</v>
@@ -7880,7 +7880,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H259" t="n">
         <v>124706</v>
@@ -8170,7 +8170,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G269" t="n">
-        <v>13.5851125717163</v>
+        <v>13.585111618042</v>
       </c>
       <c r="H269" t="n">
         <v>52002</v>
@@ -8228,7 +8228,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H271" t="n">
         <v>92437</v>
@@ -8286,7 +8286,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H273" t="n">
         <v>167282</v>
@@ -8315,7 +8315,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G274" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H274" t="n">
         <v>91826</v>
@@ -8402,7 +8402,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5396270751953</v>
+        <v>11.539626121521</v>
       </c>
       <c r="H277" t="n">
         <v>194589</v>
@@ -8460,7 +8460,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3756008148193</v>
+        <v>11.3756017684937</v>
       </c>
       <c r="H279" t="n">
         <v>165236</v>
@@ -8634,7 +8634,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063383102417</v>
       </c>
       <c r="H285" t="n">
         <v>135254</v>
@@ -8692,7 +8692,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484474182129</v>
+        <v>10.7484493255615</v>
       </c>
       <c r="H287" t="n">
         <v>33613</v>
@@ -8721,7 +8721,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.7291507720947</v>
+        <v>10.729151725769</v>
       </c>
       <c r="H288" t="n">
         <v>25029</v>
@@ -8750,7 +8750,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431400299072</v>
+        <v>11.4431409835815</v>
       </c>
       <c r="H289" t="n">
         <v>181496</v>
@@ -8837,7 +8837,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738794326782</v>
+        <v>10.8738803863525</v>
       </c>
       <c r="H292" t="n">
         <v>53600</v>
@@ -8953,7 +8953,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072345733643</v>
+        <v>10.5072355270386</v>
       </c>
       <c r="H296" t="n">
         <v>45140</v>
@@ -9040,7 +9040,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>10.9124736785889</v>
+        <v>10.9124727249146</v>
       </c>
       <c r="H299" t="n">
         <v>173611</v>
@@ -9127,7 +9127,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273591995239</v>
+        <v>11.3273582458496</v>
       </c>
       <c r="H302" t="n">
         <v>104822</v>
@@ -9388,7 +9388,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212247848511</v>
+        <v>11.2212257385254</v>
       </c>
       <c r="H311" t="n">
         <v>48985</v>
@@ -9475,7 +9475,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>11.5299777984619</v>
+        <v>11.5299787521362</v>
       </c>
       <c r="H314" t="n">
         <v>80574</v>
@@ -9504,7 +9504,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334936141968</v>
+        <v>11.4334945678711</v>
       </c>
       <c r="H315" t="n">
         <v>31751</v>
@@ -9562,7 +9562,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H317" t="n">
         <v>48953</v>
@@ -9736,7 +9736,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387308120728</v>
+        <v>11.8387317657471</v>
       </c>
       <c r="H323" t="n">
         <v>88601</v>
@@ -9794,7 +9794,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640916824341</v>
+        <v>13.0640926361084</v>
       </c>
       <c r="H325" t="n">
         <v>437770</v>
@@ -9910,7 +9910,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693298339844</v>
+        <v>13.4693307876587</v>
       </c>
       <c r="H329" t="n">
         <v>64109</v>
@@ -9997,7 +9997,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G332" t="n">
-        <v>13.4307355880737</v>
+        <v>13.430736541748</v>
       </c>
       <c r="H332" t="n">
         <v>75116</v>
@@ -10026,7 +10026,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886264801025</v>
+        <v>13.4886274337769</v>
       </c>
       <c r="H333" t="n">
         <v>19569</v>
@@ -10229,7 +10229,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807014465332</v>
+        <v>13.9807004928589</v>
       </c>
       <c r="H340" t="n">
         <v>101573</v>
@@ -10287,7 +10287,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>14.7815284729004</v>
+        <v>14.7815275192261</v>
       </c>
       <c r="H342" t="n">
         <v>193154</v>
@@ -10316,7 +10316,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.492073059082</v>
+        <v>14.4920740127563</v>
       </c>
       <c r="H343" t="n">
         <v>175404</v>
@@ -10345,7 +10345,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H344" t="n">
         <v>84729</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5692615509033</v>
+        <v>14.569260597229</v>
       </c>
       <c r="H346" t="n">
         <v>63786</v>
@@ -10432,7 +10432,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G347" t="n">
-        <v>14.5789089202881</v>
+        <v>14.5789098739624</v>
       </c>
       <c r="H347" t="n">
         <v>26791</v>
@@ -10519,7 +10519,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824256896973</v>
+        <v>14.4824247360229</v>
       </c>
       <c r="H350" t="n">
         <v>97965</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527210235596</v>
+        <v>12.5527219772339</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10722,7 +10722,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G357" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H357" t="n">
         <v>55254</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.006199836731</v>
+        <v>13.0062007904053</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10838,7 +10838,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H361" t="n">
         <v>30895</v>
@@ -10867,7 +10867,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H362" t="n">
         <v>25549</v>
@@ -10896,7 +10896,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H363" t="n">
         <v>24673</v>
@@ -10925,7 +10925,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H364" t="n">
         <v>31128</v>
@@ -10954,7 +10954,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H365" t="n">
         <v>55168</v>
@@ -11012,7 +11012,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360429763794</v>
+        <v>12.7360410690308</v>
       </c>
       <c r="H367" t="n">
         <v>41635</v>
@@ -11070,7 +11070,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H369" t="n">
         <v>33590</v>
@@ -11099,7 +11099,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H370" t="n">
         <v>58049</v>
@@ -11157,7 +11157,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4272899627686</v>
+        <v>12.4272890090942</v>
       </c>
       <c r="H372" t="n">
         <v>32892</v>
@@ -11273,7 +11273,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185388565063</v>
       </c>
       <c r="H376" t="n">
         <v>18790</v>
@@ -11302,7 +11302,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H377" t="n">
         <v>54450</v>
@@ -11360,7 +11360,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H379" t="n">
         <v>11240</v>
@@ -11389,7 +11389,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1571311950684</v>
+        <v>12.1571321487427</v>
       </c>
       <c r="H380" t="n">
         <v>38689</v>
@@ -11418,7 +11418,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H381" t="n">
         <v>64542</v>
@@ -11476,7 +11476,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G383" t="n">
-        <v>11.6940040588379</v>
+        <v>11.6940031051636</v>
       </c>
       <c r="H383" t="n">
         <v>41701</v>
@@ -11505,7 +11505,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>11.6843538284302</v>
+        <v>11.6843547821045</v>
       </c>
       <c r="H384" t="n">
         <v>27524</v>
@@ -11563,7 +11563,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G386" t="n">
-        <v>11.6843538284302</v>
+        <v>11.6843547821045</v>
       </c>
       <c r="H386" t="n">
         <v>27537</v>
@@ -11592,7 +11592,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H387" t="n">
         <v>110158</v>
@@ -11621,7 +11621,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>12.2536163330078</v>
+        <v>12.2536172866821</v>
       </c>
       <c r="H388" t="n">
         <v>47918</v>
@@ -11650,7 +11650,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966207504272</v>
+        <v>11.8966217041016</v>
       </c>
       <c r="H389" t="n">
         <v>33102</v>
@@ -11795,7 +11795,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545135498047</v>
+        <v>11.9545125961304</v>
       </c>
       <c r="H394" t="n">
         <v>7832</v>
@@ -11882,7 +11882,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H397" t="n">
         <v>62135</v>
@@ -11911,7 +11911,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G398" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H398" t="n">
         <v>107931</v>
@@ -11969,7 +11969,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G400" t="n">
-        <v>12.6492052078247</v>
+        <v>12.649206161499</v>
       </c>
       <c r="H400" t="n">
         <v>17470</v>
@@ -11998,7 +11998,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H401" t="n">
         <v>13252</v>
@@ -12027,7 +12027,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H402" t="n">
         <v>31655</v>
@@ -12085,7 +12085,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H404" t="n">
         <v>9320</v>
@@ -12114,7 +12114,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228797912598</v>
+        <v>12.8228788375854</v>
       </c>
       <c r="H405" t="n">
         <v>47428</v>
@@ -12143,7 +12143,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H406" t="n">
         <v>26294</v>
@@ -12375,7 +12375,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115072250366</v>
+        <v>12.3115081787109</v>
       </c>
       <c r="H414" t="n">
         <v>76954</v>
@@ -12433,7 +12433,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G416" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H416" t="n">
         <v>51186</v>
@@ -12462,7 +12462,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H417" t="n">
         <v>19263</v>
@@ -12491,7 +12491,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193639755249</v>
+        <v>12.9193649291992</v>
       </c>
       <c r="H418" t="n">
         <v>10876</v>
@@ -12549,7 +12549,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>13.054443359375</v>
+        <v>13.0544443130493</v>
       </c>
       <c r="H420" t="n">
         <v>17739</v>
@@ -12636,7 +12636,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>12.8904190063477</v>
+        <v>12.8904180526733</v>
       </c>
       <c r="H423" t="n">
         <v>19497</v>
@@ -12665,7 +12665,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H424" t="n">
         <v>8468</v>
@@ -12694,7 +12694,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167463302612</v>
+        <v>12.7167453765869</v>
       </c>
       <c r="H425" t="n">
         <v>35809</v>
@@ -12723,7 +12723,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5334234237671</v>
+        <v>12.5334243774414</v>
       </c>
       <c r="H426" t="n">
         <v>25449</v>
@@ -12810,7 +12810,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H429" t="n">
         <v>23103</v>
@@ -12897,7 +12897,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>13.2860088348389</v>
+        <v>13.2860078811646</v>
       </c>
       <c r="H432" t="n">
         <v>64869</v>
@@ -12984,7 +12984,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>13.9324588775635</v>
+        <v>13.9324579238892</v>
       </c>
       <c r="H435" t="n">
         <v>95509</v>
@@ -13042,7 +13042,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H437" t="n">
         <v>115869</v>
@@ -13071,7 +13071,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974496841431</v>
+        <v>12.6974487304688</v>
       </c>
       <c r="H438" t="n">
         <v>68110</v>
@@ -13100,7 +13100,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G439" t="n">
-        <v>12.6492052078247</v>
+        <v>12.649206161499</v>
       </c>
       <c r="H439" t="n">
         <v>104120</v>
@@ -13129,7 +13129,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H440" t="n">
         <v>33681</v>
@@ -13187,7 +13187,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H442" t="n">
         <v>23233</v>
@@ -13274,7 +13274,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H445" t="n">
         <v>16060</v>
@@ -13303,7 +13303,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044794082642</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H446" t="n">
         <v>35222</v>
@@ -13332,7 +13332,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H447" t="n">
         <v>14428</v>
@@ -13361,7 +13361,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>12.4851808547974</v>
+        <v>12.485179901123</v>
       </c>
       <c r="H448" t="n">
         <v>23317</v>
@@ -13390,7 +13390,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H449" t="n">
         <v>33026</v>
@@ -13448,7 +13448,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H451" t="n">
         <v>58859</v>
@@ -13622,7 +13622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H457" t="n">
         <v>24461</v>
@@ -13651,7 +13651,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>12.2536163330078</v>
+        <v>12.2536172866821</v>
       </c>
       <c r="H458" t="n">
         <v>49613</v>
@@ -13680,7 +13680,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H459" t="n">
         <v>27238</v>
@@ -13738,7 +13738,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044794082642</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H461" t="n">
         <v>38181</v>
@@ -13796,7 +13796,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>12.1764287948608</v>
+        <v>12.1764278411865</v>
       </c>
       <c r="H463" t="n">
         <v>18331</v>
@@ -13825,7 +13825,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9834575653076</v>
+        <v>11.9834585189819</v>
       </c>
       <c r="H464" t="n">
         <v>21813</v>
@@ -13883,7 +13883,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H466" t="n">
         <v>20941</v>
@@ -13912,7 +13912,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>12.0895929336548</v>
+        <v>12.0895919799805</v>
       </c>
       <c r="H467" t="n">
         <v>16532</v>
@@ -13941,7 +13941,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H468" t="n">
         <v>13736</v>
@@ -13970,7 +13970,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185388565063</v>
       </c>
       <c r="H469" t="n">
         <v>26893</v>
@@ -14028,7 +14028,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308048248291</v>
+        <v>12.3308038711548</v>
       </c>
       <c r="H471" t="n">
         <v>21463</v>
@@ -14057,7 +14057,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G472" t="n">
-        <v>12.1764287948608</v>
+        <v>12.1764278411865</v>
       </c>
       <c r="H472" t="n">
         <v>19926</v>
@@ -14144,7 +14144,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124034881592</v>
+        <v>12.0124025344849</v>
       </c>
       <c r="H475" t="n">
         <v>13507</v>
@@ -14202,7 +14202,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747074127197</v>
+        <v>11.6747055053711</v>
       </c>
       <c r="H477" t="n">
         <v>345190</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554828643799</v>
+        <v>9.45554733276367</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14289,7 +14289,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816593170166</v>
+        <v>9.65816497802734</v>
       </c>
       <c r="H480" t="n">
         <v>142514</v>
@@ -14347,7 +14347,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G482" t="n">
-        <v>9.85113620758057</v>
+        <v>9.85113716125488</v>
       </c>
       <c r="H482" t="n">
         <v>95444</v>
@@ -14405,7 +14405,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625068664551</v>
+        <v>10.3625078201294</v>
       </c>
       <c r="H484" t="n">
         <v>99264</v>
@@ -14492,7 +14492,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063383102417</v>
       </c>
       <c r="H487" t="n">
         <v>73996</v>
@@ -14666,7 +14666,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256368637085</v>
+        <v>10.8256359100342</v>
       </c>
       <c r="H493" t="n">
         <v>48038</v>
@@ -14782,7 +14782,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7388000488281</v>
+        <v>10.7387990951538</v>
       </c>
       <c r="H497" t="n">
         <v>62706</v>
@@ -14927,7 +14927,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H502" t="n">
         <v>89414</v>
@@ -14985,7 +14985,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612144470215</v>
+        <v>10.5612154006958</v>
       </c>
       <c r="H504" t="n">
         <v>62409</v>
@@ -15246,7 +15246,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H513" t="n">
         <v>68123</v>
@@ -15275,7 +15275,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763509750366</v>
       </c>
       <c r="H514" t="n">
         <v>22557</v>
@@ -15304,7 +15304,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H515" t="n">
         <v>114765</v>
@@ -15362,7 +15362,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110454559326</v>
+        <v>11.0110445022583</v>
       </c>
       <c r="H517" t="n">
         <v>116880</v>
@@ -15449,7 +15449,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763509750366</v>
       </c>
       <c r="H520" t="n">
         <v>17838</v>
@@ -15565,7 +15565,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>10.9328126907349</v>
+        <v>10.9328136444092</v>
       </c>
       <c r="H524" t="n">
         <v>31611</v>
@@ -15623,7 +15623,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.9523706436157</v>
+        <v>10.9523696899414</v>
       </c>
       <c r="H526" t="n">
         <v>85137</v>
@@ -15797,7 +15797,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H532" t="n">
         <v>61309</v>
@@ -15855,7 +15855,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634256362915</v>
+        <v>10.4634246826172</v>
       </c>
       <c r="H534" t="n">
         <v>20572</v>
@@ -15884,7 +15884,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069629669189</v>
+        <v>10.3069639205933</v>
       </c>
       <c r="H535" t="n">
         <v>59740</v>
@@ -16000,7 +16000,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H539" t="n">
         <v>38633</v>
@@ -16087,7 +16087,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261028289795</v>
+        <v>9.17261123657227</v>
       </c>
       <c r="H542" t="n">
         <v>15487</v>
@@ -16116,7 +16116,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H543" t="n">
         <v>21472</v>
@@ -16319,7 +16319,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H550" t="n">
         <v>18189</v>
@@ -16406,7 +16406,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H553" t="n">
         <v>22573</v>
@@ -16435,7 +16435,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H554" t="n">
         <v>94454</v>
@@ -16464,7 +16464,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432929992676</v>
+        <v>8.65432834625244</v>
       </c>
       <c r="H555" t="n">
         <v>68485</v>
@@ -16580,7 +16580,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H559" t="n">
         <v>111011</v>
@@ -16609,7 +16609,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H560" t="n">
         <v>77526</v>
@@ -16667,7 +16667,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H562" t="n">
         <v>31267</v>
@@ -16696,7 +16696,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H563" t="n">
         <v>28072</v>
@@ -16725,7 +16725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H564" t="n">
         <v>46125</v>
@@ -16754,7 +16754,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H565" t="n">
         <v>31639</v>
@@ -16783,7 +16783,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H566" t="n">
         <v>45222</v>
@@ -16870,7 +16870,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H569" t="n">
         <v>170656</v>
@@ -16957,7 +16957,7 @@
         <v>10.5</v>
       </c>
       <c r="G572" t="n">
-        <v>10.2678470611572</v>
+        <v>10.2678480148315</v>
       </c>
       <c r="H572" t="n">
         <v>116632</v>
@@ -17044,7 +17044,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H575" t="n">
         <v>94106</v>
@@ -17160,7 +17160,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>9.2215051651001</v>
+        <v>9.22150421142578</v>
       </c>
       <c r="H579" t="n">
         <v>84921</v>
@@ -17189,7 +17189,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G580" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H580" t="n">
         <v>59969</v>
@@ -17247,7 +17247,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12371635437012</v>
+        <v>9.1237154006958</v>
       </c>
       <c r="H582" t="n">
         <v>83347</v>
@@ -17305,7 +17305,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H584" t="n">
         <v>44575</v>
@@ -17363,7 +17363,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H586" t="n">
         <v>19894</v>
@@ -17392,7 +17392,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H587" t="n">
         <v>46974</v>
@@ -17450,7 +17450,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H589" t="n">
         <v>44363</v>
@@ -17479,7 +17479,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H590" t="n">
         <v>85332</v>
@@ -17508,7 +17508,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.99659061431885</v>
+        <v>8.99658966064453</v>
       </c>
       <c r="H591" t="n">
         <v>38459</v>
@@ -17566,7 +17566,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H593" t="n">
         <v>172995</v>
@@ -17595,7 +17595,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G594" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H594" t="n">
         <v>58404</v>
@@ -17624,7 +17624,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H595" t="n">
         <v>58894</v>
@@ -17653,7 +17653,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H596" t="n">
         <v>110779</v>
@@ -17711,7 +17711,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H598" t="n">
         <v>140106</v>
@@ -17740,7 +17740,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H599" t="n">
         <v>76971</v>
@@ -17856,7 +17856,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492267608643</v>
+        <v>9.95492362976074</v>
       </c>
       <c r="H603" t="n">
         <v>63044</v>
@@ -17914,7 +17914,7 @@
         <v>9.75</v>
       </c>
       <c r="G605" t="n">
-        <v>9.53443050384521</v>
+        <v>9.5344295501709</v>
       </c>
       <c r="H605" t="n">
         <v>44042</v>
@@ -17943,7 +17943,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H606" t="n">
         <v>38965</v>
@@ -18001,7 +18001,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H608" t="n">
         <v>28857</v>
@@ -18088,7 +18088,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H611" t="n">
         <v>15971</v>
@@ -18117,7 +18117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H612" t="n">
         <v>14746</v>
@@ -18175,7 +18175,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H614" t="n">
         <v>134678</v>
@@ -18204,7 +18204,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H615" t="n">
         <v>38849</v>
@@ -18233,7 +18233,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H616" t="n">
         <v>118933</v>
@@ -18349,7 +18349,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G620" t="n">
-        <v>9.55398750305176</v>
+        <v>9.55398845672607</v>
       </c>
       <c r="H620" t="n">
         <v>270273</v>
@@ -18378,7 +18378,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H621" t="n">
         <v>192357</v>
@@ -18436,7 +18436,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G623" t="n">
-        <v>10.0918273925781</v>
+        <v>10.0918264389038</v>
       </c>
       <c r="H623" t="n">
         <v>113503</v>
@@ -18465,7 +18465,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H624" t="n">
         <v>136644</v>
@@ -18494,7 +18494,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H625" t="n">
         <v>69374</v>
@@ -18610,7 +18610,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354545593262</v>
+        <v>9.57354640960693</v>
       </c>
       <c r="H629" t="n">
         <v>59629</v>
@@ -18697,7 +18697,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H632" t="n">
         <v>43105</v>
@@ -18726,7 +18726,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>9.13349437713623</v>
+        <v>9.13349533081055</v>
       </c>
       <c r="H633" t="n">
         <v>33022</v>
@@ -18813,7 +18813,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H636" t="n">
         <v>26549</v>
@@ -18842,7 +18842,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548358917236</v>
+        <v>9.04548454284668</v>
       </c>
       <c r="H637" t="n">
         <v>24740</v>
@@ -18871,7 +18871,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835784912109</v>
+        <v>8.91835880279541</v>
       </c>
       <c r="H638" t="n">
         <v>19976</v>
@@ -18900,7 +18900,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>8.99659061431885</v>
+        <v>8.99658966064453</v>
       </c>
       <c r="H639" t="n">
         <v>10481</v>
@@ -18958,7 +18958,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H641" t="n">
         <v>23994</v>
@@ -19103,7 +19103,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H646" t="n">
         <v>21998</v>
@@ -19277,7 +19277,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H652" t="n">
         <v>48424</v>
@@ -19306,7 +19306,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H653" t="n">
         <v>40921</v>
@@ -19335,7 +19335,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H654" t="n">
         <v>40142</v>
@@ -19393,7 +19393,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G656" t="n">
-        <v>9.2215051651001</v>
+        <v>9.22150421142578</v>
       </c>
       <c r="H656" t="n">
         <v>5166</v>
@@ -19422,7 +19422,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H657" t="n">
         <v>3751</v>
@@ -19451,7 +19451,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437942504883</v>
+        <v>9.09437847137451</v>
       </c>
       <c r="H658" t="n">
         <v>4851</v>
@@ -19480,7 +19480,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H659" t="n">
         <v>25360</v>
@@ -19741,7 +19741,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H668" t="n">
         <v>15830</v>
@@ -19973,7 +19973,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H676" t="n">
         <v>9923</v>
@@ -20031,7 +20031,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H678" t="n">
         <v>29641</v>
@@ -20060,7 +20060,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H679" t="n">
         <v>14909</v>
@@ -20147,7 +20147,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956607818604</v>
+        <v>9.74956512451172</v>
       </c>
       <c r="H682" t="n">
         <v>32449</v>
@@ -20176,7 +20176,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H683" t="n">
         <v>37382</v>
@@ -20205,7 +20205,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H684" t="n">
         <v>18917</v>
@@ -20350,7 +20350,7 @@
         <v>9.75</v>
       </c>
       <c r="G689" t="n">
-        <v>9.53443050384521</v>
+        <v>9.5344295501709</v>
       </c>
       <c r="H689" t="n">
         <v>11078</v>
@@ -20611,7 +20611,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H698" t="n">
         <v>21356</v>
@@ -20640,7 +20640,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H699" t="n">
         <v>21197</v>
@@ -20756,7 +20756,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H703" t="n">
         <v>10949</v>
@@ -20843,7 +20843,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H706" t="n">
         <v>17733</v>
@@ -20872,7 +20872,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H707" t="n">
         <v>60633</v>
@@ -20930,7 +20930,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H709" t="n">
         <v>27319</v>
@@ -20988,7 +20988,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G711" t="n">
-        <v>8.34140300750732</v>
+        <v>8.34140396118164</v>
       </c>
       <c r="H711" t="n">
         <v>50079</v>
@@ -21046,7 +21046,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H713" t="n">
         <v>161407</v>
@@ -21133,7 +21133,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G716" t="n">
-        <v>8.34140300750732</v>
+        <v>8.34140396118164</v>
       </c>
       <c r="H716" t="n">
         <v>45582</v>
@@ -21220,7 +21220,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G719" t="n">
-        <v>8.22405624389648</v>
+        <v>8.2240571975708</v>
       </c>
       <c r="H719" t="n">
         <v>28804</v>
@@ -21365,7 +21365,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924289703369</v>
+        <v>8.87924385070801</v>
       </c>
       <c r="H724" t="n">
         <v>16711</v>
@@ -21510,7 +21510,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H729" t="n">
         <v>24316</v>
@@ -21800,7 +21800,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>6.8647894859314</v>
+        <v>6.86478900909424</v>
       </c>
       <c r="H739" t="n">
         <v>73987</v>
@@ -21916,7 +21916,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H743" t="n">
         <v>14937</v>
@@ -22003,7 +22003,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385478973389</v>
+        <v>6.46385431289673</v>
       </c>
       <c r="H746" t="n">
         <v>68949</v>
@@ -22061,7 +22061,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G748" t="n">
-        <v>5.57397413253784</v>
+        <v>5.573974609375</v>
       </c>
       <c r="H748" t="n">
         <v>167124</v>
@@ -22119,7 +22119,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H750" t="n">
         <v>185723</v>
@@ -22148,7 +22148,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.71343088150024</v>
+        <v>4.7134313583374</v>
       </c>
       <c r="H751" t="n">
         <v>210848</v>
@@ -22177,7 +22177,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760669708252</v>
+        <v>4.30760622024536</v>
       </c>
       <c r="H752" t="n">
         <v>95208</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22322,7 +22322,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357624053955</v>
+        <v>4.04357671737671</v>
       </c>
       <c r="H757" t="n">
         <v>116412</v>
@@ -22380,7 +22380,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>4.29782772064209</v>
+        <v>4.29782819747925</v>
       </c>
       <c r="H759" t="n">
         <v>196124</v>
@@ -22409,7 +22409,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00935029983521</v>
+        <v>4.00934982299805</v>
       </c>
       <c r="H760" t="n">
         <v>97203</v>
@@ -22467,7 +22467,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.9800136089325</v>
+        <v>3.98001313209534</v>
       </c>
       <c r="H762" t="n">
         <v>31531</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22554,7 +22554,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691808700562</v>
+        <v>4.11691761016846</v>
       </c>
       <c r="H765" t="n">
         <v>28600</v>
@@ -22612,7 +22612,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630514144897</v>
+        <v>4.58630561828613</v>
       </c>
       <c r="H767" t="n">
         <v>113983</v>
@@ -22786,7 +22786,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055614471436</v>
+        <v>4.84055662155151</v>
       </c>
       <c r="H773" t="n">
         <v>56598</v>
@@ -22902,7 +22902,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>5.47618532180786</v>
+        <v>5.4761848449707</v>
       </c>
       <c r="H777" t="n">
         <v>121084</v>
@@ -22960,7 +22960,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H779" t="n">
         <v>69616</v>
@@ -23018,7 +23018,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H781" t="n">
         <v>53399</v>
@@ -23047,7 +23047,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485822677612</v>
+        <v>5.53485870361328</v>
       </c>
       <c r="H782" t="n">
         <v>74521</v>
@@ -23134,7 +23134,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773296356201</v>
+        <v>5.40773344039917</v>
       </c>
       <c r="H785" t="n">
         <v>58953</v>
@@ -23192,7 +23192,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H787" t="n">
         <v>18969</v>
@@ -23424,7 +23424,7 @@
         <v>5.25</v>
       </c>
       <c r="G795" t="n">
-        <v>5.13392353057861</v>
+        <v>5.13392400741577</v>
       </c>
       <c r="H795" t="n">
         <v>16038</v>
@@ -23482,7 +23482,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H797" t="n">
         <v>11846</v>
@@ -23511,7 +23511,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171281814575</v>
+        <v>5.23171234130859</v>
       </c>
       <c r="H798" t="n">
         <v>3968</v>
@@ -23540,7 +23540,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H799" t="n">
         <v>12491</v>
@@ -23569,7 +23569,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H800" t="n">
         <v>42807</v>
@@ -23656,7 +23656,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>5.24149179458618</v>
+        <v>5.24149131774902</v>
       </c>
       <c r="H803" t="n">
         <v>20595</v>
@@ -23714,7 +23714,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H805" t="n">
         <v>18129</v>
@@ -23859,7 +23859,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.97746133804321</v>
+        <v>4.97746181488037</v>
       </c>
       <c r="H810" t="n">
         <v>46277</v>
@@ -23888,7 +23888,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H811" t="n">
         <v>36173</v>
@@ -23946,7 +23946,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>5.04591369628906</v>
+        <v>5.0459132194519</v>
       </c>
       <c r="H813" t="n">
         <v>4389</v>
@@ -23975,7 +23975,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>4.97746133804321</v>
+        <v>4.97746181488037</v>
       </c>
       <c r="H814" t="n">
         <v>26888</v>
@@ -24149,7 +24149,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>5.47618532180786</v>
+        <v>5.4761848449707</v>
       </c>
       <c r="H820" t="n">
         <v>62956</v>
@@ -24323,7 +24323,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H826" t="n">
         <v>18416</v>
@@ -24352,7 +24352,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H827" t="n">
         <v>27618</v>
@@ -24381,7 +24381,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G828" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H828" t="n">
         <v>56372</v>
@@ -24410,7 +24410,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264846801758</v>
+        <v>5.63264799118042</v>
       </c>
       <c r="H829" t="n">
         <v>49059</v>
@@ -24613,7 +24613,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314111709595</v>
+        <v>6.05314064025879</v>
       </c>
       <c r="H836" t="n">
         <v>52635</v>
@@ -24700,7 +24700,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H839" t="n">
         <v>63435</v>
@@ -24729,7 +24729,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G840" t="n">
-        <v>6.73766374588013</v>
+        <v>6.73766326904297</v>
       </c>
       <c r="H840" t="n">
         <v>81839</v>
@@ -25019,7 +25019,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>6.08247661590576</v>
+        <v>6.08247709274292</v>
       </c>
       <c r="H850" t="n">
         <v>27868</v>
@@ -25048,7 +25048,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.1411509513855</v>
+        <v>6.14115142822266</v>
       </c>
       <c r="H851" t="n">
         <v>14069</v>
@@ -25077,7 +25077,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H852" t="n">
         <v>26701</v>
@@ -25164,7 +25164,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G855" t="n">
-        <v>5.92601537704468</v>
+        <v>5.92601490020752</v>
       </c>
       <c r="H855" t="n">
         <v>66134</v>
@@ -25193,7 +25193,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78911066055298</v>
+        <v>5.78911018371582</v>
       </c>
       <c r="H856" t="n">
         <v>10669</v>
@@ -25338,7 +25338,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H861" t="n">
         <v>15530</v>
@@ -25367,7 +25367,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>5.60331106185913</v>
+        <v>5.60331058502197</v>
       </c>
       <c r="H862" t="n">
         <v>22714</v>
@@ -25425,7 +25425,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>5.82822561264038</v>
+        <v>5.82822608947754</v>
       </c>
       <c r="H864" t="n">
         <v>48237</v>
@@ -25541,7 +25541,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G868" t="n">
-        <v>5.57397413253784</v>
+        <v>5.573974609375</v>
       </c>
       <c r="H868" t="n">
         <v>10349</v>
@@ -25715,7 +25715,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>5.95535135269165</v>
+        <v>5.95535182952881</v>
       </c>
       <c r="H874" t="n">
         <v>19266</v>
@@ -25947,7 +25947,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H882" t="n">
         <v>57113</v>
@@ -25976,7 +25976,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H883" t="n">
         <v>26982</v>
@@ -26005,7 +26005,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H884" t="n">
         <v>30149</v>
@@ -26034,7 +26034,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H885" t="n">
         <v>23779</v>
@@ -26063,7 +26063,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>6.53230667114258</v>
+        <v>6.53230619430542</v>
       </c>
       <c r="H886" t="n">
         <v>143444</v>
@@ -26092,7 +26092,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>6.65943241119385</v>
+        <v>6.65943193435669</v>
       </c>
       <c r="H887" t="n">
         <v>78414</v>
@@ -26237,7 +26237,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H892" t="n">
         <v>34785</v>
@@ -26266,7 +26266,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700019836426</v>
+        <v>6.76700067520142</v>
       </c>
       <c r="H893" t="n">
         <v>47611</v>
@@ -26295,7 +26295,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655862808228</v>
+        <v>6.78655815124512</v>
       </c>
       <c r="H894" t="n">
         <v>16921</v>
@@ -26353,7 +26353,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H896" t="n">
         <v>155510</v>
@@ -26411,7 +26411,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96002721786499</v>
+        <v>7.96002626419067</v>
       </c>
       <c r="H898" t="n">
         <v>68196</v>
@@ -26498,7 +26498,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>7.62754392623901</v>
+        <v>7.62754440307617</v>
       </c>
       <c r="H901" t="n">
         <v>13903</v>
@@ -26527,7 +26527,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G902" t="n">
-        <v>7.62754392623901</v>
+        <v>7.62754440307617</v>
       </c>
       <c r="H902" t="n">
         <v>45564</v>
@@ -26556,7 +26556,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75466918945312</v>
+        <v>7.75466966629028</v>
       </c>
       <c r="H903" t="n">
         <v>44412</v>
@@ -26614,7 +26614,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G905" t="n">
-        <v>7.73511123657227</v>
+        <v>7.73511171340942</v>
       </c>
       <c r="H905" t="n">
         <v>13300</v>
@@ -26672,7 +26672,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>7.39285039901733</v>
+        <v>7.39284992218018</v>
       </c>
       <c r="H907" t="n">
         <v>26842</v>
@@ -26701,7 +26701,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G908" t="n">
-        <v>7.64710187911987</v>
+        <v>7.64710140228271</v>
       </c>
       <c r="H908" t="n">
         <v>26314</v>
@@ -26730,7 +26730,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>7.41240835189819</v>
+        <v>7.41240787506104</v>
       </c>
       <c r="H909" t="n">
         <v>50527</v>
@@ -26991,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G918" t="n">
-        <v>6.8452320098877</v>
+        <v>6.84523153305054</v>
       </c>
       <c r="H918" t="n">
         <v>53696</v>
@@ -27020,7 +27020,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G919" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H919" t="n">
         <v>21477</v>
@@ -27049,7 +27049,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G920" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H920" t="n">
         <v>51184</v>
@@ -27078,7 +27078,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G921" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H921" t="n">
         <v>61586</v>
@@ -27107,7 +27107,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412593841553</v>
+        <v>6.89412641525269</v>
       </c>
       <c r="H922" t="n">
         <v>17841</v>
@@ -27194,7 +27194,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793489456177</v>
+        <v>7.16793537139893</v>
       </c>
       <c r="H925" t="n">
         <v>17282</v>
@@ -27281,7 +27281,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H928" t="n">
         <v>40663</v>
@@ -27484,7 +27484,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H935" t="n">
         <v>42761</v>
@@ -27513,7 +27513,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H936" t="n">
         <v>10858</v>
@@ -27542,7 +27542,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H937" t="n">
         <v>15176</v>
@@ -27571,7 +27571,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G938" t="n">
-        <v>7.96002721786499</v>
+        <v>7.96002626419067</v>
       </c>
       <c r="H938" t="n">
         <v>165920</v>
@@ -27803,7 +27803,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G946" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H946" t="n">
         <v>263636</v>
@@ -27861,7 +27861,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H948" t="n">
         <v>77374</v>
@@ -27890,7 +27890,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G949" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H949" t="n">
         <v>212562</v>
@@ -27948,7 +27948,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G951" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H951" t="n">
         <v>256448</v>
@@ -28064,7 +28064,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>8.59565544128418</v>
+        <v>8.5956563949585</v>
       </c>
       <c r="H955" t="n">
         <v>181604</v>
@@ -28151,7 +28151,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37074089050293</v>
+        <v>8.37073993682861</v>
       </c>
       <c r="H958" t="n">
         <v>44957</v>
@@ -28209,7 +28209,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>8.22405624389648</v>
+        <v>8.2240571975708</v>
       </c>
       <c r="H960" t="n">
         <v>34300</v>
@@ -28383,7 +28383,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>8.45874977111816</v>
+        <v>8.45875072479248</v>
       </c>
       <c r="H966" t="n">
         <v>67238</v>
@@ -28412,7 +28412,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449829101562</v>
+        <v>8.20449924468994</v>
       </c>
       <c r="H967" t="n">
         <v>42116</v>
@@ -28644,7 +28644,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.4953145980835</v>
+        <v>9.49531364440918</v>
       </c>
       <c r="H975" t="n">
         <v>336362</v>
@@ -28673,7 +28673,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>9.24106311798096</v>
+        <v>9.24106216430664</v>
       </c>
       <c r="H976" t="n">
         <v>268935</v>
@@ -28702,7 +28702,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>9.74956607818604</v>
+        <v>9.74956512451172</v>
       </c>
       <c r="H977" t="n">
         <v>117145</v>
@@ -28789,7 +28789,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H980" t="n">
         <v>214809</v>
@@ -28934,7 +28934,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9107027053833</v>
+        <v>11.9107036590576</v>
       </c>
       <c r="H985" t="n">
         <v>111245</v>
@@ -29021,7 +29021,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H988" t="n">
         <v>321229</v>
@@ -29137,7 +29137,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882518768311</v>
+        <v>13.7882528305054</v>
       </c>
       <c r="H992" t="n">
         <v>403792</v>
@@ -29253,7 +29253,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G996" t="n">
-        <v>15.0790681838989</v>
+        <v>15.0790672302246</v>
       </c>
       <c r="H996" t="n">
         <v>358240</v>
@@ -29282,7 +29282,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705652236938</v>
+        <v>14.5705642700195</v>
       </c>
       <c r="H997" t="n">
         <v>150561</v>
@@ -29427,7 +29427,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.3188648223877</v>
+        <v>13.3188638687134</v>
       </c>
       <c r="H1002" t="n">
         <v>70482</v>
@@ -29456,7 +29456,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.0059404373169</v>
+        <v>13.0059413909912</v>
       </c>
       <c r="H1003" t="n">
         <v>82659</v>
@@ -29630,7 +29630,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1009" t="n">
         <v>78089</v>
@@ -29688,7 +29688,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867233276367</v>
+        <v>12.0867223739624</v>
       </c>
       <c r="H1011" t="n">
         <v>47356</v>
@@ -29862,7 +29862,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5561113357544</v>
+        <v>12.5561103820801</v>
       </c>
       <c r="H1017" t="n">
         <v>121329</v>
@@ -29891,7 +29891,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1018" t="n">
         <v>91050</v>
@@ -29949,7 +29949,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.5365524291992</v>
+        <v>12.5365533828735</v>
       </c>
       <c r="H1020" t="n">
         <v>66770</v>
@@ -29978,7 +29978,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1021" t="n">
         <v>151231</v>
@@ -30065,7 +30065,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1024" t="n">
         <v>111837</v>
@@ -30123,7 +30123,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.5952262878418</v>
+        <v>12.5952253341675</v>
       </c>
       <c r="H1026" t="n">
         <v>82690</v>
@@ -30239,7 +30239,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1030" t="n">
         <v>99601</v>
@@ -30268,7 +30268,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1031" t="n">
         <v>57835</v>
@@ -30413,7 +30413,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1036" t="n">
         <v>90647</v>
@@ -30674,7 +30674,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.4192056655884</v>
+        <v>12.4192066192627</v>
       </c>
       <c r="H1045" t="n">
         <v>16548</v>
@@ -30732,7 +30732,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409748077393</v>
+        <v>12.3409738540649</v>
       </c>
       <c r="H1047" t="n">
         <v>46643</v>
@@ -30819,7 +30819,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H1050" t="n">
         <v>110815</v>
@@ -30906,7 +30906,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H1053" t="n">
         <v>195883</v>
@@ -30935,7 +30935,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H1054" t="n">
         <v>167159</v>
@@ -31080,7 +31080,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220985412598</v>
+        <v>10.5220994949341</v>
       </c>
       <c r="H1059" t="n">
         <v>104597</v>
@@ -31109,7 +31109,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.209174156189</v>
+        <v>10.2091732025146</v>
       </c>
       <c r="H1060" t="n">
         <v>129001</v>
@@ -31544,7 +31544,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.17261028289795</v>
+        <v>9.17261123657227</v>
       </c>
       <c r="H1075" t="n">
         <v>127062</v>
@@ -31660,7 +31660,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.3265209197998</v>
+        <v>10.3265218734741</v>
       </c>
       <c r="H1079" t="n">
         <v>87842</v>
@@ -31718,7 +31718,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H1081" t="n">
         <v>25731</v>
@@ -31747,7 +31747,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0918273925781</v>
+        <v>10.0918264389038</v>
       </c>
       <c r="H1082" t="n">
         <v>25318</v>
@@ -31834,7 +31834,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.9523706436157</v>
+        <v>10.9523696899414</v>
       </c>
       <c r="H1085" t="n">
         <v>43194</v>
@@ -31950,7 +31950,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.181960105896</v>
+        <v>13.1819591522217</v>
       </c>
       <c r="H1089" t="n">
         <v>178518</v>
@@ -32153,7 +32153,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882518768311</v>
+        <v>13.7882528305054</v>
       </c>
       <c r="H1096" t="n">
         <v>93691</v>
@@ -32240,7 +32240,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>13.8273677825928</v>
+        <v>13.8273687362671</v>
       </c>
       <c r="H1099" t="n">
         <v>108983</v>
@@ -32327,7 +32327,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>14.4532175064087</v>
+        <v>14.4532165527344</v>
       </c>
       <c r="H1102" t="n">
         <v>33492</v>
@@ -32385,7 +32385,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749856948853</v>
+        <v>14.3749866485596</v>
       </c>
       <c r="H1104" t="n">
         <v>36166</v>
@@ -32414,7 +32414,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030466079712</v>
+        <v>14.9030475616455</v>
       </c>
       <c r="H1105" t="n">
         <v>135713</v>
@@ -32443,7 +32443,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.7074699401855</v>
+        <v>14.7074689865112</v>
       </c>
       <c r="H1106" t="n">
         <v>120242</v>
@@ -32559,7 +32559,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396095275879</v>
+        <v>15.9396104812622</v>
       </c>
       <c r="H1110" t="n">
         <v>152433</v>
@@ -32791,7 +32791,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1118" t="n">
         <v>186738</v>
@@ -32820,7 +32820,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1119" t="n">
         <v>218593</v>
@@ -32878,7 +32878,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981105804443</v>
+        <v>22.1981086730957</v>
       </c>
       <c r="H1121" t="n">
         <v>87185</v>
@@ -32907,7 +32907,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.758056640625</v>
+        <v>21.7580585479736</v>
       </c>
       <c r="H1122" t="n">
         <v>177161</v>
@@ -33023,7 +33023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1126" t="n">
         <v>169849</v>
@@ -33052,7 +33052,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1127" t="n">
         <v>153071</v>
@@ -33139,7 +33139,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>21.1713218688965</v>
+        <v>21.1713237762451</v>
       </c>
       <c r="H1130" t="n">
         <v>60803</v>
@@ -33197,7 +33197,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602668762207</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1132" t="n">
         <v>103507</v>
@@ -33255,7 +33255,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602668762207</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1134" t="n">
         <v>98501</v>
@@ -33284,7 +33284,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1135" t="n">
         <v>53815</v>
@@ -33574,7 +33574,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1145" t="n">
         <v>26612</v>
@@ -33661,7 +33661,7 @@
         <v>21.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>20.7801666259766</v>
+        <v>20.7801685333252</v>
       </c>
       <c r="H1148" t="n">
         <v>26335</v>
@@ -33777,7 +33777,7 @@
         <v>21</v>
       </c>
       <c r="G1152" t="n">
-        <v>20.5356941223145</v>
+        <v>20.5356960296631</v>
       </c>
       <c r="H1152" t="n">
         <v>77191</v>
@@ -33806,7 +33806,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1153" t="n">
         <v>112291</v>
@@ -33951,7 +33951,7 @@
         <v>24.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.9583129882812</v>
+        <v>23.9583110809326</v>
       </c>
       <c r="H1158" t="n">
         <v>67635</v>
@@ -34038,7 +34038,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7848434448242</v>
+        <v>22.7848415374756</v>
       </c>
       <c r="H1161" t="n">
         <v>56547</v>
@@ -34183,7 +34183,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1166" t="n">
         <v>72421</v>
@@ -34212,7 +34212,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1167" t="n">
         <v>34211</v>
@@ -34241,7 +34241,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1168" t="n">
         <v>45591</v>
@@ -34328,7 +34328,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.2958965301514</v>
+        <v>22.2958984375</v>
       </c>
       <c r="H1171" t="n">
         <v>50849</v>
@@ -34357,7 +34357,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1172" t="n">
         <v>37810</v>
@@ -34415,7 +34415,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1174" t="n">
         <v>29225</v>
@@ -34444,7 +34444,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1175" t="n">
         <v>25765</v>
@@ -34502,7 +34502,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.5403690338135</v>
+        <v>22.5403671264648</v>
       </c>
       <c r="H1177" t="n">
         <v>15746</v>
@@ -34560,7 +34560,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1179" t="n">
         <v>25025</v>
@@ -34589,7 +34589,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1180" t="n">
         <v>34676</v>
@@ -34618,7 +34618,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1181" t="n">
         <v>48003</v>
@@ -34647,7 +34647,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1182" t="n">
         <v>39901</v>
@@ -34676,7 +34676,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1183" t="n">
         <v>60552</v>
@@ -34763,7 +34763,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1186" t="n">
         <v>55489</v>
@@ -34908,7 +34908,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1191" t="n">
         <v>39920</v>
@@ -35256,7 +35256,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.2958965301514</v>
+        <v>22.2958984375</v>
       </c>
       <c r="H1203" t="n">
         <v>114554</v>
@@ -35285,7 +35285,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1204" t="n">
         <v>133530</v>
@@ -35372,7 +35372,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.926851272583</v>
+        <v>20.9268493652344</v>
       </c>
       <c r="H1207" t="n">
         <v>80989</v>
@@ -35488,7 +35488,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1211" t="n">
         <v>36573</v>
@@ -35604,7 +35604,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511695861816</v>
+        <v>19.8511714935303</v>
       </c>
       <c r="H1215" t="n">
         <v>97038</v>
@@ -35720,7 +35720,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.7533855438232</v>
+        <v>19.7533836364746</v>
       </c>
       <c r="H1219" t="n">
         <v>54410</v>
@@ -35749,7 +35749,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470909118652</v>
+        <v>19.1470928192139</v>
       </c>
       <c r="H1220" t="n">
         <v>78205</v>
@@ -35836,7 +35836,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.2669887542725</v>
+        <v>18.2669906616211</v>
       </c>
       <c r="H1223" t="n">
         <v>95192</v>
@@ -36010,7 +36010,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.3698806762695</v>
+        <v>16.3698825836182</v>
       </c>
       <c r="H1229" t="n">
         <v>80556</v>
@@ -36039,7 +36039,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329788208008</v>
+        <v>16.2329769134521</v>
       </c>
       <c r="H1230" t="n">
         <v>93368</v>
@@ -36068,7 +36068,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743049621582</v>
+        <v>16.1743068695068</v>
       </c>
       <c r="H1231" t="n">
         <v>45139</v>
@@ -36097,7 +36097,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.9174995422363</v>
+        <v>16.917501449585</v>
       </c>
       <c r="H1232" t="n">
         <v>52351</v>
@@ -36213,7 +36213,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1236" t="n">
         <v>105949</v>
@@ -36271,7 +36271,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304267883301</v>
+        <v>17.2304248809814</v>
       </c>
       <c r="H1238" t="n">
         <v>124533</v>
@@ -36358,7 +36358,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1241" t="n">
-        <v>17.054407119751</v>
+        <v>17.0544052124023</v>
       </c>
       <c r="H1241" t="n">
         <v>48546</v>
@@ -36445,7 +36445,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042324066162</v>
+        <v>17.5042343139648</v>
       </c>
       <c r="H1244" t="n">
         <v>65827</v>
@@ -36474,7 +36474,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.4846782684326</v>
+        <v>17.484676361084</v>
       </c>
       <c r="H1245" t="n">
         <v>68340</v>
@@ -36532,7 +36532,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1247" t="n">
         <v>82416</v>
@@ -36561,7 +36561,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.5459041595459</v>
+        <v>16.5459022521973</v>
       </c>
       <c r="H1248" t="n">
         <v>44400</v>
@@ -36677,7 +36677,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.721923828125</v>
+        <v>16.7219219207764</v>
       </c>
       <c r="H1252" t="n">
         <v>39230</v>
@@ -36735,7 +36735,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761753082275</v>
+        <v>16.9761734008789</v>
       </c>
       <c r="H1254" t="n">
         <v>30692</v>
@@ -36764,7 +36764,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.721923828125</v>
+        <v>16.7219219207764</v>
       </c>
       <c r="H1255" t="n">
         <v>38089</v>
@@ -36851,7 +36851,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414817810059</v>
+        <v>16.7414798736572</v>
       </c>
       <c r="H1258" t="n">
         <v>87008</v>
@@ -36938,7 +36938,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>19.594820022583</v>
+        <v>19.5948181152344</v>
       </c>
       <c r="H1261" t="n">
         <v>421870</v>
@@ -36996,7 +36996,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6342830657959</v>
+        <v>19.6342849731445</v>
       </c>
       <c r="H1263" t="n">
         <v>110426</v>
@@ -37199,7 +37199,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1270" t="n">
         <v>151182</v>
@@ -37228,7 +37228,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>21.8542404174805</v>
+        <v>21.8542423248291</v>
       </c>
       <c r="H1271" t="n">
         <v>144900</v>
@@ -37257,7 +37257,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.8542404174805</v>
+        <v>21.8542423248291</v>
       </c>
       <c r="H1272" t="n">
         <v>100072</v>
@@ -37431,7 +37431,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1278" t="n">
         <v>268613</v>
@@ -37605,7 +37605,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.5750865936279</v>
+        <v>19.5750846862793</v>
       </c>
       <c r="H1284" t="n">
         <v>112686</v>
@@ -37779,7 +37779,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>18.5687065124512</v>
+        <v>18.5687046051025</v>
       </c>
       <c r="H1290" t="n">
         <v>80819</v>
@@ -37866,7 +37866,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.3777542114258</v>
+        <v>19.3777561187744</v>
       </c>
       <c r="H1293" t="n">
         <v>96973</v>
@@ -37895,7 +37895,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1294" t="n">
-        <v>19.2988224029541</v>
+        <v>19.2988243103027</v>
       </c>
       <c r="H1294" t="n">
         <v>80244</v>
@@ -37924,7 +37924,7 @@
         <v>19.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>19.2396259307861</v>
+        <v>19.2396240234375</v>
       </c>
       <c r="H1295" t="n">
         <v>270887</v>
@@ -37953,7 +37953,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.7132148742676</v>
+        <v>19.7132167816162</v>
       </c>
       <c r="H1296" t="n">
         <v>176673</v>
@@ -37982,7 +37982,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1297" t="n">
         <v>155909</v>
@@ -38040,7 +38040,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1299" t="n">
         <v>88312</v>
@@ -38069,7 +38069,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.5089149475098</v>
+        <v>21.5089130401611</v>
       </c>
       <c r="H1300" t="n">
         <v>61890</v>
@@ -38098,7 +38098,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1301" t="n">
         <v>220236</v>
@@ -38156,7 +38156,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>21.1635894775391</v>
+        <v>21.1635875701904</v>
       </c>
       <c r="H1303" t="n">
         <v>114500</v>
@@ -38214,7 +38214,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.8182621002197</v>
+        <v>20.8182601928711</v>
       </c>
       <c r="H1305" t="n">
         <v>89332</v>
@@ -38272,7 +38272,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1307" t="n">
         <v>216127</v>
@@ -38330,7 +38330,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.6737518310547</v>
+        <v>19.6737499237061</v>
       </c>
       <c r="H1309" t="n">
         <v>87050</v>
@@ -38359,7 +38359,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.2988224029541</v>
+        <v>19.2988243103027</v>
       </c>
       <c r="H1310" t="n">
         <v>41832</v>
@@ -38388,7 +38388,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.6145496368408</v>
+        <v>19.6145515441895</v>
       </c>
       <c r="H1311" t="n">
         <v>34200</v>
@@ -38591,7 +38591,7 @@
         <v>23.75</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.4328765869141</v>
+        <v>23.4328784942627</v>
       </c>
       <c r="H1318" t="n">
         <v>828551</v>
@@ -38649,7 +38649,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>22.2982330322266</v>
+        <v>22.2982311248779</v>
       </c>
       <c r="H1320" t="n">
         <v>98729</v>
@@ -38678,7 +38678,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>21.2622528076172</v>
+        <v>21.2622509002686</v>
       </c>
       <c r="H1321" t="n">
         <v>138690</v>
@@ -38939,7 +38939,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>22.8902206420898</v>
+        <v>22.8902225494385</v>
       </c>
       <c r="H1330" t="n">
         <v>103493</v>
@@ -39026,7 +39026,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1333" t="n">
         <v>102759</v>
@@ -39229,7 +39229,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1340" t="n">
-        <v>26.1856250762939</v>
+        <v>26.1856231689453</v>
       </c>
       <c r="H1340" t="n">
         <v>75983</v>
@@ -39490,7 +39490,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1349" t="n">
-        <v>24.05446434021</v>
+        <v>24.0544624328613</v>
       </c>
       <c r="H1349" t="n">
         <v>83400</v>
@@ -39548,7 +39548,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.4230098724365</v>
+        <v>23.4230117797852</v>
       </c>
       <c r="H1351" t="n">
         <v>42477</v>
@@ -39635,7 +39635,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G1354" t="n">
-        <v>23.1467475891113</v>
+        <v>23.14674949646</v>
       </c>
       <c r="H1354" t="n">
         <v>32490</v>
@@ -39664,7 +39664,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.7126235961914</v>
+        <v>22.71262550354</v>
       </c>
       <c r="H1355" t="n">
         <v>83180</v>
@@ -39693,7 +39693,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.0086193084717</v>
+        <v>23.008617401123</v>
       </c>
       <c r="H1356" t="n">
         <v>67559</v>
@@ -39809,7 +39809,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1360" t="n">
         <v>218042</v>
@@ -39838,7 +39838,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1361" t="n">
-        <v>23.5216751098633</v>
+        <v>23.5216770172119</v>
       </c>
       <c r="H1361" t="n">
         <v>73675</v>
@@ -39954,7 +39954,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1365" t="n">
-        <v>24.6464519500732</v>
+        <v>24.6464538574219</v>
       </c>
       <c r="H1365" t="n">
         <v>92733</v>
@@ -40041,7 +40041,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1368" t="n">
         <v>59967</v>
@@ -40186,7 +40186,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1373" t="n">
-        <v>24.9029808044434</v>
+        <v>24.902982711792</v>
       </c>
       <c r="H1373" t="n">
         <v>125191</v>
@@ -40215,7 +40215,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>24.7648525238037</v>
+        <v>24.7648506164551</v>
       </c>
       <c r="H1374" t="n">
         <v>78394</v>
@@ -40244,7 +40244,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1375" t="n">
-        <v>24.4096584320068</v>
+        <v>24.4096565246582</v>
       </c>
       <c r="H1375" t="n">
         <v>68323</v>
@@ -40273,7 +40273,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1376" t="n">
-        <v>24.4293918609619</v>
+        <v>24.4293899536133</v>
       </c>
       <c r="H1376" t="n">
         <v>54879</v>
@@ -40360,7 +40360,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1379" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1379" t="n">
         <v>48881</v>
@@ -40389,7 +40389,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.5872554779053</v>
+        <v>24.5872535705566</v>
       </c>
       <c r="H1380" t="n">
         <v>59300</v>
@@ -40476,7 +40476,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.2250881195068</v>
+        <v>26.2250900268555</v>
       </c>
       <c r="H1383" t="n">
         <v>131925</v>
@@ -40505,7 +40505,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1384" t="n">
-        <v>28.4351787567139</v>
+        <v>28.4351806640625</v>
       </c>
       <c r="H1384" t="n">
         <v>187997</v>
@@ -40708,7 +40708,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1391" t="n">
-        <v>24.5872554779053</v>
+        <v>24.5872535705566</v>
       </c>
       <c r="H1391" t="n">
         <v>74513</v>
@@ -40766,7 +40766,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1393" t="n">
-        <v>24.6267185211182</v>
+        <v>24.6267204284668</v>
       </c>
       <c r="H1393" t="n">
         <v>106208</v>
@@ -40795,7 +40795,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>24.6069889068604</v>
+        <v>24.6069869995117</v>
       </c>
       <c r="H1394" t="n">
         <v>64862</v>
@@ -40824,7 +40824,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>24.7253837585449</v>
+        <v>24.7253856658936</v>
       </c>
       <c r="H1395" t="n">
         <v>43250</v>
@@ -40882,7 +40882,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>24.4688549041748</v>
+        <v>24.4688568115234</v>
       </c>
       <c r="H1397" t="n">
         <v>69714</v>
@@ -40911,7 +40911,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>24.4293918609619</v>
+        <v>24.4293899536133</v>
       </c>
       <c r="H1398" t="n">
         <v>26167</v>
@@ -40969,7 +40969,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>24.1531295776367</v>
+        <v>24.1531276702881</v>
       </c>
       <c r="H1400" t="n">
         <v>39041</v>
@@ -41143,7 +41143,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>24.4688549041748</v>
+        <v>24.4688568115234</v>
       </c>
       <c r="H1406" t="n">
         <v>48196</v>
@@ -41201,7 +41201,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1408" t="n">
-        <v>24.05446434021</v>
+        <v>24.0544624328613</v>
       </c>
       <c r="H1408" t="n">
         <v>26194</v>
@@ -41230,7 +41230,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1409" t="n">
         <v>183680</v>
@@ -41288,7 +41288,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3899230957031</v>
+        <v>24.3899250030518</v>
       </c>
       <c r="H1411" t="n">
         <v>56923</v>
@@ -41404,7 +41404,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.3307266235352</v>
+        <v>24.3307247161865</v>
       </c>
       <c r="H1415" t="n">
         <v>94778</v>
@@ -41636,7 +41636,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.3440780639648</v>
+        <v>23.3440799713135</v>
       </c>
       <c r="H1423" t="n">
         <v>50299</v>
@@ -41694,7 +41694,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1425" t="n">
         <v>19023</v>
@@ -41839,7 +41839,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.4230098724365</v>
+        <v>23.4230117797852</v>
       </c>
       <c r="H1430" t="n">
         <v>34199</v>
@@ -41897,7 +41897,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1432" t="n">
         <v>51446</v>
@@ -42042,7 +42042,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>24.685920715332</v>
+        <v>24.6859188079834</v>
       </c>
       <c r="H1437" t="n">
         <v>70358</v>
@@ -42129,7 +42129,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>26.3434886932373</v>
+        <v>26.3434867858887</v>
       </c>
       <c r="H1440" t="n">
         <v>93973</v>
@@ -42158,7 +42158,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.0341396331787</v>
+        <v>27.0341415405273</v>
       </c>
       <c r="H1441" t="n">
         <v>85164</v>
@@ -42216,7 +42216,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>28.4154472351074</v>
+        <v>28.4154453277588</v>
       </c>
       <c r="H1443" t="n">
         <v>195373</v>
@@ -42245,7 +42245,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>29.6980895996094</v>
+        <v>29.6980876922607</v>
       </c>
       <c r="H1444" t="n">
         <v>171716</v>
@@ -42303,7 +42303,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1446" t="n">
-        <v>29.7770214080811</v>
+        <v>29.7770195007324</v>
       </c>
       <c r="H1446" t="n">
         <v>87748</v>
@@ -42361,7 +42361,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1448" t="n">
-        <v>30.3295440673828</v>
+        <v>30.3295421600342</v>
       </c>
       <c r="H1448" t="n">
         <v>98329</v>
@@ -42535,7 +42535,7 @@
         <v>30.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>30.0927486419678</v>
+        <v>30.0927467346191</v>
       </c>
       <c r="H1454" t="n">
         <v>101035</v>
@@ -42622,7 +42622,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.4218273162842</v>
+        <v>29.4218254089355</v>
       </c>
       <c r="H1457" t="n">
         <v>72194</v>
@@ -42738,7 +42738,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>30.4676723480225</v>
+        <v>30.4676742553711</v>
       </c>
       <c r="H1461" t="n">
         <v>75514</v>
@@ -42854,7 +42854,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G1465" t="n">
-        <v>35.8547706604004</v>
+        <v>35.8547668457031</v>
       </c>
       <c r="H1465" t="n">
         <v>359905</v>
@@ -42941,7 +42941,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>39.0712356567383</v>
+        <v>39.0712394714355</v>
       </c>
       <c r="H1468" t="n">
         <v>321164</v>
@@ -42970,7 +42970,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1469" t="n">
-        <v>36.269157409668</v>
+        <v>36.2691612243652</v>
       </c>
       <c r="H1469" t="n">
         <v>228974</v>
@@ -43028,7 +43028,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>40.3538818359375</v>
+        <v>40.3538856506348</v>
       </c>
       <c r="H1471" t="n">
         <v>311161</v>
@@ -43144,7 +43144,7 @@
         <v>42.6599998474121</v>
       </c>
       <c r="G1475" t="n">
-        <v>42.0903778076172</v>
+        <v>42.0903816223145</v>
       </c>
       <c r="H1475" t="n">
         <v>174798</v>
@@ -43173,7 +43173,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>42.2482414245605</v>
+        <v>42.2482452392578</v>
       </c>
       <c r="H1476" t="n">
         <v>109882</v>
@@ -43202,7 +43202,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1477" t="n">
-        <v>42.5837020874023</v>
+        <v>42.5837059020996</v>
       </c>
       <c r="H1477" t="n">
         <v>137662</v>
@@ -43231,7 +43231,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>43.0178298950195</v>
+        <v>43.0178260803223</v>
       </c>
       <c r="H1478" t="n">
         <v>116213</v>
@@ -43260,7 +43260,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>42.6231689453125</v>
+        <v>42.6231727600098</v>
       </c>
       <c r="H1479" t="n">
         <v>123515</v>
@@ -43289,7 +43289,7 @@
         <v>43</v>
       </c>
       <c r="G1480" t="n">
-        <v>42.425838470459</v>
+        <v>42.4258422851562</v>
       </c>
       <c r="H1480" t="n">
         <v>77199</v>
@@ -43376,7 +43376,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.2615966796875</v>
+        <v>41.2615928649902</v>
       </c>
       <c r="H1483" t="n">
         <v>55495</v>
@@ -43405,7 +43405,7 @@
         <v>42.6399993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.0706443786621</v>
+        <v>42.0706481933594</v>
       </c>
       <c r="H1484" t="n">
         <v>72975</v>
@@ -43637,7 +43637,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1492" t="n">
-        <v>45.5831108093262</v>
+        <v>45.5831146240234</v>
       </c>
       <c r="H1492" t="n">
         <v>178167</v>
@@ -43666,7 +43666,7 @@
         <v>38.4199981689453</v>
       </c>
       <c r="G1493" t="n">
-        <v>37.9069938659668</v>
+        <v>37.9069900512695</v>
       </c>
       <c r="H1493" t="n">
         <v>678570</v>
@@ -43724,7 +43724,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1495" t="n">
-        <v>32.6185646057129</v>
+        <v>32.6185684204102</v>
       </c>
       <c r="H1495" t="n">
         <v>546704</v>
@@ -43869,7 +43869,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1500" t="n">
-        <v>30.4676723480225</v>
+        <v>30.4676742553711</v>
       </c>
       <c r="H1500" t="n">
         <v>356068</v>
@@ -43927,7 +43927,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>30.9215316772461</v>
+        <v>30.9215297698975</v>
       </c>
       <c r="H1502" t="n">
         <v>513447</v>
@@ -43985,7 +43985,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1504" t="n">
-        <v>31.0201969146729</v>
+        <v>31.0201950073242</v>
       </c>
       <c r="H1504" t="n">
         <v>237350</v>
@@ -44043,7 +44043,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>31.3951206207275</v>
+        <v>31.3951225280762</v>
       </c>
       <c r="H1506" t="n">
         <v>180598</v>
@@ -44101,7 +44101,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1508" t="n">
-        <v>30.9215316772461</v>
+        <v>30.9215297698975</v>
       </c>
       <c r="H1508" t="n">
         <v>287718</v>
@@ -79980,6 +79980,35 @@
         <v>10935</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>10.3400001525879</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>10.0200004577637</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>10.2600002288818</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>10.2600002288818</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>10760</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455764770508</v>
+        <v>6.71455717086792</v>
       </c>
       <c r="H3" t="n">
         <v>54991</v>
@@ -485,7 +485,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4850001335144</v>
+        <v>6.48499965667725</v>
       </c>
       <c r="H4" t="n">
         <v>46846</v>
@@ -514,7 +514,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4467396736145</v>
+        <v>6.44674015045166</v>
       </c>
       <c r="H5" t="n">
         <v>108929</v>
@@ -572,7 +572,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H7" t="n">
         <v>40228</v>
@@ -630,7 +630,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H9" t="n">
         <v>104780</v>
@@ -659,7 +659,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3319616317749</v>
+        <v>6.33196115493774</v>
       </c>
       <c r="H10" t="n">
         <v>158687</v>
@@ -688,7 +688,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H11" t="n">
         <v>125780</v>
@@ -717,7 +717,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546054840088</v>
+        <v>5.70546102523804</v>
       </c>
       <c r="H12" t="n">
         <v>113455</v>
@@ -775,7 +775,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31330013275146</v>
+        <v>5.31329965591431</v>
       </c>
       <c r="H14" t="n">
         <v>81327</v>
@@ -862,7 +862,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937297821045</v>
+        <v>5.72937250137329</v>
       </c>
       <c r="H17" t="n">
         <v>38963</v>
@@ -891,7 +891,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.02588510513306</v>
+        <v>6.0258846282959</v>
       </c>
       <c r="H18" t="n">
         <v>66351</v>
@@ -920,7 +920,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935041427612</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H19" t="n">
         <v>89617</v>
@@ -949,7 +949,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>6.00197267532349</v>
+        <v>6.00197219848633</v>
       </c>
       <c r="H20" t="n">
         <v>70672</v>
@@ -978,7 +978,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458341598511</v>
+        <v>5.94458293914795</v>
       </c>
       <c r="H21" t="n">
         <v>47413</v>
@@ -1036,7 +1036,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414781570435</v>
+        <v>5.95414733886719</v>
       </c>
       <c r="H23" t="n">
         <v>39858</v>
@@ -1065,7 +1065,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458614349365</v>
       </c>
       <c r="H24" t="n">
         <v>59492</v>
@@ -1094,7 +1094,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154491424561</v>
+        <v>5.79154443740845</v>
       </c>
       <c r="H25" t="n">
         <v>42499</v>
@@ -1152,7 +1152,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>5.27504062652588</v>
+        <v>5.27504014968872</v>
       </c>
       <c r="H27" t="n">
         <v>92262</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244829177856</v>
+        <v>4.78244876861572</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1210,7 +1210,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679168701172</v>
+        <v>4.90679216384888</v>
       </c>
       <c r="H29" t="n">
         <v>118336</v>
@@ -1239,7 +1239,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62940979003906</v>
+        <v>4.62941026687622</v>
       </c>
       <c r="H30" t="n">
         <v>67579</v>
@@ -1355,7 +1355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.59546375274658</v>
+        <v>5.5954647064209</v>
       </c>
       <c r="H34" t="n">
         <v>87689</v>
@@ -1413,7 +1413,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677280426025</v>
+        <v>5.45677328109741</v>
       </c>
       <c r="H36" t="n">
         <v>102398</v>
@@ -1442,7 +1442,7 @@
         <v>5.75</v>
       </c>
       <c r="G37" t="n">
-        <v>5.49981594085693</v>
+        <v>5.49981546401978</v>
       </c>
       <c r="H37" t="n">
         <v>45357</v>
@@ -1529,7 +1529,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460823059082</v>
+        <v>5.17460870742798</v>
       </c>
       <c r="H40" t="n">
         <v>27727</v>
@@ -1587,7 +1587,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069307327271</v>
+        <v>5.26069259643555</v>
       </c>
       <c r="H42" t="n">
         <v>79999</v>
@@ -1645,7 +1645,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844957351685</v>
+        <v>4.738450050354</v>
       </c>
       <c r="H44" t="n">
         <v>146124</v>
@@ -1732,7 +1732,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749719619751</v>
+        <v>4.62749671936035</v>
       </c>
       <c r="H47" t="n">
         <v>92990</v>
@@ -1790,7 +1790,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>4.63897466659546</v>
+        <v>4.6389741897583</v>
       </c>
       <c r="H49" t="n">
         <v>45504</v>
@@ -1819,7 +1819,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984491348267</v>
+        <v>4.61984443664551</v>
       </c>
       <c r="H50" t="n">
         <v>32253</v>
@@ -1877,7 +1877,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732414245605</v>
+        <v>4.58732461929321</v>
       </c>
       <c r="H52" t="n">
         <v>22397</v>
@@ -1993,7 +1993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985179901123</v>
+        <v>4.39985275268555</v>
       </c>
       <c r="H56" t="n">
         <v>6922</v>
@@ -2080,7 +2080,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.2391619682312</v>
+        <v>4.23916244506836</v>
       </c>
       <c r="H59" t="n">
         <v>20035</v>
@@ -2138,7 +2138,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916933059692</v>
+        <v>4.01916980743408</v>
       </c>
       <c r="H61" t="n">
         <v>8387</v>
@@ -2196,7 +2196,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202053070068</v>
+        <v>4.57202005386353</v>
       </c>
       <c r="H63" t="n">
         <v>101318</v>
@@ -2254,7 +2254,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H65" t="n">
         <v>59895</v>
@@ -2283,7 +2283,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.06508111953735</v>
+        <v>4.0650806427002</v>
       </c>
       <c r="H66" t="n">
         <v>69251</v>
@@ -2312,7 +2312,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265031814575</v>
+        <v>3.94265055656433</v>
       </c>
       <c r="H67" t="n">
         <v>49492</v>
@@ -2341,7 +2341,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691870689392</v>
+        <v>3.71691846847534</v>
       </c>
       <c r="H68" t="n">
         <v>96719</v>
@@ -2370,7 +2370,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726409912109</v>
+        <v>3.79726386070251</v>
       </c>
       <c r="H69" t="n">
         <v>35741</v>
@@ -2399,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.8259584903717</v>
+        <v>3.82595872879028</v>
       </c>
       <c r="H70" t="n">
         <v>33705</v>
@@ -2544,7 +2544,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8489146232605</v>
+        <v>3.84891414642334</v>
       </c>
       <c r="H75" t="n">
         <v>62408</v>
@@ -2602,7 +2602,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723049163818</v>
+        <v>4.78723096847534</v>
       </c>
       <c r="H77" t="n">
         <v>182115</v>
@@ -2689,7 +2689,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851745605469</v>
+        <v>5.30851793289185</v>
       </c>
       <c r="H80" t="n">
         <v>273720</v>
@@ -2718,7 +2718,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373573303223</v>
+        <v>5.30373525619507</v>
       </c>
       <c r="H81" t="n">
         <v>264110</v>
@@ -2776,7 +2776,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.0550479888916</v>
+        <v>5.05504751205444</v>
       </c>
       <c r="H83" t="n">
         <v>85082</v>
@@ -2805,7 +2805,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417726516724</v>
+        <v>5.07417774200439</v>
       </c>
       <c r="H84" t="n">
         <v>122889</v>
@@ -2863,7 +2863,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>4.9546160697937</v>
+        <v>4.95461654663086</v>
       </c>
       <c r="H86" t="n">
         <v>66959</v>
@@ -2892,7 +2892,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653745651245</v>
+        <v>4.73653650283813</v>
       </c>
       <c r="H87" t="n">
         <v>101740</v>
@@ -2921,7 +2921,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680688858032</v>
+        <v>4.46680593490601</v>
       </c>
       <c r="H88" t="n">
         <v>98603</v>
@@ -2950,7 +2950,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>4.22768402099609</v>
+        <v>4.22768449783325</v>
       </c>
       <c r="H89" t="n">
         <v>127459</v>
@@ -2979,7 +2979,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G90" t="n">
-        <v>4.38646173477173</v>
+        <v>4.38646125793457</v>
       </c>
       <c r="H90" t="n">
         <v>233892</v>
@@ -3008,7 +3008,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H91" t="n">
         <v>78370</v>
@@ -3066,7 +3066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942499160767</v>
+        <v>4.18942451477051</v>
       </c>
       <c r="H93" t="n">
         <v>83730</v>
@@ -3153,7 +3153,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16072988510132</v>
+        <v>4.16073036193848</v>
       </c>
       <c r="H96" t="n">
         <v>114509</v>
@@ -3182,7 +3182,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.1167311668396</v>
+        <v>4.11673164367676</v>
       </c>
       <c r="H97" t="n">
         <v>33027</v>
@@ -3240,7 +3240,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472860336304</v>
+        <v>4.20472812652588</v>
       </c>
       <c r="H99" t="n">
         <v>30978</v>
@@ -3269,7 +3269,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846477508545</v>
+        <v>4.29846429824829</v>
       </c>
       <c r="H100" t="n">
         <v>67373</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113876342773</v>
+        <v>4.92113971710205</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3385,7 +3385,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548263549805</v>
+        <v>5.04548311233521</v>
       </c>
       <c r="H104" t="n">
         <v>88307</v>
@@ -3472,7 +3472,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756669998169</v>
+        <v>7.74756622314453</v>
       </c>
       <c r="H107" t="n">
         <v>830490</v>
@@ -3501,7 +3501,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>7.25497341156006</v>
+        <v>7.25497388839722</v>
       </c>
       <c r="H108" t="n">
         <v>611973</v>
@@ -3530,7 +3530,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367635726929</v>
+        <v>7.06367683410645</v>
       </c>
       <c r="H109" t="n">
         <v>396366</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804136276245</v>
+        <v>6.52804183959961</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3617,7 +3617,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>6.26022481918335</v>
+        <v>6.26022434234619</v>
       </c>
       <c r="H112" t="n">
         <v>219748</v>
@@ -3646,7 +3646,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237419128418</v>
+        <v>6.98237466812134</v>
       </c>
       <c r="H113" t="n">
         <v>407399</v>
@@ -3704,7 +3704,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.38456869125366</v>
+        <v>6.3845682144165</v>
       </c>
       <c r="H115" t="n">
         <v>131401</v>
@@ -3733,7 +3733,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718311309814</v>
       </c>
       <c r="H116" t="n">
         <v>279195</v>
@@ -3762,7 +3762,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718311309814</v>
       </c>
       <c r="H117" t="n">
         <v>281217</v>
@@ -3791,7 +3791,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458614349365</v>
       </c>
       <c r="H118" t="n">
         <v>228253</v>
@@ -3878,7 +3878,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370853424072</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H121" t="n">
         <v>194455</v>
@@ -3936,7 +3936,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195474624634</v>
+        <v>6.55195379257202</v>
       </c>
       <c r="H123" t="n">
         <v>388485</v>
@@ -4023,7 +4023,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>6.26022481918335</v>
+        <v>6.26022434234619</v>
       </c>
       <c r="H126" t="n">
         <v>126051</v>
@@ -4168,7 +4168,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935041427612</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H131" t="n">
         <v>52660</v>
@@ -4197,7 +4197,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370853424072</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H132" t="n">
         <v>115535</v>
@@ -4226,7 +4226,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805240631104</v>
+        <v>6.19805288314819</v>
       </c>
       <c r="H133" t="n">
         <v>77921</v>
@@ -4255,7 +4255,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>6.63803815841675</v>
+        <v>6.63803863525391</v>
       </c>
       <c r="H134" t="n">
         <v>118333</v>
@@ -4371,7 +4371,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584733963013</v>
+        <v>7.12584781646729</v>
       </c>
       <c r="H138" t="n">
         <v>47644</v>
@@ -4516,7 +4516,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H143" t="n">
         <v>31912</v>
@@ -4545,7 +4545,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H144" t="n">
         <v>21903</v>
@@ -4574,7 +4574,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H145" t="n">
         <v>55058</v>
@@ -4632,7 +4632,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.92498397827148</v>
+        <v>6.9249849319458</v>
       </c>
       <c r="H147" t="n">
         <v>105405</v>
@@ -4690,7 +4690,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87237787246704</v>
+        <v>6.8723783493042</v>
       </c>
       <c r="H149" t="n">
         <v>71959</v>
@@ -4719,7 +4719,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064521789551</v>
+        <v>6.69064474105835</v>
       </c>
       <c r="H150" t="n">
         <v>35920</v>
@@ -4748,7 +4748,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>6.85324811935425</v>
+        <v>6.85324764251709</v>
       </c>
       <c r="H151" t="n">
         <v>44123</v>
@@ -4777,7 +4777,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>6.95367956161499</v>
+        <v>6.95368003845215</v>
       </c>
       <c r="H152" t="n">
         <v>61634</v>
@@ -4864,7 +4864,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976345062256</v>
+        <v>7.03976392745972</v>
       </c>
       <c r="H155" t="n">
         <v>46790</v>
@@ -4922,7 +4922,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886375427246</v>
+        <v>7.93886518478394</v>
       </c>
       <c r="H157" t="n">
         <v>265495</v>
@@ -4980,7 +4980,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712789535522</v>
+        <v>7.86712741851807</v>
       </c>
       <c r="H159" t="n">
         <v>93100</v>
@@ -5096,7 +5096,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>7.84321546554565</v>
+        <v>7.8432149887085</v>
       </c>
       <c r="H163" t="n">
         <v>118168</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626037597656</v>
+        <v>7.77626132965088</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.996253490448</v>
+        <v>7.99625253677368</v>
       </c>
       <c r="H166" t="n">
         <v>48102</v>
@@ -5212,7 +5212,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712373733521</v>
+        <v>7.97712421417236</v>
       </c>
       <c r="H167" t="n">
         <v>31192</v>
@@ -5241,7 +5241,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451156616211</v>
+        <v>8.03451251983643</v>
       </c>
       <c r="H168" t="n">
         <v>39269</v>
@@ -5270,7 +5270,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060377120972</v>
+        <v>7.90060424804688</v>
       </c>
       <c r="H169" t="n">
         <v>42906</v>
@@ -5328,7 +5328,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669549942017</v>
+        <v>7.76669597625732</v>
       </c>
       <c r="H171" t="n">
         <v>80513</v>
@@ -5357,7 +5357,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89104032516479</v>
+        <v>7.89103937149048</v>
       </c>
       <c r="H172" t="n">
         <v>61552</v>
@@ -5415,7 +5415,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928558349609</v>
       </c>
       <c r="H174" t="n">
         <v>135297</v>
@@ -5473,7 +5473,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>9.00534915924072</v>
+        <v>9.00535011291504</v>
       </c>
       <c r="H176" t="n">
         <v>166097</v>
@@ -5560,7 +5560,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G179" t="n">
-        <v>8.35015296936035</v>
+        <v>8.35015392303467</v>
       </c>
       <c r="H179" t="n">
         <v>237396</v>
@@ -5618,7 +5618,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.41710758209229</v>
+        <v>8.4171085357666</v>
       </c>
       <c r="H181" t="n">
         <v>154982</v>
@@ -5676,7 +5676,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>8.20668125152588</v>
+        <v>8.20668029785156</v>
       </c>
       <c r="H183" t="n">
         <v>59457</v>
@@ -5734,7 +5734,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451763153076</v>
+        <v>7.9245171546936</v>
       </c>
       <c r="H185" t="n">
         <v>122464</v>
@@ -5821,7 +5821,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928558349609</v>
       </c>
       <c r="H188" t="n">
         <v>34542</v>
@@ -5850,7 +5850,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754829406738</v>
+        <v>8.29754638671875</v>
       </c>
       <c r="H189" t="n">
         <v>29985</v>
@@ -5879,7 +5879,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.27363586425781</v>
+        <v>8.2736349105835</v>
       </c>
       <c r="H190" t="n">
         <v>51064</v>
@@ -5908,7 +5908,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928558349609</v>
       </c>
       <c r="H191" t="n">
         <v>24030</v>
@@ -5937,7 +5937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G192" t="n">
-        <v>8.43623924255371</v>
+        <v>8.43623828887939</v>
       </c>
       <c r="H192" t="n">
         <v>44995</v>
@@ -5995,7 +5995,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92882919311523</v>
+        <v>8.92883110046387</v>
       </c>
       <c r="H194" t="n">
         <v>196106</v>
@@ -6024,7 +6024,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.06752109527588</v>
+        <v>9.06752014160156</v>
       </c>
       <c r="H195" t="n">
         <v>116469</v>
@@ -6082,7 +6082,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968982696533</v>
+        <v>9.23968887329102</v>
       </c>
       <c r="H197" t="n">
         <v>111328</v>
@@ -6140,7 +6140,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708324432373</v>
+        <v>9.18708229064941</v>
       </c>
       <c r="H199" t="n">
         <v>82966</v>
@@ -6169,7 +6169,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882694244385</v>
+        <v>9.03882598876953</v>
       </c>
       <c r="H200" t="n">
         <v>84914</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.13447666168213</v>
+        <v>9.13447570800781</v>
       </c>
       <c r="H201" t="n">
         <v>49199</v>
@@ -6227,7 +6227,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.17273712158203</v>
+        <v>9.1727352142334</v>
       </c>
       <c r="H202" t="n">
         <v>47674</v>
@@ -6256,7 +6256,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185760498047</v>
+        <v>9.41185855865479</v>
       </c>
       <c r="H203" t="n">
         <v>115834</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6401,7 +6401,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620338439941</v>
+        <v>9.53620147705078</v>
       </c>
       <c r="H208" t="n">
         <v>78401</v>
@@ -6720,7 +6720,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831266403198</v>
+        <v>10.4831256866455</v>
       </c>
       <c r="H219" t="n">
         <v>128669</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692100524902</v>
+        <v>10.5692110061646</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6807,7 +6807,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.837028503418</v>
+        <v>10.8370275497437</v>
       </c>
       <c r="H222" t="n">
         <v>98298</v>
@@ -6865,7 +6865,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.1144094467163</v>
+        <v>11.114408493042</v>
       </c>
       <c r="H224" t="n">
         <v>91003</v>
@@ -6981,7 +6981,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456922531128</v>
+        <v>11.7456912994385</v>
       </c>
       <c r="H228" t="n">
         <v>176751</v>
@@ -7010,7 +7010,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648229598999</v>
+        <v>11.7648220062256</v>
       </c>
       <c r="H229" t="n">
         <v>87480</v>
@@ -7039,7 +7039,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G230" t="n">
-        <v>11.630913734436</v>
+        <v>11.6309127807617</v>
       </c>
       <c r="H230" t="n">
         <v>118136</v>
@@ -7068,7 +7068,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>11.6691732406616</v>
+        <v>11.6691722869873</v>
       </c>
       <c r="H231" t="n">
         <v>95647</v>
@@ -7097,7 +7097,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708980560303</v>
+        <v>12.0708990097046</v>
       </c>
       <c r="H232" t="n">
         <v>161563</v>
@@ -7126,7 +7126,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961048126221</v>
+        <v>12.3961057662964</v>
       </c>
       <c r="H233" t="n">
         <v>317127</v>
@@ -7155,7 +7155,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H234" t="n">
         <v>153081</v>
@@ -7184,7 +7184,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H235" t="n">
         <v>95580</v>
@@ -7213,7 +7213,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474170684814</v>
+        <v>12.1474180221558</v>
       </c>
       <c r="H236" t="n">
         <v>111282</v>
@@ -7271,7 +7271,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839517593384</v>
+        <v>11.7839527130127</v>
       </c>
       <c r="H238" t="n">
         <v>75176</v>
@@ -7329,7 +7329,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.616096496582</v>
+        <v>12.6160984039307</v>
       </c>
       <c r="H240" t="n">
         <v>180021</v>
@@ -7416,7 +7416,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473434448242</v>
       </c>
       <c r="H243" t="n">
         <v>303111</v>
@@ -7474,7 +7474,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.038592338562</v>
+        <v>14.0385932922363</v>
       </c>
       <c r="H245" t="n">
         <v>494015</v>
@@ -7532,7 +7532,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>13.8456220626831</v>
+        <v>13.8456230163574</v>
       </c>
       <c r="H247" t="n">
         <v>263722</v>
@@ -7561,7 +7561,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G248" t="n">
-        <v>13.3728446960449</v>
+        <v>13.3728437423706</v>
       </c>
       <c r="H248" t="n">
         <v>127762</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272216796875</v>
+        <v>13.5272207260132</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7619,7 +7619,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G250" t="n">
-        <v>13.430736541748</v>
+        <v>13.4307355880737</v>
       </c>
       <c r="H250" t="n">
         <v>48278</v>
@@ -7793,7 +7793,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G256" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H256" t="n">
         <v>44658</v>
@@ -7822,7 +7822,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H257" t="n">
         <v>36672</v>
@@ -7851,7 +7851,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H258" t="n">
         <v>48422</v>
@@ -7938,7 +7938,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.9869031906128</v>
+        <v>12.9869041442871</v>
       </c>
       <c r="H261" t="n">
         <v>30726</v>
@@ -7996,7 +7996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H263" t="n">
         <v>90090</v>
@@ -8054,7 +8054,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877311706543</v>
+        <v>13.78773021698</v>
       </c>
       <c r="H265" t="n">
         <v>225704</v>
@@ -8112,7 +8112,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044092178345</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H267" t="n">
         <v>71289</v>
@@ -8257,7 +8257,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H272" t="n">
         <v>43627</v>
@@ -8315,7 +8315,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G274" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H274" t="n">
         <v>91826</v>
@@ -8344,7 +8344,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869724273682</v>
+        <v>11.8869733810425</v>
       </c>
       <c r="H275" t="n">
         <v>94457</v>
@@ -8402,7 +8402,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G277" t="n">
-        <v>11.539626121521</v>
+        <v>11.5396270751953</v>
       </c>
       <c r="H277" t="n">
         <v>194589</v>
@@ -8431,7 +8431,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H278" t="n">
         <v>152414</v>
@@ -8489,7 +8489,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G280" t="n">
-        <v>11.665057182312</v>
+        <v>11.6650581359863</v>
       </c>
       <c r="H280" t="n">
         <v>34289</v>
@@ -8605,7 +8605,7 @@
         <v>11.75</v>
       </c>
       <c r="G284" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H284" t="n">
         <v>114241</v>
@@ -8634,7 +8634,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.8063383102417</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H285" t="n">
         <v>135254</v>
@@ -8692,7 +8692,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484493255615</v>
+        <v>10.7484483718872</v>
       </c>
       <c r="H287" t="n">
         <v>33613</v>
@@ -8721,7 +8721,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.729151725769</v>
+        <v>10.7291507720947</v>
       </c>
       <c r="H288" t="n">
         <v>25029</v>
@@ -8808,7 +8808,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>11.1922798156738</v>
+        <v>11.1922807693481</v>
       </c>
       <c r="H291" t="n">
         <v>17482</v>
@@ -8837,7 +8837,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738803863525</v>
+        <v>10.8738794326782</v>
       </c>
       <c r="H292" t="n">
         <v>53600</v>
@@ -8895,7 +8895,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.0089588165283</v>
+        <v>11.008957862854</v>
       </c>
       <c r="H294" t="n">
         <v>9802</v>
@@ -8982,7 +8982,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695375442505</v>
+        <v>10.1695384979248</v>
       </c>
       <c r="H297" t="n">
         <v>66319</v>
@@ -9011,7 +9011,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247406005859</v>
+        <v>11.1247396469116</v>
       </c>
       <c r="H298" t="n">
         <v>108006</v>
@@ -9069,7 +9069,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685720443726</v>
+        <v>11.5685729980469</v>
       </c>
       <c r="H300" t="n">
         <v>224596</v>
@@ -9127,7 +9127,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273582458496</v>
+        <v>11.3273601531982</v>
       </c>
       <c r="H302" t="n">
         <v>104822</v>
@@ -9185,7 +9185,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.4369382858276</v>
+        <v>12.436939239502</v>
       </c>
       <c r="H304" t="n">
         <v>178543</v>
@@ -9214,7 +9214,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H305" t="n">
         <v>194476</v>
@@ -9243,7 +9243,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G306" t="n">
-        <v>11.7808399200439</v>
+        <v>11.7808389663696</v>
       </c>
       <c r="H306" t="n">
         <v>50004</v>
@@ -9272,7 +9272,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5878686904907</v>
+        <v>11.587869644165</v>
       </c>
       <c r="H307" t="n">
         <v>49320</v>
@@ -9301,7 +9301,7 @@
         <v>11.75</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H308" t="n">
         <v>79684</v>
@@ -9359,7 +9359,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>11.1922798156738</v>
+        <v>11.1922807693481</v>
       </c>
       <c r="H310" t="n">
         <v>41614</v>
@@ -9417,7 +9417,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054439544678</v>
+        <v>11.1054430007935</v>
       </c>
       <c r="H312" t="n">
         <v>33585</v>
@@ -9504,7 +9504,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334945678711</v>
+        <v>11.4334936141968</v>
       </c>
       <c r="H315" t="n">
         <v>31751</v>
@@ -9533,7 +9533,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H316" t="n">
         <v>113990</v>
@@ -9562,7 +9562,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H317" t="n">
         <v>48953</v>
@@ -9620,7 +9620,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H319" t="n">
         <v>41274</v>
@@ -9736,7 +9736,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387317657471</v>
+        <v>11.8387308120728</v>
       </c>
       <c r="H323" t="n">
         <v>88601</v>
@@ -9823,7 +9823,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044092178345</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H326" t="n">
         <v>296460</v>
@@ -9852,7 +9852,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G327" t="n">
-        <v>13.6140575408936</v>
+        <v>13.6140565872192</v>
       </c>
       <c r="H327" t="n">
         <v>135660</v>
@@ -9881,7 +9881,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H328" t="n">
         <v>133226</v>
@@ -9910,7 +9910,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693307876587</v>
+        <v>13.4693298339844</v>
       </c>
       <c r="H329" t="n">
         <v>64109</v>
@@ -9939,7 +9939,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H330" t="n">
         <v>80883</v>
@@ -9968,7 +9968,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H331" t="n">
         <v>127592</v>
@@ -9997,7 +9997,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G332" t="n">
-        <v>13.430736541748</v>
+        <v>13.4307355880737</v>
       </c>
       <c r="H332" t="n">
         <v>75116</v>
@@ -10026,7 +10026,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886274337769</v>
+        <v>13.4886264801025</v>
       </c>
       <c r="H333" t="n">
         <v>19569</v>
@@ -10084,7 +10084,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H335" t="n">
         <v>56318</v>
@@ -10113,7 +10113,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H336" t="n">
         <v>66093</v>
@@ -10229,7 +10229,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807004928589</v>
+        <v>13.9807014465332</v>
       </c>
       <c r="H340" t="n">
         <v>101573</v>
@@ -10258,7 +10258,7 @@
         <v>14.75</v>
       </c>
       <c r="G341" t="n">
-        <v>14.2315635681152</v>
+        <v>14.2315626144409</v>
       </c>
       <c r="H341" t="n">
         <v>95930</v>
@@ -10316,7 +10316,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.4920740127563</v>
+        <v>14.4920721054077</v>
       </c>
       <c r="H343" t="n">
         <v>175404</v>
@@ -10432,7 +10432,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G347" t="n">
-        <v>14.5789098739624</v>
+        <v>14.5789089202881</v>
       </c>
       <c r="H347" t="n">
         <v>26791</v>
@@ -10490,7 +10490,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052362442017</v>
+        <v>14.405237197876</v>
       </c>
       <c r="H349" t="n">
         <v>73630</v>
@@ -10519,7 +10519,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824247360229</v>
+        <v>14.4824237823486</v>
       </c>
       <c r="H350" t="n">
         <v>97965</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527219772339</v>
+        <v>12.5527210235596</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10693,7 +10693,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H356" t="n">
         <v>42754</v>
@@ -10722,7 +10722,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G357" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H357" t="n">
         <v>55254</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.0062007904053</v>
+        <v>13.0062017440796</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10867,7 +10867,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H362" t="n">
         <v>25549</v>
@@ -10896,7 +10896,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H363" t="n">
         <v>24673</v>
@@ -11012,7 +11012,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360410690308</v>
+        <v>12.7360429763794</v>
       </c>
       <c r="H367" t="n">
         <v>41635</v>
@@ -11041,7 +11041,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>12.7263927459717</v>
+        <v>12.726393699646</v>
       </c>
       <c r="H368" t="n">
         <v>31587</v>
@@ -11099,7 +11099,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H370" t="n">
         <v>58049</v>
@@ -11128,7 +11128,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755325317383</v>
+        <v>12.4755334854126</v>
       </c>
       <c r="H371" t="n">
         <v>12596</v>
@@ -11157,7 +11157,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4272890090942</v>
+        <v>12.4272899627686</v>
       </c>
       <c r="H372" t="n">
         <v>32892</v>
@@ -11215,7 +11215,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150230407715</v>
+        <v>12.2150220870972</v>
       </c>
       <c r="H374" t="n">
         <v>20005</v>
@@ -11273,7 +11273,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185388565063</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H376" t="n">
         <v>18790</v>
@@ -11302,7 +11302,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H377" t="n">
         <v>54450</v>
@@ -11360,7 +11360,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H379" t="n">
         <v>11240</v>
@@ -11418,7 +11418,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H381" t="n">
         <v>64542</v>
@@ -11447,7 +11447,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194341659546</v>
+        <v>11.8194332122803</v>
       </c>
       <c r="H382" t="n">
         <v>27743</v>
@@ -11505,7 +11505,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>11.6843547821045</v>
+        <v>11.6843538284302</v>
       </c>
       <c r="H384" t="n">
         <v>27524</v>
@@ -11534,7 +11534,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325963973999</v>
+        <v>11.7325954437256</v>
       </c>
       <c r="H385" t="n">
         <v>6733</v>
@@ -11563,7 +11563,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G386" t="n">
-        <v>11.6843547821045</v>
+        <v>11.6843538284302</v>
       </c>
       <c r="H386" t="n">
         <v>27537</v>
@@ -11592,7 +11592,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H387" t="n">
         <v>110158</v>
@@ -11621,7 +11621,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H388" t="n">
         <v>47918</v>
@@ -11650,7 +11650,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966217041016</v>
+        <v>11.8966207504272</v>
       </c>
       <c r="H389" t="n">
         <v>33102</v>
@@ -11708,7 +11708,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H391" t="n">
         <v>36167</v>
@@ -11824,7 +11824,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H395" t="n">
         <v>18587</v>
@@ -11853,7 +11853,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.243968963623</v>
+        <v>12.2439670562744</v>
       </c>
       <c r="H396" t="n">
         <v>21900</v>
@@ -11882,7 +11882,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H397" t="n">
         <v>62135</v>
@@ -11911,7 +11911,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G398" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H398" t="n">
         <v>107931</v>
@@ -12056,7 +12056,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>12.5623693466187</v>
+        <v>12.562370300293</v>
       </c>
       <c r="H403" t="n">
         <v>8745</v>
@@ -12114,7 +12114,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228788375854</v>
+        <v>12.8228797912598</v>
       </c>
       <c r="H405" t="n">
         <v>47428</v>
@@ -12143,7 +12143,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6685037612915</v>
+        <v>12.6685028076172</v>
       </c>
       <c r="H406" t="n">
         <v>26294</v>
@@ -12259,7 +12259,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H410" t="n">
         <v>21714</v>
@@ -12317,7 +12317,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H412" t="n">
         <v>20167</v>
@@ -12346,7 +12346,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G413" t="n">
-        <v>12.9097156524658</v>
+        <v>12.9097166061401</v>
       </c>
       <c r="H413" t="n">
         <v>52102</v>
@@ -12404,7 +12404,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>12.5623693466187</v>
+        <v>12.562370300293</v>
       </c>
       <c r="H415" t="n">
         <v>14241</v>
@@ -12433,7 +12433,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G416" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H416" t="n">
         <v>51186</v>
@@ -12462,7 +12462,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H417" t="n">
         <v>19263</v>
@@ -12520,7 +12520,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G419" t="n">
-        <v>12.9869031906128</v>
+        <v>12.9869041442871</v>
       </c>
       <c r="H419" t="n">
         <v>4823</v>
@@ -12549,7 +12549,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>13.0544443130493</v>
+        <v>13.054443359375</v>
       </c>
       <c r="H420" t="n">
         <v>17739</v>
@@ -12607,7 +12607,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H422" t="n">
         <v>22215</v>
@@ -12636,7 +12636,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>12.8904180526733</v>
+        <v>12.8904190063477</v>
       </c>
       <c r="H423" t="n">
         <v>19497</v>
@@ -12694,7 +12694,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167453765869</v>
+        <v>12.7167463302612</v>
       </c>
       <c r="H425" t="n">
         <v>35809</v>
@@ -12723,7 +12723,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5334243774414</v>
+        <v>12.5334234237671</v>
       </c>
       <c r="H426" t="n">
         <v>25449</v>
@@ -12781,7 +12781,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H428" t="n">
         <v>13836</v>
@@ -12839,7 +12839,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H430" t="n">
         <v>30798</v>
@@ -13042,7 +13042,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H437" t="n">
         <v>115869</v>
@@ -13158,7 +13158,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>12.7263927459717</v>
+        <v>12.726393699646</v>
       </c>
       <c r="H441" t="n">
         <v>30766</v>
@@ -13187,7 +13187,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H442" t="n">
         <v>23233</v>
@@ -13274,7 +13274,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H445" t="n">
         <v>16060</v>
@@ -13303,7 +13303,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H446" t="n">
         <v>35222</v>
@@ -13361,7 +13361,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>12.485179901123</v>
+        <v>12.4851808547974</v>
       </c>
       <c r="H448" t="n">
         <v>23317</v>
@@ -13390,7 +13390,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>12.6685037612915</v>
+        <v>12.6685028076172</v>
       </c>
       <c r="H449" t="n">
         <v>33026</v>
@@ -13419,7 +13419,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G450" t="n">
-        <v>12.6781530380249</v>
+        <v>12.6781511306763</v>
       </c>
       <c r="H450" t="n">
         <v>8729</v>
@@ -13448,7 +13448,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H451" t="n">
         <v>58859</v>
@@ -13564,7 +13564,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H455" t="n">
         <v>45659</v>
@@ -13593,7 +13593,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H456" t="n">
         <v>40685</v>
@@ -13651,7 +13651,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H458" t="n">
         <v>49613</v>
@@ -13680,7 +13680,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H459" t="n">
         <v>27238</v>
@@ -13709,7 +13709,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>12.4465866088867</v>
+        <v>12.446587562561</v>
       </c>
       <c r="H460" t="n">
         <v>60559</v>
@@ -13738,7 +13738,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H461" t="n">
         <v>38181</v>
@@ -13796,7 +13796,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>12.1764278411865</v>
+        <v>12.1764287948608</v>
       </c>
       <c r="H463" t="n">
         <v>18331</v>
@@ -13854,7 +13854,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G465" t="n">
-        <v>11.9352159500122</v>
+        <v>11.9352149963379</v>
       </c>
       <c r="H465" t="n">
         <v>21056</v>
@@ -13970,7 +13970,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185388565063</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H469" t="n">
         <v>26893</v>
@@ -14028,7 +14028,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308038711548</v>
+        <v>12.3308048248291</v>
       </c>
       <c r="H471" t="n">
         <v>21463</v>
@@ -14057,7 +14057,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G472" t="n">
-        <v>12.1764278411865</v>
+        <v>12.1764287948608</v>
       </c>
       <c r="H472" t="n">
         <v>19926</v>
@@ -14086,7 +14086,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>12.1088895797729</v>
+        <v>12.1088886260986</v>
       </c>
       <c r="H473" t="n">
         <v>20258</v>
@@ -14144,7 +14144,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124025344849</v>
+        <v>12.0124034881592</v>
       </c>
       <c r="H475" t="n">
         <v>13507</v>
@@ -14173,7 +14173,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>11.8290824890137</v>
+        <v>11.8290815353394</v>
       </c>
       <c r="H476" t="n">
         <v>75300</v>
@@ -14202,7 +14202,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747055053711</v>
+        <v>11.6747074127197</v>
       </c>
       <c r="H477" t="n">
         <v>345190</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554733276367</v>
+        <v>9.45554637908936</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14289,7 +14289,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816497802734</v>
+        <v>9.65816593170166</v>
       </c>
       <c r="H480" t="n">
         <v>142514</v>
@@ -14318,7 +14318,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711090087891</v>
+        <v>9.68711185455322</v>
       </c>
       <c r="H481" t="n">
         <v>127849</v>
@@ -14347,7 +14347,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G482" t="n">
-        <v>9.85113716125488</v>
+        <v>9.85113620758057</v>
       </c>
       <c r="H482" t="n">
         <v>95444</v>
@@ -14376,7 +14376,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923480987549</v>
+        <v>10.0923490524292</v>
       </c>
       <c r="H483" t="n">
         <v>75251</v>
@@ -14405,7 +14405,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625078201294</v>
+        <v>10.3625068664551</v>
       </c>
       <c r="H484" t="n">
         <v>99264</v>
@@ -14434,7 +14434,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107503890991</v>
+        <v>10.4107494354248</v>
       </c>
       <c r="H485" t="n">
         <v>165118</v>
@@ -14492,7 +14492,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.8063383102417</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H487" t="n">
         <v>73996</v>
@@ -14550,7 +14550,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.71950340271</v>
+        <v>10.7195024490356</v>
       </c>
       <c r="H489" t="n">
         <v>62047</v>
@@ -14579,7 +14579,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G490" t="n">
-        <v>11.4527893066406</v>
+        <v>11.4527902603149</v>
       </c>
       <c r="H490" t="n">
         <v>324231</v>
@@ -14637,7 +14637,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>10.9028234481812</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H492" t="n">
         <v>50334</v>
@@ -14695,7 +14695,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G494" t="n">
-        <v>10.9028234481812</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H494" t="n">
         <v>56326</v>
@@ -14753,7 +14753,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G496" t="n">
-        <v>10.9028234481812</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H496" t="n">
         <v>116291</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078981399536</v>
+        <v>10.7078971862793</v>
       </c>
       <c r="H500" t="n">
         <v>97230</v>
@@ -14898,7 +14898,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G501" t="n">
-        <v>10.4732036590576</v>
+        <v>10.4732046127319</v>
       </c>
       <c r="H501" t="n">
         <v>197020</v>
@@ -14927,7 +14927,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H502" t="n">
         <v>89414</v>
@@ -14956,7 +14956,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189521789551</v>
+        <v>10.2189531326294</v>
       </c>
       <c r="H503" t="n">
         <v>87325</v>
@@ -15043,7 +15043,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4536466598511</v>
+        <v>10.4536457061768</v>
       </c>
       <c r="H506" t="n">
         <v>53759</v>
@@ -15072,7 +15072,7 @@
         <v>10.75</v>
       </c>
       <c r="G507" t="n">
-        <v>10.5123195648193</v>
+        <v>10.5123205184937</v>
       </c>
       <c r="H507" t="n">
         <v>171168</v>
@@ -15101,7 +15101,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H508" t="n">
         <v>53290</v>
@@ -15130,7 +15130,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G509" t="n">
-        <v>10.4047527313232</v>
+        <v>10.4047517776489</v>
       </c>
       <c r="H509" t="n">
         <v>85761</v>
@@ -15188,7 +15188,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G511" t="n">
-        <v>10.5807723999023</v>
+        <v>10.580771446228</v>
       </c>
       <c r="H511" t="n">
         <v>29173</v>
@@ -15246,7 +15246,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H513" t="n">
         <v>68123</v>
@@ -15565,7 +15565,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>10.9328136444092</v>
+        <v>10.9328126907349</v>
       </c>
       <c r="H524" t="n">
         <v>31611</v>
@@ -15623,7 +15623,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H526" t="n">
         <v>85137</v>
@@ -15681,7 +15681,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H528" t="n">
         <v>31481</v>
@@ -15797,7 +15797,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H532" t="n">
         <v>61309</v>
@@ -15855,7 +15855,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634246826172</v>
+        <v>10.4634256362915</v>
       </c>
       <c r="H534" t="n">
         <v>20572</v>
@@ -15884,7 +15884,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069639205933</v>
+        <v>10.3069629669189</v>
       </c>
       <c r="H535" t="n">
         <v>59740</v>
@@ -15942,7 +15942,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G537" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H537" t="n">
         <v>66947</v>
@@ -16000,7 +16000,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H539" t="n">
         <v>38633</v>
@@ -16145,7 +16145,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>9.64199733734131</v>
+        <v>9.64199829101562</v>
       </c>
       <c r="H544" t="n">
         <v>45893</v>
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H545" t="n">
         <v>37787</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H546" t="n">
         <v>15589</v>
@@ -16232,7 +16232,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509262084961</v>
+        <v>9.50509357452393</v>
       </c>
       <c r="H547" t="n">
         <v>11946</v>
@@ -16261,7 +16261,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619964599609</v>
+        <v>9.45619869232178</v>
       </c>
       <c r="H548" t="n">
         <v>15955</v>
@@ -16290,7 +16290,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H549" t="n">
         <v>23576</v>
@@ -16319,7 +16319,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H550" t="n">
         <v>18189</v>
@@ -16377,7 +16377,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H552" t="n">
         <v>45912</v>
@@ -16638,7 +16638,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H561" t="n">
         <v>47843</v>
@@ -16667,7 +16667,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H562" t="n">
         <v>31267</v>
@@ -16812,7 +16812,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H567" t="n">
         <v>124458</v>
@@ -16841,7 +16841,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G568" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H568" t="n">
         <v>102747</v>
@@ -16957,7 +16957,7 @@
         <v>10.5</v>
       </c>
       <c r="G572" t="n">
-        <v>10.2678480148315</v>
+        <v>10.2678470611572</v>
       </c>
       <c r="H572" t="n">
         <v>116632</v>
@@ -16986,7 +16986,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H573" t="n">
         <v>121005</v>
@@ -17015,7 +17015,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H574" t="n">
         <v>114848</v>
@@ -17044,7 +17044,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H575" t="n">
         <v>94106</v>
@@ -17073,7 +17073,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G576" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H576" t="n">
         <v>88350</v>
@@ -17160,7 +17160,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H579" t="n">
         <v>84921</v>
@@ -17247,7 +17247,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.1237154006958</v>
+        <v>9.12371635437012</v>
       </c>
       <c r="H582" t="n">
         <v>83347</v>
@@ -17276,7 +17276,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>8.95747470855713</v>
+        <v>8.95747375488281</v>
       </c>
       <c r="H583" t="n">
         <v>20537</v>
@@ -17305,7 +17305,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H584" t="n">
         <v>44575</v>
@@ -17363,7 +17363,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H586" t="n">
         <v>19894</v>
@@ -17508,7 +17508,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H591" t="n">
         <v>38459</v>
@@ -17537,7 +17537,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H592" t="n">
         <v>73245</v>
@@ -17566,7 +17566,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H593" t="n">
         <v>172995</v>
@@ -17653,7 +17653,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H596" t="n">
         <v>110779</v>
@@ -17682,7 +17682,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H597" t="n">
         <v>168521</v>
@@ -17769,7 +17769,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H600" t="n">
         <v>116918</v>
@@ -17798,7 +17798,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G601" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H601" t="n">
         <v>24832</v>
@@ -17885,7 +17885,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H604" t="n">
         <v>44561</v>
@@ -18030,7 +18030,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H609" t="n">
         <v>8881</v>
@@ -18059,7 +18059,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H610" t="n">
         <v>26954</v>
@@ -18146,7 +18146,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G613" t="n">
-        <v>9.34863090515137</v>
+        <v>9.34862995147705</v>
       </c>
       <c r="H613" t="n">
         <v>29288</v>
@@ -18204,7 +18204,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H615" t="n">
         <v>38849</v>
@@ -18291,7 +18291,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H618" t="n">
         <v>16473</v>
@@ -18436,7 +18436,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G623" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H623" t="n">
         <v>113503</v>
@@ -18610,7 +18610,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354640960693</v>
+        <v>9.5735445022583</v>
       </c>
       <c r="H629" t="n">
         <v>59629</v>
@@ -18668,7 +18668,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H631" t="n">
         <v>25208</v>
@@ -18726,7 +18726,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>9.13349533081055</v>
+        <v>9.13349437713623</v>
       </c>
       <c r="H633" t="n">
         <v>33022</v>
@@ -18784,7 +18784,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G635" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H635" t="n">
         <v>46972</v>
@@ -18900,7 +18900,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H639" t="n">
         <v>10481</v>
@@ -19045,7 +19045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>9.43664073944092</v>
+        <v>9.4366397857666</v>
       </c>
       <c r="H644" t="n">
         <v>5673</v>
@@ -19132,7 +19132,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G647" t="n">
-        <v>9.64199733734131</v>
+        <v>9.64199829101562</v>
       </c>
       <c r="H647" t="n">
         <v>12149</v>
@@ -19190,7 +19190,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52465057373047</v>
+        <v>9.52464962005615</v>
       </c>
       <c r="H649" t="n">
         <v>25021</v>
@@ -19248,7 +19248,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H651" t="n">
         <v>135104</v>
@@ -19364,7 +19364,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G655" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H655" t="n">
         <v>14617</v>
@@ -19393,7 +19393,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G656" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H656" t="n">
         <v>5166</v>
@@ -19451,7 +19451,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437847137451</v>
+        <v>9.09437942504883</v>
       </c>
       <c r="H658" t="n">
         <v>4851</v>
@@ -19654,7 +19654,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G665" t="n">
-        <v>9.3975248336792</v>
+        <v>9.39752388000488</v>
       </c>
       <c r="H665" t="n">
         <v>4386</v>
@@ -19770,7 +19770,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H669" t="n">
         <v>10937</v>
@@ -19857,7 +19857,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H672" t="n">
         <v>48863</v>
@@ -19886,7 +19886,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G673" t="n">
-        <v>9.76912307739258</v>
+        <v>9.76912403106689</v>
       </c>
       <c r="H673" t="n">
         <v>49111</v>
@@ -19915,7 +19915,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H674" t="n">
         <v>18840</v>
@@ -19944,7 +19944,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H675" t="n">
         <v>37373</v>
@@ -20031,7 +20031,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H678" t="n">
         <v>29641</v>
@@ -20060,7 +20060,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H679" t="n">
         <v>14909</v>
@@ -20089,7 +20089,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G680" t="n">
-        <v>9.60288143157959</v>
+        <v>9.60288238525391</v>
       </c>
       <c r="H680" t="n">
         <v>7811</v>
@@ -20118,7 +20118,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H681" t="n">
         <v>7805</v>
@@ -20234,7 +20234,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G685" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H685" t="n">
         <v>86835</v>
@@ -20263,7 +20263,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>9.76912307739258</v>
+        <v>9.76912403106689</v>
       </c>
       <c r="H686" t="n">
         <v>19172</v>
@@ -20292,7 +20292,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H687" t="n">
         <v>13215</v>
@@ -20321,7 +20321,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G688" t="n">
-        <v>9.67133522033691</v>
+        <v>9.6713342666626</v>
       </c>
       <c r="H688" t="n">
         <v>38879</v>
@@ -20379,7 +20379,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575569152832</v>
+        <v>9.47575664520264</v>
       </c>
       <c r="H690" t="n">
         <v>39319</v>
@@ -20495,7 +20495,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H694" t="n">
         <v>32283</v>
@@ -20524,7 +20524,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H695" t="n">
         <v>15119</v>
@@ -20553,7 +20553,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H696" t="n">
         <v>14440</v>
@@ -20669,7 +20669,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H700" t="n">
         <v>27899</v>
@@ -20959,7 +20959,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H710" t="n">
         <v>140241</v>
@@ -20988,7 +20988,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G711" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H711" t="n">
         <v>50079</v>
@@ -21017,7 +21017,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560531616211</v>
+        <v>8.15560436248779</v>
       </c>
       <c r="H712" t="n">
         <v>38461</v>
@@ -21075,7 +21075,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G714" t="n">
-        <v>8.70322322845459</v>
+        <v>8.70322227478027</v>
       </c>
       <c r="H714" t="n">
         <v>94133</v>
@@ -21104,7 +21104,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H715" t="n">
         <v>12213</v>
@@ -21133,7 +21133,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G716" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H716" t="n">
         <v>45582</v>
@@ -21191,7 +21191,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626838684082</v>
+        <v>8.12626934051514</v>
       </c>
       <c r="H718" t="n">
         <v>75942</v>
@@ -21220,7 +21220,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G719" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H719" t="n">
         <v>28804</v>
@@ -21249,7 +21249,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742362976074</v>
+        <v>8.51742458343506</v>
       </c>
       <c r="H720" t="n">
         <v>40610</v>
@@ -21336,7 +21336,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.63477039337158</v>
+        <v>8.6347713470459</v>
       </c>
       <c r="H723" t="n">
         <v>20170</v>
@@ -21365,7 +21365,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924385070801</v>
+        <v>8.87924289703369</v>
       </c>
       <c r="H724" t="n">
         <v>16711</v>
@@ -21423,7 +21423,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902282714844</v>
+        <v>8.88902187347412</v>
       </c>
       <c r="H726" t="n">
         <v>35047</v>
@@ -21452,7 +21452,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G727" t="n">
-        <v>8.77167510986328</v>
+        <v>8.7716760635376</v>
       </c>
       <c r="H727" t="n">
         <v>143037</v>
@@ -21481,7 +21481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G728" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H728" t="n">
         <v>73666</v>
@@ -21539,7 +21539,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H730" t="n">
         <v>9948</v>
@@ -21742,7 +21742,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262937545776</v>
+        <v>7.40262889862061</v>
       </c>
       <c r="H737" t="n">
         <v>30955</v>
@@ -21800,7 +21800,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>6.86478900909424</v>
+        <v>6.8647894859314</v>
       </c>
       <c r="H739" t="n">
         <v>73987</v>
@@ -21858,7 +21858,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>7.30483961105347</v>
+        <v>7.30484008789062</v>
       </c>
       <c r="H741" t="n">
         <v>13402</v>
@@ -21945,7 +21945,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.1581563949585</v>
+        <v>7.15815687179565</v>
       </c>
       <c r="H744" t="n">
         <v>18982</v>
@@ -21974,7 +21974,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G745" t="n">
-        <v>6.83545255661011</v>
+        <v>6.83545207977295</v>
       </c>
       <c r="H745" t="n">
         <v>110100</v>
@@ -22032,7 +22032,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>5.67176342010498</v>
+        <v>5.67176389694214</v>
       </c>
       <c r="H747" t="n">
         <v>105173</v>
@@ -22061,7 +22061,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G748" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H748" t="n">
         <v>167124</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22235,7 +22235,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>4.67431545257568</v>
+        <v>4.67431497573853</v>
       </c>
       <c r="H754" t="n">
         <v>139728</v>
@@ -22264,7 +22264,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>4.44940042495728</v>
+        <v>4.44940090179443</v>
       </c>
       <c r="H755" t="n">
         <v>78287</v>
@@ -22293,7 +22293,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738519668579</v>
+        <v>4.31738567352295</v>
       </c>
       <c r="H756" t="n">
         <v>103537</v>
@@ -22322,7 +22322,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357671737671</v>
+        <v>4.04357624053955</v>
       </c>
       <c r="H757" t="n">
         <v>116412</v>
@@ -22351,7 +22351,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>3.90178203582764</v>
+        <v>3.90178227424622</v>
       </c>
       <c r="H758" t="n">
         <v>114123</v>
@@ -22380,7 +22380,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>4.29782819747925</v>
+        <v>4.29782772064209</v>
       </c>
       <c r="H759" t="n">
         <v>196124</v>
@@ -22438,7 +22438,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156101226807</v>
+        <v>3.91156077384949</v>
       </c>
       <c r="H761" t="n">
         <v>208056</v>
@@ -22496,7 +22496,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669658660889</v>
+        <v>4.12669706344604</v>
       </c>
       <c r="H763" t="n">
         <v>41597</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22583,7 +22583,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>4.35161161422729</v>
+        <v>4.35161113739014</v>
       </c>
       <c r="H766" t="n">
         <v>92230</v>
@@ -22641,7 +22641,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G768" t="n">
-        <v>4.83566761016846</v>
+        <v>4.8356671333313</v>
       </c>
       <c r="H768" t="n">
         <v>165631</v>
@@ -22670,7 +22670,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502960205078</v>
+        <v>5.08502912521362</v>
       </c>
       <c r="H769" t="n">
         <v>224657</v>
@@ -22902,7 +22902,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H777" t="n">
         <v>121084</v>
@@ -23134,7 +23134,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773344039917</v>
+        <v>5.40773296356201</v>
       </c>
       <c r="H785" t="n">
         <v>58953</v>
@@ -23163,7 +23163,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928108215332</v>
+        <v>5.33928060531616</v>
       </c>
       <c r="H786" t="n">
         <v>28269</v>
@@ -23250,7 +23250,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H789" t="n">
         <v>33919</v>
@@ -23279,7 +23279,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016469955444</v>
+        <v>5.30016565322876</v>
       </c>
       <c r="H790" t="n">
         <v>36651</v>
@@ -23337,7 +23337,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G792" t="n">
-        <v>5.20237636566162</v>
+        <v>5.20237588882446</v>
       </c>
       <c r="H792" t="n">
         <v>22334</v>
@@ -23395,7 +23395,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G794" t="n">
-        <v>5.20237636566162</v>
+        <v>5.20237588882446</v>
       </c>
       <c r="H794" t="n">
         <v>45527</v>
@@ -23424,7 +23424,7 @@
         <v>5.25</v>
       </c>
       <c r="G795" t="n">
-        <v>5.13392400741577</v>
+        <v>5.13392353057861</v>
       </c>
       <c r="H795" t="n">
         <v>16038</v>
@@ -23453,7 +23453,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>5.22193431854248</v>
+        <v>5.22193384170532</v>
       </c>
       <c r="H796" t="n">
         <v>43106</v>
@@ -23511,7 +23511,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171234130859</v>
+        <v>5.23171281814575</v>
       </c>
       <c r="H798" t="n">
         <v>3968</v>
@@ -23540,7 +23540,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H799" t="n">
         <v>12491</v>
@@ -23627,7 +23627,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G802" t="n">
-        <v>5.20237636566162</v>
+        <v>5.20237588882446</v>
       </c>
       <c r="H802" t="n">
         <v>6956</v>
@@ -23685,7 +23685,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215534210205</v>
+        <v>5.21215486526489</v>
       </c>
       <c r="H804" t="n">
         <v>58954</v>
@@ -23714,7 +23714,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H805" t="n">
         <v>18129</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166269302368</v>
+        <v>4.79166221618652</v>
       </c>
       <c r="H807" t="n">
         <v>76245</v>
@@ -23946,7 +23946,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>5.0459132194519</v>
+        <v>5.04591369628906</v>
       </c>
       <c r="H813" t="n">
         <v>4389</v>
@@ -24120,7 +24120,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220642089844</v>
+        <v>5.65220594406128</v>
       </c>
       <c r="H819" t="n">
         <v>97422</v>
@@ -24149,7 +24149,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H820" t="n">
         <v>62956</v>
@@ -24178,7 +24178,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441617965698</v>
+        <v>5.55441665649414</v>
       </c>
       <c r="H821" t="n">
         <v>85848</v>
@@ -24236,7 +24236,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H823" t="n">
         <v>49574</v>
@@ -24468,7 +24468,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G831" t="n">
-        <v>6.44429683685303</v>
+        <v>6.44429636001587</v>
       </c>
       <c r="H831" t="n">
         <v>252834</v>
@@ -24526,7 +24526,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004535675049</v>
+        <v>6.19004487991333</v>
       </c>
       <c r="H833" t="n">
         <v>244592</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402473449707</v>
+        <v>6.01402521133423</v>
       </c>
       <c r="H834" t="n">
         <v>41322</v>
@@ -24613,7 +24613,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314064025879</v>
+        <v>6.05314016342163</v>
       </c>
       <c r="H836" t="n">
         <v>52635</v>
@@ -24642,7 +24642,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672904968262</v>
+        <v>6.33672857284546</v>
       </c>
       <c r="H837" t="n">
         <v>71930</v>
@@ -24729,7 +24729,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G840" t="n">
-        <v>6.73766326904297</v>
+        <v>6.73766374588013</v>
       </c>
       <c r="H840" t="n">
         <v>81839</v>
@@ -25048,7 +25048,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.14115142822266</v>
+        <v>6.14115047454834</v>
       </c>
       <c r="H851" t="n">
         <v>14069</v>
@@ -25077,7 +25077,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H852" t="n">
         <v>26701</v>
@@ -25106,7 +25106,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.0042462348938</v>
+        <v>6.00424575805664</v>
       </c>
       <c r="H853" t="n">
         <v>11658</v>
@@ -25222,7 +25222,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955270767212</v>
+        <v>5.76955223083496</v>
       </c>
       <c r="H857" t="n">
         <v>16583</v>
@@ -25251,7 +25251,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977325439453</v>
+        <v>5.75977373123169</v>
       </c>
       <c r="H858" t="n">
         <v>12990</v>
@@ -25367,7 +25367,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>5.60331058502197</v>
+        <v>5.60331106185913</v>
       </c>
       <c r="H862" t="n">
         <v>22714</v>
@@ -25454,7 +25454,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021530151367</v>
+        <v>5.74021577835083</v>
       </c>
       <c r="H865" t="n">
         <v>27718</v>
@@ -25512,7 +25512,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>5.67176342010498</v>
+        <v>5.67176389694214</v>
       </c>
       <c r="H867" t="n">
         <v>13457</v>
@@ -25541,7 +25541,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G868" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H868" t="n">
         <v>10349</v>
@@ -25599,7 +25599,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H870" t="n">
         <v>22149</v>
@@ -25744,7 +25744,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H875" t="n">
         <v>10415</v>
@@ -25947,7 +25947,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H882" t="n">
         <v>57113</v>
@@ -25976,7 +25976,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H883" t="n">
         <v>26982</v>
@@ -26034,7 +26034,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H885" t="n">
         <v>23779</v>
@@ -26092,7 +26092,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>6.65943193435669</v>
+        <v>6.65943241119385</v>
       </c>
       <c r="H887" t="n">
         <v>78414</v>
@@ -26121,7 +26121,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>6.44429683685303</v>
+        <v>6.44429636001587</v>
       </c>
       <c r="H888" t="n">
         <v>92730</v>
@@ -26208,7 +26208,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987493515015</v>
+        <v>6.63987445831299</v>
       </c>
       <c r="H891" t="n">
         <v>52119</v>
@@ -26266,7 +26266,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700067520142</v>
+        <v>6.76700019836426</v>
       </c>
       <c r="H893" t="n">
         <v>47611</v>
@@ -26440,7 +26440,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489068984985</v>
+        <v>7.74489116668701</v>
       </c>
       <c r="H899" t="n">
         <v>112735</v>
@@ -26498,7 +26498,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H901" t="n">
         <v>13903</v>
@@ -26527,7 +26527,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G902" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H902" t="n">
         <v>45564</v>
@@ -26556,7 +26556,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75466966629028</v>
+        <v>7.75466918945312</v>
       </c>
       <c r="H903" t="n">
         <v>44412</v>
@@ -26643,7 +26643,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842802047729</v>
+        <v>7.58842849731445</v>
       </c>
       <c r="H906" t="n">
         <v>22167</v>
@@ -26672,7 +26672,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>7.39284992218018</v>
+        <v>7.39285039901733</v>
       </c>
       <c r="H907" t="n">
         <v>26842</v>
@@ -26701,7 +26701,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G908" t="n">
-        <v>7.64710140228271</v>
+        <v>7.64710187911987</v>
       </c>
       <c r="H908" t="n">
         <v>26314</v>
@@ -26730,7 +26730,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>7.41240787506104</v>
+        <v>7.41240835189819</v>
       </c>
       <c r="H909" t="n">
         <v>50527</v>
@@ -26788,7 +26788,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147317886353</v>
+        <v>7.01147270202637</v>
       </c>
       <c r="H911" t="n">
         <v>49184</v>
@@ -26817,7 +26817,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572465896606</v>
+        <v>7.26572418212891</v>
       </c>
       <c r="H912" t="n">
         <v>36837</v>
@@ -26875,7 +26875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H914" t="n">
         <v>40423</v>
@@ -26933,7 +26933,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G916" t="n">
-        <v>6.85501098632812</v>
+        <v>6.85501050949097</v>
       </c>
       <c r="H916" t="n">
         <v>242774</v>
@@ -26991,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G918" t="n">
-        <v>6.84523153305054</v>
+        <v>6.8452320098877</v>
       </c>
       <c r="H918" t="n">
         <v>53696</v>
@@ -27165,7 +27165,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H924" t="n">
         <v>41919</v>
@@ -27252,7 +27252,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191570281982</v>
+        <v>6.99191522598267</v>
       </c>
       <c r="H927" t="n">
         <v>21117</v>
@@ -27339,7 +27339,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218732833862</v>
+        <v>7.42218685150146</v>
       </c>
       <c r="H930" t="n">
         <v>419711</v>
@@ -27368,7 +27368,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G931" t="n">
-        <v>7.24616670608521</v>
+        <v>7.24616622924805</v>
       </c>
       <c r="H931" t="n">
         <v>52841</v>
@@ -27600,7 +27600,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312202453613</v>
+        <v>7.82312154769897</v>
       </c>
       <c r="H939" t="n">
         <v>72321</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>8.03825759887695</v>
+        <v>8.03825855255127</v>
       </c>
       <c r="H940" t="n">
         <v>95905</v>
@@ -27687,7 +27687,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H942" t="n">
         <v>93859</v>
@@ -27745,7 +27745,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H944" t="n">
         <v>119944</v>
@@ -27832,7 +27832,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G947" t="n">
-        <v>9.43664073944092</v>
+        <v>9.4366397857666</v>
       </c>
       <c r="H947" t="n">
         <v>81693</v>
@@ -28035,7 +28035,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G954" t="n">
-        <v>8.810791015625</v>
+        <v>8.81079196929932</v>
       </c>
       <c r="H954" t="n">
         <v>75369</v>
@@ -28064,7 +28064,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>8.5956563949585</v>
+        <v>8.59565544128418</v>
       </c>
       <c r="H955" t="n">
         <v>181604</v>
@@ -28093,7 +28093,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897270202637</v>
+        <v>8.44897174835205</v>
       </c>
       <c r="H956" t="n">
         <v>40968</v>
@@ -28151,7 +28151,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37073993682861</v>
+        <v>8.37074089050293</v>
       </c>
       <c r="H958" t="n">
         <v>44957</v>
@@ -28209,7 +28209,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H960" t="n">
         <v>34300</v>
@@ -28267,7 +28267,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339317321777</v>
+        <v>8.25339412689209</v>
       </c>
       <c r="H962" t="n">
         <v>76522</v>
@@ -28354,7 +28354,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G965" t="n">
-        <v>8.70322322845459</v>
+        <v>8.70322227478027</v>
       </c>
       <c r="H965" t="n">
         <v>55469</v>
@@ -28383,7 +28383,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>8.45875072479248</v>
+        <v>8.45874977111816</v>
       </c>
       <c r="H966" t="n">
         <v>67238</v>
@@ -28412,7 +28412,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449924468994</v>
+        <v>8.20450019836426</v>
       </c>
       <c r="H967" t="n">
         <v>42116</v>
@@ -28441,7 +28441,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H968" t="n">
         <v>21079</v>
@@ -28528,7 +28528,7 @@
         <v>8.25</v>
       </c>
       <c r="G971" t="n">
-        <v>8.06759452819824</v>
+        <v>8.06759548187256</v>
       </c>
       <c r="H971" t="n">
         <v>26338</v>
@@ -28557,7 +28557,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G972" t="n">
-        <v>8.17516231536865</v>
+        <v>8.17516136169434</v>
       </c>
       <c r="H972" t="n">
         <v>14608</v>
@@ -28586,7 +28586,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482147216797</v>
+        <v>9.07482051849365</v>
       </c>
       <c r="H973" t="n">
         <v>227616</v>
@@ -28615,7 +28615,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H974" t="n">
         <v>250262</v>
@@ -28644,7 +28644,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.49531364440918</v>
+        <v>9.4953145980835</v>
       </c>
       <c r="H975" t="n">
         <v>336362</v>
@@ -28847,7 +28847,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804306030273</v>
+        <v>11.4804315567017</v>
       </c>
       <c r="H982" t="n">
         <v>419644</v>
@@ -29108,7 +29108,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926733016968</v>
+        <v>13.5926742553711</v>
       </c>
       <c r="H991" t="n">
         <v>195792</v>
@@ -29224,7 +29224,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8639316558838</v>
+        <v>14.8639307022095</v>
       </c>
       <c r="H995" t="n">
         <v>248550</v>
@@ -29369,7 +29369,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7100219726562</v>
+        <v>13.7100210189819</v>
       </c>
       <c r="H1000" t="n">
         <v>186196</v>
@@ -29427,7 +29427,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.3188638687134</v>
+        <v>13.3188648223877</v>
       </c>
       <c r="H1002" t="n">
         <v>70482</v>
@@ -29456,7 +29456,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.0059413909912</v>
+        <v>13.0059404373169</v>
       </c>
       <c r="H1003" t="n">
         <v>82659</v>
@@ -29630,7 +29630,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.2823028564453</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1009" t="n">
         <v>78089</v>
@@ -29688,7 +29688,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867223739624</v>
+        <v>12.0867233276367</v>
       </c>
       <c r="H1011" t="n">
         <v>47356</v>
@@ -29804,7 +29804,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1015" t="n">
-        <v>12.2040691375732</v>
+        <v>12.2040700912476</v>
       </c>
       <c r="H1015" t="n">
         <v>54788</v>
@@ -29949,7 +29949,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.5365533828735</v>
+        <v>12.5365524291992</v>
       </c>
       <c r="H1020" t="n">
         <v>66770</v>
@@ -30123,7 +30123,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.5952253341675</v>
+        <v>12.5952262878418</v>
       </c>
       <c r="H1026" t="n">
         <v>82690</v>
@@ -30152,7 +30152,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583206176758</v>
+        <v>12.4583215713501</v>
       </c>
       <c r="H1027" t="n">
         <v>145125</v>
@@ -30210,7 +30210,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>12.2040691375732</v>
+        <v>12.2040700912476</v>
       </c>
       <c r="H1029" t="n">
         <v>174418</v>
@@ -30239,7 +30239,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.2823028564453</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1030" t="n">
         <v>99601</v>
@@ -30268,7 +30268,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.2823028564453</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1031" t="n">
         <v>57835</v>
@@ -30326,7 +30326,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.7151250839233</v>
+        <v>11.715124130249</v>
       </c>
       <c r="H1033" t="n">
         <v>119232</v>
@@ -30471,7 +30471,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1038" t="n">
-        <v>12.2040691375732</v>
+        <v>12.2040700912476</v>
       </c>
       <c r="H1038" t="n">
         <v>111924</v>
@@ -30500,7 +30500,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734580993652</v>
+        <v>12.6734571456909</v>
       </c>
       <c r="H1039" t="n">
         <v>102261</v>
@@ -30616,7 +30616,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1043" t="n">
         <v>36180</v>
@@ -30674,7 +30674,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.4192066192627</v>
+        <v>12.4192056655884</v>
       </c>
       <c r="H1045" t="n">
         <v>16548</v>
@@ -30703,7 +30703,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1046" t="n">
         <v>29868</v>
@@ -30732,7 +30732,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409738540649</v>
+        <v>12.3409757614136</v>
       </c>
       <c r="H1047" t="n">
         <v>46643</v>
@@ -30848,7 +30848,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.2797498703003</v>
+        <v>13.279748916626</v>
       </c>
       <c r="H1051" t="n">
         <v>108427</v>
@@ -30993,7 +30993,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H1056" t="n">
         <v>93893</v>
@@ -31109,7 +31109,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.2091732025146</v>
+        <v>10.209174156189</v>
       </c>
       <c r="H1060" t="n">
         <v>129001</v>
@@ -31167,7 +31167,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H1062" t="n">
         <v>172678</v>
@@ -31341,7 +31341,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206798553467</v>
+        <v>8.31206703186035</v>
       </c>
       <c r="H1068" t="n">
         <v>167682</v>
@@ -31370,7 +31370,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H1069" t="n">
         <v>180623</v>
@@ -31399,7 +31399,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543346405029</v>
+        <v>8.60543441772461</v>
       </c>
       <c r="H1070" t="n">
         <v>27481</v>
@@ -31428,7 +31428,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1071" t="n">
-        <v>8.70322322845459</v>
+        <v>8.70322227478027</v>
       </c>
       <c r="H1071" t="n">
         <v>29010</v>
@@ -31486,7 +31486,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.810791015625</v>
+        <v>8.81079196929932</v>
       </c>
       <c r="H1073" t="n">
         <v>41885</v>
@@ -31515,7 +31515,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570556640625</v>
+        <v>9.03570652008057</v>
       </c>
       <c r="H1074" t="n">
         <v>47397</v>
@@ -31602,7 +31602,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H1077" t="n">
         <v>64803</v>
@@ -31689,7 +31689,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.4047527313232</v>
+        <v>10.4047517776489</v>
       </c>
       <c r="H1080" t="n">
         <v>36974</v>
@@ -31718,7 +31718,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H1081" t="n">
         <v>25731</v>
@@ -31747,7 +31747,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H1082" t="n">
         <v>25318</v>
@@ -31776,7 +31776,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003293991089</v>
+        <v>10.6003313064575</v>
       </c>
       <c r="H1083" t="n">
         <v>44357</v>
@@ -31805,7 +31805,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.443868637085</v>
+        <v>10.4438676834106</v>
       </c>
       <c r="H1084" t="n">
         <v>61024</v>
@@ -31834,7 +31834,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H1085" t="n">
         <v>43194</v>
@@ -31950,7 +31950,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.1819591522217</v>
+        <v>13.181960105896</v>
       </c>
       <c r="H1089" t="n">
         <v>178518</v>
@@ -31979,7 +31979,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>13.1037292480469</v>
+        <v>13.1037282943726</v>
       </c>
       <c r="H1090" t="n">
         <v>153541</v>
@@ -32037,7 +32037,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.1428451538086</v>
+        <v>13.1428442001343</v>
       </c>
       <c r="H1092" t="n">
         <v>90633</v>
@@ -32269,7 +32269,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1100" t="n">
-        <v>14.1402931213379</v>
+        <v>14.1402940750122</v>
       </c>
       <c r="H1100" t="n">
         <v>81068</v>
@@ -32298,7 +32298,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771987915039</v>
+        <v>14.2771978378296</v>
       </c>
       <c r="H1101" t="n">
         <v>57479</v>
@@ -32414,7 +32414,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030475616455</v>
+        <v>14.9030466079712</v>
       </c>
       <c r="H1105" t="n">
         <v>135713</v>
@@ -32443,7 +32443,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.7074689865112</v>
+        <v>14.7074699401855</v>
       </c>
       <c r="H1106" t="n">
         <v>120242</v>
@@ -32530,7 +32530,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181840896606</v>
+        <v>15.1181831359863</v>
       </c>
       <c r="H1109" t="n">
         <v>121418</v>
@@ -32559,7 +32559,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396104812622</v>
+        <v>15.9396095275879</v>
       </c>
       <c r="H1110" t="n">
         <v>152433</v>
@@ -32617,7 +32617,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1112" t="n">
-        <v>17.6802558898926</v>
+        <v>17.6802539825439</v>
       </c>
       <c r="H1112" t="n">
         <v>297169</v>
@@ -32675,7 +32675,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666507720947</v>
+        <v>19.1666488647461</v>
       </c>
       <c r="H1114" t="n">
         <v>462313</v>
@@ -32878,7 +32878,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981086730957</v>
+        <v>22.1981067657471</v>
       </c>
       <c r="H1121" t="n">
         <v>87185</v>
@@ -32965,7 +32965,7 @@
         <v>21.5</v>
       </c>
       <c r="G1124" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1124" t="n">
         <v>72589</v>
@@ -33139,7 +33139,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>21.1713237762451</v>
+        <v>21.1713218688965</v>
       </c>
       <c r="H1130" t="n">
         <v>60803</v>
@@ -33168,7 +33168,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558483123779</v>
+        <v>21.8558464050293</v>
       </c>
       <c r="H1131" t="n">
         <v>109080</v>
@@ -33197,7 +33197,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602687835693</v>
+        <v>21.660270690918</v>
       </c>
       <c r="H1132" t="n">
         <v>103507</v>
@@ -33255,7 +33255,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602687835693</v>
+        <v>21.660270690918</v>
       </c>
       <c r="H1134" t="n">
         <v>98501</v>
@@ -33284,7 +33284,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1135" t="n">
         <v>53815</v>
@@ -33400,7 +33400,7 @@
         <v>21.5</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1139" t="n">
         <v>34560</v>
@@ -33458,7 +33458,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>20.9757480621338</v>
+        <v>20.9757461547852</v>
       </c>
       <c r="H1141" t="n">
         <v>56787</v>
@@ -33516,7 +33516,7 @@
         <v>21.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1143" t="n">
         <v>34032</v>
@@ -33545,7 +33545,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1144" t="n">
         <v>22284</v>
@@ -33603,7 +33603,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691135406494</v>
+        <v>21.2691116333008</v>
       </c>
       <c r="H1146" t="n">
         <v>32961</v>
@@ -33632,7 +33632,7 @@
         <v>21.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1147" t="n">
         <v>58527</v>
@@ -33748,7 +33748,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1151" t="n">
         <v>65290</v>
@@ -33777,7 +33777,7 @@
         <v>21</v>
       </c>
       <c r="G1152" t="n">
-        <v>20.5356960296631</v>
+        <v>20.5356941223145</v>
       </c>
       <c r="H1152" t="n">
         <v>77191</v>
@@ -33806,7 +33806,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1153" t="n">
         <v>112291</v>
@@ -33835,7 +33835,7 @@
         <v>23.75</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.2248935699463</v>
+        <v>23.2248954772949</v>
       </c>
       <c r="H1154" t="n">
         <v>149423</v>
@@ -33893,7 +33893,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0560989379883</v>
+        <v>24.0561008453369</v>
       </c>
       <c r="H1156" t="n">
         <v>205397</v>
@@ -33922,7 +33922,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538887023926</v>
+        <v>24.1538906097412</v>
       </c>
       <c r="H1157" t="n">
         <v>72151</v>
@@ -34009,7 +34009,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.3226833343506</v>
+        <v>23.322681427002</v>
       </c>
       <c r="H1160" t="n">
         <v>31857</v>
@@ -34038,7 +34038,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7848415374756</v>
+        <v>22.7848434448242</v>
       </c>
       <c r="H1161" t="n">
         <v>56547</v>
@@ -34067,7 +34067,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359504699707</v>
+        <v>22.7359466552734</v>
       </c>
       <c r="H1162" t="n">
         <v>32829</v>
@@ -34096,7 +34096,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1163" t="n">
         <v>63588</v>
@@ -34125,7 +34125,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1164" t="n">
         <v>33009</v>
@@ -34154,7 +34154,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>22.6381587982178</v>
+        <v>22.6381568908691</v>
       </c>
       <c r="H1165" t="n">
         <v>26738</v>
@@ -34241,7 +34241,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1168" t="n">
         <v>45591</v>
@@ -34299,7 +34299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1170" t="n">
         <v>119843</v>
@@ -34328,7 +34328,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1171" t="n">
         <v>50849</v>
@@ -34560,7 +34560,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1179" t="n">
         <v>25025</v>
@@ -34589,7 +34589,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1180" t="n">
         <v>34676</v>
@@ -34618,7 +34618,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1181" t="n">
         <v>48003</v>
@@ -34647,7 +34647,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1182" t="n">
         <v>39901</v>
@@ -34676,7 +34676,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1183" t="n">
         <v>60552</v>
@@ -34705,7 +34705,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157962799072</v>
+        <v>21.4157943725586</v>
       </c>
       <c r="H1184" t="n">
         <v>21327</v>
@@ -34792,7 +34792,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1187" t="n">
         <v>68839</v>
@@ -34850,7 +34850,7 @@
         <v>21.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1189" t="n">
         <v>47664</v>
@@ -34908,7 +34908,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1191" t="n">
         <v>39920</v>
@@ -34937,7 +34937,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113758087158</v>
+        <v>21.6113739013672</v>
       </c>
       <c r="H1192" t="n">
         <v>25913</v>
@@ -34995,7 +34995,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1194" t="n">
         <v>28298</v>
@@ -35082,7 +35082,7 @@
         <v>21.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1197" t="n">
         <v>53455</v>
@@ -35169,7 +35169,7 @@
         <v>21.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1200" t="n">
         <v>137704</v>
@@ -35198,7 +35198,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>22.6381587982178</v>
+        <v>22.6381568908691</v>
       </c>
       <c r="H1201" t="n">
         <v>116966</v>
@@ -35256,7 +35256,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1203" t="n">
         <v>114554</v>
@@ -35372,7 +35372,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.9268493652344</v>
+        <v>20.926851272583</v>
       </c>
       <c r="H1207" t="n">
         <v>80989</v>
@@ -35401,7 +35401,7 @@
         <v>21.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1208" t="n">
         <v>60298</v>
@@ -35430,7 +35430,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401184082031</v>
+        <v>20.3401165008545</v>
       </c>
       <c r="H1209" t="n">
         <v>38491</v>
@@ -35575,7 +35575,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1214" t="n">
         <v>61113</v>
@@ -35633,7 +35633,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1216" t="n">
-        <v>19.4404563903809</v>
+        <v>19.4404582977295</v>
       </c>
       <c r="H1216" t="n">
         <v>49228</v>
@@ -35691,7 +35691,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.9978561401367</v>
+        <v>19.9978580474854</v>
       </c>
       <c r="H1218" t="n">
         <v>80159</v>
@@ -35749,7 +35749,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470928192139</v>
+        <v>19.1470890045166</v>
       </c>
       <c r="H1220" t="n">
         <v>78205</v>
@@ -35836,7 +35836,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.2669906616211</v>
+        <v>18.2669887542725</v>
       </c>
       <c r="H1223" t="n">
         <v>95192</v>
@@ -35981,7 +35981,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112106323242</v>
+        <v>16.3112087249756</v>
       </c>
       <c r="H1228" t="n">
         <v>66395</v>
@@ -36039,7 +36039,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329769134521</v>
+        <v>16.2329788208008</v>
       </c>
       <c r="H1230" t="n">
         <v>93368</v>
@@ -36068,7 +36068,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743068695068</v>
+        <v>16.1743049621582</v>
       </c>
       <c r="H1231" t="n">
         <v>45139</v>
@@ -36097,7 +36097,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.917501449585</v>
+        <v>16.9174995422363</v>
       </c>
       <c r="H1232" t="n">
         <v>52351</v>
@@ -36126,7 +36126,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.5824661254883</v>
+        <v>17.5824642181396</v>
       </c>
       <c r="H1233" t="n">
         <v>88571</v>
@@ -36155,7 +36155,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348472595215</v>
+        <v>17.0348491668701</v>
       </c>
       <c r="H1234" t="n">
         <v>86836</v>
@@ -36300,7 +36300,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108669281006</v>
+        <v>17.2108688354492</v>
       </c>
       <c r="H1239" t="n">
         <v>157511</v>
@@ -36358,7 +36358,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1241" t="n">
-        <v>17.0544052124023</v>
+        <v>17.054407119751</v>
       </c>
       <c r="H1241" t="n">
         <v>48546</v>
@@ -36503,7 +36503,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979454040527</v>
+        <v>16.8979434967041</v>
       </c>
       <c r="H1246" t="n">
         <v>89023</v>
@@ -36677,7 +36677,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1252" t="n">
         <v>39230</v>
@@ -36735,7 +36735,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761734008789</v>
+        <v>16.9761753082275</v>
       </c>
       <c r="H1254" t="n">
         <v>30692</v>
@@ -36764,7 +36764,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1255" t="n">
         <v>38089</v>
@@ -36851,7 +36851,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414798736572</v>
+        <v>16.7414817810059</v>
       </c>
       <c r="H1258" t="n">
         <v>87008</v>
@@ -80009,6 +80009,35 @@
         <v>10760</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>10.3199996948242</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>5305</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455717086792</v>
+        <v>6.71455669403076</v>
       </c>
       <c r="H3" t="n">
         <v>54991</v>
@@ -514,7 +514,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44674015045166</v>
+        <v>6.4467396736145</v>
       </c>
       <c r="H5" t="n">
         <v>108929</v>
@@ -630,7 +630,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H9" t="n">
         <v>104780</v>
@@ -659,7 +659,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.33196115493774</v>
+        <v>6.3319616317749</v>
       </c>
       <c r="H10" t="n">
         <v>158687</v>
@@ -717,7 +717,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546102523804</v>
+        <v>5.70546054840088</v>
       </c>
       <c r="H12" t="n">
         <v>113455</v>
@@ -775,7 +775,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31329965591431</v>
+        <v>5.31330013275146</v>
       </c>
       <c r="H14" t="n">
         <v>81327</v>
@@ -804,7 +804,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84415149688721</v>
+        <v>5.84415197372437</v>
       </c>
       <c r="H15" t="n">
         <v>162024</v>
@@ -833,7 +833,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7485032081604</v>
+        <v>5.74850273132324</v>
       </c>
       <c r="H16" t="n">
         <v>99565</v>
@@ -862,7 +862,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937250137329</v>
+        <v>5.72937297821045</v>
       </c>
       <c r="H17" t="n">
         <v>38963</v>
@@ -891,7 +891,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.0258846282959</v>
+        <v>6.02588510513306</v>
       </c>
       <c r="H18" t="n">
         <v>66351</v>
@@ -949,7 +949,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>6.00197219848633</v>
+        <v>6.00197315216064</v>
       </c>
       <c r="H20" t="n">
         <v>70672</v>
@@ -978,7 +978,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458293914795</v>
+        <v>5.94458341598511</v>
       </c>
       <c r="H21" t="n">
         <v>47413</v>
@@ -1065,7 +1065,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>5.83458614349365</v>
+        <v>5.83458662033081</v>
       </c>
       <c r="H24" t="n">
         <v>59492</v>
@@ -1094,7 +1094,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154443740845</v>
+        <v>5.79154491424561</v>
       </c>
       <c r="H25" t="n">
         <v>42499</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244876861572</v>
+        <v>4.78244829177856</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1210,7 +1210,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679216384888</v>
+        <v>4.90679121017456</v>
       </c>
       <c r="H29" t="n">
         <v>118336</v>
@@ -1239,7 +1239,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62941026687622</v>
+        <v>4.62940979003906</v>
       </c>
       <c r="H30" t="n">
         <v>67579</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.83983755111694</v>
+        <v>4.83983707427979</v>
       </c>
       <c r="H33" t="n">
         <v>11060</v>
@@ -1355,7 +1355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5954647064209</v>
+        <v>5.59546422958374</v>
       </c>
       <c r="H34" t="n">
         <v>87689</v>
@@ -1587,7 +1587,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069259643555</v>
+        <v>5.26069307327271</v>
       </c>
       <c r="H42" t="n">
         <v>79999</v>
@@ -1645,7 +1645,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.738450050354</v>
+        <v>4.73844957351685</v>
       </c>
       <c r="H44" t="n">
         <v>146124</v>
@@ -1703,7 +1703,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028051376343</v>
+        <v>4.61028003692627</v>
       </c>
       <c r="H46" t="n">
         <v>40055</v>
@@ -1732,7 +1732,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749671936035</v>
+        <v>4.62749719619751</v>
       </c>
       <c r="H47" t="n">
         <v>92990</v>
@@ -1761,7 +1761,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G48" t="n">
-        <v>4.45915508270264</v>
+        <v>4.45915460586548</v>
       </c>
       <c r="H48" t="n">
         <v>57163</v>
@@ -1790,7 +1790,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>4.6389741897583</v>
+        <v>4.63897466659546</v>
       </c>
       <c r="H49" t="n">
         <v>45504</v>
@@ -1848,7 +1848,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671644210815</v>
+        <v>4.556715965271</v>
       </c>
       <c r="H51" t="n">
         <v>33202</v>
@@ -1877,7 +1877,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732461929321</v>
+        <v>4.58732414245605</v>
       </c>
       <c r="H52" t="n">
         <v>22397</v>
@@ -1993,7 +1993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985275268555</v>
+        <v>4.39985179901123</v>
       </c>
       <c r="H56" t="n">
         <v>6922</v>
@@ -2022,7 +2022,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40559101104736</v>
+        <v>4.40559148788452</v>
       </c>
       <c r="H57" t="n">
         <v>12685</v>
@@ -2080,7 +2080,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.23916244506836</v>
+        <v>4.2391619682312</v>
       </c>
       <c r="H59" t="n">
         <v>20035</v>
@@ -2109,7 +2109,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>4.09377574920654</v>
+        <v>4.0937762260437</v>
       </c>
       <c r="H60" t="n">
         <v>95284</v>
@@ -2138,7 +2138,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916980743408</v>
+        <v>4.01916933059692</v>
       </c>
       <c r="H61" t="n">
         <v>8387</v>
@@ -2167,7 +2167,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793968200684</v>
+        <v>4.39793920516968</v>
       </c>
       <c r="H62" t="n">
         <v>183307</v>
@@ -2196,7 +2196,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202005386353</v>
+        <v>4.57202053070068</v>
       </c>
       <c r="H63" t="n">
         <v>101318</v>
@@ -2283,7 +2283,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.0650806427002</v>
+        <v>4.06508111953735</v>
       </c>
       <c r="H66" t="n">
         <v>69251</v>
@@ -2341,7 +2341,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691846847534</v>
+        <v>3.7169189453125</v>
       </c>
       <c r="H68" t="n">
         <v>96719</v>
@@ -2399,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.82595872879028</v>
+        <v>3.82595825195312</v>
       </c>
       <c r="H70" t="n">
         <v>33705</v>
@@ -2428,7 +2428,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987460136414</v>
+        <v>3.73987436294556</v>
       </c>
       <c r="H71" t="n">
         <v>26533</v>
@@ -2486,7 +2486,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813410758972</v>
+        <v>3.77813386917114</v>
       </c>
       <c r="H73" t="n">
         <v>13357</v>
@@ -2544,7 +2544,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.84891414642334</v>
+        <v>3.8489146232605</v>
       </c>
       <c r="H75" t="n">
         <v>62408</v>
@@ -2573,7 +2573,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463863372803</v>
+        <v>4.29463815689087</v>
       </c>
       <c r="H76" t="n">
         <v>172014</v>
@@ -2602,7 +2602,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723096847534</v>
+        <v>4.78723049163818</v>
       </c>
       <c r="H77" t="n">
         <v>182115</v>
@@ -2631,7 +2631,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.45199060440063</v>
+        <v>5.45199108123779</v>
       </c>
       <c r="H78" t="n">
         <v>472702</v>
@@ -2689,7 +2689,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851793289185</v>
+        <v>5.30851745605469</v>
       </c>
       <c r="H80" t="n">
         <v>273720</v>
@@ -2718,7 +2718,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373525619507</v>
+        <v>5.30373573303223</v>
       </c>
       <c r="H81" t="n">
         <v>264110</v>
@@ -2805,7 +2805,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417774200439</v>
+        <v>5.07417726516724</v>
       </c>
       <c r="H84" t="n">
         <v>122889</v>
@@ -2834,7 +2834,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>4.93548583984375</v>
+        <v>4.93548631668091</v>
       </c>
       <c r="H85" t="n">
         <v>71889</v>
@@ -2863,7 +2863,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>4.95461654663086</v>
+        <v>4.9546160697937</v>
       </c>
       <c r="H86" t="n">
         <v>66959</v>
@@ -2892,7 +2892,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653650283813</v>
+        <v>4.73653697967529</v>
       </c>
       <c r="H87" t="n">
         <v>101740</v>
@@ -2921,7 +2921,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680593490601</v>
+        <v>4.46680688858032</v>
       </c>
       <c r="H88" t="n">
         <v>98603</v>
@@ -3153,7 +3153,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16073036193848</v>
+        <v>4.16072988510132</v>
       </c>
       <c r="H96" t="n">
         <v>114509</v>
@@ -3182,7 +3182,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.11673164367676</v>
+        <v>4.11673069000244</v>
       </c>
       <c r="H97" t="n">
         <v>33027</v>
@@ -3211,7 +3211,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603397369385</v>
+        <v>4.17603302001953</v>
       </c>
       <c r="H98" t="n">
         <v>54021</v>
@@ -3298,7 +3298,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157068252563</v>
+        <v>5.02157020568848</v>
       </c>
       <c r="H101" t="n">
         <v>322788</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113971710205</v>
+        <v>4.92113828659058</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3385,7 +3385,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548311233521</v>
+        <v>5.04548263549805</v>
       </c>
       <c r="H104" t="n">
         <v>88307</v>
@@ -3414,7 +3414,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G105" t="n">
-        <v>5.40894937515259</v>
+        <v>5.40894889831543</v>
       </c>
       <c r="H105" t="n">
         <v>257471</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H106" t="n">
         <v>756136</v>
@@ -3472,7 +3472,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756622314453</v>
+        <v>7.74756669998169</v>
       </c>
       <c r="H107" t="n">
         <v>830490</v>
@@ -3530,7 +3530,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367683410645</v>
+        <v>7.06367540359497</v>
       </c>
       <c r="H109" t="n">
         <v>396366</v>
@@ -3559,7 +3559,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H110" t="n">
         <v>192489</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804183959961</v>
+        <v>6.52804088592529</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3617,7 +3617,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>6.26022434234619</v>
+        <v>6.26022481918335</v>
       </c>
       <c r="H112" t="n">
         <v>219748</v>
@@ -3733,7 +3733,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718311309814</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H116" t="n">
         <v>279195</v>
@@ -3762,7 +3762,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718311309814</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H117" t="n">
         <v>281217</v>
@@ -3791,7 +3791,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>5.83458614349365</v>
+        <v>5.83458662033081</v>
       </c>
       <c r="H118" t="n">
         <v>228253</v>
@@ -3820,7 +3820,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>5.87762880325317</v>
+        <v>5.87762975692749</v>
       </c>
       <c r="H119" t="n">
         <v>158117</v>
@@ -3936,7 +3936,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195379257202</v>
+        <v>6.55195426940918</v>
       </c>
       <c r="H123" t="n">
         <v>388485</v>
@@ -3965,7 +3965,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.0689263343811</v>
+        <v>6.06892681121826</v>
       </c>
       <c r="H124" t="n">
         <v>130995</v>
@@ -3994,7 +3994,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83936929702759</v>
+        <v>5.83936977386475</v>
       </c>
       <c r="H125" t="n">
         <v>111496</v>
@@ -4023,7 +4023,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>6.26022434234619</v>
+        <v>6.26022481918335</v>
       </c>
       <c r="H126" t="n">
         <v>126051</v>
@@ -4052,7 +4052,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848064422607</v>
+        <v>6.40848016738892</v>
       </c>
       <c r="H127" t="n">
         <v>110989</v>
@@ -4226,7 +4226,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805288314819</v>
+        <v>6.19805240631104</v>
       </c>
       <c r="H133" t="n">
         <v>77921</v>
@@ -4255,7 +4255,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>6.63803863525391</v>
+        <v>6.63803815841675</v>
       </c>
       <c r="H134" t="n">
         <v>118333</v>
@@ -4284,7 +4284,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933616638184</v>
+        <v>6.82933568954468</v>
       </c>
       <c r="H135" t="n">
         <v>65285</v>
@@ -4429,7 +4429,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>7.05889368057251</v>
+        <v>7.05889415740967</v>
       </c>
       <c r="H140" t="n">
         <v>313570</v>
@@ -4487,7 +4487,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>6.99672174453735</v>
+        <v>6.9967212677002</v>
       </c>
       <c r="H142" t="n">
         <v>66130</v>
@@ -4516,7 +4516,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H143" t="n">
         <v>31912</v>
@@ -4545,7 +4545,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H144" t="n">
         <v>21903</v>
@@ -4574,7 +4574,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H145" t="n">
         <v>55058</v>
@@ -4603,7 +4603,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107666015625</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H146" t="n">
         <v>18313</v>
@@ -4632,7 +4632,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.9249849319458</v>
+        <v>6.92498445510864</v>
       </c>
       <c r="H147" t="n">
         <v>105405</v>
@@ -4661,7 +4661,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75281667709351</v>
+        <v>6.75281620025635</v>
       </c>
       <c r="H148" t="n">
         <v>55331</v>
@@ -4690,7 +4690,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.8723783493042</v>
+        <v>6.87237787246704</v>
       </c>
       <c r="H149" t="n">
         <v>71959</v>
@@ -4719,7 +4719,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064474105835</v>
+        <v>6.69064521789551</v>
       </c>
       <c r="H150" t="n">
         <v>35920</v>
@@ -4748,7 +4748,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>6.85324764251709</v>
+        <v>6.85324811935425</v>
       </c>
       <c r="H151" t="n">
         <v>44123</v>
@@ -4777,7 +4777,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>6.95368003845215</v>
+        <v>6.95367956161499</v>
       </c>
       <c r="H152" t="n">
         <v>61634</v>
@@ -4835,7 +4835,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>7.03019905090332</v>
+        <v>7.03019857406616</v>
       </c>
       <c r="H154" t="n">
         <v>34070</v>
@@ -4864,7 +4864,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976392745972</v>
+        <v>7.03976345062256</v>
       </c>
       <c r="H155" t="n">
         <v>46790</v>
@@ -4922,7 +4922,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886518478394</v>
+        <v>7.93886470794678</v>
       </c>
       <c r="H157" t="n">
         <v>265495</v>
@@ -4951,7 +4951,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.0919017791748</v>
+        <v>8.09190368652344</v>
       </c>
       <c r="H158" t="n">
         <v>272541</v>
@@ -4980,7 +4980,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712741851807</v>
+        <v>7.86712789535522</v>
       </c>
       <c r="H159" t="n">
         <v>93100</v>
@@ -5038,7 +5038,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.67104721069336</v>
+        <v>7.67104768753052</v>
       </c>
       <c r="H161" t="n">
         <v>97882</v>
@@ -5125,7 +5125,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234521865845</v>
+        <v>7.86234426498413</v>
       </c>
       <c r="H164" t="n">
         <v>30398</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626132965088</v>
+        <v>7.77626037597656</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5212,7 +5212,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712421417236</v>
+        <v>7.97712373733521</v>
       </c>
       <c r="H167" t="n">
         <v>31192</v>
@@ -5299,7 +5299,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.83364963531494</v>
+        <v>7.8336501121521</v>
       </c>
       <c r="H170" t="n">
         <v>41230</v>
@@ -5328,7 +5328,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669597625732</v>
+        <v>7.76669549942017</v>
       </c>
       <c r="H171" t="n">
         <v>80513</v>
@@ -5357,7 +5357,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103937149048</v>
+        <v>7.89103984832764</v>
       </c>
       <c r="H172" t="n">
         <v>61552</v>
@@ -5386,7 +5386,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.89582252502441</v>
+        <v>7.89582204818726</v>
       </c>
       <c r="H173" t="n">
         <v>38551</v>
@@ -5415,7 +5415,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928558349609</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H174" t="n">
         <v>135297</v>
@@ -5444,7 +5444,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492603302002</v>
+        <v>8.68492698669434</v>
       </c>
       <c r="H175" t="n">
         <v>251570</v>
@@ -5502,7 +5502,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622676849365</v>
+        <v>8.76622581481934</v>
       </c>
       <c r="H177" t="n">
         <v>231642</v>
@@ -5618,7 +5618,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.4171085357666</v>
+        <v>8.41710758209229</v>
       </c>
       <c r="H181" t="n">
         <v>154982</v>
@@ -5647,7 +5647,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>8.46493339538574</v>
+        <v>8.46493434906006</v>
       </c>
       <c r="H182" t="n">
         <v>82708</v>
@@ -5676,7 +5676,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>8.20668029785156</v>
+        <v>8.20668125152588</v>
       </c>
       <c r="H183" t="n">
         <v>59457</v>
@@ -5705,7 +5705,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.2545051574707</v>
+        <v>8.25450611114502</v>
       </c>
       <c r="H184" t="n">
         <v>33220</v>
@@ -5734,7 +5734,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.9245171546936</v>
+        <v>7.92451763153076</v>
       </c>
       <c r="H185" t="n">
         <v>122464</v>
@@ -5763,7 +5763,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581195831299</v>
+        <v>8.22581100463867</v>
       </c>
       <c r="H186" t="n">
         <v>99183</v>
@@ -5792,7 +5792,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34058952331543</v>
+        <v>8.34059047698975</v>
       </c>
       <c r="H187" t="n">
         <v>63159</v>
@@ -5821,7 +5821,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928558349609</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H188" t="n">
         <v>34542</v>
@@ -5850,7 +5850,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754638671875</v>
+        <v>8.29754734039307</v>
       </c>
       <c r="H189" t="n">
         <v>29985</v>
@@ -5879,7 +5879,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.2736349105835</v>
+        <v>8.27363586425781</v>
       </c>
       <c r="H190" t="n">
         <v>51064</v>
@@ -5908,7 +5908,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928558349609</v>
+        <v>8.36928367614746</v>
       </c>
       <c r="H191" t="n">
         <v>24030</v>
@@ -5995,7 +5995,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92883110046387</v>
+        <v>8.92883014678955</v>
       </c>
       <c r="H194" t="n">
         <v>196106</v>
@@ -6024,7 +6024,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.06752014160156</v>
+        <v>9.0675220489502</v>
       </c>
       <c r="H195" t="n">
         <v>116469</v>
@@ -6111,7 +6111,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317497253418</v>
+        <v>9.05317401885986</v>
       </c>
       <c r="H198" t="n">
         <v>156638</v>
@@ -6169,7 +6169,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882598876953</v>
+        <v>9.03882694244385</v>
       </c>
       <c r="H200" t="n">
         <v>84914</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.13447570800781</v>
+        <v>9.13447666168213</v>
       </c>
       <c r="H201" t="n">
         <v>49199</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6401,7 +6401,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620147705078</v>
+        <v>9.5362024307251</v>
       </c>
       <c r="H208" t="n">
         <v>78401</v>
@@ -6430,7 +6430,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587827682495</v>
+        <v>10.3587837219238</v>
       </c>
       <c r="H209" t="n">
         <v>324694</v>
@@ -6546,7 +6546,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>11.1813640594482</v>
+        <v>11.1813650131226</v>
       </c>
       <c r="H213" t="n">
         <v>187510</v>
@@ -6575,7 +6575,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1813640594482</v>
+        <v>11.1813650131226</v>
       </c>
       <c r="H214" t="n">
         <v>181372</v>
@@ -6662,7 +6662,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.0431413650513</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H217" t="n">
         <v>175009</v>
@@ -6691,7 +6691,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.0431413650513</v>
+        <v>10.043140411377</v>
       </c>
       <c r="H218" t="n">
         <v>270935</v>
@@ -6720,7 +6720,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831256866455</v>
+        <v>10.4831266403198</v>
       </c>
       <c r="H219" t="n">
         <v>128669</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692110061646</v>
+        <v>10.5692100524902</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6778,7 +6778,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8274621963501</v>
+        <v>10.8274631500244</v>
       </c>
       <c r="H221" t="n">
         <v>165457</v>
@@ -6807,7 +6807,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370275497437</v>
+        <v>10.8370265960693</v>
       </c>
       <c r="H222" t="n">
         <v>98298</v>
@@ -6865,7 +6865,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.114408493042</v>
+        <v>11.1144094467163</v>
       </c>
       <c r="H224" t="n">
         <v>91003</v>
@@ -6894,7 +6894,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630971908569</v>
+        <v>11.3630962371826</v>
       </c>
       <c r="H225" t="n">
         <v>187509</v>
@@ -6981,7 +6981,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456912994385</v>
+        <v>11.7456922531128</v>
       </c>
       <c r="H228" t="n">
         <v>176751</v>
@@ -7039,7 +7039,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G230" t="n">
-        <v>11.6309127807617</v>
+        <v>11.630913734436</v>
       </c>
       <c r="H230" t="n">
         <v>118136</v>
@@ -7068,7 +7068,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>11.6691722869873</v>
+        <v>11.6691732406616</v>
       </c>
       <c r="H231" t="n">
         <v>95647</v>
@@ -7126,7 +7126,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961057662964</v>
+        <v>12.3961048126221</v>
       </c>
       <c r="H233" t="n">
         <v>317127</v>
@@ -7271,7 +7271,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839527130127</v>
+        <v>11.7839517593384</v>
       </c>
       <c r="H238" t="n">
         <v>75176</v>
@@ -7300,7 +7300,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G239" t="n">
-        <v>12.4247999191284</v>
+        <v>12.4248008728027</v>
       </c>
       <c r="H239" t="n">
         <v>134820</v>
@@ -7329,7 +7329,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.6160984039307</v>
+        <v>12.616096496582</v>
       </c>
       <c r="H240" t="n">
         <v>180021</v>
@@ -7358,7 +7358,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169612884521</v>
+        <v>12.8169603347778</v>
       </c>
       <c r="H241" t="n">
         <v>122373</v>
@@ -7416,7 +7416,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473434448242</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H243" t="n">
         <v>303111</v>
@@ -7445,7 +7445,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446565628052</v>
+        <v>15.2446575164795</v>
       </c>
       <c r="H244" t="n">
         <v>256881</v>
@@ -7474,7 +7474,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.0385932922363</v>
+        <v>14.038592338562</v>
       </c>
       <c r="H245" t="n">
         <v>494015</v>
@@ -7532,7 +7532,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>13.8456230163574</v>
+        <v>13.8456220626831</v>
       </c>
       <c r="H247" t="n">
         <v>263722</v>
@@ -7561,7 +7561,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G248" t="n">
-        <v>13.3728437423706</v>
+        <v>13.3728446960449</v>
       </c>
       <c r="H248" t="n">
         <v>127762</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272207260132</v>
+        <v>13.5272216796875</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7619,7 +7619,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G250" t="n">
-        <v>13.4307355880737</v>
+        <v>13.430736541748</v>
       </c>
       <c r="H250" t="n">
         <v>48278</v>
@@ -7706,7 +7706,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H253" t="n">
         <v>84013</v>
@@ -7793,7 +7793,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G256" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H256" t="n">
         <v>44658</v>
@@ -7822,7 +7822,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000682830811</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H257" t="n">
         <v>36672</v>
@@ -7851,7 +7851,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H258" t="n">
         <v>48422</v>
@@ -7880,7 +7880,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H259" t="n">
         <v>124706</v>
@@ -7967,7 +7967,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H262" t="n">
         <v>39442</v>
@@ -7996,7 +7996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219835281372</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H263" t="n">
         <v>90090</v>
@@ -8054,7 +8054,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.78773021698</v>
+        <v>13.7877321243286</v>
       </c>
       <c r="H265" t="n">
         <v>225704</v>
@@ -8112,7 +8112,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044101715088</v>
+        <v>13.6044092178345</v>
       </c>
       <c r="H267" t="n">
         <v>71289</v>
@@ -8228,7 +8228,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.131630897522</v>
+        <v>13.1316299438477</v>
       </c>
       <c r="H271" t="n">
         <v>92437</v>
@@ -8257,7 +8257,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219835281372</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H272" t="n">
         <v>43627</v>
@@ -8286,7 +8286,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H273" t="n">
         <v>167282</v>
@@ -8402,7 +8402,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5396270751953</v>
+        <v>11.539626121521</v>
       </c>
       <c r="H277" t="n">
         <v>194589</v>
@@ -8431,7 +8431,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H278" t="n">
         <v>152414</v>
@@ -8489,7 +8489,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G280" t="n">
-        <v>11.6650581359863</v>
+        <v>11.665057182312</v>
       </c>
       <c r="H280" t="n">
         <v>34289</v>
@@ -8518,7 +8518,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5975179672241</v>
+        <v>11.5975170135498</v>
       </c>
       <c r="H281" t="n">
         <v>40964</v>
@@ -8721,7 +8721,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.7291507720947</v>
+        <v>10.729151725769</v>
       </c>
       <c r="H288" t="n">
         <v>25029</v>
@@ -8808,7 +8808,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H291" t="n">
         <v>17482</v>
@@ -8895,7 +8895,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.008957862854</v>
+        <v>11.0089588165283</v>
       </c>
       <c r="H294" t="n">
         <v>9802</v>
@@ -8924,7 +8924,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G295" t="n">
-        <v>10.8449335098267</v>
+        <v>10.8449325561523</v>
       </c>
       <c r="H295" t="n">
         <v>23068</v>
@@ -8953,7 +8953,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072355270386</v>
+        <v>10.5072345733643</v>
       </c>
       <c r="H296" t="n">
         <v>45140</v>
@@ -8982,7 +8982,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695384979248</v>
+        <v>10.1695375442505</v>
       </c>
       <c r="H297" t="n">
         <v>66319</v>
@@ -9011,7 +9011,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247396469116</v>
+        <v>11.1247406005859</v>
       </c>
       <c r="H298" t="n">
         <v>108006</v>
@@ -9069,7 +9069,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685729980469</v>
+        <v>11.5685720443726</v>
       </c>
       <c r="H300" t="n">
         <v>224596</v>
@@ -9127,7 +9127,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273601531982</v>
+        <v>11.3273582458496</v>
       </c>
       <c r="H302" t="n">
         <v>104822</v>
@@ -9185,7 +9185,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.436939239502</v>
+        <v>12.4369382858276</v>
       </c>
       <c r="H304" t="n">
         <v>178543</v>
@@ -9272,7 +9272,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G307" t="n">
-        <v>11.587869644165</v>
+        <v>11.5878686904907</v>
       </c>
       <c r="H307" t="n">
         <v>49320</v>
@@ -9359,7 +9359,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H310" t="n">
         <v>41614</v>
@@ -9388,7 +9388,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212257385254</v>
+        <v>11.2212247848511</v>
       </c>
       <c r="H311" t="n">
         <v>48985</v>
@@ -9417,7 +9417,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054430007935</v>
+        <v>11.1054439544678</v>
       </c>
       <c r="H312" t="n">
         <v>33585</v>
@@ -9446,7 +9446,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>11.5975179672241</v>
+        <v>11.5975170135498</v>
       </c>
       <c r="H313" t="n">
         <v>101331</v>
@@ -9504,7 +9504,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334936141968</v>
+        <v>11.4334945678711</v>
       </c>
       <c r="H315" t="n">
         <v>31751</v>
@@ -9533,7 +9533,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H316" t="n">
         <v>113990</v>
@@ -9562,7 +9562,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H317" t="n">
         <v>48953</v>
@@ -9736,7 +9736,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387308120728</v>
+        <v>11.8387317657471</v>
       </c>
       <c r="H323" t="n">
         <v>88601</v>
@@ -9823,7 +9823,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044101715088</v>
+        <v>13.6044092178345</v>
       </c>
       <c r="H326" t="n">
         <v>296460</v>
@@ -9852,7 +9852,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G327" t="n">
-        <v>13.6140565872192</v>
+        <v>13.6140575408936</v>
       </c>
       <c r="H327" t="n">
         <v>135660</v>
@@ -9881,7 +9881,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H328" t="n">
         <v>133226</v>
@@ -9910,7 +9910,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693298339844</v>
+        <v>13.4693307876587</v>
       </c>
       <c r="H329" t="n">
         <v>64109</v>
@@ -9939,7 +9939,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H330" t="n">
         <v>80883</v>
@@ -9968,7 +9968,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H331" t="n">
         <v>127592</v>
@@ -9997,7 +9997,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G332" t="n">
-        <v>13.4307355880737</v>
+        <v>13.430736541748</v>
       </c>
       <c r="H332" t="n">
         <v>75116</v>
@@ -10084,7 +10084,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H335" t="n">
         <v>56318</v>
@@ -10113,7 +10113,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H336" t="n">
         <v>66093</v>
@@ -10229,7 +10229,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807014465332</v>
+        <v>13.9807004928589</v>
       </c>
       <c r="H340" t="n">
         <v>101573</v>
@@ -10258,7 +10258,7 @@
         <v>14.75</v>
       </c>
       <c r="G341" t="n">
-        <v>14.2315626144409</v>
+        <v>14.2315635681152</v>
       </c>
       <c r="H341" t="n">
         <v>95930</v>
@@ -10316,7 +10316,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.4920721054077</v>
+        <v>14.492073059082</v>
       </c>
       <c r="H343" t="n">
         <v>175404</v>
@@ -10345,7 +10345,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H344" t="n">
         <v>84729</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.569260597229</v>
+        <v>14.5692615509033</v>
       </c>
       <c r="H346" t="n">
         <v>63786</v>
@@ -10490,7 +10490,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.405237197876</v>
+        <v>14.4052352905273</v>
       </c>
       <c r="H349" t="n">
         <v>73630</v>
@@ -10519,7 +10519,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824237823486</v>
+        <v>14.4824247360229</v>
       </c>
       <c r="H350" t="n">
         <v>97965</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527210235596</v>
+        <v>12.5527219772339</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10693,7 +10693,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000682830811</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H356" t="n">
         <v>42754</v>
@@ -10722,7 +10722,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G357" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H357" t="n">
         <v>55254</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.0062017440796</v>
+        <v>13.0062007904053</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10838,7 +10838,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H361" t="n">
         <v>30895</v>
@@ -10867,7 +10867,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H362" t="n">
         <v>25549</v>
@@ -10896,7 +10896,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H363" t="n">
         <v>24673</v>
@@ -10925,7 +10925,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.131630897522</v>
+        <v>13.1316299438477</v>
       </c>
       <c r="H364" t="n">
         <v>31128</v>
@@ -10954,7 +10954,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H365" t="n">
         <v>55168</v>
@@ -11012,7 +11012,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360429763794</v>
+        <v>12.7360420227051</v>
       </c>
       <c r="H367" t="n">
         <v>41635</v>
@@ -11041,7 +11041,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>12.726393699646</v>
+        <v>12.7263927459717</v>
       </c>
       <c r="H368" t="n">
         <v>31587</v>
@@ -11128,7 +11128,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755334854126</v>
+        <v>12.4755325317383</v>
       </c>
       <c r="H371" t="n">
         <v>12596</v>
@@ -11186,7 +11186,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>11.9641609191895</v>
+        <v>11.9641599655151</v>
       </c>
       <c r="H373" t="n">
         <v>95740</v>
@@ -11215,7 +11215,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150220870972</v>
+        <v>12.2150230407715</v>
       </c>
       <c r="H374" t="n">
         <v>20005</v>
@@ -11273,7 +11273,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H376" t="n">
         <v>18790</v>
@@ -11302,7 +11302,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H377" t="n">
         <v>54450</v>
@@ -11418,7 +11418,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H381" t="n">
         <v>64542</v>
@@ -11447,7 +11447,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194332122803</v>
+        <v>11.8194341659546</v>
       </c>
       <c r="H382" t="n">
         <v>27743</v>
@@ -11534,7 +11534,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325954437256</v>
+        <v>11.7325963973999</v>
       </c>
       <c r="H385" t="n">
         <v>6733</v>
@@ -11621,7 +11621,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>12.2536163330078</v>
+        <v>12.2536172866821</v>
       </c>
       <c r="H388" t="n">
         <v>47918</v>
@@ -11650,7 +11650,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966207504272</v>
+        <v>11.8966217041016</v>
       </c>
       <c r="H389" t="n">
         <v>33102</v>
@@ -11679,7 +11679,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>11.9641609191895</v>
+        <v>11.9641599655151</v>
       </c>
       <c r="H390" t="n">
         <v>27020</v>
@@ -11708,7 +11708,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H391" t="n">
         <v>36167</v>
@@ -11824,7 +11824,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H395" t="n">
         <v>18587</v>
@@ -11853,7 +11853,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.2439670562744</v>
+        <v>12.243968963623</v>
       </c>
       <c r="H396" t="n">
         <v>21900</v>
@@ -11882,7 +11882,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H397" t="n">
         <v>62135</v>
@@ -11911,7 +11911,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G398" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H398" t="n">
         <v>107931</v>
@@ -11998,7 +11998,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.8325290679932</v>
+        <v>12.8325281143188</v>
       </c>
       <c r="H401" t="n">
         <v>13252</v>
@@ -12056,7 +12056,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>12.562370300293</v>
+        <v>12.5623693466187</v>
       </c>
       <c r="H403" t="n">
         <v>8745</v>
@@ -12143,7 +12143,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H406" t="n">
         <v>26294</v>
@@ -12172,7 +12172,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H407" t="n">
         <v>26025</v>
@@ -12230,7 +12230,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>12.8711223602295</v>
+        <v>12.8711214065552</v>
       </c>
       <c r="H409" t="n">
         <v>6479</v>
@@ -12259,7 +12259,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483108520508</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H410" t="n">
         <v>21714</v>
@@ -12317,7 +12317,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219835281372</v>
+        <v>13.1219825744629</v>
       </c>
       <c r="H412" t="n">
         <v>20167</v>
@@ -12404,7 +12404,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>12.562370300293</v>
+        <v>12.5623693466187</v>
       </c>
       <c r="H415" t="n">
         <v>14241</v>
@@ -12433,7 +12433,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G416" t="n">
-        <v>13.0930376052856</v>
+        <v>13.09303855896</v>
       </c>
       <c r="H416" t="n">
         <v>51186</v>
@@ -12462,7 +12462,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H417" t="n">
         <v>19263</v>
@@ -12578,7 +12578,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.977255821228</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H421" t="n">
         <v>36559</v>
@@ -12607,7 +12607,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483108520508</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H422" t="n">
         <v>22215</v>
@@ -12665,7 +12665,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H424" t="n">
         <v>8468</v>
@@ -12694,7 +12694,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167463302612</v>
+        <v>12.7167453765869</v>
       </c>
       <c r="H425" t="n">
         <v>35809</v>
@@ -12723,7 +12723,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5334234237671</v>
+        <v>12.5334243774414</v>
       </c>
       <c r="H426" t="n">
         <v>25449</v>
@@ -12781,7 +12781,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483108520508</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H428" t="n">
         <v>13836</v>
@@ -12810,7 +12810,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.8325290679932</v>
+        <v>12.8325281143188</v>
       </c>
       <c r="H429" t="n">
         <v>23103</v>
@@ -12839,7 +12839,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H430" t="n">
         <v>30798</v>
@@ -12868,7 +12868,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>13.2184686660767</v>
+        <v>13.2184677124023</v>
       </c>
       <c r="H431" t="n">
         <v>67159</v>
@@ -13042,7 +13042,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H437" t="n">
         <v>115869</v>
@@ -13071,7 +13071,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974487304688</v>
+        <v>12.6974496841431</v>
       </c>
       <c r="H438" t="n">
         <v>68110</v>
@@ -13129,7 +13129,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H440" t="n">
         <v>33681</v>
@@ -13158,7 +13158,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>12.726393699646</v>
+        <v>12.7263927459717</v>
       </c>
       <c r="H441" t="n">
         <v>30766</v>
@@ -13187,7 +13187,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553405761719</v>
+        <v>12.7553396224976</v>
       </c>
       <c r="H442" t="n">
         <v>23233</v>
@@ -13390,7 +13390,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>12.6685028076172</v>
+        <v>12.6685037612915</v>
       </c>
       <c r="H449" t="n">
         <v>33026</v>
@@ -13419,7 +13419,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G450" t="n">
-        <v>12.6781511306763</v>
+        <v>12.6781520843506</v>
       </c>
       <c r="H450" t="n">
         <v>8729</v>
@@ -13477,7 +13477,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3693990707397</v>
+        <v>12.3693981170654</v>
       </c>
       <c r="H452" t="n">
         <v>28539</v>
@@ -13564,7 +13564,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H455" t="n">
         <v>45659</v>
@@ -13593,7 +13593,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H456" t="n">
         <v>40685</v>
@@ -13622,7 +13622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H457" t="n">
         <v>24461</v>
@@ -13651,7 +13651,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>12.2536163330078</v>
+        <v>12.2536172866821</v>
       </c>
       <c r="H458" t="n">
         <v>49613</v>
@@ -13709,7 +13709,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>12.446587562561</v>
+        <v>12.4465866088867</v>
       </c>
       <c r="H460" t="n">
         <v>60559</v>
@@ -13883,7 +13883,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H466" t="n">
         <v>20941</v>
@@ -13941,7 +13941,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H468" t="n">
         <v>13736</v>
@@ -13970,7 +13970,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H469" t="n">
         <v>26893</v>
@@ -14028,7 +14028,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308048248291</v>
+        <v>12.3308038711548</v>
       </c>
       <c r="H471" t="n">
         <v>21463</v>
@@ -14086,7 +14086,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>12.1088886260986</v>
+        <v>12.1088895797729</v>
       </c>
       <c r="H473" t="n">
         <v>20258</v>
@@ -14144,7 +14144,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124034881592</v>
+        <v>12.0124025344849</v>
       </c>
       <c r="H475" t="n">
         <v>13507</v>
@@ -14173,7 +14173,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>11.8290815353394</v>
+        <v>11.8290824890137</v>
       </c>
       <c r="H476" t="n">
         <v>75300</v>
@@ -14202,7 +14202,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747074127197</v>
+        <v>11.6747055053711</v>
       </c>
       <c r="H477" t="n">
         <v>345190</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554637908936</v>
+        <v>9.45554733276367</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14289,7 +14289,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816593170166</v>
+        <v>9.65816497802734</v>
       </c>
       <c r="H480" t="n">
         <v>142514</v>
@@ -14318,7 +14318,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711185455322</v>
+        <v>9.68711090087891</v>
       </c>
       <c r="H481" t="n">
         <v>127849</v>
@@ -14405,7 +14405,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625068664551</v>
+        <v>10.3625078201294</v>
       </c>
       <c r="H484" t="n">
         <v>99264</v>
@@ -14521,7 +14521,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764970779419</v>
+        <v>11.0764980316162</v>
       </c>
       <c r="H488" t="n">
         <v>85880</v>
@@ -14550,7 +14550,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.7195024490356</v>
+        <v>10.71950340271</v>
       </c>
       <c r="H489" t="n">
         <v>62047</v>
@@ -14782,7 +14782,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7387990951538</v>
+        <v>10.7388000488281</v>
       </c>
       <c r="H497" t="n">
         <v>62706</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078971862793</v>
+        <v>10.7078981399536</v>
       </c>
       <c r="H500" t="n">
         <v>97230</v>
@@ -14898,7 +14898,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G501" t="n">
-        <v>10.4732046127319</v>
+        <v>10.4732036590576</v>
       </c>
       <c r="H501" t="n">
         <v>197020</v>
@@ -14927,7 +14927,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H502" t="n">
         <v>89414</v>
@@ -14956,7 +14956,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189531326294</v>
+        <v>10.2189521789551</v>
       </c>
       <c r="H503" t="n">
         <v>87325</v>
@@ -15043,7 +15043,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4536457061768</v>
+        <v>10.4536466598511</v>
       </c>
       <c r="H506" t="n">
         <v>53759</v>
@@ -15072,7 +15072,7 @@
         <v>10.75</v>
       </c>
       <c r="G507" t="n">
-        <v>10.5123205184937</v>
+        <v>10.5123195648193</v>
       </c>
       <c r="H507" t="n">
         <v>171168</v>
@@ -15101,7 +15101,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025415420532</v>
+        <v>10.5025405883789</v>
       </c>
       <c r="H508" t="n">
         <v>53290</v>
@@ -15130,7 +15130,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G509" t="n">
-        <v>10.4047517776489</v>
+        <v>10.4047527313232</v>
       </c>
       <c r="H509" t="n">
         <v>85761</v>
@@ -15188,7 +15188,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G511" t="n">
-        <v>10.580771446228</v>
+        <v>10.5807723999023</v>
       </c>
       <c r="H511" t="n">
         <v>29173</v>
@@ -15246,7 +15246,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H513" t="n">
         <v>68123</v>
@@ -15565,7 +15565,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>10.9328126907349</v>
+        <v>10.9328136444092</v>
       </c>
       <c r="H524" t="n">
         <v>31611</v>
@@ -15623,7 +15623,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.9523706436157</v>
+        <v>10.9523696899414</v>
       </c>
       <c r="H526" t="n">
         <v>85137</v>
@@ -15681,7 +15681,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H528" t="n">
         <v>31481</v>
@@ -15797,7 +15797,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H532" t="n">
         <v>61309</v>
@@ -15855,7 +15855,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634256362915</v>
+        <v>10.4634246826172</v>
       </c>
       <c r="H534" t="n">
         <v>20572</v>
@@ -15884,7 +15884,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069629669189</v>
+        <v>10.3069639205933</v>
       </c>
       <c r="H535" t="n">
         <v>59740</v>
@@ -15942,7 +15942,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G537" t="n">
-        <v>9.81801891326904</v>
+        <v>9.81801795959473</v>
       </c>
       <c r="H537" t="n">
         <v>66947</v>
@@ -16000,7 +16000,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H539" t="n">
         <v>38633</v>
@@ -16145,7 +16145,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>9.64199829101562</v>
+        <v>9.64199733734131</v>
       </c>
       <c r="H544" t="n">
         <v>45893</v>
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H545" t="n">
         <v>37787</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H546" t="n">
         <v>15589</v>
@@ -16232,7 +16232,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509357452393</v>
+        <v>9.50509262084961</v>
       </c>
       <c r="H547" t="n">
         <v>11946</v>
@@ -16261,7 +16261,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619869232178</v>
+        <v>9.45619964599609</v>
       </c>
       <c r="H548" t="n">
         <v>15955</v>
@@ -16290,7 +16290,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H549" t="n">
         <v>23576</v>
@@ -16319,7 +16319,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H550" t="n">
         <v>18189</v>
@@ -16377,7 +16377,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H552" t="n">
         <v>45912</v>
@@ -16638,7 +16638,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>9.65177726745605</v>
+        <v>9.65177631378174</v>
       </c>
       <c r="H561" t="n">
         <v>47843</v>
@@ -16667,7 +16667,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H562" t="n">
         <v>31267</v>
@@ -16812,7 +16812,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H567" t="n">
         <v>124458</v>
@@ -16841,7 +16841,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G568" t="n">
-        <v>9.72022914886475</v>
+        <v>9.72022819519043</v>
       </c>
       <c r="H568" t="n">
         <v>102747</v>
@@ -16957,7 +16957,7 @@
         <v>10.5</v>
       </c>
       <c r="G572" t="n">
-        <v>10.2678470611572</v>
+        <v>10.2678480148315</v>
       </c>
       <c r="H572" t="n">
         <v>116632</v>
@@ -16986,7 +16986,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H573" t="n">
         <v>121005</v>
@@ -17015,7 +17015,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H574" t="n">
         <v>114848</v>
@@ -17044,7 +17044,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H575" t="n">
         <v>94106</v>
@@ -17073,7 +17073,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G576" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H576" t="n">
         <v>88350</v>
@@ -17160,7 +17160,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>9.2215051651001</v>
+        <v>9.22150421142578</v>
       </c>
       <c r="H579" t="n">
         <v>84921</v>
@@ -17247,7 +17247,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12371635437012</v>
+        <v>9.1237154006958</v>
       </c>
       <c r="H582" t="n">
         <v>83347</v>
@@ -17276,7 +17276,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>8.95747375488281</v>
+        <v>8.95747470855713</v>
       </c>
       <c r="H583" t="n">
         <v>20537</v>
@@ -17305,7 +17305,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H584" t="n">
         <v>44575</v>
@@ -17363,7 +17363,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H586" t="n">
         <v>19894</v>
@@ -17508,7 +17508,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.99659061431885</v>
+        <v>8.99658966064453</v>
       </c>
       <c r="H591" t="n">
         <v>38459</v>
@@ -17537,7 +17537,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>8.89880180358887</v>
+        <v>8.89880084991455</v>
       </c>
       <c r="H592" t="n">
         <v>73245</v>
@@ -17566,7 +17566,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H593" t="n">
         <v>172995</v>
@@ -17653,7 +17653,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H596" t="n">
         <v>110779</v>
@@ -17682,7 +17682,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H597" t="n">
         <v>168521</v>
@@ -17769,7 +17769,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H600" t="n">
         <v>116918</v>
@@ -17798,7 +17798,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G601" t="n">
-        <v>9.72022914886475</v>
+        <v>9.72022819519043</v>
       </c>
       <c r="H601" t="n">
         <v>24832</v>
@@ -17885,7 +17885,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H604" t="n">
         <v>44561</v>
@@ -18030,7 +18030,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81801891326904</v>
+        <v>9.81801795959473</v>
       </c>
       <c r="H609" t="n">
         <v>8881</v>
@@ -18059,7 +18059,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H610" t="n">
         <v>26954</v>
@@ -18146,7 +18146,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G613" t="n">
-        <v>9.34862995147705</v>
+        <v>9.34863090515137</v>
       </c>
       <c r="H613" t="n">
         <v>29288</v>
@@ -18204,7 +18204,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>9.37796783447266</v>
+        <v>9.37796688079834</v>
       </c>
       <c r="H615" t="n">
         <v>38849</v>
@@ -18291,7 +18291,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H618" t="n">
         <v>16473</v>
@@ -18436,7 +18436,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G623" t="n">
-        <v>10.0918273925781</v>
+        <v>10.0918264389038</v>
       </c>
       <c r="H623" t="n">
         <v>113503</v>
@@ -18610,7 +18610,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.5735445022583</v>
+        <v>9.57354640960693</v>
       </c>
       <c r="H629" t="n">
         <v>59629</v>
@@ -18668,7 +18668,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H631" t="n">
         <v>25208</v>
@@ -18726,7 +18726,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>9.13349437713623</v>
+        <v>9.13349533081055</v>
       </c>
       <c r="H633" t="n">
         <v>33022</v>
@@ -18784,7 +18784,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G635" t="n">
-        <v>8.89880180358887</v>
+        <v>8.89880084991455</v>
       </c>
       <c r="H635" t="n">
         <v>46972</v>
@@ -18900,7 +18900,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>8.99659061431885</v>
+        <v>8.99658966064453</v>
       </c>
       <c r="H639" t="n">
         <v>10481</v>
@@ -19045,7 +19045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>9.4366397857666</v>
+        <v>9.43664073944092</v>
       </c>
       <c r="H644" t="n">
         <v>5673</v>
@@ -19132,7 +19132,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G647" t="n">
-        <v>9.64199829101562</v>
+        <v>9.64199733734131</v>
       </c>
       <c r="H647" t="n">
         <v>12149</v>
@@ -19190,7 +19190,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52464962005615</v>
+        <v>9.52465057373047</v>
       </c>
       <c r="H649" t="n">
         <v>25021</v>
@@ -19248,7 +19248,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H651" t="n">
         <v>135104</v>
@@ -19364,7 +19364,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G655" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H655" t="n">
         <v>14617</v>
@@ -19393,7 +19393,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G656" t="n">
-        <v>9.2215051651001</v>
+        <v>9.22150421142578</v>
       </c>
       <c r="H656" t="n">
         <v>5166</v>
@@ -19451,7 +19451,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437942504883</v>
+        <v>9.09437847137451</v>
       </c>
       <c r="H658" t="n">
         <v>4851</v>
@@ -19654,7 +19654,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G665" t="n">
-        <v>9.39752388000488</v>
+        <v>9.3975248336792</v>
       </c>
       <c r="H665" t="n">
         <v>4386</v>
@@ -19770,7 +19770,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H669" t="n">
         <v>10937</v>
@@ -19857,7 +19857,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>9.65177726745605</v>
+        <v>9.65177631378174</v>
       </c>
       <c r="H672" t="n">
         <v>48863</v>
@@ -19886,7 +19886,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G673" t="n">
-        <v>9.76912403106689</v>
+        <v>9.76912307739258</v>
       </c>
       <c r="H673" t="n">
         <v>49111</v>
@@ -19915,7 +19915,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H674" t="n">
         <v>18840</v>
@@ -19944,7 +19944,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H675" t="n">
         <v>37373</v>
@@ -20031,7 +20031,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H678" t="n">
         <v>29641</v>
@@ -20060,7 +20060,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.70067119598389</v>
+        <v>9.7006721496582</v>
       </c>
       <c r="H679" t="n">
         <v>14909</v>
@@ -20089,7 +20089,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G680" t="n">
-        <v>9.60288238525391</v>
+        <v>9.60288143157959</v>
       </c>
       <c r="H680" t="n">
         <v>7811</v>
@@ -20118,7 +20118,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H681" t="n">
         <v>7805</v>
@@ -20234,7 +20234,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G685" t="n">
-        <v>9.72022914886475</v>
+        <v>9.72022819519043</v>
       </c>
       <c r="H685" t="n">
         <v>86835</v>
@@ -20263,7 +20263,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>9.76912403106689</v>
+        <v>9.76912307739258</v>
       </c>
       <c r="H686" t="n">
         <v>19172</v>
@@ -20292,7 +20292,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H687" t="n">
         <v>13215</v>
@@ -20321,7 +20321,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G688" t="n">
-        <v>9.6713342666626</v>
+        <v>9.67133522033691</v>
       </c>
       <c r="H688" t="n">
         <v>38879</v>
@@ -20379,7 +20379,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575664520264</v>
+        <v>9.47575569152832</v>
       </c>
       <c r="H690" t="n">
         <v>39319</v>
@@ -20495,7 +20495,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H694" t="n">
         <v>32283</v>
@@ -20524,7 +20524,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H695" t="n">
         <v>15119</v>
@@ -20553,7 +20553,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H696" t="n">
         <v>14440</v>
@@ -20669,7 +20669,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H700" t="n">
         <v>27899</v>
@@ -20959,7 +20959,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H710" t="n">
         <v>140241</v>
@@ -20988,7 +20988,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G711" t="n">
-        <v>8.34140300750732</v>
+        <v>8.34140396118164</v>
       </c>
       <c r="H711" t="n">
         <v>50079</v>
@@ -21017,7 +21017,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560436248779</v>
+        <v>8.15560531616211</v>
       </c>
       <c r="H712" t="n">
         <v>38461</v>
@@ -21075,7 +21075,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G714" t="n">
-        <v>8.70322227478027</v>
+        <v>8.70322322845459</v>
       </c>
       <c r="H714" t="n">
         <v>94133</v>
@@ -21104,7 +21104,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H715" t="n">
         <v>12213</v>
@@ -21133,7 +21133,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G716" t="n">
-        <v>8.34140300750732</v>
+        <v>8.34140396118164</v>
       </c>
       <c r="H716" t="n">
         <v>45582</v>
@@ -21191,7 +21191,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626934051514</v>
+        <v>8.12626838684082</v>
       </c>
       <c r="H718" t="n">
         <v>75942</v>
@@ -21220,7 +21220,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G719" t="n">
-        <v>8.22405624389648</v>
+        <v>8.2240571975708</v>
       </c>
       <c r="H719" t="n">
         <v>28804</v>
@@ -21249,7 +21249,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742458343506</v>
+        <v>8.51742362976074</v>
       </c>
       <c r="H720" t="n">
         <v>40610</v>
@@ -21336,7 +21336,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.6347713470459</v>
+        <v>8.63477039337158</v>
       </c>
       <c r="H723" t="n">
         <v>20170</v>
@@ -21365,7 +21365,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924289703369</v>
+        <v>8.87924385070801</v>
       </c>
       <c r="H724" t="n">
         <v>16711</v>
@@ -21423,7 +21423,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902187347412</v>
+        <v>8.88902282714844</v>
       </c>
       <c r="H726" t="n">
         <v>35047</v>
@@ -21452,7 +21452,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G727" t="n">
-        <v>8.7716760635376</v>
+        <v>8.77167510986328</v>
       </c>
       <c r="H727" t="n">
         <v>143037</v>
@@ -21481,7 +21481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G728" t="n">
-        <v>8.89880180358887</v>
+        <v>8.89880084991455</v>
       </c>
       <c r="H728" t="n">
         <v>73666</v>
@@ -21539,7 +21539,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H730" t="n">
         <v>9948</v>
@@ -21742,7 +21742,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262889862061</v>
+        <v>7.40262937545776</v>
       </c>
       <c r="H737" t="n">
         <v>30955</v>
@@ -21800,7 +21800,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>6.8647894859314</v>
+        <v>6.86478900909424</v>
       </c>
       <c r="H739" t="n">
         <v>73987</v>
@@ -21858,7 +21858,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>7.30484008789062</v>
+        <v>7.30483961105347</v>
       </c>
       <c r="H741" t="n">
         <v>13402</v>
@@ -21945,7 +21945,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.15815687179565</v>
+        <v>7.1581563949585</v>
       </c>
       <c r="H744" t="n">
         <v>18982</v>
@@ -21974,7 +21974,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G745" t="n">
-        <v>6.83545207977295</v>
+        <v>6.83545255661011</v>
       </c>
       <c r="H745" t="n">
         <v>110100</v>
@@ -22032,7 +22032,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>5.67176389694214</v>
+        <v>5.67176342010498</v>
       </c>
       <c r="H747" t="n">
         <v>105173</v>
@@ -22061,7 +22061,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G748" t="n">
-        <v>5.57397413253784</v>
+        <v>5.573974609375</v>
       </c>
       <c r="H748" t="n">
         <v>167124</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10225009918213</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22235,7 +22235,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>4.67431497573853</v>
+        <v>4.67431545257568</v>
       </c>
       <c r="H754" t="n">
         <v>139728</v>
@@ -22264,7 +22264,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>4.44940090179443</v>
+        <v>4.44940042495728</v>
       </c>
       <c r="H755" t="n">
         <v>78287</v>
@@ -22293,7 +22293,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738567352295</v>
+        <v>4.31738519668579</v>
       </c>
       <c r="H756" t="n">
         <v>103537</v>
@@ -22322,7 +22322,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357624053955</v>
+        <v>4.04357671737671</v>
       </c>
       <c r="H757" t="n">
         <v>116412</v>
@@ -22351,7 +22351,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>3.90178227424622</v>
+        <v>3.90178203582764</v>
       </c>
       <c r="H758" t="n">
         <v>114123</v>
@@ -22380,7 +22380,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>4.29782772064209</v>
+        <v>4.29782819747925</v>
       </c>
       <c r="H759" t="n">
         <v>196124</v>
@@ -22438,7 +22438,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156077384949</v>
+        <v>3.91156101226807</v>
       </c>
       <c r="H761" t="n">
         <v>208056</v>
@@ -22496,7 +22496,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669706344604</v>
+        <v>4.12669658660889</v>
       </c>
       <c r="H763" t="n">
         <v>41597</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10225009918213</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22583,7 +22583,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>4.35161113739014</v>
+        <v>4.35161161422729</v>
       </c>
       <c r="H766" t="n">
         <v>92230</v>
@@ -22641,7 +22641,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G768" t="n">
-        <v>4.8356671333313</v>
+        <v>4.83566761016846</v>
       </c>
       <c r="H768" t="n">
         <v>165631</v>
@@ -22670,7 +22670,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502912521362</v>
+        <v>5.08502960205078</v>
       </c>
       <c r="H769" t="n">
         <v>224657</v>
@@ -22902,7 +22902,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>5.47618532180786</v>
+        <v>5.4761848449707</v>
       </c>
       <c r="H777" t="n">
         <v>121084</v>
@@ -23134,7 +23134,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773296356201</v>
+        <v>5.40773344039917</v>
       </c>
       <c r="H785" t="n">
         <v>58953</v>
@@ -23163,7 +23163,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928060531616</v>
+        <v>5.33928108215332</v>
       </c>
       <c r="H786" t="n">
         <v>28269</v>
@@ -23250,7 +23250,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H789" t="n">
         <v>33919</v>
@@ -23279,7 +23279,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016565322876</v>
+        <v>5.30016469955444</v>
       </c>
       <c r="H790" t="n">
         <v>36651</v>
@@ -23337,7 +23337,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G792" t="n">
-        <v>5.20237588882446</v>
+        <v>5.20237636566162</v>
       </c>
       <c r="H792" t="n">
         <v>22334</v>
@@ -23395,7 +23395,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G794" t="n">
-        <v>5.20237588882446</v>
+        <v>5.20237636566162</v>
       </c>
       <c r="H794" t="n">
         <v>45527</v>
@@ -23424,7 +23424,7 @@
         <v>5.25</v>
       </c>
       <c r="G795" t="n">
-        <v>5.13392353057861</v>
+        <v>5.13392400741577</v>
       </c>
       <c r="H795" t="n">
         <v>16038</v>
@@ -23453,7 +23453,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>5.22193384170532</v>
+        <v>5.22193431854248</v>
       </c>
       <c r="H796" t="n">
         <v>43106</v>
@@ -23511,7 +23511,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171281814575</v>
+        <v>5.23171234130859</v>
       </c>
       <c r="H798" t="n">
         <v>3968</v>
@@ -23540,7 +23540,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H799" t="n">
         <v>12491</v>
@@ -23627,7 +23627,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G802" t="n">
-        <v>5.20237588882446</v>
+        <v>5.20237636566162</v>
       </c>
       <c r="H802" t="n">
         <v>6956</v>
@@ -23685,7 +23685,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215486526489</v>
+        <v>5.21215534210205</v>
       </c>
       <c r="H804" t="n">
         <v>58954</v>
@@ -23714,7 +23714,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H805" t="n">
         <v>18129</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166221618652</v>
+        <v>4.79166269302368</v>
       </c>
       <c r="H807" t="n">
         <v>76245</v>
@@ -23946,7 +23946,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>5.04591369628906</v>
+        <v>5.0459132194519</v>
       </c>
       <c r="H813" t="n">
         <v>4389</v>
@@ -24120,7 +24120,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220594406128</v>
+        <v>5.65220642089844</v>
       </c>
       <c r="H819" t="n">
         <v>97422</v>
@@ -24149,7 +24149,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>5.47618532180786</v>
+        <v>5.4761848449707</v>
       </c>
       <c r="H820" t="n">
         <v>62956</v>
@@ -24178,7 +24178,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441665649414</v>
+        <v>5.55441617965698</v>
       </c>
       <c r="H821" t="n">
         <v>85848</v>
@@ -24236,7 +24236,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H823" t="n">
         <v>49574</v>
@@ -24468,7 +24468,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G831" t="n">
-        <v>6.44429636001587</v>
+        <v>6.44429683685303</v>
       </c>
       <c r="H831" t="n">
         <v>252834</v>
@@ -24526,7 +24526,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004487991333</v>
+        <v>6.19004535675049</v>
       </c>
       <c r="H833" t="n">
         <v>244592</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402521133423</v>
+        <v>6.01402473449707</v>
       </c>
       <c r="H834" t="n">
         <v>41322</v>
@@ -24613,7 +24613,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314016342163</v>
+        <v>6.05314064025879</v>
       </c>
       <c r="H836" t="n">
         <v>52635</v>
@@ -24642,7 +24642,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672857284546</v>
+        <v>6.33672904968262</v>
       </c>
       <c r="H837" t="n">
         <v>71930</v>
@@ -24729,7 +24729,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G840" t="n">
-        <v>6.73766374588013</v>
+        <v>6.73766326904297</v>
       </c>
       <c r="H840" t="n">
         <v>81839</v>
@@ -25048,7 +25048,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.14115047454834</v>
+        <v>6.14115142822266</v>
       </c>
       <c r="H851" t="n">
         <v>14069</v>
@@ -25077,7 +25077,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H852" t="n">
         <v>26701</v>
@@ -25106,7 +25106,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.00424575805664</v>
+        <v>6.0042462348938</v>
       </c>
       <c r="H853" t="n">
         <v>11658</v>
@@ -25222,7 +25222,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955223083496</v>
+        <v>5.76955270767212</v>
       </c>
       <c r="H857" t="n">
         <v>16583</v>
@@ -25251,7 +25251,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977373123169</v>
+        <v>5.75977325439453</v>
       </c>
       <c r="H858" t="n">
         <v>12990</v>
@@ -25367,7 +25367,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>5.60331106185913</v>
+        <v>5.60331058502197</v>
       </c>
       <c r="H862" t="n">
         <v>22714</v>
@@ -25454,7 +25454,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021577835083</v>
+        <v>5.74021530151367</v>
       </c>
       <c r="H865" t="n">
         <v>27718</v>
@@ -25512,7 +25512,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>5.67176389694214</v>
+        <v>5.67176342010498</v>
       </c>
       <c r="H867" t="n">
         <v>13457</v>
@@ -25541,7 +25541,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G868" t="n">
-        <v>5.57397413253784</v>
+        <v>5.573974609375</v>
       </c>
       <c r="H868" t="n">
         <v>10349</v>
@@ -25599,7 +25599,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H870" t="n">
         <v>22149</v>
@@ -25744,7 +25744,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H875" t="n">
         <v>10415</v>
@@ -25947,7 +25947,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H882" t="n">
         <v>57113</v>
@@ -25976,7 +25976,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065782546997</v>
+        <v>5.72065830230713</v>
       </c>
       <c r="H883" t="n">
         <v>26982</v>
@@ -26034,7 +26034,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H885" t="n">
         <v>23779</v>
@@ -26092,7 +26092,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>6.65943241119385</v>
+        <v>6.65943193435669</v>
       </c>
       <c r="H887" t="n">
         <v>78414</v>
@@ -26121,7 +26121,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>6.44429636001587</v>
+        <v>6.44429683685303</v>
       </c>
       <c r="H888" t="n">
         <v>92730</v>
@@ -26208,7 +26208,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987445831299</v>
+        <v>6.63987493515015</v>
       </c>
       <c r="H891" t="n">
         <v>52119</v>
@@ -26266,7 +26266,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700019836426</v>
+        <v>6.76700067520142</v>
       </c>
       <c r="H893" t="n">
         <v>47611</v>
@@ -26440,7 +26440,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489116668701</v>
+        <v>7.74489068984985</v>
       </c>
       <c r="H899" t="n">
         <v>112735</v>
@@ -26498,7 +26498,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>7.62754392623901</v>
+        <v>7.62754440307617</v>
       </c>
       <c r="H901" t="n">
         <v>13903</v>
@@ -26527,7 +26527,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G902" t="n">
-        <v>7.62754392623901</v>
+        <v>7.62754440307617</v>
       </c>
       <c r="H902" t="n">
         <v>45564</v>
@@ -26556,7 +26556,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75466918945312</v>
+        <v>7.75466966629028</v>
       </c>
       <c r="H903" t="n">
         <v>44412</v>
@@ -26643,7 +26643,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842849731445</v>
+        <v>7.58842802047729</v>
       </c>
       <c r="H906" t="n">
         <v>22167</v>
@@ -26672,7 +26672,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>7.39285039901733</v>
+        <v>7.39284992218018</v>
       </c>
       <c r="H907" t="n">
         <v>26842</v>
@@ -26701,7 +26701,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G908" t="n">
-        <v>7.64710187911987</v>
+        <v>7.64710140228271</v>
       </c>
       <c r="H908" t="n">
         <v>26314</v>
@@ -26730,7 +26730,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>7.41240835189819</v>
+        <v>7.41240787506104</v>
       </c>
       <c r="H909" t="n">
         <v>50527</v>
@@ -26788,7 +26788,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147270202637</v>
+        <v>7.01147317886353</v>
       </c>
       <c r="H911" t="n">
         <v>49184</v>
@@ -26817,7 +26817,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572418212891</v>
+        <v>7.26572465896606</v>
       </c>
       <c r="H912" t="n">
         <v>36837</v>
@@ -26875,7 +26875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H914" t="n">
         <v>40423</v>
@@ -26933,7 +26933,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G916" t="n">
-        <v>6.85501050949097</v>
+        <v>6.85501098632812</v>
       </c>
       <c r="H916" t="n">
         <v>242774</v>
@@ -26991,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G918" t="n">
-        <v>6.8452320098877</v>
+        <v>6.84523153305054</v>
       </c>
       <c r="H918" t="n">
         <v>53696</v>
@@ -27165,7 +27165,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H924" t="n">
         <v>41919</v>
@@ -27252,7 +27252,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191522598267</v>
+        <v>6.99191570281982</v>
       </c>
       <c r="H927" t="n">
         <v>21117</v>
@@ -27339,7 +27339,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218685150146</v>
+        <v>7.42218732833862</v>
       </c>
       <c r="H930" t="n">
         <v>419711</v>
@@ -27368,7 +27368,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G931" t="n">
-        <v>7.24616622924805</v>
+        <v>7.24616670608521</v>
       </c>
       <c r="H931" t="n">
         <v>52841</v>
@@ -27600,7 +27600,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312154769897</v>
+        <v>7.82312202453613</v>
       </c>
       <c r="H939" t="n">
         <v>72321</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>8.03825855255127</v>
+        <v>8.03825759887695</v>
       </c>
       <c r="H940" t="n">
         <v>95905</v>
@@ -27687,7 +27687,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H942" t="n">
         <v>93859</v>
@@ -27745,7 +27745,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H944" t="n">
         <v>119944</v>
@@ -27832,7 +27832,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G947" t="n">
-        <v>9.4366397857666</v>
+        <v>9.43664073944092</v>
       </c>
       <c r="H947" t="n">
         <v>81693</v>
@@ -28035,7 +28035,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G954" t="n">
-        <v>8.81079196929932</v>
+        <v>8.810791015625</v>
       </c>
       <c r="H954" t="n">
         <v>75369</v>
@@ -28064,7 +28064,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>8.59565544128418</v>
+        <v>8.5956563949585</v>
       </c>
       <c r="H955" t="n">
         <v>181604</v>
@@ -28093,7 +28093,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897174835205</v>
+        <v>8.44897270202637</v>
       </c>
       <c r="H956" t="n">
         <v>40968</v>
@@ -28151,7 +28151,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37074089050293</v>
+        <v>8.37073993682861</v>
       </c>
       <c r="H958" t="n">
         <v>44957</v>
@@ -28209,7 +28209,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>8.22405624389648</v>
+        <v>8.2240571975708</v>
       </c>
       <c r="H960" t="n">
         <v>34300</v>
@@ -28267,7 +28267,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339412689209</v>
+        <v>8.25339317321777</v>
       </c>
       <c r="H962" t="n">
         <v>76522</v>
@@ -28354,7 +28354,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G965" t="n">
-        <v>8.70322227478027</v>
+        <v>8.70322322845459</v>
       </c>
       <c r="H965" t="n">
         <v>55469</v>
@@ -28383,7 +28383,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>8.45874977111816</v>
+        <v>8.45875072479248</v>
       </c>
       <c r="H966" t="n">
         <v>67238</v>
@@ -28412,7 +28412,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20450019836426</v>
+        <v>8.20449924468994</v>
       </c>
       <c r="H967" t="n">
         <v>42116</v>
@@ -28441,7 +28441,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H968" t="n">
         <v>21079</v>
@@ -28528,7 +28528,7 @@
         <v>8.25</v>
       </c>
       <c r="G971" t="n">
-        <v>8.06759548187256</v>
+        <v>8.06759452819824</v>
       </c>
       <c r="H971" t="n">
         <v>26338</v>
@@ -28557,7 +28557,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G972" t="n">
-        <v>8.17516136169434</v>
+        <v>8.17516231536865</v>
       </c>
       <c r="H972" t="n">
         <v>14608</v>
@@ -28586,7 +28586,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482051849365</v>
+        <v>9.07482147216797</v>
       </c>
       <c r="H973" t="n">
         <v>227616</v>
@@ -28615,7 +28615,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H974" t="n">
         <v>250262</v>
@@ -28644,7 +28644,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.4953145980835</v>
+        <v>9.49531364440918</v>
       </c>
       <c r="H975" t="n">
         <v>336362</v>
@@ -28847,7 +28847,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804315567017</v>
+        <v>11.4804306030273</v>
       </c>
       <c r="H982" t="n">
         <v>419644</v>
@@ -29108,7 +29108,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926742553711</v>
+        <v>13.5926733016968</v>
       </c>
       <c r="H991" t="n">
         <v>195792</v>
@@ -29224,7 +29224,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8639307022095</v>
+        <v>14.8639316558838</v>
       </c>
       <c r="H995" t="n">
         <v>248550</v>
@@ -29369,7 +29369,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7100210189819</v>
+        <v>13.7100219726562</v>
       </c>
       <c r="H1000" t="n">
         <v>186196</v>
@@ -29427,7 +29427,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.3188648223877</v>
+        <v>13.3188638687134</v>
       </c>
       <c r="H1002" t="n">
         <v>70482</v>
@@ -29456,7 +29456,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.0059404373169</v>
+        <v>13.0059413909912</v>
       </c>
       <c r="H1003" t="n">
         <v>82659</v>
@@ -29630,7 +29630,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.2823009490967</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1009" t="n">
         <v>78089</v>
@@ -29688,7 +29688,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867233276367</v>
+        <v>12.0867223739624</v>
       </c>
       <c r="H1011" t="n">
         <v>47356</v>
@@ -29804,7 +29804,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1015" t="n">
-        <v>12.2040700912476</v>
+        <v>12.2040691375732</v>
       </c>
       <c r="H1015" t="n">
         <v>54788</v>
@@ -29949,7 +29949,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.5365524291992</v>
+        <v>12.5365533828735</v>
       </c>
       <c r="H1020" t="n">
         <v>66770</v>
@@ -30123,7 +30123,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.5952262878418</v>
+        <v>12.5952253341675</v>
       </c>
       <c r="H1026" t="n">
         <v>82690</v>
@@ -30152,7 +30152,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583215713501</v>
+        <v>12.4583206176758</v>
       </c>
       <c r="H1027" t="n">
         <v>145125</v>
@@ -30210,7 +30210,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>12.2040700912476</v>
+        <v>12.2040691375732</v>
       </c>
       <c r="H1029" t="n">
         <v>174418</v>
@@ -30239,7 +30239,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.2823009490967</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1030" t="n">
         <v>99601</v>
@@ -30268,7 +30268,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.2823009490967</v>
+        <v>12.2823028564453</v>
       </c>
       <c r="H1031" t="n">
         <v>57835</v>
@@ -30326,7 +30326,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.715124130249</v>
+        <v>11.7151250839233</v>
       </c>
       <c r="H1033" t="n">
         <v>119232</v>
@@ -30471,7 +30471,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1038" t="n">
-        <v>12.2040700912476</v>
+        <v>12.2040691375732</v>
       </c>
       <c r="H1038" t="n">
         <v>111924</v>
@@ -30500,7 +30500,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734571456909</v>
+        <v>12.6734580993652</v>
       </c>
       <c r="H1039" t="n">
         <v>102261</v>
@@ -30616,7 +30616,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1043" t="n">
         <v>36180</v>
@@ -30674,7 +30674,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.4192056655884</v>
+        <v>12.4192066192627</v>
       </c>
       <c r="H1045" t="n">
         <v>16548</v>
@@ -30703,7 +30703,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1046" t="n">
         <v>29868</v>
@@ -30732,7 +30732,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409757614136</v>
+        <v>12.3409738540649</v>
       </c>
       <c r="H1047" t="n">
         <v>46643</v>
@@ -30848,7 +30848,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.279748916626</v>
+        <v>13.2797498703003</v>
       </c>
       <c r="H1051" t="n">
         <v>108427</v>
@@ -30993,7 +30993,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H1056" t="n">
         <v>93893</v>
@@ -31109,7 +31109,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.209174156189</v>
+        <v>10.2091732025146</v>
       </c>
       <c r="H1060" t="n">
         <v>129001</v>
@@ -31167,7 +31167,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025415420532</v>
+        <v>10.5025405883789</v>
       </c>
       <c r="H1062" t="n">
         <v>172678</v>
@@ -31341,7 +31341,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206703186035</v>
+        <v>8.31206798553467</v>
       </c>
       <c r="H1068" t="n">
         <v>167682</v>
@@ -31370,7 +31370,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H1069" t="n">
         <v>180623</v>
@@ -31399,7 +31399,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543441772461</v>
+        <v>8.60543346405029</v>
       </c>
       <c r="H1070" t="n">
         <v>27481</v>
@@ -31428,7 +31428,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1071" t="n">
-        <v>8.70322227478027</v>
+        <v>8.70322322845459</v>
       </c>
       <c r="H1071" t="n">
         <v>29010</v>
@@ -31486,7 +31486,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.81079196929932</v>
+        <v>8.810791015625</v>
       </c>
       <c r="H1073" t="n">
         <v>41885</v>
@@ -31515,7 +31515,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570652008057</v>
+        <v>9.03570556640625</v>
       </c>
       <c r="H1074" t="n">
         <v>47397</v>
@@ -31602,7 +31602,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H1077" t="n">
         <v>64803</v>
@@ -31689,7 +31689,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.4047517776489</v>
+        <v>10.4047527313232</v>
       </c>
       <c r="H1080" t="n">
         <v>36974</v>
@@ -31718,7 +31718,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H1081" t="n">
         <v>25731</v>
@@ -31747,7 +31747,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0918273925781</v>
+        <v>10.0918264389038</v>
       </c>
       <c r="H1082" t="n">
         <v>25318</v>
@@ -31776,7 +31776,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003313064575</v>
+        <v>10.6003293991089</v>
       </c>
       <c r="H1083" t="n">
         <v>44357</v>
@@ -31805,7 +31805,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.4438676834106</v>
+        <v>10.443868637085</v>
       </c>
       <c r="H1084" t="n">
         <v>61024</v>
@@ -31834,7 +31834,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.9523706436157</v>
+        <v>10.9523696899414</v>
       </c>
       <c r="H1085" t="n">
         <v>43194</v>
@@ -31950,7 +31950,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.181960105896</v>
+        <v>13.1819591522217</v>
       </c>
       <c r="H1089" t="n">
         <v>178518</v>
@@ -31979,7 +31979,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>13.1037282943726</v>
+        <v>13.1037292480469</v>
       </c>
       <c r="H1090" t="n">
         <v>153541</v>
@@ -32037,7 +32037,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.1428442001343</v>
+        <v>13.1428451538086</v>
       </c>
       <c r="H1092" t="n">
         <v>90633</v>
@@ -32269,7 +32269,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1100" t="n">
-        <v>14.1402940750122</v>
+        <v>14.1402931213379</v>
       </c>
       <c r="H1100" t="n">
         <v>81068</v>
@@ -32298,7 +32298,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771978378296</v>
+        <v>14.2771987915039</v>
       </c>
       <c r="H1101" t="n">
         <v>57479</v>
@@ -32414,7 +32414,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030466079712</v>
+        <v>14.9030475616455</v>
       </c>
       <c r="H1105" t="n">
         <v>135713</v>
@@ -32443,7 +32443,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.7074699401855</v>
+        <v>14.7074689865112</v>
       </c>
       <c r="H1106" t="n">
         <v>120242</v>
@@ -32530,7 +32530,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181831359863</v>
+        <v>15.1181840896606</v>
       </c>
       <c r="H1109" t="n">
         <v>121418</v>
@@ -32559,7 +32559,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396095275879</v>
+        <v>15.9396104812622</v>
       </c>
       <c r="H1110" t="n">
         <v>152433</v>
@@ -32617,7 +32617,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1112" t="n">
-        <v>17.6802539825439</v>
+        <v>17.6802558898926</v>
       </c>
       <c r="H1112" t="n">
         <v>297169</v>
@@ -32675,7 +32675,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666488647461</v>
+        <v>19.1666507720947</v>
       </c>
       <c r="H1114" t="n">
         <v>462313</v>
@@ -32878,7 +32878,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981067657471</v>
+        <v>22.1981086730957</v>
       </c>
       <c r="H1121" t="n">
         <v>87185</v>
@@ -32965,7 +32965,7 @@
         <v>21.5</v>
       </c>
       <c r="G1124" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1124" t="n">
         <v>72589</v>
@@ -33139,7 +33139,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>21.1713218688965</v>
+        <v>21.1713237762451</v>
       </c>
       <c r="H1130" t="n">
         <v>60803</v>
@@ -33168,7 +33168,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558464050293</v>
+        <v>21.8558483123779</v>
       </c>
       <c r="H1131" t="n">
         <v>109080</v>
@@ -33197,7 +33197,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.660270690918</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1132" t="n">
         <v>103507</v>
@@ -33255,7 +33255,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.660270690918</v>
+        <v>21.6602687835693</v>
       </c>
       <c r="H1134" t="n">
         <v>98501</v>
@@ -33284,7 +33284,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1135" t="n">
         <v>53815</v>
@@ -33400,7 +33400,7 @@
         <v>21.5</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1139" t="n">
         <v>34560</v>
@@ -33458,7 +33458,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>20.9757461547852</v>
+        <v>20.9757480621338</v>
       </c>
       <c r="H1141" t="n">
         <v>56787</v>
@@ -33516,7 +33516,7 @@
         <v>21.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1143" t="n">
         <v>34032</v>
@@ -33545,7 +33545,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1144" t="n">
         <v>22284</v>
@@ -33603,7 +33603,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691116333008</v>
+        <v>21.2691135406494</v>
       </c>
       <c r="H1146" t="n">
         <v>32961</v>
@@ -33632,7 +33632,7 @@
         <v>21.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1147" t="n">
         <v>58527</v>
@@ -33748,7 +33748,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1151" t="n">
         <v>65290</v>
@@ -33777,7 +33777,7 @@
         <v>21</v>
       </c>
       <c r="G1152" t="n">
-        <v>20.5356941223145</v>
+        <v>20.5356960296631</v>
       </c>
       <c r="H1152" t="n">
         <v>77191</v>
@@ -33806,7 +33806,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1153" t="n">
         <v>112291</v>
@@ -33835,7 +33835,7 @@
         <v>23.75</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.2248954772949</v>
+        <v>23.2248935699463</v>
       </c>
       <c r="H1154" t="n">
         <v>149423</v>
@@ -33893,7 +33893,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0561008453369</v>
+        <v>24.0560989379883</v>
       </c>
       <c r="H1156" t="n">
         <v>205397</v>
@@ -33922,7 +33922,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538906097412</v>
+        <v>24.1538887023926</v>
       </c>
       <c r="H1157" t="n">
         <v>72151</v>
@@ -34009,7 +34009,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.322681427002</v>
+        <v>23.3226833343506</v>
       </c>
       <c r="H1160" t="n">
         <v>31857</v>
@@ -34038,7 +34038,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7848434448242</v>
+        <v>22.7848415374756</v>
       </c>
       <c r="H1161" t="n">
         <v>56547</v>
@@ -34067,7 +34067,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359466552734</v>
+        <v>22.7359504699707</v>
       </c>
       <c r="H1162" t="n">
         <v>32829</v>
@@ -34096,7 +34096,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1163" t="n">
         <v>63588</v>
@@ -34125,7 +34125,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1164" t="n">
         <v>33009</v>
@@ -34154,7 +34154,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>22.6381568908691</v>
+        <v>22.6381587982178</v>
       </c>
       <c r="H1165" t="n">
         <v>26738</v>
@@ -34241,7 +34241,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1168" t="n">
         <v>45591</v>
@@ -34299,7 +34299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1170" t="n">
         <v>119843</v>
@@ -34328,7 +34328,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.2958965301514</v>
+        <v>22.2958984375</v>
       </c>
       <c r="H1171" t="n">
         <v>50849</v>
@@ -34560,7 +34560,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1179" t="n">
         <v>25025</v>
@@ -34589,7 +34589,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1180" t="n">
         <v>34676</v>
@@ -34618,7 +34618,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1181" t="n">
         <v>48003</v>
@@ -34647,7 +34647,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.9047412872314</v>
+        <v>21.9047393798828</v>
       </c>
       <c r="H1182" t="n">
         <v>39901</v>
@@ -34676,7 +34676,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1183" t="n">
         <v>60552</v>
@@ -34705,7 +34705,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157943725586</v>
+        <v>21.4157962799072</v>
       </c>
       <c r="H1184" t="n">
         <v>21327</v>
@@ -34792,7 +34792,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1187" t="n">
         <v>68839</v>
@@ -34850,7 +34850,7 @@
         <v>21.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1189" t="n">
         <v>47664</v>
@@ -34908,7 +34908,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1191" t="n">
         <v>39920</v>
@@ -34937,7 +34937,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113739013672</v>
+        <v>21.6113758087158</v>
       </c>
       <c r="H1192" t="n">
         <v>25913</v>
@@ -34995,7 +34995,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1194" t="n">
         <v>28298</v>
@@ -35082,7 +35082,7 @@
         <v>21.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1197" t="n">
         <v>53455</v>
@@ -35169,7 +35169,7 @@
         <v>21.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1200" t="n">
         <v>137704</v>
@@ -35198,7 +35198,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>22.6381568908691</v>
+        <v>22.6381587982178</v>
       </c>
       <c r="H1201" t="n">
         <v>116966</v>
@@ -35256,7 +35256,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.2958965301514</v>
+        <v>22.2958984375</v>
       </c>
       <c r="H1203" t="n">
         <v>114554</v>
@@ -35372,7 +35372,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.926851272583</v>
+        <v>20.9268493652344</v>
       </c>
       <c r="H1207" t="n">
         <v>80989</v>
@@ -35401,7 +35401,7 @@
         <v>21.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1208" t="n">
         <v>60298</v>
@@ -35430,7 +35430,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401165008545</v>
+        <v>20.3401184082031</v>
       </c>
       <c r="H1209" t="n">
         <v>38491</v>
@@ -35575,7 +35575,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1214" t="n">
         <v>61113</v>
@@ -35633,7 +35633,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1216" t="n">
-        <v>19.4404582977295</v>
+        <v>19.4404563903809</v>
       </c>
       <c r="H1216" t="n">
         <v>49228</v>
@@ -35691,7 +35691,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.9978580474854</v>
+        <v>19.9978561401367</v>
       </c>
       <c r="H1218" t="n">
         <v>80159</v>
@@ -35749,7 +35749,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470890045166</v>
+        <v>19.1470928192139</v>
       </c>
       <c r="H1220" t="n">
         <v>78205</v>
@@ -35836,7 +35836,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.2669887542725</v>
+        <v>18.2669906616211</v>
       </c>
       <c r="H1223" t="n">
         <v>95192</v>
@@ -35981,7 +35981,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112087249756</v>
+        <v>16.3112106323242</v>
       </c>
       <c r="H1228" t="n">
         <v>66395</v>
@@ -36039,7 +36039,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329788208008</v>
+        <v>16.2329769134521</v>
       </c>
       <c r="H1230" t="n">
         <v>93368</v>
@@ -36068,7 +36068,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743049621582</v>
+        <v>16.1743068695068</v>
       </c>
       <c r="H1231" t="n">
         <v>45139</v>
@@ -36097,7 +36097,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.9174995422363</v>
+        <v>16.917501449585</v>
       </c>
       <c r="H1232" t="n">
         <v>52351</v>
@@ -36126,7 +36126,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.5824642181396</v>
+        <v>17.5824661254883</v>
       </c>
       <c r="H1233" t="n">
         <v>88571</v>
@@ -36155,7 +36155,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348491668701</v>
+        <v>17.0348472595215</v>
       </c>
       <c r="H1234" t="n">
         <v>86836</v>
@@ -36300,7 +36300,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108688354492</v>
+        <v>17.2108669281006</v>
       </c>
       <c r="H1239" t="n">
         <v>157511</v>
@@ -36358,7 +36358,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1241" t="n">
-        <v>17.054407119751</v>
+        <v>17.0544052124023</v>
       </c>
       <c r="H1241" t="n">
         <v>48546</v>
@@ -36503,7 +36503,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979434967041</v>
+        <v>16.8979454040527</v>
       </c>
       <c r="H1246" t="n">
         <v>89023</v>
@@ -36677,7 +36677,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.721923828125</v>
+        <v>16.7219219207764</v>
       </c>
       <c r="H1252" t="n">
         <v>39230</v>
@@ -36735,7 +36735,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761753082275</v>
+        <v>16.9761734008789</v>
       </c>
       <c r="H1254" t="n">
         <v>30692</v>
@@ -36764,7 +36764,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.721923828125</v>
+        <v>16.7219219207764</v>
       </c>
       <c r="H1255" t="n">
         <v>38089</v>
@@ -36851,7 +36851,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414817810059</v>
+        <v>16.7414798736572</v>
       </c>
       <c r="H1258" t="n">
         <v>87008</v>
@@ -80038,6 +80038,35 @@
         <v>5305</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>10.3199996948242</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>10.2399997711182</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>4831</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455669403076</v>
+        <v>6.71455717086792</v>
       </c>
       <c r="H3" t="n">
         <v>54991</v>
@@ -514,7 +514,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4467396736145</v>
+        <v>6.44674015045166</v>
       </c>
       <c r="H5" t="n">
         <v>108929</v>
@@ -717,7 +717,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546054840088</v>
+        <v>5.70546102523804</v>
       </c>
       <c r="H12" t="n">
         <v>113455</v>
@@ -775,7 +775,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G14" t="n">
-        <v>5.31330013275146</v>
+        <v>5.31329965591431</v>
       </c>
       <c r="H14" t="n">
         <v>81327</v>
@@ -804,7 +804,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84415197372437</v>
+        <v>5.84415149688721</v>
       </c>
       <c r="H15" t="n">
         <v>162024</v>
@@ -833,7 +833,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.74850273132324</v>
+        <v>5.7485032081604</v>
       </c>
       <c r="H16" t="n">
         <v>99565</v>
@@ -920,7 +920,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38934993743896</v>
       </c>
       <c r="H19" t="n">
         <v>89617</v>
@@ -1036,7 +1036,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414733886719</v>
+        <v>5.95414781570435</v>
       </c>
       <c r="H23" t="n">
         <v>39858</v>
@@ -1094,7 +1094,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154491424561</v>
+        <v>5.79154443740845</v>
       </c>
       <c r="H25" t="n">
         <v>42499</v>
@@ -1123,7 +1123,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.70067882537842</v>
+        <v>5.70067834854126</v>
       </c>
       <c r="H26" t="n">
         <v>83256</v>
@@ -1152,7 +1152,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>5.27504014968872</v>
+        <v>5.27504062652588</v>
       </c>
       <c r="H27" t="n">
         <v>92262</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244829177856</v>
+        <v>4.78244876861572</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1210,7 +1210,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679121017456</v>
+        <v>4.90679216384888</v>
       </c>
       <c r="H29" t="n">
         <v>118336</v>
@@ -1239,7 +1239,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62940979003906</v>
+        <v>4.62941074371338</v>
       </c>
       <c r="H30" t="n">
         <v>67579</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.83983707427979</v>
+        <v>4.83983755111694</v>
       </c>
       <c r="H33" t="n">
         <v>11060</v>
@@ -1355,7 +1355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.59546422958374</v>
+        <v>5.59546375274658</v>
       </c>
       <c r="H34" t="n">
         <v>87689</v>
@@ -1413,7 +1413,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677328109741</v>
+        <v>5.45677280426025</v>
       </c>
       <c r="H36" t="n">
         <v>102398</v>
@@ -1500,7 +1500,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.29416990280151</v>
+        <v>5.29417037963867</v>
       </c>
       <c r="H39" t="n">
         <v>54047</v>
@@ -1558,7 +1558,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>5.23678064346313</v>
+        <v>5.23678016662598</v>
       </c>
       <c r="H41" t="n">
         <v>122685</v>
@@ -1587,7 +1587,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069307327271</v>
+        <v>5.26069259643555</v>
       </c>
       <c r="H42" t="n">
         <v>79999</v>
@@ -1703,7 +1703,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028003692627</v>
+        <v>4.61028051376343</v>
       </c>
       <c r="H46" t="n">
         <v>40055</v>
@@ -1848,7 +1848,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.556715965271</v>
+        <v>4.55671644210815</v>
       </c>
       <c r="H51" t="n">
         <v>33202</v>
@@ -1964,7 +1964,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G55" t="n">
-        <v>4.4228081703186</v>
+        <v>4.42280769348145</v>
       </c>
       <c r="H55" t="n">
         <v>73311</v>
@@ -1993,7 +1993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985179901123</v>
+        <v>4.39985275268555</v>
       </c>
       <c r="H56" t="n">
         <v>6922</v>
@@ -2022,7 +2022,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40559148788452</v>
+        <v>4.40559101104736</v>
       </c>
       <c r="H57" t="n">
         <v>12685</v>
@@ -2080,7 +2080,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.2391619682312</v>
+        <v>4.23916244506836</v>
       </c>
       <c r="H59" t="n">
         <v>20035</v>
@@ -2138,7 +2138,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916933059692</v>
+        <v>4.01916885375977</v>
       </c>
       <c r="H61" t="n">
         <v>8387</v>
@@ -2167,7 +2167,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793920516968</v>
+        <v>4.39793968200684</v>
       </c>
       <c r="H62" t="n">
         <v>183307</v>
@@ -2254,7 +2254,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H65" t="n">
         <v>59895</v>
@@ -2312,7 +2312,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265055656433</v>
+        <v>3.94265079498291</v>
       </c>
       <c r="H67" t="n">
         <v>49492</v>
@@ -2341,7 +2341,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.7169189453125</v>
+        <v>3.71691870689392</v>
       </c>
       <c r="H68" t="n">
         <v>96719</v>
@@ -2370,7 +2370,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726386070251</v>
+        <v>3.79726409912109</v>
       </c>
       <c r="H69" t="n">
         <v>35741</v>
@@ -2399,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.82595825195312</v>
+        <v>3.8259584903717</v>
       </c>
       <c r="H70" t="n">
         <v>33705</v>
@@ -2428,7 +2428,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987436294556</v>
+        <v>3.73987460136414</v>
       </c>
       <c r="H71" t="n">
         <v>26533</v>
@@ -2457,7 +2457,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>3.80682873725891</v>
+        <v>3.80682897567749</v>
       </c>
       <c r="H72" t="n">
         <v>32798</v>
@@ -2515,7 +2515,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222255706787</v>
+        <v>3.73222279548645</v>
       </c>
       <c r="H74" t="n">
         <v>23567</v>
@@ -2544,7 +2544,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8489146232605</v>
+        <v>3.84891414642334</v>
       </c>
       <c r="H75" t="n">
         <v>62408</v>
@@ -2573,7 +2573,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463815689087</v>
+        <v>4.29463863372803</v>
       </c>
       <c r="H76" t="n">
         <v>172014</v>
@@ -2689,7 +2689,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851745605469</v>
+        <v>5.30851793289185</v>
       </c>
       <c r="H80" t="n">
         <v>273720</v>
@@ -2718,7 +2718,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>5.30373573303223</v>
+        <v>5.30373525619507</v>
       </c>
       <c r="H81" t="n">
         <v>264110</v>
@@ -2747,7 +2747,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>5.12200212478638</v>
+        <v>5.12200260162354</v>
       </c>
       <c r="H82" t="n">
         <v>94676</v>
@@ -2776,7 +2776,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.05504751205444</v>
+        <v>5.0550479888916</v>
       </c>
       <c r="H83" t="n">
         <v>85082</v>
@@ -2863,7 +2863,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>4.9546160697937</v>
+        <v>4.95461654663086</v>
       </c>
       <c r="H86" t="n">
         <v>66959</v>
@@ -2892,7 +2892,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653697967529</v>
+        <v>4.73653650283813</v>
       </c>
       <c r="H87" t="n">
         <v>101740</v>
@@ -3008,7 +3008,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H91" t="n">
         <v>78370</v>
@@ -3066,7 +3066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942451477051</v>
+        <v>4.18942499160767</v>
       </c>
       <c r="H93" t="n">
         <v>83730</v>
@@ -3095,7 +3095,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550840377808</v>
+        <v>4.27550792694092</v>
       </c>
       <c r="H94" t="n">
         <v>105195</v>
@@ -3182,7 +3182,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.11673069000244</v>
+        <v>4.11673164367676</v>
       </c>
       <c r="H97" t="n">
         <v>33027</v>
@@ -3211,7 +3211,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603302001953</v>
+        <v>4.17603349685669</v>
       </c>
       <c r="H98" t="n">
         <v>54021</v>
@@ -3240,7 +3240,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472812652588</v>
+        <v>4.20472860336304</v>
       </c>
       <c r="H99" t="n">
         <v>30978</v>
@@ -3269,7 +3269,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846429824829</v>
+        <v>4.29846382141113</v>
       </c>
       <c r="H100" t="n">
         <v>67373</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113828659058</v>
+        <v>4.92113876342773</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3385,7 +3385,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548263549805</v>
+        <v>5.04548215866089</v>
       </c>
       <c r="H104" t="n">
         <v>88307</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107570648193</v>
       </c>
       <c r="H106" t="n">
         <v>756136</v>
@@ -3501,7 +3501,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>7.25497388839722</v>
+        <v>7.25497436523438</v>
       </c>
       <c r="H108" t="n">
         <v>611973</v>
@@ -3530,7 +3530,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367540359497</v>
+        <v>7.06367635726929</v>
       </c>
       <c r="H109" t="n">
         <v>396366</v>
@@ -3559,7 +3559,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107570648193</v>
       </c>
       <c r="H110" t="n">
         <v>192489</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804088592529</v>
+        <v>6.52804183959961</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3646,7 +3646,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237466812134</v>
+        <v>6.98237419128418</v>
       </c>
       <c r="H113" t="n">
         <v>407399</v>
@@ -3704,7 +3704,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.3845682144165</v>
+        <v>6.38456869125366</v>
       </c>
       <c r="H115" t="n">
         <v>131401</v>
@@ -3820,7 +3820,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>5.87762975692749</v>
+        <v>5.87762880325317</v>
       </c>
       <c r="H119" t="n">
         <v>158117</v>
@@ -3907,7 +3907,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325227737427</v>
+        <v>6.74325275421143</v>
       </c>
       <c r="H122" t="n">
         <v>283137</v>
@@ -4081,7 +4081,7 @@
         <v>6.625</v>
       </c>
       <c r="G128" t="n">
-        <v>6.33674383163452</v>
+        <v>6.33674335479736</v>
       </c>
       <c r="H128" t="n">
         <v>31549</v>
@@ -4110,7 +4110,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H129" t="n">
         <v>59634</v>
@@ -4139,7 +4139,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H130" t="n">
         <v>59773</v>
@@ -4168,7 +4168,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38934993743896</v>
       </c>
       <c r="H131" t="n">
         <v>52660</v>
@@ -4226,7 +4226,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>6.19805240631104</v>
+        <v>6.19805288314819</v>
       </c>
       <c r="H133" t="n">
         <v>77921</v>
@@ -4255,7 +4255,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>6.63803815841675</v>
+        <v>6.63803863525391</v>
       </c>
       <c r="H134" t="n">
         <v>118333</v>
@@ -4429,7 +4429,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>7.05889415740967</v>
+        <v>7.05889368057251</v>
       </c>
       <c r="H140" t="n">
         <v>313570</v>
@@ -4458,7 +4458,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>6.95846223831177</v>
+        <v>6.95846271514893</v>
       </c>
       <c r="H141" t="n">
         <v>66133</v>
@@ -4487,7 +4487,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>6.9967212677002</v>
+        <v>6.99672174453735</v>
       </c>
       <c r="H142" t="n">
         <v>66130</v>
@@ -4603,7 +4603,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107570648193</v>
       </c>
       <c r="H146" t="n">
         <v>18313</v>
@@ -4632,7 +4632,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.92498445510864</v>
+        <v>6.92498397827148</v>
       </c>
       <c r="H147" t="n">
         <v>105405</v>
@@ -4661,7 +4661,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75281620025635</v>
+        <v>6.75281667709351</v>
       </c>
       <c r="H148" t="n">
         <v>55331</v>
@@ -4864,7 +4864,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976345062256</v>
+        <v>7.03976440429688</v>
       </c>
       <c r="H155" t="n">
         <v>46790</v>
@@ -4951,7 +4951,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.09190368652344</v>
+        <v>8.0919017791748</v>
       </c>
       <c r="H158" t="n">
         <v>272541</v>
@@ -5038,7 +5038,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.67104768753052</v>
+        <v>7.67104721069336</v>
       </c>
       <c r="H161" t="n">
         <v>97882</v>
@@ -5067,7 +5067,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G162" t="n">
-        <v>7.66626453399658</v>
+        <v>7.66626501083374</v>
       </c>
       <c r="H162" t="n">
         <v>71695</v>
@@ -5125,7 +5125,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234426498413</v>
+        <v>7.86234569549561</v>
       </c>
       <c r="H164" t="n">
         <v>30398</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626037597656</v>
+        <v>7.77626132965088</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5270,7 +5270,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060424804688</v>
+        <v>7.90060472488403</v>
       </c>
       <c r="H169" t="n">
         <v>42906</v>
@@ -5299,7 +5299,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.8336501121521</v>
+        <v>7.83364868164062</v>
       </c>
       <c r="H170" t="n">
         <v>41230</v>
@@ -5357,7 +5357,7 @@
         <v>8.25</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89103984832764</v>
+        <v>7.89103937149048</v>
       </c>
       <c r="H172" t="n">
         <v>61552</v>
@@ -5415,7 +5415,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H174" t="n">
         <v>135297</v>
@@ -5444,7 +5444,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492698669434</v>
+        <v>8.68492603302002</v>
       </c>
       <c r="H175" t="n">
         <v>251570</v>
@@ -5502,7 +5502,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622581481934</v>
+        <v>8.76622676849365</v>
       </c>
       <c r="H177" t="n">
         <v>231642</v>
@@ -5560,7 +5560,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G179" t="n">
-        <v>8.35015392303467</v>
+        <v>8.35015487670898</v>
       </c>
       <c r="H179" t="n">
         <v>237396</v>
@@ -5618,7 +5618,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.41710758209229</v>
+        <v>8.41710948944092</v>
       </c>
       <c r="H181" t="n">
         <v>154982</v>
@@ -5647,7 +5647,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>8.46493434906006</v>
+        <v>8.46493339538574</v>
       </c>
       <c r="H182" t="n">
         <v>82708</v>
@@ -5705,7 +5705,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.25450611114502</v>
+        <v>8.2545051574707</v>
       </c>
       <c r="H184" t="n">
         <v>33220</v>
@@ -5734,7 +5734,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451763153076</v>
+        <v>7.92451620101929</v>
       </c>
       <c r="H185" t="n">
         <v>122464</v>
@@ -5792,7 +5792,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34059047698975</v>
+        <v>8.34058952331543</v>
       </c>
       <c r="H187" t="n">
         <v>63159</v>
@@ -5821,7 +5821,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H188" t="n">
         <v>34542</v>
@@ -5850,7 +5850,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754734039307</v>
+        <v>8.29754829406738</v>
       </c>
       <c r="H189" t="n">
         <v>29985</v>
@@ -5908,7 +5908,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928367614746</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H191" t="n">
         <v>24030</v>
@@ -5966,7 +5966,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101680755615</v>
+        <v>8.55101585388184</v>
       </c>
       <c r="H193" t="n">
         <v>104665</v>
@@ -5995,7 +5995,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92883014678955</v>
+        <v>8.92883110046387</v>
       </c>
       <c r="H194" t="n">
         <v>196106</v>
@@ -6053,7 +6053,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.10578155517578</v>
+        <v>9.10578060150146</v>
       </c>
       <c r="H196" t="n">
         <v>198688</v>
@@ -6111,7 +6111,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317401885986</v>
+        <v>9.05317497253418</v>
       </c>
       <c r="H198" t="n">
         <v>156638</v>
@@ -6227,7 +6227,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.1727352142334</v>
+        <v>9.17273616790771</v>
       </c>
       <c r="H202" t="n">
         <v>47674</v>
@@ -6256,7 +6256,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185855865479</v>
+        <v>9.41185760498047</v>
       </c>
       <c r="H203" t="n">
         <v>115834</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6401,7 +6401,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.5362024307251</v>
+        <v>9.53620147705078</v>
       </c>
       <c r="H208" t="n">
         <v>78401</v>
@@ -6430,7 +6430,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587837219238</v>
+        <v>10.3587827682495</v>
       </c>
       <c r="H209" t="n">
         <v>324694</v>
@@ -6459,7 +6459,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>10.4735612869263</v>
+        <v>10.473560333252</v>
       </c>
       <c r="H210" t="n">
         <v>301050</v>
@@ -6488,7 +6488,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.253568649292</v>
+        <v>10.2535676956177</v>
       </c>
       <c r="H211" t="n">
         <v>105355</v>
@@ -6546,7 +6546,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>11.1813650131226</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H213" t="n">
         <v>187510</v>
@@ -6575,7 +6575,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1813650131226</v>
+        <v>11.1813640594482</v>
       </c>
       <c r="H214" t="n">
         <v>181372</v>
@@ -6720,7 +6720,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831266403198</v>
+        <v>10.4831275939941</v>
       </c>
       <c r="H219" t="n">
         <v>128669</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692100524902</v>
+        <v>10.5692110061646</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6807,7 +6807,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370265960693</v>
+        <v>10.8370275497437</v>
       </c>
       <c r="H222" t="n">
         <v>98298</v>
@@ -6836,7 +6836,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.961371421814</v>
+        <v>10.9613723754883</v>
       </c>
       <c r="H223" t="n">
         <v>86558</v>
@@ -6923,7 +6923,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117849349976</v>
+        <v>11.6117839813232</v>
       </c>
       <c r="H226" t="n">
         <v>191398</v>
@@ -6981,7 +6981,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456922531128</v>
+        <v>11.7456912994385</v>
       </c>
       <c r="H228" t="n">
         <v>176751</v>
@@ -7010,7 +7010,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648220062256</v>
+        <v>11.7648229598999</v>
       </c>
       <c r="H229" t="n">
         <v>87480</v>
@@ -7126,7 +7126,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3961048126221</v>
+        <v>12.3961057662964</v>
       </c>
       <c r="H233" t="n">
         <v>317127</v>
@@ -7271,7 +7271,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839517593384</v>
+        <v>11.7839527130127</v>
       </c>
       <c r="H238" t="n">
         <v>75176</v>
@@ -7329,7 +7329,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.616096496582</v>
+        <v>12.6160974502563</v>
       </c>
       <c r="H240" t="n">
         <v>180021</v>
@@ -7387,7 +7387,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717250823975</v>
+        <v>13.3717241287231</v>
       </c>
       <c r="H242" t="n">
         <v>100896</v>
@@ -7445,7 +7445,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446575164795</v>
+        <v>15.2446565628052</v>
       </c>
       <c r="H244" t="n">
         <v>256881</v>
@@ -7474,7 +7474,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.038592338562</v>
+        <v>14.0385932922363</v>
       </c>
       <c r="H245" t="n">
         <v>494015</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272216796875</v>
+        <v>13.5272207260132</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7706,7 +7706,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H253" t="n">
         <v>84013</v>
@@ -7967,7 +7967,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H262" t="n">
         <v>39442</v>
@@ -8025,7 +8025,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G264" t="n">
-        <v>14.1061315536499</v>
+        <v>14.1061325073242</v>
       </c>
       <c r="H264" t="n">
         <v>227402</v>
@@ -8054,7 +8054,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877321243286</v>
+        <v>13.7877311706543</v>
       </c>
       <c r="H265" t="n">
         <v>225704</v>
@@ -8083,7 +8083,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973804473877</v>
+        <v>13.7973794937134</v>
       </c>
       <c r="H266" t="n">
         <v>74231</v>
@@ -8112,7 +8112,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>13.6044092178345</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H267" t="n">
         <v>71289</v>
@@ -8199,7 +8199,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921422958374</v>
+        <v>13.3921432495117</v>
       </c>
       <c r="H270" t="n">
         <v>69772</v>
@@ -8228,7 +8228,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1316299438477</v>
+        <v>13.1316318511963</v>
       </c>
       <c r="H271" t="n">
         <v>92437</v>
@@ -8286,7 +8286,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H273" t="n">
         <v>167282</v>
@@ -8315,7 +8315,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G274" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H274" t="n">
         <v>91826</v>
@@ -8373,7 +8373,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2887649536133</v>
+        <v>11.288763999939</v>
       </c>
       <c r="H276" t="n">
         <v>199685</v>
@@ -8460,7 +8460,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3756017684937</v>
+        <v>11.3756008148193</v>
       </c>
       <c r="H279" t="n">
         <v>165236</v>
@@ -8518,7 +8518,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5975170135498</v>
+        <v>11.5975179672241</v>
       </c>
       <c r="H281" t="n">
         <v>40964</v>
@@ -8547,7 +8547,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H282" t="n">
         <v>117391</v>
@@ -8576,7 +8576,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.2887649536133</v>
+        <v>11.288763999939</v>
       </c>
       <c r="H283" t="n">
         <v>93658</v>
@@ -8605,7 +8605,7 @@
         <v>11.75</v>
       </c>
       <c r="G284" t="n">
-        <v>11.337007522583</v>
+        <v>11.3370065689087</v>
       </c>
       <c r="H284" t="n">
         <v>114241</v>
@@ -8663,7 +8663,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>10.680908203125</v>
+        <v>10.6809091567993</v>
       </c>
       <c r="H286" t="n">
         <v>57845</v>
@@ -8692,7 +8692,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484483718872</v>
+        <v>10.7484493255615</v>
       </c>
       <c r="H287" t="n">
         <v>33613</v>
@@ -8721,7 +8721,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G288" t="n">
-        <v>10.729151725769</v>
+        <v>10.7291507720947</v>
       </c>
       <c r="H288" t="n">
         <v>25029</v>
@@ -8779,7 +8779,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.2501707077026</v>
+        <v>11.2501697540283</v>
       </c>
       <c r="H290" t="n">
         <v>53729</v>
@@ -8866,7 +8866,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G293" t="n">
-        <v>10.8159875869751</v>
+        <v>10.8159866333008</v>
       </c>
       <c r="H293" t="n">
         <v>37146</v>
@@ -8895,7 +8895,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.0089588165283</v>
+        <v>11.008957862854</v>
       </c>
       <c r="H294" t="n">
         <v>9802</v>
@@ -8924,7 +8924,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G295" t="n">
-        <v>10.8449325561523</v>
+        <v>10.8449335098267</v>
       </c>
       <c r="H295" t="n">
         <v>23068</v>
@@ -8953,7 +8953,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072345733643</v>
+        <v>10.5072355270386</v>
       </c>
       <c r="H296" t="n">
         <v>45140</v>
@@ -9011,7 +9011,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247406005859</v>
+        <v>11.1247396469116</v>
       </c>
       <c r="H298" t="n">
         <v>108006</v>
@@ -9069,7 +9069,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685720443726</v>
+        <v>11.5685710906982</v>
       </c>
       <c r="H300" t="n">
         <v>224596</v>
@@ -9127,7 +9127,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273582458496</v>
+        <v>11.3273591995239</v>
       </c>
       <c r="H302" t="n">
         <v>104822</v>
@@ -9156,7 +9156,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G303" t="n">
-        <v>11.7133007049561</v>
+        <v>11.7132997512817</v>
       </c>
       <c r="H303" t="n">
         <v>115357</v>
@@ -9214,7 +9214,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606470108032</v>
+        <v>12.0606460571289</v>
       </c>
       <c r="H305" t="n">
         <v>194476</v>
@@ -9243,7 +9243,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G306" t="n">
-        <v>11.7808389663696</v>
+        <v>11.7808399200439</v>
       </c>
       <c r="H306" t="n">
         <v>50004</v>
@@ -9301,7 +9301,7 @@
         <v>11.75</v>
       </c>
       <c r="G308" t="n">
-        <v>11.337007522583</v>
+        <v>11.3370065689087</v>
       </c>
       <c r="H308" t="n">
         <v>79684</v>
@@ -9388,7 +9388,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212247848511</v>
+        <v>11.2212257385254</v>
       </c>
       <c r="H311" t="n">
         <v>48985</v>
@@ -9446,7 +9446,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>11.5975170135498</v>
+        <v>11.5975179672241</v>
       </c>
       <c r="H313" t="n">
         <v>101331</v>
@@ -9504,7 +9504,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334945678711</v>
+        <v>11.4334936141968</v>
       </c>
       <c r="H315" t="n">
         <v>31751</v>
@@ -9533,7 +9533,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H316" t="n">
         <v>113990</v>
@@ -9562,7 +9562,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H317" t="n">
         <v>48953</v>
@@ -9620,7 +9620,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606470108032</v>
+        <v>12.0606460571289</v>
       </c>
       <c r="H319" t="n">
         <v>41274</v>
@@ -9649,7 +9649,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G320" t="n">
-        <v>12.1281862258911</v>
+        <v>12.1281852722168</v>
       </c>
       <c r="H320" t="n">
         <v>53946</v>
@@ -9823,7 +9823,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>13.6044092178345</v>
+        <v>13.6044101715088</v>
       </c>
       <c r="H326" t="n">
         <v>296460</v>
@@ -9852,7 +9852,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G327" t="n">
-        <v>13.6140575408936</v>
+        <v>13.6140565872192</v>
       </c>
       <c r="H327" t="n">
         <v>135660</v>
@@ -9881,7 +9881,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H328" t="n">
         <v>133226</v>
@@ -9939,7 +9939,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H330" t="n">
         <v>80883</v>
@@ -10084,7 +10084,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H335" t="n">
         <v>56318</v>
@@ -10113,7 +10113,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H336" t="n">
         <v>66093</v>
@@ -10142,7 +10142,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552703857422</v>
+        <v>13.8552713394165</v>
       </c>
       <c r="H337" t="n">
         <v>35661</v>
@@ -10229,7 +10229,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807004928589</v>
+        <v>13.9807014465332</v>
       </c>
       <c r="H340" t="n">
         <v>101573</v>
@@ -10316,7 +10316,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.492073059082</v>
+        <v>14.4920740127563</v>
       </c>
       <c r="H343" t="n">
         <v>175404</v>
@@ -10345,7 +10345,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H344" t="n">
         <v>84729</v>
@@ -10374,7 +10374,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G345" t="n">
-        <v>14.5113697052002</v>
+        <v>14.5113706588745</v>
       </c>
       <c r="H345" t="n">
         <v>53819</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5692615509033</v>
+        <v>14.569260597229</v>
       </c>
       <c r="H346" t="n">
         <v>63786</v>
@@ -10432,7 +10432,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G347" t="n">
-        <v>14.5789089202881</v>
+        <v>14.5789098739624</v>
       </c>
       <c r="H347" t="n">
         <v>26791</v>
@@ -10461,7 +10461,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.5113697052002</v>
+        <v>14.5113706588745</v>
       </c>
       <c r="H348" t="n">
         <v>81697</v>
@@ -10490,7 +10490,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052352905273</v>
+        <v>14.4052362442017</v>
       </c>
       <c r="H349" t="n">
         <v>73630</v>
@@ -10519,7 +10519,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824247360229</v>
+        <v>14.4824237823486</v>
       </c>
       <c r="H350" t="n">
         <v>97965</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527219772339</v>
+        <v>12.5527210235596</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.0062007904053</v>
+        <v>13.0062017440796</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10780,7 +10780,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447969436646</v>
       </c>
       <c r="H359" t="n">
         <v>27096</v>
@@ -10925,7 +10925,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1316299438477</v>
+        <v>13.1316318511963</v>
       </c>
       <c r="H364" t="n">
         <v>31128</v>
@@ -11099,7 +11099,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H370" t="n">
         <v>58049</v>
@@ -11186,7 +11186,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>11.9641599655151</v>
+        <v>11.9641609191895</v>
       </c>
       <c r="H373" t="n">
         <v>95740</v>
@@ -11244,7 +11244,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474828720093</v>
+        <v>12.1474838256836</v>
       </c>
       <c r="H375" t="n">
         <v>32852</v>
@@ -11331,7 +11331,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176416397095</v>
+        <v>12.4176406860352</v>
       </c>
       <c r="H378" t="n">
         <v>61237</v>
@@ -11360,7 +11360,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H379" t="n">
         <v>11240</v>
@@ -11418,7 +11418,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H381" t="n">
         <v>64542</v>
@@ -11679,7 +11679,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>11.9641599655151</v>
+        <v>11.9641609191895</v>
       </c>
       <c r="H390" t="n">
         <v>27020</v>
@@ -11708,7 +11708,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H391" t="n">
         <v>36167</v>
@@ -11737,7 +11737,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1281862258911</v>
+        <v>12.1281852722168</v>
       </c>
       <c r="H392" t="n">
         <v>25249</v>
@@ -11853,7 +11853,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.243968963623</v>
+        <v>12.2439680099487</v>
       </c>
       <c r="H396" t="n">
         <v>21900</v>
@@ -12114,7 +12114,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228797912598</v>
+        <v>12.8228788375854</v>
       </c>
       <c r="H405" t="n">
         <v>47428</v>
@@ -12172,7 +12172,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H407" t="n">
         <v>26025</v>
@@ -12230,7 +12230,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>12.8711214065552</v>
+        <v>12.8711223602295</v>
       </c>
       <c r="H409" t="n">
         <v>6479</v>
@@ -12288,7 +12288,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447969436646</v>
       </c>
       <c r="H411" t="n">
         <v>52341</v>
@@ -12346,7 +12346,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G413" t="n">
-        <v>12.9097166061401</v>
+        <v>12.9097156524658</v>
       </c>
       <c r="H413" t="n">
         <v>52102</v>
@@ -12491,7 +12491,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193649291992</v>
+        <v>12.9193658828735</v>
       </c>
       <c r="H418" t="n">
         <v>10876</v>
@@ -12578,7 +12578,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772567749023</v>
+        <v>12.9772548675537</v>
       </c>
       <c r="H421" t="n">
         <v>36559</v>
@@ -12636,7 +12636,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>12.8904190063477</v>
+        <v>12.8904180526733</v>
       </c>
       <c r="H423" t="n">
         <v>19497</v>
@@ -12868,7 +12868,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>13.2184677124023</v>
+        <v>13.2184686660767</v>
       </c>
       <c r="H431" t="n">
         <v>67159</v>
@@ -13071,7 +13071,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974496841431</v>
+        <v>12.6974487304688</v>
       </c>
       <c r="H438" t="n">
         <v>68110</v>
@@ -13129,7 +13129,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H440" t="n">
         <v>33681</v>
@@ -13303,7 +13303,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H446" t="n">
         <v>35222</v>
@@ -13535,7 +13535,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H454" t="n">
         <v>101981</v>
@@ -13564,7 +13564,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H455" t="n">
         <v>45659</v>
@@ -13593,7 +13593,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H456" t="n">
         <v>40685</v>
@@ -13622,7 +13622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H457" t="n">
         <v>24461</v>
@@ -13680,7 +13680,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>12.3501024246216</v>
+        <v>12.3501014709473</v>
       </c>
       <c r="H459" t="n">
         <v>27238</v>
@@ -13709,7 +13709,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>12.4465866088867</v>
+        <v>12.446587562561</v>
       </c>
       <c r="H460" t="n">
         <v>60559</v>
@@ -13738,7 +13738,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H461" t="n">
         <v>38181</v>
@@ -13883,7 +13883,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H466" t="n">
         <v>20941</v>
@@ -13941,7 +13941,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H468" t="n">
         <v>13736</v>
@@ -14144,7 +14144,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124025344849</v>
+        <v>12.0124034881592</v>
       </c>
       <c r="H475" t="n">
         <v>13507</v>
@@ -14202,7 +14202,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747055053711</v>
+        <v>11.6747064590454</v>
       </c>
       <c r="H477" t="n">
         <v>345190</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554733276367</v>
+        <v>9.45554637908936</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14318,7 +14318,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711090087891</v>
+        <v>9.68711185455322</v>
       </c>
       <c r="H481" t="n">
         <v>127849</v>
@@ -14347,7 +14347,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G482" t="n">
-        <v>9.85113620758057</v>
+        <v>9.85113716125488</v>
       </c>
       <c r="H482" t="n">
         <v>95444</v>
@@ -14376,7 +14376,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923490524292</v>
+        <v>10.0923480987549</v>
       </c>
       <c r="H483" t="n">
         <v>75251</v>
@@ -14434,7 +14434,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107494354248</v>
+        <v>10.4107503890991</v>
       </c>
       <c r="H485" t="n">
         <v>165118</v>
@@ -14521,7 +14521,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764980316162</v>
+        <v>11.0764970779419</v>
       </c>
       <c r="H488" t="n">
         <v>85880</v>
@@ -14550,7 +14550,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.71950340271</v>
+        <v>10.7195024490356</v>
       </c>
       <c r="H489" t="n">
         <v>62047</v>
@@ -14637,7 +14637,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028234481812</v>
       </c>
       <c r="H492" t="n">
         <v>50334</v>
@@ -14695,7 +14695,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G494" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028234481812</v>
       </c>
       <c r="H494" t="n">
         <v>56326</v>
@@ -14724,7 +14724,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G495" t="n">
-        <v>10.8159875869751</v>
+        <v>10.8159866333008</v>
       </c>
       <c r="H495" t="n">
         <v>55815</v>
@@ -14753,7 +14753,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G496" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028234481812</v>
       </c>
       <c r="H496" t="n">
         <v>116291</v>
@@ -14782,7 +14782,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7388000488281</v>
+        <v>10.7387990951538</v>
       </c>
       <c r="H497" t="n">
         <v>62706</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078981399536</v>
+        <v>10.7078971862793</v>
       </c>
       <c r="H500" t="n">
         <v>97230</v>
@@ -14898,7 +14898,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G501" t="n">
-        <v>10.4732036590576</v>
+        <v>10.4732046127319</v>
       </c>
       <c r="H501" t="n">
         <v>197020</v>
@@ -14927,7 +14927,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H502" t="n">
         <v>89414</v>
@@ -14956,7 +14956,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189521789551</v>
+        <v>10.2189531326294</v>
       </c>
       <c r="H503" t="n">
         <v>87325</v>
@@ -15043,7 +15043,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4536466598511</v>
+        <v>10.4536457061768</v>
       </c>
       <c r="H506" t="n">
         <v>53759</v>
@@ -15072,7 +15072,7 @@
         <v>10.75</v>
       </c>
       <c r="G507" t="n">
-        <v>10.5123195648193</v>
+        <v>10.5123205184937</v>
       </c>
       <c r="H507" t="n">
         <v>171168</v>
@@ -15188,7 +15188,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G511" t="n">
-        <v>10.5807723999023</v>
+        <v>10.580771446228</v>
       </c>
       <c r="H511" t="n">
         <v>29173</v>
@@ -15217,7 +15217,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G512" t="n">
-        <v>10.6394453048706</v>
+        <v>10.6394462585449</v>
       </c>
       <c r="H512" t="n">
         <v>86952</v>
@@ -15362,7 +15362,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110445022583</v>
+        <v>11.011043548584</v>
       </c>
       <c r="H517" t="n">
         <v>116880</v>
@@ -15391,7 +15391,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G518" t="n">
-        <v>10.8350238800049</v>
+        <v>10.8350229263306</v>
       </c>
       <c r="H518" t="n">
         <v>27320</v>
@@ -15420,7 +15420,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G519" t="n">
-        <v>10.7372350692749</v>
+        <v>10.7372341156006</v>
       </c>
       <c r="H519" t="n">
         <v>53671</v>
@@ -15507,7 +15507,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>10.8350238800049</v>
+        <v>10.8350229263306</v>
       </c>
       <c r="H522" t="n">
         <v>64785</v>
@@ -15536,7 +15536,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>10.913254737854</v>
+        <v>10.9132556915283</v>
       </c>
       <c r="H523" t="n">
         <v>102971</v>
@@ -15594,7 +15594,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G525" t="n">
-        <v>10.913254737854</v>
+        <v>10.9132556915283</v>
       </c>
       <c r="H525" t="n">
         <v>37350</v>
@@ -15623,7 +15623,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H526" t="n">
         <v>85137</v>
@@ -15652,7 +15652,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G527" t="n">
-        <v>10.913254737854</v>
+        <v>10.9132556915283</v>
       </c>
       <c r="H527" t="n">
         <v>77485</v>
@@ -15768,7 +15768,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G531" t="n">
-        <v>10.913254737854</v>
+        <v>10.9132556915283</v>
       </c>
       <c r="H531" t="n">
         <v>20633</v>
@@ -15826,7 +15826,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G533" t="n">
-        <v>10.6394453048706</v>
+        <v>10.6394462585449</v>
       </c>
       <c r="H533" t="n">
         <v>37510</v>
@@ -15942,7 +15942,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G537" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H537" t="n">
         <v>66947</v>
@@ -16000,7 +16000,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H539" t="n">
         <v>38633</v>
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H545" t="n">
         <v>37787</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H546" t="n">
         <v>15589</v>
@@ -16232,7 +16232,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509262084961</v>
+        <v>9.50509357452393</v>
       </c>
       <c r="H547" t="n">
         <v>11946</v>
@@ -16261,7 +16261,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619964599609</v>
+        <v>9.45619869232178</v>
       </c>
       <c r="H548" t="n">
         <v>15955</v>
@@ -16290,7 +16290,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H549" t="n">
         <v>23576</v>
@@ -16319,7 +16319,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H550" t="n">
         <v>18189</v>
@@ -16377,7 +16377,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H552" t="n">
         <v>45912</v>
@@ -16435,7 +16435,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233818054199</v>
+        <v>8.74233722686768</v>
       </c>
       <c r="H554" t="n">
         <v>94454</v>
@@ -16609,7 +16609,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669086456299</v>
       </c>
       <c r="H560" t="n">
         <v>77526</v>
@@ -16638,7 +16638,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H561" t="n">
         <v>47843</v>
@@ -16696,7 +16696,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172714233398</v>
       </c>
       <c r="H563" t="n">
         <v>28072</v>
@@ -16812,7 +16812,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H567" t="n">
         <v>124458</v>
@@ -16957,7 +16957,7 @@
         <v>10.5</v>
       </c>
       <c r="G572" t="n">
-        <v>10.2678480148315</v>
+        <v>10.2678470611572</v>
       </c>
       <c r="H572" t="n">
         <v>116632</v>
@@ -17073,7 +17073,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G576" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H576" t="n">
         <v>88350</v>
@@ -17247,7 +17247,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.1237154006958</v>
+        <v>9.12371635437012</v>
       </c>
       <c r="H582" t="n">
         <v>83347</v>
@@ -17392,7 +17392,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946296691895</v>
       </c>
       <c r="H587" t="n">
         <v>46974</v>
@@ -17508,7 +17508,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H591" t="n">
         <v>38459</v>
@@ -17537,7 +17537,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H592" t="n">
         <v>73245</v>
@@ -17566,7 +17566,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H593" t="n">
         <v>172995</v>
@@ -17711,7 +17711,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669086456299</v>
       </c>
       <c r="H598" t="n">
         <v>140106</v>
@@ -18030,7 +18030,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H609" t="n">
         <v>8881</v>
@@ -18146,7 +18146,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G613" t="n">
-        <v>9.34863090515137</v>
+        <v>9.34862995147705</v>
       </c>
       <c r="H613" t="n">
         <v>29288</v>
@@ -18175,7 +18175,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172714233398</v>
       </c>
       <c r="H614" t="n">
         <v>134678</v>
@@ -18204,7 +18204,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>9.37796688079834</v>
+        <v>9.37796783447266</v>
       </c>
       <c r="H615" t="n">
         <v>38849</v>
@@ -18291,7 +18291,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H618" t="n">
         <v>16473</v>
@@ -18465,7 +18465,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669086456299</v>
       </c>
       <c r="H624" t="n">
         <v>136644</v>
@@ -18552,7 +18552,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H627" t="n">
         <v>11623</v>
@@ -18581,7 +18581,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>9.69089221954346</v>
+        <v>9.69089317321777</v>
       </c>
       <c r="H628" t="n">
         <v>41089</v>
@@ -18610,7 +18610,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354640960693</v>
+        <v>9.57354545593262</v>
       </c>
       <c r="H629" t="n">
         <v>59629</v>
@@ -18726,7 +18726,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>9.13349533081055</v>
+        <v>9.13349437713623</v>
       </c>
       <c r="H633" t="n">
         <v>33022</v>
@@ -18784,7 +18784,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G635" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H635" t="n">
         <v>46972</v>
@@ -18813,7 +18813,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233818054199</v>
+        <v>8.74233722686768</v>
       </c>
       <c r="H636" t="n">
         <v>26549</v>
@@ -18900,7 +18900,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>8.99658966064453</v>
+        <v>8.99659061431885</v>
       </c>
       <c r="H639" t="n">
         <v>10481</v>
@@ -19045,7 +19045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>9.43664073944092</v>
+        <v>9.4366397857666</v>
       </c>
       <c r="H644" t="n">
         <v>5673</v>
@@ -19219,7 +19219,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376647949219</v>
+        <v>9.5637674331665</v>
       </c>
       <c r="H650" t="n">
         <v>28011</v>
@@ -19248,7 +19248,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H651" t="n">
         <v>135104</v>
@@ -19364,7 +19364,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G655" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H655" t="n">
         <v>14617</v>
@@ -19509,7 +19509,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G660" t="n">
-        <v>9.30951595306396</v>
+        <v>9.30951499938965</v>
       </c>
       <c r="H660" t="n">
         <v>8734</v>
@@ -19770,7 +19770,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H669" t="n">
         <v>10937</v>
@@ -19799,7 +19799,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G670" t="n">
-        <v>9.30951595306396</v>
+        <v>9.30951499938965</v>
       </c>
       <c r="H670" t="n">
         <v>10898</v>
@@ -19857,7 +19857,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H672" t="n">
         <v>48863</v>
@@ -19944,7 +19944,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H675" t="n">
         <v>37373</v>
@@ -20002,7 +20002,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H677" t="n">
         <v>7000</v>
@@ -20031,7 +20031,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H678" t="n">
         <v>29641</v>
@@ -20060,7 +20060,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>9.7006721496582</v>
+        <v>9.70067119598389</v>
       </c>
       <c r="H679" t="n">
         <v>14909</v>
@@ -20176,7 +20176,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669086456299</v>
       </c>
       <c r="H683" t="n">
         <v>37382</v>
@@ -20205,7 +20205,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.8766918182373</v>
+        <v>9.87669086456299</v>
       </c>
       <c r="H684" t="n">
         <v>18917</v>
@@ -20292,7 +20292,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H687" t="n">
         <v>13215</v>
@@ -20437,7 +20437,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H692" t="n">
         <v>28508</v>
@@ -20495,7 +20495,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H694" t="n">
         <v>32283</v>
@@ -20553,7 +20553,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H696" t="n">
         <v>14440</v>
@@ -20669,7 +20669,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H700" t="n">
         <v>27899</v>
@@ -20756,7 +20756,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172714233398</v>
       </c>
       <c r="H703" t="n">
         <v>10949</v>
@@ -21017,7 +21017,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560531616211</v>
+        <v>8.15560436248779</v>
       </c>
       <c r="H712" t="n">
         <v>38461</v>
@@ -21104,7 +21104,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H715" t="n">
         <v>12213</v>
@@ -21249,7 +21249,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742362976074</v>
+        <v>8.51742458343506</v>
       </c>
       <c r="H720" t="n">
         <v>40610</v>
@@ -21365,7 +21365,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>8.87924385070801</v>
+        <v>8.87924289703369</v>
       </c>
       <c r="H724" t="n">
         <v>16711</v>
@@ -21423,7 +21423,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902282714844</v>
+        <v>8.88902187347412</v>
       </c>
       <c r="H726" t="n">
         <v>35047</v>
@@ -21452,7 +21452,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G727" t="n">
-        <v>8.77167510986328</v>
+        <v>8.7716760635376</v>
       </c>
       <c r="H727" t="n">
         <v>143037</v>
@@ -21481,7 +21481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G728" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H728" t="n">
         <v>73666</v>
@@ -21510,7 +21510,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946296691895</v>
       </c>
       <c r="H729" t="n">
         <v>24316</v>
@@ -21539,7 +21539,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H730" t="n">
         <v>9948</v>
@@ -21742,7 +21742,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262937545776</v>
+        <v>7.40262889862061</v>
       </c>
       <c r="H737" t="n">
         <v>30955</v>
@@ -21800,7 +21800,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>6.86478900909424</v>
+        <v>6.8647894859314</v>
       </c>
       <c r="H739" t="n">
         <v>73987</v>
@@ -21858,7 +21858,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>7.30483961105347</v>
+        <v>7.30484008789062</v>
       </c>
       <c r="H741" t="n">
         <v>13402</v>
@@ -21945,7 +21945,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.1581563949585</v>
+        <v>7.15815687179565</v>
       </c>
       <c r="H744" t="n">
         <v>18982</v>
@@ -21974,7 +21974,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G745" t="n">
-        <v>6.83545255661011</v>
+        <v>6.83545207977295</v>
       </c>
       <c r="H745" t="n">
         <v>110100</v>
@@ -22061,7 +22061,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G748" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H748" t="n">
         <v>167124</v>
@@ -22119,7 +22119,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834590911865</v>
+        <v>4.93834543228149</v>
       </c>
       <c r="H750" t="n">
         <v>185723</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22235,7 +22235,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>4.67431545257568</v>
+        <v>4.67431497573853</v>
       </c>
       <c r="H754" t="n">
         <v>139728</v>
@@ -22264,7 +22264,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>4.44940042495728</v>
+        <v>4.44940090179443</v>
       </c>
       <c r="H755" t="n">
         <v>78287</v>
@@ -22322,7 +22322,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>4.04357671737671</v>
+        <v>4.04357624053955</v>
       </c>
       <c r="H757" t="n">
         <v>116412</v>
@@ -22380,7 +22380,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>4.29782819747925</v>
+        <v>4.29782772064209</v>
       </c>
       <c r="H759" t="n">
         <v>196124</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22670,7 +22670,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502960205078</v>
+        <v>5.08502912521362</v>
       </c>
       <c r="H769" t="n">
         <v>224657</v>
@@ -22699,7 +22699,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>5.07525062561035</v>
+        <v>5.07525014877319</v>
       </c>
       <c r="H770" t="n">
         <v>177286</v>
@@ -22728,7 +22728,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.03613471984863</v>
+        <v>5.03613519668579</v>
       </c>
       <c r="H771" t="n">
         <v>79810</v>
@@ -22873,7 +22873,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G776" t="n">
-        <v>5.3197226524353</v>
+        <v>5.31972312927246</v>
       </c>
       <c r="H776" t="n">
         <v>134183</v>
@@ -22902,7 +22902,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H777" t="n">
         <v>121084</v>
@@ -23221,7 +23221,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G788" t="n">
-        <v>5.36861753463745</v>
+        <v>5.36861705780029</v>
       </c>
       <c r="H788" t="n">
         <v>51246</v>
@@ -23250,7 +23250,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H789" t="n">
         <v>33919</v>
@@ -23279,7 +23279,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016469955444</v>
+        <v>5.3001651763916</v>
       </c>
       <c r="H790" t="n">
         <v>36651</v>
@@ -23366,7 +23366,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G793" t="n">
-        <v>5.36861753463745</v>
+        <v>5.36861705780029</v>
       </c>
       <c r="H793" t="n">
         <v>32168</v>
@@ -23424,7 +23424,7 @@
         <v>5.25</v>
       </c>
       <c r="G795" t="n">
-        <v>5.13392400741577</v>
+        <v>5.13392353057861</v>
       </c>
       <c r="H795" t="n">
         <v>16038</v>
@@ -23453,7 +23453,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>5.22193431854248</v>
+        <v>5.22193384170532</v>
       </c>
       <c r="H796" t="n">
         <v>43106</v>
@@ -23540,7 +23540,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H799" t="n">
         <v>12491</v>
@@ -23714,7 +23714,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259691238403</v>
+        <v>5.19259738922119</v>
       </c>
       <c r="H805" t="n">
         <v>18129</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166269302368</v>
+        <v>4.79166221618652</v>
       </c>
       <c r="H807" t="n">
         <v>76245</v>
@@ -23830,7 +23830,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G809" t="n">
-        <v>5.01657676696777</v>
+        <v>5.01657724380493</v>
       </c>
       <c r="H809" t="n">
         <v>31571</v>
@@ -23888,7 +23888,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834590911865</v>
+        <v>4.93834543228149</v>
       </c>
       <c r="H811" t="n">
         <v>36173</v>
@@ -23917,7 +23917,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G812" t="n">
-        <v>5.01657676696777</v>
+        <v>5.01657724380493</v>
       </c>
       <c r="H812" t="n">
         <v>34933</v>
@@ -24120,7 +24120,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220642089844</v>
+        <v>5.65220594406128</v>
       </c>
       <c r="H819" t="n">
         <v>97422</v>
@@ -24149,7 +24149,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>5.4761848449707</v>
+        <v>5.47618532180786</v>
       </c>
       <c r="H820" t="n">
         <v>62956</v>
@@ -24207,7 +24207,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>5.456627368927</v>
+        <v>5.45662784576416</v>
       </c>
       <c r="H822" t="n">
         <v>46868</v>
@@ -24236,7 +24236,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H823" t="n">
         <v>49574</v>
@@ -24294,7 +24294,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>5.41751194000244</v>
+        <v>5.41751146316528</v>
       </c>
       <c r="H825" t="n">
         <v>10530</v>
@@ -24323,7 +24323,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552177429199</v>
       </c>
       <c r="H826" t="n">
         <v>18416</v>
@@ -24352,7 +24352,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552177429199</v>
       </c>
       <c r="H827" t="n">
         <v>27618</v>
@@ -24410,7 +24410,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264799118042</v>
+        <v>5.63264846801758</v>
       </c>
       <c r="H829" t="n">
         <v>49059</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402473449707</v>
+        <v>6.01402521133423</v>
       </c>
       <c r="H834" t="n">
         <v>41322</v>
@@ -24729,7 +24729,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G840" t="n">
-        <v>6.73766326904297</v>
+        <v>6.73766374588013</v>
       </c>
       <c r="H840" t="n">
         <v>81839</v>
@@ -24758,7 +24758,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>6.58120107650757</v>
+        <v>6.58120155334473</v>
       </c>
       <c r="H841" t="n">
         <v>153325</v>
@@ -25048,7 +25048,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.14115142822266</v>
+        <v>6.1411509513855</v>
       </c>
       <c r="H851" t="n">
         <v>14069</v>
@@ -25077,7 +25077,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H852" t="n">
         <v>26701</v>
@@ -25106,7 +25106,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.0042462348938</v>
+        <v>6.00424575805664</v>
       </c>
       <c r="H853" t="n">
         <v>11658</v>
@@ -25193,7 +25193,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78911018371582</v>
+        <v>5.78910970687866</v>
       </c>
       <c r="H856" t="n">
         <v>10669</v>
@@ -25251,7 +25251,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977325439453</v>
+        <v>5.75977373123169</v>
       </c>
       <c r="H858" t="n">
         <v>12990</v>
@@ -25338,7 +25338,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H861" t="n">
         <v>15530</v>
@@ -25367,7 +25367,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>5.60331058502197</v>
+        <v>5.60331106185913</v>
       </c>
       <c r="H862" t="n">
         <v>22714</v>
@@ -25454,7 +25454,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021530151367</v>
+        <v>5.74021577835083</v>
       </c>
       <c r="H865" t="n">
         <v>27718</v>
@@ -25541,7 +25541,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G868" t="n">
-        <v>5.573974609375</v>
+        <v>5.57397413253784</v>
       </c>
       <c r="H868" t="n">
         <v>10349</v>
@@ -25599,7 +25599,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H870" t="n">
         <v>22149</v>
@@ -25744,7 +25744,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H875" t="n">
         <v>10415</v>
@@ -25947,7 +25947,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G882" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H882" t="n">
         <v>57113</v>
@@ -25976,7 +25976,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G883" t="n">
-        <v>5.72065830230713</v>
+        <v>5.72065782546997</v>
       </c>
       <c r="H883" t="n">
         <v>26982</v>
@@ -26005,7 +26005,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H884" t="n">
         <v>30149</v>
@@ -26034,7 +26034,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.0433611869812</v>
+        <v>6.04336166381836</v>
       </c>
       <c r="H885" t="n">
         <v>23779</v>
@@ -26295,7 +26295,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655815124512</v>
+        <v>6.78655862808228</v>
       </c>
       <c r="H894" t="n">
         <v>16921</v>
@@ -26440,7 +26440,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489068984985</v>
+        <v>7.74489116668701</v>
       </c>
       <c r="H899" t="n">
         <v>112735</v>
@@ -26643,7 +26643,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842802047729</v>
+        <v>7.58842849731445</v>
       </c>
       <c r="H906" t="n">
         <v>22167</v>
@@ -26875,7 +26875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H914" t="n">
         <v>40423</v>
@@ -26933,7 +26933,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G916" t="n">
-        <v>6.85501098632812</v>
+        <v>6.85501050949097</v>
       </c>
       <c r="H916" t="n">
         <v>242774</v>
@@ -27107,7 +27107,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412641525269</v>
+        <v>6.89412689208984</v>
       </c>
       <c r="H922" t="n">
         <v>17841</v>
@@ -27165,7 +27165,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H924" t="n">
         <v>41919</v>
@@ -27252,7 +27252,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191570281982</v>
+        <v>6.99191522598267</v>
       </c>
       <c r="H927" t="n">
         <v>21117</v>
@@ -27310,7 +27310,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G929" t="n">
-        <v>7.17771434783936</v>
+        <v>7.17771482467651</v>
       </c>
       <c r="H929" t="n">
         <v>53483</v>
@@ -27339,7 +27339,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218732833862</v>
+        <v>7.42218685150146</v>
       </c>
       <c r="H930" t="n">
         <v>419711</v>
@@ -27368,7 +27368,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G931" t="n">
-        <v>7.24616670608521</v>
+        <v>7.24616622924805</v>
       </c>
       <c r="H931" t="n">
         <v>52841</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>8.03825759887695</v>
+        <v>8.03825855255127</v>
       </c>
       <c r="H940" t="n">
         <v>95905</v>
@@ -27745,7 +27745,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H944" t="n">
         <v>119944</v>
@@ -27832,7 +27832,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G947" t="n">
-        <v>9.43664073944092</v>
+        <v>9.4366397857666</v>
       </c>
       <c r="H947" t="n">
         <v>81693</v>
@@ -27919,7 +27919,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H950" t="n">
         <v>171303</v>
@@ -28035,7 +28035,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G954" t="n">
-        <v>8.810791015625</v>
+        <v>8.81079196929932</v>
       </c>
       <c r="H954" t="n">
         <v>75369</v>
@@ -28064,7 +28064,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>8.5956563949585</v>
+        <v>8.59565544128418</v>
       </c>
       <c r="H955" t="n">
         <v>181604</v>
@@ -28093,7 +28093,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897270202637</v>
+        <v>8.44897174835205</v>
       </c>
       <c r="H956" t="n">
         <v>40968</v>
@@ -28151,7 +28151,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37073993682861</v>
+        <v>8.37074089050293</v>
       </c>
       <c r="H958" t="n">
         <v>44957</v>
@@ -28412,7 +28412,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449924468994</v>
+        <v>8.20450019836426</v>
       </c>
       <c r="H967" t="n">
         <v>42116</v>
@@ -28557,7 +28557,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G972" t="n">
-        <v>8.17516231536865</v>
+        <v>8.17516136169434</v>
       </c>
       <c r="H972" t="n">
         <v>14608</v>
@@ -28615,7 +28615,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H974" t="n">
         <v>250262</v>
@@ -28818,7 +28818,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G981" t="n">
-        <v>10.913254737854</v>
+        <v>10.9132556915283</v>
       </c>
       <c r="H981" t="n">
         <v>93949</v>
@@ -28847,7 +28847,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804306030273</v>
+        <v>11.4804315567017</v>
       </c>
       <c r="H982" t="n">
         <v>419644</v>
@@ -28992,7 +28992,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G987" t="n">
-        <v>12.4387645721436</v>
+        <v>12.4387636184692</v>
       </c>
       <c r="H987" t="n">
         <v>287079</v>
@@ -29137,7 +29137,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882537841797</v>
       </c>
       <c r="H992" t="n">
         <v>403792</v>
@@ -29195,7 +29195,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G994" t="n">
-        <v>14.4336605072021</v>
+        <v>14.4336595535278</v>
       </c>
       <c r="H994" t="n">
         <v>123949</v>
@@ -29369,7 +29369,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7100219726562</v>
+        <v>13.7100210189819</v>
       </c>
       <c r="H1000" t="n">
         <v>186196</v>
@@ -29456,7 +29456,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.0059413909912</v>
+        <v>13.0059404373169</v>
       </c>
       <c r="H1003" t="n">
         <v>82659</v>
@@ -29543,7 +29543,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>12.6538991928101</v>
+        <v>12.6539001464844</v>
       </c>
       <c r="H1006" t="n">
         <v>60410</v>
@@ -29572,7 +29572,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>12.6538991928101</v>
+        <v>12.6539001464844</v>
       </c>
       <c r="H1007" t="n">
         <v>53351</v>
@@ -29630,7 +29630,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.2823028564453</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1009" t="n">
         <v>78089</v>
@@ -29688,7 +29688,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867223739624</v>
+        <v>12.0867233276367</v>
       </c>
       <c r="H1011" t="n">
         <v>47356</v>
@@ -29746,7 +29746,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1013" t="n">
-        <v>12.5756683349609</v>
+        <v>12.5756673812866</v>
       </c>
       <c r="H1013" t="n">
         <v>75572</v>
@@ -29949,7 +29949,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.5365533828735</v>
+        <v>12.5365524291992</v>
       </c>
       <c r="H1020" t="n">
         <v>66770</v>
@@ -30123,7 +30123,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.5952253341675</v>
+        <v>12.5952262878418</v>
       </c>
       <c r="H1026" t="n">
         <v>82690</v>
@@ -30239,7 +30239,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.2823028564453</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1030" t="n">
         <v>99601</v>
@@ -30268,7 +30268,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.2823028564453</v>
+        <v>12.282301902771</v>
       </c>
       <c r="H1031" t="n">
         <v>57835</v>
@@ -30326,7 +30326,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.7151250839233</v>
+        <v>11.715124130249</v>
       </c>
       <c r="H1033" t="n">
         <v>119232</v>
@@ -30355,7 +30355,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.047607421875</v>
+        <v>12.0476083755493</v>
       </c>
       <c r="H1034" t="n">
         <v>89765</v>
@@ -30384,7 +30384,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>12.6147832870483</v>
+        <v>12.6147842407227</v>
       </c>
       <c r="H1035" t="n">
         <v>136832</v>
@@ -30529,7 +30529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>12.6147832870483</v>
+        <v>12.6147842407227</v>
       </c>
       <c r="H1040" t="n">
         <v>52689</v>
@@ -30645,7 +30645,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>12.6147832870483</v>
+        <v>12.6147842407227</v>
       </c>
       <c r="H1044" t="n">
         <v>61277</v>
@@ -30732,7 +30732,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409738540649</v>
+        <v>12.3409748077393</v>
       </c>
       <c r="H1047" t="n">
         <v>46643</v>
@@ -31138,7 +31138,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.1505012512207</v>
+        <v>10.1505002975464</v>
       </c>
       <c r="H1061" t="n">
         <v>77475</v>
@@ -31196,7 +31196,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.30951595306396</v>
+        <v>9.30951499938965</v>
       </c>
       <c r="H1063" t="n">
         <v>88124</v>
@@ -31341,7 +31341,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206798553467</v>
+        <v>8.31206703186035</v>
       </c>
       <c r="H1068" t="n">
         <v>167682</v>
@@ -31370,7 +31370,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H1069" t="n">
         <v>180623</v>
@@ -31399,7 +31399,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543346405029</v>
+        <v>8.60543441772461</v>
       </c>
       <c r="H1070" t="n">
         <v>27481</v>
@@ -31457,7 +31457,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>8.72278118133545</v>
+        <v>8.72278022766113</v>
       </c>
       <c r="H1072" t="n">
         <v>55348</v>
@@ -31486,7 +31486,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.810791015625</v>
+        <v>8.81079196929932</v>
       </c>
       <c r="H1073" t="n">
         <v>41885</v>
@@ -31602,7 +31602,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H1077" t="n">
         <v>64803</v>
@@ -31631,7 +31631,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.0722694396973</v>
+        <v>10.0722703933716</v>
       </c>
       <c r="H1078" t="n">
         <v>52506</v>
@@ -31718,7 +31718,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H1081" t="n">
         <v>25731</v>
@@ -31776,7 +31776,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003293991089</v>
+        <v>10.6003303527832</v>
       </c>
       <c r="H1083" t="n">
         <v>44357</v>
@@ -31805,7 +31805,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.443868637085</v>
+        <v>10.4438676834106</v>
       </c>
       <c r="H1084" t="n">
         <v>61024</v>
@@ -31834,7 +31834,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.9523696899414</v>
+        <v>10.9523706436157</v>
       </c>
       <c r="H1085" t="n">
         <v>43194</v>
@@ -31950,7 +31950,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.1819591522217</v>
+        <v>13.181960105896</v>
       </c>
       <c r="H1089" t="n">
         <v>178518</v>
@@ -31979,7 +31979,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>13.1037292480469</v>
+        <v>13.1037282943726</v>
       </c>
       <c r="H1090" t="n">
         <v>153541</v>
@@ -32037,7 +32037,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.1428451538086</v>
+        <v>13.1428442001343</v>
       </c>
       <c r="H1092" t="n">
         <v>90633</v>
@@ -32153,7 +32153,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882537841797</v>
       </c>
       <c r="H1096" t="n">
         <v>93691</v>
@@ -32269,7 +32269,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1100" t="n">
-        <v>14.1402931213379</v>
+        <v>14.1402940750122</v>
       </c>
       <c r="H1100" t="n">
         <v>81068</v>
@@ -32298,7 +32298,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771987915039</v>
+        <v>14.2771978378296</v>
       </c>
       <c r="H1101" t="n">
         <v>57479</v>
@@ -32443,7 +32443,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.7074689865112</v>
+        <v>14.7074699401855</v>
       </c>
       <c r="H1106" t="n">
         <v>120242</v>
@@ -32530,7 +32530,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181840896606</v>
+        <v>15.1181831359863</v>
       </c>
       <c r="H1109" t="n">
         <v>121418</v>
@@ -32675,7 +32675,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666507720947</v>
+        <v>19.1666488647461</v>
       </c>
       <c r="H1114" t="n">
         <v>462313</v>
@@ -32733,7 +32733,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>20.1445388793945</v>
+        <v>20.1445407867432</v>
       </c>
       <c r="H1116" t="n">
         <v>183683</v>
@@ -32965,7 +32965,7 @@
         <v>21.5</v>
       </c>
       <c r="G1124" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1124" t="n">
         <v>72589</v>
@@ -32994,7 +32994,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1125" t="n">
-        <v>20.1445388793945</v>
+        <v>20.1445407867432</v>
       </c>
       <c r="H1125" t="n">
         <v>125202</v>
@@ -33110,7 +33110,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>20.1445388793945</v>
+        <v>20.1445407867432</v>
       </c>
       <c r="H1129" t="n">
         <v>52762</v>
@@ -33168,7 +33168,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558483123779</v>
+        <v>21.8558464050293</v>
       </c>
       <c r="H1131" t="n">
         <v>109080</v>
@@ -33284,7 +33284,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1135" t="n">
         <v>53815</v>
@@ -33400,7 +33400,7 @@
         <v>21.5</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1139" t="n">
         <v>34560</v>
@@ -33458,7 +33458,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>20.9757480621338</v>
+        <v>20.9757461547852</v>
       </c>
       <c r="H1141" t="n">
         <v>56787</v>
@@ -33516,7 +33516,7 @@
         <v>21.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1143" t="n">
         <v>34032</v>
@@ -33632,7 +33632,7 @@
         <v>21.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1147" t="n">
         <v>58527</v>
@@ -33719,7 +33719,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>20.1934337615967</v>
+        <v>20.193431854248</v>
       </c>
       <c r="H1150" t="n">
         <v>130761</v>
@@ -33748,7 +33748,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1151" t="n">
         <v>65290</v>
@@ -33777,7 +33777,7 @@
         <v>21</v>
       </c>
       <c r="G1152" t="n">
-        <v>20.5356960296631</v>
+        <v>20.5356941223145</v>
       </c>
       <c r="H1152" t="n">
         <v>77191</v>
@@ -33835,7 +33835,7 @@
         <v>23.75</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.2248935699463</v>
+        <v>23.2248954772949</v>
       </c>
       <c r="H1154" t="n">
         <v>149423</v>
@@ -33893,7 +33893,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0560989379883</v>
+        <v>24.0561008453369</v>
       </c>
       <c r="H1156" t="n">
         <v>205397</v>
@@ -34009,7 +34009,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.3226833343506</v>
+        <v>23.322681427002</v>
       </c>
       <c r="H1160" t="n">
         <v>31857</v>
@@ -34038,7 +34038,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7848415374756</v>
+        <v>22.7848434448242</v>
       </c>
       <c r="H1161" t="n">
         <v>56547</v>
@@ -34067,7 +34067,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359504699707</v>
+        <v>22.7359485626221</v>
       </c>
       <c r="H1162" t="n">
         <v>32829</v>
@@ -34096,7 +34096,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1163" t="n">
         <v>63588</v>
@@ -34125,7 +34125,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1164" t="n">
         <v>33009</v>
@@ -34241,7 +34241,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1168" t="n">
         <v>45591</v>
@@ -34299,7 +34299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1170" t="n">
         <v>119843</v>
@@ -34328,7 +34328,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1171" t="n">
         <v>50849</v>
@@ -34560,7 +34560,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1179" t="n">
         <v>25025</v>
@@ -34589,7 +34589,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1180" t="n">
         <v>34676</v>
@@ -34647,7 +34647,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.9047393798828</v>
+        <v>21.9047412872314</v>
       </c>
       <c r="H1182" t="n">
         <v>39901</v>
@@ -34705,7 +34705,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157962799072</v>
+        <v>21.4157943725586</v>
       </c>
       <c r="H1184" t="n">
         <v>21327</v>
@@ -34850,7 +34850,7 @@
         <v>21.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1189" t="n">
         <v>47664</v>
@@ -35082,7 +35082,7 @@
         <v>21.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1197" t="n">
         <v>53455</v>
@@ -35169,7 +35169,7 @@
         <v>21.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1200" t="n">
         <v>137704</v>
@@ -35256,7 +35256,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.2958984375</v>
+        <v>22.2958965301514</v>
       </c>
       <c r="H1203" t="n">
         <v>114554</v>
@@ -35343,7 +35343,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>20.1934337615967</v>
+        <v>20.193431854248</v>
       </c>
       <c r="H1206" t="n">
         <v>140178</v>
@@ -35401,7 +35401,7 @@
         <v>21.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1208" t="n">
         <v>60298</v>
@@ -35430,7 +35430,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401184082031</v>
+        <v>20.3401165008545</v>
       </c>
       <c r="H1209" t="n">
         <v>38491</v>
@@ -35517,7 +35517,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>20.0956439971924</v>
+        <v>20.0956420898438</v>
       </c>
       <c r="H1212" t="n">
         <v>26712</v>
@@ -35575,7 +35575,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1214" t="n">
         <v>61113</v>
@@ -35691,7 +35691,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.9978561401367</v>
+        <v>19.9978580474854</v>
       </c>
       <c r="H1218" t="n">
         <v>80159</v>
@@ -35720,7 +35720,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.7533836364746</v>
+        <v>19.753381729126</v>
       </c>
       <c r="H1219" t="n">
         <v>54410</v>
@@ -35749,7 +35749,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470928192139</v>
+        <v>19.1470909118652</v>
       </c>
       <c r="H1220" t="n">
         <v>78205</v>
@@ -35836,7 +35836,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.2669906616211</v>
+        <v>18.2669887542725</v>
       </c>
       <c r="H1223" t="n">
         <v>95192</v>
@@ -35923,7 +35923,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1226" t="n">
         <v>67839</v>
@@ -35981,7 +35981,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112106323242</v>
+        <v>16.3112087249756</v>
       </c>
       <c r="H1228" t="n">
         <v>66395</v>
@@ -36039,7 +36039,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>16.2329769134521</v>
+        <v>16.2329788208008</v>
       </c>
       <c r="H1230" t="n">
         <v>93368</v>
@@ -36068,7 +36068,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1231" t="n">
-        <v>16.1743068695068</v>
+        <v>16.1743049621582</v>
       </c>
       <c r="H1231" t="n">
         <v>45139</v>
@@ -36155,7 +36155,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348472595215</v>
+        <v>17.0348491668701</v>
       </c>
       <c r="H1234" t="n">
         <v>86836</v>
@@ -36300,7 +36300,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108669281006</v>
+        <v>17.2108688354492</v>
       </c>
       <c r="H1239" t="n">
         <v>157511</v>
@@ -36474,7 +36474,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.484676361084</v>
+        <v>17.4846744537354</v>
       </c>
       <c r="H1245" t="n">
         <v>68340</v>
@@ -36503,7 +36503,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979454040527</v>
+        <v>16.8979434967041</v>
       </c>
       <c r="H1246" t="n">
         <v>89023</v>
@@ -36590,7 +36590,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1249" t="n">
-        <v>16.8588275909424</v>
+        <v>16.858829498291</v>
       </c>
       <c r="H1249" t="n">
         <v>31565</v>
@@ -36648,7 +36648,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1251" t="n">
         <v>74074</v>
@@ -36851,7 +36851,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414798736572</v>
+        <v>16.7414817810059</v>
       </c>
       <c r="H1258" t="n">
         <v>87008</v>
@@ -80067,6 +80067,35 @@
         <v>4831</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>10.3400001525879</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>10.4200000762939</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>10.1400003433228</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>10.2600002288818</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>10.2600002288818</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>4604</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455717086792</v>
+        <v>6.71455669403076</v>
       </c>
       <c r="H3" t="n">
         <v>54991</v>
@@ -485,7 +485,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48499965667725</v>
+        <v>6.48500061035156</v>
       </c>
       <c r="H4" t="n">
         <v>46846</v>
@@ -514,7 +514,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44674015045166</v>
+        <v>6.4467396736145</v>
       </c>
       <c r="H5" t="n">
         <v>108929</v>
@@ -543,7 +543,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>6.27935457229614</v>
+        <v>6.2793550491333</v>
       </c>
       <c r="H6" t="n">
         <v>57520</v>
@@ -572,7 +572,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544902801514</v>
       </c>
       <c r="H7" t="n">
         <v>40228</v>
@@ -688,7 +688,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544902801514</v>
       </c>
       <c r="H11" t="n">
         <v>125780</v>
@@ -717,7 +717,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546102523804</v>
+        <v>5.70546054840088</v>
       </c>
       <c r="H12" t="n">
         <v>113455</v>
@@ -833,7 +833,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7485032081604</v>
+        <v>5.74850273132324</v>
       </c>
       <c r="H16" t="n">
         <v>99565</v>
@@ -891,7 +891,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.02588510513306</v>
+        <v>6.0258846282959</v>
       </c>
       <c r="H18" t="n">
         <v>66351</v>
@@ -920,7 +920,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38934993743896</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H19" t="n">
         <v>89617</v>
@@ -949,7 +949,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>6.00197315216064</v>
+        <v>6.00197267532349</v>
       </c>
       <c r="H20" t="n">
         <v>70672</v>
@@ -1036,7 +1036,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414781570435</v>
+        <v>5.9541482925415</v>
       </c>
       <c r="H23" t="n">
         <v>39858</v>
@@ -1094,7 +1094,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154443740845</v>
+        <v>5.79154491424561</v>
       </c>
       <c r="H25" t="n">
         <v>42499</v>
@@ -1123,7 +1123,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.70067834854126</v>
+        <v>5.7006778717041</v>
       </c>
       <c r="H26" t="n">
         <v>83256</v>
@@ -1152,7 +1152,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>5.27504062652588</v>
+        <v>5.27504014968872</v>
       </c>
       <c r="H27" t="n">
         <v>92262</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244876861572</v>
+        <v>4.78244829177856</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1210,7 +1210,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679216384888</v>
+        <v>4.90679168701172</v>
       </c>
       <c r="H29" t="n">
         <v>118336</v>
@@ -1239,7 +1239,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62941074371338</v>
+        <v>4.62940979003906</v>
       </c>
       <c r="H30" t="n">
         <v>67579</v>
@@ -1297,7 +1297,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.06461238861084</v>
+        <v>5.064612865448</v>
       </c>
       <c r="H32" t="n">
         <v>19857</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.83983755111694</v>
+        <v>4.83983707427979</v>
       </c>
       <c r="H33" t="n">
         <v>11060</v>
@@ -1355,7 +1355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.59546375274658</v>
+        <v>5.5954647064209</v>
       </c>
       <c r="H34" t="n">
         <v>87689</v>
@@ -1413,7 +1413,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677280426025</v>
+        <v>5.45677375793457</v>
       </c>
       <c r="H36" t="n">
         <v>102398</v>
@@ -1500,7 +1500,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.29417037963867</v>
+        <v>5.29416990280151</v>
       </c>
       <c r="H39" t="n">
         <v>54047</v>
@@ -1529,7 +1529,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460870742798</v>
+        <v>5.17460918426514</v>
       </c>
       <c r="H40" t="n">
         <v>27727</v>
@@ -1558,7 +1558,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>5.23678016662598</v>
+        <v>5.23678064346313</v>
       </c>
       <c r="H41" t="n">
         <v>122685</v>
@@ -1587,7 +1587,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069259643555</v>
+        <v>5.26069307327271</v>
       </c>
       <c r="H42" t="n">
         <v>79999</v>
@@ -1645,7 +1645,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844957351685</v>
+        <v>4.73844909667969</v>
       </c>
       <c r="H44" t="n">
         <v>146124</v>
@@ -1703,7 +1703,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028051376343</v>
+        <v>4.61028003692627</v>
       </c>
       <c r="H46" t="n">
         <v>40055</v>
@@ -1732,7 +1732,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749719619751</v>
+        <v>4.62749671936035</v>
       </c>
       <c r="H47" t="n">
         <v>92990</v>
@@ -1761,7 +1761,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G48" t="n">
-        <v>4.45915460586548</v>
+        <v>4.45915508270264</v>
       </c>
       <c r="H48" t="n">
         <v>57163</v>
@@ -1819,7 +1819,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984443664551</v>
+        <v>4.61984491348267</v>
       </c>
       <c r="H50" t="n">
         <v>32253</v>
@@ -1848,7 +1848,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671644210815</v>
+        <v>4.55671691894531</v>
       </c>
       <c r="H51" t="n">
         <v>33202</v>
@@ -1906,7 +1906,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G53" t="n">
-        <v>4.53184795379639</v>
+        <v>4.53184747695923</v>
       </c>
       <c r="H53" t="n">
         <v>41654</v>
@@ -1935,7 +1935,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G54" t="n">
-        <v>4.53184795379639</v>
+        <v>4.53184747695923</v>
       </c>
       <c r="H54" t="n">
         <v>15612</v>
@@ -1964,7 +1964,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G55" t="n">
-        <v>4.42280769348145</v>
+        <v>4.4228081703186</v>
       </c>
       <c r="H55" t="n">
         <v>73311</v>
@@ -1993,7 +1993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985275268555</v>
+        <v>4.39985179901123</v>
       </c>
       <c r="H56" t="n">
         <v>6922</v>
@@ -2109,7 +2109,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>4.0937762260437</v>
+        <v>4.09377574920654</v>
       </c>
       <c r="H60" t="n">
         <v>95284</v>
@@ -2138,7 +2138,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916885375977</v>
+        <v>4.01916980743408</v>
       </c>
       <c r="H61" t="n">
         <v>8387</v>
@@ -2167,7 +2167,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793968200684</v>
+        <v>4.39793872833252</v>
       </c>
       <c r="H62" t="n">
         <v>183307</v>
@@ -2312,7 +2312,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265079498291</v>
+        <v>3.94265031814575</v>
       </c>
       <c r="H67" t="n">
         <v>49492</v>
@@ -2370,7 +2370,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726409912109</v>
+        <v>3.79726362228394</v>
       </c>
       <c r="H69" t="n">
         <v>35741</v>
@@ -2399,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.8259584903717</v>
+        <v>3.82595872879028</v>
       </c>
       <c r="H70" t="n">
         <v>33705</v>
@@ -2428,7 +2428,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987460136414</v>
+        <v>3.73987436294556</v>
       </c>
       <c r="H71" t="n">
         <v>26533</v>
@@ -2515,7 +2515,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222279548645</v>
+        <v>3.73222231864929</v>
       </c>
       <c r="H74" t="n">
         <v>23567</v>
@@ -2544,7 +2544,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.84891414642334</v>
+        <v>3.8489146232605</v>
       </c>
       <c r="H75" t="n">
         <v>62408</v>
@@ -2573,7 +2573,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463863372803</v>
+        <v>4.29463815689087</v>
       </c>
       <c r="H76" t="n">
         <v>172014</v>
@@ -2631,7 +2631,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.45199108123779</v>
+        <v>5.45199060440063</v>
       </c>
       <c r="H78" t="n">
         <v>472702</v>
@@ -2660,7 +2660,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07896041870117</v>
+        <v>5.07895946502686</v>
       </c>
       <c r="H79" t="n">
         <v>724913</v>
@@ -2689,7 +2689,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851793289185</v>
+        <v>5.30851745605469</v>
       </c>
       <c r="H80" t="n">
         <v>273720</v>
@@ -2747,7 +2747,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>5.12200260162354</v>
+        <v>5.12200212478638</v>
       </c>
       <c r="H82" t="n">
         <v>94676</v>
@@ -2776,7 +2776,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.0550479888916</v>
+        <v>5.05504751205444</v>
       </c>
       <c r="H83" t="n">
         <v>85082</v>
@@ -2805,7 +2805,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417726516724</v>
+        <v>5.07417678833008</v>
       </c>
       <c r="H84" t="n">
         <v>122889</v>
@@ -2834,7 +2834,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>4.93548631668091</v>
+        <v>4.93548583984375</v>
       </c>
       <c r="H85" t="n">
         <v>71889</v>
@@ -2892,7 +2892,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653650283813</v>
+        <v>4.73653697967529</v>
       </c>
       <c r="H87" t="n">
         <v>101740</v>
@@ -2921,7 +2921,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680688858032</v>
+        <v>4.46680641174316</v>
       </c>
       <c r="H88" t="n">
         <v>98603</v>
@@ -3037,7 +3037,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559885025024</v>
+        <v>4.18559837341309</v>
       </c>
       <c r="H92" t="n">
         <v>40037</v>
@@ -3066,7 +3066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>4.18942499160767</v>
+        <v>4.18942451477051</v>
       </c>
       <c r="H93" t="n">
         <v>83730</v>
@@ -3095,7 +3095,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550792694092</v>
+        <v>4.27550888061523</v>
       </c>
       <c r="H94" t="n">
         <v>105195</v>
@@ -3182,7 +3182,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.11673164367676</v>
+        <v>4.1167311668396</v>
       </c>
       <c r="H97" t="n">
         <v>33027</v>
@@ -3211,7 +3211,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603349685669</v>
+        <v>4.17603397369385</v>
       </c>
       <c r="H98" t="n">
         <v>54021</v>
@@ -3240,7 +3240,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472860336304</v>
+        <v>4.20472812652588</v>
       </c>
       <c r="H99" t="n">
         <v>30978</v>
@@ -3269,7 +3269,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846382141113</v>
+        <v>4.29846477508545</v>
       </c>
       <c r="H100" t="n">
         <v>67373</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113876342773</v>
+        <v>4.92113924026489</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3385,7 +3385,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>5.04548215866089</v>
+        <v>5.04548311233521</v>
       </c>
       <c r="H104" t="n">
         <v>88307</v>
@@ -3414,7 +3414,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G105" t="n">
-        <v>5.40894889831543</v>
+        <v>5.40894985198975</v>
       </c>
       <c r="H105" t="n">
         <v>257471</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107570648193</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H106" t="n">
         <v>756136</v>
@@ -3472,7 +3472,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756669998169</v>
+        <v>7.74756622314453</v>
       </c>
       <c r="H107" t="n">
         <v>830490</v>
@@ -3530,7 +3530,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367635726929</v>
+        <v>7.06367540359497</v>
       </c>
       <c r="H109" t="n">
         <v>396366</v>
@@ -3559,7 +3559,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107570648193</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H110" t="n">
         <v>192489</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804183959961</v>
+        <v>6.52804088592529</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3704,7 +3704,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.38456869125366</v>
+        <v>6.3845682144165</v>
       </c>
       <c r="H115" t="n">
         <v>131401</v>
@@ -3820,7 +3820,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>5.87762880325317</v>
+        <v>5.87762975692749</v>
       </c>
       <c r="H119" t="n">
         <v>158117</v>
@@ -3907,7 +3907,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>6.74325275421143</v>
+        <v>6.74325227737427</v>
       </c>
       <c r="H122" t="n">
         <v>283137</v>
@@ -3994,7 +3994,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83936977386475</v>
+        <v>5.83936882019043</v>
       </c>
       <c r="H125" t="n">
         <v>111496</v>
@@ -4052,7 +4052,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40848016738892</v>
+        <v>6.40848064422607</v>
       </c>
       <c r="H127" t="n">
         <v>110989</v>
@@ -4081,7 +4081,7 @@
         <v>6.625</v>
       </c>
       <c r="G128" t="n">
-        <v>6.33674335479736</v>
+        <v>6.33674383163452</v>
       </c>
       <c r="H128" t="n">
         <v>31549</v>
@@ -4110,7 +4110,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.35109090805054</v>
+        <v>6.3510913848877</v>
       </c>
       <c r="H129" t="n">
         <v>59634</v>
@@ -4139,7 +4139,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.35109090805054</v>
+        <v>6.3510913848877</v>
       </c>
       <c r="H130" t="n">
         <v>59773</v>
@@ -4168,7 +4168,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38934993743896</v>
+        <v>6.38935089111328</v>
       </c>
       <c r="H131" t="n">
         <v>52660</v>
@@ -4255,7 +4255,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>6.63803863525391</v>
+        <v>6.63803815841675</v>
       </c>
       <c r="H134" t="n">
         <v>118333</v>
@@ -4371,7 +4371,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584781646729</v>
+        <v>7.12584733963013</v>
       </c>
       <c r="H138" t="n">
         <v>47644</v>
@@ -4400,7 +4400,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>6.96802663803101</v>
+        <v>6.96802711486816</v>
       </c>
       <c r="H139" t="n">
         <v>127471</v>
@@ -4458,7 +4458,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>6.95846271514893</v>
+        <v>6.95846223831177</v>
       </c>
       <c r="H141" t="n">
         <v>66133</v>
@@ -4603,7 +4603,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107570648193</v>
+        <v>6.79107618331909</v>
       </c>
       <c r="H146" t="n">
         <v>18313</v>
@@ -4632,7 +4632,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.92498397827148</v>
+        <v>6.92498445510864</v>
       </c>
       <c r="H147" t="n">
         <v>105405</v>
@@ -4719,7 +4719,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G150" t="n">
-        <v>6.69064521789551</v>
+        <v>6.69064474105835</v>
       </c>
       <c r="H150" t="n">
         <v>35920</v>
@@ -4748,7 +4748,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>6.85324811935425</v>
+        <v>6.85324764251709</v>
       </c>
       <c r="H151" t="n">
         <v>44123</v>
@@ -4777,7 +4777,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>6.95367956161499</v>
+        <v>6.95368003845215</v>
       </c>
       <c r="H152" t="n">
         <v>61634</v>
@@ -4835,7 +4835,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>7.03019857406616</v>
+        <v>7.03019905090332</v>
       </c>
       <c r="H154" t="n">
         <v>34070</v>
@@ -4864,7 +4864,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G155" t="n">
-        <v>7.03976440429688</v>
+        <v>7.03976392745972</v>
       </c>
       <c r="H155" t="n">
         <v>46790</v>
@@ -4922,7 +4922,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886470794678</v>
+        <v>7.93886423110962</v>
       </c>
       <c r="H157" t="n">
         <v>265495</v>
@@ -4951,7 +4951,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.0919017791748</v>
+        <v>8.09190368652344</v>
       </c>
       <c r="H158" t="n">
         <v>272541</v>
@@ -4980,7 +4980,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712789535522</v>
+        <v>7.86712741851807</v>
       </c>
       <c r="H159" t="n">
         <v>93100</v>
@@ -5009,7 +5009,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91016960144043</v>
+        <v>7.91017055511475</v>
       </c>
       <c r="H160" t="n">
         <v>57170</v>
@@ -5038,7 +5038,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.67104721069336</v>
+        <v>7.6710467338562</v>
       </c>
       <c r="H161" t="n">
         <v>97882</v>
@@ -5067,7 +5067,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G162" t="n">
-        <v>7.66626501083374</v>
+        <v>7.66626453399658</v>
       </c>
       <c r="H162" t="n">
         <v>71695</v>
@@ -5125,7 +5125,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234569549561</v>
+        <v>7.86234474182129</v>
       </c>
       <c r="H164" t="n">
         <v>30398</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626132965088</v>
+        <v>7.77626085281372</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.99625253677368</v>
+        <v>7.99625301361084</v>
       </c>
       <c r="H166" t="n">
         <v>48102</v>
@@ -5212,7 +5212,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712373733521</v>
+        <v>7.97712421417236</v>
       </c>
       <c r="H167" t="n">
         <v>31192</v>
@@ -5270,7 +5270,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060472488403</v>
+        <v>7.90060424804688</v>
       </c>
       <c r="H169" t="n">
         <v>42906</v>
@@ -5299,7 +5299,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.83364868164062</v>
+        <v>7.83364963531494</v>
       </c>
       <c r="H170" t="n">
         <v>41230</v>
@@ -5386,7 +5386,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.89582204818726</v>
+        <v>7.89582252502441</v>
       </c>
       <c r="H173" t="n">
         <v>38551</v>
@@ -5473,7 +5473,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>9.00535011291504</v>
+        <v>9.00535106658936</v>
       </c>
       <c r="H176" t="n">
         <v>166097</v>
@@ -5502,7 +5502,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622676849365</v>
+        <v>8.76622772216797</v>
       </c>
       <c r="H177" t="n">
         <v>231642</v>
@@ -5531,7 +5531,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65623188018799</v>
+        <v>8.65623092651367</v>
       </c>
       <c r="H178" t="n">
         <v>104419</v>
@@ -5618,7 +5618,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.41710948944092</v>
+        <v>8.4171085357666</v>
       </c>
       <c r="H181" t="n">
         <v>154982</v>
@@ -5705,7 +5705,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.2545051574707</v>
+        <v>8.25450611114502</v>
       </c>
       <c r="H184" t="n">
         <v>33220</v>
@@ -5734,7 +5734,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451620101929</v>
+        <v>7.92451667785645</v>
       </c>
       <c r="H185" t="n">
         <v>122464</v>
@@ -5792,7 +5792,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34058952331543</v>
+        <v>8.34059047698975</v>
       </c>
       <c r="H187" t="n">
         <v>63159</v>
@@ -5966,7 +5966,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101585388184</v>
+        <v>8.55101776123047</v>
       </c>
       <c r="H193" t="n">
         <v>104665</v>
@@ -5995,7 +5995,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92883110046387</v>
+        <v>8.92883014678955</v>
       </c>
       <c r="H194" t="n">
         <v>196106</v>
@@ -6024,7 +6024,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.0675220489502</v>
+        <v>9.06752109527588</v>
       </c>
       <c r="H195" t="n">
         <v>116469</v>
@@ -6053,7 +6053,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.10578060150146</v>
+        <v>9.1057825088501</v>
       </c>
       <c r="H196" t="n">
         <v>198688</v>
@@ -6082,7 +6082,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968887329102</v>
+        <v>9.23968982696533</v>
       </c>
       <c r="H197" t="n">
         <v>111328</v>
@@ -6111,7 +6111,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317497253418</v>
+        <v>9.05317401885986</v>
       </c>
       <c r="H198" t="n">
         <v>156638</v>
@@ -6140,7 +6140,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708229064941</v>
+        <v>9.18708324432373</v>
       </c>
       <c r="H199" t="n">
         <v>82966</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.13447666168213</v>
+        <v>9.13447570800781</v>
       </c>
       <c r="H201" t="n">
         <v>49199</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6314,7 +6314,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>9.51707172393799</v>
+        <v>9.5170726776123</v>
       </c>
       <c r="H205" t="n">
         <v>125905</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489658355713</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6430,7 +6430,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587827682495</v>
+        <v>10.3587837219238</v>
       </c>
       <c r="H209" t="n">
         <v>324694</v>
@@ -6459,7 +6459,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>10.473560333252</v>
+        <v>10.4735612869263</v>
       </c>
       <c r="H210" t="n">
         <v>301050</v>
@@ -6488,7 +6488,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.2535676956177</v>
+        <v>10.253568649292</v>
       </c>
       <c r="H211" t="n">
         <v>105355</v>
@@ -6633,7 +6633,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518060684204</v>
+        <v>10.9518051147461</v>
       </c>
       <c r="H216" t="n">
         <v>101398</v>
@@ -6720,7 +6720,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831275939941</v>
+        <v>10.4831266403198</v>
       </c>
       <c r="H219" t="n">
         <v>128669</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692110061646</v>
+        <v>10.5692100524902</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6778,7 +6778,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8274631500244</v>
+        <v>10.8274621963501</v>
       </c>
       <c r="H221" t="n">
         <v>165457</v>
@@ -6836,7 +6836,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.9613723754883</v>
+        <v>10.9613704681396</v>
       </c>
       <c r="H223" t="n">
         <v>86558</v>
@@ -6894,7 +6894,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630962371826</v>
+        <v>11.3630971908569</v>
       </c>
       <c r="H225" t="n">
         <v>187509</v>
@@ -6923,7 +6923,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117839813232</v>
+        <v>11.6117858886719</v>
       </c>
       <c r="H226" t="n">
         <v>191398</v>
@@ -6981,7 +6981,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456912994385</v>
+        <v>11.7456932067871</v>
       </c>
       <c r="H228" t="n">
         <v>176751</v>
@@ -7097,7 +7097,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708990097046</v>
+        <v>12.0708980560303</v>
       </c>
       <c r="H232" t="n">
         <v>161563</v>
@@ -7155,7 +7155,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H234" t="n">
         <v>153081</v>
@@ -7184,7 +7184,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H235" t="n">
         <v>95580</v>
@@ -7271,7 +7271,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839527130127</v>
+        <v>11.7839508056641</v>
       </c>
       <c r="H238" t="n">
         <v>75176</v>
@@ -7329,7 +7329,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.6160974502563</v>
+        <v>12.616096496582</v>
       </c>
       <c r="H240" t="n">
         <v>180021</v>
@@ -7358,7 +7358,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.8169603347778</v>
+        <v>12.8169612884521</v>
       </c>
       <c r="H241" t="n">
         <v>122373</v>
@@ -7416,7 +7416,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H243" t="n">
         <v>303111</v>
@@ -7445,7 +7445,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446565628052</v>
+        <v>15.2446575164795</v>
       </c>
       <c r="H244" t="n">
         <v>256881</v>
@@ -7474,7 +7474,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.0385932922363</v>
+        <v>14.038592338562</v>
       </c>
       <c r="H245" t="n">
         <v>494015</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272207260132</v>
+        <v>13.5272226333618</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7619,7 +7619,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G250" t="n">
-        <v>13.430736541748</v>
+        <v>13.4307355880737</v>
       </c>
       <c r="H250" t="n">
         <v>48278</v>
@@ -7706,7 +7706,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772548675537</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H253" t="n">
         <v>84013</v>
@@ -7793,7 +7793,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G256" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H256" t="n">
         <v>44658</v>
@@ -7822,7 +7822,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000663757324</v>
       </c>
       <c r="H257" t="n">
         <v>36672</v>
@@ -7851,7 +7851,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H258" t="n">
         <v>48422</v>
@@ -7938,7 +7938,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.9869041442871</v>
+        <v>12.9869031906128</v>
       </c>
       <c r="H261" t="n">
         <v>30726</v>
@@ -7967,7 +7967,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772548675537</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H262" t="n">
         <v>39442</v>
@@ -8025,7 +8025,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G264" t="n">
-        <v>14.1061325073242</v>
+        <v>14.1061315536499</v>
       </c>
       <c r="H264" t="n">
         <v>227402</v>
@@ -8054,7 +8054,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877311706543</v>
+        <v>13.7877321243286</v>
       </c>
       <c r="H265" t="n">
         <v>225704</v>
@@ -8141,7 +8141,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>13.835973739624</v>
+        <v>13.8359727859497</v>
       </c>
       <c r="H268" t="n">
         <v>66219</v>
@@ -8170,7 +8170,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G269" t="n">
-        <v>13.585111618042</v>
+        <v>13.5851125717163</v>
       </c>
       <c r="H269" t="n">
         <v>52002</v>
@@ -8199,7 +8199,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G270" t="n">
-        <v>13.3921432495117</v>
+        <v>13.3921422958374</v>
       </c>
       <c r="H270" t="n">
         <v>69772</v>
@@ -8228,7 +8228,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H271" t="n">
         <v>92437</v>
@@ -8286,7 +8286,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H273" t="n">
         <v>167282</v>
@@ -8315,7 +8315,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G274" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H274" t="n">
         <v>91826</v>
@@ -8344,7 +8344,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869733810425</v>
+        <v>11.8869724273682</v>
       </c>
       <c r="H275" t="n">
         <v>94457</v>
@@ -8373,7 +8373,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>11.288763999939</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H276" t="n">
         <v>199685</v>
@@ -8460,7 +8460,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3756008148193</v>
+        <v>11.3756017684937</v>
       </c>
       <c r="H279" t="n">
         <v>165236</v>
@@ -8547,7 +8547,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>11.8676767349243</v>
+        <v>11.86767578125</v>
       </c>
       <c r="H282" t="n">
         <v>117391</v>
@@ -8576,7 +8576,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>11.288763999939</v>
+        <v>11.2887649536133</v>
       </c>
       <c r="H283" t="n">
         <v>93658</v>
@@ -8634,7 +8634,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063402175903</v>
       </c>
       <c r="H285" t="n">
         <v>135254</v>
@@ -8663,7 +8663,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>10.6809091567993</v>
+        <v>10.680908203125</v>
       </c>
       <c r="H286" t="n">
         <v>57845</v>
@@ -8692,7 +8692,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484493255615</v>
+        <v>10.7484474182129</v>
       </c>
       <c r="H287" t="n">
         <v>33613</v>
@@ -8750,7 +8750,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431409835815</v>
+        <v>11.4431400299072</v>
       </c>
       <c r="H289" t="n">
         <v>181496</v>
@@ -8779,7 +8779,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.2501697540283</v>
+        <v>11.2501707077026</v>
       </c>
       <c r="H290" t="n">
         <v>53729</v>
@@ -8808,7 +8808,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>11.1922798156738</v>
+        <v>11.1922807693481</v>
       </c>
       <c r="H291" t="n">
         <v>17482</v>
@@ -8866,7 +8866,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G293" t="n">
-        <v>10.8159866333008</v>
+        <v>10.8159875869751</v>
       </c>
       <c r="H293" t="n">
         <v>37146</v>
@@ -8895,7 +8895,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.008957862854</v>
+        <v>11.0089588165283</v>
       </c>
       <c r="H294" t="n">
         <v>9802</v>
@@ -8953,7 +8953,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072355270386</v>
+        <v>10.5072345733643</v>
       </c>
       <c r="H296" t="n">
         <v>45140</v>
@@ -9011,7 +9011,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247396469116</v>
+        <v>11.1247406005859</v>
       </c>
       <c r="H298" t="n">
         <v>108006</v>
@@ -9069,7 +9069,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685710906982</v>
+        <v>11.5685729980469</v>
       </c>
       <c r="H300" t="n">
         <v>224596</v>
@@ -9156,7 +9156,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G303" t="n">
-        <v>11.7132997512817</v>
+        <v>11.7133007049561</v>
       </c>
       <c r="H303" t="n">
         <v>115357</v>
@@ -9214,7 +9214,7 @@
         <v>12.5</v>
       </c>
       <c r="G305" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H305" t="n">
         <v>194476</v>
@@ -9272,7 +9272,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5878686904907</v>
+        <v>11.587869644165</v>
       </c>
       <c r="H307" t="n">
         <v>49320</v>
@@ -9359,7 +9359,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>11.1922798156738</v>
+        <v>11.1922807693481</v>
       </c>
       <c r="H310" t="n">
         <v>41614</v>
@@ -9388,7 +9388,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212257385254</v>
+        <v>11.2212247848511</v>
       </c>
       <c r="H311" t="n">
         <v>48985</v>
@@ -9475,7 +9475,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>11.5299787521362</v>
+        <v>11.5299777984619</v>
       </c>
       <c r="H314" t="n">
         <v>80574</v>
@@ -9504,7 +9504,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334936141968</v>
+        <v>11.4334945678711</v>
       </c>
       <c r="H315" t="n">
         <v>31751</v>
@@ -9533,7 +9533,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H316" t="n">
         <v>113990</v>
@@ -9562,7 +9562,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H317" t="n">
         <v>48953</v>
@@ -9591,7 +9591,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220518112183</v>
+        <v>12.0220527648926</v>
       </c>
       <c r="H318" t="n">
         <v>61490</v>
@@ -9620,7 +9620,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>12.0606460571289</v>
+        <v>12.0606470108032</v>
       </c>
       <c r="H319" t="n">
         <v>41274</v>
@@ -9649,7 +9649,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G320" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H320" t="n">
         <v>53946</v>
@@ -9678,7 +9678,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>12.0027542114258</v>
+        <v>12.0027551651001</v>
       </c>
       <c r="H321" t="n">
         <v>47231</v>
@@ -9707,7 +9707,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G322" t="n">
-        <v>12.0027542114258</v>
+        <v>12.0027551651001</v>
       </c>
       <c r="H322" t="n">
         <v>26238</v>
@@ -9794,7 +9794,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640926361084</v>
+        <v>13.0640916824341</v>
       </c>
       <c r="H325" t="n">
         <v>437770</v>
@@ -9852,7 +9852,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G327" t="n">
-        <v>13.6140565872192</v>
+        <v>13.6140575408936</v>
       </c>
       <c r="H327" t="n">
         <v>135660</v>
@@ -9881,7 +9881,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H328" t="n">
         <v>133226</v>
@@ -9910,7 +9910,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>13.4693307876587</v>
+        <v>13.4693298339844</v>
       </c>
       <c r="H329" t="n">
         <v>64109</v>
@@ -9939,7 +9939,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H330" t="n">
         <v>80883</v>
@@ -9997,7 +9997,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G332" t="n">
-        <v>13.430736541748</v>
+        <v>13.4307355880737</v>
       </c>
       <c r="H332" t="n">
         <v>75116</v>
@@ -10026,7 +10026,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886264801025</v>
+        <v>13.4886255264282</v>
       </c>
       <c r="H333" t="n">
         <v>19569</v>
@@ -10055,7 +10055,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.710542678833</v>
+        <v>13.7105417251587</v>
       </c>
       <c r="H334" t="n">
         <v>74737</v>
@@ -10084,7 +10084,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631963729858</v>
+        <v>13.3631973266602</v>
       </c>
       <c r="H335" t="n">
         <v>56318</v>
@@ -10113,7 +10113,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H336" t="n">
         <v>66093</v>
@@ -10142,7 +10142,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552713394165</v>
+        <v>13.8552694320679</v>
       </c>
       <c r="H337" t="n">
         <v>35661</v>
@@ -10229,7 +10229,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807014465332</v>
+        <v>13.9807004928589</v>
       </c>
       <c r="H340" t="n">
         <v>101573</v>
@@ -10287,7 +10287,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>14.7815275192261</v>
+        <v>14.7815284729004</v>
       </c>
       <c r="H342" t="n">
         <v>193154</v>
@@ -10316,7 +10316,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.4920740127563</v>
+        <v>14.492073059082</v>
       </c>
       <c r="H343" t="n">
         <v>175404</v>
@@ -10345,7 +10345,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H344" t="n">
         <v>84729</v>
@@ -10374,7 +10374,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G345" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H345" t="n">
         <v>53819</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.569260597229</v>
+        <v>14.5692615509033</v>
       </c>
       <c r="H346" t="n">
         <v>63786</v>
@@ -10432,7 +10432,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G347" t="n">
-        <v>14.5789098739624</v>
+        <v>14.5789089202881</v>
       </c>
       <c r="H347" t="n">
         <v>26791</v>
@@ -10461,7 +10461,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.5113706588745</v>
+        <v>14.5113697052002</v>
       </c>
       <c r="H348" t="n">
         <v>81697</v>
@@ -10490,7 +10490,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052362442017</v>
+        <v>14.4052352905273</v>
       </c>
       <c r="H349" t="n">
         <v>73630</v>
@@ -10519,7 +10519,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824237823486</v>
+        <v>14.4824247360229</v>
       </c>
       <c r="H350" t="n">
         <v>97965</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527210235596</v>
+        <v>12.5527219772339</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10635,7 +10635,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386615753174</v>
+        <v>12.9386625289917</v>
       </c>
       <c r="H354" t="n">
         <v>113586</v>
@@ -10664,7 +10664,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.8807706832886</v>
+        <v>12.8807697296143</v>
       </c>
       <c r="H355" t="n">
         <v>60981</v>
@@ -10693,7 +10693,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000663757324</v>
       </c>
       <c r="H356" t="n">
         <v>42754</v>
@@ -10722,7 +10722,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G357" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H357" t="n">
         <v>55254</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.0062017440796</v>
+        <v>13.006199836731</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10780,7 +10780,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.0447969436646</v>
+        <v>13.0447959899902</v>
       </c>
       <c r="H359" t="n">
         <v>27096</v>
@@ -10867,7 +10867,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G362" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H362" t="n">
         <v>25549</v>
@@ -10896,7 +10896,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H363" t="n">
         <v>24673</v>
@@ -10925,7 +10925,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H364" t="n">
         <v>31128</v>
@@ -11070,7 +11070,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H369" t="n">
         <v>33590</v>
@@ -11099,7 +11099,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H370" t="n">
         <v>58049</v>
@@ -11244,7 +11244,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474838256836</v>
+        <v>12.1474828720093</v>
       </c>
       <c r="H375" t="n">
         <v>32852</v>
@@ -11302,7 +11302,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H377" t="n">
         <v>54450</v>
@@ -11331,7 +11331,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176406860352</v>
+        <v>12.4176425933838</v>
       </c>
       <c r="H378" t="n">
         <v>61237</v>
@@ -11360,7 +11360,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H379" t="n">
         <v>11240</v>
@@ -11389,7 +11389,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1571321487427</v>
+        <v>12.1571311950684</v>
       </c>
       <c r="H380" t="n">
         <v>38689</v>
@@ -11418,7 +11418,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H381" t="n">
         <v>64542</v>
@@ -11621,7 +11621,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H388" t="n">
         <v>47918</v>
@@ -11650,7 +11650,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966217041016</v>
+        <v>11.8966207504272</v>
       </c>
       <c r="H389" t="n">
         <v>33102</v>
@@ -11708,7 +11708,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H391" t="n">
         <v>36167</v>
@@ -11737,7 +11737,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>12.1281852722168</v>
+        <v>12.1281862258911</v>
       </c>
       <c r="H392" t="n">
         <v>25249</v>
@@ -11795,7 +11795,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545125961304</v>
+        <v>11.9545135498047</v>
       </c>
       <c r="H394" t="n">
         <v>7832</v>
@@ -11853,7 +11853,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.2439680099487</v>
+        <v>12.243968963623</v>
       </c>
       <c r="H396" t="n">
         <v>21900</v>
@@ -11882,7 +11882,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H397" t="n">
         <v>62135</v>
@@ -11911,7 +11911,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G398" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H398" t="n">
         <v>107931</v>
@@ -12027,7 +12027,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H402" t="n">
         <v>31655</v>
@@ -12085,7 +12085,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H404" t="n">
         <v>9320</v>
@@ -12114,7 +12114,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>12.8228788375854</v>
+        <v>12.8228797912598</v>
       </c>
       <c r="H405" t="n">
         <v>47428</v>
@@ -12172,7 +12172,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772548675537</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H407" t="n">
         <v>26025</v>
@@ -12288,7 +12288,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>13.0447969436646</v>
+        <v>13.0447959899902</v>
       </c>
       <c r="H411" t="n">
         <v>52341</v>
@@ -12346,7 +12346,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G413" t="n">
-        <v>12.9097156524658</v>
+        <v>12.9097166061401</v>
       </c>
       <c r="H413" t="n">
         <v>52102</v>
@@ -12375,7 +12375,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115081787109</v>
+        <v>12.3115072250366</v>
       </c>
       <c r="H414" t="n">
         <v>76954</v>
@@ -12433,7 +12433,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G416" t="n">
-        <v>13.09303855896</v>
+        <v>13.0930376052856</v>
       </c>
       <c r="H416" t="n">
         <v>51186</v>
@@ -12462,7 +12462,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H417" t="n">
         <v>19263</v>
@@ -12491,7 +12491,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193658828735</v>
+        <v>12.9193639755249</v>
       </c>
       <c r="H418" t="n">
         <v>10876</v>
@@ -12520,7 +12520,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G419" t="n">
-        <v>12.9869041442871</v>
+        <v>12.9869031906128</v>
       </c>
       <c r="H419" t="n">
         <v>4823</v>
@@ -12578,7 +12578,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772548675537</v>
+        <v>12.9772567749023</v>
       </c>
       <c r="H421" t="n">
         <v>36559</v>
@@ -12636,7 +12636,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>12.8904180526733</v>
+        <v>12.8904190063477</v>
       </c>
       <c r="H423" t="n">
         <v>19497</v>
@@ -12723,7 +12723,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5334243774414</v>
+        <v>12.5334234237671</v>
       </c>
       <c r="H426" t="n">
         <v>25449</v>
@@ -12752,7 +12752,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>12.8807706832886</v>
+        <v>12.8807697296143</v>
       </c>
       <c r="H427" t="n">
         <v>13721</v>
@@ -12926,7 +12926,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>13.179874420166</v>
+        <v>13.1798753738403</v>
       </c>
       <c r="H433" t="n">
         <v>273024</v>
@@ -12984,7 +12984,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>13.9324579238892</v>
+        <v>13.9324588775635</v>
       </c>
       <c r="H435" t="n">
         <v>95509</v>
@@ -13042,7 +13042,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H437" t="n">
         <v>115869</v>
@@ -13129,7 +13129,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720176696777</v>
+        <v>12.5720167160034</v>
       </c>
       <c r="H440" t="n">
         <v>33681</v>
@@ -13187,7 +13187,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G442" t="n">
-        <v>12.7553396224976</v>
+        <v>12.7553405761719</v>
       </c>
       <c r="H442" t="n">
         <v>23233</v>
@@ -13216,7 +13216,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>12.6395578384399</v>
+        <v>12.6395568847656</v>
       </c>
       <c r="H443" t="n">
         <v>19797</v>
@@ -13332,7 +13332,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202602386475</v>
       </c>
       <c r="H447" t="n">
         <v>14428</v>
@@ -13477,7 +13477,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3693981170654</v>
+        <v>12.3693990707397</v>
       </c>
       <c r="H452" t="n">
         <v>28539</v>
@@ -13535,7 +13535,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.8676767349243</v>
+        <v>11.86767578125</v>
       </c>
       <c r="H454" t="n">
         <v>101981</v>
@@ -13564,7 +13564,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H455" t="n">
         <v>45659</v>
@@ -13593,7 +13593,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H456" t="n">
         <v>40685</v>
@@ -13622,7 +13622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H457" t="n">
         <v>24461</v>
@@ -13651,7 +13651,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>12.2536172866821</v>
+        <v>12.2536163330078</v>
       </c>
       <c r="H458" t="n">
         <v>49613</v>
@@ -13680,7 +13680,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>12.3501014709473</v>
+        <v>12.3501024246216</v>
       </c>
       <c r="H459" t="n">
         <v>27238</v>
@@ -13709,7 +13709,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>12.446587562561</v>
+        <v>12.4465866088867</v>
       </c>
       <c r="H460" t="n">
         <v>60559</v>
@@ -13854,7 +13854,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G465" t="n">
-        <v>11.9352149963379</v>
+        <v>11.9352159500122</v>
       </c>
       <c r="H465" t="n">
         <v>21056</v>
@@ -13883,7 +13883,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H466" t="n">
         <v>20941</v>
@@ -13941,7 +13941,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H468" t="n">
         <v>13736</v>
@@ -14028,7 +14028,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3308038711548</v>
+        <v>12.3308048248291</v>
       </c>
       <c r="H471" t="n">
         <v>21463</v>
@@ -14144,7 +14144,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124034881592</v>
+        <v>12.0124025344849</v>
       </c>
       <c r="H475" t="n">
         <v>13507</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554637908936</v>
+        <v>9.45554733276367</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14347,7 +14347,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G482" t="n">
-        <v>9.85113716125488</v>
+        <v>9.85113620758057</v>
       </c>
       <c r="H482" t="n">
         <v>95444</v>
@@ -14376,7 +14376,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923480987549</v>
+        <v>10.0923490524292</v>
       </c>
       <c r="H483" t="n">
         <v>75251</v>
@@ -14405,7 +14405,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625078201294</v>
+        <v>10.3625068664551</v>
       </c>
       <c r="H484" t="n">
         <v>99264</v>
@@ -14492,7 +14492,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.806339263916</v>
+        <v>10.8063402175903</v>
       </c>
       <c r="H487" t="n">
         <v>73996</v>
@@ -14550,7 +14550,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.7195024490356</v>
+        <v>10.71950340271</v>
       </c>
       <c r="H489" t="n">
         <v>62047</v>
@@ -14637,7 +14637,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>10.9028234481812</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H492" t="n">
         <v>50334</v>
@@ -14666,7 +14666,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256359100342</v>
+        <v>10.8256368637085</v>
       </c>
       <c r="H493" t="n">
         <v>48038</v>
@@ -14695,7 +14695,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G494" t="n">
-        <v>10.9028234481812</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H494" t="n">
         <v>56326</v>
@@ -14724,7 +14724,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G495" t="n">
-        <v>10.8159866333008</v>
+        <v>10.8159875869751</v>
       </c>
       <c r="H495" t="n">
         <v>55815</v>
@@ -14753,7 +14753,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G496" t="n">
-        <v>10.9028234481812</v>
+        <v>10.9028244018555</v>
       </c>
       <c r="H496" t="n">
         <v>116291</v>
@@ -14782,7 +14782,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7387990951538</v>
+        <v>10.7388000488281</v>
       </c>
       <c r="H497" t="n">
         <v>62706</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078971862793</v>
+        <v>10.7078981399536</v>
       </c>
       <c r="H500" t="n">
         <v>97230</v>
@@ -14898,7 +14898,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G501" t="n">
-        <v>10.4732046127319</v>
+        <v>10.4732036590576</v>
       </c>
       <c r="H501" t="n">
         <v>197020</v>
@@ -14956,7 +14956,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189531326294</v>
+        <v>10.2189521789551</v>
       </c>
       <c r="H503" t="n">
         <v>87325</v>
@@ -14985,7 +14985,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612154006958</v>
+        <v>10.5612144470215</v>
       </c>
       <c r="H504" t="n">
         <v>62409</v>
@@ -15043,7 +15043,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4536457061768</v>
+        <v>10.4536466598511</v>
       </c>
       <c r="H506" t="n">
         <v>53759</v>
@@ -15072,7 +15072,7 @@
         <v>10.75</v>
       </c>
       <c r="G507" t="n">
-        <v>10.5123205184937</v>
+        <v>10.5123195648193</v>
       </c>
       <c r="H507" t="n">
         <v>171168</v>
@@ -15188,7 +15188,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G511" t="n">
-        <v>10.580771446228</v>
+        <v>10.5807723999023</v>
       </c>
       <c r="H511" t="n">
         <v>29173</v>
@@ -15217,7 +15217,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G512" t="n">
-        <v>10.6394462585449</v>
+        <v>10.6394453048706</v>
       </c>
       <c r="H512" t="n">
         <v>86952</v>
@@ -15246,7 +15246,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H513" t="n">
         <v>68123</v>
@@ -15275,7 +15275,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763509750366</v>
+        <v>10.7763500213623</v>
       </c>
       <c r="H514" t="n">
         <v>22557</v>
@@ -15304,7 +15304,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H515" t="n">
         <v>114765</v>
@@ -15362,7 +15362,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.011043548584</v>
+        <v>11.0110454559326</v>
       </c>
       <c r="H517" t="n">
         <v>116880</v>
@@ -15391,7 +15391,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G518" t="n">
-        <v>10.8350229263306</v>
+        <v>10.8350238800049</v>
       </c>
       <c r="H518" t="n">
         <v>27320</v>
@@ -15420,7 +15420,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G519" t="n">
-        <v>10.7372341156006</v>
+        <v>10.7372350692749</v>
       </c>
       <c r="H519" t="n">
         <v>53671</v>
@@ -15449,7 +15449,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763509750366</v>
+        <v>10.7763500213623</v>
       </c>
       <c r="H520" t="n">
         <v>17838</v>
@@ -15507,7 +15507,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>10.8350229263306</v>
+        <v>10.8350238800049</v>
       </c>
       <c r="H522" t="n">
         <v>64785</v>
@@ -15536,7 +15536,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>10.9132556915283</v>
+        <v>10.913254737854</v>
       </c>
       <c r="H523" t="n">
         <v>102971</v>
@@ -15565,7 +15565,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>10.9328136444092</v>
+        <v>10.9328126907349</v>
       </c>
       <c r="H524" t="n">
         <v>31611</v>
@@ -15594,7 +15594,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G525" t="n">
-        <v>10.9132556915283</v>
+        <v>10.913254737854</v>
       </c>
       <c r="H525" t="n">
         <v>37350</v>
@@ -15652,7 +15652,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G527" t="n">
-        <v>10.9132556915283</v>
+        <v>10.913254737854</v>
       </c>
       <c r="H527" t="n">
         <v>77485</v>
@@ -15768,7 +15768,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G531" t="n">
-        <v>10.9132556915283</v>
+        <v>10.913254737854</v>
       </c>
       <c r="H531" t="n">
         <v>20633</v>
@@ -15797,7 +15797,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H532" t="n">
         <v>61309</v>
@@ -15826,7 +15826,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G533" t="n">
-        <v>10.6394462585449</v>
+        <v>10.6394453048706</v>
       </c>
       <c r="H533" t="n">
         <v>37510</v>
@@ -15855,7 +15855,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634246826172</v>
+        <v>10.4634256362915</v>
       </c>
       <c r="H534" t="n">
         <v>20572</v>
@@ -15884,7 +15884,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069639205933</v>
+        <v>10.3069629669189</v>
       </c>
       <c r="H535" t="n">
         <v>59740</v>
@@ -15942,7 +15942,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G537" t="n">
-        <v>9.81801891326904</v>
+        <v>9.81801795959473</v>
       </c>
       <c r="H537" t="n">
         <v>66947</v>
@@ -16087,7 +16087,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H542" t="n">
         <v>15487</v>
@@ -16116,7 +16116,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H543" t="n">
         <v>21472</v>
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H545" t="n">
         <v>37787</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H546" t="n">
         <v>15589</v>
@@ -16232,7 +16232,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509357452393</v>
+        <v>9.50509262084961</v>
       </c>
       <c r="H547" t="n">
         <v>11946</v>
@@ -16261,7 +16261,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619869232178</v>
+        <v>9.45619964599609</v>
       </c>
       <c r="H548" t="n">
         <v>15955</v>
@@ -16290,7 +16290,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H549" t="n">
         <v>23576</v>
@@ -16377,7 +16377,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H552" t="n">
         <v>45912</v>
@@ -16406,7 +16406,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H553" t="n">
         <v>22573</v>
@@ -16435,7 +16435,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233722686768</v>
+        <v>8.74233913421631</v>
       </c>
       <c r="H554" t="n">
         <v>94454</v>
@@ -16464,7 +16464,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432834625244</v>
+        <v>8.65432929992676</v>
       </c>
       <c r="H555" t="n">
         <v>68485</v>
@@ -16580,7 +16580,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H559" t="n">
         <v>111011</v>
@@ -16609,7 +16609,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.87669086456299</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H560" t="n">
         <v>77526</v>
@@ -16638,7 +16638,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>9.65177726745605</v>
+        <v>9.65177631378174</v>
       </c>
       <c r="H561" t="n">
         <v>47843</v>
@@ -16667,7 +16667,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H562" t="n">
         <v>31267</v>
@@ -16696,7 +16696,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172714233398</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H563" t="n">
         <v>28072</v>
@@ -16725,7 +16725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H564" t="n">
         <v>46125</v>
@@ -16754,7 +16754,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H565" t="n">
         <v>31639</v>
@@ -16783,7 +16783,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H566" t="n">
         <v>45222</v>
@@ -16812,7 +16812,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H567" t="n">
         <v>124458</v>
@@ -16870,7 +16870,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H569" t="n">
         <v>170656</v>
@@ -17044,7 +17044,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H575" t="n">
         <v>94106</v>
@@ -17073,7 +17073,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G576" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H576" t="n">
         <v>88350</v>
@@ -17160,7 +17160,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H579" t="n">
         <v>84921</v>
@@ -17189,7 +17189,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G580" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H580" t="n">
         <v>59969</v>
@@ -17305,7 +17305,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H584" t="n">
         <v>44575</v>
@@ -17363,7 +17363,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H586" t="n">
         <v>19894</v>
@@ -17392,7 +17392,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946296691895</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H587" t="n">
         <v>46974</v>
@@ -17450,7 +17450,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H589" t="n">
         <v>44363</v>
@@ -17479,7 +17479,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H590" t="n">
         <v>85332</v>
@@ -17537,7 +17537,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>8.89880180358887</v>
+        <v>8.89880084991455</v>
       </c>
       <c r="H592" t="n">
         <v>73245</v>
@@ -17595,7 +17595,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G594" t="n">
-        <v>9.31929397583008</v>
+        <v>9.31929302215576</v>
       </c>
       <c r="H594" t="n">
         <v>58404</v>
@@ -17624,7 +17624,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H595" t="n">
         <v>58894</v>
@@ -17653,7 +17653,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H596" t="n">
         <v>110779</v>
@@ -17711,7 +17711,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.87669086456299</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H598" t="n">
         <v>140106</v>
@@ -17740,7 +17740,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H599" t="n">
         <v>76971</v>
@@ -17856,7 +17856,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492362976074</v>
+        <v>9.95492267608643</v>
       </c>
       <c r="H603" t="n">
         <v>63044</v>
@@ -17914,7 +17914,7 @@
         <v>9.75</v>
       </c>
       <c r="G605" t="n">
-        <v>9.5344295501709</v>
+        <v>9.53443050384521</v>
       </c>
       <c r="H605" t="n">
         <v>44042</v>
@@ -17943,7 +17943,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H606" t="n">
         <v>38965</v>
@@ -18001,7 +18001,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H608" t="n">
         <v>28857</v>
@@ -18030,7 +18030,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81801891326904</v>
+        <v>9.81801795959473</v>
       </c>
       <c r="H609" t="n">
         <v>8881</v>
@@ -18088,7 +18088,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H611" t="n">
         <v>15971</v>
@@ -18117,7 +18117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H612" t="n">
         <v>14746</v>
@@ -18146,7 +18146,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G613" t="n">
-        <v>9.34862995147705</v>
+        <v>9.34863090515137</v>
       </c>
       <c r="H613" t="n">
         <v>29288</v>
@@ -18175,7 +18175,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172714233398</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H614" t="n">
         <v>134678</v>
@@ -18233,7 +18233,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H616" t="n">
         <v>118933</v>
@@ -18291,7 +18291,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H618" t="n">
         <v>16473</v>
@@ -18349,7 +18349,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G620" t="n">
-        <v>9.55398845672607</v>
+        <v>9.55398750305176</v>
       </c>
       <c r="H620" t="n">
         <v>270273</v>
@@ -18378,7 +18378,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H621" t="n">
         <v>192357</v>
@@ -18436,7 +18436,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G623" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H623" t="n">
         <v>113503</v>
@@ -18465,7 +18465,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.87669086456299</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H624" t="n">
         <v>136644</v>
@@ -18494,7 +18494,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H625" t="n">
         <v>69374</v>
@@ -18552,7 +18552,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H627" t="n">
         <v>11623</v>
@@ -18581,7 +18581,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>9.69089317321777</v>
+        <v>9.69089221954346</v>
       </c>
       <c r="H628" t="n">
         <v>41089</v>
@@ -18697,7 +18697,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H632" t="n">
         <v>43105</v>
@@ -18784,7 +18784,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G635" t="n">
-        <v>8.89880180358887</v>
+        <v>8.89880084991455</v>
       </c>
       <c r="H635" t="n">
         <v>46972</v>
@@ -18813,7 +18813,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233722686768</v>
+        <v>8.74233913421631</v>
       </c>
       <c r="H636" t="n">
         <v>26549</v>
@@ -18842,7 +18842,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548454284668</v>
+        <v>9.04548358917236</v>
       </c>
       <c r="H637" t="n">
         <v>24740</v>
@@ -18871,7 +18871,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835880279541</v>
+        <v>8.91835784912109</v>
       </c>
       <c r="H638" t="n">
         <v>19976</v>
@@ -18958,7 +18958,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H641" t="n">
         <v>23994</v>
@@ -19045,7 +19045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>9.4366397857666</v>
+        <v>9.43664073944092</v>
       </c>
       <c r="H644" t="n">
         <v>5673</v>
@@ -19103,7 +19103,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H646" t="n">
         <v>21998</v>
@@ -19219,7 +19219,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.5637674331665</v>
+        <v>9.56376647949219</v>
       </c>
       <c r="H650" t="n">
         <v>28011</v>
@@ -19248,7 +19248,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995704650879</v>
+        <v>9.28995800018311</v>
       </c>
       <c r="H651" t="n">
         <v>135104</v>
@@ -19277,7 +19277,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H652" t="n">
         <v>48424</v>
@@ -19306,7 +19306,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H653" t="n">
         <v>40921</v>
@@ -19335,7 +19335,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H654" t="n">
         <v>40142</v>
@@ -19364,7 +19364,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G655" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H655" t="n">
         <v>14617</v>
@@ -19393,7 +19393,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G656" t="n">
-        <v>9.22150421142578</v>
+        <v>9.2215051651001</v>
       </c>
       <c r="H656" t="n">
         <v>5166</v>
@@ -19422,7 +19422,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H657" t="n">
         <v>3751</v>
@@ -19451,7 +19451,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437847137451</v>
+        <v>9.09437942504883</v>
       </c>
       <c r="H658" t="n">
         <v>4851</v>
@@ -19480,7 +19480,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>9.33885192871094</v>
+        <v>9.33885097503662</v>
       </c>
       <c r="H659" t="n">
         <v>25360</v>
@@ -19509,7 +19509,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G660" t="n">
-        <v>9.30951499938965</v>
+        <v>9.30951595306396</v>
       </c>
       <c r="H660" t="n">
         <v>8734</v>
@@ -19741,7 +19741,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H668" t="n">
         <v>15830</v>
@@ -19770,7 +19770,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H669" t="n">
         <v>10937</v>
@@ -19799,7 +19799,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G670" t="n">
-        <v>9.30951499938965</v>
+        <v>9.30951595306396</v>
       </c>
       <c r="H670" t="n">
         <v>10898</v>
@@ -19857,7 +19857,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>9.65177726745605</v>
+        <v>9.65177631378174</v>
       </c>
       <c r="H672" t="n">
         <v>48863</v>
@@ -19944,7 +19944,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H675" t="n">
         <v>37373</v>
@@ -19973,7 +19973,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H676" t="n">
         <v>9923</v>
@@ -20002,7 +20002,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H677" t="n">
         <v>7000</v>
@@ -20147,7 +20147,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956607818604</v>
       </c>
       <c r="H682" t="n">
         <v>32449</v>
@@ -20176,7 +20176,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.87669086456299</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H683" t="n">
         <v>37382</v>
@@ -20205,7 +20205,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.87669086456299</v>
+        <v>9.87669277191162</v>
       </c>
       <c r="H684" t="n">
         <v>18917</v>
@@ -20292,7 +20292,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H687" t="n">
         <v>13215</v>
@@ -20350,7 +20350,7 @@
         <v>9.75</v>
       </c>
       <c r="G689" t="n">
-        <v>9.5344295501709</v>
+        <v>9.53443050384521</v>
       </c>
       <c r="H689" t="n">
         <v>11078</v>
@@ -20437,7 +20437,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H692" t="n">
         <v>28508</v>
@@ -20495,7 +20495,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H694" t="n">
         <v>32283</v>
@@ -20553,7 +20553,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890300750732</v>
+        <v>9.77890205383301</v>
       </c>
       <c r="H696" t="n">
         <v>14440</v>
@@ -20611,7 +20611,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H698" t="n">
         <v>21356</v>
@@ -20640,7 +20640,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H699" t="n">
         <v>21197</v>
@@ -20669,7 +20669,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H700" t="n">
         <v>27899</v>
@@ -20756,7 +20756,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172714233398</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H703" t="n">
         <v>10949</v>
@@ -20843,7 +20843,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H706" t="n">
         <v>17733</v>
@@ -20872,7 +20872,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>9.19216823577881</v>
+        <v>9.19216728210449</v>
       </c>
       <c r="H707" t="n">
         <v>60633</v>
@@ -20930,7 +20930,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H709" t="n">
         <v>27319</v>
@@ -20988,7 +20988,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G711" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H711" t="n">
         <v>50079</v>
@@ -21017,7 +21017,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560436248779</v>
+        <v>8.15560531616211</v>
       </c>
       <c r="H712" t="n">
         <v>38461</v>
@@ -21046,7 +21046,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211715698242</v>
+        <v>8.75211620330811</v>
       </c>
       <c r="H713" t="n">
         <v>161407</v>
@@ -21104,7 +21104,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H715" t="n">
         <v>12213</v>
@@ -21133,7 +21133,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G716" t="n">
-        <v>8.34140396118164</v>
+        <v>8.34140300750732</v>
       </c>
       <c r="H716" t="n">
         <v>45582</v>
@@ -21220,7 +21220,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G719" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H719" t="n">
         <v>28804</v>
@@ -21249,7 +21249,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742458343506</v>
+        <v>8.51742362976074</v>
       </c>
       <c r="H720" t="n">
         <v>40610</v>
@@ -21423,7 +21423,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902187347412</v>
+        <v>8.88902282714844</v>
       </c>
       <c r="H726" t="n">
         <v>35047</v>
@@ -21452,7 +21452,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G727" t="n">
-        <v>8.7716760635376</v>
+        <v>8.77167510986328</v>
       </c>
       <c r="H727" t="n">
         <v>143037</v>
@@ -21481,7 +21481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G728" t="n">
-        <v>8.89880180358887</v>
+        <v>8.89880084991455</v>
       </c>
       <c r="H728" t="n">
         <v>73666</v>
@@ -21510,7 +21510,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946296691895</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H729" t="n">
         <v>24316</v>
@@ -21539,7 +21539,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H730" t="n">
         <v>9948</v>
@@ -21742,7 +21742,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262889862061</v>
+        <v>7.40262937545776</v>
       </c>
       <c r="H737" t="n">
         <v>30955</v>
@@ -21858,7 +21858,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>7.30484008789062</v>
+        <v>7.30483961105347</v>
       </c>
       <c r="H741" t="n">
         <v>13402</v>
@@ -21916,7 +21916,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H743" t="n">
         <v>14937</v>
@@ -21945,7 +21945,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.15815687179565</v>
+        <v>7.1581563949585</v>
       </c>
       <c r="H744" t="n">
         <v>18982</v>
@@ -21974,7 +21974,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G745" t="n">
-        <v>6.83545207977295</v>
+        <v>6.83545255661011</v>
       </c>
       <c r="H745" t="n">
         <v>110100</v>
@@ -22003,7 +22003,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385431289673</v>
+        <v>6.46385478973389</v>
       </c>
       <c r="H746" t="n">
         <v>68949</v>
@@ -22119,7 +22119,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834543228149</v>
+        <v>4.93834638595581</v>
       </c>
       <c r="H750" t="n">
         <v>185723</v>
@@ -22148,7 +22148,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.7134313583374</v>
+        <v>4.71343088150024</v>
       </c>
       <c r="H751" t="n">
         <v>210848</v>
@@ -22177,7 +22177,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760622024536</v>
+        <v>4.30760669708252</v>
       </c>
       <c r="H752" t="n">
         <v>95208</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10225009918213</v>
+        <v>4.10224914550781</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22235,7 +22235,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>4.67431497573853</v>
+        <v>4.67431545257568</v>
       </c>
       <c r="H754" t="n">
         <v>139728</v>
@@ -22264,7 +22264,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>4.44940090179443</v>
+        <v>4.44940042495728</v>
       </c>
       <c r="H755" t="n">
         <v>78287</v>
@@ -22409,7 +22409,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00934982299805</v>
+        <v>4.00935029983521</v>
       </c>
       <c r="H760" t="n">
         <v>97203</v>
@@ -22467,7 +22467,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.98001313209534</v>
+        <v>3.9800136089325</v>
       </c>
       <c r="H762" t="n">
         <v>31531</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10225009918213</v>
+        <v>4.10224914550781</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22554,7 +22554,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691761016846</v>
+        <v>4.11691808700562</v>
       </c>
       <c r="H765" t="n">
         <v>28600</v>
@@ -22612,7 +22612,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630561828613</v>
+        <v>4.58630514144897</v>
       </c>
       <c r="H767" t="n">
         <v>113983</v>
@@ -22670,7 +22670,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502912521362</v>
+        <v>5.08502960205078</v>
       </c>
       <c r="H769" t="n">
         <v>224657</v>
@@ -22699,7 +22699,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>5.07525014877319</v>
+        <v>5.07525062561035</v>
       </c>
       <c r="H770" t="n">
         <v>177286</v>
@@ -22728,7 +22728,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.03613519668579</v>
+        <v>5.03613471984863</v>
       </c>
       <c r="H771" t="n">
         <v>79810</v>
@@ -22786,7 +22786,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055662155151</v>
+        <v>4.84055614471436</v>
       </c>
       <c r="H773" t="n">
         <v>56598</v>
@@ -22873,7 +22873,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G776" t="n">
-        <v>5.31972312927246</v>
+        <v>5.3197226524353</v>
       </c>
       <c r="H776" t="n">
         <v>134183</v>
@@ -22960,7 +22960,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H779" t="n">
         <v>69616</v>
@@ -23018,7 +23018,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.44684886932373</v>
+        <v>5.44684839248657</v>
       </c>
       <c r="H781" t="n">
         <v>53399</v>
@@ -23047,7 +23047,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485870361328</v>
+        <v>5.53485822677612</v>
       </c>
       <c r="H782" t="n">
         <v>74521</v>
@@ -23134,7 +23134,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773344039917</v>
+        <v>5.40773296356201</v>
       </c>
       <c r="H785" t="n">
         <v>58953</v>
@@ -23192,7 +23192,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H787" t="n">
         <v>18969</v>
@@ -23221,7 +23221,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G788" t="n">
-        <v>5.36861705780029</v>
+        <v>5.36861753463745</v>
       </c>
       <c r="H788" t="n">
         <v>51246</v>
@@ -23250,7 +23250,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H789" t="n">
         <v>33919</v>
@@ -23279,7 +23279,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.3001651763916</v>
+        <v>5.30016469955444</v>
       </c>
       <c r="H790" t="n">
         <v>36651</v>
@@ -23366,7 +23366,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G793" t="n">
-        <v>5.36861705780029</v>
+        <v>5.36861753463745</v>
       </c>
       <c r="H793" t="n">
         <v>32168</v>
@@ -23453,7 +23453,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>5.22193384170532</v>
+        <v>5.22193431854248</v>
       </c>
       <c r="H796" t="n">
         <v>43106</v>
@@ -23482,7 +23482,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H797" t="n">
         <v>11846</v>
@@ -23511,7 +23511,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171234130859</v>
+        <v>5.23171281814575</v>
       </c>
       <c r="H798" t="n">
         <v>3968</v>
@@ -23569,7 +23569,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H800" t="n">
         <v>42807</v>
@@ -23656,7 +23656,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>5.24149131774902</v>
+        <v>5.24149179458618</v>
       </c>
       <c r="H803" t="n">
         <v>20595</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166221618652</v>
+        <v>4.79166269302368</v>
       </c>
       <c r="H807" t="n">
         <v>76245</v>
@@ -23830,7 +23830,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G809" t="n">
-        <v>5.01657724380493</v>
+        <v>5.01657676696777</v>
       </c>
       <c r="H809" t="n">
         <v>31571</v>
@@ -23859,7 +23859,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H810" t="n">
         <v>46277</v>
@@ -23888,7 +23888,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834543228149</v>
+        <v>4.93834638595581</v>
       </c>
       <c r="H811" t="n">
         <v>36173</v>
@@ -23917,7 +23917,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G812" t="n">
-        <v>5.01657724380493</v>
+        <v>5.01657676696777</v>
       </c>
       <c r="H812" t="n">
         <v>34933</v>
@@ -23946,7 +23946,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>5.0459132194519</v>
+        <v>5.04591369628906</v>
       </c>
       <c r="H813" t="n">
         <v>4389</v>
@@ -23975,7 +23975,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H814" t="n">
         <v>26888</v>
@@ -24120,7 +24120,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220594406128</v>
+        <v>5.65220642089844</v>
       </c>
       <c r="H819" t="n">
         <v>97422</v>
@@ -24207,7 +24207,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>5.45662784576416</v>
+        <v>5.456627368927</v>
       </c>
       <c r="H822" t="n">
         <v>46868</v>
@@ -24236,7 +24236,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H823" t="n">
         <v>49574</v>
@@ -24294,7 +24294,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>5.41751146316528</v>
+        <v>5.41751194000244</v>
       </c>
       <c r="H825" t="n">
         <v>10530</v>
@@ -24323,7 +24323,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552177429199</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H826" t="n">
         <v>18416</v>
@@ -24352,7 +24352,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552177429199</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H827" t="n">
         <v>27618</v>
@@ -24381,7 +24381,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G828" t="n">
-        <v>5.44684886932373</v>
+        <v>5.44684839248657</v>
       </c>
       <c r="H828" t="n">
         <v>56372</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402521133423</v>
+        <v>6.01402473449707</v>
       </c>
       <c r="H834" t="n">
         <v>41322</v>
@@ -24613,7 +24613,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314064025879</v>
+        <v>6.05314111709595</v>
       </c>
       <c r="H836" t="n">
         <v>52635</v>
@@ -24700,7 +24700,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H839" t="n">
         <v>63435</v>
@@ -24758,7 +24758,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>6.58120155334473</v>
+        <v>6.58120107650757</v>
       </c>
       <c r="H841" t="n">
         <v>153325</v>
@@ -25019,7 +25019,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>6.08247709274292</v>
+        <v>6.08247661590576</v>
       </c>
       <c r="H850" t="n">
         <v>27868</v>
@@ -25106,7 +25106,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.00424575805664</v>
+        <v>6.0042462348938</v>
       </c>
       <c r="H853" t="n">
         <v>11658</v>
@@ -25164,7 +25164,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G855" t="n">
-        <v>5.92601490020752</v>
+        <v>5.92601537704468</v>
       </c>
       <c r="H855" t="n">
         <v>66134</v>
@@ -25193,7 +25193,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78910970687866</v>
+        <v>5.78911066055298</v>
       </c>
       <c r="H856" t="n">
         <v>10669</v>
@@ -25251,7 +25251,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977373123169</v>
+        <v>5.75977325439453</v>
       </c>
       <c r="H858" t="n">
         <v>12990</v>
@@ -25425,7 +25425,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>5.82822608947754</v>
+        <v>5.82822561264038</v>
       </c>
       <c r="H864" t="n">
         <v>48237</v>
@@ -25454,7 +25454,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021577835083</v>
+        <v>5.74021530151367</v>
       </c>
       <c r="H865" t="n">
         <v>27718</v>
@@ -25599,7 +25599,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H870" t="n">
         <v>22149</v>
@@ -25715,7 +25715,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>5.95535182952881</v>
+        <v>5.95535135269165</v>
       </c>
       <c r="H874" t="n">
         <v>19266</v>
@@ -25744,7 +25744,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H875" t="n">
         <v>10415</v>
@@ -26063,7 +26063,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>6.53230619430542</v>
+        <v>6.53230667114258</v>
       </c>
       <c r="H886" t="n">
         <v>143444</v>
@@ -26092,7 +26092,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>6.65943193435669</v>
+        <v>6.65943241119385</v>
       </c>
       <c r="H887" t="n">
         <v>78414</v>
@@ -26237,7 +26237,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H892" t="n">
         <v>34785</v>
@@ -26266,7 +26266,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700067520142</v>
+        <v>6.76700019836426</v>
       </c>
       <c r="H893" t="n">
         <v>47611</v>
@@ -26353,7 +26353,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H896" t="n">
         <v>155510</v>
@@ -26411,7 +26411,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H898" t="n">
         <v>68196</v>
@@ -26440,7 +26440,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489116668701</v>
+        <v>7.74489068984985</v>
       </c>
       <c r="H899" t="n">
         <v>112735</v>
@@ -26498,7 +26498,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H901" t="n">
         <v>13903</v>
@@ -26527,7 +26527,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G902" t="n">
-        <v>7.62754440307617</v>
+        <v>7.62754392623901</v>
       </c>
       <c r="H902" t="n">
         <v>45564</v>
@@ -26556,7 +26556,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75466966629028</v>
+        <v>7.75466918945312</v>
       </c>
       <c r="H903" t="n">
         <v>44412</v>
@@ -26614,7 +26614,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G905" t="n">
-        <v>7.73511171340942</v>
+        <v>7.73511123657227</v>
       </c>
       <c r="H905" t="n">
         <v>13300</v>
@@ -26643,7 +26643,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842849731445</v>
+        <v>7.58842802047729</v>
       </c>
       <c r="H906" t="n">
         <v>22167</v>
@@ -26672,7 +26672,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>7.39284992218018</v>
+        <v>7.39285039901733</v>
       </c>
       <c r="H907" t="n">
         <v>26842</v>
@@ -26701,7 +26701,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G908" t="n">
-        <v>7.64710140228271</v>
+        <v>7.64710187911987</v>
       </c>
       <c r="H908" t="n">
         <v>26314</v>
@@ -26730,7 +26730,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>7.41240787506104</v>
+        <v>7.41240835189819</v>
       </c>
       <c r="H909" t="n">
         <v>50527</v>
@@ -26875,7 +26875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H914" t="n">
         <v>40423</v>
@@ -26933,7 +26933,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G916" t="n">
-        <v>6.85501050949097</v>
+        <v>6.85501098632812</v>
       </c>
       <c r="H916" t="n">
         <v>242774</v>
@@ -26991,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G918" t="n">
-        <v>6.84523153305054</v>
+        <v>6.8452320098877</v>
       </c>
       <c r="H918" t="n">
         <v>53696</v>
@@ -27020,7 +27020,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G919" t="n">
-        <v>6.71810579299927</v>
+        <v>6.71810626983643</v>
       </c>
       <c r="H919" t="n">
         <v>21477</v>
@@ -27049,7 +27049,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G920" t="n">
-        <v>6.63009643554688</v>
+        <v>6.63009595870972</v>
       </c>
       <c r="H920" t="n">
         <v>51184</v>
@@ -27078,7 +27078,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G921" t="n">
-        <v>6.71810579299927</v>
+        <v>6.71810626983643</v>
       </c>
       <c r="H921" t="n">
         <v>61586</v>
@@ -27107,7 +27107,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412689208984</v>
+        <v>6.89412593841553</v>
       </c>
       <c r="H922" t="n">
         <v>17841</v>
@@ -27165,7 +27165,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H924" t="n">
         <v>41919</v>
@@ -27194,7 +27194,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793537139893</v>
+        <v>7.16793489456177</v>
       </c>
       <c r="H925" t="n">
         <v>17282</v>
@@ -27252,7 +27252,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191522598267</v>
+        <v>6.99191570281982</v>
       </c>
       <c r="H927" t="n">
         <v>21117</v>
@@ -27281,7 +27281,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H928" t="n">
         <v>40663</v>
@@ -27310,7 +27310,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G929" t="n">
-        <v>7.17771482467651</v>
+        <v>7.17771434783936</v>
       </c>
       <c r="H929" t="n">
         <v>53483</v>
@@ -27339,7 +27339,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218685150146</v>
+        <v>7.42218732833862</v>
       </c>
       <c r="H930" t="n">
         <v>419711</v>
@@ -27368,7 +27368,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G931" t="n">
-        <v>7.24616622924805</v>
+        <v>7.24616670608521</v>
       </c>
       <c r="H931" t="n">
         <v>52841</v>
@@ -27484,7 +27484,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>7.5395336151123</v>
+        <v>7.53953409194946</v>
       </c>
       <c r="H935" t="n">
         <v>42761</v>
@@ -27513,7 +27513,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H936" t="n">
         <v>10858</v>
@@ -27542,7 +27542,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>7.5395336151123</v>
+        <v>7.53953409194946</v>
       </c>
       <c r="H937" t="n">
         <v>15176</v>
@@ -27571,7 +27571,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G938" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H938" t="n">
         <v>165920</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>8.03825855255127</v>
+        <v>8.03825759887695</v>
       </c>
       <c r="H940" t="n">
         <v>95905</v>
@@ -27745,7 +27745,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919277191162</v>
+        <v>8.43919372558594</v>
       </c>
       <c r="H944" t="n">
         <v>119944</v>
@@ -27803,7 +27803,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G946" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H946" t="n">
         <v>263636</v>
@@ -27832,7 +27832,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G947" t="n">
-        <v>9.4366397857666</v>
+        <v>9.43664073944092</v>
       </c>
       <c r="H947" t="n">
         <v>81693</v>
@@ -27861,7 +27861,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H948" t="n">
         <v>77374</v>
@@ -27890,7 +27890,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G949" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H949" t="n">
         <v>212562</v>
@@ -27919,7 +27919,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H950" t="n">
         <v>171303</v>
@@ -27948,7 +27948,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G951" t="n">
-        <v>9.31929397583008</v>
+        <v>9.31929302215576</v>
       </c>
       <c r="H951" t="n">
         <v>256448</v>
@@ -28035,7 +28035,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G954" t="n">
-        <v>8.81079196929932</v>
+        <v>8.810791015625</v>
       </c>
       <c r="H954" t="n">
         <v>75369</v>
@@ -28093,7 +28093,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897174835205</v>
+        <v>8.44897270202637</v>
       </c>
       <c r="H956" t="n">
         <v>40968</v>
@@ -28209,7 +28209,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>8.2240571975708</v>
+        <v>8.22405624389648</v>
       </c>
       <c r="H960" t="n">
         <v>34300</v>
@@ -28383,7 +28383,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>8.45875072479248</v>
+        <v>8.45874977111816</v>
       </c>
       <c r="H966" t="n">
         <v>67238</v>
@@ -28412,7 +28412,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20450019836426</v>
+        <v>8.20449829101562</v>
       </c>
       <c r="H967" t="n">
         <v>42116</v>
@@ -28557,7 +28557,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G972" t="n">
-        <v>8.17516136169434</v>
+        <v>8.17516231536865</v>
       </c>
       <c r="H972" t="n">
         <v>14608</v>
@@ -28615,7 +28615,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614761352539</v>
+        <v>9.01614856719971</v>
       </c>
       <c r="H974" t="n">
         <v>250262</v>
@@ -28644,7 +28644,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.49531364440918</v>
+        <v>9.4953145980835</v>
       </c>
       <c r="H975" t="n">
         <v>336362</v>
@@ -28673,7 +28673,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>9.24106216430664</v>
+        <v>9.24106311798096</v>
       </c>
       <c r="H976" t="n">
         <v>268935</v>
@@ -28702,7 +28702,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956607818604</v>
       </c>
       <c r="H977" t="n">
         <v>117145</v>
@@ -28789,7 +28789,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H980" t="n">
         <v>214809</v>
@@ -28818,7 +28818,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G981" t="n">
-        <v>10.9132556915283</v>
+        <v>10.913254737854</v>
       </c>
       <c r="H981" t="n">
         <v>93949</v>
@@ -28847,7 +28847,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804315567017</v>
+        <v>11.4804306030273</v>
       </c>
       <c r="H982" t="n">
         <v>419644</v>
@@ -28934,7 +28934,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9107036590576</v>
+        <v>11.9107027053833</v>
       </c>
       <c r="H985" t="n">
         <v>111245</v>
@@ -28992,7 +28992,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G987" t="n">
-        <v>12.4387636184692</v>
+        <v>12.4387645721436</v>
       </c>
       <c r="H987" t="n">
         <v>287079</v>
@@ -29021,7 +29021,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H988" t="n">
         <v>321229</v>
@@ -29137,7 +29137,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882537841797</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H992" t="n">
         <v>403792</v>
@@ -29195,7 +29195,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G994" t="n">
-        <v>14.4336595535278</v>
+        <v>14.4336605072021</v>
       </c>
       <c r="H994" t="n">
         <v>123949</v>
@@ -29253,7 +29253,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G996" t="n">
-        <v>15.0790672302246</v>
+        <v>15.0790681838989</v>
       </c>
       <c r="H996" t="n">
         <v>358240</v>
@@ -29282,7 +29282,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705642700195</v>
+        <v>14.5705652236938</v>
       </c>
       <c r="H997" t="n">
         <v>150561</v>
@@ -29369,7 +29369,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7100210189819</v>
+        <v>13.7100219726562</v>
       </c>
       <c r="H1000" t="n">
         <v>186196</v>
@@ -29427,7 +29427,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.3188638687134</v>
+        <v>13.3188648223877</v>
       </c>
       <c r="H1002" t="n">
         <v>70482</v>
@@ -29543,7 +29543,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>12.6539001464844</v>
+        <v>12.6538991928101</v>
       </c>
       <c r="H1006" t="n">
         <v>60410</v>
@@ -29572,7 +29572,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>12.6539001464844</v>
+        <v>12.6538991928101</v>
       </c>
       <c r="H1007" t="n">
         <v>53351</v>
@@ -29746,7 +29746,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1013" t="n">
-        <v>12.5756673812866</v>
+        <v>12.5756683349609</v>
       </c>
       <c r="H1013" t="n">
         <v>75572</v>
@@ -29862,7 +29862,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5561103820801</v>
+        <v>12.5561113357544</v>
       </c>
       <c r="H1017" t="n">
         <v>121329</v>
@@ -29891,7 +29891,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.3996486663818</v>
+        <v>12.3996496200562</v>
       </c>
       <c r="H1018" t="n">
         <v>91050</v>
@@ -29978,7 +29978,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1021" t="n">
         <v>151231</v>
@@ -30065,7 +30065,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1024" t="n">
         <v>111837</v>
@@ -30326,7 +30326,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.715124130249</v>
+        <v>11.7151250839233</v>
       </c>
       <c r="H1033" t="n">
         <v>119232</v>
@@ -30355,7 +30355,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.0476083755493</v>
+        <v>12.047607421875</v>
       </c>
       <c r="H1034" t="n">
         <v>89765</v>
@@ -30384,7 +30384,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>12.6147842407227</v>
+        <v>12.6147832870483</v>
       </c>
       <c r="H1035" t="n">
         <v>136832</v>
@@ -30413,7 +30413,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.3996486663818</v>
+        <v>12.3996496200562</v>
       </c>
       <c r="H1036" t="n">
         <v>90647</v>
@@ -30529,7 +30529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>12.6147842407227</v>
+        <v>12.6147832870483</v>
       </c>
       <c r="H1040" t="n">
         <v>52689</v>
@@ -30645,7 +30645,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>12.6147842407227</v>
+        <v>12.6147832870483</v>
       </c>
       <c r="H1044" t="n">
         <v>61277</v>
@@ -30674,7 +30674,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.4192066192627</v>
+        <v>12.4192056655884</v>
       </c>
       <c r="H1045" t="n">
         <v>16548</v>
@@ -30819,7 +30819,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H1050" t="n">
         <v>110815</v>
@@ -30906,7 +30906,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H1053" t="n">
         <v>195883</v>
@@ -30935,7 +30935,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H1054" t="n">
         <v>167159</v>
@@ -31080,7 +31080,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220994949341</v>
+        <v>10.5220985412598</v>
       </c>
       <c r="H1059" t="n">
         <v>104597</v>
@@ -31109,7 +31109,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.2091732025146</v>
+        <v>10.209174156189</v>
       </c>
       <c r="H1060" t="n">
         <v>129001</v>
@@ -31138,7 +31138,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.1505002975464</v>
+        <v>10.1505012512207</v>
       </c>
       <c r="H1061" t="n">
         <v>77475</v>
@@ -31196,7 +31196,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.30951499938965</v>
+        <v>9.30951595306396</v>
       </c>
       <c r="H1063" t="n">
         <v>88124</v>
@@ -31341,7 +31341,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206703186035</v>
+        <v>8.31206798553467</v>
       </c>
       <c r="H1068" t="n">
         <v>167682</v>
@@ -31370,7 +31370,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64455032348633</v>
+        <v>8.64454936981201</v>
       </c>
       <c r="H1069" t="n">
         <v>180623</v>
@@ -31399,7 +31399,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543441772461</v>
+        <v>8.60543346405029</v>
       </c>
       <c r="H1070" t="n">
         <v>27481</v>
@@ -31457,7 +31457,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>8.72278022766113</v>
+        <v>8.72278118133545</v>
       </c>
       <c r="H1072" t="n">
         <v>55348</v>
@@ -31486,7 +31486,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.81079196929932</v>
+        <v>8.810791015625</v>
       </c>
       <c r="H1073" t="n">
         <v>41885</v>
@@ -31544,7 +31544,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H1075" t="n">
         <v>127062</v>
@@ -31602,7 +31602,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597766876221</v>
+        <v>9.46597671508789</v>
       </c>
       <c r="H1077" t="n">
         <v>64803</v>
@@ -31631,7 +31631,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.0722703933716</v>
+        <v>10.0722694396973</v>
       </c>
       <c r="H1078" t="n">
         <v>52506</v>
@@ -31660,7 +31660,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.3265218734741</v>
+        <v>10.3265209197998</v>
       </c>
       <c r="H1079" t="n">
         <v>87842</v>
@@ -31747,7 +31747,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0918264389038</v>
+        <v>10.0918273925781</v>
       </c>
       <c r="H1082" t="n">
         <v>25318</v>
@@ -31776,7 +31776,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003303527832</v>
+        <v>10.6003293991089</v>
       </c>
       <c r="H1083" t="n">
         <v>44357</v>
@@ -31805,7 +31805,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.4438676834106</v>
+        <v>10.443868637085</v>
       </c>
       <c r="H1084" t="n">
         <v>61024</v>
@@ -31979,7 +31979,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>13.1037282943726</v>
+        <v>13.1037292480469</v>
       </c>
       <c r="H1090" t="n">
         <v>153541</v>
@@ -32037,7 +32037,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.1428442001343</v>
+        <v>13.1428451538086</v>
       </c>
       <c r="H1092" t="n">
         <v>90633</v>
@@ -32153,7 +32153,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882537841797</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H1096" t="n">
         <v>93691</v>
@@ -32240,7 +32240,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>13.8273687362671</v>
+        <v>13.8273677825928</v>
       </c>
       <c r="H1099" t="n">
         <v>108983</v>
@@ -32269,7 +32269,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1100" t="n">
-        <v>14.1402940750122</v>
+        <v>14.1402931213379</v>
       </c>
       <c r="H1100" t="n">
         <v>81068</v>
@@ -32298,7 +32298,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771978378296</v>
+        <v>14.2771987915039</v>
       </c>
       <c r="H1101" t="n">
         <v>57479</v>
@@ -32327,7 +32327,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>14.4532165527344</v>
+        <v>14.4532175064087</v>
       </c>
       <c r="H1102" t="n">
         <v>33492</v>
@@ -32385,7 +32385,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749866485596</v>
+        <v>14.3749856948853</v>
       </c>
       <c r="H1104" t="n">
         <v>36166</v>
@@ -32414,7 +32414,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030475616455</v>
+        <v>14.9030466079712</v>
       </c>
       <c r="H1105" t="n">
         <v>135713</v>
@@ -32530,7 +32530,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181831359863</v>
+        <v>15.1181840896606</v>
       </c>
       <c r="H1109" t="n">
         <v>121418</v>
@@ -32559,7 +32559,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.9396104812622</v>
+        <v>15.9396095275879</v>
       </c>
       <c r="H1110" t="n">
         <v>152433</v>
@@ -32675,7 +32675,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666488647461</v>
+        <v>19.1666507720947</v>
       </c>
       <c r="H1114" t="n">
         <v>462313</v>
@@ -32733,7 +32733,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>20.1445407867432</v>
+        <v>20.1445388793945</v>
       </c>
       <c r="H1116" t="n">
         <v>183683</v>
@@ -32791,7 +32791,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.3890113830566</v>
+        <v>20.3890132904053</v>
       </c>
       <c r="H1118" t="n">
         <v>186738</v>
@@ -32820,7 +32820,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1119" t="n">
         <v>218593</v>
@@ -32878,7 +32878,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981086730957</v>
+        <v>22.1981105804443</v>
       </c>
       <c r="H1121" t="n">
         <v>87185</v>
@@ -32907,7 +32907,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.7580585479736</v>
+        <v>21.758056640625</v>
       </c>
       <c r="H1122" t="n">
         <v>177161</v>
@@ -32965,7 +32965,7 @@
         <v>21.5</v>
       </c>
       <c r="G1124" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1124" t="n">
         <v>72589</v>
@@ -32994,7 +32994,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1125" t="n">
-        <v>20.1445407867432</v>
+        <v>20.1445388793945</v>
       </c>
       <c r="H1125" t="n">
         <v>125202</v>
@@ -33023,7 +33023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1126" t="n">
         <v>169849</v>
@@ -33052,7 +33052,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1127" t="n">
         <v>153071</v>
@@ -33110,7 +33110,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>20.1445407867432</v>
+        <v>20.1445388793945</v>
       </c>
       <c r="H1129" t="n">
         <v>52762</v>
@@ -33139,7 +33139,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>21.1713237762451</v>
+        <v>21.1713218688965</v>
       </c>
       <c r="H1130" t="n">
         <v>60803</v>
@@ -33168,7 +33168,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558464050293</v>
+        <v>21.8558483123779</v>
       </c>
       <c r="H1131" t="n">
         <v>109080</v>
@@ -33197,7 +33197,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602687835693</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1132" t="n">
         <v>103507</v>
@@ -33255,7 +33255,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602687835693</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1134" t="n">
         <v>98501</v>
@@ -33400,7 +33400,7 @@
         <v>21.5</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1139" t="n">
         <v>34560</v>
@@ -33458,7 +33458,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>20.9757461547852</v>
+        <v>20.9757480621338</v>
       </c>
       <c r="H1141" t="n">
         <v>56787</v>
@@ -33516,7 +33516,7 @@
         <v>21.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1143" t="n">
         <v>34032</v>
@@ -33574,7 +33574,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1145" t="n">
         <v>26612</v>
@@ -33632,7 +33632,7 @@
         <v>21.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1147" t="n">
         <v>58527</v>
@@ -33661,7 +33661,7 @@
         <v>21.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>20.7801685333252</v>
+        <v>20.7801666259766</v>
       </c>
       <c r="H1148" t="n">
         <v>26335</v>
@@ -33719,7 +33719,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>20.193431854248</v>
+        <v>20.1934337615967</v>
       </c>
       <c r="H1150" t="n">
         <v>130761</v>
@@ -33748,7 +33748,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1151" t="n">
         <v>65290</v>
@@ -33806,7 +33806,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1153" t="n">
         <v>112291</v>
@@ -33835,7 +33835,7 @@
         <v>23.75</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.2248954772949</v>
+        <v>23.2248935699463</v>
       </c>
       <c r="H1154" t="n">
         <v>149423</v>
@@ -33893,7 +33893,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0561008453369</v>
+        <v>24.0560989379883</v>
       </c>
       <c r="H1156" t="n">
         <v>205397</v>
@@ -33951,7 +33951,7 @@
         <v>24.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.9583110809326</v>
+        <v>23.9583129882812</v>
       </c>
       <c r="H1158" t="n">
         <v>67635</v>
@@ -34009,7 +34009,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.322681427002</v>
+        <v>23.3226833343506</v>
       </c>
       <c r="H1160" t="n">
         <v>31857</v>
@@ -34067,7 +34067,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359485626221</v>
+        <v>22.7359504699707</v>
       </c>
       <c r="H1162" t="n">
         <v>32829</v>
@@ -34096,7 +34096,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1163" t="n">
         <v>63588</v>
@@ -34125,7 +34125,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1164" t="n">
         <v>33009</v>
@@ -34183,7 +34183,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1166" t="n">
         <v>72421</v>
@@ -34212,7 +34212,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1167" t="n">
         <v>34211</v>
@@ -34299,7 +34299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447933197021</v>
+        <v>22.3447914123535</v>
       </c>
       <c r="H1170" t="n">
         <v>119843</v>
@@ -34357,7 +34357,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1172" t="n">
         <v>37810</v>
@@ -34415,7 +34415,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.1492137908936</v>
+        <v>22.1492156982422</v>
       </c>
       <c r="H1174" t="n">
         <v>29225</v>
@@ -34444,7 +34444,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1175" t="n">
         <v>25765</v>
@@ -34502,7 +34502,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.5403671264648</v>
+        <v>22.5403690338135</v>
       </c>
       <c r="H1177" t="n">
         <v>15746</v>
@@ -34618,7 +34618,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1181" t="n">
         <v>48003</v>
@@ -34676,7 +34676,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1183" t="n">
         <v>60552</v>
@@ -34705,7 +34705,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157943725586</v>
+        <v>21.4157962799072</v>
       </c>
       <c r="H1184" t="n">
         <v>21327</v>
@@ -34763,7 +34763,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1186" t="n">
         <v>55489</v>
@@ -34850,7 +34850,7 @@
         <v>21.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1189" t="n">
         <v>47664</v>
@@ -34908,7 +34908,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.562479019165</v>
+        <v>21.5624809265137</v>
       </c>
       <c r="H1191" t="n">
         <v>39920</v>
@@ -35082,7 +35082,7 @@
         <v>21.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1197" t="n">
         <v>53455</v>
@@ -35169,7 +35169,7 @@
         <v>21.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1200" t="n">
         <v>137704</v>
@@ -35285,7 +35285,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1204" t="n">
         <v>133530</v>
@@ -35343,7 +35343,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>20.193431854248</v>
+        <v>20.1934337615967</v>
       </c>
       <c r="H1206" t="n">
         <v>140178</v>
@@ -35372,7 +35372,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.9268493652344</v>
+        <v>20.926851272583</v>
       </c>
       <c r="H1207" t="n">
         <v>80989</v>
@@ -35401,7 +35401,7 @@
         <v>21.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1208" t="n">
         <v>60298</v>
@@ -35430,7 +35430,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401165008545</v>
+        <v>20.3401184082031</v>
       </c>
       <c r="H1209" t="n">
         <v>38491</v>
@@ -35488,7 +35488,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3890113830566</v>
+        <v>20.3890132904053</v>
       </c>
       <c r="H1211" t="n">
         <v>36573</v>
@@ -35517,7 +35517,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>20.0956420898438</v>
+        <v>20.0956439971924</v>
       </c>
       <c r="H1212" t="n">
         <v>26712</v>
@@ -35575,7 +35575,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1214" t="n">
         <v>61113</v>
@@ -35604,7 +35604,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511714935303</v>
+        <v>19.8511695861816</v>
       </c>
       <c r="H1215" t="n">
         <v>97038</v>
@@ -35691,7 +35691,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.9978580474854</v>
+        <v>19.9978561401367</v>
       </c>
       <c r="H1218" t="n">
         <v>80159</v>
@@ -35720,7 +35720,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.753381729126</v>
+        <v>19.7533855438232</v>
       </c>
       <c r="H1219" t="n">
         <v>54410</v>
@@ -35923,7 +35923,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521949768066</v>
+        <v>17.1521968841553</v>
       </c>
       <c r="H1226" t="n">
         <v>67839</v>
@@ -35981,7 +35981,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112087249756</v>
+        <v>16.3112106323242</v>
       </c>
       <c r="H1228" t="n">
         <v>66395</v>
@@ -36010,7 +36010,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.3698825836182</v>
+        <v>16.3698806762695</v>
       </c>
       <c r="H1229" t="n">
         <v>80556</v>
@@ -36097,7 +36097,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.917501449585</v>
+        <v>16.9174995422363</v>
       </c>
       <c r="H1232" t="n">
         <v>52351</v>
@@ -36155,7 +36155,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348491668701</v>
+        <v>17.0348472595215</v>
       </c>
       <c r="H1234" t="n">
         <v>86836</v>
@@ -36213,7 +36213,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1236" t="n">
         <v>105949</v>
@@ -36271,7 +36271,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304248809814</v>
+        <v>17.2304267883301</v>
       </c>
       <c r="H1238" t="n">
         <v>124533</v>
@@ -36300,7 +36300,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108688354492</v>
+        <v>17.2108669281006</v>
       </c>
       <c r="H1239" t="n">
         <v>157511</v>
@@ -36358,7 +36358,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1241" t="n">
-        <v>17.0544052124023</v>
+        <v>17.054407119751</v>
       </c>
       <c r="H1241" t="n">
         <v>48546</v>
@@ -36445,7 +36445,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042343139648</v>
+        <v>17.5042324066162</v>
       </c>
       <c r="H1244" t="n">
         <v>65827</v>
@@ -36474,7 +36474,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.4846744537354</v>
+        <v>17.4846782684326</v>
       </c>
       <c r="H1245" t="n">
         <v>68340</v>
@@ -36503,7 +36503,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979434967041</v>
+        <v>16.8979454040527</v>
       </c>
       <c r="H1246" t="n">
         <v>89023</v>
@@ -36532,7 +36532,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1247" t="n">
         <v>82416</v>
@@ -36561,7 +36561,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.5459022521973</v>
+        <v>16.5459041595459</v>
       </c>
       <c r="H1248" t="n">
         <v>44400</v>
@@ -36590,7 +36590,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1249" t="n">
-        <v>16.858829498291</v>
+        <v>16.8588275909424</v>
       </c>
       <c r="H1249" t="n">
         <v>31565</v>
@@ -36648,7 +36648,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521949768066</v>
+        <v>17.1521968841553</v>
       </c>
       <c r="H1251" t="n">
         <v>74074</v>
@@ -36677,7 +36677,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1252" t="n">
         <v>39230</v>
@@ -36735,7 +36735,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761734008789</v>
+        <v>16.9761753082275</v>
       </c>
       <c r="H1254" t="n">
         <v>30692</v>
@@ -36764,7 +36764,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.7219219207764</v>
+        <v>16.721923828125</v>
       </c>
       <c r="H1255" t="n">
         <v>38089</v>
@@ -36938,7 +36938,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>19.5948181152344</v>
+        <v>19.594820022583</v>
       </c>
       <c r="H1261" t="n">
         <v>421870</v>
@@ -36996,7 +36996,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6342849731445</v>
+        <v>19.6342830657959</v>
       </c>
       <c r="H1263" t="n">
         <v>110426</v>
@@ -37199,7 +37199,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1270" t="n">
         <v>151182</v>
@@ -37228,7 +37228,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1271" t="n">
         <v>144900</v>
@@ -37257,7 +37257,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1272" t="n">
         <v>100072</v>
@@ -37431,7 +37431,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1278" t="n">
         <v>268613</v>
@@ -37605,7 +37605,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.5750846862793</v>
+        <v>19.5750865936279</v>
       </c>
       <c r="H1284" t="n">
         <v>112686</v>
@@ -37779,7 +37779,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>18.5687046051025</v>
+        <v>18.5687065124512</v>
       </c>
       <c r="H1290" t="n">
         <v>80819</v>
@@ -37866,7 +37866,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.3777561187744</v>
+        <v>19.3777542114258</v>
       </c>
       <c r="H1293" t="n">
         <v>96973</v>
@@ -37895,7 +37895,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1294" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1294" t="n">
         <v>80244</v>
@@ -37924,7 +37924,7 @@
         <v>19.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>19.2396240234375</v>
+        <v>19.2396259307861</v>
       </c>
       <c r="H1295" t="n">
         <v>270887</v>
@@ -37953,7 +37953,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.7132167816162</v>
+        <v>19.7132148742676</v>
       </c>
       <c r="H1296" t="n">
         <v>176673</v>
@@ -37982,7 +37982,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1297" t="n">
         <v>155909</v>
@@ -38040,7 +38040,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1299" t="n">
         <v>88312</v>
@@ -38069,7 +38069,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.5089130401611</v>
+        <v>21.5089149475098</v>
       </c>
       <c r="H1300" t="n">
         <v>61890</v>
@@ -38098,7 +38098,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1301" t="n">
         <v>220236</v>
@@ -38156,7 +38156,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>21.1635875701904</v>
+        <v>21.1635894775391</v>
       </c>
       <c r="H1303" t="n">
         <v>114500</v>
@@ -38214,7 +38214,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.8182601928711</v>
+        <v>20.8182621002197</v>
       </c>
       <c r="H1305" t="n">
         <v>89332</v>
@@ -38272,7 +38272,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1307" t="n">
         <v>216127</v>
@@ -38330,7 +38330,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.6737499237061</v>
+        <v>19.6737518310547</v>
       </c>
       <c r="H1309" t="n">
         <v>87050</v>
@@ -38359,7 +38359,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1310" t="n">
         <v>41832</v>
@@ -38388,7 +38388,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.6145515441895</v>
+        <v>19.6145496368408</v>
       </c>
       <c r="H1311" t="n">
         <v>34200</v>
@@ -38591,7 +38591,7 @@
         <v>23.75</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.4328784942627</v>
+        <v>23.4328765869141</v>
       </c>
       <c r="H1318" t="n">
         <v>828551</v>
@@ -38649,7 +38649,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>22.2982311248779</v>
+        <v>22.2982330322266</v>
       </c>
       <c r="H1320" t="n">
         <v>98729</v>
@@ -38678,7 +38678,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>21.2622509002686</v>
+        <v>21.2622528076172</v>
       </c>
       <c r="H1321" t="n">
         <v>138690</v>
@@ -38939,7 +38939,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>22.8902225494385</v>
+        <v>22.8902206420898</v>
       </c>
       <c r="H1330" t="n">
         <v>103493</v>
@@ -39026,7 +39026,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1333" t="n">
         <v>102759</v>
@@ -39229,7 +39229,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1340" t="n">
-        <v>26.1856231689453</v>
+        <v>26.1856250762939</v>
       </c>
       <c r="H1340" t="n">
         <v>75983</v>
@@ -39490,7 +39490,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1349" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1349" t="n">
         <v>83400</v>
@@ -39548,7 +39548,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1351" t="n">
         <v>42477</v>
@@ -39635,7 +39635,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G1354" t="n">
-        <v>23.14674949646</v>
+        <v>23.1467475891113</v>
       </c>
       <c r="H1354" t="n">
         <v>32490</v>
@@ -39664,7 +39664,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.71262550354</v>
+        <v>22.7126235961914</v>
       </c>
       <c r="H1355" t="n">
         <v>83180</v>
@@ -39693,7 +39693,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.008617401123</v>
+        <v>23.0086193084717</v>
       </c>
       <c r="H1356" t="n">
         <v>67559</v>
@@ -39809,7 +39809,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1360" t="n">
         <v>218042</v>
@@ -39838,7 +39838,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1361" t="n">
-        <v>23.5216770172119</v>
+        <v>23.5216751098633</v>
       </c>
       <c r="H1361" t="n">
         <v>73675</v>
@@ -39954,7 +39954,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1365" t="n">
-        <v>24.6464538574219</v>
+        <v>24.6464519500732</v>
       </c>
       <c r="H1365" t="n">
         <v>92733</v>
@@ -40041,7 +40041,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1368" t="n">
         <v>59967</v>
@@ -40186,7 +40186,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1373" t="n">
-        <v>24.902982711792</v>
+        <v>24.9029808044434</v>
       </c>
       <c r="H1373" t="n">
         <v>125191</v>
@@ -40215,7 +40215,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>24.7648506164551</v>
+        <v>24.7648525238037</v>
       </c>
       <c r="H1374" t="n">
         <v>78394</v>
@@ -40244,7 +40244,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1375" t="n">
-        <v>24.4096565246582</v>
+        <v>24.4096584320068</v>
       </c>
       <c r="H1375" t="n">
         <v>68323</v>
@@ -40273,7 +40273,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1376" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1376" t="n">
         <v>54879</v>
@@ -40360,7 +40360,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1379" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1379" t="n">
         <v>48881</v>
@@ -40389,7 +40389,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1380" t="n">
         <v>59300</v>
@@ -40476,7 +40476,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.2250900268555</v>
+        <v>26.2250881195068</v>
       </c>
       <c r="H1383" t="n">
         <v>131925</v>
@@ -40505,7 +40505,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1384" t="n">
-        <v>28.4351806640625</v>
+        <v>28.4351787567139</v>
       </c>
       <c r="H1384" t="n">
         <v>187997</v>
@@ -40708,7 +40708,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1391" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1391" t="n">
         <v>74513</v>
@@ -40766,7 +40766,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1393" t="n">
-        <v>24.6267204284668</v>
+        <v>24.6267185211182</v>
       </c>
       <c r="H1393" t="n">
         <v>106208</v>
@@ -40795,7 +40795,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>24.6069869995117</v>
+        <v>24.6069889068604</v>
       </c>
       <c r="H1394" t="n">
         <v>64862</v>
@@ -40824,7 +40824,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>24.7253856658936</v>
+        <v>24.7253837585449</v>
       </c>
       <c r="H1395" t="n">
         <v>43250</v>
@@ -40882,7 +40882,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1397" t="n">
         <v>69714</v>
@@ -40911,7 +40911,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1398" t="n">
         <v>26167</v>
@@ -40969,7 +40969,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>24.1531276702881</v>
+        <v>24.1531295776367</v>
       </c>
       <c r="H1400" t="n">
         <v>39041</v>
@@ -41143,7 +41143,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1406" t="n">
         <v>48196</v>
@@ -41201,7 +41201,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1408" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1408" t="n">
         <v>26194</v>
@@ -41230,7 +41230,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1409" t="n">
         <v>183680</v>
@@ -41288,7 +41288,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3899250030518</v>
+        <v>24.3899230957031</v>
       </c>
       <c r="H1411" t="n">
         <v>56923</v>
@@ -41404,7 +41404,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.3307247161865</v>
+        <v>24.3307266235352</v>
       </c>
       <c r="H1415" t="n">
         <v>94778</v>
@@ -41636,7 +41636,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.3440799713135</v>
+        <v>23.3440780639648</v>
       </c>
       <c r="H1423" t="n">
         <v>50299</v>
@@ -41694,7 +41694,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1425" t="n">
         <v>19023</v>
@@ -41839,7 +41839,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1430" t="n">
         <v>34199</v>
@@ -41897,7 +41897,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1432" t="n">
         <v>51446</v>
@@ -42042,7 +42042,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>24.6859188079834</v>
+        <v>24.685920715332</v>
       </c>
       <c r="H1437" t="n">
         <v>70358</v>
@@ -42129,7 +42129,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>26.3434867858887</v>
+        <v>26.3434886932373</v>
       </c>
       <c r="H1440" t="n">
         <v>93973</v>
@@ -42158,7 +42158,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.0341415405273</v>
+        <v>27.0341396331787</v>
       </c>
       <c r="H1441" t="n">
         <v>85164</v>
@@ -42216,7 +42216,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>28.4154453277588</v>
+        <v>28.4154472351074</v>
       </c>
       <c r="H1443" t="n">
         <v>195373</v>
@@ -42245,7 +42245,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>29.6980876922607</v>
+        <v>29.6980895996094</v>
       </c>
       <c r="H1444" t="n">
         <v>171716</v>
@@ -42303,7 +42303,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1446" t="n">
-        <v>29.7770195007324</v>
+        <v>29.7770214080811</v>
       </c>
       <c r="H1446" t="n">
         <v>87748</v>
@@ -42361,7 +42361,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1448" t="n">
-        <v>30.3295421600342</v>
+        <v>30.3295440673828</v>
       </c>
       <c r="H1448" t="n">
         <v>98329</v>
@@ -42535,7 +42535,7 @@
         <v>30.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>30.0927467346191</v>
+        <v>30.0927486419678</v>
       </c>
       <c r="H1454" t="n">
         <v>101035</v>
@@ -42622,7 +42622,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.4218254089355</v>
+        <v>29.4218273162842</v>
       </c>
       <c r="H1457" t="n">
         <v>72194</v>
@@ -42738,7 +42738,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1461" t="n">
         <v>75514</v>
@@ -42854,7 +42854,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G1465" t="n">
-        <v>35.8547668457031</v>
+        <v>35.8547706604004</v>
       </c>
       <c r="H1465" t="n">
         <v>359905</v>
@@ -42941,7 +42941,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>39.0712394714355</v>
+        <v>39.0712356567383</v>
       </c>
       <c r="H1468" t="n">
         <v>321164</v>
@@ -42970,7 +42970,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1469" t="n">
-        <v>36.2691612243652</v>
+        <v>36.269157409668</v>
       </c>
       <c r="H1469" t="n">
         <v>228974</v>
@@ -43028,7 +43028,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>40.3538856506348</v>
+        <v>40.3538818359375</v>
       </c>
       <c r="H1471" t="n">
         <v>311161</v>
@@ -43144,7 +43144,7 @@
         <v>42.6599998474121</v>
       </c>
       <c r="G1475" t="n">
-        <v>42.0903816223145</v>
+        <v>42.0903778076172</v>
       </c>
       <c r="H1475" t="n">
         <v>174798</v>
@@ -43173,7 +43173,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>42.2482452392578</v>
+        <v>42.2482414245605</v>
       </c>
       <c r="H1476" t="n">
         <v>109882</v>
@@ -43202,7 +43202,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1477" t="n">
-        <v>42.5837059020996</v>
+        <v>42.5837020874023</v>
       </c>
       <c r="H1477" t="n">
         <v>137662</v>
@@ -43231,7 +43231,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>43.0178260803223</v>
+        <v>43.0178298950195</v>
       </c>
       <c r="H1478" t="n">
         <v>116213</v>
@@ -43260,7 +43260,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>42.6231727600098</v>
+        <v>42.6231689453125</v>
       </c>
       <c r="H1479" t="n">
         <v>123515</v>
@@ -43289,7 +43289,7 @@
         <v>43</v>
       </c>
       <c r="G1480" t="n">
-        <v>42.4258422851562</v>
+        <v>42.425838470459</v>
       </c>
       <c r="H1480" t="n">
         <v>77199</v>
@@ -43376,7 +43376,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.2615928649902</v>
+        <v>41.2615966796875</v>
       </c>
       <c r="H1483" t="n">
         <v>55495</v>
@@ -43405,7 +43405,7 @@
         <v>42.6399993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.0706481933594</v>
+        <v>42.0706443786621</v>
       </c>
       <c r="H1484" t="n">
         <v>72975</v>
@@ -43637,7 +43637,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1492" t="n">
-        <v>45.5831146240234</v>
+        <v>45.5831108093262</v>
       </c>
       <c r="H1492" t="n">
         <v>178167</v>
@@ -43666,7 +43666,7 @@
         <v>38.4199981689453</v>
       </c>
       <c r="G1493" t="n">
-        <v>37.9069900512695</v>
+        <v>37.9069938659668</v>
       </c>
       <c r="H1493" t="n">
         <v>678570</v>
@@ -43724,7 +43724,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1495" t="n">
-        <v>32.6185684204102</v>
+        <v>32.6185646057129</v>
       </c>
       <c r="H1495" t="n">
         <v>546704</v>
@@ -43869,7 +43869,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1500" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1500" t="n">
         <v>356068</v>
@@ -43927,7 +43927,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1502" t="n">
         <v>513447</v>
@@ -43985,7 +43985,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1504" t="n">
-        <v>31.0201950073242</v>
+        <v>31.0201969146729</v>
       </c>
       <c r="H1504" t="n">
         <v>237350</v>
@@ -44043,7 +44043,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>31.3951225280762</v>
+        <v>31.3951206207275</v>
       </c>
       <c r="H1506" t="n">
         <v>180598</v>
@@ -44101,7 +44101,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1508" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1508" t="n">
         <v>287718</v>
@@ -80096,6 +80096,35 @@
         <v>4604</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>14923</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71455669403076</v>
+        <v>6.71455717086792</v>
       </c>
       <c r="H3" t="n">
         <v>54991</v>
@@ -485,7 +485,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48500061035156</v>
+        <v>6.48499965667725</v>
       </c>
       <c r="H4" t="n">
         <v>46846</v>
@@ -514,7 +514,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4467396736145</v>
+        <v>6.44674015045166</v>
       </c>
       <c r="H5" t="n">
         <v>108929</v>
@@ -543,7 +543,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2793550491333</v>
+        <v>6.27935457229614</v>
       </c>
       <c r="H6" t="n">
         <v>57520</v>
@@ -572,7 +572,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H7" t="n">
         <v>40228</v>
@@ -630,7 +630,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H9" t="n">
         <v>104780</v>
@@ -659,7 +659,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3319616317749</v>
+        <v>6.33196115493774</v>
       </c>
       <c r="H10" t="n">
         <v>158687</v>
@@ -688,7 +688,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544902801514</v>
+        <v>6.03544950485229</v>
       </c>
       <c r="H11" t="n">
         <v>125780</v>
@@ -717,7 +717,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.70546054840088</v>
+        <v>5.70546102523804</v>
       </c>
       <c r="H12" t="n">
         <v>113455</v>
@@ -833,7 +833,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>5.74850273132324</v>
+        <v>5.7485032081604</v>
       </c>
       <c r="H16" t="n">
         <v>99565</v>
@@ -862,7 +862,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937297821045</v>
+        <v>5.72937250137329</v>
       </c>
       <c r="H17" t="n">
         <v>38963</v>
@@ -949,7 +949,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>6.00197267532349</v>
+        <v>6.00197219848633</v>
       </c>
       <c r="H20" t="n">
         <v>70672</v>
@@ -978,7 +978,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458341598511</v>
+        <v>5.94458293914795</v>
       </c>
       <c r="H21" t="n">
         <v>47413</v>
@@ -1036,7 +1036,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9541482925415</v>
+        <v>5.95414733886719</v>
       </c>
       <c r="H23" t="n">
         <v>39858</v>
@@ -1065,7 +1065,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458614349365</v>
       </c>
       <c r="H24" t="n">
         <v>59492</v>
@@ -1094,7 +1094,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154491424561</v>
+        <v>5.79154443740845</v>
       </c>
       <c r="H25" t="n">
         <v>42499</v>
@@ -1123,7 +1123,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7006778717041</v>
+        <v>5.70067882537842</v>
       </c>
       <c r="H26" t="n">
         <v>83256</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244829177856</v>
+        <v>4.78244876861572</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1210,7 +1210,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679168701172</v>
+        <v>4.90679216384888</v>
       </c>
       <c r="H29" t="n">
         <v>118336</v>
@@ -1239,7 +1239,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62940979003906</v>
+        <v>4.62941026687622</v>
       </c>
       <c r="H30" t="n">
         <v>67579</v>
@@ -1297,7 +1297,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.064612865448</v>
+        <v>5.06461238861084</v>
       </c>
       <c r="H32" t="n">
         <v>19857</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.83983707427979</v>
+        <v>4.83983755111694</v>
       </c>
       <c r="H33" t="n">
         <v>11060</v>
@@ -1413,7 +1413,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677375793457</v>
+        <v>5.45677328109741</v>
       </c>
       <c r="H36" t="n">
         <v>102398</v>
@@ -1529,7 +1529,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460918426514</v>
+        <v>5.17460870742798</v>
       </c>
       <c r="H40" t="n">
         <v>27727</v>
@@ -1587,7 +1587,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069307327271</v>
+        <v>5.26069259643555</v>
       </c>
       <c r="H42" t="n">
         <v>79999</v>
@@ -1645,7 +1645,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844909667969</v>
+        <v>4.738450050354</v>
       </c>
       <c r="H44" t="n">
         <v>146124</v>
@@ -1703,7 +1703,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028003692627</v>
+        <v>4.61028051376343</v>
       </c>
       <c r="H46" t="n">
         <v>40055</v>
@@ -1790,7 +1790,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>4.63897466659546</v>
+        <v>4.6389741897583</v>
       </c>
       <c r="H49" t="n">
         <v>45504</v>
@@ -1819,7 +1819,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984491348267</v>
+        <v>4.61984443664551</v>
       </c>
       <c r="H50" t="n">
         <v>32253</v>
@@ -1848,7 +1848,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671691894531</v>
+        <v>4.55671644210815</v>
       </c>
       <c r="H51" t="n">
         <v>33202</v>
@@ -1877,7 +1877,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732414245605</v>
+        <v>4.58732461929321</v>
       </c>
       <c r="H52" t="n">
         <v>22397</v>
@@ -1906,7 +1906,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G53" t="n">
-        <v>4.53184747695923</v>
+        <v>4.53184795379639</v>
       </c>
       <c r="H53" t="n">
         <v>41654</v>
@@ -1935,7 +1935,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G54" t="n">
-        <v>4.53184747695923</v>
+        <v>4.53184795379639</v>
       </c>
       <c r="H54" t="n">
         <v>15612</v>
@@ -1993,7 +1993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985179901123</v>
+        <v>4.39985275268555</v>
       </c>
       <c r="H56" t="n">
         <v>6922</v>
@@ -2167,7 +2167,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793872833252</v>
+        <v>4.39793968200684</v>
       </c>
       <c r="H62" t="n">
         <v>183307</v>
@@ -2196,7 +2196,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202053070068</v>
+        <v>4.57202005386353</v>
       </c>
       <c r="H63" t="n">
         <v>101318</v>
@@ -2254,7 +2254,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H65" t="n">
         <v>59895</v>
@@ -2283,7 +2283,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.06508111953735</v>
+        <v>4.0650806427002</v>
       </c>
       <c r="H66" t="n">
         <v>69251</v>
@@ -2312,7 +2312,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265031814575</v>
+        <v>3.94265055656433</v>
       </c>
       <c r="H67" t="n">
         <v>49492</v>
@@ -2341,7 +2341,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691870689392</v>
+        <v>3.71691846847534</v>
       </c>
       <c r="H68" t="n">
         <v>96719</v>
@@ -2370,7 +2370,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726362228394</v>
+        <v>3.79726386070251</v>
       </c>
       <c r="H69" t="n">
         <v>35741</v>
@@ -2428,7 +2428,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987436294556</v>
+        <v>3.73987460136414</v>
       </c>
       <c r="H71" t="n">
         <v>26533</v>
@@ -2457,7 +2457,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>3.80682897567749</v>
+        <v>3.80682873725891</v>
       </c>
       <c r="H72" t="n">
         <v>32798</v>
@@ -2486,7 +2486,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813386917114</v>
+        <v>3.77813410758972</v>
       </c>
       <c r="H73" t="n">
         <v>13357</v>
@@ -2515,7 +2515,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222231864929</v>
+        <v>3.73222255706787</v>
       </c>
       <c r="H74" t="n">
         <v>23567</v>
@@ -2544,7 +2544,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8489146232605</v>
+        <v>3.84891414642334</v>
       </c>
       <c r="H75" t="n">
         <v>62408</v>
@@ -2573,7 +2573,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>4.29463815689087</v>
+        <v>4.29463863372803</v>
       </c>
       <c r="H76" t="n">
         <v>172014</v>
@@ -2602,7 +2602,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723049163818</v>
+        <v>4.78723096847534</v>
       </c>
       <c r="H77" t="n">
         <v>182115</v>
@@ -2660,7 +2660,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07895946502686</v>
+        <v>5.07896041870117</v>
       </c>
       <c r="H79" t="n">
         <v>724913</v>
@@ -2689,7 +2689,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>5.30851745605469</v>
+        <v>5.30851793289185</v>
       </c>
       <c r="H80" t="n">
         <v>273720</v>
@@ -2805,7 +2805,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417678833008</v>
+        <v>5.07417774200439</v>
       </c>
       <c r="H84" t="n">
         <v>122889</v>
@@ -2892,7 +2892,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653697967529</v>
+        <v>4.73653650283813</v>
       </c>
       <c r="H87" t="n">
         <v>101740</v>
@@ -2921,7 +2921,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680641174316</v>
+        <v>4.46680593490601</v>
       </c>
       <c r="H88" t="n">
         <v>98603</v>
@@ -3008,7 +3008,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H91" t="n">
         <v>78370</v>
@@ -3037,7 +3037,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559837341309</v>
+        <v>4.18559885025024</v>
       </c>
       <c r="H92" t="n">
         <v>40037</v>
@@ -3095,7 +3095,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>4.27550888061523</v>
+        <v>4.27550840377808</v>
       </c>
       <c r="H94" t="n">
         <v>105195</v>
@@ -3153,7 +3153,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16072988510132</v>
+        <v>4.16073036193848</v>
       </c>
       <c r="H96" t="n">
         <v>114509</v>
@@ -3182,7 +3182,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.1167311668396</v>
+        <v>4.11673164367676</v>
       </c>
       <c r="H97" t="n">
         <v>33027</v>
@@ -3269,7 +3269,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846477508545</v>
+        <v>4.29846429824829</v>
       </c>
       <c r="H100" t="n">
         <v>67373</v>
@@ -3298,7 +3298,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157020568848</v>
+        <v>5.02157068252563</v>
       </c>
       <c r="H101" t="n">
         <v>322788</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113924026489</v>
+        <v>4.92113971710205</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3414,7 +3414,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G105" t="n">
-        <v>5.40894985198975</v>
+        <v>5.40894937515259</v>
       </c>
       <c r="H105" t="n">
         <v>257471</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H106" t="n">
         <v>756136</v>
@@ -3501,7 +3501,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>7.25497436523438</v>
+        <v>7.25497388839722</v>
       </c>
       <c r="H108" t="n">
         <v>611973</v>
@@ -3530,7 +3530,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367540359497</v>
+        <v>7.06367683410645</v>
       </c>
       <c r="H109" t="n">
         <v>396366</v>
@@ -3559,7 +3559,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G110" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H110" t="n">
         <v>192489</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804088592529</v>
+        <v>6.52804183959961</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3617,7 +3617,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>6.26022481918335</v>
+        <v>6.26022434234619</v>
       </c>
       <c r="H112" t="n">
         <v>219748</v>
@@ -3646,7 +3646,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237419128418</v>
+        <v>6.98237466812134</v>
       </c>
       <c r="H113" t="n">
         <v>407399</v>
@@ -3733,7 +3733,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718311309814</v>
       </c>
       <c r="H116" t="n">
         <v>279195</v>
@@ -3762,7 +3762,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718311309814</v>
       </c>
       <c r="H117" t="n">
         <v>281217</v>
@@ -3791,7 +3791,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>5.83458662033081</v>
+        <v>5.83458614349365</v>
       </c>
       <c r="H118" t="n">
         <v>228253</v>
@@ -3820,7 +3820,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>5.87762975692749</v>
+        <v>5.87762880325317</v>
       </c>
       <c r="H119" t="n">
         <v>158117</v>
@@ -3936,7 +3936,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195426940918</v>
+        <v>6.55195379257202</v>
       </c>
       <c r="H123" t="n">
         <v>388485</v>
@@ -3965,7 +3965,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.06892681121826</v>
+        <v>6.0689263343811</v>
       </c>
       <c r="H124" t="n">
         <v>130995</v>
@@ -3994,7 +3994,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83936882019043</v>
+        <v>5.83936929702759</v>
       </c>
       <c r="H125" t="n">
         <v>111496</v>
@@ -4023,7 +4023,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>6.26022481918335</v>
+        <v>6.26022434234619</v>
       </c>
       <c r="H126" t="n">
         <v>126051</v>
@@ -4255,7 +4255,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>6.63803815841675</v>
+        <v>6.63803863525391</v>
       </c>
       <c r="H134" t="n">
         <v>118333</v>
@@ -4284,7 +4284,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933568954468</v>
+        <v>6.82933616638184</v>
       </c>
       <c r="H135" t="n">
         <v>65285</v>
@@ -4371,7 +4371,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584733963013</v>
+        <v>7.12584781646729</v>
       </c>
       <c r="H138" t="n">
         <v>47644</v>
@@ -4400,7 +4400,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>6.96802711486816</v>
+        <v>6.96802663803101</v>
       </c>
       <c r="H139" t="n">
         <v>127471</v>
@@ -4516,7 +4516,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H143" t="n">
         <v>31912</v>
@@ -4545,7 +4545,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H144" t="n">
         <v>21903</v>
@@ -4574,7 +4574,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>6.88672542572021</v>
+        <v>6.88672494888306</v>
       </c>
       <c r="H145" t="n">
         <v>55058</v>
@@ -4603,7 +4603,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>6.79107618331909</v>
+        <v>6.79107666015625</v>
       </c>
       <c r="H146" t="n">
         <v>18313</v>
@@ -4632,7 +4632,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>6.92498445510864</v>
+        <v>6.9249849319458</v>
       </c>
       <c r="H147" t="n">
         <v>105405</v>
@@ -4690,7 +4690,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87237787246704</v>
+        <v>6.8723783493042</v>
       </c>
       <c r="H149" t="n">
         <v>71959</v>
@@ -4922,7 +4922,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886423110962</v>
+        <v>7.93886518478394</v>
       </c>
       <c r="H157" t="n">
         <v>265495</v>
@@ -4951,7 +4951,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>8.09190368652344</v>
+        <v>8.0919017791748</v>
       </c>
       <c r="H158" t="n">
         <v>272541</v>
@@ -5009,7 +5009,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G160" t="n">
-        <v>7.91017055511475</v>
+        <v>7.91016960144043</v>
       </c>
       <c r="H160" t="n">
         <v>57170</v>
@@ -5038,7 +5038,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>7.6710467338562</v>
+        <v>7.67104721069336</v>
       </c>
       <c r="H161" t="n">
         <v>97882</v>
@@ -5125,7 +5125,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234474182129</v>
+        <v>7.86234521865845</v>
       </c>
       <c r="H164" t="n">
         <v>30398</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626085281372</v>
+        <v>7.77626132965088</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.99625301361084</v>
+        <v>7.99625253677368</v>
       </c>
       <c r="H166" t="n">
         <v>48102</v>
@@ -5328,7 +5328,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669549942017</v>
+        <v>7.76669597625732</v>
       </c>
       <c r="H171" t="n">
         <v>80513</v>
@@ -5415,7 +5415,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928558349609</v>
       </c>
       <c r="H174" t="n">
         <v>135297</v>
@@ -5473,7 +5473,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>9.00535106658936</v>
+        <v>9.00535011291504</v>
       </c>
       <c r="H176" t="n">
         <v>166097</v>
@@ -5502,7 +5502,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622772216797</v>
+        <v>8.76622676849365</v>
       </c>
       <c r="H177" t="n">
         <v>231642</v>
@@ -5531,7 +5531,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65623092651367</v>
+        <v>8.65623188018799</v>
       </c>
       <c r="H178" t="n">
         <v>104419</v>
@@ -5560,7 +5560,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G179" t="n">
-        <v>8.35015487670898</v>
+        <v>8.35015392303467</v>
       </c>
       <c r="H179" t="n">
         <v>237396</v>
@@ -5676,7 +5676,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>8.20668125152588</v>
+        <v>8.20668029785156</v>
       </c>
       <c r="H183" t="n">
         <v>59457</v>
@@ -5705,7 +5705,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.25450611114502</v>
+        <v>8.2545051574707</v>
       </c>
       <c r="H184" t="n">
         <v>33220</v>
@@ -5734,7 +5734,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.92451667785645</v>
+        <v>7.9245171546936</v>
       </c>
       <c r="H185" t="n">
         <v>122464</v>
@@ -5763,7 +5763,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581100463867</v>
+        <v>8.22581195831299</v>
       </c>
       <c r="H186" t="n">
         <v>99183</v>
@@ -5792,7 +5792,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34059047698975</v>
+        <v>8.34058952331543</v>
       </c>
       <c r="H187" t="n">
         <v>63159</v>
@@ -5821,7 +5821,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928558349609</v>
       </c>
       <c r="H188" t="n">
         <v>34542</v>
@@ -5850,7 +5850,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754829406738</v>
+        <v>8.29754638671875</v>
       </c>
       <c r="H189" t="n">
         <v>29985</v>
@@ -5879,7 +5879,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.27363586425781</v>
+        <v>8.2736349105835</v>
       </c>
       <c r="H190" t="n">
         <v>51064</v>
@@ -5908,7 +5908,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928462982178</v>
+        <v>8.36928558349609</v>
       </c>
       <c r="H191" t="n">
         <v>24030</v>
@@ -5966,7 +5966,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>8.55101776123047</v>
+        <v>8.55101680755615</v>
       </c>
       <c r="H193" t="n">
         <v>104665</v>
@@ -5995,7 +5995,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>8.92883014678955</v>
+        <v>8.92883110046387</v>
       </c>
       <c r="H194" t="n">
         <v>196106</v>
@@ -6024,7 +6024,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.06752109527588</v>
+        <v>9.06752014160156</v>
       </c>
       <c r="H195" t="n">
         <v>116469</v>
@@ -6053,7 +6053,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.1057825088501</v>
+        <v>9.10578155517578</v>
       </c>
       <c r="H196" t="n">
         <v>198688</v>
@@ -6082,7 +6082,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968982696533</v>
+        <v>9.23968887329102</v>
       </c>
       <c r="H197" t="n">
         <v>111328</v>
@@ -6111,7 +6111,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G198" t="n">
-        <v>9.05317401885986</v>
+        <v>9.05317497253418</v>
       </c>
       <c r="H198" t="n">
         <v>156638</v>
@@ -6140,7 +6140,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708324432373</v>
+        <v>9.18708229064941</v>
       </c>
       <c r="H199" t="n">
         <v>82966</v>
@@ -6169,7 +6169,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882694244385</v>
+        <v>9.03882598876953</v>
       </c>
       <c r="H200" t="n">
         <v>84914</v>
@@ -6227,7 +6227,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.17273616790771</v>
+        <v>9.1727352142334</v>
       </c>
       <c r="H202" t="n">
         <v>47674</v>
@@ -6256,7 +6256,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185760498047</v>
+        <v>9.41185855865479</v>
       </c>
       <c r="H203" t="n">
         <v>115834</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6314,7 +6314,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>9.5170726776123</v>
+        <v>9.51707172393799</v>
       </c>
       <c r="H205" t="n">
         <v>125905</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489658355713</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6430,7 +6430,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G209" t="n">
-        <v>10.3587837219238</v>
+        <v>10.3587827682495</v>
       </c>
       <c r="H209" t="n">
         <v>324694</v>
@@ -6633,7 +6633,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518051147461</v>
+        <v>10.9518060684204</v>
       </c>
       <c r="H216" t="n">
         <v>101398</v>
@@ -6662,7 +6662,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H217" t="n">
         <v>175009</v>
@@ -6691,7 +6691,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.043140411377</v>
+        <v>10.0431413650513</v>
       </c>
       <c r="H218" t="n">
         <v>270935</v>
@@ -6720,7 +6720,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831266403198</v>
+        <v>10.4831256866455</v>
       </c>
       <c r="H219" t="n">
         <v>128669</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692100524902</v>
+        <v>10.5692110061646</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6836,7 +6836,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G223" t="n">
-        <v>10.9613704681396</v>
+        <v>10.961371421814</v>
       </c>
       <c r="H223" t="n">
         <v>86558</v>
@@ -6865,7 +6865,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.1144094467163</v>
+        <v>11.114408493042</v>
       </c>
       <c r="H224" t="n">
         <v>91003</v>
@@ -6923,7 +6923,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117858886719</v>
+        <v>11.6117849349976</v>
       </c>
       <c r="H226" t="n">
         <v>191398</v>
@@ -6981,7 +6981,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456932067871</v>
+        <v>11.7456912994385</v>
       </c>
       <c r="H228" t="n">
         <v>176751</v>
@@ -7010,7 +7010,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648229598999</v>
+        <v>11.7648220062256</v>
       </c>
       <c r="H229" t="n">
         <v>87480</v>
@@ -7039,7 +7039,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G230" t="n">
-        <v>11.630913734436</v>
+        <v>11.6309127807617</v>
       </c>
       <c r="H230" t="n">
         <v>118136</v>
@@ -7068,7 +7068,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>11.6691732406616</v>
+        <v>11.6691722869873</v>
       </c>
       <c r="H231" t="n">
         <v>95647</v>
@@ -7097,7 +7097,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708980560303</v>
+        <v>12.0708990097046</v>
       </c>
       <c r="H232" t="n">
         <v>161563</v>
@@ -7155,7 +7155,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H234" t="n">
         <v>153081</v>
@@ -7184,7 +7184,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.936990737915</v>
+        <v>11.9369897842407</v>
       </c>
       <c r="H235" t="n">
         <v>95580</v>
@@ -7271,7 +7271,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839508056641</v>
+        <v>11.7839527130127</v>
       </c>
       <c r="H238" t="n">
         <v>75176</v>
@@ -7300,7 +7300,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G239" t="n">
-        <v>12.4248008728027</v>
+        <v>12.4247999191284</v>
       </c>
       <c r="H239" t="n">
         <v>134820</v>
@@ -7329,7 +7329,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.616096496582</v>
+        <v>12.6160984039307</v>
       </c>
       <c r="H240" t="n">
         <v>180021</v>
@@ -7387,7 +7387,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717241287231</v>
+        <v>13.3717250823975</v>
       </c>
       <c r="H242" t="n">
         <v>100896</v>
@@ -7416,7 +7416,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473434448242</v>
       </c>
       <c r="H243" t="n">
         <v>303111</v>
@@ -7445,7 +7445,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446575164795</v>
+        <v>15.2446565628052</v>
       </c>
       <c r="H244" t="n">
         <v>256881</v>
@@ -7474,7 +7474,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.038592338562</v>
+        <v>14.0385932922363</v>
       </c>
       <c r="H245" t="n">
         <v>494015</v>
@@ -7532,7 +7532,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>13.8456220626831</v>
+        <v>13.8456230163574</v>
       </c>
       <c r="H247" t="n">
         <v>263722</v>
@@ -7561,7 +7561,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G248" t="n">
-        <v>13.3728446960449</v>
+        <v>13.3728437423706</v>
       </c>
       <c r="H248" t="n">
         <v>127762</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272226333618</v>
+        <v>13.5272207260132</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7706,7 +7706,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>12.9772567749023</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H253" t="n">
         <v>84013</v>
@@ -7822,7 +7822,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000663757324</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H257" t="n">
         <v>36672</v>
@@ -7880,7 +7880,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H259" t="n">
         <v>124706</v>
@@ -7938,7 +7938,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.9869031906128</v>
+        <v>12.9869041442871</v>
       </c>
       <c r="H261" t="n">
         <v>30726</v>
@@ -7967,7 +7967,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>12.9772567749023</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H262" t="n">
         <v>39442</v>
@@ -7996,7 +7996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H263" t="n">
         <v>90090</v>
@@ -8054,7 +8054,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7877321243286</v>
+        <v>13.78773021698</v>
       </c>
       <c r="H265" t="n">
         <v>225704</v>
@@ -8083,7 +8083,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973794937134</v>
+        <v>13.7973804473877</v>
       </c>
       <c r="H266" t="n">
         <v>74231</v>
@@ -8141,7 +8141,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>13.8359727859497</v>
+        <v>13.835973739624</v>
       </c>
       <c r="H268" t="n">
         <v>66219</v>
@@ -8170,7 +8170,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G269" t="n">
-        <v>13.5851125717163</v>
+        <v>13.585111618042</v>
       </c>
       <c r="H269" t="n">
         <v>52002</v>
@@ -8257,7 +8257,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H272" t="n">
         <v>43627</v>
@@ -8286,7 +8286,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G273" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H273" t="n">
         <v>167282</v>
@@ -8344,7 +8344,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869724273682</v>
+        <v>11.8869733810425</v>
       </c>
       <c r="H275" t="n">
         <v>94457</v>
@@ -8402,7 +8402,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G277" t="n">
-        <v>11.539626121521</v>
+        <v>11.5396270751953</v>
       </c>
       <c r="H277" t="n">
         <v>194589</v>
@@ -8431,7 +8431,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H278" t="n">
         <v>152414</v>
@@ -8489,7 +8489,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G280" t="n">
-        <v>11.665057182312</v>
+        <v>11.6650581359863</v>
       </c>
       <c r="H280" t="n">
         <v>34289</v>
@@ -8605,7 +8605,7 @@
         <v>11.75</v>
       </c>
       <c r="G284" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H284" t="n">
         <v>114241</v>
@@ -8634,7 +8634,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>10.8063402175903</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H285" t="n">
         <v>135254</v>
@@ -8692,7 +8692,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484474182129</v>
+        <v>10.7484483718872</v>
       </c>
       <c r="H287" t="n">
         <v>33613</v>
@@ -8750,7 +8750,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431400299072</v>
+        <v>11.4431409835815</v>
       </c>
       <c r="H289" t="n">
         <v>181496</v>
@@ -8895,7 +8895,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>11.0089588165283</v>
+        <v>11.008957862854</v>
       </c>
       <c r="H294" t="n">
         <v>9802</v>
@@ -8953,7 +8953,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G296" t="n">
-        <v>10.5072345733643</v>
+        <v>10.5072355270386</v>
       </c>
       <c r="H296" t="n">
         <v>45140</v>
@@ -8982,7 +8982,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695375442505</v>
+        <v>10.1695384979248</v>
       </c>
       <c r="H297" t="n">
         <v>66319</v>
@@ -9011,7 +9011,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247406005859</v>
+        <v>11.1247396469116</v>
       </c>
       <c r="H298" t="n">
         <v>108006</v>
@@ -9127,7 +9127,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273591995239</v>
+        <v>11.3273601531982</v>
       </c>
       <c r="H302" t="n">
         <v>104822</v>
@@ -9185,7 +9185,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.4369382858276</v>
+        <v>12.436939239502</v>
       </c>
       <c r="H304" t="n">
         <v>178543</v>
@@ -9243,7 +9243,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G306" t="n">
-        <v>11.7808399200439</v>
+        <v>11.7808389663696</v>
       </c>
       <c r="H306" t="n">
         <v>50004</v>
@@ -9301,7 +9301,7 @@
         <v>11.75</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H308" t="n">
         <v>79684</v>
@@ -9388,7 +9388,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212247848511</v>
+        <v>11.2212257385254</v>
       </c>
       <c r="H311" t="n">
         <v>48985</v>
@@ -9417,7 +9417,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>11.1054439544678</v>
+        <v>11.1054430007935</v>
       </c>
       <c r="H312" t="n">
         <v>33585</v>
@@ -9475,7 +9475,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>11.5299777984619</v>
+        <v>11.5299787521362</v>
       </c>
       <c r="H314" t="n">
         <v>80574</v>
@@ -9504,7 +9504,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.4334945678711</v>
+        <v>11.4334936141968</v>
       </c>
       <c r="H315" t="n">
         <v>31751</v>
@@ -9533,7 +9533,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H316" t="n">
         <v>113990</v>
@@ -9562,7 +9562,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H317" t="n">
         <v>48953</v>
@@ -9591,7 +9591,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220527648926</v>
+        <v>12.0220518112183</v>
       </c>
       <c r="H318" t="n">
         <v>61490</v>
@@ -9678,7 +9678,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H321" t="n">
         <v>47231</v>
@@ -9707,7 +9707,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G322" t="n">
-        <v>12.0027551651001</v>
+        <v>12.0027542114258</v>
       </c>
       <c r="H322" t="n">
         <v>26238</v>
@@ -9736,7 +9736,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387317657471</v>
+        <v>11.8387308120728</v>
       </c>
       <c r="H323" t="n">
         <v>88601</v>
@@ -9794,7 +9794,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640916824341</v>
+        <v>13.0640926361084</v>
       </c>
       <c r="H325" t="n">
         <v>437770</v>
@@ -9852,7 +9852,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G327" t="n">
-        <v>13.6140575408936</v>
+        <v>13.6140565872192</v>
       </c>
       <c r="H327" t="n">
         <v>135660</v>
@@ -9881,7 +9881,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H328" t="n">
         <v>133226</v>
@@ -9939,7 +9939,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H330" t="n">
         <v>80883</v>
@@ -9968,7 +9968,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H331" t="n">
         <v>127592</v>
@@ -10026,7 +10026,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886255264282</v>
+        <v>13.4886264801025</v>
       </c>
       <c r="H333" t="n">
         <v>19569</v>
@@ -10055,7 +10055,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.7105417251587</v>
+        <v>13.710542678833</v>
       </c>
       <c r="H334" t="n">
         <v>74737</v>
@@ -10084,7 +10084,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>13.3631973266602</v>
+        <v>13.3631963729858</v>
       </c>
       <c r="H335" t="n">
         <v>56318</v>
@@ -10113,7 +10113,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394886016846</v>
+        <v>13.7394876480103</v>
       </c>
       <c r="H336" t="n">
         <v>66093</v>
@@ -10142,7 +10142,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552694320679</v>
+        <v>13.8552703857422</v>
       </c>
       <c r="H337" t="n">
         <v>35661</v>
@@ -10229,7 +10229,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807004928589</v>
+        <v>13.9807014465332</v>
       </c>
       <c r="H340" t="n">
         <v>101573</v>
@@ -10258,7 +10258,7 @@
         <v>14.75</v>
       </c>
       <c r="G341" t="n">
-        <v>14.2315635681152</v>
+        <v>14.2315626144409</v>
       </c>
       <c r="H341" t="n">
         <v>95930</v>
@@ -10287,7 +10287,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>14.7815284729004</v>
+        <v>14.7815275192261</v>
       </c>
       <c r="H342" t="n">
         <v>193154</v>
@@ -10316,7 +10316,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>14.492073059082</v>
+        <v>14.4920721054077</v>
       </c>
       <c r="H343" t="n">
         <v>175404</v>
@@ -10345,7 +10345,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H344" t="n">
         <v>84729</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5692615509033</v>
+        <v>14.569260597229</v>
       </c>
       <c r="H346" t="n">
         <v>63786</v>
@@ -10490,7 +10490,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052352905273</v>
+        <v>14.405237197876</v>
       </c>
       <c r="H349" t="n">
         <v>73630</v>
@@ -10519,7 +10519,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824247360229</v>
+        <v>14.4824237823486</v>
       </c>
       <c r="H350" t="n">
         <v>97965</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527219772339</v>
+        <v>12.5527210235596</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10635,7 +10635,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>12.9386625289917</v>
+        <v>12.9386615753174</v>
       </c>
       <c r="H354" t="n">
         <v>113586</v>
@@ -10664,7 +10664,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.8807697296143</v>
+        <v>12.8807706832886</v>
       </c>
       <c r="H355" t="n">
         <v>60981</v>
@@ -10693,7 +10693,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000663757324</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H356" t="n">
         <v>42754</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.006199836731</v>
+        <v>13.0062017440796</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10838,7 +10838,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H361" t="n">
         <v>30895</v>
@@ -10954,7 +10954,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H365" t="n">
         <v>55168</v>
@@ -11012,7 +11012,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360420227051</v>
+        <v>12.7360429763794</v>
       </c>
       <c r="H367" t="n">
         <v>41635</v>
@@ -11041,7 +11041,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>12.7263927459717</v>
+        <v>12.726393699646</v>
       </c>
       <c r="H368" t="n">
         <v>31587</v>
@@ -11070,7 +11070,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H369" t="n">
         <v>33590</v>
@@ -11128,7 +11128,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755325317383</v>
+        <v>12.4755334854126</v>
       </c>
       <c r="H371" t="n">
         <v>12596</v>
@@ -11215,7 +11215,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150230407715</v>
+        <v>12.2150220870972</v>
       </c>
       <c r="H374" t="n">
         <v>20005</v>
@@ -11273,7 +11273,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H376" t="n">
         <v>18790</v>
@@ -11331,7 +11331,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176425933838</v>
+        <v>12.4176416397095</v>
       </c>
       <c r="H378" t="n">
         <v>61237</v>
@@ -11389,7 +11389,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1571311950684</v>
+        <v>12.1571321487427</v>
       </c>
       <c r="H380" t="n">
         <v>38689</v>
@@ -11418,7 +11418,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580284118652</v>
+        <v>11.8580274581909</v>
       </c>
       <c r="H381" t="n">
         <v>64542</v>
@@ -11447,7 +11447,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194341659546</v>
+        <v>11.8194332122803</v>
       </c>
       <c r="H382" t="n">
         <v>27743</v>
@@ -11534,7 +11534,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325963973999</v>
+        <v>11.7325954437256</v>
       </c>
       <c r="H385" t="n">
         <v>6733</v>
@@ -11708,7 +11708,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H391" t="n">
         <v>36167</v>
@@ -11795,7 +11795,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545135498047</v>
+        <v>11.9545125961304</v>
       </c>
       <c r="H394" t="n">
         <v>7832</v>
@@ -11824,7 +11824,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H395" t="n">
         <v>18587</v>
@@ -11853,7 +11853,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.243968963623</v>
+        <v>12.2439670562744</v>
       </c>
       <c r="H396" t="n">
         <v>21900</v>
@@ -11998,7 +11998,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H401" t="n">
         <v>13252</v>
@@ -12027,7 +12027,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H402" t="n">
         <v>31655</v>
@@ -12056,7 +12056,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>12.5623693466187</v>
+        <v>12.562370300293</v>
       </c>
       <c r="H403" t="n">
         <v>8745</v>
@@ -12085,7 +12085,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H404" t="n">
         <v>9320</v>
@@ -12143,7 +12143,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6685037612915</v>
+        <v>12.6685028076172</v>
       </c>
       <c r="H406" t="n">
         <v>26294</v>
@@ -12172,7 +12172,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9772567749023</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H407" t="n">
         <v>26025</v>
@@ -12259,7 +12259,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H410" t="n">
         <v>21714</v>
@@ -12317,7 +12317,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219825744629</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H412" t="n">
         <v>20167</v>
@@ -12375,7 +12375,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115072250366</v>
+        <v>12.3115081787109</v>
       </c>
       <c r="H414" t="n">
         <v>76954</v>
@@ -12404,7 +12404,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>12.5623693466187</v>
+        <v>12.562370300293</v>
       </c>
       <c r="H415" t="n">
         <v>14241</v>
@@ -12491,7 +12491,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193639755249</v>
+        <v>12.9193649291992</v>
       </c>
       <c r="H418" t="n">
         <v>10876</v>
@@ -12520,7 +12520,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G419" t="n">
-        <v>12.9869031906128</v>
+        <v>12.9869041442871</v>
       </c>
       <c r="H419" t="n">
         <v>4823</v>
@@ -12578,7 +12578,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G421" t="n">
-        <v>12.9772567749023</v>
+        <v>12.977255821228</v>
       </c>
       <c r="H421" t="n">
         <v>36559</v>
@@ -12607,7 +12607,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H422" t="n">
         <v>22215</v>
@@ -12665,7 +12665,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H424" t="n">
         <v>8468</v>
@@ -12694,7 +12694,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>12.7167453765869</v>
+        <v>12.7167463302612</v>
       </c>
       <c r="H425" t="n">
         <v>35809</v>
@@ -12752,7 +12752,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>12.8807697296143</v>
+        <v>12.8807706832886</v>
       </c>
       <c r="H427" t="n">
         <v>13721</v>
@@ -12781,7 +12781,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H428" t="n">
         <v>13836</v>
@@ -12810,7 +12810,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H429" t="n">
         <v>23103</v>
@@ -12839,7 +12839,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H430" t="n">
         <v>30798</v>
@@ -12926,7 +12926,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>13.1798753738403</v>
+        <v>13.179874420166</v>
       </c>
       <c r="H433" t="n">
         <v>273024</v>
@@ -12984,7 +12984,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>13.9324588775635</v>
+        <v>13.9324579238892</v>
       </c>
       <c r="H435" t="n">
         <v>95509</v>
@@ -13129,7 +13129,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G440" t="n">
-        <v>12.5720167160034</v>
+        <v>12.5720176696777</v>
       </c>
       <c r="H440" t="n">
         <v>33681</v>
@@ -13158,7 +13158,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>12.7263927459717</v>
+        <v>12.726393699646</v>
       </c>
       <c r="H441" t="n">
         <v>30766</v>
@@ -13216,7 +13216,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>12.6395568847656</v>
+        <v>12.6395578384399</v>
       </c>
       <c r="H443" t="n">
         <v>19797</v>
@@ -13303,7 +13303,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H446" t="n">
         <v>35222</v>
@@ -13332,7 +13332,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202602386475</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H447" t="n">
         <v>14428</v>
@@ -13390,7 +13390,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>12.6685037612915</v>
+        <v>12.6685028076172</v>
       </c>
       <c r="H449" t="n">
         <v>33026</v>
@@ -13419,7 +13419,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G450" t="n">
-        <v>12.6781520843506</v>
+        <v>12.6781511306763</v>
       </c>
       <c r="H450" t="n">
         <v>8729</v>
@@ -13564,7 +13564,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483791351318</v>
+        <v>11.8483781814575</v>
       </c>
       <c r="H455" t="n">
         <v>45659</v>
@@ -13593,7 +13593,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H456" t="n">
         <v>40685</v>
@@ -13622,7 +13622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H457" t="n">
         <v>24461</v>
@@ -13709,7 +13709,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>12.4465866088867</v>
+        <v>12.446587562561</v>
       </c>
       <c r="H460" t="n">
         <v>60559</v>
@@ -13738,7 +13738,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H461" t="n">
         <v>38181</v>
@@ -13854,7 +13854,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G465" t="n">
-        <v>11.9352159500122</v>
+        <v>11.9352149963379</v>
       </c>
       <c r="H465" t="n">
         <v>21056</v>
@@ -13883,7 +13883,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H466" t="n">
         <v>20941</v>
@@ -13941,7 +13941,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H468" t="n">
         <v>13736</v>
@@ -13970,7 +13970,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.118537902832</v>
+        <v>12.1185369491577</v>
       </c>
       <c r="H469" t="n">
         <v>26893</v>
@@ -14086,7 +14086,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>12.1088895797729</v>
+        <v>12.1088886260986</v>
       </c>
       <c r="H473" t="n">
         <v>20258</v>
@@ -14144,7 +14144,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>12.0124025344849</v>
+        <v>12.0124034881592</v>
       </c>
       <c r="H475" t="n">
         <v>13507</v>
@@ -14173,7 +14173,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>11.8290824890137</v>
+        <v>11.8290815353394</v>
       </c>
       <c r="H476" t="n">
         <v>75300</v>
@@ -14202,7 +14202,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747064590454</v>
+        <v>11.6747074127197</v>
       </c>
       <c r="H477" t="n">
         <v>345190</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554733276367</v>
+        <v>9.45554637908936</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14289,7 +14289,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>9.65816497802734</v>
+        <v>9.65816593170166</v>
       </c>
       <c r="H480" t="n">
         <v>142514</v>
@@ -14434,7 +14434,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107503890991</v>
+        <v>10.4107494354248</v>
       </c>
       <c r="H485" t="n">
         <v>165118</v>
@@ -14492,7 +14492,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.8063402175903</v>
+        <v>10.806339263916</v>
       </c>
       <c r="H487" t="n">
         <v>73996</v>
@@ -14550,7 +14550,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G489" t="n">
-        <v>10.71950340271</v>
+        <v>10.7195024490356</v>
       </c>
       <c r="H489" t="n">
         <v>62047</v>
@@ -14666,7 +14666,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256368637085</v>
+        <v>10.8256359100342</v>
       </c>
       <c r="H493" t="n">
         <v>48038</v>
@@ -14782,7 +14782,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7388000488281</v>
+        <v>10.7387990951538</v>
       </c>
       <c r="H497" t="n">
         <v>62706</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078981399536</v>
+        <v>10.7078971862793</v>
       </c>
       <c r="H500" t="n">
         <v>97230</v>
@@ -14898,7 +14898,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G501" t="n">
-        <v>10.4732036590576</v>
+        <v>10.4732046127319</v>
       </c>
       <c r="H501" t="n">
         <v>197020</v>
@@ -14956,7 +14956,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189521789551</v>
+        <v>10.2189531326294</v>
       </c>
       <c r="H503" t="n">
         <v>87325</v>
@@ -14985,7 +14985,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612144470215</v>
+        <v>10.5612154006958</v>
       </c>
       <c r="H504" t="n">
         <v>62409</v>
@@ -15043,7 +15043,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4536466598511</v>
+        <v>10.4536457061768</v>
       </c>
       <c r="H506" t="n">
         <v>53759</v>
@@ -15072,7 +15072,7 @@
         <v>10.75</v>
       </c>
       <c r="G507" t="n">
-        <v>10.5123195648193</v>
+        <v>10.5123205184937</v>
       </c>
       <c r="H507" t="n">
         <v>171168</v>
@@ -15101,7 +15101,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G508" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H508" t="n">
         <v>53290</v>
@@ -15130,7 +15130,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G509" t="n">
-        <v>10.4047527313232</v>
+        <v>10.4047517776489</v>
       </c>
       <c r="H509" t="n">
         <v>85761</v>
@@ -15188,7 +15188,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G511" t="n">
-        <v>10.5807723999023</v>
+        <v>10.580771446228</v>
       </c>
       <c r="H511" t="n">
         <v>29173</v>
@@ -15275,7 +15275,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G514" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763509750366</v>
       </c>
       <c r="H514" t="n">
         <v>22557</v>
@@ -15304,7 +15304,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H515" t="n">
         <v>114765</v>
@@ -15362,7 +15362,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110454559326</v>
+        <v>11.0110445022583</v>
       </c>
       <c r="H517" t="n">
         <v>116880</v>
@@ -15449,7 +15449,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G520" t="n">
-        <v>10.7763500213623</v>
+        <v>10.7763509750366</v>
       </c>
       <c r="H520" t="n">
         <v>17838</v>
@@ -15681,7 +15681,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H528" t="n">
         <v>31481</v>
@@ -15942,7 +15942,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G537" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H537" t="n">
         <v>66947</v>
@@ -16087,7 +16087,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261028289795</v>
+        <v>9.17261123657227</v>
       </c>
       <c r="H542" t="n">
         <v>15487</v>
@@ -16116,7 +16116,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H543" t="n">
         <v>21472</v>
@@ -16145,7 +16145,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>9.64199733734131</v>
+        <v>9.64199829101562</v>
       </c>
       <c r="H544" t="n">
         <v>45893</v>
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H545" t="n">
         <v>37787</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H546" t="n">
         <v>15589</v>
@@ -16232,7 +16232,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509262084961</v>
+        <v>9.50509357452393</v>
       </c>
       <c r="H547" t="n">
         <v>11946</v>
@@ -16261,7 +16261,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G548" t="n">
-        <v>9.45619964599609</v>
+        <v>9.45619869232178</v>
       </c>
       <c r="H548" t="n">
         <v>15955</v>
@@ -16290,7 +16290,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H549" t="n">
         <v>23576</v>
@@ -16377,7 +16377,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G552" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H552" t="n">
         <v>45912</v>
@@ -16406,7 +16406,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H553" t="n">
         <v>22573</v>
@@ -16435,7 +16435,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G554" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H554" t="n">
         <v>94454</v>
@@ -16464,7 +16464,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432929992676</v>
+        <v>8.65432834625244</v>
       </c>
       <c r="H555" t="n">
         <v>68485</v>
@@ -16580,7 +16580,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H559" t="n">
         <v>111011</v>
@@ -16609,7 +16609,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H560" t="n">
         <v>77526</v>
@@ -16638,7 +16638,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H561" t="n">
         <v>47843</v>
@@ -16696,7 +16696,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H563" t="n">
         <v>28072</v>
@@ -16725,7 +16725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H564" t="n">
         <v>46125</v>
@@ -16754,7 +16754,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H565" t="n">
         <v>31639</v>
@@ -16783,7 +16783,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H566" t="n">
         <v>45222</v>
@@ -16812,7 +16812,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H567" t="n">
         <v>124458</v>
@@ -16841,7 +16841,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G568" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H568" t="n">
         <v>102747</v>
@@ -16870,7 +16870,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H569" t="n">
         <v>170656</v>
@@ -16986,7 +16986,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H573" t="n">
         <v>121005</v>
@@ -17015,7 +17015,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H574" t="n">
         <v>114848</v>
@@ -17073,7 +17073,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G576" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H576" t="n">
         <v>88350</v>
@@ -17189,7 +17189,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G580" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H580" t="n">
         <v>59969</v>
@@ -17276,7 +17276,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>8.95747470855713</v>
+        <v>8.95747375488281</v>
       </c>
       <c r="H583" t="n">
         <v>20537</v>
@@ -17392,7 +17392,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H587" t="n">
         <v>46974</v>
@@ -17450,7 +17450,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H589" t="n">
         <v>44363</v>
@@ -17479,7 +17479,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H590" t="n">
         <v>85332</v>
@@ -17537,7 +17537,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H592" t="n">
         <v>73245</v>
@@ -17595,7 +17595,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G594" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H594" t="n">
         <v>58404</v>
@@ -17624,7 +17624,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H595" t="n">
         <v>58894</v>
@@ -17682,7 +17682,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H597" t="n">
         <v>168521</v>
@@ -17711,7 +17711,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H598" t="n">
         <v>140106</v>
@@ -17740,7 +17740,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H599" t="n">
         <v>76971</v>
@@ -17769,7 +17769,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H600" t="n">
         <v>116918</v>
@@ -17798,7 +17798,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G601" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H601" t="n">
         <v>24832</v>
@@ -17856,7 +17856,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492267608643</v>
+        <v>9.95492362976074</v>
       </c>
       <c r="H603" t="n">
         <v>63044</v>
@@ -17885,7 +17885,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H604" t="n">
         <v>44561</v>
@@ -17914,7 +17914,7 @@
         <v>9.75</v>
       </c>
       <c r="G605" t="n">
-        <v>9.53443050384521</v>
+        <v>9.5344295501709</v>
       </c>
       <c r="H605" t="n">
         <v>44042</v>
@@ -17943,7 +17943,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H606" t="n">
         <v>38965</v>
@@ -18001,7 +18001,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H608" t="n">
         <v>28857</v>
@@ -18030,7 +18030,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H609" t="n">
         <v>8881</v>
@@ -18059,7 +18059,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H610" t="n">
         <v>26954</v>
@@ -18088,7 +18088,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H611" t="n">
         <v>15971</v>
@@ -18117,7 +18117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H612" t="n">
         <v>14746</v>
@@ -18146,7 +18146,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G613" t="n">
-        <v>9.34863090515137</v>
+        <v>9.34862995147705</v>
       </c>
       <c r="H613" t="n">
         <v>29288</v>
@@ -18175,7 +18175,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H614" t="n">
         <v>134678</v>
@@ -18233,7 +18233,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H616" t="n">
         <v>118933</v>
@@ -18291,7 +18291,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H618" t="n">
         <v>16473</v>
@@ -18349,7 +18349,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G620" t="n">
-        <v>9.55398750305176</v>
+        <v>9.55398845672607</v>
       </c>
       <c r="H620" t="n">
         <v>270273</v>
@@ -18378,7 +18378,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H621" t="n">
         <v>192357</v>
@@ -18465,7 +18465,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H624" t="n">
         <v>136644</v>
@@ -18494,7 +18494,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H625" t="n">
         <v>69374</v>
@@ -18610,7 +18610,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354545593262</v>
+        <v>9.5735445022583</v>
       </c>
       <c r="H629" t="n">
         <v>59629</v>
@@ -18668,7 +18668,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H631" t="n">
         <v>25208</v>
@@ -18697,7 +18697,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H632" t="n">
         <v>43105</v>
@@ -18784,7 +18784,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G635" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H635" t="n">
         <v>46972</v>
@@ -18813,7 +18813,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G636" t="n">
-        <v>8.74233913421631</v>
+        <v>8.74233818054199</v>
       </c>
       <c r="H636" t="n">
         <v>26549</v>
@@ -18842,7 +18842,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548358917236</v>
+        <v>9.04548454284668</v>
       </c>
       <c r="H637" t="n">
         <v>24740</v>
@@ -18871,7 +18871,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>8.91835784912109</v>
+        <v>8.91835880279541</v>
       </c>
       <c r="H638" t="n">
         <v>19976</v>
@@ -18958,7 +18958,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H641" t="n">
         <v>23994</v>
@@ -19045,7 +19045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>9.43664073944092</v>
+        <v>9.4366397857666</v>
       </c>
       <c r="H644" t="n">
         <v>5673</v>
@@ -19103,7 +19103,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H646" t="n">
         <v>21998</v>
@@ -19132,7 +19132,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G647" t="n">
-        <v>9.64199733734131</v>
+        <v>9.64199829101562</v>
       </c>
       <c r="H647" t="n">
         <v>12149</v>
@@ -19190,7 +19190,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52465057373047</v>
+        <v>9.52464962005615</v>
       </c>
       <c r="H649" t="n">
         <v>25021</v>
@@ -19248,7 +19248,7 @@
         <v>9.5</v>
       </c>
       <c r="G651" t="n">
-        <v>9.28995800018311</v>
+        <v>9.28995704650879</v>
       </c>
       <c r="H651" t="n">
         <v>135104</v>
@@ -19277,7 +19277,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H652" t="n">
         <v>48424</v>
@@ -19306,7 +19306,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H653" t="n">
         <v>40921</v>
@@ -19335,7 +19335,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H654" t="n">
         <v>40142</v>
@@ -19364,7 +19364,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G655" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H655" t="n">
         <v>14617</v>
@@ -19422,7 +19422,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H657" t="n">
         <v>3751</v>
@@ -19480,7 +19480,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>9.33885097503662</v>
+        <v>9.33885192871094</v>
       </c>
       <c r="H659" t="n">
         <v>25360</v>
@@ -19654,7 +19654,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G665" t="n">
-        <v>9.3975248336792</v>
+        <v>9.39752388000488</v>
       </c>
       <c r="H665" t="n">
         <v>4386</v>
@@ -19741,7 +19741,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H668" t="n">
         <v>15830</v>
@@ -19770,7 +19770,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G669" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H669" t="n">
         <v>10937</v>
@@ -19857,7 +19857,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H672" t="n">
         <v>48863</v>
@@ -19886,7 +19886,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G673" t="n">
-        <v>9.76912307739258</v>
+        <v>9.76912403106689</v>
       </c>
       <c r="H673" t="n">
         <v>49111</v>
@@ -19915,7 +19915,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H674" t="n">
         <v>18840</v>
@@ -19944,7 +19944,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H675" t="n">
         <v>37373</v>
@@ -19973,7 +19973,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H676" t="n">
         <v>9923</v>
@@ -20089,7 +20089,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G680" t="n">
-        <v>9.60288143157959</v>
+        <v>9.60288238525391</v>
       </c>
       <c r="H680" t="n">
         <v>7811</v>
@@ -20118,7 +20118,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H681" t="n">
         <v>7805</v>
@@ -20147,7 +20147,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956607818604</v>
+        <v>9.74956512451172</v>
       </c>
       <c r="H682" t="n">
         <v>32449</v>
@@ -20176,7 +20176,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H683" t="n">
         <v>37382</v>
@@ -20205,7 +20205,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.87669277191162</v>
+        <v>9.8766918182373</v>
       </c>
       <c r="H684" t="n">
         <v>18917</v>
@@ -20234,7 +20234,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G685" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H685" t="n">
         <v>86835</v>
@@ -20263,7 +20263,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>9.76912307739258</v>
+        <v>9.76912403106689</v>
       </c>
       <c r="H686" t="n">
         <v>19172</v>
@@ -20292,7 +20292,7 @@
         <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H687" t="n">
         <v>13215</v>
@@ -20321,7 +20321,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G688" t="n">
-        <v>9.67133522033691</v>
+        <v>9.6713342666626</v>
       </c>
       <c r="H688" t="n">
         <v>38879</v>
@@ -20350,7 +20350,7 @@
         <v>9.75</v>
       </c>
       <c r="G689" t="n">
-        <v>9.53443050384521</v>
+        <v>9.5344295501709</v>
       </c>
       <c r="H689" t="n">
         <v>11078</v>
@@ -20379,7 +20379,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G690" t="n">
-        <v>9.47575569152832</v>
+        <v>9.47575664520264</v>
       </c>
       <c r="H690" t="n">
         <v>39319</v>
@@ -20495,7 +20495,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H694" t="n">
         <v>32283</v>
@@ -20524,7 +20524,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H695" t="n">
         <v>15119</v>
@@ -20553,7 +20553,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>9.77890205383301</v>
+        <v>9.77890300750732</v>
       </c>
       <c r="H696" t="n">
         <v>14440</v>
@@ -20611,7 +20611,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H698" t="n">
         <v>21356</v>
@@ -20640,7 +20640,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H699" t="n">
         <v>21197</v>
@@ -20669,7 +20669,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H700" t="n">
         <v>27899</v>
@@ -20756,7 +20756,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H703" t="n">
         <v>10949</v>
@@ -20843,7 +20843,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H706" t="n">
         <v>17733</v>
@@ -20872,7 +20872,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>9.19216728210449</v>
+        <v>9.19216823577881</v>
       </c>
       <c r="H707" t="n">
         <v>60633</v>
@@ -20930,7 +20930,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H709" t="n">
         <v>27319</v>
@@ -20959,7 +20959,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H710" t="n">
         <v>140241</v>
@@ -21017,7 +21017,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560531616211</v>
+        <v>8.15560436248779</v>
       </c>
       <c r="H712" t="n">
         <v>38461</v>
@@ -21046,7 +21046,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>8.75211620330811</v>
+        <v>8.75211715698242</v>
       </c>
       <c r="H713" t="n">
         <v>161407</v>
@@ -21075,7 +21075,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G714" t="n">
-        <v>8.70322322845459</v>
+        <v>8.70322227478027</v>
       </c>
       <c r="H714" t="n">
         <v>94133</v>
@@ -21104,7 +21104,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H715" t="n">
         <v>12213</v>
@@ -21191,7 +21191,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626838684082</v>
+        <v>8.12626934051514</v>
       </c>
       <c r="H718" t="n">
         <v>75942</v>
@@ -21249,7 +21249,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742362976074</v>
+        <v>8.51742458343506</v>
       </c>
       <c r="H720" t="n">
         <v>40610</v>
@@ -21336,7 +21336,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.63477039337158</v>
+        <v>8.6347713470459</v>
       </c>
       <c r="H723" t="n">
         <v>20170</v>
@@ -21423,7 +21423,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>8.88902282714844</v>
+        <v>8.88902187347412</v>
       </c>
       <c r="H726" t="n">
         <v>35047</v>
@@ -21452,7 +21452,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G727" t="n">
-        <v>8.77167510986328</v>
+        <v>8.7716760635376</v>
       </c>
       <c r="H727" t="n">
         <v>143037</v>
@@ -21481,7 +21481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G728" t="n">
-        <v>8.89880084991455</v>
+        <v>8.89880180358887</v>
       </c>
       <c r="H728" t="n">
         <v>73666</v>
@@ -21510,7 +21510,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H729" t="n">
         <v>24316</v>
@@ -21539,7 +21539,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H730" t="n">
         <v>9948</v>
@@ -21742,7 +21742,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G737" t="n">
-        <v>7.40262937545776</v>
+        <v>7.40262889862061</v>
       </c>
       <c r="H737" t="n">
         <v>30955</v>
@@ -21858,7 +21858,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>7.30483961105347</v>
+        <v>7.30484008789062</v>
       </c>
       <c r="H741" t="n">
         <v>13402</v>
@@ -21916,7 +21916,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H743" t="n">
         <v>14937</v>
@@ -21945,7 +21945,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G744" t="n">
-        <v>7.1581563949585</v>
+        <v>7.15815687179565</v>
       </c>
       <c r="H744" t="n">
         <v>18982</v>
@@ -21974,7 +21974,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G745" t="n">
-        <v>6.83545255661011</v>
+        <v>6.83545207977295</v>
       </c>
       <c r="H745" t="n">
         <v>110100</v>
@@ -22003,7 +22003,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385478973389</v>
+        <v>6.46385431289673</v>
       </c>
       <c r="H746" t="n">
         <v>68949</v>
@@ -22032,7 +22032,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>5.67176342010498</v>
+        <v>5.67176389694214</v>
       </c>
       <c r="H747" t="n">
         <v>105173</v>
@@ -22119,7 +22119,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H750" t="n">
         <v>185723</v>
@@ -22148,7 +22148,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.71343088150024</v>
+        <v>4.7134313583374</v>
       </c>
       <c r="H751" t="n">
         <v>210848</v>
@@ -22177,7 +22177,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760669708252</v>
+        <v>4.30760622024536</v>
       </c>
       <c r="H752" t="n">
         <v>95208</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22235,7 +22235,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>4.67431545257568</v>
+        <v>4.67431497573853</v>
       </c>
       <c r="H754" t="n">
         <v>139728</v>
@@ -22264,7 +22264,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>4.44940042495728</v>
+        <v>4.44940090179443</v>
       </c>
       <c r="H755" t="n">
         <v>78287</v>
@@ -22293,7 +22293,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738519668579</v>
+        <v>4.31738567352295</v>
       </c>
       <c r="H756" t="n">
         <v>103537</v>
@@ -22351,7 +22351,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>3.90178203582764</v>
+        <v>3.90178227424622</v>
       </c>
       <c r="H758" t="n">
         <v>114123</v>
@@ -22409,7 +22409,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00935029983521</v>
+        <v>4.00934982299805</v>
       </c>
       <c r="H760" t="n">
         <v>97203</v>
@@ -22438,7 +22438,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156101226807</v>
+        <v>3.91156077384949</v>
       </c>
       <c r="H761" t="n">
         <v>208056</v>
@@ -22467,7 +22467,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.9800136089325</v>
+        <v>3.98001313209534</v>
       </c>
       <c r="H762" t="n">
         <v>31531</v>
@@ -22496,7 +22496,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669658660889</v>
+        <v>4.12669706344604</v>
       </c>
       <c r="H763" t="n">
         <v>41597</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224914550781</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22554,7 +22554,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691808700562</v>
+        <v>4.11691761016846</v>
       </c>
       <c r="H765" t="n">
         <v>28600</v>
@@ -22583,7 +22583,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>4.35161161422729</v>
+        <v>4.35161113739014</v>
       </c>
       <c r="H766" t="n">
         <v>92230</v>
@@ -22612,7 +22612,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630514144897</v>
+        <v>4.58630561828613</v>
       </c>
       <c r="H767" t="n">
         <v>113983</v>
@@ -22641,7 +22641,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G768" t="n">
-        <v>4.83566761016846</v>
+        <v>4.8356671333313</v>
       </c>
       <c r="H768" t="n">
         <v>165631</v>
@@ -22670,7 +22670,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>5.08502960205078</v>
+        <v>5.08502912521362</v>
       </c>
       <c r="H769" t="n">
         <v>224657</v>
@@ -22786,7 +22786,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055614471436</v>
+        <v>4.84055662155151</v>
       </c>
       <c r="H773" t="n">
         <v>56598</v>
@@ -22960,7 +22960,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H779" t="n">
         <v>69616</v>
@@ -23018,7 +23018,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H781" t="n">
         <v>53399</v>
@@ -23047,7 +23047,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485822677612</v>
+        <v>5.53485870361328</v>
       </c>
       <c r="H782" t="n">
         <v>74521</v>
@@ -23163,7 +23163,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928108215332</v>
+        <v>5.33928060531616</v>
       </c>
       <c r="H786" t="n">
         <v>28269</v>
@@ -23192,7 +23192,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H787" t="n">
         <v>18969</v>
@@ -23250,7 +23250,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H789" t="n">
         <v>33919</v>
@@ -23279,7 +23279,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016469955444</v>
+        <v>5.30016565322876</v>
       </c>
       <c r="H790" t="n">
         <v>36651</v>
@@ -23337,7 +23337,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G792" t="n">
-        <v>5.20237636566162</v>
+        <v>5.20237588882446</v>
       </c>
       <c r="H792" t="n">
         <v>22334</v>
@@ -23395,7 +23395,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G794" t="n">
-        <v>5.20237636566162</v>
+        <v>5.20237588882446</v>
       </c>
       <c r="H794" t="n">
         <v>45527</v>
@@ -23453,7 +23453,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>5.22193431854248</v>
+        <v>5.22193384170532</v>
       </c>
       <c r="H796" t="n">
         <v>43106</v>
@@ -23482,7 +23482,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H797" t="n">
         <v>11846</v>
@@ -23569,7 +23569,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104927062988</v>
+        <v>5.26104974746704</v>
       </c>
       <c r="H800" t="n">
         <v>42807</v>
@@ -23627,7 +23627,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G802" t="n">
-        <v>5.20237636566162</v>
+        <v>5.20237588882446</v>
       </c>
       <c r="H802" t="n">
         <v>6956</v>
@@ -23656,7 +23656,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>5.24149179458618</v>
+        <v>5.24149131774902</v>
       </c>
       <c r="H803" t="n">
         <v>20595</v>
@@ -23685,7 +23685,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>5.21215534210205</v>
+        <v>5.21215486526489</v>
       </c>
       <c r="H804" t="n">
         <v>58954</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166269302368</v>
+        <v>4.79166221618652</v>
       </c>
       <c r="H807" t="n">
         <v>76245</v>
@@ -23859,7 +23859,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.97746133804321</v>
+        <v>4.97746181488037</v>
       </c>
       <c r="H810" t="n">
         <v>46277</v>
@@ -23888,7 +23888,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>4.93834638595581</v>
+        <v>4.93834590911865</v>
       </c>
       <c r="H811" t="n">
         <v>36173</v>
@@ -23975,7 +23975,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>4.97746133804321</v>
+        <v>4.97746181488037</v>
       </c>
       <c r="H814" t="n">
         <v>26888</v>
@@ -24120,7 +24120,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G819" t="n">
-        <v>5.65220642089844</v>
+        <v>5.65220594406128</v>
       </c>
       <c r="H819" t="n">
         <v>97422</v>
@@ -24178,7 +24178,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441617965698</v>
+        <v>5.55441665649414</v>
       </c>
       <c r="H821" t="n">
         <v>85848</v>
@@ -24236,7 +24236,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.4370698928833</v>
+        <v>5.43706941604614</v>
       </c>
       <c r="H823" t="n">
         <v>49574</v>
@@ -24323,7 +24323,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H826" t="n">
         <v>18416</v>
@@ -24352,7 +24352,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552272796631</v>
+        <v>5.50552225112915</v>
       </c>
       <c r="H827" t="n">
         <v>27618</v>
@@ -24381,7 +24381,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G828" t="n">
-        <v>5.44684839248657</v>
+        <v>5.44684886932373</v>
       </c>
       <c r="H828" t="n">
         <v>56372</v>
@@ -24410,7 +24410,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>5.63264846801758</v>
+        <v>5.63264799118042</v>
       </c>
       <c r="H829" t="n">
         <v>49059</v>
@@ -24468,7 +24468,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G831" t="n">
-        <v>6.44429683685303</v>
+        <v>6.44429636001587</v>
       </c>
       <c r="H831" t="n">
         <v>252834</v>
@@ -24526,7 +24526,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004535675049</v>
+        <v>6.19004487991333</v>
       </c>
       <c r="H833" t="n">
         <v>244592</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>6.01402473449707</v>
+        <v>6.01402521133423</v>
       </c>
       <c r="H834" t="n">
         <v>41322</v>
@@ -24613,7 +24613,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314111709595</v>
+        <v>6.05314016342163</v>
       </c>
       <c r="H836" t="n">
         <v>52635</v>
@@ -24642,7 +24642,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G837" t="n">
-        <v>6.33672904968262</v>
+        <v>6.33672857284546</v>
       </c>
       <c r="H837" t="n">
         <v>71930</v>
@@ -24700,7 +24700,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H839" t="n">
         <v>63435</v>
@@ -25019,7 +25019,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>6.08247661590576</v>
+        <v>6.08247709274292</v>
       </c>
       <c r="H850" t="n">
         <v>27868</v>
@@ -25048,7 +25048,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G851" t="n">
-        <v>6.1411509513855</v>
+        <v>6.14115047454834</v>
       </c>
       <c r="H851" t="n">
         <v>14069</v>
@@ -25106,7 +25106,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>6.0042462348938</v>
+        <v>6.00424575805664</v>
       </c>
       <c r="H853" t="n">
         <v>11658</v>
@@ -25164,7 +25164,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G855" t="n">
-        <v>5.92601537704468</v>
+        <v>5.92601490020752</v>
       </c>
       <c r="H855" t="n">
         <v>66134</v>
@@ -25193,7 +25193,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.78911066055298</v>
+        <v>5.78911018371582</v>
       </c>
       <c r="H856" t="n">
         <v>10669</v>
@@ -25222,7 +25222,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>5.76955270767212</v>
+        <v>5.76955223083496</v>
       </c>
       <c r="H857" t="n">
         <v>16583</v>
@@ -25251,7 +25251,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977325439453</v>
+        <v>5.75977373123169</v>
       </c>
       <c r="H858" t="n">
         <v>12990</v>
@@ -25338,7 +25338,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H861" t="n">
         <v>15530</v>
@@ -25425,7 +25425,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>5.82822561264038</v>
+        <v>5.82822608947754</v>
       </c>
       <c r="H864" t="n">
         <v>48237</v>
@@ -25454,7 +25454,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021530151367</v>
+        <v>5.74021577835083</v>
       </c>
       <c r="H865" t="n">
         <v>27718</v>
@@ -25512,7 +25512,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>5.67176342010498</v>
+        <v>5.67176389694214</v>
       </c>
       <c r="H867" t="n">
         <v>13457</v>
@@ -25599,7 +25599,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H870" t="n">
         <v>22149</v>
@@ -25715,7 +25715,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>5.95535135269165</v>
+        <v>5.95535182952881</v>
       </c>
       <c r="H874" t="n">
         <v>19266</v>
@@ -25744,7 +25744,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756254196167</v>
+        <v>5.85756206512451</v>
       </c>
       <c r="H875" t="n">
         <v>10415</v>
@@ -26005,7 +26005,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623640060425</v>
+        <v>5.91623592376709</v>
       </c>
       <c r="H884" t="n">
         <v>30149</v>
@@ -26063,7 +26063,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>6.53230667114258</v>
+        <v>6.53230619430542</v>
       </c>
       <c r="H886" t="n">
         <v>143444</v>
@@ -26121,7 +26121,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>6.44429683685303</v>
+        <v>6.44429636001587</v>
       </c>
       <c r="H888" t="n">
         <v>92730</v>
@@ -26208,7 +26208,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987493515015</v>
+        <v>6.63987445831299</v>
       </c>
       <c r="H891" t="n">
         <v>52119</v>
@@ -26237,7 +26237,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H892" t="n">
         <v>34785</v>
@@ -26295,7 +26295,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655862808228</v>
+        <v>6.78655815124512</v>
       </c>
       <c r="H894" t="n">
         <v>16921</v>
@@ -26353,7 +26353,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H896" t="n">
         <v>155510</v>
@@ -26411,7 +26411,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96002721786499</v>
+        <v>7.96002626419067</v>
       </c>
       <c r="H898" t="n">
         <v>68196</v>
@@ -26440,7 +26440,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489068984985</v>
+        <v>7.74489116668701</v>
       </c>
       <c r="H899" t="n">
         <v>112735</v>
@@ -26614,7 +26614,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G905" t="n">
-        <v>7.73511123657227</v>
+        <v>7.73511171340942</v>
       </c>
       <c r="H905" t="n">
         <v>13300</v>
@@ -26643,7 +26643,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>7.58842802047729</v>
+        <v>7.58842849731445</v>
       </c>
       <c r="H906" t="n">
         <v>22167</v>
@@ -26788,7 +26788,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147317886353</v>
+        <v>7.01147270202637</v>
       </c>
       <c r="H911" t="n">
         <v>49184</v>
@@ -26817,7 +26817,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G912" t="n">
-        <v>7.26572465896606</v>
+        <v>7.26572418212891</v>
       </c>
       <c r="H912" t="n">
         <v>36837</v>
@@ -26875,7 +26875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H914" t="n">
         <v>40423</v>
@@ -26933,7 +26933,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G916" t="n">
-        <v>6.85501098632812</v>
+        <v>6.85501050949097</v>
       </c>
       <c r="H916" t="n">
         <v>242774</v>
@@ -27020,7 +27020,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G919" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H919" t="n">
         <v>21477</v>
@@ -27049,7 +27049,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G920" t="n">
-        <v>6.63009595870972</v>
+        <v>6.63009643554688</v>
       </c>
       <c r="H920" t="n">
         <v>51184</v>
@@ -27078,7 +27078,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G921" t="n">
-        <v>6.71810626983643</v>
+        <v>6.71810579299927</v>
       </c>
       <c r="H921" t="n">
         <v>61586</v>
@@ -27107,7 +27107,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412593841553</v>
+        <v>6.89412641525269</v>
       </c>
       <c r="H922" t="n">
         <v>17841</v>
@@ -27165,7 +27165,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904144287109</v>
+        <v>7.11904096603394</v>
       </c>
       <c r="H924" t="n">
         <v>41919</v>
@@ -27194,7 +27194,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793489456177</v>
+        <v>7.16793537139893</v>
       </c>
       <c r="H925" t="n">
         <v>17282</v>
@@ -27252,7 +27252,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>6.99191570281982</v>
+        <v>6.99191522598267</v>
       </c>
       <c r="H927" t="n">
         <v>21117</v>
@@ -27281,7 +27281,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H928" t="n">
         <v>40663</v>
@@ -27339,7 +27339,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>7.42218732833862</v>
+        <v>7.42218685150146</v>
       </c>
       <c r="H930" t="n">
         <v>419711</v>
@@ -27368,7 +27368,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G931" t="n">
-        <v>7.24616670608521</v>
+        <v>7.24616622924805</v>
       </c>
       <c r="H931" t="n">
         <v>52841</v>
@@ -27484,7 +27484,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H935" t="n">
         <v>42761</v>
@@ -27513,7 +27513,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798597335815</v>
+        <v>7.60798645019531</v>
       </c>
       <c r="H936" t="n">
         <v>10858</v>
@@ -27542,7 +27542,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>7.53953409194946</v>
+        <v>7.5395336151123</v>
       </c>
       <c r="H937" t="n">
         <v>15176</v>
@@ -27571,7 +27571,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G938" t="n">
-        <v>7.96002721786499</v>
+        <v>7.96002626419067</v>
       </c>
       <c r="H938" t="n">
         <v>165920</v>
@@ -27600,7 +27600,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312202453613</v>
+        <v>7.82312154769897</v>
       </c>
       <c r="H939" t="n">
         <v>72321</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>8.03825759887695</v>
+        <v>8.03825855255127</v>
       </c>
       <c r="H940" t="n">
         <v>95905</v>
@@ -27687,7 +27687,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H942" t="n">
         <v>93859</v>
@@ -27745,7 +27745,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G944" t="n">
-        <v>8.43919372558594</v>
+        <v>8.43919277191162</v>
       </c>
       <c r="H944" t="n">
         <v>119944</v>
@@ -27803,7 +27803,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G946" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H946" t="n">
         <v>263636</v>
@@ -27832,7 +27832,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G947" t="n">
-        <v>9.43664073944092</v>
+        <v>9.4366397857666</v>
       </c>
       <c r="H947" t="n">
         <v>81693</v>
@@ -27861,7 +27861,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H948" t="n">
         <v>77374</v>
@@ -27890,7 +27890,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G949" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H949" t="n">
         <v>212562</v>
@@ -27948,7 +27948,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G951" t="n">
-        <v>9.31929302215576</v>
+        <v>9.31929397583008</v>
       </c>
       <c r="H951" t="n">
         <v>256448</v>
@@ -28035,7 +28035,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G954" t="n">
-        <v>8.810791015625</v>
+        <v>8.81079196929932</v>
       </c>
       <c r="H954" t="n">
         <v>75369</v>
@@ -28093,7 +28093,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897270202637</v>
+        <v>8.44897174835205</v>
       </c>
       <c r="H956" t="n">
         <v>40968</v>
@@ -28267,7 +28267,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339317321777</v>
+        <v>8.25339412689209</v>
       </c>
       <c r="H962" t="n">
         <v>76522</v>
@@ -28354,7 +28354,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G965" t="n">
-        <v>8.70322322845459</v>
+        <v>8.70322227478027</v>
       </c>
       <c r="H965" t="n">
         <v>55469</v>
@@ -28412,7 +28412,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20449829101562</v>
+        <v>8.20450019836426</v>
       </c>
       <c r="H967" t="n">
         <v>42116</v>
@@ -28441,7 +28441,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H968" t="n">
         <v>21079</v>
@@ -28528,7 +28528,7 @@
         <v>8.25</v>
       </c>
       <c r="G971" t="n">
-        <v>8.06759452819824</v>
+        <v>8.06759548187256</v>
       </c>
       <c r="H971" t="n">
         <v>26338</v>
@@ -28557,7 +28557,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G972" t="n">
-        <v>8.17516231536865</v>
+        <v>8.17516136169434</v>
       </c>
       <c r="H972" t="n">
         <v>14608</v>
@@ -28586,7 +28586,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482147216797</v>
+        <v>9.07482051849365</v>
       </c>
       <c r="H973" t="n">
         <v>227616</v>
@@ -28615,7 +28615,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>9.01614856719971</v>
+        <v>9.01614761352539</v>
       </c>
       <c r="H974" t="n">
         <v>250262</v>
@@ -28673,7 +28673,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>9.24106311798096</v>
+        <v>9.24106216430664</v>
       </c>
       <c r="H976" t="n">
         <v>268935</v>
@@ -28702,7 +28702,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>9.74956607818604</v>
+        <v>9.74956512451172</v>
       </c>
       <c r="H977" t="n">
         <v>117145</v>
@@ -28789,7 +28789,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H980" t="n">
         <v>214809</v>
@@ -28847,7 +28847,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804306030273</v>
+        <v>11.4804315567017</v>
       </c>
       <c r="H982" t="n">
         <v>419644</v>
@@ -28934,7 +28934,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9107027053833</v>
+        <v>11.9107036590576</v>
       </c>
       <c r="H985" t="n">
         <v>111245</v>
@@ -29021,7 +29021,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H988" t="n">
         <v>321229</v>
@@ -29108,7 +29108,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926733016968</v>
+        <v>13.5926742553711</v>
       </c>
       <c r="H991" t="n">
         <v>195792</v>
@@ -29137,7 +29137,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882518768311</v>
+        <v>13.7882528305054</v>
       </c>
       <c r="H992" t="n">
         <v>403792</v>
@@ -29224,7 +29224,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8639316558838</v>
+        <v>14.8639307022095</v>
       </c>
       <c r="H995" t="n">
         <v>248550</v>
@@ -29253,7 +29253,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G996" t="n">
-        <v>15.0790681838989</v>
+        <v>15.0790672302246</v>
       </c>
       <c r="H996" t="n">
         <v>358240</v>
@@ -29282,7 +29282,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>14.5705652236938</v>
+        <v>14.5705642700195</v>
       </c>
       <c r="H997" t="n">
         <v>150561</v>
@@ -29369,7 +29369,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7100219726562</v>
+        <v>13.7100210189819</v>
       </c>
       <c r="H1000" t="n">
         <v>186196</v>
@@ -29630,7 +29630,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1009" t="n">
         <v>78089</v>
@@ -29804,7 +29804,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1015" t="n">
-        <v>12.2040691375732</v>
+        <v>12.2040700912476</v>
       </c>
       <c r="H1015" t="n">
         <v>54788</v>
@@ -29862,7 +29862,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5561113357544</v>
+        <v>12.5561103820801</v>
       </c>
       <c r="H1017" t="n">
         <v>121329</v>
@@ -29891,7 +29891,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1018" t="n">
         <v>91050</v>
@@ -29978,7 +29978,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1021" t="n">
         <v>151231</v>
@@ -30065,7 +30065,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406330108643</v>
+        <v>13.2406339645386</v>
       </c>
       <c r="H1024" t="n">
         <v>111837</v>
@@ -30152,7 +30152,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4583206176758</v>
+        <v>12.4583215713501</v>
       </c>
       <c r="H1027" t="n">
         <v>145125</v>
@@ -30210,7 +30210,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>12.2040691375732</v>
+        <v>12.2040700912476</v>
       </c>
       <c r="H1029" t="n">
         <v>174418</v>
@@ -30239,7 +30239,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1030" t="n">
         <v>99601</v>
@@ -30268,7 +30268,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.282301902771</v>
+        <v>12.2823009490967</v>
       </c>
       <c r="H1031" t="n">
         <v>57835</v>
@@ -30326,7 +30326,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.7151250839233</v>
+        <v>11.715124130249</v>
       </c>
       <c r="H1033" t="n">
         <v>119232</v>
@@ -30413,7 +30413,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.3996496200562</v>
+        <v>12.3996486663818</v>
       </c>
       <c r="H1036" t="n">
         <v>90647</v>
@@ -30471,7 +30471,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1038" t="n">
-        <v>12.2040691375732</v>
+        <v>12.2040700912476</v>
       </c>
       <c r="H1038" t="n">
         <v>111924</v>
@@ -30500,7 +30500,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.6734580993652</v>
+        <v>12.6734571456909</v>
       </c>
       <c r="H1039" t="n">
         <v>102261</v>
@@ -30616,7 +30616,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1043" t="n">
         <v>36180</v>
@@ -30703,7 +30703,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.380090713501</v>
+        <v>12.3800897598267</v>
       </c>
       <c r="H1046" t="n">
         <v>29868</v>
@@ -30732,7 +30732,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409748077393</v>
+        <v>12.3409757614136</v>
       </c>
       <c r="H1047" t="n">
         <v>46643</v>
@@ -30819,7 +30819,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450553894043</v>
+        <v>13.0450563430786</v>
       </c>
       <c r="H1050" t="n">
         <v>110815</v>
@@ -30848,7 +30848,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.2797498703003</v>
+        <v>13.279748916626</v>
       </c>
       <c r="H1051" t="n">
         <v>108427</v>
@@ -30906,7 +30906,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567930221558</v>
+        <v>10.7567920684814</v>
       </c>
       <c r="H1053" t="n">
         <v>195883</v>
@@ -30935,7 +30935,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H1054" t="n">
         <v>167159</v>
@@ -30993,7 +30993,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H1056" t="n">
         <v>93893</v>
@@ -31080,7 +31080,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220985412598</v>
+        <v>10.5220994949341</v>
       </c>
       <c r="H1059" t="n">
         <v>104597</v>
@@ -31167,7 +31167,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.5025405883789</v>
+        <v>10.5025415420532</v>
       </c>
       <c r="H1062" t="n">
         <v>172678</v>
@@ -31341,7 +31341,7 @@
         <v>8.5</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.31206798553467</v>
+        <v>8.31206703186035</v>
       </c>
       <c r="H1068" t="n">
         <v>167682</v>
@@ -31370,7 +31370,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.64454936981201</v>
+        <v>8.64455032348633</v>
       </c>
       <c r="H1069" t="n">
         <v>180623</v>
@@ -31399,7 +31399,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.60543346405029</v>
+        <v>8.60543441772461</v>
       </c>
       <c r="H1070" t="n">
         <v>27481</v>
@@ -31428,7 +31428,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1071" t="n">
-        <v>8.70322322845459</v>
+        <v>8.70322227478027</v>
       </c>
       <c r="H1071" t="n">
         <v>29010</v>
@@ -31486,7 +31486,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.810791015625</v>
+        <v>8.81079196929932</v>
       </c>
       <c r="H1073" t="n">
         <v>41885</v>
@@ -31515,7 +31515,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.03570556640625</v>
+        <v>9.03570652008057</v>
       </c>
       <c r="H1074" t="n">
         <v>47397</v>
@@ -31544,7 +31544,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.17261028289795</v>
+        <v>9.17261123657227</v>
       </c>
       <c r="H1075" t="n">
         <v>127062</v>
@@ -31602,7 +31602,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.46597671508789</v>
+        <v>9.46597766876221</v>
       </c>
       <c r="H1077" t="n">
         <v>64803</v>
@@ -31660,7 +31660,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.3265209197998</v>
+        <v>10.3265218734741</v>
       </c>
       <c r="H1079" t="n">
         <v>87842</v>
@@ -31689,7 +31689,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.4047527313232</v>
+        <v>10.4047517776489</v>
       </c>
       <c r="H1080" t="n">
         <v>36974</v>
@@ -31776,7 +31776,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003293991089</v>
+        <v>10.6003313064575</v>
       </c>
       <c r="H1083" t="n">
         <v>44357</v>
@@ -31805,7 +31805,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.443868637085</v>
+        <v>10.4438676834106</v>
       </c>
       <c r="H1084" t="n">
         <v>61024</v>
@@ -31979,7 +31979,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>13.1037292480469</v>
+        <v>13.1037282943726</v>
       </c>
       <c r="H1090" t="n">
         <v>153541</v>
@@ -32037,7 +32037,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.1428451538086</v>
+        <v>13.1428442001343</v>
       </c>
       <c r="H1092" t="n">
         <v>90633</v>
@@ -32153,7 +32153,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882518768311</v>
+        <v>13.7882528305054</v>
       </c>
       <c r="H1096" t="n">
         <v>93691</v>
@@ -32240,7 +32240,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>13.8273677825928</v>
+        <v>13.8273687362671</v>
       </c>
       <c r="H1099" t="n">
         <v>108983</v>
@@ -32269,7 +32269,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1100" t="n">
-        <v>14.1402931213379</v>
+        <v>14.1402940750122</v>
       </c>
       <c r="H1100" t="n">
         <v>81068</v>
@@ -32298,7 +32298,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771987915039</v>
+        <v>14.2771978378296</v>
       </c>
       <c r="H1101" t="n">
         <v>57479</v>
@@ -32327,7 +32327,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>14.4532175064087</v>
+        <v>14.4532165527344</v>
       </c>
       <c r="H1102" t="n">
         <v>33492</v>
@@ -32385,7 +32385,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749856948853</v>
+        <v>14.3749866485596</v>
       </c>
       <c r="H1104" t="n">
         <v>36166</v>
@@ -32530,7 +32530,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.1181840896606</v>
+        <v>15.1181831359863</v>
       </c>
       <c r="H1109" t="n">
         <v>121418</v>
@@ -32617,7 +32617,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1112" t="n">
-        <v>17.6802558898926</v>
+        <v>17.6802539825439</v>
       </c>
       <c r="H1112" t="n">
         <v>297169</v>
@@ -32675,7 +32675,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666507720947</v>
+        <v>19.1666488647461</v>
       </c>
       <c r="H1114" t="n">
         <v>462313</v>
@@ -32791,7 +32791,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1118" t="n">
         <v>186738</v>
@@ -32820,7 +32820,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1119" t="n">
         <v>218593</v>
@@ -32878,7 +32878,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981105804443</v>
+        <v>22.1981067657471</v>
       </c>
       <c r="H1121" t="n">
         <v>87185</v>
@@ -32907,7 +32907,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.758056640625</v>
+        <v>21.7580585479736</v>
       </c>
       <c r="H1122" t="n">
         <v>177161</v>
@@ -32965,7 +32965,7 @@
         <v>21.5</v>
       </c>
       <c r="G1124" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1124" t="n">
         <v>72589</v>
@@ -33023,7 +33023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1126" t="n">
         <v>169849</v>
@@ -33052,7 +33052,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1127" t="n">
         <v>153071</v>
@@ -33168,7 +33168,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558483123779</v>
+        <v>21.8558464050293</v>
       </c>
       <c r="H1131" t="n">
         <v>109080</v>
@@ -33197,7 +33197,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.6602668762207</v>
+        <v>21.660270690918</v>
       </c>
       <c r="H1132" t="n">
         <v>103507</v>
@@ -33255,7 +33255,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.6602668762207</v>
+        <v>21.660270690918</v>
       </c>
       <c r="H1134" t="n">
         <v>98501</v>
@@ -33400,7 +33400,7 @@
         <v>21.5</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1139" t="n">
         <v>34560</v>
@@ -33458,7 +33458,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>20.9757480621338</v>
+        <v>20.9757461547852</v>
       </c>
       <c r="H1141" t="n">
         <v>56787</v>
@@ -33516,7 +33516,7 @@
         <v>21.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1143" t="n">
         <v>34032</v>
@@ -33545,7 +33545,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1144" t="n">
         <v>22284</v>
@@ -33574,7 +33574,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.122428894043</v>
+        <v>21.1224308013916</v>
       </c>
       <c r="H1145" t="n">
         <v>26612</v>
@@ -33603,7 +33603,7 @@
         <v>21.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.2691135406494</v>
+        <v>21.2691116333008</v>
       </c>
       <c r="H1146" t="n">
         <v>32961</v>
@@ -33632,7 +33632,7 @@
         <v>21.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1147" t="n">
         <v>58527</v>
@@ -33661,7 +33661,7 @@
         <v>21.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>20.7801666259766</v>
+        <v>20.7801685333252</v>
       </c>
       <c r="H1148" t="n">
         <v>26335</v>
@@ -33748,7 +33748,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1151" t="n">
         <v>65290</v>
@@ -33835,7 +33835,7 @@
         <v>23.75</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.2248935699463</v>
+        <v>23.2248954772949</v>
       </c>
       <c r="H1154" t="n">
         <v>149423</v>
@@ -33893,7 +33893,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.0560989379883</v>
+        <v>24.0561008453369</v>
       </c>
       <c r="H1156" t="n">
         <v>205397</v>
@@ -33922,7 +33922,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>24.1538887023926</v>
+        <v>24.1538906097412</v>
       </c>
       <c r="H1157" t="n">
         <v>72151</v>
@@ -33951,7 +33951,7 @@
         <v>24.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.9583129882812</v>
+        <v>23.9583110809326</v>
       </c>
       <c r="H1158" t="n">
         <v>67635</v>
@@ -34009,7 +34009,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.3226833343506</v>
+        <v>23.322681427002</v>
       </c>
       <c r="H1160" t="n">
         <v>31857</v>
@@ -34067,7 +34067,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359504699707</v>
+        <v>22.7359466552734</v>
       </c>
       <c r="H1162" t="n">
         <v>32829</v>
@@ -34096,7 +34096,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1163" t="n">
         <v>63588</v>
@@ -34125,7 +34125,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1164" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1164" t="n">
         <v>33009</v>
@@ -34154,7 +34154,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>22.6381587982178</v>
+        <v>22.6381568908691</v>
       </c>
       <c r="H1165" t="n">
         <v>26738</v>
@@ -34183,7 +34183,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1166" t="n">
         <v>72421</v>
@@ -34212,7 +34212,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1167" t="n">
         <v>34211</v>
@@ -34299,7 +34299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.3447914123535</v>
+        <v>22.3447933197021</v>
       </c>
       <c r="H1170" t="n">
         <v>119843</v>
@@ -34357,7 +34357,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1172" t="n">
         <v>37810</v>
@@ -34415,7 +34415,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.1492156982422</v>
+        <v>22.1492137908936</v>
       </c>
       <c r="H1174" t="n">
         <v>29225</v>
@@ -34444,7 +34444,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470016479492</v>
+        <v>22.2470035552979</v>
       </c>
       <c r="H1175" t="n">
         <v>25765</v>
@@ -34502,7 +34502,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.5403690338135</v>
+        <v>22.5403671264648</v>
       </c>
       <c r="H1177" t="n">
         <v>15746</v>
@@ -34705,7 +34705,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157962799072</v>
+        <v>21.4157943725586</v>
       </c>
       <c r="H1184" t="n">
         <v>21327</v>
@@ -34763,7 +34763,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1186" t="n">
         <v>55489</v>
@@ -34792,7 +34792,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1187" t="n">
         <v>68839</v>
@@ -34850,7 +34850,7 @@
         <v>21.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1189" t="n">
         <v>47664</v>
@@ -34937,7 +34937,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113758087158</v>
+        <v>21.6113739013672</v>
       </c>
       <c r="H1192" t="n">
         <v>25913</v>
@@ -34995,7 +34995,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202186584473</v>
+        <v>21.2202205657959</v>
       </c>
       <c r="H1194" t="n">
         <v>28298</v>
@@ -35082,7 +35082,7 @@
         <v>21.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1197" t="n">
         <v>53455</v>
@@ -35169,7 +35169,7 @@
         <v>21.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1200" t="n">
         <v>137704</v>
@@ -35198,7 +35198,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>22.6381587982178</v>
+        <v>22.6381568908691</v>
       </c>
       <c r="H1201" t="n">
         <v>116966</v>
@@ -35285,7 +35285,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135860443115</v>
+        <v>21.5135841369629</v>
       </c>
       <c r="H1204" t="n">
         <v>133530</v>
@@ -35401,7 +35401,7 @@
         <v>21.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.0246391296387</v>
+        <v>21.0246410369873</v>
       </c>
       <c r="H1208" t="n">
         <v>60298</v>
@@ -35430,7 +35430,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>20.3401184082031</v>
+        <v>20.3401165008545</v>
       </c>
       <c r="H1209" t="n">
         <v>38491</v>
@@ -35488,7 +35488,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3890132904053</v>
+        <v>20.3890113830566</v>
       </c>
       <c r="H1211" t="n">
         <v>36573</v>
@@ -35575,7 +35575,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467510223389</v>
+        <v>20.0467491149902</v>
       </c>
       <c r="H1214" t="n">
         <v>61113</v>
@@ -35604,7 +35604,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511695861816</v>
+        <v>19.8511714935303</v>
       </c>
       <c r="H1215" t="n">
         <v>97038</v>
@@ -35633,7 +35633,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1216" t="n">
-        <v>19.4404563903809</v>
+        <v>19.4404582977295</v>
       </c>
       <c r="H1216" t="n">
         <v>49228</v>
@@ -35691,7 +35691,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.9978561401367</v>
+        <v>19.9978580474854</v>
       </c>
       <c r="H1218" t="n">
         <v>80159</v>
@@ -35720,7 +35720,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.7533855438232</v>
+        <v>19.7533836364746</v>
       </c>
       <c r="H1219" t="n">
         <v>54410</v>
@@ -35749,7 +35749,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470909118652</v>
+        <v>19.1470890045166</v>
       </c>
       <c r="H1220" t="n">
         <v>78205</v>
@@ -35981,7 +35981,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112106323242</v>
+        <v>16.3112087249756</v>
       </c>
       <c r="H1228" t="n">
         <v>66395</v>
@@ -36010,7 +36010,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.3698806762695</v>
+        <v>16.3698825836182</v>
       </c>
       <c r="H1229" t="n">
         <v>80556</v>
@@ -36126,7 +36126,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.5824661254883</v>
+        <v>17.5824642181396</v>
       </c>
       <c r="H1233" t="n">
         <v>88571</v>
@@ -36155,7 +36155,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348472595215</v>
+        <v>17.0348491668701</v>
       </c>
       <c r="H1234" t="n">
         <v>86836</v>
@@ -36213,7 +36213,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1236" t="n">
         <v>105949</v>
@@ -36271,7 +36271,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304267883301</v>
+        <v>17.2304248809814</v>
       </c>
       <c r="H1238" t="n">
         <v>124533</v>
@@ -36300,7 +36300,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>17.2108669281006</v>
+        <v>17.2108688354492</v>
       </c>
       <c r="H1239" t="n">
         <v>157511</v>
@@ -36445,7 +36445,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>17.5042324066162</v>
+        <v>17.5042343139648</v>
       </c>
       <c r="H1244" t="n">
         <v>65827</v>
@@ -36474,7 +36474,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1245" t="n">
-        <v>17.4846782684326</v>
+        <v>17.484676361084</v>
       </c>
       <c r="H1245" t="n">
         <v>68340</v>
@@ -36503,7 +36503,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979454040527</v>
+        <v>16.8979434967041</v>
       </c>
       <c r="H1246" t="n">
         <v>89023</v>
@@ -36532,7 +36532,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676723480225</v>
+        <v>16.4676704406738</v>
       </c>
       <c r="H1247" t="n">
         <v>82416</v>
@@ -36561,7 +36561,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.5459041595459</v>
+        <v>16.5459022521973</v>
       </c>
       <c r="H1248" t="n">
         <v>44400</v>
@@ -36938,7 +36938,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>19.594820022583</v>
+        <v>19.5948181152344</v>
       </c>
       <c r="H1261" t="n">
         <v>421870</v>
@@ -36996,7 +36996,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6342830657959</v>
+        <v>19.6342849731445</v>
       </c>
       <c r="H1263" t="n">
         <v>110426</v>
@@ -37199,7 +37199,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1270" t="n">
         <v>151182</v>
@@ -37228,7 +37228,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>21.8542404174805</v>
+        <v>21.8542423248291</v>
       </c>
       <c r="H1271" t="n">
         <v>144900</v>
@@ -37257,7 +37257,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.8542404174805</v>
+        <v>21.8542423248291</v>
       </c>
       <c r="H1272" t="n">
         <v>100072</v>
@@ -37431,7 +37431,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1278" t="n">
         <v>268613</v>
@@ -37605,7 +37605,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.5750865936279</v>
+        <v>19.5750846862793</v>
       </c>
       <c r="H1284" t="n">
         <v>112686</v>
@@ -37779,7 +37779,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>18.5687065124512</v>
+        <v>18.5687046051025</v>
       </c>
       <c r="H1290" t="n">
         <v>80819</v>
@@ -37866,7 +37866,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.3777542114258</v>
+        <v>19.3777561187744</v>
       </c>
       <c r="H1293" t="n">
         <v>96973</v>
@@ -37895,7 +37895,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1294" t="n">
-        <v>19.2988224029541</v>
+        <v>19.2988243103027</v>
       </c>
       <c r="H1294" t="n">
         <v>80244</v>
@@ -37924,7 +37924,7 @@
         <v>19.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>19.2396259307861</v>
+        <v>19.2396240234375</v>
       </c>
       <c r="H1295" t="n">
         <v>270887</v>
@@ -37953,7 +37953,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.7132148742676</v>
+        <v>19.7132167816162</v>
       </c>
       <c r="H1296" t="n">
         <v>176673</v>
@@ -37982,7 +37982,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1297" t="n">
         <v>155909</v>
@@ -38040,7 +38040,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1299" t="n">
         <v>88312</v>
@@ -38069,7 +38069,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.5089149475098</v>
+        <v>21.5089130401611</v>
       </c>
       <c r="H1300" t="n">
         <v>61890</v>
@@ -38098,7 +38098,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3115844726562</v>
+        <v>21.3115863800049</v>
       </c>
       <c r="H1301" t="n">
         <v>220236</v>
@@ -38156,7 +38156,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>21.1635894775391</v>
+        <v>21.1635875701904</v>
       </c>
       <c r="H1303" t="n">
         <v>114500</v>
@@ -38214,7 +38214,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.8182621002197</v>
+        <v>20.8182601928711</v>
       </c>
       <c r="H1305" t="n">
         <v>89332</v>
@@ -38272,7 +38272,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1769409179688</v>
+        <v>20.1769428253174</v>
       </c>
       <c r="H1307" t="n">
         <v>216127</v>
@@ -38330,7 +38330,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.6737518310547</v>
+        <v>19.6737499237061</v>
       </c>
       <c r="H1309" t="n">
         <v>87050</v>
@@ -38359,7 +38359,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.2988224029541</v>
+        <v>19.2988243103027</v>
       </c>
       <c r="H1310" t="n">
         <v>41832</v>
@@ -38388,7 +38388,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.6145496368408</v>
+        <v>19.6145515441895</v>
       </c>
       <c r="H1311" t="n">
         <v>34200</v>
@@ -38591,7 +38591,7 @@
         <v>23.75</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.4328765869141</v>
+        <v>23.4328784942627</v>
       </c>
       <c r="H1318" t="n">
         <v>828551</v>
@@ -38649,7 +38649,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>22.2982330322266</v>
+        <v>22.2982311248779</v>
       </c>
       <c r="H1320" t="n">
         <v>98729</v>
@@ -38678,7 +38678,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>21.2622528076172</v>
+        <v>21.2622509002686</v>
       </c>
       <c r="H1321" t="n">
         <v>138690</v>
@@ -38939,7 +38939,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>22.8902206420898</v>
+        <v>22.8902225494385</v>
       </c>
       <c r="H1330" t="n">
         <v>103493</v>
@@ -39026,7 +39026,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1333" t="n">
         <v>102759</v>
@@ -39229,7 +39229,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1340" t="n">
-        <v>26.1856250762939</v>
+        <v>26.1856231689453</v>
       </c>
       <c r="H1340" t="n">
         <v>75983</v>
@@ -39490,7 +39490,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1349" t="n">
-        <v>24.05446434021</v>
+        <v>24.0544624328613</v>
       </c>
       <c r="H1349" t="n">
         <v>83400</v>
@@ -39548,7 +39548,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.4230098724365</v>
+        <v>23.4230117797852</v>
       </c>
       <c r="H1351" t="n">
         <v>42477</v>
@@ -39635,7 +39635,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G1354" t="n">
-        <v>23.1467475891113</v>
+        <v>23.14674949646</v>
       </c>
       <c r="H1354" t="n">
         <v>32490</v>
@@ -39664,7 +39664,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.7126235961914</v>
+        <v>22.71262550354</v>
       </c>
       <c r="H1355" t="n">
         <v>83180</v>
@@ -39693,7 +39693,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.0086193084717</v>
+        <v>23.008617401123</v>
       </c>
       <c r="H1356" t="n">
         <v>67559</v>
@@ -39809,7 +39809,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1360" t="n">
         <v>218042</v>
@@ -39838,7 +39838,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1361" t="n">
-        <v>23.5216751098633</v>
+        <v>23.5216770172119</v>
       </c>
       <c r="H1361" t="n">
         <v>73675</v>
@@ -39954,7 +39954,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1365" t="n">
-        <v>24.6464519500732</v>
+        <v>24.6464538574219</v>
       </c>
       <c r="H1365" t="n">
         <v>92733</v>
@@ -40041,7 +40041,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1368" t="n">
         <v>59967</v>
@@ -40186,7 +40186,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1373" t="n">
-        <v>24.9029808044434</v>
+        <v>24.902982711792</v>
       </c>
       <c r="H1373" t="n">
         <v>125191</v>
@@ -40215,7 +40215,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>24.7648525238037</v>
+        <v>24.7648506164551</v>
       </c>
       <c r="H1374" t="n">
         <v>78394</v>
@@ -40244,7 +40244,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1375" t="n">
-        <v>24.4096584320068</v>
+        <v>24.4096565246582</v>
       </c>
       <c r="H1375" t="n">
         <v>68323</v>
@@ -40273,7 +40273,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1376" t="n">
-        <v>24.4293918609619</v>
+        <v>24.4293899536133</v>
       </c>
       <c r="H1376" t="n">
         <v>54879</v>
@@ -40360,7 +40360,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1379" t="n">
-        <v>24.5675201416016</v>
+        <v>24.5675220489502</v>
       </c>
       <c r="H1379" t="n">
         <v>48881</v>
@@ -40389,7 +40389,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.5872554779053</v>
+        <v>24.5872535705566</v>
       </c>
       <c r="H1380" t="n">
         <v>59300</v>
@@ -40476,7 +40476,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.2250881195068</v>
+        <v>26.2250900268555</v>
       </c>
       <c r="H1383" t="n">
         <v>131925</v>
@@ -40505,7 +40505,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1384" t="n">
-        <v>28.4351787567139</v>
+        <v>28.4351806640625</v>
       </c>
       <c r="H1384" t="n">
         <v>187997</v>
@@ -40708,7 +40708,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1391" t="n">
-        <v>24.5872554779053</v>
+        <v>24.5872535705566</v>
       </c>
       <c r="H1391" t="n">
         <v>74513</v>
@@ -40766,7 +40766,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1393" t="n">
-        <v>24.6267185211182</v>
+        <v>24.6267204284668</v>
       </c>
       <c r="H1393" t="n">
         <v>106208</v>
@@ -40795,7 +40795,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>24.6069889068604</v>
+        <v>24.6069869995117</v>
       </c>
       <c r="H1394" t="n">
         <v>64862</v>
@@ -40824,7 +40824,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>24.7253837585449</v>
+        <v>24.7253856658936</v>
       </c>
       <c r="H1395" t="n">
         <v>43250</v>
@@ -40882,7 +40882,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>24.4688549041748</v>
+        <v>24.4688568115234</v>
       </c>
       <c r="H1397" t="n">
         <v>69714</v>
@@ -40911,7 +40911,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>24.4293918609619</v>
+        <v>24.4293899536133</v>
       </c>
       <c r="H1398" t="n">
         <v>26167</v>
@@ -40969,7 +40969,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>24.1531295776367</v>
+        <v>24.1531276702881</v>
       </c>
       <c r="H1400" t="n">
         <v>39041</v>
@@ -41143,7 +41143,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>24.4688549041748</v>
+        <v>24.4688568115234</v>
       </c>
       <c r="H1406" t="n">
         <v>48196</v>
@@ -41201,7 +41201,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1408" t="n">
-        <v>24.05446434021</v>
+        <v>24.0544624328613</v>
       </c>
       <c r="H1408" t="n">
         <v>26194</v>
@@ -41230,7 +41230,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1409" t="n">
         <v>183680</v>
@@ -41288,7 +41288,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3899230957031</v>
+        <v>24.3899250030518</v>
       </c>
       <c r="H1411" t="n">
         <v>56923</v>
@@ -41404,7 +41404,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.3307266235352</v>
+        <v>24.3307247161865</v>
       </c>
       <c r="H1415" t="n">
         <v>94778</v>
@@ -41636,7 +41636,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.3440780639648</v>
+        <v>23.3440799713135</v>
       </c>
       <c r="H1423" t="n">
         <v>50299</v>
@@ -41694,7 +41694,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1425" t="n">
         <v>19023</v>
@@ -41839,7 +41839,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.4230098724365</v>
+        <v>23.4230117797852</v>
       </c>
       <c r="H1430" t="n">
         <v>34199</v>
@@ -41897,7 +41897,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7387390136719</v>
+        <v>23.7387371063232</v>
       </c>
       <c r="H1432" t="n">
         <v>51446</v>
@@ -42042,7 +42042,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>24.685920715332</v>
+        <v>24.6859188079834</v>
       </c>
       <c r="H1437" t="n">
         <v>70358</v>
@@ -42129,7 +42129,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>26.3434886932373</v>
+        <v>26.3434867858887</v>
       </c>
       <c r="H1440" t="n">
         <v>93973</v>
@@ -42158,7 +42158,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.0341396331787</v>
+        <v>27.0341415405273</v>
       </c>
       <c r="H1441" t="n">
         <v>85164</v>
@@ -42216,7 +42216,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>28.4154472351074</v>
+        <v>28.4154453277588</v>
       </c>
       <c r="H1443" t="n">
         <v>195373</v>
@@ -42245,7 +42245,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>29.6980895996094</v>
+        <v>29.6980876922607</v>
       </c>
       <c r="H1444" t="n">
         <v>171716</v>
@@ -42303,7 +42303,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1446" t="n">
-        <v>29.7770214080811</v>
+        <v>29.7770195007324</v>
       </c>
       <c r="H1446" t="n">
         <v>87748</v>
@@ -42361,7 +42361,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1448" t="n">
-        <v>30.3295440673828</v>
+        <v>30.3295421600342</v>
       </c>
       <c r="H1448" t="n">
         <v>98329</v>
@@ -42535,7 +42535,7 @@
         <v>30.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>30.0927486419678</v>
+        <v>30.0927467346191</v>
       </c>
       <c r="H1454" t="n">
         <v>101035</v>
@@ -42622,7 +42622,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.4218273162842</v>
+        <v>29.4218254089355</v>
       </c>
       <c r="H1457" t="n">
         <v>72194</v>
@@ -42738,7 +42738,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>30.4676723480225</v>
+        <v>30.4676742553711</v>
       </c>
       <c r="H1461" t="n">
         <v>75514</v>
@@ -42854,7 +42854,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G1465" t="n">
-        <v>35.8547706604004</v>
+        <v>35.8547668457031</v>
       </c>
       <c r="H1465" t="n">
         <v>359905</v>
@@ -42941,7 +42941,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>39.0712356567383</v>
+        <v>39.0712394714355</v>
       </c>
       <c r="H1468" t="n">
         <v>321164</v>
@@ -42970,7 +42970,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1469" t="n">
-        <v>36.269157409668</v>
+        <v>36.2691612243652</v>
       </c>
       <c r="H1469" t="n">
         <v>228974</v>
@@ -43028,7 +43028,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>40.3538818359375</v>
+        <v>40.3538856506348</v>
       </c>
       <c r="H1471" t="n">
         <v>311161</v>
@@ -43144,7 +43144,7 @@
         <v>42.6599998474121</v>
       </c>
       <c r="G1475" t="n">
-        <v>42.0903778076172</v>
+        <v>42.0903816223145</v>
       </c>
       <c r="H1475" t="n">
         <v>174798</v>
@@ -43173,7 +43173,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>42.2482414245605</v>
+        <v>42.2482452392578</v>
       </c>
       <c r="H1476" t="n">
         <v>109882</v>
@@ -43202,7 +43202,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1477" t="n">
-        <v>42.5837020874023</v>
+        <v>42.5837059020996</v>
       </c>
       <c r="H1477" t="n">
         <v>137662</v>
@@ -43231,7 +43231,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>43.0178298950195</v>
+        <v>43.0178260803223</v>
       </c>
       <c r="H1478" t="n">
         <v>116213</v>
@@ -43260,7 +43260,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>42.6231689453125</v>
+        <v>42.6231727600098</v>
       </c>
       <c r="H1479" t="n">
         <v>123515</v>
@@ -43289,7 +43289,7 @@
         <v>43</v>
       </c>
       <c r="G1480" t="n">
-        <v>42.425838470459</v>
+        <v>42.4258422851562</v>
       </c>
       <c r="H1480" t="n">
         <v>77199</v>
@@ -43376,7 +43376,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.2615966796875</v>
+        <v>41.2615928649902</v>
       </c>
       <c r="H1483" t="n">
         <v>55495</v>
@@ -43405,7 +43405,7 @@
         <v>42.6399993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.0706443786621</v>
+        <v>42.0706481933594</v>
       </c>
       <c r="H1484" t="n">
         <v>72975</v>
@@ -43637,7 +43637,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1492" t="n">
-        <v>45.5831108093262</v>
+        <v>45.5831146240234</v>
       </c>
       <c r="H1492" t="n">
         <v>178167</v>
@@ -43666,7 +43666,7 @@
         <v>38.4199981689453</v>
       </c>
       <c r="G1493" t="n">
-        <v>37.9069938659668</v>
+        <v>37.9069900512695</v>
       </c>
       <c r="H1493" t="n">
         <v>678570</v>
@@ -43724,7 +43724,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1495" t="n">
-        <v>32.6185646057129</v>
+        <v>32.6185684204102</v>
       </c>
       <c r="H1495" t="n">
         <v>546704</v>
@@ -43869,7 +43869,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1500" t="n">
-        <v>30.4676723480225</v>
+        <v>30.4676742553711</v>
       </c>
       <c r="H1500" t="n">
         <v>356068</v>
@@ -43927,7 +43927,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>30.9215316772461</v>
+        <v>30.9215297698975</v>
       </c>
       <c r="H1502" t="n">
         <v>513447</v>
@@ -43985,7 +43985,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1504" t="n">
-        <v>31.0201969146729</v>
+        <v>31.0201950073242</v>
       </c>
       <c r="H1504" t="n">
         <v>237350</v>
@@ -44043,7 +44043,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>31.3951206207275</v>
+        <v>31.3951225280762</v>
       </c>
       <c r="H1506" t="n">
         <v>180598</v>
@@ -44101,7 +44101,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1508" t="n">
-        <v>30.9215316772461</v>
+        <v>30.9215297698975</v>
       </c>
       <c r="H1508" t="n">
         <v>287718</v>
@@ -80125,6 +80125,35 @@
         <v>14923</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>10.1199998855591</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>10.039999961853</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>7589</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48499965667725</v>
+        <v>6.4850001335144</v>
       </c>
       <c r="H4" t="n">
         <v>46846</v>
@@ -514,7 +514,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44674015045166</v>
+        <v>6.4467396736145</v>
       </c>
       <c r="H5" t="n">
         <v>108929</v>
@@ -572,7 +572,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544998168945</v>
       </c>
       <c r="H7" t="n">
         <v>40228</v>
@@ -601,7 +601,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>6.06414461135864</v>
+        <v>6.06414413452148</v>
       </c>
       <c r="H8" t="n">
         <v>43060</v>
@@ -688,7 +688,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03544950485229</v>
+        <v>6.03544998168945</v>
       </c>
       <c r="H11" t="n">
         <v>125780</v>
@@ -862,7 +862,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.72937250137329</v>
+        <v>5.72937297821045</v>
       </c>
       <c r="H17" t="n">
         <v>38963</v>
@@ -891,7 +891,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.0258846282959</v>
+        <v>6.02588510513306</v>
       </c>
       <c r="H18" t="n">
         <v>66351</v>
@@ -978,7 +978,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458293914795</v>
+        <v>5.94458341598511</v>
       </c>
       <c r="H21" t="n">
         <v>47413</v>
@@ -1007,7 +1007,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1884880065918</v>
+        <v>6.18848752975464</v>
       </c>
       <c r="H22" t="n">
         <v>27596</v>
@@ -1036,7 +1036,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.95414733886719</v>
+        <v>5.9541482925415</v>
       </c>
       <c r="H23" t="n">
         <v>39858</v>
@@ -1065,7 +1065,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>5.83458614349365</v>
+        <v>5.83458662033081</v>
       </c>
       <c r="H24" t="n">
         <v>59492</v>
@@ -1094,7 +1094,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154443740845</v>
+        <v>5.79154491424561</v>
       </c>
       <c r="H25" t="n">
         <v>42499</v>
@@ -1123,7 +1123,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.70067882537842</v>
+        <v>5.7006778717041</v>
       </c>
       <c r="H26" t="n">
         <v>83256</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244876861572</v>
+        <v>4.78244781494141</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1210,7 +1210,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679216384888</v>
+        <v>4.90679168701172</v>
       </c>
       <c r="H29" t="n">
         <v>118336</v>
@@ -1239,7 +1239,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62941026687622</v>
+        <v>4.62940979003906</v>
       </c>
       <c r="H30" t="n">
         <v>67579</v>
@@ -1268,7 +1268,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>4.87331438064575</v>
+        <v>4.87331390380859</v>
       </c>
       <c r="H31" t="n">
         <v>39515</v>
@@ -1297,7 +1297,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.06461238861084</v>
+        <v>5.064612865448</v>
       </c>
       <c r="H32" t="n">
         <v>19857</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.83983755111694</v>
+        <v>4.8398380279541</v>
       </c>
       <c r="H33" t="n">
         <v>11060</v>
@@ -1355,7 +1355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5954647064209</v>
+        <v>5.59546422958374</v>
       </c>
       <c r="H34" t="n">
         <v>87689</v>
@@ -1384,7 +1384,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>5.4424262046814</v>
+        <v>5.44242572784424</v>
       </c>
       <c r="H35" t="n">
         <v>178566</v>
@@ -1413,7 +1413,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677328109741</v>
+        <v>5.45677280426025</v>
       </c>
       <c r="H36" t="n">
         <v>102398</v>
@@ -1471,7 +1471,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.3228645324707</v>
+        <v>5.32286500930786</v>
       </c>
       <c r="H38" t="n">
         <v>45985</v>
@@ -1529,7 +1529,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460870742798</v>
+        <v>5.17460823059082</v>
       </c>
       <c r="H40" t="n">
         <v>27727</v>
@@ -1587,7 +1587,7 @@
         <v>5.5</v>
       </c>
       <c r="G42" t="n">
-        <v>5.26069259643555</v>
+        <v>5.26069307327271</v>
       </c>
       <c r="H42" t="n">
         <v>79999</v>
@@ -1616,7 +1616,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.97374629974365</v>
+        <v>4.97374582290649</v>
       </c>
       <c r="H43" t="n">
         <v>183347</v>
@@ -1645,7 +1645,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.738450050354</v>
+        <v>4.73844957351685</v>
       </c>
       <c r="H44" t="n">
         <v>146124</v>
@@ -1732,7 +1732,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749671936035</v>
+        <v>4.62749719619751</v>
       </c>
       <c r="H47" t="n">
         <v>92990</v>
@@ -1761,7 +1761,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G48" t="n">
-        <v>4.45915508270264</v>
+        <v>4.45915460586548</v>
       </c>
       <c r="H48" t="n">
         <v>57163</v>
@@ -1790,7 +1790,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>4.6389741897583</v>
+        <v>4.63897466659546</v>
       </c>
       <c r="H49" t="n">
         <v>45504</v>
@@ -1819,7 +1819,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984443664551</v>
+        <v>4.61984491348267</v>
       </c>
       <c r="H50" t="n">
         <v>32253</v>
@@ -1848,7 +1848,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671644210815</v>
+        <v>4.55671691894531</v>
       </c>
       <c r="H51" t="n">
         <v>33202</v>
@@ -1877,7 +1877,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>4.58732461929321</v>
+        <v>4.58732414245605</v>
       </c>
       <c r="H52" t="n">
         <v>22397</v>
@@ -1906,7 +1906,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G53" t="n">
-        <v>4.53184795379639</v>
+        <v>4.53184747695923</v>
       </c>
       <c r="H53" t="n">
         <v>41654</v>
@@ -1935,7 +1935,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G54" t="n">
-        <v>4.53184795379639</v>
+        <v>4.53184747695923</v>
       </c>
       <c r="H54" t="n">
         <v>15612</v>
@@ -1993,7 +1993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>4.39985275268555</v>
+        <v>4.39985227584839</v>
       </c>
       <c r="H56" t="n">
         <v>6922</v>
@@ -2080,7 +2080,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.23916244506836</v>
+        <v>4.23916292190552</v>
       </c>
       <c r="H59" t="n">
         <v>20035</v>
@@ -2138,7 +2138,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G61" t="n">
-        <v>4.01916980743408</v>
+        <v>4.01916933059692</v>
       </c>
       <c r="H61" t="n">
         <v>8387</v>
@@ -2167,7 +2167,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793968200684</v>
+        <v>4.39793920516968</v>
       </c>
       <c r="H62" t="n">
         <v>183307</v>
@@ -2196,7 +2196,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>4.57202005386353</v>
+        <v>4.57202053070068</v>
       </c>
       <c r="H63" t="n">
         <v>101318</v>
@@ -2225,7 +2225,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871948242188</v>
+        <v>4.46871995925903</v>
       </c>
       <c r="H64" t="n">
         <v>136790</v>
@@ -2254,7 +2254,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H65" t="n">
         <v>59895</v>
@@ -2283,7 +2283,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.0650806427002</v>
+        <v>4.06508111953735</v>
       </c>
       <c r="H66" t="n">
         <v>69251</v>
@@ -2341,7 +2341,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691846847534</v>
+        <v>3.71691870689392</v>
       </c>
       <c r="H68" t="n">
         <v>96719</v>
@@ -2399,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.82595872879028</v>
+        <v>3.8259584903717</v>
       </c>
       <c r="H70" t="n">
         <v>33705</v>
@@ -2428,7 +2428,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987460136414</v>
+        <v>3.73987483978271</v>
       </c>
       <c r="H71" t="n">
         <v>26533</v>
@@ -2486,7 +2486,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.77813410758972</v>
+        <v>3.7781343460083</v>
       </c>
       <c r="H73" t="n">
         <v>13357</v>
@@ -2515,7 +2515,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222255706787</v>
+        <v>3.73222231864929</v>
       </c>
       <c r="H74" t="n">
         <v>23567</v>
@@ -2544,7 +2544,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G75" t="n">
-        <v>3.84891414642334</v>
+        <v>3.84891438484192</v>
       </c>
       <c r="H75" t="n">
         <v>62408</v>
@@ -2602,7 +2602,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723096847534</v>
+        <v>4.78723049163818</v>
       </c>
       <c r="H77" t="n">
         <v>182115</v>
@@ -2660,7 +2660,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>5.07896041870117</v>
+        <v>5.07895994186401</v>
       </c>
       <c r="H79" t="n">
         <v>724913</v>
@@ -2776,7 +2776,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G83" t="n">
-        <v>5.05504751205444</v>
+        <v>5.0550479888916</v>
       </c>
       <c r="H83" t="n">
         <v>85082</v>
@@ -2834,7 +2834,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>4.93548583984375</v>
+        <v>4.93548631668091</v>
       </c>
       <c r="H85" t="n">
         <v>71889</v>
@@ -2892,7 +2892,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G87" t="n">
-        <v>4.73653650283813</v>
+        <v>4.73653697967529</v>
       </c>
       <c r="H87" t="n">
         <v>101740</v>
@@ -2921,7 +2921,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680593490601</v>
+        <v>4.46680688858032</v>
       </c>
       <c r="H88" t="n">
         <v>98603</v>
@@ -3008,7 +3008,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.36159229278564</v>
+        <v>4.3615927696228</v>
       </c>
       <c r="H91" t="n">
         <v>78370</v>
@@ -3037,7 +3037,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.18559885025024</v>
+        <v>4.1855993270874</v>
       </c>
       <c r="H92" t="n">
         <v>40037</v>
@@ -3153,7 +3153,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>4.16073036193848</v>
+        <v>4.16072940826416</v>
       </c>
       <c r="H96" t="n">
         <v>114509</v>
@@ -3182,7 +3182,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G97" t="n">
-        <v>4.11673164367676</v>
+        <v>4.1167311668396</v>
       </c>
       <c r="H97" t="n">
         <v>33027</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113971710205</v>
+        <v>4.92113924026489</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3472,7 +3472,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756622314453</v>
+        <v>7.74756669998169</v>
       </c>
       <c r="H107" t="n">
         <v>830490</v>
@@ -3530,7 +3530,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>7.06367683410645</v>
+        <v>7.06367635726929</v>
       </c>
       <c r="H109" t="n">
         <v>396366</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804183959961</v>
+        <v>6.52804136276245</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3617,7 +3617,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>6.26022434234619</v>
+        <v>6.26022481918335</v>
       </c>
       <c r="H112" t="n">
         <v>219748</v>
@@ -3646,7 +3646,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237466812134</v>
+        <v>6.98237419128418</v>
       </c>
       <c r="H113" t="n">
         <v>407399</v>
@@ -3675,7 +3675,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>6.79585886001587</v>
+        <v>6.79585933685303</v>
       </c>
       <c r="H114" t="n">
         <v>508219</v>
@@ -3704,7 +3704,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.3845682144165</v>
+        <v>6.38456773757935</v>
       </c>
       <c r="H115" t="n">
         <v>131401</v>
@@ -3733,7 +3733,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718311309814</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H116" t="n">
         <v>279195</v>
@@ -3762,7 +3762,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718311309814</v>
+        <v>6.21718263626099</v>
       </c>
       <c r="H117" t="n">
         <v>281217</v>
@@ -3791,7 +3791,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>5.83458614349365</v>
+        <v>5.83458662033081</v>
       </c>
       <c r="H118" t="n">
         <v>228253</v>
@@ -3849,7 +3849,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>6.06414461135864</v>
+        <v>6.06414413452148</v>
       </c>
       <c r="H120" t="n">
         <v>187928</v>
@@ -3878,7 +3878,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370901107788</v>
+        <v>6.07370853424072</v>
       </c>
       <c r="H121" t="n">
         <v>194455</v>
@@ -3936,7 +3936,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195379257202</v>
+        <v>6.55195426940918</v>
       </c>
       <c r="H123" t="n">
         <v>388485</v>
@@ -4023,7 +4023,7 @@
         <v>6.54500007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>6.26022434234619</v>
+        <v>6.26022481918335</v>
       </c>
       <c r="H126" t="n">
         <v>126051</v>
@@ -4081,7 +4081,7 @@
         <v>6.625</v>
       </c>
       <c r="G128" t="n">
-        <v>6.33674383163452</v>
+        <v>6.33674430847168</v>
       </c>
       <c r="H128" t="n">
         <v>31549</v>
@@ -4197,7 +4197,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370901107788</v>
+        <v>6.07370853424072</v>
       </c>
       <c r="H132" t="n">
         <v>115535</v>
@@ -4284,7 +4284,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>6.82933616638184</v>
+        <v>6.82933568954468</v>
       </c>
       <c r="H135" t="n">
         <v>65285</v>
@@ -4342,7 +4342,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>6.97280979156494</v>
+        <v>6.97280931472778</v>
       </c>
       <c r="H137" t="n">
         <v>53595</v>
@@ -4371,7 +4371,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.12584781646729</v>
+        <v>7.12584733963013</v>
       </c>
       <c r="H138" t="n">
         <v>47644</v>
@@ -4429,7 +4429,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>7.05889368057251</v>
+        <v>7.05889320373535</v>
       </c>
       <c r="H140" t="n">
         <v>313570</v>
@@ -4487,7 +4487,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>6.99672174453735</v>
+        <v>6.9967212677002</v>
       </c>
       <c r="H142" t="n">
         <v>66130</v>
@@ -4661,7 +4661,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75281667709351</v>
+        <v>6.75281715393066</v>
       </c>
       <c r="H148" t="n">
         <v>55331</v>
@@ -4690,7 +4690,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.8723783493042</v>
+        <v>6.87237787246704</v>
       </c>
       <c r="H149" t="n">
         <v>71959</v>
@@ -4748,7 +4748,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>6.85324764251709</v>
+        <v>6.85324811935425</v>
       </c>
       <c r="H151" t="n">
         <v>44123</v>
@@ -4777,7 +4777,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>6.95368003845215</v>
+        <v>6.95367908477783</v>
       </c>
       <c r="H152" t="n">
         <v>61634</v>
@@ -4806,7 +4806,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>6.97280979156494</v>
+        <v>6.97280931472778</v>
       </c>
       <c r="H153" t="n">
         <v>63748</v>
@@ -4922,7 +4922,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886518478394</v>
+        <v>7.93886375427246</v>
       </c>
       <c r="H157" t="n">
         <v>265495</v>
@@ -4980,7 +4980,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712741851807</v>
+        <v>7.86712789535522</v>
       </c>
       <c r="H159" t="n">
         <v>93100</v>
@@ -5067,7 +5067,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G162" t="n">
-        <v>7.66626453399658</v>
+        <v>7.66626405715942</v>
       </c>
       <c r="H162" t="n">
         <v>71695</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626132965088</v>
+        <v>7.77626085281372</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.99625253677368</v>
+        <v>7.99625396728516</v>
       </c>
       <c r="H166" t="n">
         <v>48102</v>
@@ -5241,7 +5241,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451251983643</v>
+        <v>8.03451156616211</v>
       </c>
       <c r="H168" t="n">
         <v>39269</v>
@@ -5270,7 +5270,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060424804688</v>
+        <v>7.90060520172119</v>
       </c>
       <c r="H169" t="n">
         <v>42906</v>
@@ -5386,7 +5386,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.89582252502441</v>
+        <v>7.8958215713501</v>
       </c>
       <c r="H173" t="n">
         <v>38551</v>
@@ -5415,7 +5415,7 @@
         <v>8.75</v>
       </c>
       <c r="G174" t="n">
-        <v>8.36928558349609</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H174" t="n">
         <v>135297</v>
@@ -5473,7 +5473,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>9.00535011291504</v>
+        <v>9.00534915924072</v>
       </c>
       <c r="H176" t="n">
         <v>166097</v>
@@ -5502,7 +5502,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622676849365</v>
+        <v>8.76622772216797</v>
       </c>
       <c r="H177" t="n">
         <v>231642</v>
@@ -5531,7 +5531,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65623188018799</v>
+        <v>8.65623092651367</v>
       </c>
       <c r="H178" t="n">
         <v>104419</v>
@@ -5589,7 +5589,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.17798614501953</v>
+        <v>8.17798519134521</v>
       </c>
       <c r="H180" t="n">
         <v>197433</v>
@@ -5618,7 +5618,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.4171085357666</v>
+        <v>8.41710948944092</v>
       </c>
       <c r="H181" t="n">
         <v>154982</v>
@@ -5676,7 +5676,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>8.20668029785156</v>
+        <v>8.20668125152588</v>
       </c>
       <c r="H183" t="n">
         <v>59457</v>
@@ -5705,7 +5705,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>8.2545051574707</v>
+        <v>8.25450611114502</v>
       </c>
       <c r="H184" t="n">
         <v>33220</v>
@@ -5821,7 +5821,7 @@
         <v>8.75</v>
       </c>
       <c r="G188" t="n">
-        <v>8.36928558349609</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H188" t="n">
         <v>34542</v>
@@ -5850,7 +5850,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.29754638671875</v>
+        <v>8.29754734039307</v>
       </c>
       <c r="H189" t="n">
         <v>29985</v>
@@ -5879,7 +5879,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.2736349105835</v>
+        <v>8.27363586425781</v>
       </c>
       <c r="H190" t="n">
         <v>51064</v>
@@ -5908,7 +5908,7 @@
         <v>8.75</v>
       </c>
       <c r="G191" t="n">
-        <v>8.36928558349609</v>
+        <v>8.36928462982178</v>
       </c>
       <c r="H191" t="n">
         <v>24030</v>
@@ -5937,7 +5937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G192" t="n">
-        <v>8.43623828887939</v>
+        <v>8.43623924255371</v>
       </c>
       <c r="H192" t="n">
         <v>44995</v>
@@ -6024,7 +6024,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G195" t="n">
-        <v>9.06752014160156</v>
+        <v>9.06752109527588</v>
       </c>
       <c r="H195" t="n">
         <v>116469</v>
@@ -6082,7 +6082,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968887329102</v>
+        <v>9.23968982696533</v>
       </c>
       <c r="H197" t="n">
         <v>111328</v>
@@ -6140,7 +6140,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G199" t="n">
-        <v>9.18708229064941</v>
+        <v>9.18708324432373</v>
       </c>
       <c r="H199" t="n">
         <v>82966</v>
@@ -6169,7 +6169,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882598876953</v>
+        <v>9.03882694244385</v>
       </c>
       <c r="H200" t="n">
         <v>84914</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.13447570800781</v>
+        <v>9.13447666168213</v>
       </c>
       <c r="H201" t="n">
         <v>49199</v>
@@ -6256,7 +6256,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185855865479</v>
+        <v>9.41185760498047</v>
       </c>
       <c r="H203" t="n">
         <v>115834</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489753723145</v>
+        <v>9.56489562988281</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6401,7 +6401,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.53620147705078</v>
+        <v>9.5362024307251</v>
       </c>
       <c r="H208" t="n">
         <v>78401</v>
@@ -6488,7 +6488,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.253568649292</v>
+        <v>10.2535705566406</v>
       </c>
       <c r="H211" t="n">
         <v>105355</v>
@@ -6604,7 +6604,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G215" t="n">
-        <v>11.200493812561</v>
+        <v>11.2004928588867</v>
       </c>
       <c r="H215" t="n">
         <v>33710</v>
@@ -6633,7 +6633,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518060684204</v>
+        <v>10.9518051147461</v>
       </c>
       <c r="H216" t="n">
         <v>101398</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692110061646</v>
+        <v>10.5692100524902</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6778,7 +6778,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8274621963501</v>
+        <v>10.8274612426758</v>
       </c>
       <c r="H221" t="n">
         <v>165457</v>
@@ -6807,7 +6807,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.8370275497437</v>
+        <v>10.837028503418</v>
       </c>
       <c r="H222" t="n">
         <v>98298</v>
@@ -6865,7 +6865,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>11.114408493042</v>
+        <v>11.1144094467163</v>
       </c>
       <c r="H224" t="n">
         <v>91003</v>
@@ -6894,7 +6894,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630971908569</v>
+        <v>11.3630962371826</v>
       </c>
       <c r="H225" t="n">
         <v>187509</v>
@@ -6923,7 +6923,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117849349976</v>
+        <v>11.6117839813232</v>
       </c>
       <c r="H226" t="n">
         <v>191398</v>
@@ -6981,7 +6981,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7456912994385</v>
+        <v>11.7456922531128</v>
       </c>
       <c r="H228" t="n">
         <v>176751</v>
@@ -7010,7 +7010,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>11.7648220062256</v>
+        <v>11.7648229598999</v>
       </c>
       <c r="H229" t="n">
         <v>87480</v>
@@ -7039,7 +7039,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G230" t="n">
-        <v>11.6309127807617</v>
+        <v>11.630913734436</v>
       </c>
       <c r="H230" t="n">
         <v>118136</v>
@@ -7068,7 +7068,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>11.6691722869873</v>
+        <v>11.6691732406616</v>
       </c>
       <c r="H231" t="n">
         <v>95647</v>
@@ -7097,7 +7097,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0708990097046</v>
+        <v>12.0708999633789</v>
       </c>
       <c r="H232" t="n">
         <v>161563</v>
@@ -7155,7 +7155,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H234" t="n">
         <v>153081</v>
@@ -7184,7 +7184,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>11.9369897842407</v>
+        <v>11.936990737915</v>
       </c>
       <c r="H235" t="n">
         <v>95580</v>
@@ -7213,7 +7213,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474180221558</v>
+        <v>12.1474170684814</v>
       </c>
       <c r="H236" t="n">
         <v>111282</v>
@@ -7242,7 +7242,7 @@
         <v>12.25</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7169981002808</v>
+        <v>11.7169971466064</v>
       </c>
       <c r="H237" t="n">
         <v>107537</v>
@@ -7329,7 +7329,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.6160984039307</v>
+        <v>12.6160974502563</v>
       </c>
       <c r="H240" t="n">
         <v>180021</v>
@@ -7387,7 +7387,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717250823975</v>
+        <v>13.3717231750488</v>
       </c>
       <c r="H242" t="n">
         <v>100896</v>
@@ -7416,7 +7416,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473434448242</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H243" t="n">
         <v>303111</v>
@@ -7445,7 +7445,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446565628052</v>
+        <v>15.2446575164795</v>
       </c>
       <c r="H244" t="n">
         <v>256881</v>
@@ -7474,7 +7474,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>14.0385932922363</v>
+        <v>14.038592338562</v>
       </c>
       <c r="H245" t="n">
         <v>494015</v>
@@ -7561,7 +7561,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G248" t="n">
-        <v>13.3728437423706</v>
+        <v>13.3728446960449</v>
       </c>
       <c r="H248" t="n">
         <v>127762</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272207260132</v>
+        <v>13.5272216796875</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7619,7 +7619,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G250" t="n">
-        <v>13.4307355880737</v>
+        <v>13.430736541748</v>
       </c>
       <c r="H250" t="n">
         <v>48278</v>
@@ -7735,7 +7735,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8132305145264</v>
+        <v>12.8132295608521</v>
       </c>
       <c r="H254" t="n">
         <v>50394</v>
@@ -7764,7 +7764,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>13.1509284973145</v>
+        <v>13.1509294509888</v>
       </c>
       <c r="H255" t="n">
         <v>47379</v>
@@ -7822,7 +7822,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000682830811</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H257" t="n">
         <v>36672</v>
@@ -7880,7 +7880,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H259" t="n">
         <v>124706</v>
@@ -7996,7 +7996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219835281372</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H263" t="n">
         <v>90090</v>
@@ -8054,7 +8054,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>13.78773021698</v>
+        <v>13.7877311706543</v>
       </c>
       <c r="H265" t="n">
         <v>225704</v>
@@ -8083,7 +8083,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973804473877</v>
+        <v>13.7973794937134</v>
       </c>
       <c r="H266" t="n">
         <v>74231</v>
@@ -8170,7 +8170,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G269" t="n">
-        <v>13.585111618042</v>
+        <v>13.5851125717163</v>
       </c>
       <c r="H269" t="n">
         <v>52002</v>
@@ -8228,7 +8228,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.131630897522</v>
+        <v>13.1316318511963</v>
       </c>
       <c r="H271" t="n">
         <v>92437</v>
@@ -8257,7 +8257,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219835281372</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H272" t="n">
         <v>43627</v>
@@ -8344,7 +8344,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869733810425</v>
+        <v>11.8869724273682</v>
       </c>
       <c r="H275" t="n">
         <v>94457</v>
@@ -8402,7 +8402,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5396270751953</v>
+        <v>11.539626121521</v>
       </c>
       <c r="H277" t="n">
         <v>194589</v>
@@ -8431,7 +8431,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H278" t="n">
         <v>152414</v>
@@ -8489,7 +8489,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G280" t="n">
-        <v>11.6650581359863</v>
+        <v>11.665057182312</v>
       </c>
       <c r="H280" t="n">
         <v>34289</v>
@@ -8547,7 +8547,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H282" t="n">
         <v>117391</v>
@@ -8605,7 +8605,7 @@
         <v>11.75</v>
       </c>
       <c r="G284" t="n">
-        <v>11.337007522583</v>
+        <v>11.3370065689087</v>
       </c>
       <c r="H284" t="n">
         <v>114241</v>
@@ -8692,7 +8692,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G287" t="n">
-        <v>10.7484483718872</v>
+        <v>10.7484493255615</v>
       </c>
       <c r="H287" t="n">
         <v>33613</v>
@@ -8837,7 +8837,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738794326782</v>
+        <v>10.8738784790039</v>
       </c>
       <c r="H292" t="n">
         <v>53600</v>
@@ -8924,7 +8924,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G295" t="n">
-        <v>10.8449335098267</v>
+        <v>10.8449325561523</v>
       </c>
       <c r="H295" t="n">
         <v>23068</v>
@@ -8982,7 +8982,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695384979248</v>
+        <v>10.1695365905762</v>
       </c>
       <c r="H297" t="n">
         <v>66319</v>
@@ -9011,7 +9011,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247396469116</v>
+        <v>11.1247406005859</v>
       </c>
       <c r="H298" t="n">
         <v>108006</v>
@@ -9040,7 +9040,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>10.9124727249146</v>
+        <v>10.9124736785889</v>
       </c>
       <c r="H299" t="n">
         <v>173611</v>
@@ -9069,7 +9069,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685729980469</v>
+        <v>11.5685720443726</v>
       </c>
       <c r="H300" t="n">
         <v>224596</v>
@@ -9098,7 +9098,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H301" t="n">
         <v>68761</v>
@@ -9127,7 +9127,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>11.3273601531982</v>
+        <v>11.3273591995239</v>
       </c>
       <c r="H302" t="n">
         <v>104822</v>
@@ -9301,7 +9301,7 @@
         <v>11.75</v>
       </c>
       <c r="G308" t="n">
-        <v>11.337007522583</v>
+        <v>11.3370065689087</v>
       </c>
       <c r="H308" t="n">
         <v>79684</v>
@@ -9330,7 +9330,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.259819984436</v>
+        <v>11.2598190307617</v>
       </c>
       <c r="H309" t="n">
         <v>85197</v>
@@ -9388,7 +9388,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212257385254</v>
+        <v>11.2212247848511</v>
       </c>
       <c r="H311" t="n">
         <v>48985</v>
@@ -9475,7 +9475,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>11.5299787521362</v>
+        <v>11.5299777984619</v>
       </c>
       <c r="H314" t="n">
         <v>80574</v>
@@ -9591,7 +9591,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>12.0220518112183</v>
+        <v>12.0220527648926</v>
       </c>
       <c r="H318" t="n">
         <v>61490</v>
@@ -9736,7 +9736,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387308120728</v>
+        <v>11.8387317657471</v>
       </c>
       <c r="H323" t="n">
         <v>88601</v>
@@ -9765,7 +9765,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>11.915919303894</v>
+        <v>11.9159202575684</v>
       </c>
       <c r="H324" t="n">
         <v>37512</v>
@@ -9852,7 +9852,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G327" t="n">
-        <v>13.6140565872192</v>
+        <v>13.6140584945679</v>
       </c>
       <c r="H327" t="n">
         <v>135660</v>
@@ -9881,7 +9881,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H328" t="n">
         <v>133226</v>
@@ -9968,7 +9968,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H331" t="n">
         <v>127592</v>
@@ -9997,7 +9997,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G332" t="n">
-        <v>13.4307355880737</v>
+        <v>13.430736541748</v>
       </c>
       <c r="H332" t="n">
         <v>75116</v>
@@ -10026,7 +10026,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886264801025</v>
+        <v>13.4886255264282</v>
       </c>
       <c r="H333" t="n">
         <v>19569</v>
@@ -10055,7 +10055,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.710542678833</v>
+        <v>13.7105417251587</v>
       </c>
       <c r="H334" t="n">
         <v>74737</v>
@@ -10113,7 +10113,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G336" t="n">
-        <v>13.7394876480103</v>
+        <v>13.7394886016846</v>
       </c>
       <c r="H336" t="n">
         <v>66093</v>
@@ -10142,7 +10142,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552703857422</v>
+        <v>13.8552694320679</v>
       </c>
       <c r="H337" t="n">
         <v>35661</v>
@@ -10345,7 +10345,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473443984985</v>
+        <v>14.3473453521729</v>
       </c>
       <c r="H344" t="n">
         <v>84729</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>14.569260597229</v>
+        <v>14.5692615509033</v>
       </c>
       <c r="H346" t="n">
         <v>63786</v>
@@ -10490,7 +10490,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.405237197876</v>
+        <v>14.4052362442017</v>
       </c>
       <c r="H349" t="n">
         <v>73630</v>
@@ -10519,7 +10519,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>14.4824237823486</v>
+        <v>14.4824247360229</v>
       </c>
       <c r="H350" t="n">
         <v>97965</v>
@@ -10548,7 +10548,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G351" t="n">
-        <v>13.9999980926514</v>
+        <v>13.9999990463257</v>
       </c>
       <c r="H351" t="n">
         <v>100826</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527210235596</v>
+        <v>12.5527200698853</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10693,7 +10693,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000682830811</v>
+        <v>12.9000673294067</v>
       </c>
       <c r="H356" t="n">
         <v>42754</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.0062017440796</v>
+        <v>13.006199836731</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10809,7 +10809,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H360" t="n">
         <v>18254</v>
@@ -10838,7 +10838,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H361" t="n">
         <v>30895</v>
@@ -10896,7 +10896,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H363" t="n">
         <v>24673</v>
@@ -10925,7 +10925,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.131630897522</v>
+        <v>13.1316318511963</v>
       </c>
       <c r="H364" t="n">
         <v>31128</v>
@@ -10954,7 +10954,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H365" t="n">
         <v>55168</v>
@@ -11012,7 +11012,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360429763794</v>
+        <v>12.7360420227051</v>
       </c>
       <c r="H367" t="n">
         <v>41635</v>
@@ -11070,7 +11070,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H369" t="n">
         <v>33590</v>
@@ -11128,7 +11128,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755334854126</v>
+        <v>12.4755325317383</v>
       </c>
       <c r="H371" t="n">
         <v>12596</v>
@@ -11186,7 +11186,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>11.9641609191895</v>
+        <v>11.9641599655151</v>
       </c>
       <c r="H373" t="n">
         <v>95740</v>
@@ -11215,7 +11215,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>12.2150220870972</v>
+        <v>12.2150230407715</v>
       </c>
       <c r="H374" t="n">
         <v>20005</v>
@@ -11244,7 +11244,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474828720093</v>
+        <v>12.1474838256836</v>
       </c>
       <c r="H375" t="n">
         <v>32852</v>
@@ -11273,7 +11273,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H376" t="n">
         <v>18790</v>
@@ -11302,7 +11302,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H377" t="n">
         <v>54450</v>
@@ -11331,7 +11331,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G378" t="n">
-        <v>12.4176416397095</v>
+        <v>12.4176425933838</v>
       </c>
       <c r="H378" t="n">
         <v>61237</v>
@@ -11389,7 +11389,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1571321487427</v>
+        <v>12.1571311950684</v>
       </c>
       <c r="H380" t="n">
         <v>38689</v>
@@ -11476,7 +11476,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G383" t="n">
-        <v>11.6940031051636</v>
+        <v>11.6940021514893</v>
       </c>
       <c r="H383" t="n">
         <v>41701</v>
@@ -11505,7 +11505,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>11.6843538284302</v>
+        <v>11.6843547821045</v>
       </c>
       <c r="H384" t="n">
         <v>27524</v>
@@ -11534,7 +11534,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>11.7325954437256</v>
+        <v>11.7325963973999</v>
       </c>
       <c r="H385" t="n">
         <v>6733</v>
@@ -11563,7 +11563,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G386" t="n">
-        <v>11.6843538284302</v>
+        <v>11.6843547821045</v>
       </c>
       <c r="H386" t="n">
         <v>27537</v>
@@ -11592,7 +11592,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H387" t="n">
         <v>110158</v>
@@ -11650,7 +11650,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966207504272</v>
+        <v>11.8966217041016</v>
       </c>
       <c r="H389" t="n">
         <v>33102</v>
@@ -11679,7 +11679,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>11.9641609191895</v>
+        <v>11.9641599655151</v>
       </c>
       <c r="H390" t="n">
         <v>27020</v>
@@ -11708,7 +11708,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H391" t="n">
         <v>36167</v>
@@ -11795,7 +11795,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545125961304</v>
+        <v>11.9545135498047</v>
       </c>
       <c r="H394" t="n">
         <v>7832</v>
@@ -11824,7 +11824,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.195725440979</v>
+        <v>12.1957263946533</v>
       </c>
       <c r="H395" t="n">
         <v>18587</v>
@@ -11853,7 +11853,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.2439670562744</v>
+        <v>12.2439680099487</v>
       </c>
       <c r="H396" t="n">
         <v>21900</v>
@@ -11882,7 +11882,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H397" t="n">
         <v>62135</v>
@@ -11998,7 +11998,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.8325290679932</v>
+        <v>12.8325281143188</v>
       </c>
       <c r="H401" t="n">
         <v>13252</v>
@@ -12027,7 +12027,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H402" t="n">
         <v>31655</v>
@@ -12056,7 +12056,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>12.562370300293</v>
+        <v>12.5623693466187</v>
       </c>
       <c r="H403" t="n">
         <v>8745</v>
@@ -12085,7 +12085,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H404" t="n">
         <v>9320</v>
@@ -12201,7 +12201,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421764373779</v>
+        <v>12.8421773910522</v>
       </c>
       <c r="H408" t="n">
         <v>32363</v>
@@ -12259,7 +12259,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483108520508</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H410" t="n">
         <v>21714</v>
@@ -12317,7 +12317,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219835281372</v>
+        <v>13.1219844818115</v>
       </c>
       <c r="H412" t="n">
         <v>20167</v>
@@ -12375,7 +12375,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3115081787109</v>
+        <v>12.3115072250366</v>
       </c>
       <c r="H414" t="n">
         <v>76954</v>
@@ -12404,7 +12404,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>12.562370300293</v>
+        <v>12.5623693466187</v>
       </c>
       <c r="H415" t="n">
         <v>14241</v>
@@ -12462,7 +12462,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H417" t="n">
         <v>19263</v>
@@ -12607,7 +12607,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483108520508</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H422" t="n">
         <v>22215</v>
@@ -12665,7 +12665,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.9290132522583</v>
+        <v>12.929012298584</v>
       </c>
       <c r="H424" t="n">
         <v>8468</v>
@@ -12723,7 +12723,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5334234237671</v>
+        <v>12.5334243774414</v>
       </c>
       <c r="H426" t="n">
         <v>25449</v>
@@ -12781,7 +12781,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483108520508</v>
+        <v>12.9483098983765</v>
       </c>
       <c r="H428" t="n">
         <v>13836</v>
@@ -12810,7 +12810,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.8325290679932</v>
+        <v>12.8325281143188</v>
       </c>
       <c r="H429" t="n">
         <v>23103</v>
@@ -12839,7 +12839,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351476669312</v>
+        <v>13.0351467132568</v>
       </c>
       <c r="H430" t="n">
         <v>30798</v>
@@ -12897,7 +12897,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>13.2860078811646</v>
+        <v>13.2860088348389</v>
       </c>
       <c r="H432" t="n">
         <v>64869</v>
@@ -13042,7 +13042,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842855453491</v>
+        <v>12.7842845916748</v>
       </c>
       <c r="H437" t="n">
         <v>115869</v>
@@ -13071,7 +13071,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6974487304688</v>
+        <v>12.6974477767944</v>
       </c>
       <c r="H438" t="n">
         <v>68110</v>
@@ -13245,7 +13245,7 @@
         <v>13</v>
       </c>
       <c r="G444" t="n">
-        <v>12.5430727005005</v>
+        <v>12.5430717468262</v>
       </c>
       <c r="H444" t="n">
         <v>22029</v>
@@ -13274,7 +13274,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H445" t="n">
         <v>16060</v>
@@ -13303,7 +13303,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H446" t="n">
         <v>35222</v>
@@ -13332,7 +13332,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202611923218</v>
+        <v>12.6202592849731</v>
       </c>
       <c r="H447" t="n">
         <v>14428</v>
@@ -13361,7 +13361,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>12.4851808547974</v>
+        <v>12.485179901123</v>
       </c>
       <c r="H448" t="n">
         <v>23317</v>
@@ -13419,7 +13419,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G450" t="n">
-        <v>12.6781511306763</v>
+        <v>12.6781530380249</v>
       </c>
       <c r="H450" t="n">
         <v>8729</v>
@@ -13448,7 +13448,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>12.4948291778564</v>
+        <v>12.4948301315308</v>
       </c>
       <c r="H451" t="n">
         <v>58859</v>
@@ -13535,7 +13535,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.86767578125</v>
+        <v>11.8676767349243</v>
       </c>
       <c r="H454" t="n">
         <v>101981</v>
@@ -13593,7 +13593,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.993106842041</v>
+        <v>11.9931077957153</v>
       </c>
       <c r="H456" t="n">
         <v>40685</v>
@@ -13622,7 +13622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H457" t="n">
         <v>24461</v>
@@ -13709,7 +13709,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>12.446587562561</v>
+        <v>12.4465866088867</v>
       </c>
       <c r="H460" t="n">
         <v>60559</v>
@@ -13738,7 +13738,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044775009155</v>
+        <v>12.5044784545898</v>
       </c>
       <c r="H461" t="n">
         <v>38181</v>
@@ -13854,7 +13854,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G465" t="n">
-        <v>11.9352149963379</v>
+        <v>11.9352159500122</v>
       </c>
       <c r="H465" t="n">
         <v>21056</v>
@@ -13883,7 +13883,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H466" t="n">
         <v>20941</v>
@@ -13941,7 +13941,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738092422485</v>
+        <v>11.9738101959229</v>
       </c>
       <c r="H468" t="n">
         <v>13736</v>
@@ -13970,7 +13970,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>12.1185369491577</v>
+        <v>12.118537902832</v>
       </c>
       <c r="H469" t="n">
         <v>26893</v>
@@ -14086,7 +14086,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>12.1088886260986</v>
+        <v>12.1088895797729</v>
       </c>
       <c r="H473" t="n">
         <v>20258</v>
@@ -14173,7 +14173,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>11.8290815353394</v>
+        <v>11.829083442688</v>
       </c>
       <c r="H476" t="n">
         <v>75300</v>
@@ -14231,7 +14231,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G478" t="n">
-        <v>10.1502408981323</v>
+        <v>10.150239944458</v>
       </c>
       <c r="H478" t="n">
         <v>249899</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554637908936</v>
+        <v>9.45554733276367</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14318,7 +14318,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711185455322</v>
+        <v>9.68711090087891</v>
       </c>
       <c r="H481" t="n">
         <v>127849</v>
@@ -14347,7 +14347,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G482" t="n">
-        <v>9.85113620758057</v>
+        <v>9.85113525390625</v>
       </c>
       <c r="H482" t="n">
         <v>95444</v>
@@ -14376,7 +14376,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923490524292</v>
+        <v>10.0923480987549</v>
       </c>
       <c r="H483" t="n">
         <v>75251</v>
@@ -14405,7 +14405,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625068664551</v>
+        <v>10.3625078201294</v>
       </c>
       <c r="H484" t="n">
         <v>99264</v>
@@ -14434,7 +14434,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107494354248</v>
+        <v>10.4107503890991</v>
       </c>
       <c r="H485" t="n">
         <v>165118</v>
@@ -14521,7 +14521,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764970779419</v>
+        <v>11.0764961242676</v>
       </c>
       <c r="H488" t="n">
         <v>85880</v>
@@ -14637,7 +14637,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028253555298</v>
       </c>
       <c r="H492" t="n">
         <v>50334</v>
@@ -14666,7 +14666,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256359100342</v>
+        <v>10.8256378173828</v>
       </c>
       <c r="H493" t="n">
         <v>48038</v>
@@ -14695,7 +14695,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G494" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028253555298</v>
       </c>
       <c r="H494" t="n">
         <v>56326</v>
@@ -14753,7 +14753,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G496" t="n">
-        <v>10.9028244018555</v>
+        <v>10.9028253555298</v>
       </c>
       <c r="H496" t="n">
         <v>116291</v>
@@ -14782,7 +14782,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7387990951538</v>
+        <v>10.7388000488281</v>
       </c>
       <c r="H497" t="n">
         <v>62706</v>
@@ -14811,7 +14811,7 @@
         <v>11.25</v>
       </c>
       <c r="G498" t="n">
-        <v>10.8545818328857</v>
+        <v>10.8545808792114</v>
       </c>
       <c r="H498" t="n">
         <v>41656</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078971862793</v>
+        <v>10.7078981399536</v>
       </c>
       <c r="H500" t="n">
         <v>97230</v>
@@ -14898,7 +14898,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G501" t="n">
-        <v>10.4732046127319</v>
+        <v>10.4732036590576</v>
       </c>
       <c r="H501" t="n">
         <v>197020</v>
@@ -14927,7 +14927,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H502" t="n">
         <v>89414</v>
@@ -14956,7 +14956,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189531326294</v>
+        <v>10.2189521789551</v>
       </c>
       <c r="H503" t="n">
         <v>87325</v>
@@ -14985,7 +14985,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612154006958</v>
+        <v>10.5612144470215</v>
       </c>
       <c r="H504" t="n">
         <v>62409</v>
@@ -15043,7 +15043,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4536457061768</v>
+        <v>10.4536466598511</v>
       </c>
       <c r="H506" t="n">
         <v>53759</v>
@@ -15072,7 +15072,7 @@
         <v>10.75</v>
       </c>
       <c r="G507" t="n">
-        <v>10.5123205184937</v>
+        <v>10.5123195648193</v>
       </c>
       <c r="H507" t="n">
         <v>171168</v>
@@ -15130,7 +15130,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G509" t="n">
-        <v>10.4047517776489</v>
+        <v>10.4047527313232</v>
       </c>
       <c r="H509" t="n">
         <v>85761</v>
@@ -15159,7 +15159,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H510" t="n">
         <v>74515</v>
@@ -15188,7 +15188,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G511" t="n">
-        <v>10.580771446228</v>
+        <v>10.5807723999023</v>
       </c>
       <c r="H511" t="n">
         <v>29173</v>
@@ -15246,7 +15246,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H513" t="n">
         <v>68123</v>
@@ -15304,7 +15304,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H515" t="n">
         <v>114765</v>
@@ -15362,7 +15362,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110445022583</v>
+        <v>11.0110454559326</v>
       </c>
       <c r="H517" t="n">
         <v>116880</v>
@@ -15681,7 +15681,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H528" t="n">
         <v>31481</v>
@@ -15710,7 +15710,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G529" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H529" t="n">
         <v>46104</v>
@@ -15739,7 +15739,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G530" t="n">
-        <v>10.9914865493774</v>
+        <v>10.9914855957031</v>
       </c>
       <c r="H530" t="n">
         <v>50487</v>
@@ -15797,7 +15797,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.815465927124</v>
+        <v>10.8154668807983</v>
       </c>
       <c r="H532" t="n">
         <v>61309</v>
@@ -15855,7 +15855,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634256362915</v>
+        <v>10.4634265899658</v>
       </c>
       <c r="H534" t="n">
         <v>20572</v>
@@ -15884,7 +15884,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069629669189</v>
+        <v>10.3069620132446</v>
       </c>
       <c r="H535" t="n">
         <v>59740</v>
@@ -15942,7 +15942,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G537" t="n">
-        <v>9.81801891326904</v>
+        <v>9.81801795959473</v>
       </c>
       <c r="H537" t="n">
         <v>66947</v>
@@ -16087,7 +16087,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H542" t="n">
         <v>15487</v>
@@ -16145,7 +16145,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>9.64199829101562</v>
+        <v>9.64199733734131</v>
       </c>
       <c r="H544" t="n">
         <v>45893</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H546" t="n">
         <v>15589</v>
@@ -16232,7 +16232,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509357452393</v>
+        <v>9.50509262084961</v>
       </c>
       <c r="H547" t="n">
         <v>11946</v>
@@ -16290,7 +16290,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H549" t="n">
         <v>23576</v>
@@ -16348,7 +16348,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G551" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H551" t="n">
         <v>15436</v>
@@ -16406,7 +16406,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H553" t="n">
         <v>22573</v>
@@ -16464,7 +16464,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432834625244</v>
+        <v>8.65432929992676</v>
       </c>
       <c r="H555" t="n">
         <v>68485</v>
@@ -16522,7 +16522,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.84990692138672</v>
+        <v>8.8499059677124</v>
       </c>
       <c r="H557" t="n">
         <v>76043</v>
@@ -16580,7 +16580,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H559" t="n">
         <v>111011</v>
@@ -16638,7 +16638,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>9.65177726745605</v>
+        <v>9.65177631378174</v>
       </c>
       <c r="H561" t="n">
         <v>47843</v>
@@ -16667,7 +16667,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H562" t="n">
         <v>31267</v>
@@ -16696,7 +16696,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H563" t="n">
         <v>28072</v>
@@ -16783,7 +16783,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H566" t="n">
         <v>45222</v>
@@ -16812,7 +16812,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H567" t="n">
         <v>124458</v>
@@ -16841,7 +16841,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G568" t="n">
-        <v>9.72022914886475</v>
+        <v>9.72022819519043</v>
       </c>
       <c r="H568" t="n">
         <v>102747</v>
@@ -16870,7 +16870,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H569" t="n">
         <v>170656</v>
@@ -16986,7 +16986,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H573" t="n">
         <v>121005</v>
@@ -17015,7 +17015,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H574" t="n">
         <v>114848</v>
@@ -17044,7 +17044,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818885803223</v>
+        <v>9.36818790435791</v>
       </c>
       <c r="H575" t="n">
         <v>94106</v>
@@ -17073,7 +17073,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G576" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H576" t="n">
         <v>88350</v>
@@ -17102,7 +17102,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G577" t="n">
-        <v>9.20194721221924</v>
+        <v>9.20194816589355</v>
       </c>
       <c r="H577" t="n">
         <v>140529</v>
@@ -17247,7 +17247,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12371635437012</v>
+        <v>9.1237154006958</v>
       </c>
       <c r="H582" t="n">
         <v>83347</v>
@@ -17276,7 +17276,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>8.95747375488281</v>
+        <v>8.95747470855713</v>
       </c>
       <c r="H583" t="n">
         <v>20537</v>
@@ -17305,7 +17305,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H584" t="n">
         <v>44575</v>
@@ -17363,7 +17363,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H586" t="n">
         <v>19894</v>
@@ -17392,7 +17392,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H587" t="n">
         <v>46974</v>
@@ -17479,7 +17479,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H590" t="n">
         <v>85332</v>
@@ -17653,7 +17653,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.98681163787842</v>
+        <v>8.9868106842041</v>
       </c>
       <c r="H596" t="n">
         <v>110779</v>
@@ -17682,7 +17682,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H597" t="n">
         <v>168521</v>
@@ -17740,7 +17740,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H599" t="n">
         <v>76971</v>
@@ -17769,7 +17769,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H600" t="n">
         <v>116918</v>
@@ -17798,7 +17798,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G601" t="n">
-        <v>9.72022914886475</v>
+        <v>9.72022819519043</v>
       </c>
       <c r="H601" t="n">
         <v>24832</v>
@@ -17856,7 +17856,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492362976074</v>
+        <v>9.95492267608643</v>
       </c>
       <c r="H603" t="n">
         <v>63044</v>
@@ -17885,7 +17885,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H604" t="n">
         <v>44561</v>
@@ -17943,7 +17943,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H606" t="n">
         <v>38965</v>
@@ -18001,7 +18001,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H608" t="n">
         <v>28857</v>
@@ -18030,7 +18030,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81801891326904</v>
+        <v>9.81801795959473</v>
       </c>
       <c r="H609" t="n">
         <v>8881</v>
@@ -18059,7 +18059,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H610" t="n">
         <v>26954</v>
@@ -18088,7 +18088,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H611" t="n">
         <v>15971</v>
@@ -18117,7 +18117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H612" t="n">
         <v>14746</v>
@@ -18146,7 +18146,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G613" t="n">
-        <v>9.34862995147705</v>
+        <v>9.34863090515137</v>
       </c>
       <c r="H613" t="n">
         <v>29288</v>
@@ -18175,7 +18175,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H614" t="n">
         <v>134678</v>
@@ -18233,7 +18233,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H616" t="n">
         <v>118933</v>
@@ -18378,7 +18378,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045017242432</v>
+        <v>9.71045112609863</v>
       </c>
       <c r="H621" t="n">
         <v>192357</v>
@@ -18494,7 +18494,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H625" t="n">
         <v>69374</v>
@@ -18552,7 +18552,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H627" t="n">
         <v>11623</v>
@@ -18610,7 +18610,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.5735445022583</v>
+        <v>9.57354545593262</v>
       </c>
       <c r="H629" t="n">
         <v>59629</v>
@@ -18668,7 +18668,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H631" t="n">
         <v>25208</v>
@@ -18697,7 +18697,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H632" t="n">
         <v>43105</v>
@@ -18842,7 +18842,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548454284668</v>
+        <v>9.04548358917236</v>
       </c>
       <c r="H637" t="n">
         <v>24740</v>
@@ -19016,7 +19016,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>9.28017807006836</v>
+        <v>9.28017902374268</v>
       </c>
       <c r="H643" t="n">
         <v>15942</v>
@@ -19045,7 +19045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>9.4366397857666</v>
+        <v>9.43664073944092</v>
       </c>
       <c r="H644" t="n">
         <v>5673</v>
@@ -19103,7 +19103,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62243938446045</v>
+        <v>9.62244033813477</v>
       </c>
       <c r="H646" t="n">
         <v>21998</v>
@@ -19132,7 +19132,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G647" t="n">
-        <v>9.64199829101562</v>
+        <v>9.64199733734131</v>
       </c>
       <c r="H647" t="n">
         <v>12149</v>
@@ -19190,7 +19190,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52464962005615</v>
+        <v>9.52465057373047</v>
       </c>
       <c r="H649" t="n">
         <v>25021</v>
@@ -19219,7 +19219,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376647949219</v>
+        <v>9.56376552581787</v>
       </c>
       <c r="H650" t="n">
         <v>28011</v>
@@ -19306,7 +19306,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H653" t="n">
         <v>40921</v>
@@ -19364,7 +19364,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G655" t="n">
-        <v>9.16283130645752</v>
+        <v>9.16283226013184</v>
       </c>
       <c r="H655" t="n">
         <v>14617</v>
@@ -19451,7 +19451,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437942504883</v>
+        <v>9.09437847137451</v>
       </c>
       <c r="H658" t="n">
         <v>4851</v>
@@ -19625,7 +19625,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G664" t="n">
-        <v>9.35840892791748</v>
+        <v>9.3584098815918</v>
       </c>
       <c r="H664" t="n">
         <v>8674</v>
@@ -19654,7 +19654,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G665" t="n">
-        <v>9.39752388000488</v>
+        <v>9.3975248336792</v>
       </c>
       <c r="H665" t="n">
         <v>4386</v>
@@ -19741,7 +19741,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.4268627166748</v>
+        <v>9.42686176300049</v>
       </c>
       <c r="H668" t="n">
         <v>15830</v>
@@ -19828,7 +19828,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G671" t="n">
-        <v>9.35840892791748</v>
+        <v>9.3584098815918</v>
       </c>
       <c r="H671" t="n">
         <v>9974</v>
@@ -19857,7 +19857,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>9.65177726745605</v>
+        <v>9.65177631378174</v>
       </c>
       <c r="H672" t="n">
         <v>48863</v>
@@ -19886,7 +19886,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G673" t="n">
-        <v>9.76912403106689</v>
+        <v>9.76912307739258</v>
       </c>
       <c r="H673" t="n">
         <v>49111</v>
@@ -19915,7 +19915,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846000671387</v>
+        <v>9.79846096038818</v>
       </c>
       <c r="H674" t="n">
         <v>18840</v>
@@ -19973,7 +19973,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934410095215</v>
+        <v>9.75934314727783</v>
       </c>
       <c r="H676" t="n">
         <v>9923</v>
@@ -20002,7 +20002,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H677" t="n">
         <v>7000</v>
@@ -20089,7 +20089,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G680" t="n">
-        <v>9.60288238525391</v>
+        <v>9.60288143157959</v>
       </c>
       <c r="H680" t="n">
         <v>7811</v>
@@ -20118,7 +20118,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310436248779</v>
+        <v>9.59310340881348</v>
       </c>
       <c r="H681" t="n">
         <v>7805</v>
@@ -20147,7 +20147,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956703186035</v>
       </c>
       <c r="H682" t="n">
         <v>32449</v>
@@ -20234,7 +20234,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G685" t="n">
-        <v>9.72022914886475</v>
+        <v>9.72022819519043</v>
       </c>
       <c r="H685" t="n">
         <v>86835</v>
@@ -20263,7 +20263,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>9.76912403106689</v>
+        <v>9.76912307739258</v>
       </c>
       <c r="H686" t="n">
         <v>19172</v>
@@ -20321,7 +20321,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G688" t="n">
-        <v>9.6713342666626</v>
+        <v>9.67133522033691</v>
       </c>
       <c r="H688" t="n">
         <v>38879</v>
@@ -20437,7 +20437,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H692" t="n">
         <v>28508</v>
@@ -20524,7 +20524,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713291168213</v>
+        <v>9.85713386535645</v>
       </c>
       <c r="H695" t="n">
         <v>15119</v>
@@ -20611,7 +20611,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H698" t="n">
         <v>21356</v>
@@ -20640,7 +20640,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155529022217</v>
+        <v>9.66155624389648</v>
       </c>
       <c r="H699" t="n">
         <v>21197</v>
@@ -20669,7 +20669,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332443237305</v>
+        <v>9.58332538604736</v>
       </c>
       <c r="H700" t="n">
         <v>27899</v>
@@ -20698,7 +20698,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G701" t="n">
-        <v>9.28017807006836</v>
+        <v>9.28017902374268</v>
       </c>
       <c r="H701" t="n">
         <v>43482</v>
@@ -20756,7 +20756,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172618865967</v>
+        <v>9.21172523498535</v>
       </c>
       <c r="H703" t="n">
         <v>10949</v>
@@ -20843,7 +20843,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H706" t="n">
         <v>17733</v>
@@ -20901,7 +20901,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>8.96725368499756</v>
+        <v>8.96725273132324</v>
       </c>
       <c r="H708" t="n">
         <v>75982</v>
@@ -20959,7 +20959,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H710" t="n">
         <v>140241</v>
@@ -21017,7 +21017,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560436248779</v>
+        <v>8.15560531616211</v>
       </c>
       <c r="H712" t="n">
         <v>38461</v>
@@ -21075,7 +21075,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G714" t="n">
-        <v>8.70322227478027</v>
+        <v>8.70322322845459</v>
       </c>
       <c r="H714" t="n">
         <v>94133</v>
@@ -21162,7 +21162,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G717" t="n">
-        <v>8.38051891326904</v>
+        <v>8.38051795959473</v>
       </c>
       <c r="H717" t="n">
         <v>28141</v>
@@ -21191,7 +21191,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626934051514</v>
+        <v>8.12626838684082</v>
       </c>
       <c r="H718" t="n">
         <v>75942</v>
@@ -21249,7 +21249,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742458343506</v>
+        <v>8.51742362976074</v>
       </c>
       <c r="H720" t="n">
         <v>40610</v>
@@ -21278,7 +21278,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G721" t="n">
-        <v>8.54676055908203</v>
+        <v>8.54675960540771</v>
       </c>
       <c r="H721" t="n">
         <v>58974</v>
@@ -21336,7 +21336,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.6347713470459</v>
+        <v>8.63477039337158</v>
       </c>
       <c r="H723" t="n">
         <v>20170</v>
@@ -21452,7 +21452,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G727" t="n">
-        <v>8.7716760635376</v>
+        <v>8.77167510986328</v>
       </c>
       <c r="H727" t="n">
         <v>143037</v>
@@ -21510,7 +21510,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946392059326</v>
+        <v>8.86946487426758</v>
       </c>
       <c r="H729" t="n">
         <v>24316</v>
@@ -21626,7 +21626,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G733" t="n">
-        <v>8.41963481903076</v>
+        <v>8.41963386535645</v>
       </c>
       <c r="H733" t="n">
         <v>27723</v>
@@ -21655,7 +21655,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G734" t="n">
-        <v>8.04803562164307</v>
+        <v>8.04803657531738</v>
       </c>
       <c r="H734" t="n">
         <v>59734</v>
@@ -21858,7 +21858,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>7.30484008789062</v>
+        <v>7.30483961105347</v>
       </c>
       <c r="H741" t="n">
         <v>13402</v>
@@ -21916,7 +21916,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H743" t="n">
         <v>14937</v>
@@ -21974,7 +21974,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G745" t="n">
-        <v>6.83545207977295</v>
+        <v>6.83545255661011</v>
       </c>
       <c r="H745" t="n">
         <v>110100</v>
@@ -22003,7 +22003,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385431289673</v>
+        <v>6.46385478973389</v>
       </c>
       <c r="H746" t="n">
         <v>68949</v>
@@ -22032,7 +22032,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>5.67176389694214</v>
+        <v>5.67176342010498</v>
       </c>
       <c r="H747" t="n">
         <v>105173</v>
@@ -22148,7 +22148,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.7134313583374</v>
+        <v>4.71343088150024</v>
       </c>
       <c r="H751" t="n">
         <v>210848</v>
@@ -22177,7 +22177,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760622024536</v>
+        <v>4.30760669708252</v>
       </c>
       <c r="H752" t="n">
         <v>95208</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10225009918213</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22235,7 +22235,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>4.67431497573853</v>
+        <v>4.67431545257568</v>
       </c>
       <c r="H754" t="n">
         <v>139728</v>
@@ -22293,7 +22293,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738567352295</v>
+        <v>4.31738519668579</v>
       </c>
       <c r="H756" t="n">
         <v>103537</v>
@@ -22351,7 +22351,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>3.90178227424622</v>
+        <v>3.90178203582764</v>
       </c>
       <c r="H758" t="n">
         <v>114123</v>
@@ -22409,7 +22409,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00934982299805</v>
+        <v>4.00935029983521</v>
       </c>
       <c r="H760" t="n">
         <v>97203</v>
@@ -22438,7 +22438,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156077384949</v>
+        <v>3.91156101226807</v>
       </c>
       <c r="H761" t="n">
         <v>208056</v>
@@ -22467,7 +22467,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.98001313209534</v>
+        <v>3.9800136089325</v>
       </c>
       <c r="H762" t="n">
         <v>31531</v>
@@ -22496,7 +22496,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669706344604</v>
+        <v>4.12669658660889</v>
       </c>
       <c r="H763" t="n">
         <v>41597</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10225009918213</v>
+        <v>4.10224962234497</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22554,7 +22554,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691761016846</v>
+        <v>4.11691808700562</v>
       </c>
       <c r="H765" t="n">
         <v>28600</v>
@@ -22583,7 +22583,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>4.35161113739014</v>
+        <v>4.35161161422729</v>
       </c>
       <c r="H766" t="n">
         <v>92230</v>
@@ -22612,7 +22612,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630561828613</v>
+        <v>4.58630514144897</v>
       </c>
       <c r="H767" t="n">
         <v>113983</v>
@@ -22641,7 +22641,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G768" t="n">
-        <v>4.8356671333313</v>
+        <v>4.83566761016846</v>
       </c>
       <c r="H768" t="n">
         <v>165631</v>
@@ -22699,7 +22699,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>5.07525062561035</v>
+        <v>5.07525014877319</v>
       </c>
       <c r="H770" t="n">
         <v>177286</v>
@@ -22786,7 +22786,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055662155151</v>
+        <v>4.84055614471436</v>
       </c>
       <c r="H773" t="n">
         <v>56598</v>
@@ -22960,7 +22960,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H779" t="n">
         <v>69616</v>
@@ -23047,7 +23047,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485870361328</v>
+        <v>5.53485822677612</v>
       </c>
       <c r="H782" t="n">
         <v>74521</v>
@@ -23076,7 +23076,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H783" t="n">
         <v>31901</v>
@@ -23105,7 +23105,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G784" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H784" t="n">
         <v>18450</v>
@@ -23134,7 +23134,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>5.40773296356201</v>
+        <v>5.40773344039917</v>
       </c>
       <c r="H785" t="n">
         <v>58953</v>
@@ -23163,7 +23163,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>5.33928060531616</v>
+        <v>5.33928108215332</v>
       </c>
       <c r="H786" t="n">
         <v>28269</v>
@@ -23192,7 +23192,7 @@
         <v>5.5</v>
       </c>
       <c r="G787" t="n">
-        <v>5.37839603424072</v>
+        <v>5.37839651107788</v>
       </c>
       <c r="H787" t="n">
         <v>18969</v>
@@ -23250,7 +23250,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H789" t="n">
         <v>33919</v>
@@ -23279,7 +23279,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.30016565322876</v>
+        <v>5.3001651763916</v>
       </c>
       <c r="H790" t="n">
         <v>36651</v>
@@ -23337,7 +23337,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G792" t="n">
-        <v>5.20237588882446</v>
+        <v>5.20237636566162</v>
       </c>
       <c r="H792" t="n">
         <v>22334</v>
@@ -23395,7 +23395,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G794" t="n">
-        <v>5.20237588882446</v>
+        <v>5.20237636566162</v>
       </c>
       <c r="H794" t="n">
         <v>45527</v>
@@ -23482,7 +23482,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H797" t="n">
         <v>11846</v>
@@ -23511,7 +23511,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>5.23171281814575</v>
+        <v>5.23171329498291</v>
       </c>
       <c r="H798" t="n">
         <v>3968</v>
@@ -23540,7 +23540,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H799" t="n">
         <v>12491</v>
@@ -23569,7 +23569,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G800" t="n">
-        <v>5.26104974746704</v>
+        <v>5.26104927062988</v>
       </c>
       <c r="H800" t="n">
         <v>42807</v>
@@ -23627,7 +23627,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G802" t="n">
-        <v>5.20237588882446</v>
+        <v>5.20237636566162</v>
       </c>
       <c r="H802" t="n">
         <v>6956</v>
@@ -23656,7 +23656,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>5.24149131774902</v>
+        <v>5.24149179458618</v>
       </c>
       <c r="H803" t="n">
         <v>20595</v>
@@ -23714,7 +23714,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>5.19259738922119</v>
+        <v>5.19259691238403</v>
       </c>
       <c r="H805" t="n">
         <v>18129</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.79166221618652</v>
+        <v>4.79166269302368</v>
       </c>
       <c r="H807" t="n">
         <v>76245</v>
@@ -23859,7 +23859,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H810" t="n">
         <v>46277</v>
@@ -23975,7 +23975,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>4.97746181488037</v>
+        <v>4.97746133804321</v>
       </c>
       <c r="H814" t="n">
         <v>26888</v>
@@ -24004,7 +24004,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>5.05569267272949</v>
+        <v>5.05569219589233</v>
       </c>
       <c r="H815" t="n">
         <v>6706</v>
@@ -24178,7 +24178,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>5.55441665649414</v>
+        <v>5.55441617965698</v>
       </c>
       <c r="H821" t="n">
         <v>85848</v>
@@ -24236,7 +24236,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>5.43706941604614</v>
+        <v>5.4370698928833</v>
       </c>
       <c r="H823" t="n">
         <v>49574</v>
@@ -24265,7 +24265,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>5.52507972717285</v>
+        <v>5.52508020401001</v>
       </c>
       <c r="H824" t="n">
         <v>33168</v>
@@ -24323,7 +24323,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G826" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H826" t="n">
         <v>18416</v>
@@ -24352,7 +24352,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.50552225112915</v>
+        <v>5.50552272796631</v>
       </c>
       <c r="H827" t="n">
         <v>27618</v>
@@ -24468,7 +24468,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G831" t="n">
-        <v>6.44429636001587</v>
+        <v>6.44429683685303</v>
       </c>
       <c r="H831" t="n">
         <v>252834</v>
@@ -24497,7 +24497,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>6.47363328933716</v>
+        <v>6.4736328125</v>
       </c>
       <c r="H832" t="n">
         <v>140160</v>
@@ -24526,7 +24526,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>6.19004487991333</v>
+        <v>6.19004535675049</v>
       </c>
       <c r="H833" t="n">
         <v>244592</v>
@@ -24584,7 +24584,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G835" t="n">
-        <v>6.06291961669922</v>
+        <v>6.06291913986206</v>
       </c>
       <c r="H835" t="n">
         <v>33914</v>
@@ -24613,7 +24613,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>6.05314016342163</v>
+        <v>6.05314111709595</v>
       </c>
       <c r="H836" t="n">
         <v>52635</v>
@@ -24787,7 +24787,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>6.4345178604126</v>
+        <v>6.43451738357544</v>
       </c>
       <c r="H842" t="n">
         <v>35606</v>
@@ -24874,7 +24874,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>6.09225606918335</v>
+        <v>6.09225654602051</v>
       </c>
       <c r="H845" t="n">
         <v>47625</v>
@@ -24932,7 +24932,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>6.41495990753174</v>
+        <v>6.41495943069458</v>
       </c>
       <c r="H847" t="n">
         <v>89877</v>
@@ -24990,7 +24990,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G849" t="n">
-        <v>6.18026638031006</v>
+        <v>6.1802659034729</v>
       </c>
       <c r="H849" t="n">
         <v>15790</v>
@@ -25077,7 +25077,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H852" t="n">
         <v>26701</v>
@@ -25251,7 +25251,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G858" t="n">
-        <v>5.75977373123169</v>
+        <v>5.75977325439453</v>
       </c>
       <c r="H858" t="n">
         <v>12990</v>
@@ -25280,7 +25280,7 @@
         <v>6</v>
       </c>
       <c r="G859" t="n">
-        <v>5.8673415184021</v>
+        <v>5.86734104156494</v>
       </c>
       <c r="H859" t="n">
         <v>45161</v>
@@ -25338,7 +25338,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H861" t="n">
         <v>15530</v>
@@ -25425,7 +25425,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>5.82822608947754</v>
+        <v>5.82822561264038</v>
       </c>
       <c r="H864" t="n">
         <v>48237</v>
@@ -25454,7 +25454,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>5.74021577835083</v>
+        <v>5.74021530151367</v>
       </c>
       <c r="H865" t="n">
         <v>27718</v>
@@ -25483,7 +25483,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>5.66198396682739</v>
+        <v>5.66198444366455</v>
       </c>
       <c r="H866" t="n">
         <v>71869</v>
@@ -25512,7 +25512,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>5.67176389694214</v>
+        <v>5.67176342010498</v>
       </c>
       <c r="H867" t="n">
         <v>13457</v>
@@ -25599,7 +25599,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H870" t="n">
         <v>22149</v>
@@ -25744,7 +25744,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G875" t="n">
-        <v>5.85756206512451</v>
+        <v>5.85756254196167</v>
       </c>
       <c r="H875" t="n">
         <v>10415</v>
@@ -25860,7 +25860,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>5.30994367599487</v>
+        <v>5.30994415283203</v>
       </c>
       <c r="H879" t="n">
         <v>76906</v>
@@ -26005,7 +26005,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>5.91623592376709</v>
+        <v>5.91623640060425</v>
       </c>
       <c r="H884" t="n">
         <v>30149</v>
@@ -26034,7 +26034,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>6.04336166381836</v>
+        <v>6.0433611869812</v>
       </c>
       <c r="H885" t="n">
         <v>23779</v>
@@ -26063,7 +26063,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>6.53230619430542</v>
+        <v>6.53230714797974</v>
       </c>
       <c r="H886" t="n">
         <v>143444</v>
@@ -26121,7 +26121,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>6.44429636001587</v>
+        <v>6.44429683685303</v>
       </c>
       <c r="H888" t="n">
         <v>92730</v>
@@ -26150,7 +26150,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>6.31717109680176</v>
+        <v>6.3171706199646</v>
       </c>
       <c r="H889" t="n">
         <v>65895</v>
@@ -26208,7 +26208,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>6.63987445831299</v>
+        <v>6.63987493515015</v>
       </c>
       <c r="H891" t="n">
         <v>52119</v>
@@ -26266,7 +26266,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G893" t="n">
-        <v>6.76700019836426</v>
+        <v>6.76700067520142</v>
       </c>
       <c r="H893" t="n">
         <v>47611</v>
@@ -26295,7 +26295,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G894" t="n">
-        <v>6.78655815124512</v>
+        <v>6.78655862808228</v>
       </c>
       <c r="H894" t="n">
         <v>16921</v>
@@ -26324,7 +26324,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>6.80611610412598</v>
+        <v>6.80611658096313</v>
       </c>
       <c r="H895" t="n">
         <v>40065</v>
@@ -26353,7 +26353,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G896" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H896" t="n">
         <v>155510</v>
@@ -26382,7 +26382,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G897" t="n">
-        <v>7.87201642990112</v>
+        <v>7.87201690673828</v>
       </c>
       <c r="H897" t="n">
         <v>235831</v>
@@ -26411,7 +26411,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H898" t="n">
         <v>68196</v>
@@ -26440,7 +26440,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>7.74489116668701</v>
+        <v>7.74489068984985</v>
       </c>
       <c r="H899" t="n">
         <v>112735</v>
@@ -26469,7 +26469,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G900" t="n">
-        <v>7.72533273696899</v>
+        <v>7.72533321380615</v>
       </c>
       <c r="H900" t="n">
         <v>24539</v>
@@ -26585,7 +26585,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G904" t="n">
-        <v>7.676438331604</v>
+        <v>7.67643785476685</v>
       </c>
       <c r="H904" t="n">
         <v>7737</v>
@@ -26614,7 +26614,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G905" t="n">
-        <v>7.73511171340942</v>
+        <v>7.73511123657227</v>
       </c>
       <c r="H905" t="n">
         <v>13300</v>
@@ -26788,7 +26788,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>7.01147270202637</v>
+        <v>7.01147317886353</v>
       </c>
       <c r="H911" t="n">
         <v>49184</v>
@@ -26875,7 +26875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G914" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H914" t="n">
         <v>40423</v>
@@ -27107,7 +27107,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>6.89412641525269</v>
+        <v>6.89412593841553</v>
       </c>
       <c r="H922" t="n">
         <v>17841</v>
@@ -27165,7 +27165,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G924" t="n">
-        <v>7.11904096603394</v>
+        <v>7.11904144287109</v>
       </c>
       <c r="H924" t="n">
         <v>41919</v>
@@ -27194,7 +27194,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>7.16793537139893</v>
+        <v>7.16793489456177</v>
       </c>
       <c r="H925" t="n">
         <v>17282</v>
@@ -27223,7 +27223,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G926" t="n">
-        <v>7.07992506027222</v>
+        <v>7.07992553710938</v>
       </c>
       <c r="H926" t="n">
         <v>23209</v>
@@ -27281,7 +27281,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>7.20705080032349</v>
+        <v>7.20705127716064</v>
       </c>
       <c r="H928" t="n">
         <v>40663</v>
@@ -27310,7 +27310,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G929" t="n">
-        <v>7.17771434783936</v>
+        <v>7.17771482467651</v>
       </c>
       <c r="H929" t="n">
         <v>53483</v>
@@ -27368,7 +27368,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G931" t="n">
-        <v>7.24616622924805</v>
+        <v>7.24616670608521</v>
       </c>
       <c r="H931" t="n">
         <v>52841</v>
@@ -27513,7 +27513,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>7.60798645019531</v>
+        <v>7.60798597335815</v>
       </c>
       <c r="H936" t="n">
         <v>10858</v>
@@ -27571,7 +27571,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G938" t="n">
-        <v>7.96002626419067</v>
+        <v>7.96002721786499</v>
       </c>
       <c r="H938" t="n">
         <v>165920</v>
@@ -27600,7 +27600,7 @@
         <v>8</v>
       </c>
       <c r="G939" t="n">
-        <v>7.82312154769897</v>
+        <v>7.82312202453613</v>
       </c>
       <c r="H939" t="n">
         <v>72321</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>8.03825855255127</v>
+        <v>8.03825759887695</v>
       </c>
       <c r="H940" t="n">
         <v>95905</v>
@@ -27658,7 +27658,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G941" t="n">
-        <v>8.41963481903076</v>
+        <v>8.41963386535645</v>
       </c>
       <c r="H941" t="n">
         <v>135022</v>
@@ -27687,7 +27687,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G942" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H942" t="n">
         <v>93859</v>
@@ -27716,7 +27716,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G943" t="n">
-        <v>8.54676055908203</v>
+        <v>8.54675960540771</v>
       </c>
       <c r="H943" t="n">
         <v>95249</v>
@@ -27803,7 +27803,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G946" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H946" t="n">
         <v>263636</v>
@@ -27832,7 +27832,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G947" t="n">
-        <v>9.4366397857666</v>
+        <v>9.43664073944092</v>
       </c>
       <c r="H947" t="n">
         <v>81693</v>
@@ -27861,7 +27861,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G948" t="n">
-        <v>9.11393642425537</v>
+        <v>9.11393737792969</v>
       </c>
       <c r="H948" t="n">
         <v>77374</v>
@@ -27890,7 +27890,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G949" t="n">
-        <v>9.68111324310303</v>
+        <v>9.68111228942871</v>
       </c>
       <c r="H949" t="n">
         <v>212562</v>
@@ -27919,7 +27919,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G950" t="n">
-        <v>9.73000812530518</v>
+        <v>9.73000717163086</v>
       </c>
       <c r="H950" t="n">
         <v>171303</v>
@@ -28035,7 +28035,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G954" t="n">
-        <v>8.81079196929932</v>
+        <v>8.810791015625</v>
       </c>
       <c r="H954" t="n">
         <v>75369</v>
@@ -28093,7 +28093,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G956" t="n">
-        <v>8.44897174835205</v>
+        <v>8.44897270202637</v>
       </c>
       <c r="H956" t="n">
         <v>40968</v>
@@ -28151,7 +28151,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G958" t="n">
-        <v>8.37074089050293</v>
+        <v>8.37074184417725</v>
       </c>
       <c r="H958" t="n">
         <v>44957</v>
@@ -28238,7 +28238,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G961" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H961" t="n">
         <v>93370</v>
@@ -28267,7 +28267,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G962" t="n">
-        <v>8.25339412689209</v>
+        <v>8.25339317321777</v>
       </c>
       <c r="H962" t="n">
         <v>76522</v>
@@ -28354,7 +28354,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G965" t="n">
-        <v>8.70322227478027</v>
+        <v>8.70322322845459</v>
       </c>
       <c r="H965" t="n">
         <v>55469</v>
@@ -28412,7 +28412,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G967" t="n">
-        <v>8.20450019836426</v>
+        <v>8.20449924468994</v>
       </c>
       <c r="H967" t="n">
         <v>42116</v>
@@ -28441,7 +28441,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G968" t="n">
-        <v>8.28273010253906</v>
+        <v>8.28273105621338</v>
       </c>
       <c r="H968" t="n">
         <v>21079</v>
@@ -28499,7 +28499,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G970" t="n">
-        <v>8.16538429260254</v>
+        <v>8.16538333892822</v>
       </c>
       <c r="H970" t="n">
         <v>54837</v>
@@ -28528,7 +28528,7 @@
         <v>8.25</v>
       </c>
       <c r="G971" t="n">
-        <v>8.06759548187256</v>
+        <v>8.06759452819824</v>
       </c>
       <c r="H971" t="n">
         <v>26338</v>
@@ -28557,7 +28557,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G972" t="n">
-        <v>8.17516136169434</v>
+        <v>8.17516231536865</v>
       </c>
       <c r="H972" t="n">
         <v>14608</v>
@@ -28586,7 +28586,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G973" t="n">
-        <v>9.07482051849365</v>
+        <v>9.07482147216797</v>
       </c>
       <c r="H973" t="n">
         <v>227616</v>
@@ -28673,7 +28673,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>9.24106216430664</v>
+        <v>9.24106311798096</v>
       </c>
       <c r="H976" t="n">
         <v>268935</v>
@@ -28702,7 +28702,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G977" t="n">
-        <v>9.74956512451172</v>
+        <v>9.74956703186035</v>
       </c>
       <c r="H977" t="n">
         <v>117145</v>
@@ -28760,7 +28760,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G979" t="n">
-        <v>10.6198873519897</v>
+        <v>10.6198883056641</v>
       </c>
       <c r="H979" t="n">
         <v>373643</v>
@@ -28789,7 +28789,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H980" t="n">
         <v>214809</v>
@@ -28847,7 +28847,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G982" t="n">
-        <v>11.4804315567017</v>
+        <v>11.4804306030273</v>
       </c>
       <c r="H982" t="n">
         <v>419644</v>
@@ -29021,7 +29021,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H988" t="n">
         <v>321229</v>
@@ -29079,7 +29079,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G990" t="n">
-        <v>12.9472665786743</v>
+        <v>12.947265625</v>
       </c>
       <c r="H990" t="n">
         <v>379890</v>
@@ -29108,7 +29108,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>13.5926742553711</v>
+        <v>13.5926733016968</v>
       </c>
       <c r="H991" t="n">
         <v>195792</v>
@@ -29137,7 +29137,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H992" t="n">
         <v>403792</v>
@@ -29224,7 +29224,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8639307022095</v>
+        <v>14.8639316558838</v>
       </c>
       <c r="H995" t="n">
         <v>248550</v>
@@ -29659,7 +29659,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.1258392333984</v>
+        <v>12.1258382797241</v>
       </c>
       <c r="H1010" t="n">
         <v>53968</v>
@@ -29688,7 +29688,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1011" t="n">
-        <v>12.0867233276367</v>
+        <v>12.0867223739624</v>
       </c>
       <c r="H1011" t="n">
         <v>47356</v>
@@ -29717,7 +29717,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>12.6343421936035</v>
+        <v>12.6343412399292</v>
       </c>
       <c r="H1012" t="n">
         <v>183097</v>
@@ -29804,7 +29804,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1015" t="n">
-        <v>12.2040700912476</v>
+        <v>12.2040691375732</v>
       </c>
       <c r="H1015" t="n">
         <v>54788</v>
@@ -29978,7 +29978,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1021" t="n">
         <v>151231</v>
@@ -30007,7 +30007,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.3384227752686</v>
+        <v>13.3384237289429</v>
       </c>
       <c r="H1022" t="n">
         <v>98883</v>
@@ -30036,7 +30036,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1023" t="n">
         <v>117635</v>
@@ -30065,7 +30065,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.2406339645386</v>
+        <v>13.2406330108643</v>
       </c>
       <c r="H1024" t="n">
         <v>111837</v>
@@ -30181,7 +30181,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1028" t="n">
-        <v>12.3605327606201</v>
+        <v>12.3605318069458</v>
       </c>
       <c r="H1028" t="n">
         <v>66190</v>
@@ -30210,7 +30210,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>12.2040700912476</v>
+        <v>12.2040691375732</v>
       </c>
       <c r="H1029" t="n">
         <v>174418</v>
@@ -30326,7 +30326,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>11.715124130249</v>
+        <v>11.7151250839233</v>
       </c>
       <c r="H1033" t="n">
         <v>119232</v>
@@ -30471,7 +30471,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1038" t="n">
-        <v>12.2040700912476</v>
+        <v>12.2040691375732</v>
       </c>
       <c r="H1038" t="n">
         <v>111924</v>
@@ -30587,7 +30587,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.1845121383667</v>
+        <v>12.184513092041</v>
       </c>
       <c r="H1042" t="n">
         <v>39400</v>
@@ -30616,7 +30616,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1043" t="n">
         <v>36180</v>
@@ -30703,7 +30703,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.3800897598267</v>
+        <v>12.380090713501</v>
       </c>
       <c r="H1046" t="n">
         <v>29868</v>
@@ -30732,7 +30732,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.3409757614136</v>
+        <v>12.3409748077393</v>
       </c>
       <c r="H1047" t="n">
         <v>46643</v>
@@ -30819,7 +30819,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>13.0450563430786</v>
+        <v>13.0450553894043</v>
       </c>
       <c r="H1050" t="n">
         <v>110815</v>
@@ -30848,7 +30848,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.279748916626</v>
+        <v>13.2797498703003</v>
       </c>
       <c r="H1051" t="n">
         <v>108427</v>
@@ -30906,7 +30906,7 @@
         <v>11</v>
       </c>
       <c r="G1053" t="n">
-        <v>10.7567920684814</v>
+        <v>10.7567930221558</v>
       </c>
       <c r="H1053" t="n">
         <v>195883</v>
@@ -30935,7 +30935,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>10.9719285964966</v>
+        <v>10.9719295501709</v>
       </c>
       <c r="H1054" t="n">
         <v>167159</v>
@@ -30993,7 +30993,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.6785612106323</v>
+        <v>10.6785621643066</v>
       </c>
       <c r="H1056" t="n">
         <v>93893</v>
@@ -31022,7 +31022,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1057" t="n">
-        <v>10.5416564941406</v>
+        <v>10.5416574478149</v>
       </c>
       <c r="H1057" t="n">
         <v>98409</v>
@@ -31080,7 +31080,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5220994949341</v>
+        <v>10.5220985412598</v>
       </c>
       <c r="H1059" t="n">
         <v>104597</v>
@@ -31138,7 +31138,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.1505012512207</v>
+        <v>10.1505002975464</v>
       </c>
       <c r="H1061" t="n">
         <v>77475</v>
@@ -31225,7 +31225,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1064" t="n">
-        <v>8.96725368499756</v>
+        <v>8.96725273132324</v>
       </c>
       <c r="H1064" t="n">
         <v>109713</v>
@@ -31283,7 +31283,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1066" t="n">
-        <v>8.32184600830078</v>
+        <v>8.3218469619751</v>
       </c>
       <c r="H1066" t="n">
         <v>93675</v>
@@ -31428,7 +31428,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1071" t="n">
-        <v>8.70322227478027</v>
+        <v>8.70322322845459</v>
       </c>
       <c r="H1071" t="n">
         <v>29010</v>
@@ -31486,7 +31486,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.81079196929932</v>
+        <v>8.810791015625</v>
       </c>
       <c r="H1073" t="n">
         <v>41885</v>
@@ -31544,7 +31544,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.17261123657227</v>
+        <v>9.17261028289795</v>
       </c>
       <c r="H1075" t="n">
         <v>127062</v>
@@ -31689,7 +31689,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.4047517776489</v>
+        <v>10.4047527313232</v>
       </c>
       <c r="H1080" t="n">
         <v>36974</v>
@@ -31718,7 +31718,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.3851947784424</v>
+        <v>10.3851938247681</v>
       </c>
       <c r="H1081" t="n">
         <v>25731</v>
@@ -31776,7 +31776,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.6003313064575</v>
+        <v>10.6003303527832</v>
       </c>
       <c r="H1083" t="n">
         <v>44357</v>
@@ -31863,7 +31863,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1086" t="n">
-        <v>11.6368932723999</v>
+        <v>11.6368942260742</v>
       </c>
       <c r="H1086" t="n">
         <v>318089</v>
@@ -31892,7 +31892,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1087" t="n">
-        <v>12.7321310043335</v>
+        <v>12.7321319580078</v>
       </c>
       <c r="H1087" t="n">
         <v>194830</v>
@@ -31979,7 +31979,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>13.1037282943726</v>
+        <v>13.1037292480469</v>
       </c>
       <c r="H1090" t="n">
         <v>153541</v>
@@ -32037,7 +32037,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.1428442001343</v>
+        <v>13.1428451538086</v>
       </c>
       <c r="H1092" t="n">
         <v>90633</v>
@@ -32153,7 +32153,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>13.7882528305054</v>
+        <v>13.7882518768311</v>
       </c>
       <c r="H1096" t="n">
         <v>93691</v>
@@ -32182,7 +32182,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1097" t="n">
-        <v>13.8078098297119</v>
+        <v>13.8078107833862</v>
       </c>
       <c r="H1097" t="n">
         <v>143314</v>
@@ -32240,7 +32240,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>13.8273687362671</v>
+        <v>13.8273677825928</v>
       </c>
       <c r="H1099" t="n">
         <v>108983</v>
@@ -32269,7 +32269,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1100" t="n">
-        <v>14.1402940750122</v>
+        <v>14.1402931213379</v>
       </c>
       <c r="H1100" t="n">
         <v>81068</v>
@@ -32298,7 +32298,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.2771978378296</v>
+        <v>14.2771987915039</v>
       </c>
       <c r="H1101" t="n">
         <v>57479</v>
@@ -32327,7 +32327,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>14.4532165527344</v>
+        <v>14.4532175064087</v>
       </c>
       <c r="H1102" t="n">
         <v>33492</v>
@@ -32385,7 +32385,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.3749866485596</v>
+        <v>14.3749856948853</v>
       </c>
       <c r="H1104" t="n">
         <v>36166</v>
@@ -32414,7 +32414,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.9030466079712</v>
+        <v>14.9030475616455</v>
       </c>
       <c r="H1105" t="n">
         <v>135713</v>
@@ -32588,7 +32588,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.6436920166016</v>
+        <v>16.6436939239502</v>
       </c>
       <c r="H1111" t="n">
         <v>320219</v>
@@ -32617,7 +32617,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1112" t="n">
-        <v>17.6802539825439</v>
+        <v>17.6802558898926</v>
       </c>
       <c r="H1112" t="n">
         <v>297169</v>
@@ -32675,7 +32675,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>19.1666488647461</v>
+        <v>19.1666507720947</v>
       </c>
       <c r="H1114" t="n">
         <v>462313</v>
@@ -32878,7 +32878,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>22.1981067657471</v>
+        <v>22.1981086730957</v>
       </c>
       <c r="H1121" t="n">
         <v>87185</v>
@@ -32907,7 +32907,7 @@
         <v>22.25</v>
       </c>
       <c r="G1122" t="n">
-        <v>21.7580585479736</v>
+        <v>21.758056640625</v>
       </c>
       <c r="H1122" t="n">
         <v>177161</v>
@@ -32965,7 +32965,7 @@
         <v>21.5</v>
       </c>
       <c r="G1124" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1124" t="n">
         <v>72589</v>
@@ -33023,7 +33023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1126" t="n">
         <v>169849</v>
@@ -33052,7 +33052,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1127" t="n">
         <v>153071</v>
@@ -33168,7 +33168,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>21.8558464050293</v>
+        <v>21.8558483123779</v>
       </c>
       <c r="H1131" t="n">
         <v>109080</v>
@@ -33197,7 +33197,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>21.660270690918</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1132" t="n">
         <v>103507</v>
@@ -33226,7 +33226,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>21.3669013977051</v>
+        <v>21.3669033050537</v>
       </c>
       <c r="H1133" t="n">
         <v>58754</v>
@@ -33255,7 +33255,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.660270690918</v>
+        <v>21.6602668762207</v>
       </c>
       <c r="H1134" t="n">
         <v>98501</v>
@@ -33371,7 +33371,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1138" t="n">
-        <v>21.3669013977051</v>
+        <v>21.3669033050537</v>
       </c>
       <c r="H1138" t="n">
         <v>29778</v>
@@ -33400,7 +33400,7 @@
         <v>21.5</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1139" t="n">
         <v>34560</v>
@@ -33458,7 +33458,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>20.9757461547852</v>
+        <v>20.9757480621338</v>
       </c>
       <c r="H1141" t="n">
         <v>56787</v>
@@ -33516,7 +33516,7 @@
         <v>21.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1143" t="n">
         <v>34032</v>
@@ -33545,7 +33545,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1144" t="n">
         <v>22284</v>
@@ -33574,7 +33574,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.1224308013916</v>
+        <v>21.122428894043</v>
       </c>
       <c r="H1145" t="n">
         <v>26612</v>
@@ -33632,7 +33632,7 @@
         <v>21.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1147" t="n">
         <v>58527</v>
@@ -33661,7 +33661,7 @@
         <v>21.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>20.7801685333252</v>
+        <v>20.7801666259766</v>
       </c>
       <c r="H1148" t="n">
         <v>26335</v>
@@ -33748,7 +33748,7 @@
         <v>20.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1151" t="n">
         <v>65290</v>
@@ -33806,7 +33806,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1153" t="n">
         <v>112291</v>
@@ -33835,7 +33835,7 @@
         <v>23.75</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.2248954772949</v>
+        <v>23.2248935699463</v>
       </c>
       <c r="H1154" t="n">
         <v>149423</v>
@@ -33864,7 +33864,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>25.2784633636475</v>
+        <v>25.2784614562988</v>
       </c>
       <c r="H1155" t="n">
         <v>130182</v>
@@ -34009,7 +34009,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.322681427002</v>
+        <v>23.3226833343506</v>
       </c>
       <c r="H1160" t="n">
         <v>31857</v>
@@ -34067,7 +34067,7 @@
         <v>23.25</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.7359466552734</v>
+        <v>22.7359504699707</v>
       </c>
       <c r="H1162" t="n">
         <v>32829</v>
@@ -34154,7 +34154,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>22.6381568908691</v>
+        <v>22.6381587982178</v>
       </c>
       <c r="H1165" t="n">
         <v>26738</v>
@@ -34183,7 +34183,7 @@
         <v>22.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1166" t="n">
         <v>72421</v>
@@ -34357,7 +34357,7 @@
         <v>22.75</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1172" t="n">
         <v>37810</v>
@@ -34386,7 +34386,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1173" t="n">
-        <v>22.4425830841064</v>
+        <v>22.4425811767578</v>
       </c>
       <c r="H1173" t="n">
         <v>39056</v>
@@ -34444,7 +34444,7 @@
         <v>22.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2470035552979</v>
+        <v>22.2470016479492</v>
       </c>
       <c r="H1175" t="n">
         <v>25765</v>
@@ -34473,7 +34473,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.5892658233643</v>
+        <v>22.5892639160156</v>
       </c>
       <c r="H1176" t="n">
         <v>56416</v>
@@ -34502,7 +34502,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.5403671264648</v>
+        <v>22.5403690338135</v>
       </c>
       <c r="H1177" t="n">
         <v>15746</v>
@@ -34618,7 +34618,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1181" t="n">
         <v>48003</v>
@@ -34676,7 +34676,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1183" t="n">
         <v>60552</v>
@@ -34705,7 +34705,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.4157943725586</v>
+        <v>21.4157962799072</v>
       </c>
       <c r="H1184" t="n">
         <v>21327</v>
@@ -34763,7 +34763,7 @@
         <v>22</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1186" t="n">
         <v>55489</v>
@@ -34792,7 +34792,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1187" t="n">
         <v>68839</v>
@@ -34821,7 +34821,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1188" t="n">
         <v>33357</v>
@@ -34850,7 +34850,7 @@
         <v>21.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1189" t="n">
         <v>47664</v>
@@ -34908,7 +34908,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>21.5624809265137</v>
+        <v>21.562479019165</v>
       </c>
       <c r="H1191" t="n">
         <v>39920</v>
@@ -34937,7 +34937,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>21.6113739013672</v>
+        <v>21.6113758087158</v>
       </c>
       <c r="H1192" t="n">
         <v>25913</v>
@@ -34995,7 +34995,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>21.2202205657959</v>
+        <v>21.2202186584473</v>
       </c>
       <c r="H1194" t="n">
         <v>28298</v>
@@ -35024,7 +35024,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1195" t="n">
         <v>52260</v>
@@ -35053,7 +35053,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>21.0735321044922</v>
+        <v>21.0735340118408</v>
       </c>
       <c r="H1196" t="n">
         <v>33762</v>
@@ -35082,7 +35082,7 @@
         <v>21.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1197" t="n">
         <v>53455</v>
@@ -35169,7 +35169,7 @@
         <v>21.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1200" t="n">
         <v>137704</v>
@@ -35198,7 +35198,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>22.6381568908691</v>
+        <v>22.6381587982178</v>
       </c>
       <c r="H1201" t="n">
         <v>116966</v>
@@ -35285,7 +35285,7 @@
         <v>22</v>
       </c>
       <c r="G1204" t="n">
-        <v>21.5135841369629</v>
+        <v>21.5135860443115</v>
       </c>
       <c r="H1204" t="n">
         <v>133530</v>
@@ -35372,7 +35372,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.926851272583</v>
+        <v>20.9268531799316</v>
       </c>
       <c r="H1207" t="n">
         <v>80989</v>
@@ -35401,7 +35401,7 @@
         <v>21.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.0246410369873</v>
+        <v>21.0246391296387</v>
       </c>
       <c r="H1208" t="n">
         <v>60298</v>
@@ -35575,7 +35575,7 @@
         <v>20.5</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.0467491149902</v>
+        <v>20.0467510223389</v>
       </c>
       <c r="H1214" t="n">
         <v>61113</v>
@@ -35604,7 +35604,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.8511714935303</v>
+        <v>19.8511695861816</v>
       </c>
       <c r="H1215" t="n">
         <v>97038</v>
@@ -35633,7 +35633,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1216" t="n">
-        <v>19.4404582977295</v>
+        <v>19.4404563903809</v>
       </c>
       <c r="H1216" t="n">
         <v>49228</v>
@@ -35691,7 +35691,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.9978580474854</v>
+        <v>19.9978542327881</v>
       </c>
       <c r="H1218" t="n">
         <v>80159</v>
@@ -35749,7 +35749,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>19.1470890045166</v>
+        <v>19.1470909118652</v>
       </c>
       <c r="H1220" t="n">
         <v>78205</v>
@@ -35807,7 +35807,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1222" t="n">
         <v>72053</v>
@@ -35923,7 +35923,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1226" t="n">
         <v>67839</v>
@@ -35952,7 +35952,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.7831478118896</v>
+        <v>15.783148765564</v>
       </c>
       <c r="H1227" t="n">
         <v>144180</v>
@@ -35981,7 +35981,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>16.3112087249756</v>
+        <v>16.3112106323242</v>
       </c>
       <c r="H1228" t="n">
         <v>66395</v>
@@ -36126,7 +36126,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.5824642181396</v>
+        <v>17.5824680328369</v>
       </c>
       <c r="H1233" t="n">
         <v>88571</v>
@@ -36155,7 +36155,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.0348491668701</v>
+        <v>17.0348472595215</v>
       </c>
       <c r="H1234" t="n">
         <v>86836</v>
@@ -36213,7 +36213,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1236" t="n">
         <v>105949</v>
@@ -36271,7 +36271,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.2304248809814</v>
+        <v>17.2304267883301</v>
       </c>
       <c r="H1238" t="n">
         <v>124533</v>
@@ -36387,7 +36387,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.4038944244385</v>
+        <v>18.4038963317871</v>
       </c>
       <c r="H1242" t="n">
         <v>230145</v>
@@ -36416,7 +36416,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1243" t="n">
-        <v>17.6411418914795</v>
+        <v>17.6411399841309</v>
       </c>
       <c r="H1243" t="n">
         <v>155083</v>
@@ -36503,7 +36503,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.8979434967041</v>
+        <v>16.8979454040527</v>
       </c>
       <c r="H1246" t="n">
         <v>89023</v>
@@ -36532,7 +36532,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.4676704406738</v>
+        <v>16.4676723480225</v>
       </c>
       <c r="H1247" t="n">
         <v>82416</v>
@@ -36619,7 +36619,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1250" t="n">
-        <v>16.6436920166016</v>
+        <v>16.6436939239502</v>
       </c>
       <c r="H1250" t="n">
         <v>43473</v>
@@ -36648,7 +36648,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.1521968841553</v>
+        <v>17.1521949768066</v>
       </c>
       <c r="H1251" t="n">
         <v>74074</v>
@@ -36706,7 +36706,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1253" t="n">
-        <v>16.8392696380615</v>
+        <v>16.8392677307129</v>
       </c>
       <c r="H1253" t="n">
         <v>21288</v>
@@ -36735,7 +36735,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.9761753082275</v>
+        <v>16.9761772155762</v>
       </c>
       <c r="H1254" t="n">
         <v>30692</v>
@@ -36851,7 +36851,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.7414817810059</v>
+        <v>16.7414836883545</v>
       </c>
       <c r="H1258" t="n">
         <v>87008</v>
@@ -36938,7 +36938,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>19.5948181152344</v>
+        <v>19.594820022583</v>
       </c>
       <c r="H1261" t="n">
         <v>421870</v>
@@ -36996,7 +36996,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6342849731445</v>
+        <v>19.6342830657959</v>
       </c>
       <c r="H1263" t="n">
         <v>110426</v>
@@ -37199,7 +37199,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1270" t="n">
         <v>151182</v>
@@ -37228,7 +37228,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1271" t="n">
         <v>144900</v>
@@ -37257,7 +37257,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.8542423248291</v>
+        <v>21.8542404174805</v>
       </c>
       <c r="H1272" t="n">
         <v>100072</v>
@@ -37431,7 +37431,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1278" t="n">
         <v>268613</v>
@@ -37605,7 +37605,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.5750846862793</v>
+        <v>19.5750865936279</v>
       </c>
       <c r="H1284" t="n">
         <v>112686</v>
@@ -37779,7 +37779,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>18.5687046051025</v>
+        <v>18.5687065124512</v>
       </c>
       <c r="H1290" t="n">
         <v>80819</v>
@@ -37866,7 +37866,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.3777561187744</v>
+        <v>19.3777542114258</v>
       </c>
       <c r="H1293" t="n">
         <v>96973</v>
@@ -37895,7 +37895,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1294" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1294" t="n">
         <v>80244</v>
@@ -37924,7 +37924,7 @@
         <v>19.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>19.2396240234375</v>
+        <v>19.2396259307861</v>
       </c>
       <c r="H1295" t="n">
         <v>270887</v>
@@ -37953,7 +37953,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.7132167816162</v>
+        <v>19.7132148742676</v>
       </c>
       <c r="H1296" t="n">
         <v>176673</v>
@@ -37982,7 +37982,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1297" t="n">
         <v>155909</v>
@@ -38040,7 +38040,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1299" t="n">
         <v>88312</v>
@@ -38069,7 +38069,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.5089130401611</v>
+        <v>21.5089149475098</v>
       </c>
       <c r="H1300" t="n">
         <v>61890</v>
@@ -38098,7 +38098,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3115863800049</v>
+        <v>21.3115844726562</v>
       </c>
       <c r="H1301" t="n">
         <v>220236</v>
@@ -38156,7 +38156,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>21.1635875701904</v>
+        <v>21.1635894775391</v>
       </c>
       <c r="H1303" t="n">
         <v>114500</v>
@@ -38214,7 +38214,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.8182601928711</v>
+        <v>20.8182621002197</v>
       </c>
       <c r="H1305" t="n">
         <v>89332</v>
@@ -38272,7 +38272,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1769428253174</v>
+        <v>20.1769409179688</v>
       </c>
       <c r="H1307" t="n">
         <v>216127</v>
@@ -38330,7 +38330,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.6737499237061</v>
+        <v>19.6737518310547</v>
       </c>
       <c r="H1309" t="n">
         <v>87050</v>
@@ -38359,7 +38359,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.2988243103027</v>
+        <v>19.2988224029541</v>
       </c>
       <c r="H1310" t="n">
         <v>41832</v>
@@ -38388,7 +38388,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.6145515441895</v>
+        <v>19.6145496368408</v>
       </c>
       <c r="H1311" t="n">
         <v>34200</v>
@@ -38591,7 +38591,7 @@
         <v>23.75</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.4328784942627</v>
+        <v>23.4328765869141</v>
       </c>
       <c r="H1318" t="n">
         <v>828551</v>
@@ -38649,7 +38649,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>22.2982311248779</v>
+        <v>22.2982330322266</v>
       </c>
       <c r="H1320" t="n">
         <v>98729</v>
@@ -38678,7 +38678,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>21.2622509002686</v>
+        <v>21.2622528076172</v>
       </c>
       <c r="H1321" t="n">
         <v>138690</v>
@@ -38939,7 +38939,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>22.8902225494385</v>
+        <v>22.8902206420898</v>
       </c>
       <c r="H1330" t="n">
         <v>103493</v>
@@ -39026,7 +39026,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1333" t="n">
         <v>102759</v>
@@ -39229,7 +39229,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1340" t="n">
-        <v>26.1856231689453</v>
+        <v>26.1856250762939</v>
       </c>
       <c r="H1340" t="n">
         <v>75983</v>
@@ -39490,7 +39490,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1349" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1349" t="n">
         <v>83400</v>
@@ -39548,7 +39548,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1351" t="n">
         <v>42477</v>
@@ -39635,7 +39635,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G1354" t="n">
-        <v>23.14674949646</v>
+        <v>23.1467475891113</v>
       </c>
       <c r="H1354" t="n">
         <v>32490</v>
@@ -39664,7 +39664,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.71262550354</v>
+        <v>22.7126235961914</v>
       </c>
       <c r="H1355" t="n">
         <v>83180</v>
@@ -39693,7 +39693,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.008617401123</v>
+        <v>23.0086193084717</v>
       </c>
       <c r="H1356" t="n">
         <v>67559</v>
@@ -39809,7 +39809,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1360" t="n">
         <v>218042</v>
@@ -39838,7 +39838,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1361" t="n">
-        <v>23.5216770172119</v>
+        <v>23.5216751098633</v>
       </c>
       <c r="H1361" t="n">
         <v>73675</v>
@@ -39954,7 +39954,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1365" t="n">
-        <v>24.6464538574219</v>
+        <v>24.6464519500732</v>
       </c>
       <c r="H1365" t="n">
         <v>92733</v>
@@ -40041,7 +40041,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1368" t="n">
         <v>59967</v>
@@ -40186,7 +40186,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1373" t="n">
-        <v>24.902982711792</v>
+        <v>24.9029808044434</v>
       </c>
       <c r="H1373" t="n">
         <v>125191</v>
@@ -40215,7 +40215,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>24.7648506164551</v>
+        <v>24.7648525238037</v>
       </c>
       <c r="H1374" t="n">
         <v>78394</v>
@@ -40244,7 +40244,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1375" t="n">
-        <v>24.4096565246582</v>
+        <v>24.4096584320068</v>
       </c>
       <c r="H1375" t="n">
         <v>68323</v>
@@ -40273,7 +40273,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1376" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1376" t="n">
         <v>54879</v>
@@ -40360,7 +40360,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1379" t="n">
-        <v>24.5675220489502</v>
+        <v>24.5675201416016</v>
       </c>
       <c r="H1379" t="n">
         <v>48881</v>
@@ -40389,7 +40389,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1380" t="n">
         <v>59300</v>
@@ -40476,7 +40476,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.2250900268555</v>
+        <v>26.2250881195068</v>
       </c>
       <c r="H1383" t="n">
         <v>131925</v>
@@ -40505,7 +40505,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1384" t="n">
-        <v>28.4351806640625</v>
+        <v>28.4351787567139</v>
       </c>
       <c r="H1384" t="n">
         <v>187997</v>
@@ -40708,7 +40708,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1391" t="n">
-        <v>24.5872535705566</v>
+        <v>24.5872554779053</v>
       </c>
       <c r="H1391" t="n">
         <v>74513</v>
@@ -40766,7 +40766,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1393" t="n">
-        <v>24.6267204284668</v>
+        <v>24.6267185211182</v>
       </c>
       <c r="H1393" t="n">
         <v>106208</v>
@@ -40795,7 +40795,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>24.6069869995117</v>
+        <v>24.6069889068604</v>
       </c>
       <c r="H1394" t="n">
         <v>64862</v>
@@ -40824,7 +40824,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>24.7253856658936</v>
+        <v>24.7253837585449</v>
       </c>
       <c r="H1395" t="n">
         <v>43250</v>
@@ -40882,7 +40882,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1397" t="n">
         <v>69714</v>
@@ -40911,7 +40911,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>24.4293899536133</v>
+        <v>24.4293918609619</v>
       </c>
       <c r="H1398" t="n">
         <v>26167</v>
@@ -40969,7 +40969,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>24.1531276702881</v>
+        <v>24.1531295776367</v>
       </c>
       <c r="H1400" t="n">
         <v>39041</v>
@@ -41143,7 +41143,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>24.4688568115234</v>
+        <v>24.4688549041748</v>
       </c>
       <c r="H1406" t="n">
         <v>48196</v>
@@ -41201,7 +41201,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1408" t="n">
-        <v>24.0544624328613</v>
+        <v>24.05446434021</v>
       </c>
       <c r="H1408" t="n">
         <v>26194</v>
@@ -41230,7 +41230,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1409" t="n">
         <v>183680</v>
@@ -41288,7 +41288,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3899250030518</v>
+        <v>24.3899230957031</v>
       </c>
       <c r="H1411" t="n">
         <v>56923</v>
@@ -41404,7 +41404,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.3307247161865</v>
+        <v>24.3307266235352</v>
       </c>
       <c r="H1415" t="n">
         <v>94778</v>
@@ -41636,7 +41636,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.3440799713135</v>
+        <v>23.3440780639648</v>
       </c>
       <c r="H1423" t="n">
         <v>50299</v>
@@ -41694,7 +41694,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1425" t="n">
         <v>19023</v>
@@ -41839,7 +41839,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.4230117797852</v>
+        <v>23.4230098724365</v>
       </c>
       <c r="H1430" t="n">
         <v>34199</v>
@@ -41897,7 +41897,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7387371063232</v>
+        <v>23.7387390136719</v>
       </c>
       <c r="H1432" t="n">
         <v>51446</v>
@@ -42042,7 +42042,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>24.6859188079834</v>
+        <v>24.685920715332</v>
       </c>
       <c r="H1437" t="n">
         <v>70358</v>
@@ -42129,7 +42129,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>26.3434867858887</v>
+        <v>26.3434886932373</v>
       </c>
       <c r="H1440" t="n">
         <v>93973</v>
@@ -42158,7 +42158,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.0341415405273</v>
+        <v>27.0341396331787</v>
       </c>
       <c r="H1441" t="n">
         <v>85164</v>
@@ -42216,7 +42216,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>28.4154453277588</v>
+        <v>28.4154472351074</v>
       </c>
       <c r="H1443" t="n">
         <v>195373</v>
@@ -42245,7 +42245,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>29.6980876922607</v>
+        <v>29.6980895996094</v>
       </c>
       <c r="H1444" t="n">
         <v>171716</v>
@@ -42303,7 +42303,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1446" t="n">
-        <v>29.7770195007324</v>
+        <v>29.7770214080811</v>
       </c>
       <c r="H1446" t="n">
         <v>87748</v>
@@ -42361,7 +42361,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1448" t="n">
-        <v>30.3295421600342</v>
+        <v>30.3295440673828</v>
       </c>
       <c r="H1448" t="n">
         <v>98329</v>
@@ -42535,7 +42535,7 @@
         <v>30.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>30.0927467346191</v>
+        <v>30.0927486419678</v>
       </c>
       <c r="H1454" t="n">
         <v>101035</v>
@@ -42622,7 +42622,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.4218254089355</v>
+        <v>29.4218273162842</v>
       </c>
       <c r="H1457" t="n">
         <v>72194</v>
@@ -42738,7 +42738,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1461" t="n">
         <v>75514</v>
@@ -42854,7 +42854,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G1465" t="n">
-        <v>35.8547668457031</v>
+        <v>35.8547706604004</v>
       </c>
       <c r="H1465" t="n">
         <v>359905</v>
@@ -42941,7 +42941,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>39.0712394714355</v>
+        <v>39.0712356567383</v>
       </c>
       <c r="H1468" t="n">
         <v>321164</v>
@@ -42970,7 +42970,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1469" t="n">
-        <v>36.2691612243652</v>
+        <v>36.269157409668</v>
       </c>
       <c r="H1469" t="n">
         <v>228974</v>
@@ -43028,7 +43028,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>40.3538856506348</v>
+        <v>40.3538818359375</v>
       </c>
       <c r="H1471" t="n">
         <v>311161</v>
@@ -43144,7 +43144,7 @@
         <v>42.6599998474121</v>
       </c>
       <c r="G1475" t="n">
-        <v>42.0903816223145</v>
+        <v>42.0903778076172</v>
       </c>
       <c r="H1475" t="n">
         <v>174798</v>
@@ -43173,7 +43173,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>42.2482452392578</v>
+        <v>42.2482414245605</v>
       </c>
       <c r="H1476" t="n">
         <v>109882</v>
@@ -43202,7 +43202,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1477" t="n">
-        <v>42.5837059020996</v>
+        <v>42.5837020874023</v>
       </c>
       <c r="H1477" t="n">
         <v>137662</v>
@@ -43231,7 +43231,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>43.0178260803223</v>
+        <v>43.0178298950195</v>
       </c>
       <c r="H1478" t="n">
         <v>116213</v>
@@ -43260,7 +43260,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>42.6231727600098</v>
+        <v>42.6231689453125</v>
       </c>
       <c r="H1479" t="n">
         <v>123515</v>
@@ -43289,7 +43289,7 @@
         <v>43</v>
       </c>
       <c r="G1480" t="n">
-        <v>42.4258422851562</v>
+        <v>42.425838470459</v>
       </c>
       <c r="H1480" t="n">
         <v>77199</v>
@@ -43376,7 +43376,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.2615928649902</v>
+        <v>41.2615966796875</v>
       </c>
       <c r="H1483" t="n">
         <v>55495</v>
@@ -43405,7 +43405,7 @@
         <v>42.6399993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.0706481933594</v>
+        <v>42.0706443786621</v>
       </c>
       <c r="H1484" t="n">
         <v>72975</v>
@@ -43637,7 +43637,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1492" t="n">
-        <v>45.5831146240234</v>
+        <v>45.5831108093262</v>
       </c>
       <c r="H1492" t="n">
         <v>178167</v>
@@ -43666,7 +43666,7 @@
         <v>38.4199981689453</v>
       </c>
       <c r="G1493" t="n">
-        <v>37.9069900512695</v>
+        <v>37.9069938659668</v>
       </c>
       <c r="H1493" t="n">
         <v>678570</v>
@@ -43724,7 +43724,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1495" t="n">
-        <v>32.6185684204102</v>
+        <v>32.6185646057129</v>
       </c>
       <c r="H1495" t="n">
         <v>546704</v>
@@ -43869,7 +43869,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1500" t="n">
-        <v>30.4676742553711</v>
+        <v>30.4676723480225</v>
       </c>
       <c r="H1500" t="n">
         <v>356068</v>
@@ -43927,7 +43927,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1502" t="n">
         <v>513447</v>
@@ -43985,7 +43985,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1504" t="n">
-        <v>31.0201950073242</v>
+        <v>31.0201969146729</v>
       </c>
       <c r="H1504" t="n">
         <v>237350</v>
@@ -44043,7 +44043,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>31.3951225280762</v>
+        <v>31.3951206207275</v>
       </c>
       <c r="H1506" t="n">
         <v>180598</v>
@@ -44101,7 +44101,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1508" t="n">
-        <v>30.9215297698975</v>
+        <v>30.9215316772461</v>
       </c>
       <c r="H1508" t="n">
         <v>287718</v>
@@ -80154,6 +80154,35 @@
         <v>7589</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>10.5799999237061</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>10.5799999237061</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>12283</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIB.MI.xlsx
+++ b/data/DIB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>6.84846591949463</v>
+        <v>6.84846544265747</v>
       </c>
       <c r="H2" t="n">
         <v>24440</v>
@@ -601,7 +601,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>6.06414413452148</v>
+        <v>6.0641450881958</v>
       </c>
       <c r="H8" t="n">
         <v>43060</v>
@@ -630,7 +630,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H9" t="n">
         <v>104780</v>
@@ -659,7 +659,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>6.33196115493774</v>
+        <v>6.3319616317749</v>
       </c>
       <c r="H10" t="n">
         <v>158687</v>
@@ -746,7 +746,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>5.71502590179443</v>
+        <v>5.71502542495728</v>
       </c>
       <c r="H13" t="n">
         <v>108547</v>
@@ -891,7 +891,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>6.02588510513306</v>
+        <v>6.0258846282959</v>
       </c>
       <c r="H18" t="n">
         <v>66351</v>
@@ -920,7 +920,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935041427612</v>
       </c>
       <c r="H19" t="n">
         <v>89617</v>
@@ -949,7 +949,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>6.00197219848633</v>
+        <v>6.00197172164917</v>
       </c>
       <c r="H20" t="n">
         <v>70672</v>
@@ -978,7 +978,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>5.94458341598511</v>
+        <v>5.94458293914795</v>
       </c>
       <c r="H21" t="n">
         <v>47413</v>
@@ -1094,7 +1094,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G25" t="n">
-        <v>5.79154491424561</v>
+        <v>5.79154396057129</v>
       </c>
       <c r="H25" t="n">
         <v>42499</v>
@@ -1123,7 +1123,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7006778717041</v>
+        <v>5.70067834854126</v>
       </c>
       <c r="H26" t="n">
         <v>83256</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.78244781494141</v>
+        <v>4.78244876861572</v>
       </c>
       <c r="H28" t="n">
         <v>130285</v>
@@ -1210,7 +1210,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>4.90679168701172</v>
+        <v>4.90679216384888</v>
       </c>
       <c r="H29" t="n">
         <v>118336</v>
@@ -1239,7 +1239,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.62940979003906</v>
+        <v>4.62941026687622</v>
       </c>
       <c r="H30" t="n">
         <v>67579</v>
@@ -1268,7 +1268,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>4.87331390380859</v>
+        <v>4.87331438064575</v>
       </c>
       <c r="H31" t="n">
         <v>39515</v>
@@ -1297,7 +1297,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>5.064612865448</v>
+        <v>5.06461238861084</v>
       </c>
       <c r="H32" t="n">
         <v>19857</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.8398380279541</v>
+        <v>4.83983755111694</v>
       </c>
       <c r="H33" t="n">
         <v>11060</v>
@@ -1355,7 +1355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>5.59546422958374</v>
+        <v>5.5954647064209</v>
       </c>
       <c r="H34" t="n">
         <v>87689</v>
@@ -1384,7 +1384,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>5.44242572784424</v>
+        <v>5.4424262046814</v>
       </c>
       <c r="H35" t="n">
         <v>178566</v>
@@ -1413,7 +1413,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>5.45677280426025</v>
+        <v>5.45677328109741</v>
       </c>
       <c r="H36" t="n">
         <v>102398</v>
@@ -1471,7 +1471,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.32286500930786</v>
+        <v>5.3228645324707</v>
       </c>
       <c r="H38" t="n">
         <v>45985</v>
@@ -1529,7 +1529,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>5.17460823059082</v>
+        <v>5.17460918426514</v>
       </c>
       <c r="H40" t="n">
         <v>27727</v>
@@ -1645,7 +1645,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73844957351685</v>
+        <v>4.738450050354</v>
       </c>
       <c r="H44" t="n">
         <v>146124</v>
@@ -1674,7 +1674,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G45" t="n">
-        <v>4.68297290802002</v>
+        <v>4.68297338485718</v>
       </c>
       <c r="H45" t="n">
         <v>133017</v>
@@ -1703,7 +1703,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>4.61028051376343</v>
+        <v>4.61028003692627</v>
       </c>
       <c r="H46" t="n">
         <v>40055</v>
@@ -1732,7 +1732,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G47" t="n">
-        <v>4.62749719619751</v>
+        <v>4.62749671936035</v>
       </c>
       <c r="H47" t="n">
         <v>92990</v>
@@ -1819,7 +1819,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G50" t="n">
-        <v>4.61984491348267</v>
+        <v>4.61984443664551</v>
       </c>
       <c r="H50" t="n">
         <v>32253</v>
@@ -1848,7 +1848,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G51" t="n">
-        <v>4.55671691894531</v>
+        <v>4.55671644210815</v>
       </c>
       <c r="H51" t="n">
         <v>33202</v>
@@ -1964,7 +1964,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G55" t="n">
-        <v>4.4228081703186</v>
+        <v>4.42280864715576</v>
       </c>
       <c r="H55" t="n">
         <v>73311</v>
@@ -2051,7 +2051,7 @@
         <v>4.59200000762939</v>
       </c>
       <c r="G58" t="n">
-        <v>4.3922004699707</v>
+        <v>4.39219999313354</v>
       </c>
       <c r="H58" t="n">
         <v>25581</v>
@@ -2080,7 +2080,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G59" t="n">
-        <v>4.23916292190552</v>
+        <v>4.2391619682312</v>
       </c>
       <c r="H59" t="n">
         <v>20035</v>
@@ -2109,7 +2109,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>4.09377574920654</v>
+        <v>4.0937762260437</v>
       </c>
       <c r="H60" t="n">
         <v>95284</v>
@@ -2167,7 +2167,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>4.39793920516968</v>
+        <v>4.39793968200684</v>
       </c>
       <c r="H62" t="n">
         <v>183307</v>
@@ -2225,7 +2225,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>4.46871995925903</v>
+        <v>4.46871948242188</v>
       </c>
       <c r="H64" t="n">
         <v>136790</v>
@@ -2254,7 +2254,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H65" t="n">
         <v>59895</v>
@@ -2283,7 +2283,7 @@
         <v>4.25</v>
       </c>
       <c r="G66" t="n">
-        <v>4.06508111953735</v>
+        <v>4.06508159637451</v>
       </c>
       <c r="H66" t="n">
         <v>69251</v>
@@ -2312,7 +2312,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94265055656433</v>
+        <v>3.94265103340149</v>
       </c>
       <c r="H67" t="n">
         <v>49492</v>
@@ -2341,7 +2341,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G68" t="n">
-        <v>3.71691870689392</v>
+        <v>3.71691846847534</v>
       </c>
       <c r="H68" t="n">
         <v>96719</v>
@@ -2370,7 +2370,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G69" t="n">
-        <v>3.79726386070251</v>
+        <v>3.79726409912109</v>
       </c>
       <c r="H69" t="n">
         <v>35741</v>
@@ -2399,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3.8259584903717</v>
+        <v>3.82595872879028</v>
       </c>
       <c r="H70" t="n">
         <v>33705</v>
@@ -2428,7 +2428,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G71" t="n">
-        <v>3.73987483978271</v>
+        <v>3.73987460136414</v>
       </c>
       <c r="H71" t="n">
         <v>26533</v>
@@ -2486,7 +2486,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>3.7781343460083</v>
+        <v>3.77813410758972</v>
       </c>
       <c r="H73" t="n">
         <v>13357</v>
@@ -2515,7 +2515,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G74" t="n">
-        <v>3.73222231864929</v>
+        <v>3.73222255706787</v>
       </c>
       <c r="H74" t="n">
         <v>23567</v>
@@ -2602,7 +2602,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G77" t="n">
-        <v>4.78723049163818</v>
+        <v>4.78723096847534</v>
       </c>
       <c r="H77" t="n">
         <v>182115</v>
@@ -2631,7 +2631,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.45199060440063</v>
+        <v>5.45199108123779</v>
       </c>
       <c r="H78" t="n">
         <v>472702</v>
@@ -2805,7 +2805,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G84" t="n">
-        <v>5.07417774200439</v>
+        <v>5.07417726516724</v>
       </c>
       <c r="H84" t="n">
         <v>122889</v>
@@ -2834,7 +2834,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>4.93548631668091</v>
+        <v>4.93548679351807</v>
       </c>
       <c r="H85" t="n">
         <v>71889</v>
@@ -2863,7 +2863,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>4.95461654663086</v>
+        <v>4.9546160697937</v>
       </c>
       <c r="H86" t="n">
         <v>66959</v>
@@ -2921,7 +2921,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>4.46680688858032</v>
+        <v>4.46680641174316</v>
       </c>
       <c r="H88" t="n">
         <v>98603</v>
@@ -3008,7 +3008,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>4.3615927696228</v>
+        <v>4.36159229278564</v>
       </c>
       <c r="H91" t="n">
         <v>78370</v>
@@ -3037,7 +3037,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G92" t="n">
-        <v>4.1855993270874</v>
+        <v>4.18559837341309</v>
       </c>
       <c r="H92" t="n">
         <v>40037</v>
@@ -3124,7 +3124,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G95" t="n">
-        <v>4.31376886367798</v>
+        <v>4.31376838684082</v>
       </c>
       <c r="H95" t="n">
         <v>42012</v>
@@ -3211,7 +3211,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G98" t="n">
-        <v>4.17603397369385</v>
+        <v>4.17603349685669</v>
       </c>
       <c r="H98" t="n">
         <v>54021</v>
@@ -3240,7 +3240,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>4.20472812652588</v>
+        <v>4.20472764968872</v>
       </c>
       <c r="H99" t="n">
         <v>30978</v>
@@ -3269,7 +3269,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29846429824829</v>
+        <v>4.29846477508545</v>
       </c>
       <c r="H100" t="n">
         <v>67373</v>
@@ -3298,7 +3298,7 @@
         <v>5.25</v>
       </c>
       <c r="G101" t="n">
-        <v>5.02157068252563</v>
+        <v>5.02157115936279</v>
       </c>
       <c r="H101" t="n">
         <v>322788</v>
@@ -3327,7 +3327,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>4.92113924026489</v>
+        <v>4.92113971710205</v>
       </c>
       <c r="H102" t="n">
         <v>328956</v>
@@ -3356,7 +3356,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G103" t="n">
-        <v>4.95939874649048</v>
+        <v>4.95939826965332</v>
       </c>
       <c r="H103" t="n">
         <v>129996</v>
@@ -3472,7 +3472,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.74756669998169</v>
+        <v>7.74756622314453</v>
       </c>
       <c r="H107" t="n">
         <v>830490</v>
@@ -3588,7 +3588,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>6.52804136276245</v>
+        <v>6.52804183959961</v>
       </c>
       <c r="H111" t="n">
         <v>199475</v>
@@ -3646,7 +3646,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.98237419128418</v>
+        <v>6.98237466812134</v>
       </c>
       <c r="H113" t="n">
         <v>407399</v>
@@ -3704,7 +3704,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G115" t="n">
-        <v>6.38456773757935</v>
+        <v>6.38456869125366</v>
       </c>
       <c r="H115" t="n">
         <v>131401</v>
@@ -3733,7 +3733,7 @@
         <v>6.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718311309814</v>
       </c>
       <c r="H116" t="n">
         <v>279195</v>
@@ -3762,7 +3762,7 @@
         <v>6.5</v>
       </c>
       <c r="G117" t="n">
-        <v>6.21718263626099</v>
+        <v>6.21718311309814</v>
       </c>
       <c r="H117" t="n">
         <v>281217</v>
@@ -3849,7 +3849,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>6.06414413452148</v>
+        <v>6.0641450881958</v>
       </c>
       <c r="H120" t="n">
         <v>187928</v>
@@ -3878,7 +3878,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>6.07370853424072</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H121" t="n">
         <v>194455</v>
@@ -3936,7 +3936,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>6.55195426940918</v>
+        <v>6.55195379257202</v>
       </c>
       <c r="H123" t="n">
         <v>388485</v>
@@ -3965,7 +3965,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G124" t="n">
-        <v>6.0689263343811</v>
+        <v>6.06892681121826</v>
       </c>
       <c r="H124" t="n">
         <v>130995</v>
@@ -4110,7 +4110,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H129" t="n">
         <v>59634</v>
@@ -4139,7 +4139,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>6.3510913848877</v>
+        <v>6.35109090805054</v>
       </c>
       <c r="H130" t="n">
         <v>59773</v>
@@ -4168,7 +4168,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>6.38935089111328</v>
+        <v>6.38935041427612</v>
       </c>
       <c r="H131" t="n">
         <v>52660</v>
@@ -4197,7 +4197,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>6.07370853424072</v>
+        <v>6.07370901107788</v>
       </c>
       <c r="H132" t="n">
         <v>115535</v>
@@ -4313,7 +4313,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>7.16888999938965</v>
+        <v>7.16888952255249</v>
       </c>
       <c r="H136" t="n">
         <v>187338</v>
@@ -4458,7 +4458,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>6.95846223831177</v>
+        <v>6.95846176147461</v>
       </c>
       <c r="H141" t="n">
         <v>66133</v>
@@ -4487,7 +4487,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>6.9967212677002</v>
+        <v>6.99672174453735</v>
       </c>
       <c r="H142" t="n">
         <v>66130</v>
@@ -4516,7 +4516,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H143" t="n">
         <v>31912</v>
@@ -4545,7 +4545,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H144" t="n">
         <v>21903</v>
@@ -4574,7 +4574,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>6.88672494888306</v>
+        <v>6.88672542572021</v>
       </c>
       <c r="H145" t="n">
         <v>55058</v>
@@ -4661,7 +4661,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75281715393066</v>
+        <v>6.75281667709351</v>
       </c>
       <c r="H148" t="n">
         <v>55331</v>
@@ -4690,7 +4690,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87237787246704</v>
+        <v>6.8723783493042</v>
       </c>
       <c r="H149" t="n">
         <v>71959</v>
@@ -4777,7 +4777,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>6.95367908477783</v>
+        <v>6.95367956161499</v>
       </c>
       <c r="H152" t="n">
         <v>61634</v>
@@ -4893,7 +4893,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.33627557754517</v>
+        <v>7.33627605438232</v>
       </c>
       <c r="H156" t="n">
         <v>116091</v>
@@ -4922,7 +4922,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>7.93886375427246</v>
+        <v>7.93886518478394</v>
       </c>
       <c r="H157" t="n">
         <v>265495</v>
@@ -4980,7 +4980,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>7.86712789535522</v>
+        <v>7.86712694168091</v>
       </c>
       <c r="H159" t="n">
         <v>93100</v>
@@ -5067,7 +5067,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G162" t="n">
-        <v>7.66626405715942</v>
+        <v>7.66626501083374</v>
       </c>
       <c r="H162" t="n">
         <v>71695</v>
@@ -5096,7 +5096,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>7.8432149887085</v>
+        <v>7.84321594238281</v>
       </c>
       <c r="H163" t="n">
         <v>118168</v>
@@ -5125,7 +5125,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G164" t="n">
-        <v>7.86234521865845</v>
+        <v>7.86234474182129</v>
       </c>
       <c r="H164" t="n">
         <v>30398</v>
@@ -5154,7 +5154,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>7.77626085281372</v>
+        <v>7.7762598991394</v>
       </c>
       <c r="H165" t="n">
         <v>36369</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>7.99625396728516</v>
+        <v>7.996253490448</v>
       </c>
       <c r="H166" t="n">
         <v>48102</v>
@@ -5212,7 +5212,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97712421417236</v>
+        <v>7.97712326049805</v>
       </c>
       <c r="H167" t="n">
         <v>31192</v>
@@ -5241,7 +5241,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>8.03451156616211</v>
+        <v>8.03451251983643</v>
       </c>
       <c r="H168" t="n">
         <v>39269</v>
@@ -5270,7 +5270,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G169" t="n">
-        <v>7.90060520172119</v>
+        <v>7.90060472488403</v>
       </c>
       <c r="H169" t="n">
         <v>42906</v>
@@ -5299,7 +5299,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>7.83364963531494</v>
+        <v>7.8336501121521</v>
       </c>
       <c r="H170" t="n">
         <v>41230</v>
@@ -5328,7 +5328,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.76669597625732</v>
+        <v>7.76669549942017</v>
       </c>
       <c r="H171" t="n">
         <v>80513</v>
@@ -5386,7 +5386,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>7.8958215713501</v>
+        <v>7.89582204818726</v>
       </c>
       <c r="H173" t="n">
         <v>38551</v>
@@ -5444,7 +5444,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>8.68492603302002</v>
+        <v>8.68492698669434</v>
       </c>
       <c r="H175" t="n">
         <v>251570</v>
@@ -5473,7 +5473,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>9.00534915924072</v>
+        <v>9.00535011291504</v>
       </c>
       <c r="H176" t="n">
         <v>166097</v>
@@ -5502,7 +5502,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>8.76622772216797</v>
+        <v>8.76622676849365</v>
       </c>
       <c r="H177" t="n">
         <v>231642</v>
@@ -5531,7 +5531,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>8.65623092651367</v>
+        <v>8.65623188018799</v>
       </c>
       <c r="H178" t="n">
         <v>104419</v>
@@ -5589,7 +5589,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.17798519134521</v>
+        <v>8.17798614501953</v>
       </c>
       <c r="H180" t="n">
         <v>197433</v>
@@ -5618,7 +5618,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.41710948944092</v>
+        <v>8.4171085357666</v>
       </c>
       <c r="H181" t="n">
         <v>154982</v>
@@ -5676,7 +5676,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>8.20668125152588</v>
+        <v>8.20668029785156</v>
       </c>
       <c r="H183" t="n">
         <v>59457</v>
@@ -5734,7 +5734,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>7.9245171546936</v>
+        <v>7.92451572418213</v>
       </c>
       <c r="H185" t="n">
         <v>122464</v>
@@ -5763,7 +5763,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.22581195831299</v>
+        <v>8.22581100463867</v>
       </c>
       <c r="H186" t="n">
         <v>99183</v>
@@ -5792,7 +5792,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G187" t="n">
-        <v>8.34058952331543</v>
+        <v>8.34059047698975</v>
       </c>
       <c r="H187" t="n">
         <v>63159</v>
@@ -5879,7 +5879,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G190" t="n">
-        <v>8.27363586425781</v>
+        <v>8.2736349105835</v>
       </c>
       <c r="H190" t="n">
         <v>51064</v>
@@ -6053,7 +6053,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G196" t="n">
-        <v>9.10578155517578</v>
+        <v>9.1057825088501</v>
       </c>
       <c r="H196" t="n">
         <v>198688</v>
@@ -6082,7 +6082,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>9.23968982696533</v>
+        <v>9.23968887329102</v>
       </c>
       <c r="H197" t="n">
         <v>111328</v>
@@ -6169,7 +6169,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>9.03882694244385</v>
+        <v>9.03882598876953</v>
       </c>
       <c r="H200" t="n">
         <v>84914</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>9.13447666168213</v>
+        <v>9.13447570800781</v>
       </c>
       <c r="H201" t="n">
         <v>49199</v>
@@ -6227,7 +6227,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>9.1727352142334</v>
+        <v>9.17273616790771</v>
       </c>
       <c r="H202" t="n">
         <v>47674</v>
@@ -6256,7 +6256,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>9.41185760498047</v>
+        <v>9.41185855865479</v>
       </c>
       <c r="H203" t="n">
         <v>115834</v>
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H204" t="n">
         <v>155270</v>
@@ -6343,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H206" t="n">
         <v>54350</v>
@@ -6372,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>9.56489562988281</v>
+        <v>9.56489753723145</v>
       </c>
       <c r="H207" t="n">
         <v>27951</v>
@@ -6401,7 +6401,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G208" t="n">
-        <v>9.5362024307251</v>
+        <v>9.53620147705078</v>
       </c>
       <c r="H208" t="n">
         <v>78401</v>
@@ -6488,7 +6488,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G211" t="n">
-        <v>10.2535705566406</v>
+        <v>10.2535696029663</v>
       </c>
       <c r="H211" t="n">
         <v>105355</v>
@@ -6546,7 +6546,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>11.1813640594482</v>
+        <v>11.1813631057739</v>
       </c>
       <c r="H213" t="n">
         <v>187510</v>
@@ -6575,7 +6575,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1813640594482</v>
+        <v>11.1813631057739</v>
       </c>
       <c r="H214" t="n">
         <v>181372</v>
@@ -6604,7 +6604,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2004928588867</v>
+        <v>11.200493812561</v>
       </c>
       <c r="H215" t="n">
         <v>33710</v>
@@ -6633,7 +6633,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.9518051147461</v>
+        <v>10.9518060684204</v>
       </c>
       <c r="H216" t="n">
         <v>101398</v>
@@ -6662,7 +6662,7 @@
         <v>10.5</v>
       </c>
       <c r="G217" t="n">
-        <v>10.0431413650513</v>
+        <v>10.0431423187256</v>
       </c>
       <c r="H217" t="n">
         <v>175009</v>
@@ -6691,7 +6691,7 @@
         <v>10.5</v>
       </c>
       <c r="G218" t="n">
-        <v>10.0431413650513</v>
+        <v>10.0431423187256</v>
       </c>
       <c r="H218" t="n">
         <v>270935</v>
@@ -6720,7 +6720,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G219" t="n">
-        <v>10.4831256866455</v>
+        <v>10.4831266403198</v>
       </c>
       <c r="H219" t="n">
         <v>128669</v>
@@ -6749,7 +6749,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>10.5692100524902</v>
+        <v>10.5692110061646</v>
       </c>
       <c r="H220" t="n">
         <v>43079</v>
@@ -6778,7 +6778,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8274612426758</v>
+        <v>10.8274621963501</v>
       </c>
       <c r="H221" t="n">
         <v>165457</v>
@@ -6807,7 +6807,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G222" t="n">
-        <v>10.837028503418</v>
+        <v>10.8370265960693</v>
       </c>
       <c r="H222" t="n">
         <v>98298</v>
@@ -6894,7 +6894,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G225" t="n">
-        <v>11.3630962371826</v>
+        <v>11.3630971908569</v>
       </c>
       <c r="H225" t="n">
         <v>187509</v>
@@ -6923,7 +6923,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6117839813232</v>
+        <v>11.6117849349976</v>
       </c>
       <c r="H226" t="n">
         <v>191398</v>
@@ -7213,7 +7213,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.1474170684814</v>
+        <v>12.1474180221558</v>
       </c>
       <c r="H236" t="n">
         <v>111282</v>
@@ -7242,7 +7242,7 @@
         <v>12.25</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7169971466064</v>
+        <v>11.7169990539551</v>
       </c>
       <c r="H237" t="n">
         <v>107537</v>
@@ -7271,7 +7271,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7839527130127</v>
+        <v>11.7839508056641</v>
       </c>
       <c r="H238" t="n">
         <v>75176</v>
@@ -7300,7 +7300,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G239" t="n">
-        <v>12.4247999191284</v>
+        <v>12.4248008728027</v>
       </c>
       <c r="H239" t="n">
         <v>134820</v>
@@ -7329,7 +7329,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G240" t="n">
-        <v>12.6160974502563</v>
+        <v>12.6160984039307</v>
       </c>
       <c r="H240" t="n">
         <v>180021</v>
@@ -7387,7 +7387,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>13.3717231750488</v>
+        <v>13.3717260360718</v>
       </c>
       <c r="H242" t="n">
         <v>100896</v>
@@ -7416,7 +7416,7 @@
         <v>15</v>
       </c>
       <c r="G243" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473434448242</v>
       </c>
       <c r="H243" t="n">
         <v>303111</v>
@@ -7445,7 +7445,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>15.2446575164795</v>
+        <v>15.2446565628052</v>
       </c>
       <c r="H244" t="n">
         <v>256881</v>
@@ -7561,7 +7561,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G248" t="n">
-        <v>13.3728446960449</v>
+        <v>13.3728437423706</v>
       </c>
       <c r="H248" t="n">
         <v>127762</v>
@@ -7590,7 +7590,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5272216796875</v>
+        <v>13.5272207260132</v>
       </c>
       <c r="H249" t="n">
         <v>82424</v>
@@ -7619,7 +7619,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G250" t="n">
-        <v>13.430736541748</v>
+        <v>13.4307346343994</v>
       </c>
       <c r="H250" t="n">
         <v>48278</v>
@@ -7822,7 +7822,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H257" t="n">
         <v>36672</v>
@@ -7880,7 +7880,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H259" t="n">
         <v>124706</v>
@@ -7909,7 +7909,7 @@
         <v>13.5</v>
       </c>
       <c r="G260" t="n">
-        <v>13.0254983901978</v>
+        <v>13.0254974365234</v>
       </c>
       <c r="H260" t="n">
         <v>62786</v>
@@ -7996,7 +7996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H263" t="n">
         <v>90090</v>
@@ -8083,7 +8083,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>13.7973794937134</v>
+        <v>13.7973804473877</v>
       </c>
       <c r="H266" t="n">
         <v>74231</v>
@@ -8228,7 +8228,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H271" t="n">
         <v>92437</v>
@@ -8257,7 +8257,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H272" t="n">
         <v>43627</v>
@@ -8344,7 +8344,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>11.8869724273682</v>
+        <v>11.8869733810425</v>
       </c>
       <c r="H275" t="n">
         <v>94457</v>
@@ -8431,7 +8431,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G278" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H278" t="n">
         <v>152414</v>
@@ -8489,7 +8489,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G280" t="n">
-        <v>11.665057182312</v>
+        <v>11.6650581359863</v>
       </c>
       <c r="H280" t="n">
         <v>34289</v>
@@ -8518,7 +8518,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5975179672241</v>
+        <v>11.5975170135498</v>
       </c>
       <c r="H281" t="n">
         <v>40964</v>
@@ -8605,7 +8605,7 @@
         <v>11.75</v>
       </c>
       <c r="G284" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H284" t="n">
         <v>114241</v>
@@ -8750,7 +8750,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G289" t="n">
-        <v>11.4431409835815</v>
+        <v>11.4431400299072</v>
       </c>
       <c r="H289" t="n">
         <v>181496</v>
@@ -8779,7 +8779,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>11.2501707077026</v>
+        <v>11.250171661377</v>
       </c>
       <c r="H290" t="n">
         <v>53729</v>
@@ -8808,7 +8808,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H291" t="n">
         <v>17482</v>
@@ -8837,7 +8837,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>10.8738784790039</v>
+        <v>10.8738794326782</v>
       </c>
       <c r="H292" t="n">
         <v>53600</v>
@@ -8924,7 +8924,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G295" t="n">
-        <v>10.8449325561523</v>
+        <v>10.8449335098267</v>
       </c>
       <c r="H295" t="n">
         <v>23068</v>
@@ -8982,7 +8982,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1695365905762</v>
+        <v>10.1695375442505</v>
       </c>
       <c r="H297" t="n">
         <v>66319</v>
@@ -9011,7 +9011,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G298" t="n">
-        <v>11.1247406005859</v>
+        <v>11.1247396469116</v>
       </c>
       <c r="H298" t="n">
         <v>108006</v>
@@ -9040,7 +9040,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>10.9124736785889</v>
+        <v>10.9124727249146</v>
       </c>
       <c r="H299" t="n">
         <v>173611</v>
@@ -9069,7 +9069,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G300" t="n">
-        <v>11.5685720443726</v>
+        <v>11.5685729980469</v>
       </c>
       <c r="H300" t="n">
         <v>224596</v>
@@ -9098,7 +9098,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H301" t="n">
         <v>68761</v>
@@ -9272,7 +9272,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G307" t="n">
-        <v>11.587869644165</v>
+        <v>11.5878686904907</v>
       </c>
       <c r="H307" t="n">
         <v>49320</v>
@@ -9301,7 +9301,7 @@
         <v>11.75</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3370065689087</v>
+        <v>11.337007522583</v>
       </c>
       <c r="H308" t="n">
         <v>79684</v>
@@ -9330,7 +9330,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>11.2598190307617</v>
+        <v>11.259819984436</v>
       </c>
       <c r="H309" t="n">
         <v>85197</v>
@@ -9359,7 +9359,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>11.1922807693481</v>
+        <v>11.1922798156738</v>
       </c>
       <c r="H310" t="n">
         <v>41614</v>
@@ -9388,7 +9388,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>11.2212247848511</v>
+        <v>11.2212257385254</v>
       </c>
       <c r="H311" t="n">
         <v>48985</v>
@@ -9446,7 +9446,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>11.5975179672241</v>
+        <v>11.5975170135498</v>
       </c>
       <c r="H313" t="n">
         <v>101331</v>
@@ -9533,7 +9533,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H316" t="n">
         <v>113990</v>
@@ -9562,7 +9562,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G317" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H317" t="n">
         <v>48953</v>
@@ -9736,7 +9736,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.8387317657471</v>
+        <v>11.8387308120728</v>
       </c>
       <c r="H323" t="n">
         <v>88601</v>
@@ -9794,7 +9794,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G325" t="n">
-        <v>13.0640926361084</v>
+        <v>13.0640916824341</v>
       </c>
       <c r="H325" t="n">
         <v>437770</v>
@@ -9852,7 +9852,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G327" t="n">
-        <v>13.6140584945679</v>
+        <v>13.6140565872192</v>
       </c>
       <c r="H327" t="n">
         <v>135660</v>
@@ -9968,7 +9968,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H331" t="n">
         <v>127592</v>
@@ -9997,7 +9997,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G332" t="n">
-        <v>13.430736541748</v>
+        <v>13.4307346343994</v>
       </c>
       <c r="H332" t="n">
         <v>75116</v>
@@ -10026,7 +10026,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>13.4886255264282</v>
+        <v>13.4886274337769</v>
       </c>
       <c r="H333" t="n">
         <v>19569</v>
@@ -10055,7 +10055,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G334" t="n">
-        <v>13.7105417251587</v>
+        <v>13.710542678833</v>
       </c>
       <c r="H334" t="n">
         <v>74737</v>
@@ -10142,7 +10142,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>13.8552694320679</v>
+        <v>13.8552703857422</v>
       </c>
       <c r="H337" t="n">
         <v>35661</v>
@@ -10229,7 +10229,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G340" t="n">
-        <v>13.9807014465332</v>
+        <v>13.9807004928589</v>
       </c>
       <c r="H340" t="n">
         <v>101573</v>
@@ -10345,7 +10345,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G344" t="n">
-        <v>14.3473453521729</v>
+        <v>14.3473443984985</v>
       </c>
       <c r="H344" t="n">
         <v>84729</v>
@@ -10490,7 +10490,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G349" t="n">
-        <v>14.4052362442017</v>
+        <v>14.405237197876</v>
       </c>
       <c r="H349" t="n">
         <v>73630</v>
@@ -10606,7 +10606,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>12.5527200698853</v>
+        <v>12.5527210235596</v>
       </c>
       <c r="H353" t="n">
         <v>295065</v>
@@ -10693,7 +10693,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G356" t="n">
-        <v>12.9000673294067</v>
+        <v>12.9000682830811</v>
       </c>
       <c r="H356" t="n">
         <v>42754</v>
@@ -10751,7 +10751,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>13.006199836731</v>
+        <v>13.0062007904053</v>
       </c>
       <c r="H358" t="n">
         <v>44368</v>
@@ -10780,7 +10780,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447950363159</v>
       </c>
       <c r="H359" t="n">
         <v>27096</v>
@@ -10809,7 +10809,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H360" t="n">
         <v>18254</v>
@@ -10838,7 +10838,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H361" t="n">
         <v>30895</v>
@@ -10896,7 +10896,7 @@
         <v>13.25</v>
       </c>
       <c r="G363" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H363" t="n">
         <v>24673</v>
@@ -10925,7 +10925,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1316318511963</v>
+        <v>13.131630897522</v>
       </c>
       <c r="H364" t="n">
         <v>31128</v>
@@ -10954,7 +10954,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G365" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H365" t="n">
         <v>55168</v>
@@ -11012,7 +11012,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7360420227051</v>
+        <v>12.7360429763794</v>
       </c>
       <c r="H367" t="n">
         <v>41635</v>
@@ -11070,7 +11070,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>12.6202592849731</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H369" t="n">
         <v>33590</v>
@@ -11128,7 +11128,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>12.4755325317383</v>
+        <v>12.4755334854126</v>
       </c>
       <c r="H371" t="n">
         <v>12596</v>
@@ -11186,7 +11186,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>11.9641599655151</v>
+        <v>11.9641609191895</v>
       </c>
       <c r="H373" t="n">
         <v>95740</v>
@@ -11244,7 +11244,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>12.1474838256836</v>
+        <v>12.147481918335</v>
       </c>
       <c r="H375" t="n">
         <v>32852</v>
@@ -11302,7 +11302,7 @@
         <v>13.25</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H377" t="n">
         <v>54450</v>
@@ -11389,7 +11389,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>12.1571311950684</v>
+        <v>12.1571321487427</v>
       </c>
       <c r="H380" t="n">
         <v>38689</v>
@@ -11418,7 +11418,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580274581909</v>
+        <v>11.8580284118652</v>
       </c>
       <c r="H381" t="n">
         <v>64542</v>
@@ -11447,7 +11447,7 @@
         <v>12.25</v>
       </c>
       <c r="G382" t="n">
-        <v>11.8194332122803</v>
+        <v>11.8194341659546</v>
       </c>
       <c r="H382" t="n">
         <v>27743</v>
@@ -11505,7 +11505,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>11.6843547821045</v>
+        <v>11.6843538284302</v>
       </c>
       <c r="H384" t="n">
         <v>27524</v>
@@ -11563,7 +11563,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G386" t="n">
-        <v>11.6843547821045</v>
+        <v>11.6843538284302</v>
       </c>
       <c r="H386" t="n">
         <v>27537</v>
@@ -11592,7 +11592,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H387" t="n">
         <v>110158</v>
@@ -11650,7 +11650,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G389" t="n">
-        <v>11.8966217041016</v>
+        <v>11.8966207504272</v>
       </c>
       <c r="H389" t="n">
         <v>33102</v>
@@ -11679,7 +11679,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>11.9641599655151</v>
+        <v>11.9641609191895</v>
       </c>
       <c r="H390" t="n">
         <v>27020</v>
@@ -11708,7 +11708,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H391" t="n">
         <v>36167</v>
@@ -11795,7 +11795,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.9545135498047</v>
+        <v>11.9545125961304</v>
       </c>
       <c r="H394" t="n">
         <v>7832</v>
@@ -11824,7 +11824,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>12.1957263946533</v>
+        <v>12.195725440979</v>
       </c>
       <c r="H395" t="n">
         <v>18587</v>
@@ -11853,7 +11853,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>12.2439680099487</v>
+        <v>12.2439670562744</v>
       </c>
       <c r="H396" t="n">
         <v>21900</v>
@@ -11882,7 +11882,7 @@
         <v>13.25</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H397" t="n">
         <v>62135</v>
@@ -11998,7 +11998,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H401" t="n">
         <v>13252</v>
@@ -12027,7 +12027,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>12.6202592849731</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H402" t="n">
         <v>31655</v>
@@ -12085,7 +12085,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>12.6202592849731</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H404" t="n">
         <v>9320</v>
@@ -12201,7 +12201,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G408" t="n">
-        <v>12.8421773910522</v>
+        <v>12.8421764373779</v>
       </c>
       <c r="H408" t="n">
         <v>32363</v>
@@ -12230,7 +12230,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>12.8711223602295</v>
+        <v>12.8711214065552</v>
       </c>
       <c r="H409" t="n">
         <v>6479</v>
@@ -12259,7 +12259,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H410" t="n">
         <v>21714</v>
@@ -12288,7 +12288,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>13.0447959899902</v>
+        <v>13.0447950363159</v>
       </c>
       <c r="H411" t="n">
         <v>52341</v>
@@ -12317,7 +12317,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>13.1219844818115</v>
+        <v>13.1219835281372</v>
       </c>
       <c r="H412" t="n">
         <v>20167</v>
@@ -12346,7 +12346,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G413" t="n">
-        <v>12.9097166061401</v>
+        <v>12.9097156524658</v>
       </c>
       <c r="H413" t="n">
         <v>52102</v>
@@ -12462,7 +12462,7 @@
         <v>13.25</v>
       </c>
       <c r="G417" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H417" t="n">
         <v>19263</v>
@@ -12491,7 +12491,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>12.9193649291992</v>
+        <v>12.9193639755249</v>
       </c>
       <c r="H418" t="n">
         <v>10876</v>
@@ -12607,7 +12607,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G422" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H422" t="n">
         <v>22215</v>
@@ -12665,7 +12665,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>12.929012298584</v>
+        <v>12.9290132522583</v>
       </c>
       <c r="H424" t="n">
         <v>8468</v>
@@ -12723,7 +12723,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5334243774414</v>
+        <v>12.5334234237671</v>
       </c>
       <c r="H426" t="n">
         <v>25449</v>
@@ -12781,7 +12781,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>12.9483098983765</v>
+        <v>12.9483108520508</v>
       </c>
       <c r="H428" t="n">
         <v>13836</v>
@@ -12810,7 +12810,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.8325281143188</v>
+        <v>12.8325290679932</v>
       </c>
       <c r="H429" t="n">
         <v>23103</v>
@@ -12839,7 +12839,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>13.0351467132568</v>
+        <v>13.0351476669312</v>
       </c>
       <c r="H430" t="n">
         <v>30798</v>
@@ -13042,7 +13042,7 @@
         <v>13.25</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7842845916748</v>
+        <v>12.7842855453491</v>
       </c>
       <c r="H437" t="n">
         <v>115869</v>
@@ -13245,7 +13245,7 @@
         <v>13</v>
       </c>
       <c r="G444" t="n">
-        <v>12.5430717468262</v>
+        <v>12.5430727005005</v>
       </c>
       <c r="H444" t="n">
         <v>22029</v>
@@ -13274,7 +13274,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H445" t="n">
         <v>16060</v>
@@ -13303,7 +13303,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G446" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H446" t="n">
         <v>35222</v>
@@ -13332,7 +13332,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>12.6202592849731</v>
+        <v>12.6202611923218</v>
       </c>
       <c r="H447" t="n">
         <v>14428</v>
@@ -13361,7 +13361,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>12.485179901123</v>
+        <v>12.4851808547974</v>
       </c>
       <c r="H448" t="n">
         <v>23317</v>
@@ -13419,7 +13419,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G450" t="n">
-        <v>12.6781530380249</v>
+        <v>12.6781511306763</v>
       </c>
       <c r="H450" t="n">
         <v>8729</v>
@@ -13448,7 +13448,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>12.4948301315308</v>
+        <v>12.4948291778564</v>
       </c>
       <c r="H451" t="n">
         <v>58859</v>
@@ -13477,7 +13477,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3693990707397</v>
+        <v>12.3694000244141</v>
       </c>
       <c r="H452" t="n">
         <v>28539</v>
@@ -13564,7 +13564,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>11.8483781814575</v>
+        <v>11.8483791351318</v>
       </c>
       <c r="H455" t="n">
         <v>45659</v>
@@ -13593,7 +13593,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>11.9931077957153</v>
+        <v>11.993106842041</v>
       </c>
       <c r="H456" t="n">
         <v>40685</v>
@@ -13622,7 +13622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H457" t="n">
         <v>24461</v>
@@ -13738,7 +13738,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G461" t="n">
-        <v>12.5044784545898</v>
+        <v>12.5044775009155</v>
       </c>
       <c r="H461" t="n">
         <v>38181</v>
@@ -13825,7 +13825,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9834585189819</v>
+        <v>11.9834594726562</v>
       </c>
       <c r="H464" t="n">
         <v>21813</v>
@@ -13883,7 +13883,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H466" t="n">
         <v>20941</v>
@@ -13941,7 +13941,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G468" t="n">
-        <v>11.9738101959229</v>
+        <v>11.9738092422485</v>
       </c>
       <c r="H468" t="n">
         <v>13736</v>
@@ -14086,7 +14086,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>12.1088895797729</v>
+        <v>12.1088886260986</v>
       </c>
       <c r="H473" t="n">
         <v>20258</v>
@@ -14173,7 +14173,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>11.829083442688</v>
+        <v>11.8290815353394</v>
       </c>
       <c r="H476" t="n">
         <v>75300</v>
@@ -14202,7 +14202,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>11.6747074127197</v>
+        <v>11.6747064590454</v>
       </c>
       <c r="H477" t="n">
         <v>345190</v>
@@ -14231,7 +14231,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G478" t="n">
-        <v>10.150239944458</v>
+        <v>10.1502408981323</v>
       </c>
       <c r="H478" t="n">
         <v>249899</v>
@@ -14260,7 +14260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G479" t="n">
-        <v>9.45554733276367</v>
+        <v>9.45554637908936</v>
       </c>
       <c r="H479" t="n">
         <v>447071</v>
@@ -14318,7 +14318,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G481" t="n">
-        <v>9.68711090087891</v>
+        <v>9.68711185455322</v>
       </c>
       <c r="H481" t="n">
         <v>127849</v>
@@ -14347,7 +14347,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G482" t="n">
-        <v>9.85113525390625</v>
+        <v>9.85113620758057</v>
       </c>
       <c r="H482" t="n">
         <v>95444</v>
@@ -14376,7 +14376,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0923480987549</v>
+        <v>10.0923490524292</v>
       </c>
       <c r="H483" t="n">
         <v>75251</v>
@@ -14405,7 +14405,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>10.3625078201294</v>
+        <v>10.3625068664551</v>
       </c>
       <c r="H484" t="n">
         <v>99264</v>
@@ -14434,7 +14434,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G485" t="n">
-        <v>10.4107503890991</v>
+        <v>10.4107494354248</v>
       </c>
       <c r="H485" t="n">
         <v>165118</v>
@@ -14521,7 +14521,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>11.0764961242676</v>
+        <v>11.0764970779419</v>
       </c>
       <c r="H488" t="n">
         <v>85880</v>
@@ -14608,7 +14608,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G491" t="n">
-        <v>11.2791166305542</v>
+        <v>11.2791156768799</v>
       </c>
       <c r="H491" t="n">
         <v>116323</v>
@@ -14666,7 +14666,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G493" t="n">
-        <v>10.8256378173828</v>
+        <v>10.8256359100342</v>
       </c>
       <c r="H493" t="n">
         <v>48038</v>
@@ -14782,7 +14782,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G497" t="n">
-        <v>10.7388000488281</v>
+        <v>10.7387990951538</v>
       </c>
       <c r="H497" t="n">
         <v>62706</v>
@@ -14811,7 +14811,7 @@
         <v>11.25</v>
       </c>
       <c r="G498" t="n">
-        <v>10.8545808792114</v>
+        <v>10.8545818328857</v>
       </c>
       <c r="H498" t="n">
         <v>41656</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>10.7078981399536</v>
+        <v>10.7078971862793</v>
       </c>
       <c r="H500" t="n">
         <v>97230</v>
@@ -14898,7 +14898,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G501" t="n">
-        <v>10.4732036590576</v>
+        <v>10.4732046127319</v>
       </c>
       <c r="H501" t="n">
         <v>197020</v>
@@ -14927,7 +14927,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G502" t="n">
-        <v>10.3851938247681</v>
+        <v>10.3851947784424</v>
       </c>
       <c r="H502" t="n">
         <v>89414</v>
@@ -14956,7 +14956,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>10.2189521789551</v>
+        <v>10.2189531326294</v>
       </c>
       <c r="H503" t="n">
         <v>87325</v>
@@ -14985,7 +14985,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>10.5612144470215</v>
+        <v>10.5612154006958</v>
       </c>
       <c r="H504" t="n">
         <v>62409</v>
@@ -15043,7 +15043,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4536466598511</v>
+        <v>10.4536457061768</v>
       </c>
       <c r="H506" t="n">
         <v>53759</v>
@@ -15072,7 +15072,7 @@
         <v>10.75</v>
       </c>
       <c r="G507" t="n">
-        <v>10.5123195648193</v>
+        <v>10.5123205184937</v>
       </c>
       <c r="H507" t="n">
         <v>171168</v>
@@ -15130,7 +15130,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G509" t="n">
-        <v>10.4047527313232</v>
+        <v>10.4047517776489</v>
       </c>
       <c r="H509" t="n">
         <v>85761</v>
@@ -15159,7 +15159,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H510" t="n">
         <v>74515</v>
@@ -15188,7 +15188,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G511" t="n">
-        <v>10.5807723999023</v>
+        <v>10.580771446228</v>
       </c>
       <c r="H511" t="n">
         <v>29173</v>
@@ -15246,7 +15246,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H513" t="n">
         <v>68123</v>
@@ -15304,7 +15304,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G515" t="n">
-        <v>10.9719295501709</v>
+        <v>10.9719285964966</v>
       </c>
       <c r="H515" t="n">
         <v>114765</v>
@@ -15362,7 +15362,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G517" t="n">
-        <v>11.0110454559326</v>
+        <v>11.0110445022583</v>
       </c>
       <c r="H517" t="n">
         <v>116880</v>
@@ -15681,7 +15681,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G528" t="n">
-        <v>10.6785621643066</v>
+        <v>10.6785612106323</v>
       </c>
       <c r="H528" t="n">
         <v>31481</v>
@@ -15710,7 +15710,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G529" t="n">
-        <v>10.6198883056641</v>
+        <v>10.6198873519897</v>
       </c>
       <c r="H529" t="n">
         <v>46104</v>
@@ -15739,7 +15739,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G530" t="n">
-        <v>10.9914855957031</v>
+        <v>10.9914865493774</v>
       </c>
       <c r="H530" t="n">
         <v>50487</v>
@@ -15797,7 +15797,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G532" t="n">
-        <v>10.8154668807983</v>
+        <v>10.815465927124</v>
       </c>
       <c r="H532" t="n">
         <v>61309</v>
@@ -15855,7 +15855,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>10.4634265899658</v>
+        <v>10.4634256362915</v>
       </c>
       <c r="H534" t="n">
         <v>20572</v>
@@ -15884,7 +15884,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G535" t="n">
-        <v>10.3069620132446</v>
+        <v>10.3069629669189</v>
       </c>
       <c r="H535" t="n">
         <v>59740</v>
@@ -15942,7 +15942,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G537" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H537" t="n">
         <v>66947</v>
@@ -16087,7 +16087,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>9.17261028289795</v>
+        <v>9.17261123657227</v>
       </c>
       <c r="H542" t="n">
         <v>15487</v>
@@ -16145,7 +16145,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>9.64199733734131</v>
+        <v>9.64199829101562</v>
       </c>
       <c r="H544" t="n">
         <v>45893</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H546" t="n">
         <v>15589</v>
@@ -16232,7 +16232,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>9.50509262084961</v>
+        <v>9.50509357452393</v>
       </c>
       <c r="H547" t="n">
         <v>11946</v>
@@ -16290,7 +16290,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H549" t="n">
         <v>23576</v>
@@ -16348,7 +16348,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G551" t="n">
-        <v>9.20194816589355</v>
+        <v>9.20194721221924</v>
       </c>
       <c r="H551" t="n">
         <v>15436</v>
@@ -16406,7 +16406,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H553" t="n">
         <v>22573</v>
@@ -16464,7 +16464,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G555" t="n">
-        <v>8.65432929992676</v>
+        <v>8.65432834625244</v>
       </c>
       <c r="H555" t="n">
         <v>68485</v>
@@ -16522,7 +16522,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.8499059677124</v>
+        <v>8.84990692138672</v>
       </c>
       <c r="H557" t="n">
         <v>76043</v>
@@ -16580,7 +16580,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H559" t="n">
         <v>111011</v>
@@ -16638,7 +16638,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H561" t="n">
         <v>47843</v>
@@ -16667,7 +16667,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H562" t="n">
         <v>31267</v>
@@ -16696,7 +16696,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H563" t="n">
         <v>28072</v>
@@ -16783,7 +16783,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G566" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H566" t="n">
         <v>45222</v>
@@ -16812,7 +16812,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H567" t="n">
         <v>124458</v>
@@ -16841,7 +16841,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G568" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H568" t="n">
         <v>102747</v>
@@ -16870,7 +16870,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G569" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H569" t="n">
         <v>170656</v>
@@ -16986,7 +16986,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H573" t="n">
         <v>121005</v>
@@ -17015,7 +17015,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H574" t="n">
         <v>114848</v>
@@ -17044,7 +17044,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>9.36818790435791</v>
+        <v>9.36818885803223</v>
       </c>
       <c r="H575" t="n">
         <v>94106</v>
@@ -17073,7 +17073,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G576" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H576" t="n">
         <v>88350</v>
@@ -17102,7 +17102,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G577" t="n">
-        <v>9.20194816589355</v>
+        <v>9.20194721221924</v>
       </c>
       <c r="H577" t="n">
         <v>140529</v>
@@ -17247,7 +17247,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>9.1237154006958</v>
+        <v>9.12371635437012</v>
       </c>
       <c r="H582" t="n">
         <v>83347</v>
@@ -17276,7 +17276,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>8.95747470855713</v>
+        <v>8.95747375488281</v>
       </c>
       <c r="H583" t="n">
         <v>20537</v>
@@ -17305,7 +17305,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H584" t="n">
         <v>44575</v>
@@ -17363,7 +17363,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G586" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H586" t="n">
         <v>19894</v>
@@ -17392,7 +17392,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G587" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H587" t="n">
         <v>46974</v>
@@ -17479,7 +17479,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G590" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H590" t="n">
         <v>85332</v>
@@ -17653,7 +17653,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G596" t="n">
-        <v>8.9868106842041</v>
+        <v>8.98681163787842</v>
       </c>
       <c r="H596" t="n">
         <v>110779</v>
@@ -17682,7 +17682,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H597" t="n">
         <v>168521</v>
@@ -17740,7 +17740,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G599" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H599" t="n">
         <v>76971</v>
@@ -17769,7 +17769,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H600" t="n">
         <v>116918</v>
@@ -17798,7 +17798,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G601" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H601" t="n">
         <v>24832</v>
@@ -17856,7 +17856,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G603" t="n">
-        <v>9.95492267608643</v>
+        <v>9.95492362976074</v>
       </c>
       <c r="H603" t="n">
         <v>63044</v>
@@ -17885,7 +17885,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G604" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H604" t="n">
         <v>44561</v>
@@ -17943,7 +17943,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H606" t="n">
         <v>38965</v>
@@ -18001,7 +18001,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H608" t="n">
         <v>28857</v>
@@ -18030,7 +18030,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81801795959473</v>
+        <v>9.81801891326904</v>
       </c>
       <c r="H609" t="n">
         <v>8881</v>
@@ -18059,7 +18059,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H610" t="n">
         <v>26954</v>
@@ -18088,7 +18088,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H611" t="n">
         <v>15971</v>
@@ -18117,7 +18117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G612" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H612" t="n">
         <v>14746</v>
@@ -18146,7 +18146,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G613" t="n">
-        <v>9.34863090515137</v>
+        <v>9.34862995147705</v>
       </c>
       <c r="H613" t="n">
         <v>29288</v>
@@ -18175,7 +18175,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H614" t="n">
         <v>134678</v>
@@ -18233,7 +18233,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H616" t="n">
         <v>118933</v>
@@ -18378,7 +18378,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G621" t="n">
-        <v>9.71045112609863</v>
+        <v>9.71045017242432</v>
       </c>
       <c r="H621" t="n">
         <v>192357</v>
@@ -18494,7 +18494,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H625" t="n">
         <v>69374</v>
@@ -18552,7 +18552,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G627" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H627" t="n">
         <v>11623</v>
@@ -18610,7 +18610,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>9.57354545593262</v>
+        <v>9.5735445022583</v>
       </c>
       <c r="H629" t="n">
         <v>59629</v>
@@ -18668,7 +18668,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H631" t="n">
         <v>25208</v>
@@ -18697,7 +18697,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H632" t="n">
         <v>43105</v>
@@ -18842,7 +18842,7 @@
         <v>9.25</v>
       </c>
       <c r="G637" t="n">
-        <v>9.04548358917236</v>
+        <v>9.04548454284668</v>
       </c>
       <c r="H637" t="n">
         <v>24740</v>
@@ -19016,7 +19016,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>9.28017902374268</v>
+        <v>9.28017807006836</v>
       </c>
       <c r="H643" t="n">
         <v>15942</v>
@@ -19045,7 +19045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>9.43664073944092</v>
+        <v>9.4366397857666</v>
       </c>
       <c r="H644" t="n">
         <v>5673</v>
@@ -19103,7 +19103,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>9.62244033813477</v>
+        <v>9.62243938446045</v>
       </c>
       <c r="H646" t="n">
         <v>21998</v>
@@ -19132,7 +19132,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G647" t="n">
-        <v>9.64199733734131</v>
+        <v>9.64199829101562</v>
       </c>
       <c r="H647" t="n">
         <v>12149</v>
@@ -19190,7 +19190,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G649" t="n">
-        <v>9.52465057373047</v>
+        <v>9.52464962005615</v>
       </c>
       <c r="H649" t="n">
         <v>25021</v>
@@ -19219,7 +19219,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G650" t="n">
-        <v>9.56376552581787</v>
+        <v>9.56376647949219</v>
       </c>
       <c r="H650" t="n">
         <v>28011</v>
@@ -19306,7 +19306,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G653" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H653" t="n">
         <v>40921</v>
@@ -19364,7 +19364,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G655" t="n">
-        <v>9.16283226013184</v>
+        <v>9.16283130645752</v>
       </c>
       <c r="H655" t="n">
         <v>14617</v>
@@ -19451,7 +19451,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>9.09437847137451</v>
+        <v>9.09437942504883</v>
       </c>
       <c r="H658" t="n">
         <v>4851</v>
@@ -19625,7 +19625,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G664" t="n">
-        <v>9.3584098815918</v>
+        <v>9.35840892791748</v>
       </c>
       <c r="H664" t="n">
         <v>8674</v>
@@ -19654,7 +19654,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G665" t="n">
-        <v>9.3975248336792</v>
+        <v>9.39752388000488</v>
       </c>
       <c r="H665" t="n">
         <v>4386</v>
@@ -19741,7 +19741,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G668" t="n">
-        <v>9.42686176300049</v>
+        <v>9.4268627166748</v>
       </c>
       <c r="H668" t="n">
         <v>15830</v>
@@ -19828,7 +19828,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G671" t="n">
-        <v>9.3584098815918</v>
+        <v>9.35840892791748</v>
       </c>
       <c r="H671" t="n">
         <v>9974</v>
@@ -19857,7 +19857,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>9.65177631378174</v>
+        <v>9.65177726745605</v>
       </c>
       <c r="H672" t="n">
         <v>48863</v>
@@ -19886,7 +19886,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G673" t="n">
-        <v>9.76912307739258</v>
+        <v>9.76912403106689</v>
       </c>
       <c r="H673" t="n">
         <v>49111</v>
@@ -19915,7 +19915,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>9.79846096038818</v>
+        <v>9.79846000671387</v>
       </c>
       <c r="H674" t="n">
         <v>18840</v>
@@ -19973,7 +19973,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G676" t="n">
-        <v>9.75934314727783</v>
+        <v>9.75934410095215</v>
       </c>
       <c r="H676" t="n">
         <v>9923</v>
@@ -20002,7 +20002,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H677" t="n">
         <v>7000</v>
@@ -20089,7 +20089,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G680" t="n">
-        <v>9.60288143157959</v>
+        <v>9.60288238525391</v>
       </c>
       <c r="H680" t="n">
         <v>7811</v>
@@ -20118,7 +20118,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>9.59310340881348</v>
+        <v>9.59310436248779</v>
       </c>
       <c r="H681" t="n">
         <v>7805</v>
@@ -20147,7 +20147,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G682" t="n">
-        <v>9.74956703186035</v>
+        <v>9.74956512451172</v>
       </c>
       <c r="H682" t="n">
         <v>32449</v>
@@ -20234,7 +20234,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G685" t="n">
-        <v>9.72022819519043</v>
+        <v>9.72022914886475</v>
       </c>
       <c r="H685" t="n">
         <v>86835</v>
@@ -20263,7 +20263,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>9.76912307739258</v>
+        <v>9.76912403106689</v>
       </c>
       <c r="H686" t="n">
         <v>19172</v>
@@ -20321,7 +20321,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G688" t="n">
-        <v>9.67133522033691</v>
+        <v>9.6713342666626</v>
       </c>
       <c r="H688" t="n">
         <v>38879</v>
@@ -20437,7 +20437,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73000717163086</v>
+        <v>9.73000812530518</v>
       </c>
       <c r="H692" t="n">
         <v>28508</v>
@@ -20524,7 +20524,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.85713386535645</v>
+        <v>9.85713291168213</v>
       </c>
       <c r="H695" t="n">
         <v>15119</v>
@@ -20611,7 +20611,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G698" t="n">
-        <v>9.68111228942871</v>
+        <v>9.68111324310303</v>
       </c>
       <c r="H698" t="n">
         <v>21356</v>
@@ -20640,7 +20640,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G699" t="n">
-        <v>9.66155624389648</v>
+        <v>9.66155529022217</v>
       </c>
       <c r="H699" t="n">
         <v>21197</v>
@@ -20669,7 +20669,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G700" t="n">
-        <v>9.58332538604736</v>
+        <v>9.58332443237305</v>
       </c>
       <c r="H700" t="n">
         <v>27899</v>
@@ -20698,7 +20698,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G701" t="n">
-        <v>9.28017902374268</v>
+        <v>9.28017807006836</v>
       </c>
       <c r="H701" t="n">
         <v>43482</v>
@@ -20756,7 +20756,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>9.21172523498535</v>
+        <v>9.21172618865967</v>
       </c>
       <c r="H703" t="n">
         <v>10949</v>
@@ -20843,7 +20843,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G706" t="n">
-        <v>9.11393737792969</v>
+        <v>9.11393642425537</v>
       </c>
       <c r="H706" t="n">
         <v>17733</v>
@@ -20901,7 +20901,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>8.96725273132324</v>
+        <v>8.96725368499756</v>
       </c>
       <c r="H708" t="n">
         <v>75982</v>
@@ -20959,7 +20959,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G710" t="n">
-        <v>8.28273105621338</v>
+        <v>8.28273010253906</v>
       </c>
       <c r="H710" t="n">
         <v>140241</v>
@@ -21017,7 +21017,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.15560531616211</v>
+        <v>8.15560436248779</v>
       </c>
       <c r="H712" t="n">
         <v>38461</v>
@@ -21075,7 +21075,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G714" t="n">
-        <v>8.70322322845459</v>
+        <v>8.70322227478027</v>
       </c>
       <c r="H714" t="n">
         <v>94133</v>
@@ -21162,7 +21162,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G717" t="n">
-        <v>8.38051795959473</v>
+        <v>8.38051891326904</v>
       </c>
       <c r="H717" t="n">
         <v>28141</v>
@@ -21191,7 +21191,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>8.12626838684082</v>
+        <v>8.12626934051514</v>
       </c>
       <c r="H718" t="n">
         <v>75942</v>
@@ -21249,7 +21249,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>8.51742362976074</v>
+        <v>8.51742458343506</v>
       </c>
       <c r="H720" t="n">
         <v>40610</v>
@@ -21278,7 +21278,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G721" t="n">
-        <v>8.54675960540771</v>
+        <v>8.54676055908203</v>
       </c>
       <c r="H721" t="n">
         <v>58974</v>
@@ -21336,7 +21336,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>8.63477039337158</v>
+        <v>8.6347713470459</v>
       </c>
       <c r="H723" t="n">
         <v>20170</v>
@@ -21452,7 +21452,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G727" t="n">
-        <v>8.77167510986328</v>
+        <v>8.7716760635376</v>
       </c>
       <c r="H727" t="n">
         <v>143037</v>
@@ -21510,7 +21510,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G729" t="n">
-        <v>8.86946487426758</v>
+        <v>8.86946392059326</v>
       </c>
       <c r="H729" t="n">
         <v>24316</v>
@@ -21626,7 +21626,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G733" t="n">
-        <v>8.41963386535645</v>
+        <v>8.41963481903076</v>
       </c>
       <c r="H733" t="n">
         <v>27723</v>
@@ -21655,7 +21655,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G734" t="n">
-        <v>8.04803657531738</v>
+        <v>8.04803562164307</v>
       </c>
       <c r="H734" t="n">
         <v>59734</v>
@@ -21858,7 +21858,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>7.30483961105347</v>
+        <v>7.30484008789062</v>
       </c>
       <c r="H741" t="n">
         <v>13402</v>
@@ -21916,7 +21916,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.20705127716064</v>
+        <v>7.20705080032349</v>
       </c>
       <c r="H743" t="n">
         <v>14937</v>
@@ -21974,7 +21974,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G745" t="n">
-        <v>6.83545255661011</v>
+        <v>6.83545207977295</v>
       </c>
       <c r="H745" t="n">
         <v>110100</v>
@@ -22003,7 +22003,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G746" t="n">
-        <v>6.46385478973389</v>
+        <v>6.46385431289673</v>
       </c>
       <c r="H746" t="n">
         <v>68949</v>
@@ -22032,7 +22032,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>5.67176342010498</v>
+        <v>5.67176389694214</v>
       </c>
       <c r="H747" t="n">
         <v>105173</v>
@@ -22148,7 +22148,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.71343088150024</v>
+        <v>4.7134313583374</v>
       </c>
       <c r="H751" t="n">
         <v>210848</v>
@@ -22177,7 +22177,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.30760669708252</v>
+        <v>4.30760622024536</v>
       </c>
       <c r="H752" t="n">
         <v>95208</v>
@@ -22206,7 +22206,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G753" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H753" t="n">
         <v>158037</v>
@@ -22235,7 +22235,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>4.67431545257568</v>
+        <v>4.67431497573853</v>
       </c>
       <c r="H754" t="n">
         <v>139728</v>
@@ -22293,7 +22293,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>4.31738519668579</v>
+        <v>4.31738567352295</v>
       </c>
       <c r="H756" t="n">
         <v>103537</v>
@@ -22351,7 +22351,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>3.90178203582764</v>
+        <v>3.90178227424622</v>
       </c>
       <c r="H758" t="n">
         <v>114123</v>
@@ -22409,7 +22409,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>4.00935029983521</v>
+        <v>4.00934982299805</v>
       </c>
       <c r="H760" t="n">
         <v>97203</v>
@@ -22438,7 +22438,7 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3.91156101226807</v>
+        <v>3.91156077384949</v>
       </c>
       <c r="H761" t="n">
         <v>208056</v>
@@ -22467,7 +22467,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>3.9800136089325</v>
+        <v>3.98001313209534</v>
       </c>
       <c r="H762" t="n">
         <v>31531</v>
@@ -22496,7 +22496,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G763" t="n">
-        <v>4.12669658660889</v>
+        <v>4.12669706344604</v>
       </c>
       <c r="H763" t="n">
         <v>41597</v>
@@ -22525,7 +22525,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10224962234497</v>
+        <v>4.10225009918213</v>
       </c>
       <c r="H764" t="n">
         <v>34127</v>
@@ -22554,7 +22554,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>4.11691808700562</v>
+        <v>4.11691761016846</v>
       </c>
       <c r="H765" t="n">
         <v>28600</v>
@@ -22583,7 +22583,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>4.35161161422729</v>
+        <v>4.35161113739014</v>
       </c>
       <c r="H766" t="n">
         <v>92230</v>
@@ -22612,7 +22612,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>4.58630514144897</v>
+        <v>4.58630561828613</v>
       </c>
       <c r="H767" t="n">
         <v>113983</v>
@@ -22641,7 +22641,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G768" t="n">
-        <v>4.83566761016846</v>
+        <v>4.8356671333313</v>
       </c>
       <c r="H768" t="n">
         <v>165631</v>
@@ -22699,7 +22699,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>5.07525014877319</v>
+        <v>5.07525062561035</v>
       </c>
       <c r="H770" t="n">
         <v>177286</v>
@@ -22786,7 +22786,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.84055614471436</v>
+        <v>4.84055662155151</v>
       </c>
       <c r="H773" t="n">
         <v>56598</v>
@@ -22960,7 +22960,7 @@
         <v>5.5</v>
       </c>
       <c r="G779" t="n">
-        <v>5.37839651107788</v>
+        <v>5.37839603424072</v>
       </c>
       <c r="H779" t="n">
         <v>69616</v>
@@ -23047,7 +23047,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G782" t="n">
-        <v>5.53485822677612</v>
+        <v>5.53485870361328</v>
       </c>
       <c r="H782" t="n">
         <v>74521</v>
@@ -23076,7 +23076,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       <c r="H783" t="n">
         <v>31901</v>
@@ -23105,7 +23105,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G784" t="n">
-        <v>5.52508020401001</v>
+        <v>5.52507972717285</v>
       </c>
       